--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297E5C49-216F-472A-B417-DB974D27B229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDCE40C-980B-4328-813E-783FDCB4333D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="577">
   <si>
     <t>Id</t>
   </si>
@@ -1506,18 +1506,6 @@
   </si>
   <si>
     <t>被动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅自己</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定间隔</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -2087,32 +2075,16 @@
     <t>Skill_3_Begin</t>
   </si>
   <si>
-    <t>m3攻速提升buff,m32攻速提升buff</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t>m32攻击,m32结束,m32自身结束</t>
+  </si>
+  <si>
+    <t>m32追加,m32启动</t>
+  </si>
+  <si>
+    <t>固定间隔</t>
   </si>
   <si>
     <t>自己以外</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>#重构体消除自身buff</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>被治疗</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>m32重构体</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>m32追加,m32启动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>m32攻击,m32结束,m32自身结束,m32重构体</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2667,10 +2639,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -2839,7 +2811,7 @@
         <v>39</v>
       </c>
       <c r="AZ1" s="7" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BA1" t="s">
         <v>40</v>
@@ -3009,7 +2981,7 @@
         <v>93</v>
       </c>
       <c r="AZ2" s="7" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="BA2" t="s">
         <v>94</v>
@@ -3051,7 +3023,7 @@
         <v>106</v>
       </c>
       <c r="BN2" s="7" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BO2" t="s">
         <v>107</v>
@@ -3277,16 +3249,16 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B5" t="s">
         <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F5" t="str">
         <f>"char_"&amp;E5&amp;"_"&amp;D5</f>
@@ -3332,16 +3304,16 @@
         <v>1</v>
       </c>
       <c r="AG5" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AH5" t="s">
         <v>122</v>
       </c>
       <c r="AI5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AJ5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="AM5">
         <v>1</v>
@@ -3356,19 +3328,19 @@
         <v>0.25</v>
       </c>
       <c r="BB5" t="s">
+        <v>453</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>454</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>455</v>
+      </c>
+      <c r="BE5" t="s">
         <v>456</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BF5" t="s">
         <v>457</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>458</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>459</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>460</v>
       </c>
       <c r="BG5" t="s">
         <v>128</v>
@@ -3377,10 +3349,10 @@
         <v>6</v>
       </c>
       <c r="BI5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="BJ5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="BM5" t="s">
         <v>123</v>
@@ -3400,19 +3372,19 @@
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B6" t="s">
         <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3457,13 +3429,13 @@
         <v>-1</v>
       </c>
       <c r="AG6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AH6" t="s">
         <v>122</v>
       </c>
       <c r="AI6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -3478,16 +3450,16 @@
         <v>0</v>
       </c>
       <c r="AV6" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AW6">
         <v>0.25</v>
       </c>
       <c r="BB6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="BD6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="BE6" t="str">
         <f>"half_"&amp;D6</f>
@@ -3507,7 +3479,7 @@
         <v>127</v>
       </c>
       <c r="BJ6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="BM6" t="s">
         <v>123</v>
@@ -3521,16 +3493,16 @@
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B7" t="s">
         <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F7" t="str">
         <f>"char_"&amp;E7&amp;"_"&amp;D7</f>
@@ -3582,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="AG7" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="AH7" t="s">
         <v>122</v>
       </c>
       <c r="AI7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -3603,19 +3575,19 @@
         <v>0.25</v>
       </c>
       <c r="BB7" t="s">
+        <v>453</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>454</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>455</v>
+      </c>
+      <c r="BE7" t="s">
         <v>456</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BF7" t="s">
         <v>457</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>458</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>459</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>460</v>
       </c>
       <c r="BG7" t="s">
         <v>128</v>
@@ -3624,10 +3596,10 @@
         <v>6</v>
       </c>
       <c r="BI7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="BJ7" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="BM7" t="s">
         <v>124</v>
@@ -3636,7 +3608,7 @@
         <v>124</v>
       </c>
       <c r="BP7" s="17" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="BQ7" t="s">
         <v>125</v>
@@ -6424,7 +6396,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH820"/>
+  <dimension ref="A1:DH819"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6523,7 +6495,7 @@
         <v>133</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I1" t="s">
         <v>134</v>
@@ -6655,7 +6627,7 @@
         <v>175</v>
       </c>
       <c r="AZ1" s="7" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BA1" t="s">
         <v>176</v>
@@ -6709,10 +6681,10 @@
         <v>191</v>
       </c>
       <c r="BS1" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="BT1" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="BT1" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="BU1" s="4" t="s">
         <v>192</v>
@@ -6760,7 +6732,7 @@
         <v>206</v>
       </c>
       <c r="CJ1" s="7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="CK1" t="s">
         <v>207</v>
@@ -6852,7 +6824,7 @@
         <v>51</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I2" t="s">
         <v>230</v>
@@ -7041,10 +7013,10 @@
         <v>290</v>
       </c>
       <c r="BS2" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="BT2" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="BT2" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="BU2" s="4" t="s">
         <v>291</v>
@@ -7092,7 +7064,7 @@
         <v>305</v>
       </c>
       <c r="CJ2" s="7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="CK2" t="s">
         <v>306</v>
@@ -7184,7 +7156,7 @@
         <v>114</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I3" t="s">
         <v>112</v>
@@ -7196,7 +7168,7 @@
         <v>330</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>114</v>
@@ -7373,7 +7345,7 @@
         <v>113</v>
       </c>
       <c r="BS3" s="7" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="BT3" s="4" t="s">
         <v>113</v>
@@ -7424,7 +7396,7 @@
         <v>342</v>
       </c>
       <c r="CJ3" s="7" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="CK3" t="s">
         <v>116</v>
@@ -7507,13 +7479,13 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C6" t="s">
         <v>346</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>402</v>
@@ -7523,34 +7495,34 @@
         <v>1</v>
       </c>
       <c r="AO6" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AR6" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="CS6" s="7" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C7" t="s">
         <v>346</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="P7"/>
       <c r="AC7">
         <v>1</v>
       </c>
       <c r="AO7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AR7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AW7">
         <v>1</v>
@@ -7565,16 +7537,16 @@
         <v>55</v>
       </c>
       <c r="CE7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="CF7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="CG7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="CL7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="CM7">
         <v>22</v>
@@ -7583,21 +7555,21 @@
         <v>10</v>
       </c>
       <c r="CW7" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C8" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>347</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AC8">
         <v>1</v>
@@ -7613,7 +7585,7 @@
       </c>
       <c r="CJ8" s="3"/>
       <c r="CS8" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="DB8">
         <v>1</v>
@@ -7627,7 +7599,7 @@
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C9" t="s">
         <v>346</v>
@@ -7639,7 +7611,7 @@
         <v>347</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="M9"/>
       <c r="N9"/>
@@ -7666,7 +7638,7 @@
         <v>1</v>
       </c>
       <c r="BM9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="BS9" s="11"/>
       <c r="BT9" s="11"/>
@@ -7676,7 +7648,7 @@
       <c r="BX9" s="11"/>
       <c r="BY9"/>
       <c r="CL9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="CM9">
         <v>8</v>
@@ -7690,7 +7662,7 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C10" t="s">
         <v>346</v>
@@ -7716,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="AR10" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="BB10">
         <v>99</v>
@@ -7732,7 +7704,7 @@
       <c r="BX10" s="11"/>
       <c r="BY10"/>
       <c r="CL10" s="12" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="CM10">
         <v>0.2</v>
@@ -7746,7 +7718,7 @@
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C11" t="s">
         <v>346</v>
@@ -7755,7 +7727,7 @@
         <v>347</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AC11">
         <v>1</v>
@@ -7785,7 +7757,7 @@
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="CP11">
         <v>99999</v>
@@ -7793,7 +7765,7 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C12" t="s">
         <v>346</v>
@@ -7809,7 +7781,7 @@
       <c r="N12"/>
       <c r="O12" s="13"/>
       <c r="P12" s="14" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="Q12" s="13"/>
       <c r="R12" s="14"/>
@@ -7839,7 +7811,7 @@
       <c r="BY12" s="15"/>
       <c r="BZ12" s="15"/>
       <c r="CL12" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="CM12">
         <v>22</v>
@@ -7872,42 +7844,31 @@
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C14" t="s">
         <v>346</v>
       </c>
       <c r="D14" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E14" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F14" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="J14" t="s">
-        <v>428</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="L14" s="13"/>
+        <v>425</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>486</v>
+      </c>
       <c r="M14"/>
-      <c r="N14" s="13"/>
       <c r="O14"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="13"/>
       <c r="AC14">
         <v>1</v>
       </c>
@@ -7918,30 +7879,28 @@
         <v>1</v>
       </c>
       <c r="BM14" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="BN14" s="7" t="s">
-        <v>581</v>
+        <v>573</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>574</v>
       </c>
       <c r="BR14">
         <v>30</v>
       </c>
-      <c r="BT14" s="15">
+      <c r="BT14" s="4">
         <v>13</v>
       </c>
-      <c r="BU14" s="15">
+      <c r="BU14" s="4">
         <v>15</v>
       </c>
-      <c r="BV14" s="15">
-        <v>1</v>
-      </c>
-      <c r="BW14" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="BX14" s="15"/>
-      <c r="BY14" s="15"/>
-      <c r="CL14" s="14" t="s">
-        <v>491</v>
+      <c r="BV14" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW14" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="CL14" s="12" t="s">
+        <v>488</v>
       </c>
       <c r="CP14">
         <v>30</v>
@@ -7952,28 +7911,18 @@
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C15" t="s">
         <v>346</v>
       </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
+      <c r="J15" s="3"/>
       <c r="M15"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="14" t="s">
-        <v>484</v>
+      <c r="O15" s="12" t="s">
+        <v>481</v>
       </c>
       <c r="P15"/>
       <c r="Q15"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
       <c r="AC15">
         <v>1</v>
       </c>
@@ -7981,46 +7930,40 @@
         <v>1</v>
       </c>
       <c r="AO15" t="s">
+        <v>432</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>460</v>
+      </c>
+      <c r="AU15">
+        <v>1</v>
+      </c>
+      <c r="AW15">
+        <v>1</v>
+      </c>
+      <c r="AX15">
+        <v>1</v>
+      </c>
+      <c r="BB15">
+        <v>1</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>490</v>
+      </c>
+      <c r="BZ15" t="s">
+        <v>491</v>
+      </c>
+      <c r="CE15" t="s">
+        <v>434</v>
+      </c>
+      <c r="CF15" t="s">
         <v>435</v>
       </c>
-      <c r="AQ15" t="s">
-        <v>463</v>
-      </c>
-      <c r="AU15">
-        <v>1</v>
-      </c>
-      <c r="AW15">
-        <v>1</v>
-      </c>
-      <c r="AX15">
-        <v>1</v>
-      </c>
-      <c r="BB15">
-        <v>1</v>
-      </c>
-      <c r="BN15" t="s">
-        <v>493</v>
-      </c>
-      <c r="BT15" s="15"/>
-      <c r="BU15" s="15"/>
-      <c r="BV15" s="15"/>
-      <c r="BW15" s="15"/>
-      <c r="BX15" s="15"/>
-      <c r="BY15" s="15"/>
-      <c r="BZ15" t="s">
-        <v>494</v>
-      </c>
-      <c r="CE15" t="s">
-        <v>437</v>
-      </c>
-      <c r="CF15" t="s">
-        <v>438</v>
-      </c>
       <c r="CG15" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="CL15" s="7" t="s">
-        <v>576</v>
+        <v>492</v>
       </c>
       <c r="CM15">
         <v>22</v>
@@ -8032,12 +7975,12 @@
         <v>10</v>
       </c>
       <c r="CW15" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C16" t="s">
         <v>346</v>
@@ -8045,22 +7988,10 @@
       <c r="I16">
         <v>1</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L16" s="13"/>
       <c r="M16"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="13"/>
-      <c r="X16" s="13"/>
       <c r="AC16">
         <v>1</v>
       </c>
@@ -8068,16 +7999,16 @@
         <v>1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AO16" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AR16" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AV16" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AX16">
         <v>1</v>
@@ -8088,18 +8019,18 @@
       <c r="BB16">
         <v>1</v>
       </c>
-      <c r="BT16" s="15"/>
-      <c r="BU16" s="15"/>
-      <c r="BV16" s="15"/>
-      <c r="BW16" s="15"/>
-      <c r="BX16" s="15"/>
-      <c r="BY16" s="15"/>
       <c r="BZ16" s="16"/>
       <c r="CF16" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="CG16" t="s">
-        <v>426</v>
+        <v>423</v>
+      </c>
+      <c r="CL16" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="CP16">
+        <v>0.1</v>
       </c>
       <c r="DB16">
         <v>1</v>
@@ -8110,7 +8041,7 @@
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C17" t="s">
         <v>346</v>
@@ -8118,24 +8049,15 @@
       <c r="I17">
         <v>1</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L17" s="13"/>
       <c r="M17"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="14" t="s">
-        <v>484</v>
+      <c r="O17" s="12" t="s">
+        <v>481</v>
       </c>
       <c r="P17"/>
       <c r="Q17"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
       <c r="AC17">
         <v>1</v>
       </c>
@@ -8148,14 +8070,8 @@
       <c r="BB17">
         <v>1</v>
       </c>
-      <c r="BT17" s="15"/>
-      <c r="BU17" s="15"/>
-      <c r="BV17" s="15"/>
-      <c r="BW17" s="15"/>
-      <c r="BX17" s="15"/>
-      <c r="BY17" s="15"/>
       <c r="CL17" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="CM17">
         <v>22</v>
@@ -8169,7 +8085,7 @@
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>580</v>
+        <v>496</v>
       </c>
       <c r="C18" t="s">
         <v>346</v>
@@ -8177,32 +8093,20 @@
       <c r="I18">
         <v>1</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="L18" s="13"/>
       <c r="M18"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="14" t="s">
-        <v>484</v>
+      <c r="O18" s="12" t="s">
+        <v>481</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
       <c r="AC18">
         <v>1</v>
       </c>
       <c r="AJ18" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AR18" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="BB18">
         <v>1</v>
@@ -8210,14 +8114,8 @@
       <c r="BQ18">
         <v>0.1</v>
       </c>
-      <c r="BT18" s="15"/>
-      <c r="BU18" s="15"/>
-      <c r="BV18" s="15"/>
-      <c r="BW18" s="15"/>
-      <c r="BX18" s="15"/>
-      <c r="BY18" s="15"/>
-      <c r="CL18" s="14" t="s">
-        <v>499</v>
+      <c r="CL18" s="12" t="s">
+        <v>496</v>
       </c>
       <c r="CP18">
         <v>0.2</v>
@@ -8225,7 +8123,7 @@
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C19" t="s">
         <v>346</v>
@@ -8233,29 +8131,17 @@
       <c r="I19">
         <v>1</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L19" s="13"/>
       <c r="M19"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" t="s">
         <v>348</v>
       </c>
-      <c r="AW19" s="13"/>
+      <c r="AW19" s="3"/>
       <c r="BB19">
         <v>1</v>
       </c>
@@ -8265,17 +8151,17 @@
       <c r="BW19"/>
       <c r="BX19"/>
       <c r="BY19"/>
-      <c r="BZ19" s="13"/>
-      <c r="CA19" s="13"/>
-      <c r="CB19" s="13"/>
-      <c r="CC19" s="13"/>
-      <c r="CD19" s="13"/>
-      <c r="CF19" s="13"/>
-      <c r="CG19" s="13"/>
-      <c r="CH19" s="13"/>
-      <c r="CI19" s="13"/>
-      <c r="CL19" s="14" t="s">
-        <v>500</v>
+      <c r="BZ19" s="3"/>
+      <c r="CA19" s="3"/>
+      <c r="CB19" s="3"/>
+      <c r="CC19" s="3"/>
+      <c r="CD19" s="3"/>
+      <c r="CF19" s="3"/>
+      <c r="CG19" s="3"/>
+      <c r="CH19" s="3"/>
+      <c r="CI19" s="3"/>
+      <c r="CL19" s="12" t="s">
+        <v>497</v>
       </c>
       <c r="CP19">
         <v>40</v>
@@ -8289,7 +8175,7 @@
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C20" t="s">
         <v>346</v>
@@ -8297,24 +8183,13 @@
       <c r="I20">
         <v>1</v>
       </c>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
       <c r="M20"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="14" t="s">
-        <v>484</v>
-      </c>
-      <c r="P20" s="14" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
+      <c r="O20" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>497</v>
+      </c>
       <c r="AC20">
         <v>1</v>
       </c>
@@ -8324,19 +8199,13 @@
       <c r="BB20">
         <v>99</v>
       </c>
-      <c r="BT20" s="15"/>
-      <c r="BU20" s="15"/>
-      <c r="BV20" s="15"/>
-      <c r="BW20" s="15"/>
-      <c r="BX20" s="15"/>
-      <c r="BY20" s="15"/>
       <c r="CK20" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C21" t="s">
         <v>346</v>
@@ -8344,22 +8213,11 @@
       <c r="I21">
         <v>1</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L21" s="13"/>
       <c r="M21"/>
       <c r="N21"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13"/>
-      <c r="U21" s="13"/>
-      <c r="V21" s="13"/>
-      <c r="W21" s="13"/>
-      <c r="X21" s="13"/>
       <c r="AC21">
         <v>1</v>
       </c>
@@ -8373,19 +8231,14 @@
         <v>0.1</v>
       </c>
       <c r="BT21"/>
-      <c r="BU21" s="15"/>
-      <c r="BV21" s="15"/>
-      <c r="BW21" s="15"/>
-      <c r="BX21" s="15"/>
-      <c r="BY21" s="15"/>
       <c r="BZ21" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="CE21" t="s">
-        <v>437</v>
-      </c>
-      <c r="CG21" s="13"/>
-      <c r="CH21" s="13"/>
+        <v>434</v>
+      </c>
+      <c r="CG21" s="3"/>
+      <c r="CH21" s="3"/>
       <c r="DB21">
         <v>1</v>
       </c>
@@ -8398,7 +8251,7 @@
     </row>
     <row r="22" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C22" t="s">
         <v>346</v>
@@ -8406,24 +8259,14 @@
       <c r="I22">
         <v>1</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="K22" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>506</v>
+      <c r="L22" s="3" t="s">
+        <v>503</v>
       </c>
       <c r="M22"/>
       <c r="N22"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
-      <c r="U22" s="13"/>
-      <c r="V22" s="13"/>
-      <c r="W22" s="13"/>
-      <c r="X22" s="13"/>
       <c r="AC22">
         <v>1</v>
       </c>
@@ -8437,18 +8280,13 @@
         <v>0.2</v>
       </c>
       <c r="BT22"/>
-      <c r="BU22" s="15"/>
-      <c r="BV22" s="15"/>
-      <c r="BW22" s="15"/>
-      <c r="BX22" s="15"/>
-      <c r="BY22" s="15"/>
       <c r="BZ22" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="CE22" t="s">
-        <v>437</v>
-      </c>
-      <c r="CH22" s="13"/>
+        <v>434</v>
+      </c>
+      <c r="CH22" s="3"/>
       <c r="DB22">
         <v>1</v>
       </c>
@@ -8461,63 +8299,50 @@
     </row>
     <row r="23" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C23" t="s">
         <v>346</v>
       </c>
       <c r="D23" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E23" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F23" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>579</v>
+      <c r="I23">
+        <v>1</v>
       </c>
       <c r="M23"/>
-      <c r="N23" s="13"/>
       <c r="O23" s="12" t="s">
-        <v>580</v>
-      </c>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-      <c r="U23" s="13"/>
-      <c r="V23" s="13"/>
-      <c r="W23" s="13"/>
-      <c r="X23" s="13"/>
+        <v>496</v>
+      </c>
       <c r="AC23">
         <v>1</v>
       </c>
       <c r="AG23" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="AO23" s="7" t="s">
-        <v>482</v>
+        <v>576</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>432</v>
       </c>
       <c r="AR23" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AW23">
         <v>1</v>
       </c>
       <c r="AX23">
-        <v>583</v>
+        <v>1</v>
       </c>
       <c r="AZ23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB23">
         <v>1</v>
@@ -8525,26 +8350,20 @@
       <c r="BM23" s="7"/>
       <c r="BN23" s="7"/>
       <c r="BQ23">
-        <v>1</v>
-      </c>
-      <c r="BT23" s="15"/>
-      <c r="BU23" s="15"/>
-      <c r="BV23" s="15"/>
-      <c r="BW23" s="15"/>
-      <c r="BX23" s="15"/>
-      <c r="BY23" s="15"/>
+        <v>0.1</v>
+      </c>
       <c r="CE23" s="7" t="s">
-        <v>405</v>
+        <v>575</v>
       </c>
       <c r="CF23" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="CG23" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="CK23" s="7"/>
       <c r="CL23" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="CM23">
         <v>22</v>
@@ -8556,29 +8375,18 @@
         <v>10</v>
       </c>
       <c r="CW23" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="DB23">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="C24" t="s">
-        <v>346</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>402</v>
-      </c>
+      <c r="K24" s="13"/>
       <c r="L24" s="13"/>
-      <c r="M24"/>
+      <c r="M24" s="13"/>
       <c r="N24" s="13"/>
-      <c r="O24" s="14"/>
+      <c r="O24" s="13"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
@@ -8588,86 +8396,99 @@
       <c r="V24" s="13"/>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
-      <c r="AC24">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="AO24" s="7"/>
-      <c r="BB24">
-        <v>1</v>
-      </c>
-      <c r="BQ24">
-        <v>0.1</v>
-      </c>
+      <c r="BS24" s="15"/>
       <c r="BT24" s="15"/>
       <c r="BU24" s="15"/>
       <c r="BV24" s="15"/>
       <c r="BW24" s="15"/>
       <c r="BX24" s="15"/>
-      <c r="BY24" s="15"/>
-      <c r="CE24" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="CK24" t="s">
-        <v>495</v>
-      </c>
-      <c r="DB24">
-        <v>1</v>
-      </c>
+      <c r="BY24"/>
     </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="13"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="13"/>
-      <c r="X25" s="13"/>
-      <c r="BS25" s="15"/>
-      <c r="BT25" s="15"/>
-      <c r="BU25" s="15"/>
-      <c r="BV25" s="15"/>
-      <c r="BW25" s="15"/>
-      <c r="BX25" s="15"/>
-      <c r="BY25"/>
+      <c r="A25" t="s">
+        <v>506</v>
+      </c>
+      <c r="C25" t="s">
+        <v>346</v>
+      </c>
+      <c r="D25" t="s">
+        <v>507</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="F25" t="s">
+        <v>509</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+      <c r="J25" t="s">
+        <v>425</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="O25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB25">
+        <v>1</v>
+      </c>
+      <c r="BM25" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="BN25" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="BR25">
+        <v>1</v>
+      </c>
+      <c r="BT25" s="4">
+        <v>11</v>
+      </c>
+      <c r="BU25" s="4">
+        <v>15</v>
+      </c>
+      <c r="BV25" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW25" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="CL25" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="CM25" t="s">
+        <v>542</v>
+      </c>
+      <c r="CP25">
+        <v>25</v>
+      </c>
     </row>
     <row r="26" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="C26" t="s">
         <v>346</v>
       </c>
-      <c r="D26" t="s">
-        <v>510</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="F26" t="s">
-        <v>512</v>
-      </c>
-      <c r="G26">
-        <v>3</v>
-      </c>
-      <c r="J26" t="s">
-        <v>428</v>
+      <c r="I26">
+        <v>1</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="O26"/>
-      <c r="W26"/>
-      <c r="X26"/>
+        <v>402</v>
+      </c>
+      <c r="M26"/>
+      <c r="O26" s="12"/>
+      <c r="P26"/>
+      <c r="Q26"/>
       <c r="AC26">
         <v>1</v>
       </c>
@@ -8677,40 +8498,22 @@
       <c r="BB26">
         <v>1</v>
       </c>
-      <c r="BM26" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="BN26" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="BR26">
-        <v>1</v>
-      </c>
-      <c r="BT26" s="4">
-        <v>11</v>
-      </c>
-      <c r="BU26" s="4">
-        <v>15</v>
-      </c>
-      <c r="BV26" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW26" s="4" t="s">
-        <v>490</v>
+      <c r="BQ26">
+        <v>0.1</v>
       </c>
       <c r="CL26" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="CM26" t="s">
-        <v>545</v>
+        <v>567</v>
+      </c>
+      <c r="CM26">
+        <v>-100</v>
       </c>
       <c r="CP26">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>546</v>
+      <c r="A27" s="7" t="s">
+        <v>560</v>
       </c>
       <c r="C27" t="s">
         <v>346</v>
@@ -8719,37 +8522,39 @@
         <v>1</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>402</v>
+        <v>347</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>544</v>
       </c>
       <c r="M27"/>
-      <c r="O27" s="12"/>
+      <c r="O27" s="12" t="s">
+        <v>513</v>
+      </c>
       <c r="P27"/>
       <c r="Q27"/>
       <c r="AC27">
         <v>1</v>
       </c>
-      <c r="AG27" t="s">
-        <v>348</v>
+      <c r="AJ27" t="s">
+        <v>460</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>433</v>
       </c>
       <c r="BB27">
         <v>1</v>
       </c>
-      <c r="BQ27">
-        <v>0.1</v>
-      </c>
       <c r="CL27" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="CM27">
-        <v>-100</v>
+        <v>514</v>
       </c>
       <c r="CP27">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C28" t="s">
         <v>346</v>
@@ -8757,269 +8562,287 @@
       <c r="I28">
         <v>1</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="M28"/>
       <c r="O28" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="P28"/>
-      <c r="Q28"/>
+        <v>514</v>
+      </c>
       <c r="AC28">
         <v>1</v>
       </c>
-      <c r="AJ28" t="s">
-        <v>463</v>
-      </c>
-      <c r="AR28" t="s">
-        <v>436</v>
+      <c r="AG28" t="s">
+        <v>348</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>422</v>
+      </c>
+      <c r="AX28">
+        <v>1</v>
+      </c>
+      <c r="AZ28">
+        <v>1</v>
       </c>
       <c r="BB28">
-        <v>1</v>
-      </c>
-      <c r="CL28" s="12" t="s">
-        <v>517</v>
-      </c>
-      <c r="CP28">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C29" t="s">
-        <v>346</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>517</v>
+        <v>439</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>544</v>
       </c>
       <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AF29">
         <v>1</v>
       </c>
       <c r="AG29" t="s">
         <v>348</v>
       </c>
-      <c r="AV29" t="s">
+      <c r="BB29">
+        <v>1</v>
+      </c>
+      <c r="CJ29" s="3"/>
+      <c r="CS29" t="s">
+        <v>545</v>
+      </c>
+      <c r="DB29">
+        <v>1</v>
+      </c>
+      <c r="DE29">
+        <v>1</v>
+      </c>
+      <c r="DF29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ30" s="3"/>
+    </row>
+    <row r="31" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AJ31" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>433</v>
+      </c>
+      <c r="BB31">
+        <v>1</v>
+      </c>
+      <c r="BQ31">
+        <v>0.1</v>
+      </c>
+      <c r="CJ31" s="3"/>
+      <c r="CS31" s="7" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="32" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ32" s="3"/>
+    </row>
+    <row r="33" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>546</v>
+      </c>
+      <c r="C33" t="s">
+        <v>346</v>
+      </c>
+      <c r="D33" t="s">
+        <v>507</v>
+      </c>
+      <c r="E33" t="s">
+        <v>508</v>
+      </c>
+      <c r="F33" t="s">
+        <v>509</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="J33" t="s">
         <v>425</v>
       </c>
-      <c r="AX29">
-        <v>1</v>
-      </c>
-      <c r="AZ29">
-        <v>1</v>
-      </c>
-      <c r="BB29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="C30" t="s">
-        <v>442</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L30" s="3" t="s">
+      <c r="K33" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="O33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+      <c r="AC33">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB33">
+        <v>1</v>
+      </c>
+      <c r="BM33" t="s">
         <v>547</v>
       </c>
-      <c r="AC30">
-        <v>1</v>
-      </c>
-      <c r="AF30">
-        <v>1</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB30">
-        <v>1</v>
-      </c>
-      <c r="CJ30" s="3"/>
-      <c r="CS30" t="s">
-        <v>548</v>
-      </c>
-      <c r="DB30">
-        <v>1</v>
-      </c>
-      <c r="DE30">
-        <v>1</v>
-      </c>
-      <c r="DF30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ31" s="3"/>
-    </row>
-    <row r="32" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="AC32">
-        <v>1</v>
-      </c>
-      <c r="AJ32" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="AR32" t="s">
-        <v>436</v>
-      </c>
-      <c r="BB32">
-        <v>1</v>
-      </c>
-      <c r="BQ32">
-        <v>0.1</v>
-      </c>
-      <c r="CJ32" s="3"/>
-      <c r="CS32" s="7" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="33" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ33" s="3"/>
+      <c r="BR33">
+        <v>25</v>
+      </c>
+      <c r="BT33" s="4">
+        <v>1</v>
+      </c>
+      <c r="BU33" s="4">
+        <v>1</v>
+      </c>
+      <c r="BV33" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW33" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="CL33" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="CM33" t="s">
+        <v>512</v>
+      </c>
+      <c r="CN33">
+        <v>2</v>
+      </c>
+      <c r="CO33">
+        <v>80</v>
+      </c>
+      <c r="CP33">
+        <v>25</v>
+      </c>
     </row>
     <row r="34" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>549</v>
+        <v>515</v>
       </c>
       <c r="C34" t="s">
-        <v>346</v>
-      </c>
-      <c r="D34" t="s">
-        <v>510</v>
-      </c>
-      <c r="E34" t="s">
-        <v>511</v>
-      </c>
-      <c r="F34" t="s">
-        <v>512</v>
-      </c>
-      <c r="G34">
-        <v>3</v>
-      </c>
-      <c r="J34" t="s">
-        <v>428</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="O34"/>
-      <c r="W34"/>
+        <v>516</v>
+      </c>
+      <c r="O34" s="12" t="s">
+        <v>513</v>
+      </c>
       <c r="X34"/>
       <c r="AC34">
-        <v>1</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>348</v>
+        <v>2</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>427</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>444</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>422</v>
+      </c>
+      <c r="AX34">
+        <v>1</v>
       </c>
       <c r="BB34">
         <v>1</v>
       </c>
-      <c r="BM34" t="s">
-        <v>550</v>
-      </c>
-      <c r="BR34">
-        <v>25</v>
-      </c>
-      <c r="BT34" s="4">
-        <v>1</v>
-      </c>
-      <c r="BU34" s="4">
-        <v>1</v>
-      </c>
-      <c r="BV34" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW34" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="CL34" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="CM34" t="s">
-        <v>515</v>
-      </c>
-      <c r="CN34">
-        <v>2</v>
-      </c>
-      <c r="CO34">
-        <v>80</v>
-      </c>
-      <c r="CP34">
-        <v>25</v>
+      <c r="BN34" t="s">
+        <v>517</v>
+      </c>
+      <c r="BZ34" t="s">
+        <v>518</v>
+      </c>
+      <c r="CE34" t="s">
+        <v>434</v>
+      </c>
+      <c r="CW34" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C35" t="s">
-        <v>519</v>
+        <v>346</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>516</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="P35"/>
+      <c r="Q35"/>
       <c r="X35"/>
       <c r="AC35">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>348</v>
+      </c>
+      <c r="AH35">
+        <v>1</v>
       </c>
       <c r="AO35" t="s">
-        <v>430</v>
-      </c>
-      <c r="AR35" t="s">
-        <v>447</v>
-      </c>
-      <c r="AV35" t="s">
-        <v>425</v>
+        <v>432</v>
+      </c>
+      <c r="AT35">
+        <v>1</v>
+      </c>
+      <c r="AW35">
+        <v>1</v>
       </c>
       <c r="AX35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BB35">
         <v>1</v>
       </c>
-      <c r="BN35" t="s">
-        <v>520</v>
-      </c>
-      <c r="BZ35" t="s">
-        <v>521</v>
-      </c>
-      <c r="CE35" t="s">
-        <v>437</v>
-      </c>
-      <c r="CW35" t="s">
-        <v>350</v>
+      <c r="CF35" t="s">
+        <v>435</v>
+      </c>
+      <c r="CG35" t="s">
+        <v>423</v>
+      </c>
+      <c r="CL35" t="s">
+        <v>436</v>
+      </c>
+      <c r="CM35">
+        <v>22</v>
+      </c>
+      <c r="CP35">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>519</v>
+      </c>
+      <c r="C36" t="s">
         <v>520</v>
-      </c>
-      <c r="C36" t="s">
-        <v>346</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -9027,11 +8850,12 @@
       <c r="K36" s="3" t="s">
         <v>347</v>
       </c>
+      <c r="L36" s="3" t="s">
+        <v>521</v>
+      </c>
       <c r="O36" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="P36"/>
-      <c r="Q36"/>
+        <v>513</v>
+      </c>
       <c r="X36"/>
       <c r="AC36">
         <v>1</v>
@@ -9039,60 +8863,35 @@
       <c r="AG36" t="s">
         <v>348</v>
       </c>
-      <c r="AH36">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="s">
-        <v>435</v>
-      </c>
-      <c r="AT36">
-        <v>1</v>
-      </c>
-      <c r="AW36">
-        <v>1</v>
-      </c>
-      <c r="AX36">
-        <v>0.5</v>
-      </c>
       <c r="BB36">
         <v>1</v>
       </c>
-      <c r="CF36" t="s">
-        <v>438</v>
-      </c>
-      <c r="CG36" t="s">
-        <v>426</v>
-      </c>
-      <c r="CL36" t="s">
-        <v>439</v>
-      </c>
-      <c r="CM36">
-        <v>22</v>
-      </c>
-      <c r="CP36">
-        <v>10</v>
+      <c r="CS36" t="s">
+        <v>548</v>
+      </c>
+      <c r="DB36">
+        <v>1</v>
+      </c>
+      <c r="DE36">
+        <v>1</v>
+      </c>
+      <c r="DF36">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="C37" t="s">
-        <v>523</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
+        <v>550</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>347</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="X37"/>
+        <v>429</v>
+      </c>
       <c r="AC37">
         <v>1</v>
       </c>
@@ -9104,15 +8903,6 @@
       </c>
       <c r="CS37" t="s">
         <v>551</v>
-      </c>
-      <c r="DB37">
-        <v>1</v>
-      </c>
-      <c r="DE37">
-        <v>1</v>
-      </c>
-      <c r="DF37">
-        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:110" x14ac:dyDescent="0.25">
@@ -9120,13 +8910,16 @@
         <v>552</v>
       </c>
       <c r="C38" t="s">
-        <v>553</v>
+        <v>346</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>347</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AC38">
         <v>1</v>
@@ -9137,13 +8930,16 @@
       <c r="BB38">
         <v>1</v>
       </c>
-      <c r="CS38" t="s">
-        <v>554</v>
+      <c r="CL38" t="s">
+        <v>553</v>
+      </c>
+      <c r="CP38">
+        <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C39" t="s">
         <v>346</v>
@@ -9152,72 +8948,86 @@
         <v>1</v>
       </c>
       <c r="K39" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="AC39">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>448</v>
+      </c>
+      <c r="AT39">
+        <v>20</v>
+      </c>
+      <c r="BB39">
+        <v>1</v>
+      </c>
+      <c r="CK39" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="CL39" s="12"/>
+      <c r="DB39">
+        <v>1</v>
+      </c>
+      <c r="DE39">
+        <v>1</v>
+      </c>
+      <c r="DF39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>510</v>
+      </c>
+      <c r="C41" t="s">
+        <v>346</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L39" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="AC39">
-        <v>1</v>
-      </c>
-      <c r="AG39" t="s">
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="AC41">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="s">
         <v>348</v>
       </c>
-      <c r="BB39">
-        <v>1</v>
-      </c>
-      <c r="CL39" t="s">
-        <v>556</v>
-      </c>
-      <c r="CP39">
+      <c r="BB41">
+        <v>1</v>
+      </c>
+      <c r="BQ41">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>557</v>
-      </c>
-      <c r="C40" t="s">
-        <v>346</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="L40" s="3" t="s">
+      <c r="BT41"/>
+      <c r="BZ41" s="18" t="s">
         <v>572</v>
       </c>
-      <c r="AC40">
-        <v>1</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>451</v>
-      </c>
-      <c r="AT40">
-        <v>20</v>
-      </c>
-      <c r="BB40">
-        <v>1</v>
-      </c>
-      <c r="CK40" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="CL40" s="12"/>
-      <c r="DB40">
-        <v>1</v>
-      </c>
-      <c r="DE40">
-        <v>1</v>
-      </c>
-      <c r="DF40">
+      <c r="CE41" t="s">
+        <v>434</v>
+      </c>
+      <c r="CG41" s="3"/>
+      <c r="CH41" s="3"/>
+      <c r="DB41">
+        <v>1</v>
+      </c>
+      <c r="DE41">
+        <v>1</v>
+      </c>
+      <c r="DF41">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C42" t="s">
         <v>346</v>
@@ -9227,6 +9037,9 @@
       </c>
       <c r="K42" s="3" t="s">
         <v>347</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>503</v>
       </c>
       <c r="M42"/>
       <c r="N42"/>
@@ -9240,16 +9053,15 @@
         <v>1</v>
       </c>
       <c r="BQ42">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BT42"/>
       <c r="BZ42" s="18" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="CE42" t="s">
-        <v>437</v>
-      </c>
-      <c r="CG42" s="3"/>
+        <v>434</v>
+      </c>
       <c r="CH42" s="3"/>
       <c r="DB42">
         <v>1</v>
@@ -9263,7 +9075,7 @@
     </row>
     <row r="43" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C43" t="s">
         <v>346</v>
@@ -9275,10 +9087,10 @@
         <v>347</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="M43"/>
-      <c r="N43"/>
+        <v>503</v>
+      </c>
+      <c r="O43"/>
+      <c r="X43"/>
       <c r="AC43">
         <v>1</v>
       </c>
@@ -9288,69 +9100,24 @@
       <c r="BB43">
         <v>1</v>
       </c>
-      <c r="BQ43">
-        <v>1</v>
-      </c>
-      <c r="BT43"/>
-      <c r="BZ43" s="18" t="s">
-        <v>568</v>
-      </c>
-      <c r="CE43" t="s">
-        <v>437</v>
-      </c>
-      <c r="CH43" s="3"/>
-      <c r="DB43">
-        <v>1</v>
-      </c>
-      <c r="DE43">
-        <v>1</v>
-      </c>
-      <c r="DF43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>525</v>
-      </c>
-      <c r="C44" t="s">
-        <v>346</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="O44"/>
-      <c r="X44"/>
-      <c r="AC44">
-        <v>1</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB44">
-        <v>1</v>
-      </c>
-      <c r="CK44" s="12" t="s">
-        <v>558</v>
-      </c>
+      <c r="CK43" s="12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="46" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ46" s="3"/>
     </row>
     <row r="47" spans="1:110" x14ac:dyDescent="0.25">
       <c r="CJ47" s="3"/>
     </row>
-    <row r="48" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ48" s="3"/>
+    <row r="53" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ53" s="3"/>
     </row>
     <row r="54" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ54" s="3"/>
     </row>
-    <row r="55" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ55" s="3"/>
+    <row r="56" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ56" s="3"/>
     </row>
     <row r="57" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ57" s="3"/>
@@ -9362,50 +9129,50 @@
       <c r="CJ59" s="3"/>
     </row>
     <row r="60" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ60" s="3"/>
+      <c r="BT60"/>
     </row>
     <row r="61" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT61"/>
     </row>
     <row r="62" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT62"/>
+      <c r="CJ62" s="3"/>
     </row>
     <row r="63" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT63"/>
       <c r="CJ63" s="3"/>
     </row>
     <row r="64" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ64" s="3"/>
     </row>
     <row r="65" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ65" s="3"/>
+      <c r="BT65"/>
     </row>
     <row r="66" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT66"/>
-    </row>
-    <row r="67" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ67" s="3"/>
+      <c r="CJ66" s="3"/>
+    </row>
+    <row r="70" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT70"/>
     </row>
     <row r="71" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT71"/>
-    </row>
-    <row r="72" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ72" s="3"/>
+      <c r="CJ71" s="3"/>
+    </row>
+    <row r="79" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ79" s="3"/>
     </row>
     <row r="80" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ80" s="3"/>
     </row>
     <row r="81" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ81" s="3"/>
-    </row>
-    <row r="82" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT82"/>
+      <c r="BT81"/>
+    </row>
+    <row r="86" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT86"/>
     </row>
     <row r="87" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT87"/>
+      <c r="CJ87" s="3"/>
     </row>
     <row r="88" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT88"/>
       <c r="CJ88" s="3"/>
     </row>
     <row r="89" spans="72:88" x14ac:dyDescent="0.25">
@@ -9418,10 +9185,10 @@
       <c r="CJ91" s="3"/>
     </row>
     <row r="92" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ92" s="3"/>
+      <c r="BT92"/>
     </row>
     <row r="93" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT93"/>
+      <c r="CJ93" s="3"/>
     </row>
     <row r="94" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ94" s="3"/>
@@ -9433,10 +9200,10 @@
       <c r="CJ96" s="3"/>
     </row>
     <row r="97" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ97" s="3"/>
+      <c r="BT97"/>
     </row>
     <row r="98" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT98"/>
+      <c r="CJ98" s="3"/>
     </row>
     <row r="99" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ99" s="3"/>
@@ -9447,8 +9214,8 @@
     <row r="101" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ101" s="3"/>
     </row>
-    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="3"/>
+    <row r="104" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ104" s="3"/>
     </row>
     <row r="105" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ105" s="3"/>
@@ -9462,11 +9229,11 @@
     <row r="108" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ108" s="3"/>
     </row>
-    <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ109" s="3"/>
+    <row r="110" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT110"/>
     </row>
     <row r="111" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT111"/>
+      <c r="CJ111" s="3"/>
     </row>
     <row r="112" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ112" s="3"/>
@@ -9477,17 +9244,17 @@
     <row r="114" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ114" s="3"/>
     </row>
-    <row r="115" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ115" s="3"/>
-    </row>
-    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="3"/>
+    <row r="118" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ118" s="3"/>
+    </row>
+    <row r="120" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT120"/>
     </row>
     <row r="121" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT121"/>
+      <c r="CJ121" s="3"/>
     </row>
     <row r="122" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT122"/>
       <c r="CJ122" s="3"/>
     </row>
     <row r="123" spans="72:88" x14ac:dyDescent="0.25">
@@ -9499,50 +9266,50 @@
     <row r="125" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ125" s="3"/>
     </row>
-    <row r="126" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ126" s="3"/>
+    <row r="127" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT127"/>
     </row>
     <row r="128" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT128"/>
+      <c r="CJ128" s="3"/>
     </row>
     <row r="129" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ129" s="3"/>
     </row>
-    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ130" s="3"/>
+    <row r="131" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ131" s="3"/>
     </row>
     <row r="132" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ132" s="3"/>
     </row>
-    <row r="133" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ133" s="3"/>
+    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT134"/>
     </row>
     <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT135"/>
-    </row>
-    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ136" s="3"/>
+      <c r="CJ135" s="3"/>
+    </row>
+    <row r="138" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ138" s="3"/>
     </row>
     <row r="139" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ139" s="3"/>
     </row>
-    <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ140" s="3"/>
-    </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ143" s="3"/>
-    </row>
-    <row r="145" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ145" s="3"/>
+    <row r="142" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ142" s="3"/>
+    </row>
+    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ144" s="3"/>
+    </row>
+    <row r="146" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT146"/>
     </row>
     <row r="147" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT147"/>
+      <c r="CJ147" s="3"/>
     </row>
     <row r="148" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ148" s="3"/>
     </row>
-    <row r="149" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ149" s="3"/>
+    <row r="150" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ150" s="3"/>
     </row>
     <row r="151" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ151" s="3"/>
@@ -9550,186 +9317,187 @@
     <row r="152" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ152" s="3"/>
     </row>
-    <row r="153" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ153" s="3"/>
+    <row r="157" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ157" s="3"/>
     </row>
     <row r="158" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ158" s="3"/>
     </row>
-    <row r="159" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ159" s="3"/>
+    <row r="161" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ161" s="3"/>
     </row>
     <row r="162" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ162" s="3"/>
     </row>
-    <row r="163" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ163" s="3"/>
-    </row>
-    <row r="167" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ167" s="3"/>
-    </row>
-    <row r="171" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="3"/>
+    <row r="166" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ166" s="3"/>
+    </row>
+    <row r="170" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ170" s="3"/>
+    </row>
+    <row r="172" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ172" s="3"/>
     </row>
     <row r="173" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ173" s="3"/>
     </row>
-    <row r="174" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ174" s="3"/>
+    <row r="175" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ175" s="3"/>
     </row>
     <row r="176" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ176" s="3"/>
     </row>
-    <row r="177" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ177" s="3"/>
+    <row r="178" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT178"/>
     </row>
     <row r="179" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT179"/>
+      <c r="CJ179" s="3"/>
     </row>
     <row r="180" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT180"/>
       <c r="CJ180" s="3"/>
     </row>
-    <row r="181" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ181" s="3"/>
-    </row>
-    <row r="183" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ183" s="3"/>
+    <row r="182" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ182" s="3"/>
+    </row>
+    <row r="191" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT191"/>
     </row>
     <row r="192" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT192"/>
+      <c r="CJ192" s="3"/>
     </row>
     <row r="193" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT193"/>
       <c r="CJ193" s="3"/>
     </row>
     <row r="194" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ194" s="3"/>
     </row>
     <row r="195" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ195" s="3"/>
+      <c r="BT195"/>
     </row>
     <row r="196" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT196"/>
+      <c r="CJ196" s="3"/>
     </row>
     <row r="197" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT197"/>
       <c r="CJ197" s="3"/>
     </row>
-    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ198" s="3"/>
+    <row r="199" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT199"/>
     </row>
     <row r="200" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT200"/>
+      <c r="CJ200" s="3"/>
     </row>
     <row r="201" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT201"/>
       <c r="CJ201" s="3"/>
     </row>
-    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ202" s="3"/>
+    <row r="203" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT203"/>
     </row>
     <row r="204" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT204"/>
-    </row>
-    <row r="205" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ205" s="3"/>
-    </row>
-    <row r="208" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ208" s="3"/>
-    </row>
-    <row r="212" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ212" s="3"/>
+      <c r="CJ204" s="3"/>
+    </row>
+    <row r="207" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ207" s="3"/>
+    </row>
+    <row r="211" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ211" s="3"/>
+    </row>
+    <row r="213" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT213"/>
     </row>
     <row r="214" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT214"/>
-    </row>
-    <row r="215" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ215" s="3"/>
+      <c r="CJ214" s="3"/>
+    </row>
+    <row r="221" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT221"/>
     </row>
     <row r="222" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT222"/>
+      <c r="CJ222" s="3"/>
     </row>
     <row r="223" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ223" s="3"/>
     </row>
-    <row r="224" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ224" s="3"/>
+    <row r="225" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT225"/>
     </row>
     <row r="226" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT226"/>
+      <c r="CJ226" s="3"/>
     </row>
     <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT227"/>
       <c r="CJ227" s="3"/>
     </row>
-    <row r="228" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ228" s="3"/>
+    <row r="233" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT233"/>
     </row>
     <row r="234" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT234"/>
+      <c r="CJ234" s="3"/>
     </row>
     <row r="235" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT235"/>
       <c r="CJ235" s="3"/>
     </row>
     <row r="236" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT236"/>
       <c r="CJ236" s="3"/>
     </row>
-    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ237" s="3"/>
+    <row r="241" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT241"/>
     </row>
     <row r="242" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT242"/>
     </row>
-    <row r="243" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT243"/>
+    <row r="246" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT246"/>
     </row>
     <row r="247" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT247"/>
+      <c r="CJ247" s="3"/>
     </row>
     <row r="248" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ248" s="3"/>
+      <c r="BT248"/>
     </row>
     <row r="249" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT249"/>
-    </row>
-    <row r="250" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ250" s="3"/>
+      <c r="CJ249" s="3"/>
+    </row>
+    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT259"/>
     </row>
     <row r="260" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT260"/>
-    </row>
-    <row r="261" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ261" s="3"/>
+      <c r="CJ260" s="3"/>
+    </row>
+    <row r="262" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT262"/>
     </row>
     <row r="263" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT263"/>
-    </row>
-    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ264" s="3"/>
+      <c r="CJ263" s="3"/>
+    </row>
+    <row r="271" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT271"/>
     </row>
     <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT272"/>
-    </row>
-    <row r="273" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ273" s="3"/>
+      <c r="CJ272" s="3"/>
+    </row>
+    <row r="276" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT276"/>
     </row>
     <row r="277" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT277"/>
-    </row>
-    <row r="278" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ278" s="3"/>
+      <c r="CJ277" s="3"/>
+    </row>
+    <row r="279" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT279"/>
     </row>
     <row r="280" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT280"/>
-    </row>
-    <row r="281" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ281" s="3"/>
+      <c r="CJ280" s="3"/>
+    </row>
+    <row r="296" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT296"/>
     </row>
     <row r="297" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT297"/>
+      <c r="CJ297" s="3"/>
     </row>
     <row r="298" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT298"/>
@@ -9741,50 +9509,49 @@
     </row>
     <row r="300" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT300"/>
-      <c r="CJ300" s="3"/>
-    </row>
-    <row r="301" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT301"/>
+    </row>
+    <row r="302" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT302"/>
     </row>
     <row r="303" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT303"/>
+      <c r="CJ303" s="3"/>
     </row>
     <row r="304" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT304"/>
       <c r="CJ304" s="3"/>
     </row>
     <row r="305" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT305"/>
       <c r="CJ305" s="3"/>
     </row>
-    <row r="306" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ306" s="3"/>
+    <row r="309" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT309"/>
     </row>
     <row r="310" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT310"/>
-    </row>
-    <row r="311" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ311" s="3"/>
+      <c r="CJ310" s="3"/>
+    </row>
+    <row r="312" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT312"/>
     </row>
     <row r="313" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT313"/>
+      <c r="CJ313" s="3"/>
     </row>
     <row r="314" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT314"/>
       <c r="CJ314" s="3"/>
     </row>
     <row r="315" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT315"/>
       <c r="CJ315" s="3"/>
     </row>
-    <row r="316" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ316" s="3"/>
+    <row r="331" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT331"/>
     </row>
     <row r="332" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT332"/>
-    </row>
-    <row r="333" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ333" s="3"/>
+      <c r="CJ332" s="3"/>
+    </row>
+    <row r="340" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ340" s="3"/>
     </row>
     <row r="341" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ341" s="3"/>
@@ -9798,47 +9565,47 @@
     <row r="344" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ344" s="3"/>
     </row>
-    <row r="345" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ345" s="3"/>
+    <row r="346" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT346"/>
     </row>
     <row r="347" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT347"/>
+      <c r="CJ347" s="3"/>
     </row>
     <row r="348" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ348" s="3"/>
+      <c r="BT348"/>
     </row>
     <row r="349" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT349"/>
+      <c r="CJ349" s="3"/>
     </row>
     <row r="350" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT350"/>
       <c r="CJ350" s="3"/>
     </row>
-    <row r="351" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ351" s="3"/>
+    <row r="352" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT352"/>
     </row>
     <row r="353" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT353"/>
+      <c r="CJ353" s="3"/>
     </row>
     <row r="354" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT354"/>
       <c r="CJ354" s="3"/>
     </row>
     <row r="355" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT355"/>
       <c r="CJ355" s="3"/>
     </row>
-    <row r="356" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ356" s="3"/>
-    </row>
-    <row r="358" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ358" s="3"/>
-    </row>
-    <row r="360" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ360" s="3"/>
-    </row>
-    <row r="362" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ362" s="3"/>
+    <row r="357" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ357" s="3"/>
+    </row>
+    <row r="359" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ359" s="3"/>
+    </row>
+    <row r="361" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ361" s="3"/>
+    </row>
+    <row r="364" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ364" s="3"/>
     </row>
     <row r="365" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ365" s="3"/>
@@ -9856,17 +9623,17 @@
       <c r="CJ369" s="3"/>
     </row>
     <row r="370" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ370" s="3"/>
+      <c r="BT370"/>
     </row>
     <row r="371" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT371"/>
+      <c r="CJ371" s="3"/>
     </row>
     <row r="372" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT372"/>
       <c r="CJ372" s="3"/>
     </row>
     <row r="373" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT373"/>
       <c r="CJ373" s="3"/>
     </row>
     <row r="374" spans="72:88" x14ac:dyDescent="0.25">
@@ -9878,36 +9645,37 @@
     <row r="376" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ376" s="3"/>
     </row>
-    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ377" s="3"/>
+    <row r="378" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ378" s="3"/>
     </row>
     <row r="379" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ379" s="3"/>
     </row>
     <row r="380" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ380" s="3"/>
+      <c r="BT380"/>
     </row>
     <row r="381" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT381"/>
+      <c r="CJ381" s="3"/>
     </row>
     <row r="382" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT382"/>
       <c r="CJ382" s="3"/>
     </row>
     <row r="383" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT383"/>
       <c r="CJ383" s="3"/>
     </row>
     <row r="384" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ384" s="3"/>
     </row>
-    <row r="385" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ385" s="3"/>
+    <row r="386" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ386" s="3"/>
     </row>
     <row r="387" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ387" s="3"/>
     </row>
     <row r="388" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT388"/>
       <c r="CJ388" s="3"/>
     </row>
     <row r="389" spans="72:88" x14ac:dyDescent="0.25">
@@ -9915,7 +9683,6 @@
       <c r="CJ389" s="3"/>
     </row>
     <row r="390" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT390"/>
       <c r="CJ390" s="3"/>
     </row>
     <row r="391" spans="72:88" x14ac:dyDescent="0.25">
@@ -9924,70 +9691,70 @@
     <row r="392" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ392" s="3"/>
     </row>
-    <row r="393" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ393" s="3"/>
+    <row r="394" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT394"/>
+      <c r="CJ394" s="3"/>
     </row>
     <row r="395" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT395"/>
       <c r="CJ395" s="3"/>
     </row>
     <row r="396" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ396" s="3"/>
     </row>
-    <row r="397" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ397" s="3"/>
+    <row r="398" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT398"/>
+      <c r="CJ398" s="3"/>
     </row>
     <row r="399" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT399"/>
       <c r="CJ399" s="3"/>
     </row>
     <row r="400" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT400"/>
       <c r="CJ400" s="3"/>
     </row>
-    <row r="401" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ401" s="3"/>
-    </row>
-    <row r="403" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ403" s="3"/>
-    </row>
-    <row r="405" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ405" s="3"/>
+    <row r="402" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ402" s="3"/>
+    </row>
+    <row r="404" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ404" s="3"/>
+    </row>
+    <row r="407" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ407" s="3"/>
     </row>
     <row r="408" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ408" s="3"/>
     </row>
-    <row r="409" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ409" s="3"/>
+    <row r="412" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT412"/>
     </row>
     <row r="413" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT413"/>
+      <c r="CJ413" s="3"/>
     </row>
     <row r="414" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT414"/>
       <c r="CJ414" s="3"/>
     </row>
     <row r="415" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT415"/>
       <c r="CJ415" s="3"/>
     </row>
     <row r="416" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ416" s="3"/>
     </row>
     <row r="417" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ417" s="3"/>
+      <c r="BT417"/>
     </row>
     <row r="418" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT418"/>
-    </row>
-    <row r="419" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ419" s="3"/>
+      <c r="CJ418" s="3"/>
+    </row>
+    <row r="420" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ420" s="3"/>
     </row>
     <row r="421" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ421" s="3"/>
     </row>
-    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ422" s="3"/>
+    <row r="423" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ423" s="3"/>
     </row>
     <row r="424" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ424" s="3"/>
@@ -10007,74 +9774,75 @@
     <row r="429" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ429" s="3"/>
     </row>
-    <row r="430" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ430" s="3"/>
+    <row r="431" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT431"/>
     </row>
     <row r="432" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT432"/>
+      <c r="CJ432" s="3"/>
     </row>
     <row r="433" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ433" s="3"/>
     </row>
-    <row r="434" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ434" s="3"/>
+    <row r="466" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS466" s="8"/>
+      <c r="BT466" s="9"/>
     </row>
     <row r="467" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS467" s="8"/>
-      <c r="BT467" s="9"/>
-    </row>
-    <row r="468" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H468" s="8"/>
-      <c r="CJ468" s="8"/>
+      <c r="H467" s="8"/>
+      <c r="CJ467" s="8"/>
+    </row>
+    <row r="473" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT473"/>
     </row>
     <row r="474" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT474"/>
+      <c r="CJ474" s="3"/>
     </row>
     <row r="475" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT475"/>
       <c r="CJ475" s="3"/>
     </row>
     <row r="476" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT476"/>
       <c r="CJ476" s="3"/>
     </row>
-    <row r="477" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ477" s="3"/>
+    <row r="493" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT493"/>
     </row>
     <row r="494" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT494"/>
-    </row>
-    <row r="495" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ495" s="3"/>
+      <c r="CJ494" s="3"/>
+    </row>
+    <row r="526" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT526"/>
     </row>
     <row r="527" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT527"/>
+      <c r="CJ527" s="3"/>
     </row>
     <row r="528" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT528"/>
       <c r="CJ528" s="3"/>
     </row>
-    <row r="529" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ529" s="3"/>
+    <row r="544" spans="72:72" x14ac:dyDescent="0.25">
+      <c r="BT544"/>
     </row>
     <row r="545" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT545"/>
-    </row>
-    <row r="546" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ546" s="3"/>
+      <c r="CJ545" s="3"/>
+    </row>
+    <row r="551" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT551"/>
     </row>
     <row r="552" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT552"/>
+      <c r="CJ552" s="3"/>
     </row>
     <row r="553" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT553"/>
       <c r="CJ553" s="3"/>
     </row>
-    <row r="554" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ554" s="3"/>
+    <row r="558" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT558"/>
     </row>
     <row r="559" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT559"/>
+      <c r="CJ559" s="3"/>
     </row>
     <row r="560" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT560"/>
@@ -10133,40 +9901,40 @@
       <c r="CJ573" s="3"/>
     </row>
     <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT574"/>
       <c r="CJ574" s="3"/>
     </row>
-    <row r="575" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ575" s="3"/>
+    <row r="578" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT578"/>
     </row>
     <row r="579" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT579"/>
+      <c r="CJ579" s="3"/>
     </row>
     <row r="580" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT580"/>
       <c r="CJ580" s="3"/>
     </row>
     <row r="581" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ581" s="3"/>
+      <c r="BT581"/>
     </row>
     <row r="582" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT582"/>
-    </row>
-    <row r="583" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ583" s="3"/>
+      <c r="CJ582" s="3"/>
+    </row>
+    <row r="585" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT585"/>
     </row>
     <row r="586" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT586"/>
+      <c r="CJ586" s="3"/>
     </row>
     <row r="587" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT587"/>
       <c r="CJ587" s="3"/>
     </row>
-    <row r="588" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ588" s="3"/>
+    <row r="618" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT618"/>
     </row>
     <row r="619" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT619"/>
+      <c r="CJ619" s="3"/>
     </row>
     <row r="620" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT620"/>
@@ -10193,26 +9961,26 @@
       <c r="CJ625" s="3"/>
     </row>
     <row r="626" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT626"/>
       <c r="CJ626" s="3"/>
     </row>
-    <row r="627" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ627" s="3"/>
+    <row r="628" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT628"/>
     </row>
     <row r="629" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT629"/>
-    </row>
-    <row r="630" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ630" s="3"/>
+      <c r="CJ629" s="3"/>
+    </row>
+    <row r="633" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT633"/>
     </row>
     <row r="634" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT634"/>
-    </row>
-    <row r="635" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ635" s="3"/>
+      <c r="CJ634" s="3"/>
+    </row>
+    <row r="637" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT637"/>
     </row>
     <row r="638" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT638"/>
+      <c r="CJ638" s="3"/>
     </row>
     <row r="639" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT639"/>
@@ -10223,20 +9991,20 @@
       <c r="CJ640" s="3"/>
     </row>
     <row r="641" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT641"/>
       <c r="CJ641" s="3"/>
     </row>
-    <row r="642" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ642" s="3"/>
+    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT648"/>
     </row>
     <row r="649" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT649"/>
-    </row>
-    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ650" s="3"/>
+      <c r="CJ649" s="3"/>
+    </row>
+    <row r="652" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT652"/>
     </row>
     <row r="653" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT653"/>
+      <c r="CJ653" s="3"/>
     </row>
     <row r="654" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT654"/>
@@ -10247,74 +10015,74 @@
       <c r="CJ655" s="3"/>
     </row>
     <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT656"/>
       <c r="CJ656" s="3"/>
     </row>
-    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ657" s="3"/>
+    <row r="658" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT658"/>
     </row>
     <row r="659" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT659"/>
+      <c r="CJ659" s="3"/>
     </row>
     <row r="660" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT660"/>
       <c r="CJ660" s="3"/>
     </row>
     <row r="661" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ661" s="3"/>
-    </row>
-    <row r="662" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ662">
+      <c r="CJ661">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="663" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ663">
+        <v>0.2</v>
       </c>
     </row>
     <row r="664" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ664">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="666" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ666">
         <v>0.2</v>
       </c>
     </row>
-    <row r="665" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ665">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="667" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ667">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="674" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ674">
-        <v>1</v>
+    <row r="673" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ673">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="675" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ675">
+        <v>0.4</v>
       </c>
     </row>
     <row r="676" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ676">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ677">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="679" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ679">
+        <v>0.5</v>
       </c>
     </row>
     <row r="680" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ680">
-        <v>0.5</v>
+        <v>0.66700000000000004</v>
       </c>
     </row>
     <row r="681" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ681">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="682" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ682">
         <v>0.2</v>
       </c>
+    </row>
+    <row r="684" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT684"/>
     </row>
     <row r="685" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT685"/>
+      <c r="CJ685" s="3"/>
     </row>
     <row r="686" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT686"/>
@@ -10345,20 +10113,20 @@
       <c r="CJ692" s="3"/>
     </row>
     <row r="693" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT693"/>
       <c r="CJ693" s="3"/>
     </row>
     <row r="694" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ694" s="3"/>
+      <c r="BT694"/>
     </row>
     <row r="695" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT695"/>
-    </row>
-    <row r="696" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ696" s="3"/>
+      <c r="CJ695" s="3"/>
+    </row>
+    <row r="704" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT704"/>
     </row>
     <row r="705" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT705"/>
+      <c r="CJ705" s="3"/>
     </row>
     <row r="706" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT706"/>
@@ -10385,40 +10153,40 @@
       <c r="CJ711" s="3"/>
     </row>
     <row r="712" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT712"/>
       <c r="CJ712" s="3"/>
     </row>
     <row r="713" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ713" s="3"/>
+      <c r="BT713"/>
     </row>
     <row r="714" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT714"/>
-    </row>
-    <row r="715" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ715" s="3"/>
+      <c r="CJ714" s="3"/>
+    </row>
+    <row r="719" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT719"/>
     </row>
     <row r="720" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT720"/>
+      <c r="CJ720" s="3"/>
     </row>
     <row r="721" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT721"/>
       <c r="CJ721" s="3"/>
     </row>
     <row r="722" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ722" s="3"/>
+      <c r="BT722"/>
     </row>
     <row r="723" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT723"/>
+      <c r="CJ723" s="3"/>
     </row>
     <row r="724" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT724"/>
       <c r="CJ724" s="3"/>
     </row>
     <row r="725" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ725" s="3"/>
+      <c r="BT725"/>
     </row>
     <row r="726" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT726"/>
+      <c r="CJ726" s="3"/>
     </row>
     <row r="727" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT727"/>
@@ -10429,42 +10197,42 @@
       <c r="CJ728" s="3"/>
     </row>
     <row r="729" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT729"/>
       <c r="CJ729" s="3"/>
     </row>
-    <row r="730" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ730" s="3"/>
+    <row r="733" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT733"/>
     </row>
     <row r="734" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT734"/>
+      <c r="CJ734" s="3"/>
     </row>
     <row r="735" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT735"/>
       <c r="CJ735" s="3"/>
     </row>
     <row r="736" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT736"/>
       <c r="CJ736" s="3"/>
     </row>
     <row r="737" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ737" s="3"/>
+      <c r="BT737"/>
     </row>
     <row r="738" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT738"/>
+      <c r="CJ738" s="3"/>
     </row>
     <row r="739" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ739" s="3"/>
+      <c r="BS739" s="8"/>
+      <c r="BT739" s="9"/>
     </row>
     <row r="740" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS740" s="8"/>
-      <c r="BT740" s="9"/>
-    </row>
-    <row r="741" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H741" s="8"/>
-      <c r="CJ741" s="8"/>
+      <c r="H740" s="8"/>
+      <c r="CJ740" s="8"/>
+    </row>
+    <row r="757" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT757"/>
     </row>
     <row r="758" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT758"/>
+      <c r="CJ758" s="3"/>
     </row>
     <row r="759" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT759"/>
@@ -10475,30 +10243,30 @@
       <c r="CJ760" s="3"/>
     </row>
     <row r="761" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT761"/>
       <c r="CJ761" s="3"/>
     </row>
     <row r="762" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ762" s="3"/>
+      <c r="BT762"/>
     </row>
     <row r="763" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT763"/>
+      <c r="CJ763" s="3"/>
     </row>
     <row r="764" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT764"/>
+      <c r="BS764" s="8"/>
+      <c r="BT764" s="9"/>
       <c r="CJ764" s="3"/>
     </row>
     <row r="765" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS765" s="8"/>
-      <c r="BT765" s="9"/>
-      <c r="CJ765" s="3"/>
-    </row>
-    <row r="766" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H766" s="8"/>
-      <c r="CJ766" s="8"/>
+      <c r="H765" s="8"/>
+      <c r="CJ765" s="8"/>
+    </row>
+    <row r="768" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT768"/>
     </row>
     <row r="769" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT769"/>
+      <c r="CJ769" s="3"/>
     </row>
     <row r="770" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT770"/>
@@ -10525,14 +10293,14 @@
       <c r="CJ775" s="3"/>
     </row>
     <row r="776" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT776"/>
       <c r="CJ776" s="3"/>
     </row>
-    <row r="777" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ777" s="3"/>
+    <row r="778" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT778"/>
     </row>
     <row r="779" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT779"/>
+      <c r="CJ779" s="3"/>
     </row>
     <row r="780" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT780"/>
@@ -10551,14 +10319,14 @@
       <c r="CJ783" s="3"/>
     </row>
     <row r="784" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT784"/>
       <c r="CJ784" s="3"/>
     </row>
     <row r="785" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ785" s="3"/>
+      <c r="BT785"/>
     </row>
     <row r="786" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT786"/>
+      <c r="CJ786" s="3"/>
     </row>
     <row r="787" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT787"/>
@@ -10673,25 +10441,21 @@
       <c r="CJ814" s="3"/>
     </row>
     <row r="815" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT815"/>
       <c r="CJ815" s="3"/>
     </row>
     <row r="816" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ816" s="3"/>
+      <c r="BT816"/>
     </row>
     <row r="817" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT817"/>
+      <c r="CJ817" s="3"/>
     </row>
     <row r="818" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT818"/>
       <c r="CJ818" s="3"/>
     </row>
     <row r="819" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT819"/>
       <c r="CJ819" s="3"/>
-    </row>
-    <row r="820" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ820" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -10850,58 +10614,58 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="P4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C5" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H6" s="12">
         <v>1</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -10910,32 +10674,32 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C8" t="s">
+        <v>472</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
         <v>475</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H9" s="12">
         <v>1</v>
@@ -10944,24 +10708,24 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C10" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H11" s="12">
         <v>1</v>
@@ -10970,10 +10734,10 @@
     </row>
     <row r="12" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H12" s="12">
         <v>1</v>
@@ -10982,103 +10746,103 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C13" t="s">
         <v>200</v>
       </c>
       <c r="P13" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H14" s="12">
         <v>1</v>
       </c>
       <c r="J14"/>
       <c r="P14" s="12" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C15" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="P15" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C16" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P16" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J17" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H18" s="12">
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C19" t="s">
         <v>200</v>
       </c>
       <c r="P19" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -11207,7 +10971,7 @@
         <v>114</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -11217,13 +10981,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B5" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -11232,7 +10996,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDCE40C-980B-4328-813E-783FDCB4333D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD2BD06-843A-4A4D-B01D-6A499CADADB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2084,7 +2084,8 @@
     <t>固定间隔</t>
   </si>
   <si>
-    <t>自己以外</t>
+    <t>仅自己</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3399,7 +3400,7 @@
         <v>5433</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="O6">
         <v>221</v>
@@ -8329,8 +8330,8 @@
       <c r="AG23" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="AO23" t="s">
-        <v>432</v>
+      <c r="AO23" s="7" t="s">
+        <v>479</v>
       </c>
       <c r="AR23" t="s">
         <v>444</v>
@@ -8340,9 +8341,6 @@
       </c>
       <c r="AX23">
         <v>1</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
       </c>
       <c r="BB23">
         <v>1</v>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\学习专用\ark_-n\Excel\一方通行\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D259E10D-4B69-4B61-945B-5729D0C1A3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A24E17E-B627-42C0-91BB-D9F005CFF0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -21,8 +21,22 @@
     <sheet name="BulletData" sheetId="4" r:id="rId6"/>
     <sheet name="EffectData" sheetId="9" r:id="rId7"/>
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
+    <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -39,6 +53,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -47,6 +62,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -72,6 +88,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -80,6 +97,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -94,6 +112,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -102,6 +121,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -119,6 +139,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -127,6 +148,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -141,6 +163,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -149,6 +172,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -174,6 +198,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -182,6 +207,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -197,6 +223,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:
@@ -206,6 +233,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -222,6 +250,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -230,6 +259,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -247,6 +277,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -255,6 +286,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -267,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="585">
   <si>
     <t>Id</t>
   </si>
@@ -1972,19 +2004,91 @@
     <t>UnitTypeEnum[]</t>
   </si>
   <si>
-    <t>可无视buff抑制检测</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsCancelable</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <t>Id</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅单面</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>相对路径</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面atlas</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面skel</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面atlas</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面skel</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnlyFront</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseAppHotfixResPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontAtlasPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontPngPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontSkelPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackAtlasPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackPngPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackSkelPath</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>string?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1996,6 +2100,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2003,18 +2108,21 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2022,30 +2130,35 @@
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2053,6 +2166,7 @@
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2065,6 +2179,7 @@
       <sz val="11"/>
       <color rgb="FF333639"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="major"/>
     </font>
@@ -2078,38 +2193,28 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF333639"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2148,8 +2253,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2212,12 +2320,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{C396AF54-67AF-4F3C-B767-7A3706B9078E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2520,7 +2629,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
@@ -2550,7 +2659,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2558,48 +2667,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BS590"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" customWidth="1"/>
-    <col min="5" max="5" width="5.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.54296875" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08984375" customWidth="1"/>
-    <col min="13" max="13" width="5.54296875" customWidth="1"/>
+    <col min="12" max="12" width="4.08203125" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1"/>
     <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.7265625" customWidth="1"/>
-    <col min="16" max="16" width="10.81640625" customWidth="1"/>
-    <col min="17" max="18" width="3.81640625" customWidth="1"/>
-    <col min="19" max="20" width="3.54296875" customWidth="1"/>
-    <col min="21" max="21" width="10.26953125" customWidth="1"/>
-    <col min="22" max="22" width="9.54296875" customWidth="1"/>
-    <col min="23" max="23" width="10.7265625" customWidth="1"/>
-    <col min="24" max="24" width="12.81640625" customWidth="1"/>
-    <col min="25" max="25" width="13.08984375" customWidth="1"/>
-    <col min="26" max="26" width="10.7265625" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1"/>
+    <col min="26" max="26" width="10.75" customWidth="1"/>
     <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08984375" customWidth="1"/>
-    <col min="31" max="31" width="9.7265625" customWidth="1"/>
-    <col min="32" max="32" width="7.81640625" customWidth="1"/>
-    <col min="33" max="33" width="15.81640625" customWidth="1"/>
-    <col min="34" max="34" width="13.81640625" customWidth="1"/>
-    <col min="35" max="35" width="34.453125" customWidth="1"/>
-    <col min="36" max="37" width="9.81640625" customWidth="1"/>
-    <col min="43" max="43" width="12.453125" customWidth="1"/>
-    <col min="50" max="50" width="24.36328125" customWidth="1"/>
-    <col min="52" max="52" width="17.7265625" customWidth="1"/>
-    <col min="53" max="53" width="7.81640625" customWidth="1"/>
-    <col min="56" max="56" width="24.26953125" customWidth="1"/>
-    <col min="57" max="57" width="13.26953125" customWidth="1"/>
-    <col min="58" max="58" width="16.08984375" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1"/>
+    <col min="31" max="31" width="9.75" customWidth="1"/>
+    <col min="32" max="32" width="7.83203125" customWidth="1"/>
+    <col min="33" max="33" width="15.83203125" customWidth="1"/>
+    <col min="34" max="34" width="13.83203125" customWidth="1"/>
+    <col min="35" max="35" width="34.5" customWidth="1"/>
+    <col min="36" max="37" width="9.83203125" customWidth="1"/>
+    <col min="43" max="43" width="12.5" customWidth="1"/>
+    <col min="50" max="50" width="24.33203125" customWidth="1"/>
+    <col min="52" max="52" width="17.75" customWidth="1"/>
+    <col min="53" max="53" width="7.83203125" customWidth="1"/>
+    <col min="56" max="56" width="24.25" customWidth="1"/>
+    <col min="57" max="57" width="13.25" customWidth="1"/>
+    <col min="58" max="58" width="16.08203125" customWidth="1"/>
     <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.54296875" customWidth="1"/>
+    <col min="64" max="64" width="39.58203125" customWidth="1"/>
     <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.81640625" customWidth="1"/>
+    <col min="66" max="66" width="14.83203125" customWidth="1"/>
     <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1796875" customWidth="1"/>
+    <col min="71" max="71" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.25">
@@ -3535,2760 +3644,2760 @@
       <c r="AI27" s="1"/>
       <c r="BK27" s="1"/>
     </row>
-    <row r="28" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D28" s="17"/>
       <c r="E28" s="16"/>
       <c r="BO28" s="19"/>
       <c r="BR28" s="19"/>
     </row>
-    <row r="29" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D29" s="17"/>
       <c r="E29" s="16"/>
       <c r="BO29" s="19"/>
       <c r="BR29" s="19"/>
     </row>
-    <row r="30" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D30" s="17"/>
       <c r="E30" s="16"/>
       <c r="BO30" s="19"/>
       <c r="BR30" s="19"/>
     </row>
-    <row r="31" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D31" s="17"/>
       <c r="E31" s="16"/>
       <c r="BO31" s="19"/>
       <c r="BR31" s="19"/>
     </row>
-    <row r="32" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D32" s="17"/>
       <c r="E32" s="16"/>
       <c r="BO32" s="19"/>
       <c r="BR32" s="19"/>
     </row>
-    <row r="33" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D33" s="17"/>
       <c r="E33" s="16"/>
       <c r="BO33" s="19"/>
       <c r="BR33" s="19"/>
     </row>
-    <row r="34" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D34" s="17"/>
       <c r="E34" s="16"/>
       <c r="BO34" s="19"/>
       <c r="BR34" s="19"/>
     </row>
-    <row r="35" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D35" s="17"/>
       <c r="E35" s="16"/>
       <c r="BR35" s="19"/>
     </row>
-    <row r="36" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="17"/>
       <c r="E36" s="16"/>
       <c r="BR36" s="19"/>
     </row>
-    <row r="37" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="17"/>
       <c r="E37" s="16"/>
       <c r="BR37" s="19"/>
     </row>
-    <row r="38" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="17"/>
       <c r="E38" s="16"/>
       <c r="BO38" s="19"/>
       <c r="BR38" s="19"/>
     </row>
-    <row r="39" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="17"/>
       <c r="E39" s="16"/>
       <c r="BO39" s="19"/>
       <c r="BR39" s="19"/>
     </row>
-    <row r="40" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="17"/>
       <c r="E40" s="16"/>
       <c r="BO40" s="19"/>
       <c r="BR40" s="19"/>
     </row>
-    <row r="41" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="17"/>
       <c r="E41" s="16"/>
       <c r="BO41" s="19"/>
       <c r="BR41" s="19"/>
     </row>
-    <row r="42" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="17"/>
       <c r="E42" s="16"/>
       <c r="BO42" s="19"/>
       <c r="BR42" s="19"/>
     </row>
-    <row r="43" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="17"/>
       <c r="E43" s="16"/>
       <c r="BO43" s="19"/>
       <c r="BR43" s="19"/>
     </row>
-    <row r="44" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="17"/>
       <c r="E44" s="16"/>
       <c r="BO44" s="19"/>
       <c r="BR44" s="19"/>
     </row>
-    <row r="45" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="17"/>
       <c r="E45" s="16"/>
       <c r="BO45" s="19"/>
       <c r="BR45" s="19"/>
     </row>
-    <row r="46" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="17"/>
       <c r="E46" s="16"/>
       <c r="BO46" s="19"/>
       <c r="BR46" s="19"/>
     </row>
-    <row r="47" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="17"/>
       <c r="E47" s="16"/>
       <c r="BO47" s="19"/>
       <c r="BR47" s="19"/>
     </row>
-    <row r="48" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="17"/>
       <c r="E48" s="16"/>
       <c r="BO48" s="19"/>
       <c r="BR48" s="19"/>
     </row>
-    <row r="49" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="17"/>
       <c r="E49" s="16"/>
       <c r="BO49" s="19"/>
       <c r="BR49" s="19"/>
     </row>
-    <row r="50" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="17"/>
       <c r="E50" s="16"/>
       <c r="BO50" s="19"/>
       <c r="BR50" s="19"/>
     </row>
-    <row r="51" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="17"/>
       <c r="E51" s="16"/>
       <c r="BO51" s="19"/>
       <c r="BR51" s="19"/>
     </row>
-    <row r="52" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="17"/>
       <c r="E52" s="16"/>
       <c r="BO52" s="19"/>
       <c r="BR52" s="19"/>
     </row>
-    <row r="53" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="17"/>
       <c r="E53" s="16"/>
       <c r="BO53" s="19"/>
       <c r="BR53" s="19"/>
     </row>
-    <row r="54" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="17"/>
       <c r="E54" s="16"/>
       <c r="BO54" s="19"/>
       <c r="BR54" s="19"/>
     </row>
-    <row r="55" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="17"/>
       <c r="E55" s="16"/>
       <c r="BO55" s="19"/>
       <c r="BR55" s="19"/>
     </row>
-    <row r="56" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="17"/>
       <c r="E56" s="16"/>
       <c r="BO56" s="19"/>
       <c r="BR56" s="19"/>
     </row>
-    <row r="57" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="17"/>
       <c r="E57" s="16"/>
       <c r="BO57" s="19"/>
       <c r="BR57" s="19"/>
     </row>
-    <row r="58" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="17"/>
       <c r="E58" s="16"/>
       <c r="BO58" s="19"/>
       <c r="BR58" s="19"/>
     </row>
-    <row r="59" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="17"/>
       <c r="E59" s="16"/>
       <c r="BO59" s="19"/>
       <c r="BR59" s="19"/>
     </row>
-    <row r="60" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="17"/>
       <c r="E60" s="16"/>
       <c r="BO60" s="19"/>
       <c r="BR60" s="19"/>
     </row>
-    <row r="61" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="17"/>
       <c r="E61" s="16"/>
       <c r="BO61" s="19"/>
       <c r="BR61" s="19"/>
     </row>
-    <row r="62" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="17"/>
       <c r="E62" s="16"/>
       <c r="BO62" s="19"/>
       <c r="BR62" s="19"/>
     </row>
-    <row r="63" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="17"/>
       <c r="E63" s="16"/>
       <c r="BO63" s="19"/>
       <c r="BR63" s="19"/>
     </row>
-    <row r="64" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="17"/>
       <c r="E64" s="16"/>
       <c r="BO64" s="19"/>
       <c r="BR64" s="19"/>
     </row>
-    <row r="65" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="17"/>
       <c r="E65" s="16"/>
       <c r="BO65" s="19"/>
       <c r="BR65" s="19"/>
     </row>
-    <row r="66" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="17"/>
       <c r="E66" s="16"/>
       <c r="BO66" s="19"/>
       <c r="BR66" s="19"/>
     </row>
-    <row r="67" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="17"/>
       <c r="E67" s="16"/>
       <c r="BO67" s="19"/>
       <c r="BR67" s="19"/>
     </row>
-    <row r="68" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="17"/>
       <c r="E68" s="16"/>
       <c r="BO68" s="19"/>
       <c r="BR68" s="19"/>
     </row>
-    <row r="69" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="17"/>
       <c r="E69" s="16"/>
       <c r="BO69" s="19"/>
       <c r="BR69" s="19"/>
     </row>
-    <row r="70" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="17"/>
       <c r="E70" s="16"/>
       <c r="BO70" s="19"/>
       <c r="BR70" s="19"/>
     </row>
-    <row r="71" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="17"/>
       <c r="E71" s="16"/>
       <c r="BO71" s="19"/>
       <c r="BR71" s="19"/>
     </row>
-    <row r="72" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="17"/>
       <c r="E72" s="16"/>
       <c r="BO72" s="19"/>
       <c r="BR72" s="19"/>
     </row>
-    <row r="73" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="17"/>
       <c r="E73" s="16"/>
       <c r="BO73" s="19"/>
       <c r="BR73" s="19"/>
     </row>
-    <row r="74" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="17"/>
       <c r="E74" s="16"/>
       <c r="BO74" s="19"/>
       <c r="BR74" s="19"/>
     </row>
-    <row r="75" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="17"/>
       <c r="E75" s="16"/>
       <c r="BO75" s="19"/>
       <c r="BR75" s="19"/>
     </row>
-    <row r="76" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="17"/>
       <c r="E76" s="16"/>
       <c r="BO76" s="19"/>
       <c r="BR76" s="19"/>
     </row>
-    <row r="77" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="17"/>
       <c r="E77" s="16"/>
       <c r="BO77" s="19"/>
       <c r="BR77" s="19"/>
     </row>
-    <row r="78" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="17"/>
       <c r="E78" s="16"/>
       <c r="BO78" s="19"/>
       <c r="BR78" s="19"/>
     </row>
-    <row r="79" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="17"/>
       <c r="E79" s="16"/>
       <c r="BO79" s="19"/>
       <c r="BR79" s="19"/>
     </row>
-    <row r="80" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="17"/>
       <c r="E80" s="16"/>
       <c r="BO80" s="19"/>
       <c r="BR80" s="19"/>
     </row>
-    <row r="81" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="17"/>
       <c r="E81" s="16"/>
       <c r="BO81" s="19"/>
       <c r="BR81" s="19"/>
     </row>
-    <row r="82" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="17"/>
       <c r="E82" s="16"/>
       <c r="BO82" s="19"/>
       <c r="BR82" s="19"/>
     </row>
-    <row r="83" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="17"/>
       <c r="E83" s="16"/>
       <c r="BO83" s="19"/>
       <c r="BR83" s="19"/>
     </row>
-    <row r="84" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="17"/>
       <c r="E84" s="16"/>
       <c r="BO84" s="19"/>
       <c r="BR84" s="19"/>
     </row>
-    <row r="85" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="17"/>
       <c r="E85" s="16"/>
       <c r="BO85" s="19"/>
       <c r="BR85" s="19"/>
     </row>
-    <row r="86" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="17"/>
       <c r="E86" s="16"/>
       <c r="BO86" s="19"/>
       <c r="BR86" s="19"/>
     </row>
-    <row r="87" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="17"/>
       <c r="E87" s="16"/>
       <c r="BO87" s="19"/>
       <c r="BR87" s="19"/>
     </row>
-    <row r="88" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="17"/>
       <c r="E88" s="16"/>
       <c r="BO88" s="19"/>
       <c r="BR88" s="19"/>
     </row>
-    <row r="89" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="17"/>
       <c r="E89" s="16"/>
       <c r="BO89" s="19"/>
       <c r="BR89" s="19"/>
     </row>
-    <row r="90" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="17"/>
       <c r="E90" s="16"/>
       <c r="BO90" s="19"/>
       <c r="BR90" s="19"/>
     </row>
-    <row r="91" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="17"/>
       <c r="E91" s="16"/>
       <c r="BO91" s="19"/>
       <c r="BR91" s="19"/>
     </row>
-    <row r="92" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="17"/>
       <c r="E92" s="16"/>
       <c r="BO92" s="19"/>
       <c r="BR92" s="19"/>
     </row>
-    <row r="93" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="17"/>
       <c r="E93" s="16"/>
       <c r="BO93" s="19"/>
       <c r="BR93" s="19"/>
     </row>
-    <row r="94" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="17"/>
       <c r="E94" s="16"/>
       <c r="BO94" s="19"/>
       <c r="BR94" s="19"/>
     </row>
-    <row r="95" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="17"/>
       <c r="E95" s="16"/>
       <c r="BO95" s="19"/>
       <c r="BR95" s="19"/>
     </row>
-    <row r="96" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="17"/>
       <c r="E96" s="16"/>
       <c r="BO96" s="19"/>
       <c r="BR96" s="19"/>
     </row>
-    <row r="97" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="17"/>
       <c r="E97" s="16"/>
       <c r="BO97" s="19"/>
       <c r="BR97" s="19"/>
     </row>
-    <row r="98" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="17"/>
       <c r="E98" s="16"/>
       <c r="BO98" s="19"/>
       <c r="BR98" s="19"/>
     </row>
-    <row r="99" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="17"/>
       <c r="E99" s="16"/>
       <c r="BO99" s="19"/>
       <c r="BR99" s="19"/>
     </row>
-    <row r="100" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="17"/>
       <c r="E100" s="16"/>
       <c r="BO100" s="19"/>
       <c r="BR100" s="19"/>
     </row>
-    <row r="101" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="17"/>
       <c r="E101" s="16"/>
       <c r="BO101" s="19"/>
       <c r="BR101" s="19"/>
     </row>
-    <row r="102" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="17"/>
       <c r="E102" s="16"/>
       <c r="BO102" s="19"/>
       <c r="BR102" s="19"/>
     </row>
-    <row r="103" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="17"/>
       <c r="E103" s="16"/>
       <c r="BO103" s="19"/>
       <c r="BR103" s="19"/>
     </row>
-    <row r="104" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="17"/>
       <c r="E104" s="16"/>
       <c r="BO104" s="19"/>
       <c r="BR104" s="19"/>
     </row>
-    <row r="105" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="17"/>
       <c r="E105" s="16"/>
       <c r="BO105" s="19"/>
       <c r="BR105" s="19"/>
     </row>
-    <row r="106" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="17"/>
       <c r="E106" s="16"/>
       <c r="BO106" s="19"/>
       <c r="BR106" s="19"/>
     </row>
-    <row r="107" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="17"/>
       <c r="E107" s="16"/>
       <c r="BO107" s="19"/>
       <c r="BR107" s="19"/>
     </row>
-    <row r="108" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="17"/>
       <c r="E108" s="16"/>
       <c r="BO108" s="19"/>
       <c r="BR108" s="19"/>
     </row>
-    <row r="109" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="17"/>
       <c r="E109" s="16"/>
       <c r="BO109" s="19"/>
       <c r="BR109" s="19"/>
     </row>
-    <row r="110" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="17"/>
       <c r="E110" s="16"/>
       <c r="BO110" s="19"/>
       <c r="BR110" s="19"/>
     </row>
-    <row r="111" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="17"/>
       <c r="E111" s="16"/>
       <c r="BO111" s="19"/>
       <c r="BR111" s="19"/>
     </row>
-    <row r="112" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="17"/>
       <c r="E112" s="16"/>
       <c r="BO112" s="19"/>
       <c r="BR112" s="19"/>
     </row>
-    <row r="113" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="17"/>
       <c r="E113" s="16"/>
       <c r="BO113" s="19"/>
       <c r="BR113" s="19"/>
     </row>
-    <row r="114" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="17"/>
       <c r="E114" s="16"/>
       <c r="BO114" s="19"/>
       <c r="BR114" s="19"/>
     </row>
-    <row r="115" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="17"/>
       <c r="E115" s="16"/>
       <c r="BO115" s="19"/>
       <c r="BR115" s="19"/>
     </row>
-    <row r="116" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="17"/>
       <c r="E116" s="16"/>
       <c r="BO116" s="19"/>
       <c r="BR116" s="19"/>
     </row>
-    <row r="117" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="17"/>
       <c r="E117" s="16"/>
       <c r="BO117" s="19"/>
       <c r="BR117" s="19"/>
     </row>
-    <row r="118" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="17"/>
       <c r="E118" s="16"/>
       <c r="BO118" s="19"/>
       <c r="BR118" s="19"/>
     </row>
-    <row r="119" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="17"/>
       <c r="E119" s="16"/>
       <c r="BO119" s="19"/>
       <c r="BR119" s="19"/>
     </row>
-    <row r="120" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="17"/>
       <c r="E120" s="16"/>
       <c r="BO120" s="19"/>
       <c r="BR120" s="19"/>
     </row>
-    <row r="121" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="17"/>
       <c r="E121" s="16"/>
       <c r="BO121" s="19"/>
       <c r="BR121" s="19"/>
     </row>
-    <row r="122" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="17"/>
       <c r="E122" s="16"/>
       <c r="BO122" s="19"/>
       <c r="BR122" s="19"/>
     </row>
-    <row r="123" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="17"/>
       <c r="E123" s="16"/>
       <c r="BO123" s="19"/>
       <c r="BR123" s="19"/>
     </row>
-    <row r="124" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="17"/>
       <c r="E124" s="16"/>
       <c r="BO124" s="19"/>
       <c r="BR124" s="19"/>
     </row>
-    <row r="125" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="17"/>
       <c r="E125" s="16"/>
       <c r="BO125" s="19"/>
       <c r="BR125" s="19"/>
     </row>
-    <row r="126" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="17"/>
       <c r="E126" s="16"/>
       <c r="BO126" s="19"/>
       <c r="BR126" s="19"/>
     </row>
-    <row r="127" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="17"/>
       <c r="E127" s="16"/>
       <c r="BO127" s="19"/>
       <c r="BR127" s="19"/>
     </row>
-    <row r="128" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="17"/>
       <c r="E128" s="16"/>
       <c r="BO128" s="19"/>
       <c r="BR128" s="19"/>
     </row>
-    <row r="129" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="17"/>
       <c r="E129" s="16"/>
       <c r="BO129" s="19"/>
       <c r="BR129" s="19"/>
     </row>
-    <row r="130" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="17"/>
       <c r="E130" s="16"/>
       <c r="BO130" s="19"/>
       <c r="BR130" s="19"/>
     </row>
-    <row r="131" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="17"/>
       <c r="E131" s="16"/>
       <c r="BO131" s="19"/>
       <c r="BR131" s="19"/>
     </row>
-    <row r="132" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="17"/>
       <c r="E132" s="16"/>
       <c r="BO132" s="19"/>
       <c r="BR132" s="19"/>
     </row>
-    <row r="133" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="17"/>
       <c r="E133" s="16"/>
       <c r="BO133" s="19"/>
       <c r="BR133" s="19"/>
     </row>
-    <row r="134" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="17"/>
       <c r="E134" s="16"/>
       <c r="BO134" s="19"/>
       <c r="BR134" s="19"/>
     </row>
-    <row r="135" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="17"/>
       <c r="E135" s="16"/>
       <c r="BO135" s="19"/>
       <c r="BR135" s="19"/>
     </row>
-    <row r="136" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="17"/>
       <c r="E136" s="16"/>
       <c r="BO136" s="19"/>
       <c r="BR136" s="19"/>
     </row>
-    <row r="137" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="17"/>
       <c r="E137" s="16"/>
       <c r="BO137" s="19"/>
       <c r="BR137" s="19"/>
     </row>
-    <row r="138" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="17"/>
       <c r="E138" s="16"/>
       <c r="BO138" s="19"/>
       <c r="BR138" s="19"/>
     </row>
-    <row r="139" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="17"/>
       <c r="E139" s="16"/>
       <c r="BO139" s="19"/>
       <c r="BR139" s="19"/>
     </row>
-    <row r="140" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="17"/>
       <c r="E140" s="16"/>
       <c r="BO140" s="19"/>
       <c r="BR140" s="19"/>
     </row>
-    <row r="141" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="17"/>
       <c r="E141" s="16"/>
       <c r="BO141" s="19"/>
       <c r="BR141" s="19"/>
     </row>
-    <row r="142" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="17"/>
       <c r="E142" s="16"/>
       <c r="BO142" s="19"/>
       <c r="BR142" s="19"/>
     </row>
-    <row r="143" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="17"/>
       <c r="E143" s="16"/>
       <c r="BO143" s="19"/>
       <c r="BR143" s="19"/>
     </row>
-    <row r="144" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="17"/>
       <c r="E144" s="16"/>
       <c r="BO144" s="19"/>
       <c r="BR144" s="19"/>
     </row>
-    <row r="145" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="17"/>
       <c r="E145" s="16"/>
       <c r="BO145" s="19"/>
       <c r="BR145" s="19"/>
     </row>
-    <row r="146" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="17"/>
       <c r="E146" s="16"/>
       <c r="BO146" s="19"/>
       <c r="BR146" s="19"/>
     </row>
-    <row r="147" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="17"/>
       <c r="E147" s="16"/>
       <c r="BO147" s="19"/>
       <c r="BR147" s="19"/>
     </row>
-    <row r="148" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="17"/>
       <c r="E148" s="16"/>
       <c r="BO148" s="19"/>
       <c r="BR148" s="19"/>
     </row>
-    <row r="149" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="17"/>
       <c r="E149" s="16"/>
       <c r="BO149" s="19"/>
       <c r="BR149" s="19"/>
     </row>
-    <row r="150" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="17"/>
       <c r="E150" s="16"/>
       <c r="BO150" s="19"/>
       <c r="BR150" s="19"/>
     </row>
-    <row r="151" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="17"/>
       <c r="E151" s="16"/>
       <c r="BO151" s="19"/>
       <c r="BR151" s="19"/>
     </row>
-    <row r="152" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="17"/>
       <c r="E152" s="16"/>
       <c r="BO152" s="19"/>
       <c r="BR152" s="19"/>
     </row>
-    <row r="153" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="17"/>
       <c r="E153" s="16"/>
       <c r="BO153" s="19"/>
       <c r="BR153" s="19"/>
     </row>
-    <row r="154" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="17"/>
       <c r="E154" s="16"/>
       <c r="BO154" s="19"/>
       <c r="BR154" s="19"/>
     </row>
-    <row r="155" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="17"/>
       <c r="E155" s="16"/>
       <c r="BO155" s="19"/>
       <c r="BR155" s="19"/>
     </row>
-    <row r="156" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="17"/>
       <c r="E156" s="16"/>
       <c r="BO156" s="19"/>
       <c r="BR156" s="19"/>
     </row>
-    <row r="157" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="17"/>
       <c r="E157" s="16"/>
       <c r="BO157" s="19"/>
       <c r="BR157" s="19"/>
     </row>
-    <row r="158" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="17"/>
       <c r="E158" s="16"/>
       <c r="BO158" s="19"/>
       <c r="BR158" s="19"/>
     </row>
-    <row r="159" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="17"/>
       <c r="E159" s="16"/>
       <c r="BO159" s="19"/>
       <c r="BR159" s="19"/>
     </row>
-    <row r="160" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="17"/>
       <c r="E160" s="16"/>
       <c r="BO160" s="19"/>
       <c r="BR160" s="19"/>
     </row>
-    <row r="161" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="17"/>
       <c r="E161" s="16"/>
       <c r="BO161" s="19"/>
       <c r="BR161" s="19"/>
     </row>
-    <row r="162" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="17"/>
       <c r="E162" s="16"/>
       <c r="BO162" s="19"/>
       <c r="BR162" s="19"/>
     </row>
-    <row r="163" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="17"/>
       <c r="E163" s="16"/>
       <c r="BO163" s="19"/>
       <c r="BR163" s="19"/>
     </row>
-    <row r="164" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="17"/>
       <c r="E164" s="16"/>
       <c r="BO164" s="19"/>
       <c r="BR164" s="19"/>
     </row>
-    <row r="165" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="17"/>
       <c r="E165" s="16"/>
       <c r="BO165" s="19"/>
       <c r="BR165" s="19"/>
     </row>
-    <row r="166" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="17"/>
       <c r="E166" s="16"/>
       <c r="BO166" s="19"/>
       <c r="BR166" s="19"/>
     </row>
-    <row r="167" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="17"/>
       <c r="E167" s="16"/>
       <c r="BO167" s="19"/>
       <c r="BR167" s="19"/>
     </row>
-    <row r="168" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="17"/>
       <c r="E168" s="16"/>
       <c r="BO168" s="19"/>
       <c r="BR168" s="19"/>
     </row>
-    <row r="169" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="17"/>
       <c r="E169" s="16"/>
       <c r="BO169" s="19"/>
       <c r="BR169" s="19"/>
     </row>
-    <row r="170" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="17"/>
       <c r="E170" s="16"/>
       <c r="BO170" s="19"/>
       <c r="BR170" s="19"/>
     </row>
-    <row r="171" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="17"/>
       <c r="E171" s="16"/>
       <c r="BO171" s="19"/>
       <c r="BR171" s="19"/>
     </row>
-    <row r="172" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="17"/>
       <c r="E172" s="16"/>
       <c r="BO172" s="19"/>
       <c r="BR172" s="19"/>
     </row>
-    <row r="173" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="17"/>
       <c r="E173" s="16"/>
       <c r="BO173" s="19"/>
       <c r="BR173" s="19"/>
     </row>
-    <row r="174" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="17"/>
       <c r="E174" s="16"/>
       <c r="BO174" s="19"/>
       <c r="BR174" s="19"/>
     </row>
-    <row r="175" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="17"/>
       <c r="E175" s="16"/>
       <c r="BO175" s="19"/>
       <c r="BR175" s="19"/>
     </row>
-    <row r="176" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="17"/>
       <c r="E176" s="16"/>
       <c r="BO176" s="19"/>
       <c r="BR176" s="19"/>
     </row>
-    <row r="177" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="17"/>
       <c r="E177" s="16"/>
       <c r="BO177" s="19"/>
       <c r="BR177" s="19"/>
     </row>
-    <row r="178" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="17"/>
       <c r="E178" s="16"/>
       <c r="BO178" s="19"/>
       <c r="BR178" s="19"/>
     </row>
-    <row r="179" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="17"/>
       <c r="E179" s="16"/>
       <c r="BO179" s="19"/>
       <c r="BR179" s="19"/>
     </row>
-    <row r="180" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="17"/>
       <c r="E180" s="16"/>
       <c r="BO180" s="19"/>
       <c r="BR180" s="19"/>
     </row>
-    <row r="181" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="17"/>
       <c r="E181" s="16"/>
       <c r="BO181" s="19"/>
       <c r="BR181" s="19"/>
     </row>
-    <row r="182" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="17"/>
       <c r="E182" s="16"/>
       <c r="BO182" s="19"/>
       <c r="BR182" s="19"/>
     </row>
-    <row r="183" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="17"/>
       <c r="E183" s="16"/>
       <c r="BO183" s="19"/>
       <c r="BR183" s="19"/>
     </row>
-    <row r="184" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="17"/>
       <c r="E184" s="16"/>
       <c r="BO184" s="19"/>
       <c r="BR184" s="19"/>
     </row>
-    <row r="185" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="17"/>
       <c r="E185" s="16"/>
       <c r="BO185" s="19"/>
       <c r="BR185" s="19"/>
     </row>
-    <row r="186" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="17"/>
       <c r="E186" s="16"/>
       <c r="BO186" s="19"/>
       <c r="BR186" s="19"/>
     </row>
-    <row r="187" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="17"/>
       <c r="E187" s="16"/>
       <c r="BO187" s="19"/>
       <c r="BR187" s="19"/>
     </row>
-    <row r="188" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="17"/>
       <c r="E188" s="16"/>
       <c r="BO188" s="19"/>
       <c r="BR188" s="19"/>
     </row>
-    <row r="189" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="17"/>
       <c r="E189" s="16"/>
       <c r="BO189" s="19"/>
       <c r="BR189" s="19"/>
     </row>
-    <row r="190" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="17"/>
       <c r="E190" s="16"/>
       <c r="BO190" s="19"/>
       <c r="BR190" s="19"/>
     </row>
-    <row r="191" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="17"/>
       <c r="E191" s="16"/>
       <c r="BO191" s="19"/>
       <c r="BR191" s="19"/>
     </row>
-    <row r="192" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="17"/>
       <c r="E192" s="16"/>
       <c r="BO192" s="19"/>
       <c r="BR192" s="19"/>
     </row>
-    <row r="193" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="17"/>
       <c r="E193" s="16"/>
       <c r="BO193" s="19"/>
       <c r="BR193" s="19"/>
     </row>
-    <row r="194" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="17"/>
       <c r="E194" s="16"/>
       <c r="BO194" s="19"/>
       <c r="BR194" s="19"/>
     </row>
-    <row r="195" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="17"/>
       <c r="E195" s="16"/>
       <c r="BO195" s="19"/>
       <c r="BR195" s="19"/>
     </row>
-    <row r="196" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="17"/>
       <c r="E196" s="16"/>
       <c r="BO196" s="19"/>
       <c r="BR196" s="19"/>
     </row>
-    <row r="197" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="17"/>
       <c r="E197" s="16"/>
       <c r="BO197" s="19"/>
       <c r="BR197" s="19"/>
     </row>
-    <row r="198" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="17"/>
       <c r="E198" s="16"/>
       <c r="BO198" s="19"/>
       <c r="BR198" s="19"/>
     </row>
-    <row r="199" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="17"/>
       <c r="E199" s="16"/>
       <c r="BO199" s="19"/>
       <c r="BR199" s="19"/>
     </row>
-    <row r="200" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="17"/>
       <c r="E200" s="16"/>
       <c r="BO200" s="19"/>
       <c r="BR200" s="19"/>
     </row>
-    <row r="201" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="17"/>
       <c r="E201" s="16"/>
       <c r="BO201" s="19"/>
       <c r="BR201" s="19"/>
     </row>
-    <row r="202" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="17"/>
       <c r="E202" s="16"/>
       <c r="BO202" s="19"/>
       <c r="BR202" s="19"/>
     </row>
-    <row r="203" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="17"/>
       <c r="E203" s="16"/>
       <c r="BO203" s="19"/>
       <c r="BR203" s="19"/>
     </row>
-    <row r="204" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="17"/>
       <c r="E204" s="16"/>
       <c r="BO204" s="19"/>
       <c r="BR204" s="19"/>
     </row>
-    <row r="205" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="17"/>
       <c r="E205" s="16"/>
       <c r="BO205" s="19"/>
       <c r="BR205" s="19"/>
     </row>
-    <row r="206" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="17"/>
       <c r="E206" s="16"/>
       <c r="BO206" s="19"/>
       <c r="BR206" s="19"/>
     </row>
-    <row r="207" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="17"/>
       <c r="E207" s="16"/>
       <c r="BO207" s="19"/>
       <c r="BR207" s="19"/>
     </row>
-    <row r="208" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="17"/>
       <c r="E208" s="16"/>
       <c r="BO208" s="19"/>
       <c r="BR208" s="19"/>
     </row>
-    <row r="209" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="17"/>
       <c r="E209" s="16"/>
       <c r="BO209" s="19"/>
       <c r="BR209" s="19"/>
     </row>
-    <row r="210" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="17"/>
       <c r="E210" s="16"/>
       <c r="BO210" s="19"/>
       <c r="BR210" s="19"/>
     </row>
-    <row r="211" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="17"/>
       <c r="E211" s="16"/>
       <c r="BO211" s="19"/>
       <c r="BR211" s="19"/>
     </row>
-    <row r="212" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="17"/>
       <c r="E212" s="16"/>
       <c r="BO212" s="19"/>
       <c r="BR212" s="19"/>
     </row>
-    <row r="213" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="17"/>
       <c r="E213" s="16"/>
       <c r="BO213" s="19"/>
       <c r="BR213" s="19"/>
     </row>
-    <row r="214" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="17"/>
       <c r="E214" s="16"/>
       <c r="BO214" s="19"/>
       <c r="BR214" s="19"/>
     </row>
-    <row r="215" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="17"/>
       <c r="E215" s="16"/>
       <c r="BO215" s="19"/>
       <c r="BR215" s="19"/>
     </row>
-    <row r="216" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="17"/>
       <c r="E216" s="16"/>
       <c r="BO216" s="19"/>
       <c r="BR216" s="19"/>
     </row>
-    <row r="217" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="17"/>
       <c r="E217" s="16"/>
       <c r="BO217" s="19"/>
       <c r="BR217" s="19"/>
     </row>
-    <row r="218" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="17"/>
       <c r="E218" s="16"/>
       <c r="BO218" s="19"/>
       <c r="BR218" s="19"/>
     </row>
-    <row r="219" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="17"/>
       <c r="E219" s="16"/>
       <c r="BO219" s="19"/>
       <c r="BR219" s="19"/>
     </row>
-    <row r="220" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="17"/>
       <c r="E220" s="16"/>
       <c r="BO220" s="19"/>
       <c r="BR220" s="19"/>
     </row>
-    <row r="221" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="17"/>
       <c r="E221" s="16"/>
       <c r="BO221" s="19"/>
       <c r="BR221" s="19"/>
     </row>
-    <row r="222" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="17"/>
       <c r="E222" s="16"/>
       <c r="BO222" s="19"/>
       <c r="BR222" s="19"/>
     </row>
-    <row r="223" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="17"/>
       <c r="E223" s="16"/>
       <c r="BO223" s="19"/>
       <c r="BR223" s="19"/>
     </row>
-    <row r="224" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="17"/>
       <c r="E224" s="16"/>
       <c r="BO224" s="19"/>
       <c r="BR224" s="19"/>
     </row>
-    <row r="225" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="17"/>
       <c r="E225" s="16"/>
       <c r="BO225" s="19"/>
       <c r="BR225" s="19"/>
     </row>
-    <row r="226" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="17"/>
       <c r="E226" s="16"/>
       <c r="BO226" s="19"/>
       <c r="BR226" s="19"/>
     </row>
-    <row r="227" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="17"/>
       <c r="E227" s="16"/>
       <c r="BO227" s="19"/>
       <c r="BR227" s="19"/>
     </row>
-    <row r="228" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="17"/>
       <c r="E228" s="16"/>
       <c r="BO228" s="19"/>
       <c r="BR228" s="19"/>
     </row>
-    <row r="229" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="17"/>
       <c r="E229" s="16"/>
       <c r="BO229" s="19"/>
       <c r="BR229" s="19"/>
     </row>
-    <row r="230" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="17"/>
       <c r="E230" s="16"/>
       <c r="BO230" s="19"/>
       <c r="BR230" s="19"/>
     </row>
-    <row r="231" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="17"/>
       <c r="E231" s="16"/>
       <c r="BO231" s="19"/>
       <c r="BR231" s="19"/>
     </row>
-    <row r="232" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="17"/>
       <c r="E232" s="16"/>
       <c r="BO232" s="19"/>
       <c r="BR232" s="19"/>
     </row>
-    <row r="233" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="17"/>
       <c r="E233" s="16"/>
       <c r="BO233" s="19"/>
       <c r="BR233" s="19"/>
     </row>
-    <row r="234" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="17"/>
       <c r="E234" s="16"/>
       <c r="BO234" s="19"/>
       <c r="BR234" s="19"/>
     </row>
-    <row r="235" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="17"/>
       <c r="E235" s="16"/>
       <c r="BR235" s="19"/>
     </row>
-    <row r="236" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="17"/>
       <c r="E236" s="16"/>
       <c r="BO236" s="19"/>
       <c r="BR236" s="19"/>
     </row>
-    <row r="237" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="17"/>
       <c r="E237" s="16"/>
       <c r="BO237" s="19"/>
       <c r="BR237" s="19"/>
     </row>
-    <row r="238" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="17"/>
       <c r="E238" s="16"/>
       <c r="BO238" s="19"/>
       <c r="BR238" s="19"/>
     </row>
-    <row r="239" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="17"/>
       <c r="E239" s="16"/>
       <c r="BO239" s="19"/>
       <c r="BR239" s="19"/>
     </row>
-    <row r="240" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="17"/>
       <c r="E240" s="16"/>
       <c r="BO240" s="19"/>
       <c r="BR240" s="19"/>
     </row>
-    <row r="241" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="17"/>
       <c r="E241" s="16"/>
       <c r="BO241" s="19"/>
       <c r="BR241" s="19"/>
     </row>
-    <row r="242" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="17"/>
       <c r="E242" s="16"/>
       <c r="BO242" s="19"/>
       <c r="BR242" s="19"/>
     </row>
-    <row r="243" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="17"/>
       <c r="E243" s="16"/>
       <c r="BO243" s="19"/>
       <c r="BR243" s="19"/>
     </row>
-    <row r="244" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="17"/>
       <c r="E244" s="16"/>
       <c r="BO244" s="19"/>
       <c r="BR244" s="19"/>
     </row>
-    <row r="245" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="17"/>
       <c r="E245" s="16"/>
       <c r="BO245" s="19"/>
       <c r="BR245" s="19"/>
     </row>
-    <row r="246" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="17"/>
       <c r="E246" s="16"/>
       <c r="BO246" s="19"/>
       <c r="BR246" s="19"/>
     </row>
-    <row r="247" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="17"/>
       <c r="E247" s="16"/>
       <c r="BO247" s="19"/>
       <c r="BR247" s="19"/>
     </row>
-    <row r="248" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="17"/>
       <c r="E248" s="16"/>
       <c r="BO248" s="19"/>
       <c r="BR248" s="19"/>
     </row>
-    <row r="249" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="17"/>
       <c r="E249" s="16"/>
       <c r="BO249" s="19"/>
       <c r="BR249" s="19"/>
     </row>
-    <row r="250" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="17"/>
       <c r="E250" s="16"/>
       <c r="BO250" s="19"/>
       <c r="BR250" s="19"/>
     </row>
-    <row r="251" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="17"/>
       <c r="E251" s="16"/>
       <c r="BO251" s="19"/>
       <c r="BR251" s="19"/>
     </row>
-    <row r="252" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="17"/>
       <c r="E252" s="16"/>
       <c r="BO252" s="19"/>
       <c r="BR252" s="19"/>
     </row>
-    <row r="253" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="17"/>
       <c r="E253" s="16"/>
       <c r="BO253" s="19"/>
       <c r="BR253" s="19"/>
     </row>
-    <row r="254" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="17"/>
       <c r="E254" s="16"/>
       <c r="BO254" s="19"/>
       <c r="BR254" s="19"/>
     </row>
-    <row r="255" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="17"/>
       <c r="E255" s="16"/>
       <c r="BO255" s="19"/>
       <c r="BR255" s="19"/>
     </row>
-    <row r="256" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="17"/>
       <c r="E256" s="16"/>
       <c r="BO256" s="19"/>
       <c r="BR256" s="19"/>
     </row>
-    <row r="257" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="17"/>
       <c r="E257" s="16"/>
       <c r="BO257" s="19"/>
       <c r="BR257" s="19"/>
     </row>
-    <row r="258" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="17"/>
       <c r="E258" s="16"/>
       <c r="BO258" s="19"/>
       <c r="BR258" s="19"/>
     </row>
-    <row r="259" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="17"/>
       <c r="E259" s="16"/>
       <c r="BO259" s="19"/>
       <c r="BR259" s="19"/>
     </row>
-    <row r="260" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="17"/>
       <c r="E260" s="16"/>
       <c r="BO260" s="19"/>
       <c r="BR260" s="19"/>
     </row>
-    <row r="261" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="17"/>
       <c r="E261" s="16"/>
       <c r="BO261" s="19"/>
       <c r="BR261" s="19"/>
     </row>
-    <row r="262" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="17"/>
       <c r="E262" s="16"/>
       <c r="BO262" s="19"/>
       <c r="BR262" s="19"/>
     </row>
-    <row r="263" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="17"/>
       <c r="E263" s="16"/>
       <c r="BO263" s="19"/>
       <c r="BR263" s="19"/>
     </row>
-    <row r="264" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="17"/>
       <c r="E264" s="16"/>
       <c r="BO264" s="19"/>
       <c r="BR264" s="19"/>
     </row>
-    <row r="265" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="17"/>
       <c r="E265" s="16"/>
       <c r="BO265" s="19"/>
       <c r="BR265" s="19"/>
     </row>
-    <row r="266" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="17"/>
       <c r="E266" s="16"/>
       <c r="BO266" s="19"/>
       <c r="BR266" s="19"/>
     </row>
-    <row r="267" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="17"/>
       <c r="E267" s="16"/>
       <c r="BO267" s="19"/>
       <c r="BR267" s="19"/>
     </row>
-    <row r="268" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="17"/>
       <c r="E268" s="16"/>
       <c r="BO268" s="19"/>
       <c r="BR268" s="19"/>
     </row>
-    <row r="269" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="17"/>
       <c r="E269" s="16"/>
       <c r="BO269" s="19"/>
       <c r="BR269" s="19"/>
     </row>
-    <row r="270" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="17"/>
       <c r="E270" s="16"/>
       <c r="BO270" s="19"/>
       <c r="BR270" s="19"/>
     </row>
-    <row r="271" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="17"/>
       <c r="E271" s="16"/>
       <c r="BO271" s="19"/>
       <c r="BR271" s="19"/>
     </row>
-    <row r="272" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="17"/>
       <c r="E272" s="16"/>
       <c r="BO272" s="19"/>
       <c r="BR272" s="19"/>
     </row>
-    <row r="273" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="17"/>
       <c r="E273" s="16"/>
       <c r="BO273" s="19"/>
       <c r="BR273" s="19"/>
     </row>
-    <row r="274" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="17"/>
       <c r="E274" s="16"/>
       <c r="BO274" s="19"/>
       <c r="BR274" s="19"/>
     </row>
-    <row r="275" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="17"/>
       <c r="E275" s="16"/>
       <c r="BO275" s="19"/>
       <c r="BR275" s="19"/>
     </row>
-    <row r="276" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="17"/>
       <c r="E276" s="16"/>
       <c r="BO276" s="19"/>
       <c r="BR276" s="19"/>
     </row>
-    <row r="277" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="17"/>
       <c r="E277" s="16"/>
       <c r="BO277" s="19"/>
       <c r="BR277" s="19"/>
     </row>
-    <row r="278" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="17"/>
       <c r="E278" s="16"/>
       <c r="BR278" s="19"/>
     </row>
-    <row r="279" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="17"/>
       <c r="E279" s="16"/>
       <c r="BO279" s="19"/>
       <c r="BR279" s="19"/>
     </row>
-    <row r="280" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="17"/>
       <c r="E280" s="16"/>
       <c r="BO280" s="19"/>
       <c r="BR280" s="19"/>
     </row>
-    <row r="281" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="17"/>
       <c r="E281" s="16"/>
       <c r="BO281" s="19"/>
       <c r="BR281" s="19"/>
     </row>
-    <row r="282" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="17"/>
       <c r="E282" s="16"/>
       <c r="BO282" s="19"/>
       <c r="BR282" s="19"/>
     </row>
-    <row r="283" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="17"/>
       <c r="E283" s="16"/>
       <c r="BO283" s="19"/>
       <c r="BR283" s="19"/>
     </row>
-    <row r="284" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="17"/>
       <c r="E284" s="16"/>
       <c r="BO284" s="19"/>
       <c r="BR284" s="19"/>
     </row>
-    <row r="285" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="17"/>
       <c r="E285" s="16"/>
       <c r="BO285" s="19"/>
       <c r="BR285" s="19"/>
     </row>
-    <row r="286" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="17"/>
       <c r="E286" s="16"/>
       <c r="BO286" s="19"/>
       <c r="BR286" s="19"/>
     </row>
-    <row r="287" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="17"/>
       <c r="E287" s="16"/>
       <c r="BO287" s="19"/>
       <c r="BR287" s="19"/>
     </row>
-    <row r="288" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="17"/>
       <c r="E288" s="16"/>
       <c r="BO288" s="19"/>
       <c r="BR288" s="19"/>
     </row>
-    <row r="289" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="17"/>
       <c r="E289" s="16"/>
       <c r="BO289" s="19"/>
       <c r="BR289" s="19"/>
     </row>
-    <row r="290" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="17"/>
       <c r="E290" s="16"/>
       <c r="BO290" s="19"/>
       <c r="BR290" s="19"/>
     </row>
-    <row r="291" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="17"/>
       <c r="E291" s="16"/>
       <c r="BO291" s="19"/>
       <c r="BR291" s="19"/>
     </row>
-    <row r="292" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="17"/>
       <c r="E292" s="16"/>
       <c r="BO292" s="19"/>
       <c r="BR292" s="19"/>
     </row>
-    <row r="293" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="17"/>
       <c r="E293" s="16"/>
       <c r="BO293" s="19"/>
       <c r="BR293" s="19"/>
     </row>
-    <row r="294" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="17"/>
       <c r="E294" s="16"/>
       <c r="BO294" s="19"/>
       <c r="BR294" s="19"/>
     </row>
-    <row r="295" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="17"/>
       <c r="E295" s="16"/>
       <c r="BO295" s="19"/>
       <c r="BR295" s="19"/>
     </row>
-    <row r="296" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="17"/>
       <c r="E296" s="16"/>
       <c r="BO296" s="19"/>
       <c r="BR296" s="19"/>
     </row>
-    <row r="297" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="17"/>
       <c r="E297" s="16"/>
       <c r="BO297" s="19"/>
       <c r="BR297" s="19"/>
     </row>
-    <row r="298" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="17"/>
       <c r="E298" s="16"/>
       <c r="BO298" s="19"/>
       <c r="BR298" s="19"/>
     </row>
-    <row r="299" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="17"/>
       <c r="E299" s="16"/>
       <c r="BO299" s="19"/>
       <c r="BR299" s="19"/>
     </row>
-    <row r="300" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="17"/>
       <c r="E300" s="16"/>
       <c r="BO300" s="19"/>
       <c r="BR300" s="19"/>
     </row>
-    <row r="301" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="17"/>
       <c r="E301" s="16"/>
       <c r="BO301" s="19"/>
       <c r="BR301" s="19"/>
     </row>
-    <row r="302" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="17"/>
       <c r="E302" s="16"/>
       <c r="BO302" s="19"/>
       <c r="BR302" s="19"/>
     </row>
-    <row r="303" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="17"/>
       <c r="E303" s="16"/>
       <c r="BO303" s="19"/>
       <c r="BR303" s="19"/>
     </row>
-    <row r="304" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="17"/>
       <c r="E304" s="16"/>
       <c r="BO304" s="19"/>
       <c r="BR304" s="19"/>
     </row>
-    <row r="305" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="17"/>
       <c r="E305" s="16"/>
       <c r="BO305" s="19"/>
       <c r="BR305" s="19"/>
     </row>
-    <row r="306" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="17"/>
       <c r="E306" s="16"/>
       <c r="BO306" s="19"/>
       <c r="BR306" s="19"/>
     </row>
-    <row r="307" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="17"/>
       <c r="E307" s="16"/>
       <c r="BO307" s="19"/>
       <c r="BR307" s="19"/>
     </row>
-    <row r="308" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="17"/>
       <c r="E308" s="16"/>
       <c r="BO308" s="19"/>
       <c r="BR308" s="19"/>
     </row>
-    <row r="309" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="17"/>
       <c r="E309" s="16"/>
       <c r="BO309" s="19"/>
       <c r="BR309" s="19"/>
     </row>
-    <row r="310" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="17"/>
       <c r="E310" s="16"/>
       <c r="BO310" s="19"/>
       <c r="BR310" s="19"/>
     </row>
-    <row r="311" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="17"/>
       <c r="E311" s="16"/>
       <c r="BO311" s="19"/>
       <c r="BR311" s="19"/>
     </row>
-    <row r="312" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="17"/>
       <c r="E312" s="16"/>
       <c r="BO312" s="19"/>
       <c r="BR312" s="19"/>
     </row>
-    <row r="313" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="17"/>
       <c r="E313" s="16"/>
       <c r="BO313" s="19"/>
       <c r="BR313" s="19"/>
     </row>
-    <row r="314" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="17"/>
       <c r="E314" s="16"/>
       <c r="BO314" s="19"/>
       <c r="BR314" s="19"/>
     </row>
-    <row r="315" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="17"/>
       <c r="E315" s="16"/>
       <c r="BO315" s="19"/>
       <c r="BR315" s="19"/>
     </row>
-    <row r="316" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="17"/>
       <c r="E316" s="16"/>
       <c r="BO316" s="19"/>
       <c r="BR316" s="19"/>
     </row>
-    <row r="317" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="17"/>
       <c r="E317" s="16"/>
       <c r="BO317" s="19"/>
       <c r="BR317" s="19"/>
     </row>
-    <row r="318" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="17"/>
       <c r="E318" s="16"/>
       <c r="BO318" s="19"/>
       <c r="BR318" s="19"/>
     </row>
-    <row r="319" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="17"/>
       <c r="E319" s="16"/>
       <c r="BO319" s="19"/>
       <c r="BR319" s="19"/>
     </row>
-    <row r="320" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="17"/>
       <c r="E320" s="16"/>
       <c r="BO320" s="19"/>
       <c r="BR320" s="19"/>
     </row>
-    <row r="321" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="17"/>
       <c r="E321" s="16"/>
       <c r="BO321" s="19"/>
       <c r="BR321" s="19"/>
     </row>
-    <row r="322" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="17"/>
       <c r="E322" s="16"/>
       <c r="BO322" s="19"/>
       <c r="BR322" s="19"/>
     </row>
-    <row r="323" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="17"/>
       <c r="E323" s="16"/>
       <c r="BO323" s="19"/>
       <c r="BR323" s="19"/>
     </row>
-    <row r="324" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="17"/>
       <c r="E324" s="16"/>
       <c r="BO324" s="19"/>
       <c r="BR324" s="19"/>
     </row>
-    <row r="325" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="17"/>
       <c r="E325" s="16"/>
       <c r="BO325" s="19"/>
       <c r="BR325" s="19"/>
     </row>
-    <row r="326" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="17"/>
       <c r="E326" s="16"/>
       <c r="BO326" s="19"/>
       <c r="BR326" s="19"/>
     </row>
-    <row r="327" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="17"/>
       <c r="E327" s="16"/>
       <c r="BO327" s="19"/>
       <c r="BR327" s="19"/>
     </row>
-    <row r="328" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="17"/>
       <c r="E328" s="16"/>
       <c r="BO328" s="19"/>
       <c r="BR328" s="19"/>
     </row>
-    <row r="329" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="17"/>
       <c r="E329" s="16"/>
       <c r="BO329" s="19"/>
       <c r="BR329" s="19"/>
     </row>
-    <row r="330" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="17"/>
       <c r="E330" s="16"/>
       <c r="BO330" s="19"/>
       <c r="BR330" s="19"/>
     </row>
-    <row r="331" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="17"/>
       <c r="E331" s="16"/>
       <c r="BO331" s="19"/>
       <c r="BR331" s="19"/>
     </row>
-    <row r="332" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="17"/>
       <c r="E332" s="16"/>
       <c r="BO332" s="19"/>
       <c r="BR332" s="19"/>
     </row>
-    <row r="333" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="17"/>
       <c r="E333" s="16"/>
       <c r="BO333" s="19"/>
       <c r="BR333" s="19"/>
     </row>
-    <row r="334" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="17"/>
       <c r="E334" s="16"/>
       <c r="BR334" s="19"/>
     </row>
-    <row r="335" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="17"/>
       <c r="E335" s="16"/>
       <c r="BR335" s="19"/>
     </row>
-    <row r="336" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="17"/>
       <c r="E336" s="16"/>
       <c r="BR336" s="19"/>
     </row>
-    <row r="337" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="17"/>
       <c r="E337" s="16"/>
       <c r="BO337" s="19"/>
       <c r="BR337" s="19"/>
     </row>
-    <row r="338" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="17"/>
       <c r="E338" s="16"/>
       <c r="BO338" s="19"/>
       <c r="BR338" s="19"/>
     </row>
-    <row r="339" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="17"/>
       <c r="E339" s="16"/>
       <c r="BO339" s="19"/>
       <c r="BR339" s="19"/>
     </row>
-    <row r="340" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="17"/>
       <c r="E340" s="16"/>
       <c r="BO340" s="19"/>
       <c r="BR340" s="19"/>
     </row>
-    <row r="341" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="17"/>
       <c r="E341" s="16"/>
       <c r="BO341" s="19"/>
       <c r="BR341" s="19"/>
     </row>
-    <row r="342" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="17"/>
       <c r="E342" s="16"/>
       <c r="BO342" s="19"/>
       <c r="BR342" s="19"/>
     </row>
-    <row r="343" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="17"/>
       <c r="E343" s="16"/>
       <c r="BO343" s="19"/>
       <c r="BR343" s="19"/>
     </row>
-    <row r="344" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="17"/>
       <c r="E344" s="16"/>
       <c r="BO344" s="19"/>
       <c r="BR344" s="19"/>
     </row>
-    <row r="345" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="17"/>
       <c r="E345" s="16"/>
       <c r="BO345" s="19"/>
       <c r="BR345" s="19"/>
     </row>
-    <row r="346" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="17"/>
       <c r="E346" s="16"/>
       <c r="BO346" s="19"/>
       <c r="BR346" s="19"/>
     </row>
-    <row r="347" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="17"/>
       <c r="E347" s="16"/>
       <c r="BO347" s="19"/>
       <c r="BR347" s="19"/>
     </row>
-    <row r="348" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="17"/>
       <c r="E348" s="16"/>
       <c r="BO348" s="19"/>
       <c r="BR348" s="19"/>
     </row>
-    <row r="349" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="17"/>
       <c r="E349" s="16"/>
       <c r="BO349" s="19"/>
       <c r="BR349" s="19"/>
     </row>
-    <row r="350" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="17"/>
       <c r="E350" s="16"/>
       <c r="BO350" s="19"/>
       <c r="BR350" s="19"/>
     </row>
-    <row r="351" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="17"/>
       <c r="E351" s="16"/>
       <c r="BO351" s="19"/>
       <c r="BR351" s="19"/>
     </row>
-    <row r="352" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="17"/>
       <c r="E352" s="16"/>
       <c r="BO352" s="19"/>
       <c r="BR352" s="19"/>
     </row>
-    <row r="353" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="17"/>
       <c r="E353" s="16"/>
       <c r="BO353" s="19"/>
       <c r="BR353" s="19"/>
     </row>
-    <row r="354" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="17"/>
       <c r="E354" s="16"/>
       <c r="BO354" s="19"/>
       <c r="BR354" s="19"/>
     </row>
-    <row r="355" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="17"/>
       <c r="E355" s="16"/>
       <c r="BO355" s="19"/>
       <c r="BR355" s="19"/>
     </row>
-    <row r="356" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="17"/>
       <c r="E356" s="16"/>
       <c r="BO356" s="19"/>
       <c r="BR356" s="19"/>
     </row>
-    <row r="357" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="17"/>
       <c r="E357" s="16"/>
       <c r="BO357" s="19"/>
       <c r="BR357" s="19"/>
     </row>
-    <row r="358" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="17"/>
       <c r="E358" s="16"/>
       <c r="BO358" s="19"/>
       <c r="BR358" s="19"/>
     </row>
-    <row r="359" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="17"/>
       <c r="E359" s="16"/>
       <c r="BO359" s="19"/>
       <c r="BR359" s="19"/>
     </row>
-    <row r="360" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="17"/>
       <c r="E360" s="16"/>
       <c r="BO360" s="19"/>
       <c r="BR360" s="19"/>
     </row>
-    <row r="361" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="17"/>
       <c r="E361" s="16"/>
       <c r="BO361" s="19"/>
       <c r="BR361" s="19"/>
     </row>
-    <row r="362" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="17"/>
       <c r="E362" s="16"/>
       <c r="BO362" s="19"/>
       <c r="BR362" s="19"/>
     </row>
-    <row r="363" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="17"/>
       <c r="E363" s="16"/>
       <c r="BO363" s="19"/>
       <c r="BR363" s="19"/>
     </row>
-    <row r="364" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="17"/>
       <c r="E364" s="16"/>
       <c r="BO364" s="19"/>
       <c r="BR364" s="19"/>
     </row>
-    <row r="365" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="17"/>
       <c r="E365" s="16"/>
       <c r="BO365" s="19"/>
       <c r="BR365" s="19"/>
     </row>
-    <row r="366" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="17"/>
       <c r="E366" s="16"/>
       <c r="BO366" s="19"/>
       <c r="BR366" s="19"/>
     </row>
-    <row r="367" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="17"/>
       <c r="E367" s="16"/>
       <c r="BO367" s="19"/>
       <c r="BR367" s="19"/>
     </row>
-    <row r="368" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="17"/>
       <c r="E368" s="16"/>
       <c r="BO368" s="19"/>
       <c r="BR368" s="19"/>
     </row>
-    <row r="369" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="17"/>
       <c r="E369" s="16"/>
       <c r="BO369" s="19"/>
       <c r="BR369" s="19"/>
     </row>
-    <row r="370" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="17"/>
       <c r="E370" s="16"/>
       <c r="BO370" s="19"/>
       <c r="BR370" s="19"/>
     </row>
-    <row r="371" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="17"/>
       <c r="E371" s="16"/>
       <c r="BR371" s="19"/>
     </row>
-    <row r="372" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="17"/>
       <c r="E372" s="16"/>
       <c r="BR372" s="19"/>
     </row>
-    <row r="373" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="17"/>
       <c r="E373" s="16"/>
       <c r="BO373" s="19"/>
       <c r="BR373" s="19"/>
     </row>
-    <row r="374" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="17"/>
       <c r="E374" s="16"/>
       <c r="BO374" s="19"/>
       <c r="BR374" s="19"/>
     </row>
-    <row r="375" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="17"/>
       <c r="E375" s="16"/>
       <c r="BO375" s="19"/>
       <c r="BR375" s="19"/>
     </row>
-    <row r="376" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="17"/>
       <c r="E376" s="16"/>
       <c r="BO376" s="19"/>
       <c r="BR376" s="19"/>
     </row>
-    <row r="377" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="17"/>
       <c r="E377" s="16"/>
       <c r="BO377" s="19"/>
       <c r="BR377" s="19"/>
     </row>
-    <row r="378" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="17"/>
       <c r="E378" s="16"/>
       <c r="BO378" s="19"/>
       <c r="BR378" s="19"/>
     </row>
-    <row r="379" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="17"/>
       <c r="E379" s="16"/>
       <c r="BO379" s="19"/>
       <c r="BR379" s="19"/>
     </row>
-    <row r="380" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="17"/>
       <c r="E380" s="16"/>
       <c r="BO380" s="19"/>
       <c r="BR380" s="19"/>
     </row>
-    <row r="381" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="17"/>
       <c r="E381" s="16"/>
       <c r="BO381" s="19"/>
       <c r="BR381" s="19"/>
     </row>
-    <row r="382" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="17"/>
       <c r="E382" s="16"/>
       <c r="BO382" s="19"/>
       <c r="BR382" s="19"/>
     </row>
-    <row r="383" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="17"/>
       <c r="E383" s="16"/>
       <c r="BO383" s="19"/>
       <c r="BR383" s="19"/>
     </row>
-    <row r="384" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="17"/>
       <c r="E384" s="16"/>
       <c r="BO384" s="19"/>
       <c r="BR384" s="19"/>
     </row>
-    <row r="385" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="17"/>
       <c r="E385" s="16"/>
       <c r="BO385" s="19"/>
       <c r="BR385" s="19"/>
     </row>
-    <row r="386" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="17"/>
       <c r="E386" s="16"/>
       <c r="BO386" s="19"/>
       <c r="BR386" s="19"/>
     </row>
-    <row r="387" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="17"/>
       <c r="E387" s="16"/>
       <c r="BO387" s="19"/>
       <c r="BR387" s="19"/>
     </row>
-    <row r="388" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="17"/>
       <c r="E388" s="16"/>
       <c r="BO388" s="19"/>
       <c r="BR388" s="19"/>
     </row>
-    <row r="389" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="17"/>
       <c r="E389" s="16"/>
       <c r="BO389" s="19"/>
       <c r="BR389" s="19"/>
     </row>
-    <row r="390" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="17"/>
       <c r="E390" s="16"/>
       <c r="BO390" s="19"/>
       <c r="BR390" s="19"/>
     </row>
-    <row r="391" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="17"/>
       <c r="E391" s="16"/>
       <c r="BO391" s="19"/>
       <c r="BR391" s="19"/>
     </row>
-    <row r="392" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="17"/>
       <c r="E392" s="16"/>
       <c r="BO392" s="19"/>
       <c r="BR392" s="19"/>
     </row>
-    <row r="393" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="17"/>
       <c r="E393" s="16"/>
       <c r="BO393" s="19"/>
       <c r="BR393" s="19"/>
     </row>
-    <row r="394" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="17"/>
       <c r="E394" s="16"/>
       <c r="BO394" s="19"/>
       <c r="BR394" s="19"/>
     </row>
-    <row r="395" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="17"/>
       <c r="E395" s="16"/>
       <c r="BO395" s="19"/>
       <c r="BR395" s="19"/>
     </row>
-    <row r="396" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="17"/>
       <c r="E396" s="16"/>
       <c r="BR396" s="19"/>
     </row>
-    <row r="397" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="17"/>
       <c r="E397" s="16"/>
       <c r="BR397" s="19"/>
     </row>
-    <row r="398" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="17"/>
       <c r="E398" s="16"/>
       <c r="BO398" s="19"/>
       <c r="BR398" s="19"/>
     </row>
-    <row r="399" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="17"/>
       <c r="E399" s="16"/>
       <c r="BO399" s="19"/>
       <c r="BR399" s="19"/>
     </row>
-    <row r="400" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="17"/>
       <c r="E400" s="16"/>
       <c r="BR400" s="19"/>
     </row>
-    <row r="401" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="17"/>
       <c r="E401" s="16"/>
       <c r="BR401" s="19"/>
     </row>
-    <row r="402" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="17"/>
       <c r="E402" s="16"/>
       <c r="BO402" s="19"/>
       <c r="BR402" s="19"/>
     </row>
-    <row r="403" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="17"/>
       <c r="E403" s="16"/>
       <c r="BO403" s="19"/>
       <c r="BR403" s="19"/>
     </row>
-    <row r="404" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="17"/>
       <c r="E404" s="16"/>
       <c r="BO404" s="19"/>
       <c r="BR404" s="19"/>
     </row>
-    <row r="405" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="17"/>
       <c r="E405" s="16"/>
       <c r="BO405" s="19"/>
       <c r="BR405" s="19"/>
     </row>
-    <row r="406" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="17"/>
       <c r="E406" s="16"/>
       <c r="BO406" s="19"/>
       <c r="BR406" s="19"/>
     </row>
-    <row r="407" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="17"/>
       <c r="E407" s="16"/>
       <c r="BO407" s="19"/>
       <c r="BR407" s="19"/>
     </row>
-    <row r="408" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="17"/>
       <c r="E408" s="16"/>
       <c r="BO408" s="19"/>
       <c r="BR408" s="19"/>
     </row>
-    <row r="409" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="17"/>
       <c r="E409" s="16"/>
       <c r="BO409" s="19"/>
       <c r="BR409" s="19"/>
     </row>
-    <row r="410" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="17"/>
       <c r="E410" s="16"/>
       <c r="BO410" s="19"/>
       <c r="BR410" s="19"/>
     </row>
-    <row r="411" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="17"/>
       <c r="E411" s="16"/>
       <c r="BO411" s="19"/>
       <c r="BR411" s="19"/>
     </row>
-    <row r="412" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="17"/>
       <c r="E412" s="16"/>
       <c r="BO412" s="19"/>
       <c r="BR412" s="19"/>
     </row>
-    <row r="413" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="17"/>
       <c r="E413" s="16"/>
       <c r="BO413" s="19"/>
       <c r="BR413" s="19"/>
     </row>
-    <row r="414" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="17"/>
       <c r="E414" s="16"/>
       <c r="BO414" s="19"/>
       <c r="BR414" s="19"/>
     </row>
-    <row r="415" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="17"/>
       <c r="E415" s="16"/>
       <c r="BO415" s="19"/>
       <c r="BR415" s="19"/>
     </row>
-    <row r="416" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="17"/>
       <c r="E416" s="16"/>
       <c r="BO416" s="19"/>
       <c r="BR416" s="19"/>
     </row>
-    <row r="417" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D417" s="17"/>
       <c r="E417" s="16"/>
       <c r="BO417" s="19"/>
       <c r="BR417" s="19"/>
     </row>
-    <row r="418" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D418" s="17"/>
       <c r="E418" s="16"/>
       <c r="BO418" s="19"/>
       <c r="BR418" s="19"/>
     </row>
-    <row r="419" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D419" s="17"/>
       <c r="E419" s="16"/>
     </row>
-    <row r="420" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D420" s="17"/>
       <c r="E420" s="16"/>
     </row>
-    <row r="421" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D421" s="17"/>
       <c r="E421" s="16"/>
     </row>
-    <row r="422" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D422" s="17"/>
       <c r="E422" s="16"/>
     </row>
-    <row r="423" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D423" s="17"/>
       <c r="E423" s="16"/>
     </row>
-    <row r="424" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D424" s="17"/>
       <c r="E424" s="16"/>
     </row>
-    <row r="425" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D425" s="17"/>
       <c r="E425" s="16"/>
     </row>
-    <row r="426" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D426" s="17"/>
       <c r="E426" s="16"/>
     </row>
-    <row r="427" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D427" s="17"/>
       <c r="E427" s="16"/>
     </row>
-    <row r="428" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D428" s="17"/>
       <c r="E428" s="16"/>
     </row>
-    <row r="429" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D429" s="17"/>
       <c r="E429" s="16"/>
     </row>
-    <row r="430" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D430" s="17"/>
       <c r="E430" s="16"/>
     </row>
-    <row r="431" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D431" s="17"/>
       <c r="E431" s="16"/>
     </row>
-    <row r="432" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D432" s="17"/>
       <c r="E432" s="16"/>
     </row>
-    <row r="433" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D433" s="17"/>
       <c r="E433" s="16"/>
     </row>
-    <row r="434" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D434" s="17"/>
       <c r="E434" s="16"/>
     </row>
-    <row r="435" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D435" s="17"/>
       <c r="E435" s="16"/>
     </row>
-    <row r="436" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D436" s="17"/>
       <c r="E436" s="16"/>
     </row>
-    <row r="437" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D437" s="17"/>
       <c r="E437" s="16"/>
     </row>
-    <row r="438" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D438" s="17"/>
       <c r="E438" s="16"/>
     </row>
-    <row r="439" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D439" s="17"/>
       <c r="E439" s="16"/>
     </row>
-    <row r="440" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D440" s="17"/>
       <c r="E440" s="16"/>
     </row>
-    <row r="441" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D441" s="17"/>
       <c r="E441" s="16"/>
     </row>
-    <row r="442" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D442" s="17"/>
       <c r="E442" s="16"/>
     </row>
-    <row r="443" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D443" s="17"/>
       <c r="E443" s="16"/>
     </row>
-    <row r="444" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D444" s="17"/>
       <c r="E444" s="16"/>
     </row>
-    <row r="445" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D445" s="17"/>
       <c r="E445" s="16"/>
     </row>
-    <row r="446" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D446" s="17"/>
       <c r="E446" s="16"/>
     </row>
-    <row r="447" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D447" s="17"/>
       <c r="E447" s="16"/>
     </row>
-    <row r="448" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D448" s="17"/>
       <c r="E448" s="16"/>
     </row>
-    <row r="449" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D449" s="17"/>
       <c r="E449" s="16"/>
     </row>
-    <row r="450" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D450" s="17"/>
       <c r="E450" s="16"/>
     </row>
-    <row r="451" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D451" s="17"/>
       <c r="E451" s="16"/>
     </row>
-    <row r="452" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D452" s="17"/>
       <c r="E452" s="16"/>
     </row>
-    <row r="453" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D453" s="17"/>
       <c r="E453" s="16"/>
     </row>
-    <row r="454" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D454" s="17"/>
       <c r="E454" s="16"/>
     </row>
-    <row r="455" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D455" s="17"/>
       <c r="E455" s="16"/>
     </row>
-    <row r="456" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D456" s="17"/>
       <c r="E456" s="16"/>
     </row>
-    <row r="457" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D457" s="17"/>
       <c r="E457" s="16"/>
     </row>
-    <row r="458" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D458" s="17"/>
       <c r="E458" s="16"/>
     </row>
-    <row r="459" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D459" s="17"/>
       <c r="E459" s="16"/>
     </row>
-    <row r="460" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D460" s="17"/>
       <c r="E460" s="16"/>
     </row>
-    <row r="461" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D461" s="17"/>
       <c r="E461" s="16"/>
     </row>
-    <row r="462" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D462" s="17"/>
       <c r="E462" s="16"/>
     </row>
-    <row r="463" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D463" s="17"/>
       <c r="E463" s="16"/>
     </row>
-    <row r="464" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D464" s="17"/>
       <c r="E464" s="16"/>
     </row>
-    <row r="465" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D465" s="17"/>
       <c r="E465" s="16"/>
     </row>
-    <row r="466" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D466" s="17"/>
       <c r="E466" s="16"/>
     </row>
-    <row r="467" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D467" s="17"/>
       <c r="E467" s="16"/>
     </row>
-    <row r="468" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D468" s="17"/>
       <c r="E468" s="16"/>
     </row>
-    <row r="469" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D469" s="17"/>
       <c r="E469" s="16"/>
     </row>
-    <row r="470" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D470" s="17"/>
       <c r="E470" s="16"/>
     </row>
-    <row r="471" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D471" s="17"/>
       <c r="E471" s="16"/>
     </row>
-    <row r="472" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D472" s="17"/>
       <c r="E472" s="16"/>
     </row>
-    <row r="473" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D473" s="17"/>
       <c r="E473" s="16"/>
     </row>
-    <row r="474" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D474" s="17"/>
       <c r="E474" s="16"/>
     </row>
-    <row r="475" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D475" s="17"/>
       <c r="E475" s="16"/>
     </row>
-    <row r="476" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D476" s="17"/>
       <c r="E476" s="16"/>
     </row>
-    <row r="477" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D477" s="17"/>
       <c r="E477" s="16"/>
     </row>
-    <row r="478" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D478" s="17"/>
       <c r="E478" s="16"/>
     </row>
-    <row r="479" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D479" s="17"/>
       <c r="E479" s="16"/>
     </row>
-    <row r="480" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D480" s="17"/>
       <c r="E480" s="16"/>
     </row>
-    <row r="481" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D481" s="17"/>
       <c r="E481" s="16"/>
     </row>
-    <row r="482" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D482" s="17"/>
       <c r="E482" s="16"/>
     </row>
-    <row r="483" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D483" s="17"/>
       <c r="E483" s="16"/>
     </row>
-    <row r="484" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D484" s="17"/>
       <c r="E484" s="16"/>
     </row>
-    <row r="485" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D485" s="17"/>
       <c r="E485" s="16"/>
     </row>
-    <row r="486" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D486" s="17"/>
       <c r="E486" s="16"/>
     </row>
-    <row r="487" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D487" s="17"/>
       <c r="E487" s="16"/>
     </row>
-    <row r="488" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D488" s="17"/>
       <c r="E488" s="16"/>
     </row>
-    <row r="489" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D489" s="17"/>
       <c r="E489" s="16"/>
     </row>
-    <row r="490" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D490" s="17"/>
       <c r="E490" s="16"/>
     </row>
-    <row r="491" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D491" s="17"/>
       <c r="E491" s="16"/>
     </row>
-    <row r="492" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D492" s="17"/>
       <c r="E492" s="16"/>
     </row>
-    <row r="493" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D493" s="17"/>
       <c r="E493" s="16"/>
     </row>
-    <row r="494" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D494" s="17"/>
       <c r="E494" s="16"/>
     </row>
-    <row r="495" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D495" s="17"/>
       <c r="E495" s="16"/>
     </row>
-    <row r="496" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D496" s="17"/>
       <c r="E496" s="16"/>
     </row>
-    <row r="497" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D497" s="17"/>
       <c r="E497" s="16"/>
     </row>
-    <row r="498" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D498" s="17"/>
       <c r="E498" s="16"/>
     </row>
-    <row r="566" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="566" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D566" s="17"/>
       <c r="E566" s="16"/>
     </row>
-    <row r="567" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="567" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D567" s="17"/>
       <c r="E567" s="16"/>
     </row>
-    <row r="568" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="568" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D568" s="17"/>
       <c r="E568" s="16"/>
     </row>
-    <row r="569" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="569" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D569" s="17"/>
       <c r="E569" s="16"/>
     </row>
-    <row r="570" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="570" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D570" s="17"/>
       <c r="E570" s="16"/>
     </row>
-    <row r="571" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="571" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D571" s="17"/>
       <c r="E571" s="16"/>
     </row>
-    <row r="572" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="572" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D572" s="17"/>
       <c r="E572" s="16"/>
     </row>
-    <row r="573" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="573" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D573" s="17"/>
       <c r="E573" s="16"/>
     </row>
-    <row r="574" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="574" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D574" s="17"/>
       <c r="E574" s="16"/>
     </row>
-    <row r="575" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="575" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D575" s="17"/>
       <c r="E575" s="16"/>
     </row>
-    <row r="576" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="576" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D576" s="17"/>
       <c r="E576" s="16"/>
     </row>
-    <row r="577" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="577" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D577" s="17"/>
       <c r="E577" s="16"/>
     </row>
-    <row r="578" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="578" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D578" s="17"/>
       <c r="E578" s="16"/>
     </row>
-    <row r="579" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="579" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D579" s="17"/>
       <c r="E579" s="16"/>
     </row>
-    <row r="580" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="580" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D580" s="17"/>
       <c r="E580" s="16"/>
     </row>
-    <row r="581" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="581" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D581" s="17"/>
       <c r="E581" s="16"/>
     </row>
-    <row r="582" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="582" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D582" s="17"/>
       <c r="E582" s="16"/>
     </row>
-    <row r="583" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="583" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D583" s="17"/>
       <c r="E583" s="16"/>
     </row>
-    <row r="584" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="584" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D584" s="17"/>
       <c r="E584" s="16"/>
     </row>
-    <row r="585" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="585" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D585" s="17"/>
       <c r="E585" s="16"/>
     </row>
-    <row r="586" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="586" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D586" s="17"/>
       <c r="E586" s="16"/>
     </row>
-    <row r="587" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="587" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D587" s="17"/>
       <c r="E587" s="16"/>
     </row>
-    <row r="588" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="588" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D588" s="17"/>
       <c r="E588" s="16"/>
     </row>
-    <row r="589" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D589" s="17"/>
       <c r="E589" s="16"/>
     </row>
-    <row r="590" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D590" s="17"/>
       <c r="E590" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -6298,84 +6407,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DH815"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08984375" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="7.7265625" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" customWidth="1"/>
-    <col min="6" max="6" width="31.36328125" customWidth="1"/>
-    <col min="7" max="7" width="7.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.81640625" customWidth="1"/>
-    <col min="9" max="9" width="7.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="11" max="13" width="8.36328125" style="4" customWidth="1"/>
-    <col min="14" max="14" width="11.7265625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="13.08984375" style="4" customWidth="1"/>
-    <col min="16" max="16" width="11.54296875" style="4" customWidth="1"/>
-    <col min="17" max="17" width="21.453125" style="4" customWidth="1"/>
-    <col min="18" max="18" width="19.81640625" style="4" customWidth="1"/>
-    <col min="19" max="19" width="16.54296875" style="4" customWidth="1"/>
-    <col min="20" max="20" width="19.08984375" style="4" customWidth="1"/>
-    <col min="21" max="21" width="18.36328125" style="4" customWidth="1"/>
-    <col min="22" max="22" width="17.7265625" style="4" customWidth="1"/>
-    <col min="23" max="23" width="8.36328125" style="4" customWidth="1"/>
-    <col min="24" max="24" width="18.453125" style="4" customWidth="1"/>
-    <col min="25" max="25" width="16.54296875" customWidth="1"/>
-    <col min="26" max="26" width="10.6328125" customWidth="1"/>
-    <col min="27" max="27" width="8.36328125" customWidth="1"/>
-    <col min="28" max="28" width="15.1796875" customWidth="1"/>
-    <col min="29" max="30" width="8.54296875" customWidth="1"/>
-    <col min="31" max="31" width="13.453125" customWidth="1"/>
-    <col min="32" max="32" width="13.7265625" customWidth="1"/>
-    <col min="33" max="33" width="14.54296875" customWidth="1"/>
-    <col min="34" max="34" width="17.453125" customWidth="1"/>
-    <col min="35" max="35" width="8.54296875" customWidth="1"/>
-    <col min="36" max="36" width="12.453125" customWidth="1"/>
-    <col min="37" max="37" width="8.54296875" customWidth="1"/>
-    <col min="38" max="39" width="8.36328125" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="4" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="4" customWidth="1"/>
+    <col min="17" max="17" width="21.5" style="4" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" style="4" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" style="4" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="4" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="4" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" style="4" customWidth="1"/>
+    <col min="24" max="24" width="18.5" style="4" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.26953125" customWidth="1"/>
-    <col min="42" max="43" width="11.81640625" customWidth="1"/>
-    <col min="44" max="44" width="18.453125" customWidth="1"/>
-    <col min="45" max="45" width="12.26953125" customWidth="1"/>
-    <col min="46" max="46" width="11.90625" customWidth="1"/>
-    <col min="47" max="47" width="19.54296875" customWidth="1"/>
-    <col min="48" max="48" width="12.6328125" customWidth="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1"/>
+    <col min="42" max="43" width="11.83203125" customWidth="1"/>
+    <col min="44" max="44" width="18.4140625" customWidth="1"/>
+    <col min="45" max="45" width="12.25" customWidth="1"/>
+    <col min="46" max="46" width="11.9140625" customWidth="1"/>
+    <col min="47" max="47" width="19.58203125" customWidth="1"/>
+    <col min="48" max="48" width="12.6640625" customWidth="1"/>
     <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.7265625" customWidth="1"/>
-    <col min="52" max="52" width="19.7265625" customWidth="1"/>
-    <col min="53" max="53" width="5.08984375" customWidth="1"/>
-    <col min="54" max="54" width="8.453125" customWidth="1"/>
-    <col min="55" max="55" width="13.453125" customWidth="1"/>
-    <col min="56" max="56" width="14.6328125" customWidth="1"/>
-    <col min="57" max="57" width="10.1796875" customWidth="1"/>
-    <col min="58" max="58" width="8.26953125" customWidth="1"/>
-    <col min="59" max="65" width="8.36328125" customWidth="1"/>
-    <col min="66" max="68" width="11.26953125" customWidth="1"/>
-    <col min="69" max="69" width="6.54296875" customWidth="1"/>
+    <col min="51" max="51" width="11.75" customWidth="1"/>
+    <col min="52" max="52" width="19.75" customWidth="1"/>
+    <col min="53" max="53" width="5.08203125" customWidth="1"/>
+    <col min="54" max="54" width="8.5" customWidth="1"/>
+    <col min="55" max="55" width="13.5" customWidth="1"/>
+    <col min="56" max="56" width="14.6640625" customWidth="1"/>
+    <col min="57" max="57" width="10.1640625" customWidth="1"/>
+    <col min="58" max="58" width="8.25" customWidth="1"/>
+    <col min="59" max="65" width="8.33203125" customWidth="1"/>
+    <col min="66" max="68" width="11.25" customWidth="1"/>
+    <col min="69" max="69" width="6.58203125" customWidth="1"/>
     <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.36328125" style="5" customWidth="1"/>
-    <col min="73" max="74" width="8.453125" style="5" customWidth="1"/>
-    <col min="75" max="76" width="7.81640625" style="5" customWidth="1"/>
-    <col min="77" max="77" width="22.1796875" style="5" customWidth="1"/>
-    <col min="78" max="78" width="13.453125" customWidth="1"/>
-    <col min="79" max="79" width="21.1796875" customWidth="1"/>
-    <col min="80" max="80" width="15.7265625" customWidth="1"/>
-    <col min="81" max="81" width="15.54296875" customWidth="1"/>
-    <col min="82" max="82" width="12.81640625" customWidth="1"/>
-    <col min="83" max="83" width="16.1796875" customWidth="1"/>
+    <col min="72" max="72" width="7.33203125" style="5" customWidth="1"/>
+    <col min="73" max="74" width="8.5" style="5" customWidth="1"/>
+    <col min="75" max="76" width="7.83203125" style="5" customWidth="1"/>
+    <col min="77" max="77" width="22.1640625" style="5" customWidth="1"/>
+    <col min="78" max="78" width="13.5" customWidth="1"/>
+    <col min="79" max="79" width="21.1640625" customWidth="1"/>
+    <col min="80" max="80" width="15.75" customWidth="1"/>
+    <col min="81" max="81" width="15.58203125" customWidth="1"/>
+    <col min="82" max="82" width="12.83203125" customWidth="1"/>
+    <col min="83" max="83" width="16.1640625" customWidth="1"/>
     <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.81640625" customWidth="1"/>
-    <col min="88" max="88" width="23.54296875" customWidth="1"/>
-    <col min="89" max="89" width="12.81640625" customWidth="1"/>
-    <col min="90" max="90" width="17.08984375" customWidth="1"/>
+    <col min="86" max="87" width="12.83203125" customWidth="1"/>
+    <col min="88" max="88" width="23.58203125" customWidth="1"/>
+    <col min="89" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="17.08203125" customWidth="1"/>
     <col min="97" max="97" width="14" customWidth="1"/>
     <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08984375" customWidth="1"/>
-    <col min="101" max="101" width="13.7265625" customWidth="1"/>
-    <col min="108" max="108" width="15.453125" customWidth="1"/>
+    <col min="100" max="100" width="11.08203125" customWidth="1"/>
+    <col min="101" max="101" width="13.75" customWidth="1"/>
+    <col min="108" max="108" width="15.5" customWidth="1"/>
     <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10512,7 +10621,7 @@
       <c r="CJ815" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -10521,21 +10630,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.08984375" customWidth="1"/>
-    <col min="15" max="15" width="9.453125" customWidth="1"/>
-    <col min="16" max="16" width="22.1796875" customWidth="1"/>
-    <col min="17" max="17" width="12.81640625" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10572,11 +10680,8 @@
       <c r="O1" t="s">
         <v>485</v>
       </c>
-      <c r="P1" s="20" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10619,14 +10724,11 @@
       <c r="O2" t="s">
         <v>495</v>
       </c>
-      <c r="P2" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="P2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10670,13 +10772,10 @@
         <v>343</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>398</v>
       </c>
@@ -10689,11 +10788,11 @@
       <c r="J4" t="s">
         <v>497</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="P4" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>408</v>
       </c>
@@ -10706,11 +10805,11 @@
       <c r="J5" t="s">
         <v>500</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="P5" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>410</v>
       </c>
@@ -10720,12 +10819,11 @@
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="P6"/>
-      <c r="Q6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>503</v>
       </c>
@@ -10738,11 +10836,11 @@
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="P7" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>506</v>
       </c>
@@ -10755,11 +10853,11 @@
       <c r="N8">
         <v>1</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="P8" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>415</v>
       </c>
@@ -10770,9 +10868,8 @@
         <v>1</v>
       </c>
       <c r="K9"/>
-      <c r="P9"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>437</v>
       </c>
@@ -10782,11 +10879,11 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="P10" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>435</v>
       </c>
@@ -10797,9 +10894,8 @@
         <v>1</v>
       </c>
       <c r="K11"/>
-      <c r="P11"/>
-    </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>433</v>
       </c>
@@ -10810,20 +10906,19 @@
         <v>1</v>
       </c>
       <c r="K12"/>
-      <c r="P12"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>509</v>
       </c>
       <c r="C13" t="s">
         <v>231</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="P13" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>450</v>
       </c>
@@ -10834,12 +10929,11 @@
         <v>1</v>
       </c>
       <c r="J14"/>
-      <c r="P14"/>
-      <c r="Q14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>512</v>
       </c>
@@ -10852,11 +10946,11 @@
       <c r="J15" t="s">
         <v>500</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="P15" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>513</v>
       </c>
@@ -10867,7 +10961,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>515</v>
       </c>
@@ -10878,7 +10972,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>517</v>
       </c>
@@ -10889,7 +10983,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>519</v>
       </c>
@@ -10900,7 +10994,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>390</v>
       </c>
@@ -10913,20 +11007,19 @@
       <c r="J20" t="s">
         <v>521</v>
       </c>
-      <c r="P20"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>522</v>
       </c>
       <c r="C21" t="s">
         <v>231</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="P21" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>414</v>
       </c>
@@ -10938,7 +11031,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -10947,11 +11040,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" customWidth="1"/>
-    <col min="4" max="4" width="27.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10991,7 +11084,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -11000,11 +11093,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="3" max="3" width="27.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11092,7 +11185,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -11101,13 +11194,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08984375" customWidth="1"/>
-    <col min="5" max="10" width="11.26953125" customWidth="1"/>
-    <col min="11" max="11" width="6.36328125" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11319,7 +11412,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -11329,15 +11422,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A2:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="47.81640625" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -11405,7 +11498,117 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85EE8CB0-B427-4844-821D-4F02A6E9CDE7}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="20"/>
+    <col min="2" max="2" width="13.83203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="20" customWidth="1"/>
+    <col min="7" max="7" width="15" style="20" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="20" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>572</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>576</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>584</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A24E17E-B627-42C0-91BB-D9F005CFF0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7E0BEB-407A-433A-99E2-165B81C1A651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="587">
   <si>
     <t>Id</t>
   </si>
@@ -2081,6 +2081,14 @@
   </si>
   <si>
     <t>string?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可无视buff抑制检测</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsCancelable</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -10630,7 +10638,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -10639,11 +10647,12 @@
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="14" max="14" width="16.08203125" customWidth="1"/>
     <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="16" max="16" width="19.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10680,8 +10689,11 @@
       <c r="O1" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P1" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10724,11 +10736,14 @@
       <c r="O2" t="s">
         <v>495</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="Q2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10772,10 +10787,13 @@
         <v>343</v>
       </c>
       <c r="P3" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>398</v>
       </c>
@@ -10788,11 +10806,11 @@
       <c r="J4" t="s">
         <v>497</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>408</v>
       </c>
@@ -10805,11 +10823,11 @@
       <c r="J5" t="s">
         <v>500</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>410</v>
       </c>
@@ -10819,11 +10837,11 @@
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>503</v>
       </c>
@@ -10836,11 +10854,11 @@
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>506</v>
       </c>
@@ -10853,11 +10871,11 @@
       <c r="N8">
         <v>1</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>415</v>
       </c>
@@ -10869,7 +10887,7 @@
       </c>
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>437</v>
       </c>
@@ -10879,11 +10897,11 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>435</v>
       </c>
@@ -10895,7 +10913,7 @@
       </c>
       <c r="K11"/>
     </row>
-    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>433</v>
       </c>
@@ -10907,18 +10925,18 @@
       </c>
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>509</v>
       </c>
       <c r="C13" t="s">
         <v>231</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>450</v>
       </c>
@@ -10929,11 +10947,11 @@
         <v>1</v>
       </c>
       <c r="J14"/>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>512</v>
       </c>
@@ -10946,11 +10964,11 @@
       <c r="J15" t="s">
         <v>500</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>513</v>
       </c>
@@ -10961,7 +10979,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>515</v>
       </c>
@@ -10972,7 +10990,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>517</v>
       </c>
@@ -10983,7 +11001,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>519</v>
       </c>
@@ -10994,7 +11012,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>390</v>
       </c>
@@ -11008,18 +11026,18 @@
         <v>521</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>522</v>
       </c>
       <c r="C21" t="s">
         <v>231</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>414</v>
       </c>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7E0BEB-407A-433A-99E2-165B81C1A651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78892753-F74A-4F3B-9213-187921244F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3338" yWindow="1421" windowWidth="17953" windowHeight="10398" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -2084,12 +2084,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>可无视buff抑制检测</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsCancelable</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>不可被抵挡</t>
+  </si>
+  <si>
+    <t>NotCancelable</t>
   </si>
 </sst>
 </file>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78892753-F74A-4F3B-9213-187921244F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C83589-2C1C-4405-B106-95A5CF2C0F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3338" yWindow="1421" windowWidth="17953" windowHeight="10398" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="586">
   <si>
     <t>Id</t>
   </si>
@@ -2077,10 +2077,6 @@
   </si>
   <si>
     <t>bool</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>string?</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -10688,7 +10684,7 @@
         <v>485</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10735,7 +10731,7 @@
         <v>495</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="Q2" t="s">
         <v>349</v>
@@ -11527,12 +11523,12 @@
     <col min="1" max="1" width="8.6640625" style="20"/>
     <col min="2" max="2" width="13.83203125" style="20" customWidth="1"/>
     <col min="3" max="3" width="20.58203125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="13.1640625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="20" customWidth="1"/>
-    <col min="7" max="7" width="15" style="20" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" style="20" customWidth="1"/>
-    <col min="9" max="9" width="14.25" style="20" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="39.5" style="20" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="32.25" style="20" customWidth="1"/>
+    <col min="9" max="9" width="39.9140625" style="20" customWidth="1"/>
     <col min="10" max="16384" width="8.6640625" style="20"/>
   </cols>
   <sheetData>
@@ -11614,13 +11610,13 @@
         <v>582</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C83589-2C1C-4405-B106-95A5CF2C0F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBCC442-3644-4C42-A42F-1FE1E8E028FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,14 +46,13 @@
     <author>PC</author>
   </authors>
   <commentList>
-    <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{0379C7A9-D991-4A21-88DD-9E4A331E1726}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -62,7 +61,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -81,14 +79,13 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{3E4A2232-15C8-46C8-84B3-5A1E5C958B92}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -97,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -105,14 +101,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{FAB3A062-3D99-4909-9B26-62956785CF60}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -121,7 +116,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -132,14 +126,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{57547B10-E9EC-4B44-A315-093066824BB2}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -148,7 +141,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -156,14 +148,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{8CF5D19F-1B33-4A1B-A7CA-31C4C7016343}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -172,7 +163,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -299,7 +289,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="586">
   <si>
     <t>Id</t>
   </si>
@@ -2005,79 +1995,79 @@
   </si>
   <si>
     <t>Id</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>仅单面</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>相对路径</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>正面atlas</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>正面png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>正面skel</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>背面atlas</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>背面png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>背面skel</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>OnlyFront</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>UseAppHotfixResPath</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>FrontAtlasPath</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>FrontPngPath</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>FrontSkelPath</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BackAtlasPath</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BackPngPath</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BackSkelPath</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>bool</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>不可被抵挡</t>
@@ -2114,96 +2104,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFC000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FF333639"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333639"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF333639"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333639"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -2224,6 +2128,80 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333639"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333639"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2263,7 +2241,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2273,16 +2251,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2294,7 +2273,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2306,23 +2285,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2661,7 +2633,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2825,7 +2797,7 @@
       <c r="AY1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="8" t="s">
         <v>41</v>
       </c>
       <c r="BA1" t="s">
@@ -2995,7 +2967,7 @@
       <c r="AY2" t="s">
         <v>95</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="AZ2" s="8" t="s">
         <v>96</v>
       </c>
       <c r="BA2" t="s">
@@ -3037,7 +3009,7 @@
       <c r="BM2" t="s">
         <v>109</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BN2" s="8" t="s">
         <v>110</v>
       </c>
       <c r="BO2" t="s">
@@ -3272,7 +3244,7 @@
       <c r="D5" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="5" t="s">
         <v>128</v>
       </c>
       <c r="F5" t="str">
@@ -3395,7 +3367,7 @@
       <c r="D6" t="s">
         <v>145</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="5" t="s">
         <v>146</v>
       </c>
       <c r="F6" t="s">
@@ -3516,7 +3488,7 @@
       <c r="D7" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="5" t="s">
         <v>128</v>
       </c>
       <c r="F7" t="str">
@@ -3613,13 +3585,13 @@
       <c r="BJ7" t="s">
         <v>140</v>
       </c>
-      <c r="BM7" s="13" t="s">
+      <c r="BM7" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="BN7" s="13" t="s">
+      <c r="BN7" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="BP7" s="18" t="s">
+      <c r="BP7" s="17" t="s">
         <v>155</v>
       </c>
       <c r="BQ7" t="s">
@@ -3630,2776 +3602,2776 @@
       </c>
     </row>
     <row r="17" spans="4:70" x14ac:dyDescent="0.25">
-      <c r="AI17" s="1"/>
+      <c r="AI17" s="8"/>
     </row>
     <row r="23" spans="4:70" x14ac:dyDescent="0.25">
-      <c r="AI23" s="1"/>
-      <c r="BK23" s="1"/>
+      <c r="AI23" s="8"/>
+      <c r="BK23" s="8"/>
     </row>
     <row r="25" spans="4:70" x14ac:dyDescent="0.25">
-      <c r="AI25" s="1"/>
+      <c r="AI25" s="8"/>
     </row>
     <row r="26" spans="4:70" x14ac:dyDescent="0.25">
-      <c r="AI26" s="1"/>
+      <c r="AI26" s="8"/>
     </row>
     <row r="27" spans="4:70" x14ac:dyDescent="0.25">
-      <c r="AI27" s="1"/>
-      <c r="BK27" s="1"/>
+      <c r="AI27" s="8"/>
+      <c r="BK27" s="8"/>
     </row>
     <row r="28" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D28" s="17"/>
-      <c r="E28" s="16"/>
-      <c r="BO28" s="19"/>
-      <c r="BR28" s="19"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="5"/>
+      <c r="BO28" s="6"/>
+      <c r="BR28" s="6"/>
     </row>
     <row r="29" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D29" s="17"/>
-      <c r="E29" s="16"/>
-      <c r="BO29" s="19"/>
-      <c r="BR29" s="19"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="5"/>
+      <c r="BO29" s="6"/>
+      <c r="BR29" s="6"/>
     </row>
     <row r="30" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D30" s="17"/>
-      <c r="E30" s="16"/>
-      <c r="BO30" s="19"/>
-      <c r="BR30" s="19"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="5"/>
+      <c r="BO30" s="6"/>
+      <c r="BR30" s="6"/>
     </row>
     <row r="31" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D31" s="17"/>
-      <c r="E31" s="16"/>
-      <c r="BO31" s="19"/>
-      <c r="BR31" s="19"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="5"/>
+      <c r="BO31" s="6"/>
+      <c r="BR31" s="6"/>
     </row>
     <row r="32" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D32" s="17"/>
-      <c r="E32" s="16"/>
-      <c r="BO32" s="19"/>
-      <c r="BR32" s="19"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="5"/>
+      <c r="BO32" s="6"/>
+      <c r="BR32" s="6"/>
     </row>
     <row r="33" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D33" s="17"/>
-      <c r="E33" s="16"/>
-      <c r="BO33" s="19"/>
-      <c r="BR33" s="19"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="5"/>
+      <c r="BO33" s="6"/>
+      <c r="BR33" s="6"/>
     </row>
     <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D34" s="17"/>
-      <c r="E34" s="16"/>
-      <c r="BO34" s="19"/>
-      <c r="BR34" s="19"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="5"/>
+      <c r="BO34" s="6"/>
+      <c r="BR34" s="6"/>
     </row>
     <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D35" s="17"/>
-      <c r="E35" s="16"/>
-      <c r="BR35" s="19"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="5"/>
+      <c r="BR35" s="6"/>
     </row>
     <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D36" s="17"/>
-      <c r="E36" s="16"/>
-      <c r="BR36" s="19"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="5"/>
+      <c r="BR36" s="6"/>
     </row>
     <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D37" s="17"/>
-      <c r="E37" s="16"/>
-      <c r="BR37" s="19"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="5"/>
+      <c r="BR37" s="6"/>
     </row>
     <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D38" s="17"/>
-      <c r="E38" s="16"/>
-      <c r="BO38" s="19"/>
-      <c r="BR38" s="19"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="5"/>
+      <c r="BO38" s="6"/>
+      <c r="BR38" s="6"/>
     </row>
     <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D39" s="17"/>
-      <c r="E39" s="16"/>
-      <c r="BO39" s="19"/>
-      <c r="BR39" s="19"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="5"/>
+      <c r="BO39" s="6"/>
+      <c r="BR39" s="6"/>
     </row>
     <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D40" s="17"/>
-      <c r="E40" s="16"/>
-      <c r="BO40" s="19"/>
-      <c r="BR40" s="19"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="5"/>
+      <c r="BO40" s="6"/>
+      <c r="BR40" s="6"/>
     </row>
     <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D41" s="17"/>
-      <c r="E41" s="16"/>
-      <c r="BO41" s="19"/>
-      <c r="BR41" s="19"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="5"/>
+      <c r="BO41" s="6"/>
+      <c r="BR41" s="6"/>
     </row>
     <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D42" s="17"/>
-      <c r="E42" s="16"/>
-      <c r="BO42" s="19"/>
-      <c r="BR42" s="19"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="5"/>
+      <c r="BO42" s="6"/>
+      <c r="BR42" s="6"/>
     </row>
     <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D43" s="17"/>
-      <c r="E43" s="16"/>
-      <c r="BO43" s="19"/>
-      <c r="BR43" s="19"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="5"/>
+      <c r="BO43" s="6"/>
+      <c r="BR43" s="6"/>
     </row>
     <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D44" s="17"/>
-      <c r="E44" s="16"/>
-      <c r="BO44" s="19"/>
-      <c r="BR44" s="19"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="5"/>
+      <c r="BO44" s="6"/>
+      <c r="BR44" s="6"/>
     </row>
     <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D45" s="17"/>
-      <c r="E45" s="16"/>
-      <c r="BO45" s="19"/>
-      <c r="BR45" s="19"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="5"/>
+      <c r="BO45" s="6"/>
+      <c r="BR45" s="6"/>
     </row>
     <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D46" s="17"/>
-      <c r="E46" s="16"/>
-      <c r="BO46" s="19"/>
-      <c r="BR46" s="19"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="5"/>
+      <c r="BO46" s="6"/>
+      <c r="BR46" s="6"/>
     </row>
     <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D47" s="17"/>
-      <c r="E47" s="16"/>
-      <c r="BO47" s="19"/>
-      <c r="BR47" s="19"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="5"/>
+      <c r="BO47" s="6"/>
+      <c r="BR47" s="6"/>
     </row>
     <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D48" s="17"/>
-      <c r="E48" s="16"/>
-      <c r="BO48" s="19"/>
-      <c r="BR48" s="19"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="5"/>
+      <c r="BO48" s="6"/>
+      <c r="BR48" s="6"/>
     </row>
     <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D49" s="17"/>
-      <c r="E49" s="16"/>
-      <c r="BO49" s="19"/>
-      <c r="BR49" s="19"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="5"/>
+      <c r="BO49" s="6"/>
+      <c r="BR49" s="6"/>
     </row>
     <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D50" s="17"/>
-      <c r="E50" s="16"/>
-      <c r="BO50" s="19"/>
-      <c r="BR50" s="19"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="5"/>
+      <c r="BO50" s="6"/>
+      <c r="BR50" s="6"/>
     </row>
     <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D51" s="17"/>
-      <c r="E51" s="16"/>
-      <c r="BO51" s="19"/>
-      <c r="BR51" s="19"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="5"/>
+      <c r="BO51" s="6"/>
+      <c r="BR51" s="6"/>
     </row>
     <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D52" s="17"/>
-      <c r="E52" s="16"/>
-      <c r="BO52" s="19"/>
-      <c r="BR52" s="19"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="5"/>
+      <c r="BO52" s="6"/>
+      <c r="BR52" s="6"/>
     </row>
     <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D53" s="17"/>
-      <c r="E53" s="16"/>
-      <c r="BO53" s="19"/>
-      <c r="BR53" s="19"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="5"/>
+      <c r="BO53" s="6"/>
+      <c r="BR53" s="6"/>
     </row>
     <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D54" s="17"/>
-      <c r="E54" s="16"/>
-      <c r="BO54" s="19"/>
-      <c r="BR54" s="19"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="5"/>
+      <c r="BO54" s="6"/>
+      <c r="BR54" s="6"/>
     </row>
     <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D55" s="17"/>
-      <c r="E55" s="16"/>
-      <c r="BO55" s="19"/>
-      <c r="BR55" s="19"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="5"/>
+      <c r="BO55" s="6"/>
+      <c r="BR55" s="6"/>
     </row>
     <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D56" s="17"/>
-      <c r="E56" s="16"/>
-      <c r="BO56" s="19"/>
-      <c r="BR56" s="19"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="5"/>
+      <c r="BO56" s="6"/>
+      <c r="BR56" s="6"/>
     </row>
     <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D57" s="17"/>
-      <c r="E57" s="16"/>
-      <c r="BO57" s="19"/>
-      <c r="BR57" s="19"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="5"/>
+      <c r="BO57" s="6"/>
+      <c r="BR57" s="6"/>
     </row>
     <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D58" s="17"/>
-      <c r="E58" s="16"/>
-      <c r="BO58" s="19"/>
-      <c r="BR58" s="19"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="5"/>
+      <c r="BO58" s="6"/>
+      <c r="BR58" s="6"/>
     </row>
     <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D59" s="17"/>
-      <c r="E59" s="16"/>
-      <c r="BO59" s="19"/>
-      <c r="BR59" s="19"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="5"/>
+      <c r="BO59" s="6"/>
+      <c r="BR59" s="6"/>
     </row>
     <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D60" s="17"/>
-      <c r="E60" s="16"/>
-      <c r="BO60" s="19"/>
-      <c r="BR60" s="19"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="5"/>
+      <c r="BO60" s="6"/>
+      <c r="BR60" s="6"/>
     </row>
     <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D61" s="17"/>
-      <c r="E61" s="16"/>
-      <c r="BO61" s="19"/>
-      <c r="BR61" s="19"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="5"/>
+      <c r="BO61" s="6"/>
+      <c r="BR61" s="6"/>
     </row>
     <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D62" s="17"/>
-      <c r="E62" s="16"/>
-      <c r="BO62" s="19"/>
-      <c r="BR62" s="19"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="5"/>
+      <c r="BO62" s="6"/>
+      <c r="BR62" s="6"/>
     </row>
     <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D63" s="17"/>
-      <c r="E63" s="16"/>
-      <c r="BO63" s="19"/>
-      <c r="BR63" s="19"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="5"/>
+      <c r="BO63" s="6"/>
+      <c r="BR63" s="6"/>
     </row>
     <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D64" s="17"/>
-      <c r="E64" s="16"/>
-      <c r="BO64" s="19"/>
-      <c r="BR64" s="19"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="5"/>
+      <c r="BO64" s="6"/>
+      <c r="BR64" s="6"/>
     </row>
     <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D65" s="17"/>
-      <c r="E65" s="16"/>
-      <c r="BO65" s="19"/>
-      <c r="BR65" s="19"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="5"/>
+      <c r="BO65" s="6"/>
+      <c r="BR65" s="6"/>
     </row>
     <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D66" s="17"/>
-      <c r="E66" s="16"/>
-      <c r="BO66" s="19"/>
-      <c r="BR66" s="19"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="5"/>
+      <c r="BO66" s="6"/>
+      <c r="BR66" s="6"/>
     </row>
     <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D67" s="17"/>
-      <c r="E67" s="16"/>
-      <c r="BO67" s="19"/>
-      <c r="BR67" s="19"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="5"/>
+      <c r="BO67" s="6"/>
+      <c r="BR67" s="6"/>
     </row>
     <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D68" s="17"/>
-      <c r="E68" s="16"/>
-      <c r="BO68" s="19"/>
-      <c r="BR68" s="19"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="5"/>
+      <c r="BO68" s="6"/>
+      <c r="BR68" s="6"/>
     </row>
     <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D69" s="17"/>
-      <c r="E69" s="16"/>
-      <c r="BO69" s="19"/>
-      <c r="BR69" s="19"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="5"/>
+      <c r="BO69" s="6"/>
+      <c r="BR69" s="6"/>
     </row>
     <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D70" s="17"/>
-      <c r="E70" s="16"/>
-      <c r="BO70" s="19"/>
-      <c r="BR70" s="19"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="5"/>
+      <c r="BO70" s="6"/>
+      <c r="BR70" s="6"/>
     </row>
     <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D71" s="17"/>
-      <c r="E71" s="16"/>
-      <c r="BO71" s="19"/>
-      <c r="BR71" s="19"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="5"/>
+      <c r="BO71" s="6"/>
+      <c r="BR71" s="6"/>
     </row>
     <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D72" s="17"/>
-      <c r="E72" s="16"/>
-      <c r="BO72" s="19"/>
-      <c r="BR72" s="19"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="5"/>
+      <c r="BO72" s="6"/>
+      <c r="BR72" s="6"/>
     </row>
     <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D73" s="17"/>
-      <c r="E73" s="16"/>
-      <c r="BO73" s="19"/>
-      <c r="BR73" s="19"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="5"/>
+      <c r="BO73" s="6"/>
+      <c r="BR73" s="6"/>
     </row>
     <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D74" s="17"/>
-      <c r="E74" s="16"/>
-      <c r="BO74" s="19"/>
-      <c r="BR74" s="19"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="5"/>
+      <c r="BO74" s="6"/>
+      <c r="BR74" s="6"/>
     </row>
     <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D75" s="17"/>
-      <c r="E75" s="16"/>
-      <c r="BO75" s="19"/>
-      <c r="BR75" s="19"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="5"/>
+      <c r="BO75" s="6"/>
+      <c r="BR75" s="6"/>
     </row>
     <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D76" s="17"/>
-      <c r="E76" s="16"/>
-      <c r="BO76" s="19"/>
-      <c r="BR76" s="19"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="5"/>
+      <c r="BO76" s="6"/>
+      <c r="BR76" s="6"/>
     </row>
     <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D77" s="17"/>
-      <c r="E77" s="16"/>
-      <c r="BO77" s="19"/>
-      <c r="BR77" s="19"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="5"/>
+      <c r="BO77" s="6"/>
+      <c r="BR77" s="6"/>
     </row>
     <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D78" s="17"/>
-      <c r="E78" s="16"/>
-      <c r="BO78" s="19"/>
-      <c r="BR78" s="19"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="5"/>
+      <c r="BO78" s="6"/>
+      <c r="BR78" s="6"/>
     </row>
     <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D79" s="17"/>
-      <c r="E79" s="16"/>
-      <c r="BO79" s="19"/>
-      <c r="BR79" s="19"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="5"/>
+      <c r="BO79" s="6"/>
+      <c r="BR79" s="6"/>
     </row>
     <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D80" s="17"/>
-      <c r="E80" s="16"/>
-      <c r="BO80" s="19"/>
-      <c r="BR80" s="19"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="5"/>
+      <c r="BO80" s="6"/>
+      <c r="BR80" s="6"/>
     </row>
     <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D81" s="17"/>
-      <c r="E81" s="16"/>
-      <c r="BO81" s="19"/>
-      <c r="BR81" s="19"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="5"/>
+      <c r="BO81" s="6"/>
+      <c r="BR81" s="6"/>
     </row>
     <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D82" s="17"/>
-      <c r="E82" s="16"/>
-      <c r="BO82" s="19"/>
-      <c r="BR82" s="19"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="5"/>
+      <c r="BO82" s="6"/>
+      <c r="BR82" s="6"/>
     </row>
     <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D83" s="17"/>
-      <c r="E83" s="16"/>
-      <c r="BO83" s="19"/>
-      <c r="BR83" s="19"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="5"/>
+      <c r="BO83" s="6"/>
+      <c r="BR83" s="6"/>
     </row>
     <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D84" s="17"/>
-      <c r="E84" s="16"/>
-      <c r="BO84" s="19"/>
-      <c r="BR84" s="19"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="5"/>
+      <c r="BO84" s="6"/>
+      <c r="BR84" s="6"/>
     </row>
     <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D85" s="17"/>
-      <c r="E85" s="16"/>
-      <c r="BO85" s="19"/>
-      <c r="BR85" s="19"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="5"/>
+      <c r="BO85" s="6"/>
+      <c r="BR85" s="6"/>
     </row>
     <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D86" s="17"/>
-      <c r="E86" s="16"/>
-      <c r="BO86" s="19"/>
-      <c r="BR86" s="19"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="5"/>
+      <c r="BO86" s="6"/>
+      <c r="BR86" s="6"/>
     </row>
     <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D87" s="17"/>
-      <c r="E87" s="16"/>
-      <c r="BO87" s="19"/>
-      <c r="BR87" s="19"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="5"/>
+      <c r="BO87" s="6"/>
+      <c r="BR87" s="6"/>
     </row>
     <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D88" s="17"/>
-      <c r="E88" s="16"/>
-      <c r="BO88" s="19"/>
-      <c r="BR88" s="19"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="5"/>
+      <c r="BO88" s="6"/>
+      <c r="BR88" s="6"/>
     </row>
     <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D89" s="17"/>
-      <c r="E89" s="16"/>
-      <c r="BO89" s="19"/>
-      <c r="BR89" s="19"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="5"/>
+      <c r="BO89" s="6"/>
+      <c r="BR89" s="6"/>
     </row>
     <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D90" s="17"/>
-      <c r="E90" s="16"/>
-      <c r="BO90" s="19"/>
-      <c r="BR90" s="19"/>
+      <c r="D90" s="18"/>
+      <c r="E90" s="5"/>
+      <c r="BO90" s="6"/>
+      <c r="BR90" s="6"/>
     </row>
     <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D91" s="17"/>
-      <c r="E91" s="16"/>
-      <c r="BO91" s="19"/>
-      <c r="BR91" s="19"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="5"/>
+      <c r="BO91" s="6"/>
+      <c r="BR91" s="6"/>
     </row>
     <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D92" s="17"/>
-      <c r="E92" s="16"/>
-      <c r="BO92" s="19"/>
-      <c r="BR92" s="19"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="5"/>
+      <c r="BO92" s="6"/>
+      <c r="BR92" s="6"/>
     </row>
     <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D93" s="17"/>
-      <c r="E93" s="16"/>
-      <c r="BO93" s="19"/>
-      <c r="BR93" s="19"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="5"/>
+      <c r="BO93" s="6"/>
+      <c r="BR93" s="6"/>
     </row>
     <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D94" s="17"/>
-      <c r="E94" s="16"/>
-      <c r="BO94" s="19"/>
-      <c r="BR94" s="19"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="5"/>
+      <c r="BO94" s="6"/>
+      <c r="BR94" s="6"/>
     </row>
     <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D95" s="17"/>
-      <c r="E95" s="16"/>
-      <c r="BO95" s="19"/>
-      <c r="BR95" s="19"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="5"/>
+      <c r="BO95" s="6"/>
+      <c r="BR95" s="6"/>
     </row>
     <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D96" s="17"/>
-      <c r="E96" s="16"/>
-      <c r="BO96" s="19"/>
-      <c r="BR96" s="19"/>
+      <c r="D96" s="18"/>
+      <c r="E96" s="5"/>
+      <c r="BO96" s="6"/>
+      <c r="BR96" s="6"/>
     </row>
     <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D97" s="17"/>
-      <c r="E97" s="16"/>
-      <c r="BO97" s="19"/>
-      <c r="BR97" s="19"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="5"/>
+      <c r="BO97" s="6"/>
+      <c r="BR97" s="6"/>
     </row>
     <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D98" s="17"/>
-      <c r="E98" s="16"/>
-      <c r="BO98" s="19"/>
-      <c r="BR98" s="19"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="5"/>
+      <c r="BO98" s="6"/>
+      <c r="BR98" s="6"/>
     </row>
     <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D99" s="17"/>
-      <c r="E99" s="16"/>
-      <c r="BO99" s="19"/>
-      <c r="BR99" s="19"/>
+      <c r="D99" s="18"/>
+      <c r="E99" s="5"/>
+      <c r="BO99" s="6"/>
+      <c r="BR99" s="6"/>
     </row>
     <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D100" s="17"/>
-      <c r="E100" s="16"/>
-      <c r="BO100" s="19"/>
-      <c r="BR100" s="19"/>
+      <c r="D100" s="18"/>
+      <c r="E100" s="5"/>
+      <c r="BO100" s="6"/>
+      <c r="BR100" s="6"/>
     </row>
     <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D101" s="17"/>
-      <c r="E101" s="16"/>
-      <c r="BO101" s="19"/>
-      <c r="BR101" s="19"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="5"/>
+      <c r="BO101" s="6"/>
+      <c r="BR101" s="6"/>
     </row>
     <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D102" s="17"/>
-      <c r="E102" s="16"/>
-      <c r="BO102" s="19"/>
-      <c r="BR102" s="19"/>
+      <c r="D102" s="18"/>
+      <c r="E102" s="5"/>
+      <c r="BO102" s="6"/>
+      <c r="BR102" s="6"/>
     </row>
     <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D103" s="17"/>
-      <c r="E103" s="16"/>
-      <c r="BO103" s="19"/>
-      <c r="BR103" s="19"/>
+      <c r="D103" s="18"/>
+      <c r="E103" s="5"/>
+      <c r="BO103" s="6"/>
+      <c r="BR103" s="6"/>
     </row>
     <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D104" s="17"/>
-      <c r="E104" s="16"/>
-      <c r="BO104" s="19"/>
-      <c r="BR104" s="19"/>
+      <c r="D104" s="18"/>
+      <c r="E104" s="5"/>
+      <c r="BO104" s="6"/>
+      <c r="BR104" s="6"/>
     </row>
     <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D105" s="17"/>
-      <c r="E105" s="16"/>
-      <c r="BO105" s="19"/>
-      <c r="BR105" s="19"/>
+      <c r="D105" s="18"/>
+      <c r="E105" s="5"/>
+      <c r="BO105" s="6"/>
+      <c r="BR105" s="6"/>
     </row>
     <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D106" s="17"/>
-      <c r="E106" s="16"/>
-      <c r="BO106" s="19"/>
-      <c r="BR106" s="19"/>
+      <c r="D106" s="18"/>
+      <c r="E106" s="5"/>
+      <c r="BO106" s="6"/>
+      <c r="BR106" s="6"/>
     </row>
     <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D107" s="17"/>
-      <c r="E107" s="16"/>
-      <c r="BO107" s="19"/>
-      <c r="BR107" s="19"/>
+      <c r="D107" s="18"/>
+      <c r="E107" s="5"/>
+      <c r="BO107" s="6"/>
+      <c r="BR107" s="6"/>
     </row>
     <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D108" s="17"/>
-      <c r="E108" s="16"/>
-      <c r="BO108" s="19"/>
-      <c r="BR108" s="19"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="5"/>
+      <c r="BO108" s="6"/>
+      <c r="BR108" s="6"/>
     </row>
     <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D109" s="17"/>
-      <c r="E109" s="16"/>
-      <c r="BO109" s="19"/>
-      <c r="BR109" s="19"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="5"/>
+      <c r="BO109" s="6"/>
+      <c r="BR109" s="6"/>
     </row>
     <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D110" s="17"/>
-      <c r="E110" s="16"/>
-      <c r="BO110" s="19"/>
-      <c r="BR110" s="19"/>
+      <c r="D110" s="18"/>
+      <c r="E110" s="5"/>
+      <c r="BO110" s="6"/>
+      <c r="BR110" s="6"/>
     </row>
     <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D111" s="17"/>
-      <c r="E111" s="16"/>
-      <c r="BO111" s="19"/>
-      <c r="BR111" s="19"/>
+      <c r="D111" s="18"/>
+      <c r="E111" s="5"/>
+      <c r="BO111" s="6"/>
+      <c r="BR111" s="6"/>
     </row>
     <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D112" s="17"/>
-      <c r="E112" s="16"/>
-      <c r="BO112" s="19"/>
-      <c r="BR112" s="19"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="5"/>
+      <c r="BO112" s="6"/>
+      <c r="BR112" s="6"/>
     </row>
     <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D113" s="17"/>
-      <c r="E113" s="16"/>
-      <c r="BO113" s="19"/>
-      <c r="BR113" s="19"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="5"/>
+      <c r="BO113" s="6"/>
+      <c r="BR113" s="6"/>
     </row>
     <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D114" s="17"/>
-      <c r="E114" s="16"/>
-      <c r="BO114" s="19"/>
-      <c r="BR114" s="19"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="5"/>
+      <c r="BO114" s="6"/>
+      <c r="BR114" s="6"/>
     </row>
     <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D115" s="17"/>
-      <c r="E115" s="16"/>
-      <c r="BO115" s="19"/>
-      <c r="BR115" s="19"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="5"/>
+      <c r="BO115" s="6"/>
+      <c r="BR115" s="6"/>
     </row>
     <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D116" s="17"/>
-      <c r="E116" s="16"/>
-      <c r="BO116" s="19"/>
-      <c r="BR116" s="19"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="5"/>
+      <c r="BO116" s="6"/>
+      <c r="BR116" s="6"/>
     </row>
     <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D117" s="17"/>
-      <c r="E117" s="16"/>
-      <c r="BO117" s="19"/>
-      <c r="BR117" s="19"/>
+      <c r="D117" s="18"/>
+      <c r="E117" s="5"/>
+      <c r="BO117" s="6"/>
+      <c r="BR117" s="6"/>
     </row>
     <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D118" s="17"/>
-      <c r="E118" s="16"/>
-      <c r="BO118" s="19"/>
-      <c r="BR118" s="19"/>
+      <c r="D118" s="18"/>
+      <c r="E118" s="5"/>
+      <c r="BO118" s="6"/>
+      <c r="BR118" s="6"/>
     </row>
     <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D119" s="17"/>
-      <c r="E119" s="16"/>
-      <c r="BO119" s="19"/>
-      <c r="BR119" s="19"/>
+      <c r="D119" s="18"/>
+      <c r="E119" s="5"/>
+      <c r="BO119" s="6"/>
+      <c r="BR119" s="6"/>
     </row>
     <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D120" s="17"/>
-      <c r="E120" s="16"/>
-      <c r="BO120" s="19"/>
-      <c r="BR120" s="19"/>
+      <c r="D120" s="18"/>
+      <c r="E120" s="5"/>
+      <c r="BO120" s="6"/>
+      <c r="BR120" s="6"/>
     </row>
     <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D121" s="17"/>
-      <c r="E121" s="16"/>
-      <c r="BO121" s="19"/>
-      <c r="BR121" s="19"/>
+      <c r="D121" s="18"/>
+      <c r="E121" s="5"/>
+      <c r="BO121" s="6"/>
+      <c r="BR121" s="6"/>
     </row>
     <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D122" s="17"/>
-      <c r="E122" s="16"/>
-      <c r="BO122" s="19"/>
-      <c r="BR122" s="19"/>
+      <c r="D122" s="18"/>
+      <c r="E122" s="5"/>
+      <c r="BO122" s="6"/>
+      <c r="BR122" s="6"/>
     </row>
     <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D123" s="17"/>
-      <c r="E123" s="16"/>
-      <c r="BO123" s="19"/>
-      <c r="BR123" s="19"/>
+      <c r="D123" s="18"/>
+      <c r="E123" s="5"/>
+      <c r="BO123" s="6"/>
+      <c r="BR123" s="6"/>
     </row>
     <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D124" s="17"/>
-      <c r="E124" s="16"/>
-      <c r="BO124" s="19"/>
-      <c r="BR124" s="19"/>
+      <c r="D124" s="18"/>
+      <c r="E124" s="5"/>
+      <c r="BO124" s="6"/>
+      <c r="BR124" s="6"/>
     </row>
     <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D125" s="17"/>
-      <c r="E125" s="16"/>
-      <c r="BO125" s="19"/>
-      <c r="BR125" s="19"/>
+      <c r="D125" s="18"/>
+      <c r="E125" s="5"/>
+      <c r="BO125" s="6"/>
+      <c r="BR125" s="6"/>
     </row>
     <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D126" s="17"/>
-      <c r="E126" s="16"/>
-      <c r="BO126" s="19"/>
-      <c r="BR126" s="19"/>
+      <c r="D126" s="18"/>
+      <c r="E126" s="5"/>
+      <c r="BO126" s="6"/>
+      <c r="BR126" s="6"/>
     </row>
     <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D127" s="17"/>
-      <c r="E127" s="16"/>
-      <c r="BO127" s="19"/>
-      <c r="BR127" s="19"/>
+      <c r="D127" s="18"/>
+      <c r="E127" s="5"/>
+      <c r="BO127" s="6"/>
+      <c r="BR127" s="6"/>
     </row>
     <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D128" s="17"/>
-      <c r="E128" s="16"/>
-      <c r="BO128" s="19"/>
-      <c r="BR128" s="19"/>
+      <c r="D128" s="18"/>
+      <c r="E128" s="5"/>
+      <c r="BO128" s="6"/>
+      <c r="BR128" s="6"/>
     </row>
     <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D129" s="17"/>
-      <c r="E129" s="16"/>
-      <c r="BO129" s="19"/>
-      <c r="BR129" s="19"/>
+      <c r="D129" s="18"/>
+      <c r="E129" s="5"/>
+      <c r="BO129" s="6"/>
+      <c r="BR129" s="6"/>
     </row>
     <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D130" s="17"/>
-      <c r="E130" s="16"/>
-      <c r="BO130" s="19"/>
-      <c r="BR130" s="19"/>
+      <c r="D130" s="18"/>
+      <c r="E130" s="5"/>
+      <c r="BO130" s="6"/>
+      <c r="BR130" s="6"/>
     </row>
     <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D131" s="17"/>
-      <c r="E131" s="16"/>
-      <c r="BO131" s="19"/>
-      <c r="BR131" s="19"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="5"/>
+      <c r="BO131" s="6"/>
+      <c r="BR131" s="6"/>
     </row>
     <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D132" s="17"/>
-      <c r="E132" s="16"/>
-      <c r="BO132" s="19"/>
-      <c r="BR132" s="19"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="5"/>
+      <c r="BO132" s="6"/>
+      <c r="BR132" s="6"/>
     </row>
     <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D133" s="17"/>
-      <c r="E133" s="16"/>
-      <c r="BO133" s="19"/>
-      <c r="BR133" s="19"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="5"/>
+      <c r="BO133" s="6"/>
+      <c r="BR133" s="6"/>
     </row>
     <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D134" s="17"/>
-      <c r="E134" s="16"/>
-      <c r="BO134" s="19"/>
-      <c r="BR134" s="19"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="5"/>
+      <c r="BO134" s="6"/>
+      <c r="BR134" s="6"/>
     </row>
     <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D135" s="17"/>
-      <c r="E135" s="16"/>
-      <c r="BO135" s="19"/>
-      <c r="BR135" s="19"/>
+      <c r="D135" s="18"/>
+      <c r="E135" s="5"/>
+      <c r="BO135" s="6"/>
+      <c r="BR135" s="6"/>
     </row>
     <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D136" s="17"/>
-      <c r="E136" s="16"/>
-      <c r="BO136" s="19"/>
-      <c r="BR136" s="19"/>
+      <c r="D136" s="18"/>
+      <c r="E136" s="5"/>
+      <c r="BO136" s="6"/>
+      <c r="BR136" s="6"/>
     </row>
     <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D137" s="17"/>
-      <c r="E137" s="16"/>
-      <c r="BO137" s="19"/>
-      <c r="BR137" s="19"/>
+      <c r="D137" s="18"/>
+      <c r="E137" s="5"/>
+      <c r="BO137" s="6"/>
+      <c r="BR137" s="6"/>
     </row>
     <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D138" s="17"/>
-      <c r="E138" s="16"/>
-      <c r="BO138" s="19"/>
-      <c r="BR138" s="19"/>
+      <c r="D138" s="18"/>
+      <c r="E138" s="5"/>
+      <c r="BO138" s="6"/>
+      <c r="BR138" s="6"/>
     </row>
     <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D139" s="17"/>
-      <c r="E139" s="16"/>
-      <c r="BO139" s="19"/>
-      <c r="BR139" s="19"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="5"/>
+      <c r="BO139" s="6"/>
+      <c r="BR139" s="6"/>
     </row>
     <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D140" s="17"/>
-      <c r="E140" s="16"/>
-      <c r="BO140" s="19"/>
-      <c r="BR140" s="19"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="5"/>
+      <c r="BO140" s="6"/>
+      <c r="BR140" s="6"/>
     </row>
     <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D141" s="17"/>
-      <c r="E141" s="16"/>
-      <c r="BO141" s="19"/>
-      <c r="BR141" s="19"/>
+      <c r="D141" s="18"/>
+      <c r="E141" s="5"/>
+      <c r="BO141" s="6"/>
+      <c r="BR141" s="6"/>
     </row>
     <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D142" s="17"/>
-      <c r="E142" s="16"/>
-      <c r="BO142" s="19"/>
-      <c r="BR142" s="19"/>
+      <c r="D142" s="18"/>
+      <c r="E142" s="5"/>
+      <c r="BO142" s="6"/>
+      <c r="BR142" s="6"/>
     </row>
     <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D143" s="17"/>
-      <c r="E143" s="16"/>
-      <c r="BO143" s="19"/>
-      <c r="BR143" s="19"/>
+      <c r="D143" s="18"/>
+      <c r="E143" s="5"/>
+      <c r="BO143" s="6"/>
+      <c r="BR143" s="6"/>
     </row>
     <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D144" s="17"/>
-      <c r="E144" s="16"/>
-      <c r="BO144" s="19"/>
-      <c r="BR144" s="19"/>
+      <c r="D144" s="18"/>
+      <c r="E144" s="5"/>
+      <c r="BO144" s="6"/>
+      <c r="BR144" s="6"/>
     </row>
     <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D145" s="17"/>
-      <c r="E145" s="16"/>
-      <c r="BO145" s="19"/>
-      <c r="BR145" s="19"/>
+      <c r="D145" s="18"/>
+      <c r="E145" s="5"/>
+      <c r="BO145" s="6"/>
+      <c r="BR145" s="6"/>
     </row>
     <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D146" s="17"/>
-      <c r="E146" s="16"/>
-      <c r="BO146" s="19"/>
-      <c r="BR146" s="19"/>
+      <c r="D146" s="18"/>
+      <c r="E146" s="5"/>
+      <c r="BO146" s="6"/>
+      <c r="BR146" s="6"/>
     </row>
     <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D147" s="17"/>
-      <c r="E147" s="16"/>
-      <c r="BO147" s="19"/>
-      <c r="BR147" s="19"/>
+      <c r="D147" s="18"/>
+      <c r="E147" s="5"/>
+      <c r="BO147" s="6"/>
+      <c r="BR147" s="6"/>
     </row>
     <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D148" s="17"/>
-      <c r="E148" s="16"/>
-      <c r="BO148" s="19"/>
-      <c r="BR148" s="19"/>
+      <c r="D148" s="18"/>
+      <c r="E148" s="5"/>
+      <c r="BO148" s="6"/>
+      <c r="BR148" s="6"/>
     </row>
     <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D149" s="17"/>
-      <c r="E149" s="16"/>
-      <c r="BO149" s="19"/>
-      <c r="BR149" s="19"/>
+      <c r="D149" s="18"/>
+      <c r="E149" s="5"/>
+      <c r="BO149" s="6"/>
+      <c r="BR149" s="6"/>
     </row>
     <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D150" s="17"/>
-      <c r="E150" s="16"/>
-      <c r="BO150" s="19"/>
-      <c r="BR150" s="19"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="5"/>
+      <c r="BO150" s="6"/>
+      <c r="BR150" s="6"/>
     </row>
     <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D151" s="17"/>
-      <c r="E151" s="16"/>
-      <c r="BO151" s="19"/>
-      <c r="BR151" s="19"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="5"/>
+      <c r="BO151" s="6"/>
+      <c r="BR151" s="6"/>
     </row>
     <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D152" s="17"/>
-      <c r="E152" s="16"/>
-      <c r="BO152" s="19"/>
-      <c r="BR152" s="19"/>
+      <c r="D152" s="18"/>
+      <c r="E152" s="5"/>
+      <c r="BO152" s="6"/>
+      <c r="BR152" s="6"/>
     </row>
     <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D153" s="17"/>
-      <c r="E153" s="16"/>
-      <c r="BO153" s="19"/>
-      <c r="BR153" s="19"/>
+      <c r="D153" s="18"/>
+      <c r="E153" s="5"/>
+      <c r="BO153" s="6"/>
+      <c r="BR153" s="6"/>
     </row>
     <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D154" s="17"/>
-      <c r="E154" s="16"/>
-      <c r="BO154" s="19"/>
-      <c r="BR154" s="19"/>
+      <c r="D154" s="18"/>
+      <c r="E154" s="5"/>
+      <c r="BO154" s="6"/>
+      <c r="BR154" s="6"/>
     </row>
     <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D155" s="17"/>
-      <c r="E155" s="16"/>
-      <c r="BO155" s="19"/>
-      <c r="BR155" s="19"/>
+      <c r="D155" s="18"/>
+      <c r="E155" s="5"/>
+      <c r="BO155" s="6"/>
+      <c r="BR155" s="6"/>
     </row>
     <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D156" s="17"/>
-      <c r="E156" s="16"/>
-      <c r="BO156" s="19"/>
-      <c r="BR156" s="19"/>
+      <c r="D156" s="18"/>
+      <c r="E156" s="5"/>
+      <c r="BO156" s="6"/>
+      <c r="BR156" s="6"/>
     </row>
     <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D157" s="17"/>
-      <c r="E157" s="16"/>
-      <c r="BO157" s="19"/>
-      <c r="BR157" s="19"/>
+      <c r="D157" s="18"/>
+      <c r="E157" s="5"/>
+      <c r="BO157" s="6"/>
+      <c r="BR157" s="6"/>
     </row>
     <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D158" s="17"/>
-      <c r="E158" s="16"/>
-      <c r="BO158" s="19"/>
-      <c r="BR158" s="19"/>
+      <c r="D158" s="18"/>
+      <c r="E158" s="5"/>
+      <c r="BO158" s="6"/>
+      <c r="BR158" s="6"/>
     </row>
     <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D159" s="17"/>
-      <c r="E159" s="16"/>
-      <c r="BO159" s="19"/>
-      <c r="BR159" s="19"/>
+      <c r="D159" s="18"/>
+      <c r="E159" s="5"/>
+      <c r="BO159" s="6"/>
+      <c r="BR159" s="6"/>
     </row>
     <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D160" s="17"/>
-      <c r="E160" s="16"/>
-      <c r="BO160" s="19"/>
-      <c r="BR160" s="19"/>
+      <c r="D160" s="18"/>
+      <c r="E160" s="5"/>
+      <c r="BO160" s="6"/>
+      <c r="BR160" s="6"/>
     </row>
     <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D161" s="17"/>
-      <c r="E161" s="16"/>
-      <c r="BO161" s="19"/>
-      <c r="BR161" s="19"/>
+      <c r="D161" s="18"/>
+      <c r="E161" s="5"/>
+      <c r="BO161" s="6"/>
+      <c r="BR161" s="6"/>
     </row>
     <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D162" s="17"/>
-      <c r="E162" s="16"/>
-      <c r="BO162" s="19"/>
-      <c r="BR162" s="19"/>
+      <c r="D162" s="18"/>
+      <c r="E162" s="5"/>
+      <c r="BO162" s="6"/>
+      <c r="BR162" s="6"/>
     </row>
     <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D163" s="17"/>
-      <c r="E163" s="16"/>
-      <c r="BO163" s="19"/>
-      <c r="BR163" s="19"/>
+      <c r="D163" s="18"/>
+      <c r="E163" s="5"/>
+      <c r="BO163" s="6"/>
+      <c r="BR163" s="6"/>
     </row>
     <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D164" s="17"/>
-      <c r="E164" s="16"/>
-      <c r="BO164" s="19"/>
-      <c r="BR164" s="19"/>
+      <c r="D164" s="18"/>
+      <c r="E164" s="5"/>
+      <c r="BO164" s="6"/>
+      <c r="BR164" s="6"/>
     </row>
     <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D165" s="17"/>
-      <c r="E165" s="16"/>
-      <c r="BO165" s="19"/>
-      <c r="BR165" s="19"/>
+      <c r="D165" s="18"/>
+      <c r="E165" s="5"/>
+      <c r="BO165" s="6"/>
+      <c r="BR165" s="6"/>
     </row>
     <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D166" s="17"/>
-      <c r="E166" s="16"/>
-      <c r="BO166" s="19"/>
-      <c r="BR166" s="19"/>
+      <c r="D166" s="18"/>
+      <c r="E166" s="5"/>
+      <c r="BO166" s="6"/>
+      <c r="BR166" s="6"/>
     </row>
     <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D167" s="17"/>
-      <c r="E167" s="16"/>
-      <c r="BO167" s="19"/>
-      <c r="BR167" s="19"/>
+      <c r="D167" s="18"/>
+      <c r="E167" s="5"/>
+      <c r="BO167" s="6"/>
+      <c r="BR167" s="6"/>
     </row>
     <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D168" s="17"/>
-      <c r="E168" s="16"/>
-      <c r="BO168" s="19"/>
-      <c r="BR168" s="19"/>
+      <c r="D168" s="18"/>
+      <c r="E168" s="5"/>
+      <c r="BO168" s="6"/>
+      <c r="BR168" s="6"/>
     </row>
     <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D169" s="17"/>
-      <c r="E169" s="16"/>
-      <c r="BO169" s="19"/>
-      <c r="BR169" s="19"/>
+      <c r="D169" s="18"/>
+      <c r="E169" s="5"/>
+      <c r="BO169" s="6"/>
+      <c r="BR169" s="6"/>
     </row>
     <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D170" s="17"/>
-      <c r="E170" s="16"/>
-      <c r="BO170" s="19"/>
-      <c r="BR170" s="19"/>
+      <c r="D170" s="18"/>
+      <c r="E170" s="5"/>
+      <c r="BO170" s="6"/>
+      <c r="BR170" s="6"/>
     </row>
     <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D171" s="17"/>
-      <c r="E171" s="16"/>
-      <c r="BO171" s="19"/>
-      <c r="BR171" s="19"/>
+      <c r="D171" s="18"/>
+      <c r="E171" s="5"/>
+      <c r="BO171" s="6"/>
+      <c r="BR171" s="6"/>
     </row>
     <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D172" s="17"/>
-      <c r="E172" s="16"/>
-      <c r="BO172" s="19"/>
-      <c r="BR172" s="19"/>
+      <c r="D172" s="18"/>
+      <c r="E172" s="5"/>
+      <c r="BO172" s="6"/>
+      <c r="BR172" s="6"/>
     </row>
     <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D173" s="17"/>
-      <c r="E173" s="16"/>
-      <c r="BO173" s="19"/>
-      <c r="BR173" s="19"/>
+      <c r="D173" s="18"/>
+      <c r="E173" s="5"/>
+      <c r="BO173" s="6"/>
+      <c r="BR173" s="6"/>
     </row>
     <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D174" s="17"/>
-      <c r="E174" s="16"/>
-      <c r="BO174" s="19"/>
-      <c r="BR174" s="19"/>
+      <c r="D174" s="18"/>
+      <c r="E174" s="5"/>
+      <c r="BO174" s="6"/>
+      <c r="BR174" s="6"/>
     </row>
     <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D175" s="17"/>
-      <c r="E175" s="16"/>
-      <c r="BO175" s="19"/>
-      <c r="BR175" s="19"/>
+      <c r="D175" s="18"/>
+      <c r="E175" s="5"/>
+      <c r="BO175" s="6"/>
+      <c r="BR175" s="6"/>
     </row>
     <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D176" s="17"/>
-      <c r="E176" s="16"/>
-      <c r="BO176" s="19"/>
-      <c r="BR176" s="19"/>
+      <c r="D176" s="18"/>
+      <c r="E176" s="5"/>
+      <c r="BO176" s="6"/>
+      <c r="BR176" s="6"/>
     </row>
     <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D177" s="17"/>
-      <c r="E177" s="16"/>
-      <c r="BO177" s="19"/>
-      <c r="BR177" s="19"/>
+      <c r="D177" s="18"/>
+      <c r="E177" s="5"/>
+      <c r="BO177" s="6"/>
+      <c r="BR177" s="6"/>
     </row>
     <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D178" s="17"/>
-      <c r="E178" s="16"/>
-      <c r="BO178" s="19"/>
-      <c r="BR178" s="19"/>
+      <c r="D178" s="18"/>
+      <c r="E178" s="5"/>
+      <c r="BO178" s="6"/>
+      <c r="BR178" s="6"/>
     </row>
     <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D179" s="17"/>
-      <c r="E179" s="16"/>
-      <c r="BO179" s="19"/>
-      <c r="BR179" s="19"/>
+      <c r="D179" s="18"/>
+      <c r="E179" s="5"/>
+      <c r="BO179" s="6"/>
+      <c r="BR179" s="6"/>
     </row>
     <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D180" s="17"/>
-      <c r="E180" s="16"/>
-      <c r="BO180" s="19"/>
-      <c r="BR180" s="19"/>
+      <c r="D180" s="18"/>
+      <c r="E180" s="5"/>
+      <c r="BO180" s="6"/>
+      <c r="BR180" s="6"/>
     </row>
     <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D181" s="17"/>
-      <c r="E181" s="16"/>
-      <c r="BO181" s="19"/>
-      <c r="BR181" s="19"/>
+      <c r="D181" s="18"/>
+      <c r="E181" s="5"/>
+      <c r="BO181" s="6"/>
+      <c r="BR181" s="6"/>
     </row>
     <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D182" s="17"/>
-      <c r="E182" s="16"/>
-      <c r="BO182" s="19"/>
-      <c r="BR182" s="19"/>
+      <c r="D182" s="18"/>
+      <c r="E182" s="5"/>
+      <c r="BO182" s="6"/>
+      <c r="BR182" s="6"/>
     </row>
     <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D183" s="17"/>
-      <c r="E183" s="16"/>
-      <c r="BO183" s="19"/>
-      <c r="BR183" s="19"/>
+      <c r="D183" s="18"/>
+      <c r="E183" s="5"/>
+      <c r="BO183" s="6"/>
+      <c r="BR183" s="6"/>
     </row>
     <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D184" s="17"/>
-      <c r="E184" s="16"/>
-      <c r="BO184" s="19"/>
-      <c r="BR184" s="19"/>
+      <c r="D184" s="18"/>
+      <c r="E184" s="5"/>
+      <c r="BO184" s="6"/>
+      <c r="BR184" s="6"/>
     </row>
     <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D185" s="17"/>
-      <c r="E185" s="16"/>
-      <c r="BO185" s="19"/>
-      <c r="BR185" s="19"/>
+      <c r="D185" s="18"/>
+      <c r="E185" s="5"/>
+      <c r="BO185" s="6"/>
+      <c r="BR185" s="6"/>
     </row>
     <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D186" s="17"/>
-      <c r="E186" s="16"/>
-      <c r="BO186" s="19"/>
-      <c r="BR186" s="19"/>
+      <c r="D186" s="18"/>
+      <c r="E186" s="5"/>
+      <c r="BO186" s="6"/>
+      <c r="BR186" s="6"/>
     </row>
     <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D187" s="17"/>
-      <c r="E187" s="16"/>
-      <c r="BO187" s="19"/>
-      <c r="BR187" s="19"/>
+      <c r="D187" s="18"/>
+      <c r="E187" s="5"/>
+      <c r="BO187" s="6"/>
+      <c r="BR187" s="6"/>
     </row>
     <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D188" s="17"/>
-      <c r="E188" s="16"/>
-      <c r="BO188" s="19"/>
-      <c r="BR188" s="19"/>
+      <c r="D188" s="18"/>
+      <c r="E188" s="5"/>
+      <c r="BO188" s="6"/>
+      <c r="BR188" s="6"/>
     </row>
     <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D189" s="17"/>
-      <c r="E189" s="16"/>
-      <c r="BO189" s="19"/>
-      <c r="BR189" s="19"/>
+      <c r="D189" s="18"/>
+      <c r="E189" s="5"/>
+      <c r="BO189" s="6"/>
+      <c r="BR189" s="6"/>
     </row>
     <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D190" s="17"/>
-      <c r="E190" s="16"/>
-      <c r="BO190" s="19"/>
-      <c r="BR190" s="19"/>
+      <c r="D190" s="18"/>
+      <c r="E190" s="5"/>
+      <c r="BO190" s="6"/>
+      <c r="BR190" s="6"/>
     </row>
     <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D191" s="17"/>
-      <c r="E191" s="16"/>
-      <c r="BO191" s="19"/>
-      <c r="BR191" s="19"/>
+      <c r="D191" s="18"/>
+      <c r="E191" s="5"/>
+      <c r="BO191" s="6"/>
+      <c r="BR191" s="6"/>
     </row>
     <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D192" s="17"/>
-      <c r="E192" s="16"/>
-      <c r="BO192" s="19"/>
-      <c r="BR192" s="19"/>
+      <c r="D192" s="18"/>
+      <c r="E192" s="5"/>
+      <c r="BO192" s="6"/>
+      <c r="BR192" s="6"/>
     </row>
     <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D193" s="17"/>
-      <c r="E193" s="16"/>
-      <c r="BO193" s="19"/>
-      <c r="BR193" s="19"/>
+      <c r="D193" s="18"/>
+      <c r="E193" s="5"/>
+      <c r="BO193" s="6"/>
+      <c r="BR193" s="6"/>
     </row>
     <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D194" s="17"/>
-      <c r="E194" s="16"/>
-      <c r="BO194" s="19"/>
-      <c r="BR194" s="19"/>
+      <c r="D194" s="18"/>
+      <c r="E194" s="5"/>
+      <c r="BO194" s="6"/>
+      <c r="BR194" s="6"/>
     </row>
     <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D195" s="17"/>
-      <c r="E195" s="16"/>
-      <c r="BO195" s="19"/>
-      <c r="BR195" s="19"/>
+      <c r="D195" s="18"/>
+      <c r="E195" s="5"/>
+      <c r="BO195" s="6"/>
+      <c r="BR195" s="6"/>
     </row>
     <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D196" s="17"/>
-      <c r="E196" s="16"/>
-      <c r="BO196" s="19"/>
-      <c r="BR196" s="19"/>
+      <c r="D196" s="18"/>
+      <c r="E196" s="5"/>
+      <c r="BO196" s="6"/>
+      <c r="BR196" s="6"/>
     </row>
     <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D197" s="17"/>
-      <c r="E197" s="16"/>
-      <c r="BO197" s="19"/>
-      <c r="BR197" s="19"/>
+      <c r="D197" s="18"/>
+      <c r="E197" s="5"/>
+      <c r="BO197" s="6"/>
+      <c r="BR197" s="6"/>
     </row>
     <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D198" s="17"/>
-      <c r="E198" s="16"/>
-      <c r="BO198" s="19"/>
-      <c r="BR198" s="19"/>
+      <c r="D198" s="18"/>
+      <c r="E198" s="5"/>
+      <c r="BO198" s="6"/>
+      <c r="BR198" s="6"/>
     </row>
     <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D199" s="17"/>
-      <c r="E199" s="16"/>
-      <c r="BO199" s="19"/>
-      <c r="BR199" s="19"/>
+      <c r="D199" s="18"/>
+      <c r="E199" s="5"/>
+      <c r="BO199" s="6"/>
+      <c r="BR199" s="6"/>
     </row>
     <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D200" s="17"/>
-      <c r="E200" s="16"/>
-      <c r="BO200" s="19"/>
-      <c r="BR200" s="19"/>
+      <c r="D200" s="18"/>
+      <c r="E200" s="5"/>
+      <c r="BO200" s="6"/>
+      <c r="BR200" s="6"/>
     </row>
     <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D201" s="17"/>
-      <c r="E201" s="16"/>
-      <c r="BO201" s="19"/>
-      <c r="BR201" s="19"/>
+      <c r="D201" s="18"/>
+      <c r="E201" s="5"/>
+      <c r="BO201" s="6"/>
+      <c r="BR201" s="6"/>
     </row>
     <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D202" s="17"/>
-      <c r="E202" s="16"/>
-      <c r="BO202" s="19"/>
-      <c r="BR202" s="19"/>
+      <c r="D202" s="18"/>
+      <c r="E202" s="5"/>
+      <c r="BO202" s="6"/>
+      <c r="BR202" s="6"/>
     </row>
     <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D203" s="17"/>
-      <c r="E203" s="16"/>
-      <c r="BO203" s="19"/>
-      <c r="BR203" s="19"/>
+      <c r="D203" s="18"/>
+      <c r="E203" s="5"/>
+      <c r="BO203" s="6"/>
+      <c r="BR203" s="6"/>
     </row>
     <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D204" s="17"/>
-      <c r="E204" s="16"/>
-      <c r="BO204" s="19"/>
-      <c r="BR204" s="19"/>
+      <c r="D204" s="18"/>
+      <c r="E204" s="5"/>
+      <c r="BO204" s="6"/>
+      <c r="BR204" s="6"/>
     </row>
     <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D205" s="17"/>
-      <c r="E205" s="16"/>
-      <c r="BO205" s="19"/>
-      <c r="BR205" s="19"/>
+      <c r="D205" s="18"/>
+      <c r="E205" s="5"/>
+      <c r="BO205" s="6"/>
+      <c r="BR205" s="6"/>
     </row>
     <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D206" s="17"/>
-      <c r="E206" s="16"/>
-      <c r="BO206" s="19"/>
-      <c r="BR206" s="19"/>
+      <c r="D206" s="18"/>
+      <c r="E206" s="5"/>
+      <c r="BO206" s="6"/>
+      <c r="BR206" s="6"/>
     </row>
     <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D207" s="17"/>
-      <c r="E207" s="16"/>
-      <c r="BO207" s="19"/>
-      <c r="BR207" s="19"/>
+      <c r="D207" s="18"/>
+      <c r="E207" s="5"/>
+      <c r="BO207" s="6"/>
+      <c r="BR207" s="6"/>
     </row>
     <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D208" s="17"/>
-      <c r="E208" s="16"/>
-      <c r="BO208" s="19"/>
-      <c r="BR208" s="19"/>
+      <c r="D208" s="18"/>
+      <c r="E208" s="5"/>
+      <c r="BO208" s="6"/>
+      <c r="BR208" s="6"/>
     </row>
     <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D209" s="17"/>
-      <c r="E209" s="16"/>
-      <c r="BO209" s="19"/>
-      <c r="BR209" s="19"/>
+      <c r="D209" s="18"/>
+      <c r="E209" s="5"/>
+      <c r="BO209" s="6"/>
+      <c r="BR209" s="6"/>
     </row>
     <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D210" s="17"/>
-      <c r="E210" s="16"/>
-      <c r="BO210" s="19"/>
-      <c r="BR210" s="19"/>
+      <c r="D210" s="18"/>
+      <c r="E210" s="5"/>
+      <c r="BO210" s="6"/>
+      <c r="BR210" s="6"/>
     </row>
     <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D211" s="17"/>
-      <c r="E211" s="16"/>
-      <c r="BO211" s="19"/>
-      <c r="BR211" s="19"/>
+      <c r="D211" s="18"/>
+      <c r="E211" s="5"/>
+      <c r="BO211" s="6"/>
+      <c r="BR211" s="6"/>
     </row>
     <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D212" s="17"/>
-      <c r="E212" s="16"/>
-      <c r="BO212" s="19"/>
-      <c r="BR212" s="19"/>
+      <c r="D212" s="18"/>
+      <c r="E212" s="5"/>
+      <c r="BO212" s="6"/>
+      <c r="BR212" s="6"/>
     </row>
     <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D213" s="17"/>
-      <c r="E213" s="16"/>
-      <c r="BO213" s="19"/>
-      <c r="BR213" s="19"/>
+      <c r="D213" s="18"/>
+      <c r="E213" s="5"/>
+      <c r="BO213" s="6"/>
+      <c r="BR213" s="6"/>
     </row>
     <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D214" s="17"/>
-      <c r="E214" s="16"/>
-      <c r="BO214" s="19"/>
-      <c r="BR214" s="19"/>
+      <c r="D214" s="18"/>
+      <c r="E214" s="5"/>
+      <c r="BO214" s="6"/>
+      <c r="BR214" s="6"/>
     </row>
     <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D215" s="17"/>
-      <c r="E215" s="16"/>
-      <c r="BO215" s="19"/>
-      <c r="BR215" s="19"/>
+      <c r="D215" s="18"/>
+      <c r="E215" s="5"/>
+      <c r="BO215" s="6"/>
+      <c r="BR215" s="6"/>
     </row>
     <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D216" s="17"/>
-      <c r="E216" s="16"/>
-      <c r="BO216" s="19"/>
-      <c r="BR216" s="19"/>
+      <c r="D216" s="18"/>
+      <c r="E216" s="5"/>
+      <c r="BO216" s="6"/>
+      <c r="BR216" s="6"/>
     </row>
     <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D217" s="17"/>
-      <c r="E217" s="16"/>
-      <c r="BO217" s="19"/>
-      <c r="BR217" s="19"/>
+      <c r="D217" s="18"/>
+      <c r="E217" s="5"/>
+      <c r="BO217" s="6"/>
+      <c r="BR217" s="6"/>
     </row>
     <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D218" s="17"/>
-      <c r="E218" s="16"/>
-      <c r="BO218" s="19"/>
-      <c r="BR218" s="19"/>
+      <c r="D218" s="18"/>
+      <c r="E218" s="5"/>
+      <c r="BO218" s="6"/>
+      <c r="BR218" s="6"/>
     </row>
     <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D219" s="17"/>
-      <c r="E219" s="16"/>
-      <c r="BO219" s="19"/>
-      <c r="BR219" s="19"/>
+      <c r="D219" s="18"/>
+      <c r="E219" s="5"/>
+      <c r="BO219" s="6"/>
+      <c r="BR219" s="6"/>
     </row>
     <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D220" s="17"/>
-      <c r="E220" s="16"/>
-      <c r="BO220" s="19"/>
-      <c r="BR220" s="19"/>
+      <c r="D220" s="18"/>
+      <c r="E220" s="5"/>
+      <c r="BO220" s="6"/>
+      <c r="BR220" s="6"/>
     </row>
     <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D221" s="17"/>
-      <c r="E221" s="16"/>
-      <c r="BO221" s="19"/>
-      <c r="BR221" s="19"/>
+      <c r="D221" s="18"/>
+      <c r="E221" s="5"/>
+      <c r="BO221" s="6"/>
+      <c r="BR221" s="6"/>
     </row>
     <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D222" s="17"/>
-      <c r="E222" s="16"/>
-      <c r="BO222" s="19"/>
-      <c r="BR222" s="19"/>
+      <c r="D222" s="18"/>
+      <c r="E222" s="5"/>
+      <c r="BO222" s="6"/>
+      <c r="BR222" s="6"/>
     </row>
     <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D223" s="17"/>
-      <c r="E223" s="16"/>
-      <c r="BO223" s="19"/>
-      <c r="BR223" s="19"/>
+      <c r="D223" s="18"/>
+      <c r="E223" s="5"/>
+      <c r="BO223" s="6"/>
+      <c r="BR223" s="6"/>
     </row>
     <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D224" s="17"/>
-      <c r="E224" s="16"/>
-      <c r="BO224" s="19"/>
-      <c r="BR224" s="19"/>
+      <c r="D224" s="18"/>
+      <c r="E224" s="5"/>
+      <c r="BO224" s="6"/>
+      <c r="BR224" s="6"/>
     </row>
     <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D225" s="17"/>
-      <c r="E225" s="16"/>
-      <c r="BO225" s="19"/>
-      <c r="BR225" s="19"/>
+      <c r="D225" s="18"/>
+      <c r="E225" s="5"/>
+      <c r="BO225" s="6"/>
+      <c r="BR225" s="6"/>
     </row>
     <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D226" s="17"/>
-      <c r="E226" s="16"/>
-      <c r="BO226" s="19"/>
-      <c r="BR226" s="19"/>
+      <c r="D226" s="18"/>
+      <c r="E226" s="5"/>
+      <c r="BO226" s="6"/>
+      <c r="BR226" s="6"/>
     </row>
     <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D227" s="17"/>
-      <c r="E227" s="16"/>
-      <c r="BO227" s="19"/>
-      <c r="BR227" s="19"/>
+      <c r="D227" s="18"/>
+      <c r="E227" s="5"/>
+      <c r="BO227" s="6"/>
+      <c r="BR227" s="6"/>
     </row>
     <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D228" s="17"/>
-      <c r="E228" s="16"/>
-      <c r="BO228" s="19"/>
-      <c r="BR228" s="19"/>
+      <c r="D228" s="18"/>
+      <c r="E228" s="5"/>
+      <c r="BO228" s="6"/>
+      <c r="BR228" s="6"/>
     </row>
     <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D229" s="17"/>
-      <c r="E229" s="16"/>
-      <c r="BO229" s="19"/>
-      <c r="BR229" s="19"/>
+      <c r="D229" s="18"/>
+      <c r="E229" s="5"/>
+      <c r="BO229" s="6"/>
+      <c r="BR229" s="6"/>
     </row>
     <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D230" s="17"/>
-      <c r="E230" s="16"/>
-      <c r="BO230" s="19"/>
-      <c r="BR230" s="19"/>
+      <c r="D230" s="18"/>
+      <c r="E230" s="5"/>
+      <c r="BO230" s="6"/>
+      <c r="BR230" s="6"/>
     </row>
     <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D231" s="17"/>
-      <c r="E231" s="16"/>
-      <c r="BO231" s="19"/>
-      <c r="BR231" s="19"/>
+      <c r="D231" s="18"/>
+      <c r="E231" s="5"/>
+      <c r="BO231" s="6"/>
+      <c r="BR231" s="6"/>
     </row>
     <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D232" s="17"/>
-      <c r="E232" s="16"/>
-      <c r="BO232" s="19"/>
-      <c r="BR232" s="19"/>
+      <c r="D232" s="18"/>
+      <c r="E232" s="5"/>
+      <c r="BO232" s="6"/>
+      <c r="BR232" s="6"/>
     </row>
     <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D233" s="17"/>
-      <c r="E233" s="16"/>
-      <c r="BO233" s="19"/>
-      <c r="BR233" s="19"/>
+      <c r="D233" s="18"/>
+      <c r="E233" s="5"/>
+      <c r="BO233" s="6"/>
+      <c r="BR233" s="6"/>
     </row>
     <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D234" s="17"/>
-      <c r="E234" s="16"/>
-      <c r="BO234" s="19"/>
-      <c r="BR234" s="19"/>
+      <c r="D234" s="18"/>
+      <c r="E234" s="5"/>
+      <c r="BO234" s="6"/>
+      <c r="BR234" s="6"/>
     </row>
     <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D235" s="17"/>
-      <c r="E235" s="16"/>
-      <c r="BR235" s="19"/>
+      <c r="D235" s="18"/>
+      <c r="E235" s="5"/>
+      <c r="BR235" s="6"/>
     </row>
     <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D236" s="17"/>
-      <c r="E236" s="16"/>
-      <c r="BO236" s="19"/>
-      <c r="BR236" s="19"/>
+      <c r="D236" s="18"/>
+      <c r="E236" s="5"/>
+      <c r="BO236" s="6"/>
+      <c r="BR236" s="6"/>
     </row>
     <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D237" s="17"/>
-      <c r="E237" s="16"/>
-      <c r="BO237" s="19"/>
-      <c r="BR237" s="19"/>
+      <c r="D237" s="18"/>
+      <c r="E237" s="5"/>
+      <c r="BO237" s="6"/>
+      <c r="BR237" s="6"/>
     </row>
     <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D238" s="17"/>
-      <c r="E238" s="16"/>
-      <c r="BO238" s="19"/>
-      <c r="BR238" s="19"/>
+      <c r="D238" s="18"/>
+      <c r="E238" s="5"/>
+      <c r="BO238" s="6"/>
+      <c r="BR238" s="6"/>
     </row>
     <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D239" s="17"/>
-      <c r="E239" s="16"/>
-      <c r="BO239" s="19"/>
-      <c r="BR239" s="19"/>
+      <c r="D239" s="18"/>
+      <c r="E239" s="5"/>
+      <c r="BO239" s="6"/>
+      <c r="BR239" s="6"/>
     </row>
     <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D240" s="17"/>
-      <c r="E240" s="16"/>
-      <c r="BO240" s="19"/>
-      <c r="BR240" s="19"/>
+      <c r="D240" s="18"/>
+      <c r="E240" s="5"/>
+      <c r="BO240" s="6"/>
+      <c r="BR240" s="6"/>
     </row>
     <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D241" s="17"/>
-      <c r="E241" s="16"/>
-      <c r="BO241" s="19"/>
-      <c r="BR241" s="19"/>
+      <c r="D241" s="18"/>
+      <c r="E241" s="5"/>
+      <c r="BO241" s="6"/>
+      <c r="BR241" s="6"/>
     </row>
     <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D242" s="17"/>
-      <c r="E242" s="16"/>
-      <c r="BO242" s="19"/>
-      <c r="BR242" s="19"/>
+      <c r="D242" s="18"/>
+      <c r="E242" s="5"/>
+      <c r="BO242" s="6"/>
+      <c r="BR242" s="6"/>
     </row>
     <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D243" s="17"/>
-      <c r="E243" s="16"/>
-      <c r="BO243" s="19"/>
-      <c r="BR243" s="19"/>
+      <c r="D243" s="18"/>
+      <c r="E243" s="5"/>
+      <c r="BO243" s="6"/>
+      <c r="BR243" s="6"/>
     </row>
     <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D244" s="17"/>
-      <c r="E244" s="16"/>
-      <c r="BO244" s="19"/>
-      <c r="BR244" s="19"/>
+      <c r="D244" s="18"/>
+      <c r="E244" s="5"/>
+      <c r="BO244" s="6"/>
+      <c r="BR244" s="6"/>
     </row>
     <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D245" s="17"/>
-      <c r="E245" s="16"/>
-      <c r="BO245" s="19"/>
-      <c r="BR245" s="19"/>
+      <c r="D245" s="18"/>
+      <c r="E245" s="5"/>
+      <c r="BO245" s="6"/>
+      <c r="BR245" s="6"/>
     </row>
     <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D246" s="17"/>
-      <c r="E246" s="16"/>
-      <c r="BO246" s="19"/>
-      <c r="BR246" s="19"/>
+      <c r="D246" s="18"/>
+      <c r="E246" s="5"/>
+      <c r="BO246" s="6"/>
+      <c r="BR246" s="6"/>
     </row>
     <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D247" s="17"/>
-      <c r="E247" s="16"/>
-      <c r="BO247" s="19"/>
-      <c r="BR247" s="19"/>
+      <c r="D247" s="18"/>
+      <c r="E247" s="5"/>
+      <c r="BO247" s="6"/>
+      <c r="BR247" s="6"/>
     </row>
     <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D248" s="17"/>
-      <c r="E248" s="16"/>
-      <c r="BO248" s="19"/>
-      <c r="BR248" s="19"/>
+      <c r="D248" s="18"/>
+      <c r="E248" s="5"/>
+      <c r="BO248" s="6"/>
+      <c r="BR248" s="6"/>
     </row>
     <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D249" s="17"/>
-      <c r="E249" s="16"/>
-      <c r="BO249" s="19"/>
-      <c r="BR249" s="19"/>
+      <c r="D249" s="18"/>
+      <c r="E249" s="5"/>
+      <c r="BO249" s="6"/>
+      <c r="BR249" s="6"/>
     </row>
     <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D250" s="17"/>
-      <c r="E250" s="16"/>
-      <c r="BO250" s="19"/>
-      <c r="BR250" s="19"/>
+      <c r="D250" s="18"/>
+      <c r="E250" s="5"/>
+      <c r="BO250" s="6"/>
+      <c r="BR250" s="6"/>
     </row>
     <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D251" s="17"/>
-      <c r="E251" s="16"/>
-      <c r="BO251" s="19"/>
-      <c r="BR251" s="19"/>
+      <c r="D251" s="18"/>
+      <c r="E251" s="5"/>
+      <c r="BO251" s="6"/>
+      <c r="BR251" s="6"/>
     </row>
     <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D252" s="17"/>
-      <c r="E252" s="16"/>
-      <c r="BO252" s="19"/>
-      <c r="BR252" s="19"/>
+      <c r="D252" s="18"/>
+      <c r="E252" s="5"/>
+      <c r="BO252" s="6"/>
+      <c r="BR252" s="6"/>
     </row>
     <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D253" s="17"/>
-      <c r="E253" s="16"/>
-      <c r="BO253" s="19"/>
-      <c r="BR253" s="19"/>
+      <c r="D253" s="18"/>
+      <c r="E253" s="5"/>
+      <c r="BO253" s="6"/>
+      <c r="BR253" s="6"/>
     </row>
     <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D254" s="17"/>
-      <c r="E254" s="16"/>
-      <c r="BO254" s="19"/>
-      <c r="BR254" s="19"/>
+      <c r="D254" s="18"/>
+      <c r="E254" s="5"/>
+      <c r="BO254" s="6"/>
+      <c r="BR254" s="6"/>
     </row>
     <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D255" s="17"/>
-      <c r="E255" s="16"/>
-      <c r="BO255" s="19"/>
-      <c r="BR255" s="19"/>
+      <c r="D255" s="18"/>
+      <c r="E255" s="5"/>
+      <c r="BO255" s="6"/>
+      <c r="BR255" s="6"/>
     </row>
     <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D256" s="17"/>
-      <c r="E256" s="16"/>
-      <c r="BO256" s="19"/>
-      <c r="BR256" s="19"/>
+      <c r="D256" s="18"/>
+      <c r="E256" s="5"/>
+      <c r="BO256" s="6"/>
+      <c r="BR256" s="6"/>
     </row>
     <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D257" s="17"/>
-      <c r="E257" s="16"/>
-      <c r="BO257" s="19"/>
-      <c r="BR257" s="19"/>
+      <c r="D257" s="18"/>
+      <c r="E257" s="5"/>
+      <c r="BO257" s="6"/>
+      <c r="BR257" s="6"/>
     </row>
     <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D258" s="17"/>
-      <c r="E258" s="16"/>
-      <c r="BO258" s="19"/>
-      <c r="BR258" s="19"/>
+      <c r="D258" s="18"/>
+      <c r="E258" s="5"/>
+      <c r="BO258" s="6"/>
+      <c r="BR258" s="6"/>
     </row>
     <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D259" s="17"/>
-      <c r="E259" s="16"/>
-      <c r="BO259" s="19"/>
-      <c r="BR259" s="19"/>
+      <c r="D259" s="18"/>
+      <c r="E259" s="5"/>
+      <c r="BO259" s="6"/>
+      <c r="BR259" s="6"/>
     </row>
     <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D260" s="17"/>
-      <c r="E260" s="16"/>
-      <c r="BO260" s="19"/>
-      <c r="BR260" s="19"/>
+      <c r="D260" s="18"/>
+      <c r="E260" s="5"/>
+      <c r="BO260" s="6"/>
+      <c r="BR260" s="6"/>
     </row>
     <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D261" s="17"/>
-      <c r="E261" s="16"/>
-      <c r="BO261" s="19"/>
-      <c r="BR261" s="19"/>
+      <c r="D261" s="18"/>
+      <c r="E261" s="5"/>
+      <c r="BO261" s="6"/>
+      <c r="BR261" s="6"/>
     </row>
     <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D262" s="17"/>
-      <c r="E262" s="16"/>
-      <c r="BO262" s="19"/>
-      <c r="BR262" s="19"/>
+      <c r="D262" s="18"/>
+      <c r="E262" s="5"/>
+      <c r="BO262" s="6"/>
+      <c r="BR262" s="6"/>
     </row>
     <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D263" s="17"/>
-      <c r="E263" s="16"/>
-      <c r="BO263" s="19"/>
-      <c r="BR263" s="19"/>
+      <c r="D263" s="18"/>
+      <c r="E263" s="5"/>
+      <c r="BO263" s="6"/>
+      <c r="BR263" s="6"/>
     </row>
     <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D264" s="17"/>
-      <c r="E264" s="16"/>
-      <c r="BO264" s="19"/>
-      <c r="BR264" s="19"/>
+      <c r="D264" s="18"/>
+      <c r="E264" s="5"/>
+      <c r="BO264" s="6"/>
+      <c r="BR264" s="6"/>
     </row>
     <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D265" s="17"/>
-      <c r="E265" s="16"/>
-      <c r="BO265" s="19"/>
-      <c r="BR265" s="19"/>
+      <c r="D265" s="18"/>
+      <c r="E265" s="5"/>
+      <c r="BO265" s="6"/>
+      <c r="BR265" s="6"/>
     </row>
     <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D266" s="17"/>
-      <c r="E266" s="16"/>
-      <c r="BO266" s="19"/>
-      <c r="BR266" s="19"/>
+      <c r="D266" s="18"/>
+      <c r="E266" s="5"/>
+      <c r="BO266" s="6"/>
+      <c r="BR266" s="6"/>
     </row>
     <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D267" s="17"/>
-      <c r="E267" s="16"/>
-      <c r="BO267" s="19"/>
-      <c r="BR267" s="19"/>
+      <c r="D267" s="18"/>
+      <c r="E267" s="5"/>
+      <c r="BO267" s="6"/>
+      <c r="BR267" s="6"/>
     </row>
     <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D268" s="17"/>
-      <c r="E268" s="16"/>
-      <c r="BO268" s="19"/>
-      <c r="BR268" s="19"/>
+      <c r="D268" s="18"/>
+      <c r="E268" s="5"/>
+      <c r="BO268" s="6"/>
+      <c r="BR268" s="6"/>
     </row>
     <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D269" s="17"/>
-      <c r="E269" s="16"/>
-      <c r="BO269" s="19"/>
-      <c r="BR269" s="19"/>
+      <c r="D269" s="18"/>
+      <c r="E269" s="5"/>
+      <c r="BO269" s="6"/>
+      <c r="BR269" s="6"/>
     </row>
     <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D270" s="17"/>
-      <c r="E270" s="16"/>
-      <c r="BO270" s="19"/>
-      <c r="BR270" s="19"/>
+      <c r="D270" s="18"/>
+      <c r="E270" s="5"/>
+      <c r="BO270" s="6"/>
+      <c r="BR270" s="6"/>
     </row>
     <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D271" s="17"/>
-      <c r="E271" s="16"/>
-      <c r="BO271" s="19"/>
-      <c r="BR271" s="19"/>
+      <c r="D271" s="18"/>
+      <c r="E271" s="5"/>
+      <c r="BO271" s="6"/>
+      <c r="BR271" s="6"/>
     </row>
     <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D272" s="17"/>
-      <c r="E272" s="16"/>
-      <c r="BO272" s="19"/>
-      <c r="BR272" s="19"/>
+      <c r="D272" s="18"/>
+      <c r="E272" s="5"/>
+      <c r="BO272" s="6"/>
+      <c r="BR272" s="6"/>
     </row>
     <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D273" s="17"/>
-      <c r="E273" s="16"/>
-      <c r="BO273" s="19"/>
-      <c r="BR273" s="19"/>
+      <c r="D273" s="18"/>
+      <c r="E273" s="5"/>
+      <c r="BO273" s="6"/>
+      <c r="BR273" s="6"/>
     </row>
     <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D274" s="17"/>
-      <c r="E274" s="16"/>
-      <c r="BO274" s="19"/>
-      <c r="BR274" s="19"/>
+      <c r="D274" s="18"/>
+      <c r="E274" s="5"/>
+      <c r="BO274" s="6"/>
+      <c r="BR274" s="6"/>
     </row>
     <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D275" s="17"/>
-      <c r="E275" s="16"/>
-      <c r="BO275" s="19"/>
-      <c r="BR275" s="19"/>
+      <c r="D275" s="18"/>
+      <c r="E275" s="5"/>
+      <c r="BO275" s="6"/>
+      <c r="BR275" s="6"/>
     </row>
     <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D276" s="17"/>
-      <c r="E276" s="16"/>
-      <c r="BO276" s="19"/>
-      <c r="BR276" s="19"/>
+      <c r="D276" s="18"/>
+      <c r="E276" s="5"/>
+      <c r="BO276" s="6"/>
+      <c r="BR276" s="6"/>
     </row>
     <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D277" s="17"/>
-      <c r="E277" s="16"/>
-      <c r="BO277" s="19"/>
-      <c r="BR277" s="19"/>
+      <c r="D277" s="18"/>
+      <c r="E277" s="5"/>
+      <c r="BO277" s="6"/>
+      <c r="BR277" s="6"/>
     </row>
     <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D278" s="17"/>
-      <c r="E278" s="16"/>
-      <c r="BR278" s="19"/>
+      <c r="D278" s="18"/>
+      <c r="E278" s="5"/>
+      <c r="BR278" s="6"/>
     </row>
     <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D279" s="17"/>
-      <c r="E279" s="16"/>
-      <c r="BO279" s="19"/>
-      <c r="BR279" s="19"/>
+      <c r="D279" s="18"/>
+      <c r="E279" s="5"/>
+      <c r="BO279" s="6"/>
+      <c r="BR279" s="6"/>
     </row>
     <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D280" s="17"/>
-      <c r="E280" s="16"/>
-      <c r="BO280" s="19"/>
-      <c r="BR280" s="19"/>
+      <c r="D280" s="18"/>
+      <c r="E280" s="5"/>
+      <c r="BO280" s="6"/>
+      <c r="BR280" s="6"/>
     </row>
     <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D281" s="17"/>
-      <c r="E281" s="16"/>
-      <c r="BO281" s="19"/>
-      <c r="BR281" s="19"/>
+      <c r="D281" s="18"/>
+      <c r="E281" s="5"/>
+      <c r="BO281" s="6"/>
+      <c r="BR281" s="6"/>
     </row>
     <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D282" s="17"/>
-      <c r="E282" s="16"/>
-      <c r="BO282" s="19"/>
-      <c r="BR282" s="19"/>
+      <c r="D282" s="18"/>
+      <c r="E282" s="5"/>
+      <c r="BO282" s="6"/>
+      <c r="BR282" s="6"/>
     </row>
     <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D283" s="17"/>
-      <c r="E283" s="16"/>
-      <c r="BO283" s="19"/>
-      <c r="BR283" s="19"/>
+      <c r="D283" s="18"/>
+      <c r="E283" s="5"/>
+      <c r="BO283" s="6"/>
+      <c r="BR283" s="6"/>
     </row>
     <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D284" s="17"/>
-      <c r="E284" s="16"/>
-      <c r="BO284" s="19"/>
-      <c r="BR284" s="19"/>
+      <c r="D284" s="18"/>
+      <c r="E284" s="5"/>
+      <c r="BO284" s="6"/>
+      <c r="BR284" s="6"/>
     </row>
     <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D285" s="17"/>
-      <c r="E285" s="16"/>
-      <c r="BO285" s="19"/>
-      <c r="BR285" s="19"/>
+      <c r="D285" s="18"/>
+      <c r="E285" s="5"/>
+      <c r="BO285" s="6"/>
+      <c r="BR285" s="6"/>
     </row>
     <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D286" s="17"/>
-      <c r="E286" s="16"/>
-      <c r="BO286" s="19"/>
-      <c r="BR286" s="19"/>
+      <c r="D286" s="18"/>
+      <c r="E286" s="5"/>
+      <c r="BO286" s="6"/>
+      <c r="BR286" s="6"/>
     </row>
     <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D287" s="17"/>
-      <c r="E287" s="16"/>
-      <c r="BO287" s="19"/>
-      <c r="BR287" s="19"/>
+      <c r="D287" s="18"/>
+      <c r="E287" s="5"/>
+      <c r="BO287" s="6"/>
+      <c r="BR287" s="6"/>
     </row>
     <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D288" s="17"/>
-      <c r="E288" s="16"/>
-      <c r="BO288" s="19"/>
-      <c r="BR288" s="19"/>
+      <c r="D288" s="18"/>
+      <c r="E288" s="5"/>
+      <c r="BO288" s="6"/>
+      <c r="BR288" s="6"/>
     </row>
     <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D289" s="17"/>
-      <c r="E289" s="16"/>
-      <c r="BO289" s="19"/>
-      <c r="BR289" s="19"/>
+      <c r="D289" s="18"/>
+      <c r="E289" s="5"/>
+      <c r="BO289" s="6"/>
+      <c r="BR289" s="6"/>
     </row>
     <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D290" s="17"/>
-      <c r="E290" s="16"/>
-      <c r="BO290" s="19"/>
-      <c r="BR290" s="19"/>
+      <c r="D290" s="18"/>
+      <c r="E290" s="5"/>
+      <c r="BO290" s="6"/>
+      <c r="BR290" s="6"/>
     </row>
     <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D291" s="17"/>
-      <c r="E291" s="16"/>
-      <c r="BO291" s="19"/>
-      <c r="BR291" s="19"/>
+      <c r="D291" s="18"/>
+      <c r="E291" s="5"/>
+      <c r="BO291" s="6"/>
+      <c r="BR291" s="6"/>
     </row>
     <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D292" s="17"/>
-      <c r="E292" s="16"/>
-      <c r="BO292" s="19"/>
-      <c r="BR292" s="19"/>
+      <c r="D292" s="18"/>
+      <c r="E292" s="5"/>
+      <c r="BO292" s="6"/>
+      <c r="BR292" s="6"/>
     </row>
     <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D293" s="17"/>
-      <c r="E293" s="16"/>
-      <c r="BO293" s="19"/>
-      <c r="BR293" s="19"/>
+      <c r="D293" s="18"/>
+      <c r="E293" s="5"/>
+      <c r="BO293" s="6"/>
+      <c r="BR293" s="6"/>
     </row>
     <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D294" s="17"/>
-      <c r="E294" s="16"/>
-      <c r="BO294" s="19"/>
-      <c r="BR294" s="19"/>
+      <c r="D294" s="18"/>
+      <c r="E294" s="5"/>
+      <c r="BO294" s="6"/>
+      <c r="BR294" s="6"/>
     </row>
     <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D295" s="17"/>
-      <c r="E295" s="16"/>
-      <c r="BO295" s="19"/>
-      <c r="BR295" s="19"/>
+      <c r="D295" s="18"/>
+      <c r="E295" s="5"/>
+      <c r="BO295" s="6"/>
+      <c r="BR295" s="6"/>
     </row>
     <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D296" s="17"/>
-      <c r="E296" s="16"/>
-      <c r="BO296" s="19"/>
-      <c r="BR296" s="19"/>
+      <c r="D296" s="18"/>
+      <c r="E296" s="5"/>
+      <c r="BO296" s="6"/>
+      <c r="BR296" s="6"/>
     </row>
     <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D297" s="17"/>
-      <c r="E297" s="16"/>
-      <c r="BO297" s="19"/>
-      <c r="BR297" s="19"/>
+      <c r="D297" s="18"/>
+      <c r="E297" s="5"/>
+      <c r="BO297" s="6"/>
+      <c r="BR297" s="6"/>
     </row>
     <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D298" s="17"/>
-      <c r="E298" s="16"/>
-      <c r="BO298" s="19"/>
-      <c r="BR298" s="19"/>
+      <c r="D298" s="18"/>
+      <c r="E298" s="5"/>
+      <c r="BO298" s="6"/>
+      <c r="BR298" s="6"/>
     </row>
     <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D299" s="17"/>
-      <c r="E299" s="16"/>
-      <c r="BO299" s="19"/>
-      <c r="BR299" s="19"/>
+      <c r="D299" s="18"/>
+      <c r="E299" s="5"/>
+      <c r="BO299" s="6"/>
+      <c r="BR299" s="6"/>
     </row>
     <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D300" s="17"/>
-      <c r="E300" s="16"/>
-      <c r="BO300" s="19"/>
-      <c r="BR300" s="19"/>
+      <c r="D300" s="18"/>
+      <c r="E300" s="5"/>
+      <c r="BO300" s="6"/>
+      <c r="BR300" s="6"/>
     </row>
     <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D301" s="17"/>
-      <c r="E301" s="16"/>
-      <c r="BO301" s="19"/>
-      <c r="BR301" s="19"/>
+      <c r="D301" s="18"/>
+      <c r="E301" s="5"/>
+      <c r="BO301" s="6"/>
+      <c r="BR301" s="6"/>
     </row>
     <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D302" s="17"/>
-      <c r="E302" s="16"/>
-      <c r="BO302" s="19"/>
-      <c r="BR302" s="19"/>
+      <c r="D302" s="18"/>
+      <c r="E302" s="5"/>
+      <c r="BO302" s="6"/>
+      <c r="BR302" s="6"/>
     </row>
     <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D303" s="17"/>
-      <c r="E303" s="16"/>
-      <c r="BO303" s="19"/>
-      <c r="BR303" s="19"/>
+      <c r="D303" s="18"/>
+      <c r="E303" s="5"/>
+      <c r="BO303" s="6"/>
+      <c r="BR303" s="6"/>
     </row>
     <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D304" s="17"/>
-      <c r="E304" s="16"/>
-      <c r="BO304" s="19"/>
-      <c r="BR304" s="19"/>
+      <c r="D304" s="18"/>
+      <c r="E304" s="5"/>
+      <c r="BO304" s="6"/>
+      <c r="BR304" s="6"/>
     </row>
     <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D305" s="17"/>
-      <c r="E305" s="16"/>
-      <c r="BO305" s="19"/>
-      <c r="BR305" s="19"/>
+      <c r="D305" s="18"/>
+      <c r="E305" s="5"/>
+      <c r="BO305" s="6"/>
+      <c r="BR305" s="6"/>
     </row>
     <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D306" s="17"/>
-      <c r="E306" s="16"/>
-      <c r="BO306" s="19"/>
-      <c r="BR306" s="19"/>
+      <c r="D306" s="18"/>
+      <c r="E306" s="5"/>
+      <c r="BO306" s="6"/>
+      <c r="BR306" s="6"/>
     </row>
     <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D307" s="17"/>
-      <c r="E307" s="16"/>
-      <c r="BO307" s="19"/>
-      <c r="BR307" s="19"/>
+      <c r="D307" s="18"/>
+      <c r="E307" s="5"/>
+      <c r="BO307" s="6"/>
+      <c r="BR307" s="6"/>
     </row>
     <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D308" s="17"/>
-      <c r="E308" s="16"/>
-      <c r="BO308" s="19"/>
-      <c r="BR308" s="19"/>
+      <c r="D308" s="18"/>
+      <c r="E308" s="5"/>
+      <c r="BO308" s="6"/>
+      <c r="BR308" s="6"/>
     </row>
     <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D309" s="17"/>
-      <c r="E309" s="16"/>
-      <c r="BO309" s="19"/>
-      <c r="BR309" s="19"/>
+      <c r="D309" s="18"/>
+      <c r="E309" s="5"/>
+      <c r="BO309" s="6"/>
+      <c r="BR309" s="6"/>
     </row>
     <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D310" s="17"/>
-      <c r="E310" s="16"/>
-      <c r="BO310" s="19"/>
-      <c r="BR310" s="19"/>
+      <c r="D310" s="18"/>
+      <c r="E310" s="5"/>
+      <c r="BO310" s="6"/>
+      <c r="BR310" s="6"/>
     </row>
     <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D311" s="17"/>
-      <c r="E311" s="16"/>
-      <c r="BO311" s="19"/>
-      <c r="BR311" s="19"/>
+      <c r="D311" s="18"/>
+      <c r="E311" s="5"/>
+      <c r="BO311" s="6"/>
+      <c r="BR311" s="6"/>
     </row>
     <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D312" s="17"/>
-      <c r="E312" s="16"/>
-      <c r="BO312" s="19"/>
-      <c r="BR312" s="19"/>
+      <c r="D312" s="18"/>
+      <c r="E312" s="5"/>
+      <c r="BO312" s="6"/>
+      <c r="BR312" s="6"/>
     </row>
     <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D313" s="17"/>
-      <c r="E313" s="16"/>
-      <c r="BO313" s="19"/>
-      <c r="BR313" s="19"/>
+      <c r="D313" s="18"/>
+      <c r="E313" s="5"/>
+      <c r="BO313" s="6"/>
+      <c r="BR313" s="6"/>
     </row>
     <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D314" s="17"/>
-      <c r="E314" s="16"/>
-      <c r="BO314" s="19"/>
-      <c r="BR314" s="19"/>
+      <c r="D314" s="18"/>
+      <c r="E314" s="5"/>
+      <c r="BO314" s="6"/>
+      <c r="BR314" s="6"/>
     </row>
     <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D315" s="17"/>
-      <c r="E315" s="16"/>
-      <c r="BO315" s="19"/>
-      <c r="BR315" s="19"/>
+      <c r="D315" s="18"/>
+      <c r="E315" s="5"/>
+      <c r="BO315" s="6"/>
+      <c r="BR315" s="6"/>
     </row>
     <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D316" s="17"/>
-      <c r="E316" s="16"/>
-      <c r="BO316" s="19"/>
-      <c r="BR316" s="19"/>
+      <c r="D316" s="18"/>
+      <c r="E316" s="5"/>
+      <c r="BO316" s="6"/>
+      <c r="BR316" s="6"/>
     </row>
     <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D317" s="17"/>
-      <c r="E317" s="16"/>
-      <c r="BO317" s="19"/>
-      <c r="BR317" s="19"/>
+      <c r="D317" s="18"/>
+      <c r="E317" s="5"/>
+      <c r="BO317" s="6"/>
+      <c r="BR317" s="6"/>
     </row>
     <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D318" s="17"/>
-      <c r="E318" s="16"/>
-      <c r="BO318" s="19"/>
-      <c r="BR318" s="19"/>
+      <c r="D318" s="18"/>
+      <c r="E318" s="5"/>
+      <c r="BO318" s="6"/>
+      <c r="BR318" s="6"/>
     </row>
     <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D319" s="17"/>
-      <c r="E319" s="16"/>
-      <c r="BO319" s="19"/>
-      <c r="BR319" s="19"/>
+      <c r="D319" s="18"/>
+      <c r="E319" s="5"/>
+      <c r="BO319" s="6"/>
+      <c r="BR319" s="6"/>
     </row>
     <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D320" s="17"/>
-      <c r="E320" s="16"/>
-      <c r="BO320" s="19"/>
-      <c r="BR320" s="19"/>
+      <c r="D320" s="18"/>
+      <c r="E320" s="5"/>
+      <c r="BO320" s="6"/>
+      <c r="BR320" s="6"/>
     </row>
     <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D321" s="17"/>
-      <c r="E321" s="16"/>
-      <c r="BO321" s="19"/>
-      <c r="BR321" s="19"/>
+      <c r="D321" s="18"/>
+      <c r="E321" s="5"/>
+      <c r="BO321" s="6"/>
+      <c r="BR321" s="6"/>
     </row>
     <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D322" s="17"/>
-      <c r="E322" s="16"/>
-      <c r="BO322" s="19"/>
-      <c r="BR322" s="19"/>
+      <c r="D322" s="18"/>
+      <c r="E322" s="5"/>
+      <c r="BO322" s="6"/>
+      <c r="BR322" s="6"/>
     </row>
     <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D323" s="17"/>
-      <c r="E323" s="16"/>
-      <c r="BO323" s="19"/>
-      <c r="BR323" s="19"/>
+      <c r="D323" s="18"/>
+      <c r="E323" s="5"/>
+      <c r="BO323" s="6"/>
+      <c r="BR323" s="6"/>
     </row>
     <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D324" s="17"/>
-      <c r="E324" s="16"/>
-      <c r="BO324" s="19"/>
-      <c r="BR324" s="19"/>
+      <c r="D324" s="18"/>
+      <c r="E324" s="5"/>
+      <c r="BO324" s="6"/>
+      <c r="BR324" s="6"/>
     </row>
     <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D325" s="17"/>
-      <c r="E325" s="16"/>
-      <c r="BO325" s="19"/>
-      <c r="BR325" s="19"/>
+      <c r="D325" s="18"/>
+      <c r="E325" s="5"/>
+      <c r="BO325" s="6"/>
+      <c r="BR325" s="6"/>
     </row>
     <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D326" s="17"/>
-      <c r="E326" s="16"/>
-      <c r="BO326" s="19"/>
-      <c r="BR326" s="19"/>
+      <c r="D326" s="18"/>
+      <c r="E326" s="5"/>
+      <c r="BO326" s="6"/>
+      <c r="BR326" s="6"/>
     </row>
     <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D327" s="17"/>
-      <c r="E327" s="16"/>
-      <c r="BO327" s="19"/>
-      <c r="BR327" s="19"/>
+      <c r="D327" s="18"/>
+      <c r="E327" s="5"/>
+      <c r="BO327" s="6"/>
+      <c r="BR327" s="6"/>
     </row>
     <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D328" s="17"/>
-      <c r="E328" s="16"/>
-      <c r="BO328" s="19"/>
-      <c r="BR328" s="19"/>
+      <c r="D328" s="18"/>
+      <c r="E328" s="5"/>
+      <c r="BO328" s="6"/>
+      <c r="BR328" s="6"/>
     </row>
     <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D329" s="17"/>
-      <c r="E329" s="16"/>
-      <c r="BO329" s="19"/>
-      <c r="BR329" s="19"/>
+      <c r="D329" s="18"/>
+      <c r="E329" s="5"/>
+      <c r="BO329" s="6"/>
+      <c r="BR329" s="6"/>
     </row>
     <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D330" s="17"/>
-      <c r="E330" s="16"/>
-      <c r="BO330" s="19"/>
-      <c r="BR330" s="19"/>
+      <c r="D330" s="18"/>
+      <c r="E330" s="5"/>
+      <c r="BO330" s="6"/>
+      <c r="BR330" s="6"/>
     </row>
     <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D331" s="17"/>
-      <c r="E331" s="16"/>
-      <c r="BO331" s="19"/>
-      <c r="BR331" s="19"/>
+      <c r="D331" s="18"/>
+      <c r="E331" s="5"/>
+      <c r="BO331" s="6"/>
+      <c r="BR331" s="6"/>
     </row>
     <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D332" s="17"/>
-      <c r="E332" s="16"/>
-      <c r="BO332" s="19"/>
-      <c r="BR332" s="19"/>
+      <c r="D332" s="18"/>
+      <c r="E332" s="5"/>
+      <c r="BO332" s="6"/>
+      <c r="BR332" s="6"/>
     </row>
     <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D333" s="17"/>
-      <c r="E333" s="16"/>
-      <c r="BO333" s="19"/>
-      <c r="BR333" s="19"/>
+      <c r="D333" s="18"/>
+      <c r="E333" s="5"/>
+      <c r="BO333" s="6"/>
+      <c r="BR333" s="6"/>
     </row>
     <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D334" s="17"/>
-      <c r="E334" s="16"/>
-      <c r="BR334" s="19"/>
+      <c r="D334" s="18"/>
+      <c r="E334" s="5"/>
+      <c r="BR334" s="6"/>
     </row>
     <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D335" s="17"/>
-      <c r="E335" s="16"/>
-      <c r="BR335" s="19"/>
+      <c r="D335" s="18"/>
+      <c r="E335" s="5"/>
+      <c r="BR335" s="6"/>
     </row>
     <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D336" s="17"/>
-      <c r="E336" s="16"/>
-      <c r="BR336" s="19"/>
+      <c r="D336" s="18"/>
+      <c r="E336" s="5"/>
+      <c r="BR336" s="6"/>
     </row>
     <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D337" s="17"/>
-      <c r="E337" s="16"/>
-      <c r="BO337" s="19"/>
-      <c r="BR337" s="19"/>
+      <c r="D337" s="18"/>
+      <c r="E337" s="5"/>
+      <c r="BO337" s="6"/>
+      <c r="BR337" s="6"/>
     </row>
     <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D338" s="17"/>
-      <c r="E338" s="16"/>
-      <c r="BO338" s="19"/>
-      <c r="BR338" s="19"/>
+      <c r="D338" s="18"/>
+      <c r="E338" s="5"/>
+      <c r="BO338" s="6"/>
+      <c r="BR338" s="6"/>
     </row>
     <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D339" s="17"/>
-      <c r="E339" s="16"/>
-      <c r="BO339" s="19"/>
-      <c r="BR339" s="19"/>
+      <c r="D339" s="18"/>
+      <c r="E339" s="5"/>
+      <c r="BO339" s="6"/>
+      <c r="BR339" s="6"/>
     </row>
     <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D340" s="17"/>
-      <c r="E340" s="16"/>
-      <c r="BO340" s="19"/>
-      <c r="BR340" s="19"/>
+      <c r="D340" s="18"/>
+      <c r="E340" s="5"/>
+      <c r="BO340" s="6"/>
+      <c r="BR340" s="6"/>
     </row>
     <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D341" s="17"/>
-      <c r="E341" s="16"/>
-      <c r="BO341" s="19"/>
-      <c r="BR341" s="19"/>
+      <c r="D341" s="18"/>
+      <c r="E341" s="5"/>
+      <c r="BO341" s="6"/>
+      <c r="BR341" s="6"/>
     </row>
     <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D342" s="17"/>
-      <c r="E342" s="16"/>
-      <c r="BO342" s="19"/>
-      <c r="BR342" s="19"/>
+      <c r="D342" s="18"/>
+      <c r="E342" s="5"/>
+      <c r="BO342" s="6"/>
+      <c r="BR342" s="6"/>
     </row>
     <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D343" s="17"/>
-      <c r="E343" s="16"/>
-      <c r="BO343" s="19"/>
-      <c r="BR343" s="19"/>
+      <c r="D343" s="18"/>
+      <c r="E343" s="5"/>
+      <c r="BO343" s="6"/>
+      <c r="BR343" s="6"/>
     </row>
     <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D344" s="17"/>
-      <c r="E344" s="16"/>
-      <c r="BO344" s="19"/>
-      <c r="BR344" s="19"/>
+      <c r="D344" s="18"/>
+      <c r="E344" s="5"/>
+      <c r="BO344" s="6"/>
+      <c r="BR344" s="6"/>
     </row>
     <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D345" s="17"/>
-      <c r="E345" s="16"/>
-      <c r="BO345" s="19"/>
-      <c r="BR345" s="19"/>
+      <c r="D345" s="18"/>
+      <c r="E345" s="5"/>
+      <c r="BO345" s="6"/>
+      <c r="BR345" s="6"/>
     </row>
     <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D346" s="17"/>
-      <c r="E346" s="16"/>
-      <c r="BO346" s="19"/>
-      <c r="BR346" s="19"/>
+      <c r="D346" s="18"/>
+      <c r="E346" s="5"/>
+      <c r="BO346" s="6"/>
+      <c r="BR346" s="6"/>
     </row>
     <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D347" s="17"/>
-      <c r="E347" s="16"/>
-      <c r="BO347" s="19"/>
-      <c r="BR347" s="19"/>
+      <c r="D347" s="18"/>
+      <c r="E347" s="5"/>
+      <c r="BO347" s="6"/>
+      <c r="BR347" s="6"/>
     </row>
     <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D348" s="17"/>
-      <c r="E348" s="16"/>
-      <c r="BO348" s="19"/>
-      <c r="BR348" s="19"/>
+      <c r="D348" s="18"/>
+      <c r="E348" s="5"/>
+      <c r="BO348" s="6"/>
+      <c r="BR348" s="6"/>
     </row>
     <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D349" s="17"/>
-      <c r="E349" s="16"/>
-      <c r="BO349" s="19"/>
-      <c r="BR349" s="19"/>
+      <c r="D349" s="18"/>
+      <c r="E349" s="5"/>
+      <c r="BO349" s="6"/>
+      <c r="BR349" s="6"/>
     </row>
     <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D350" s="17"/>
-      <c r="E350" s="16"/>
-      <c r="BO350" s="19"/>
-      <c r="BR350" s="19"/>
+      <c r="D350" s="18"/>
+      <c r="E350" s="5"/>
+      <c r="BO350" s="6"/>
+      <c r="BR350" s="6"/>
     </row>
     <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D351" s="17"/>
-      <c r="E351" s="16"/>
-      <c r="BO351" s="19"/>
-      <c r="BR351" s="19"/>
+      <c r="D351" s="18"/>
+      <c r="E351" s="5"/>
+      <c r="BO351" s="6"/>
+      <c r="BR351" s="6"/>
     </row>
     <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D352" s="17"/>
-      <c r="E352" s="16"/>
-      <c r="BO352" s="19"/>
-      <c r="BR352" s="19"/>
+      <c r="D352" s="18"/>
+      <c r="E352" s="5"/>
+      <c r="BO352" s="6"/>
+      <c r="BR352" s="6"/>
     </row>
     <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D353" s="17"/>
-      <c r="E353" s="16"/>
-      <c r="BO353" s="19"/>
-      <c r="BR353" s="19"/>
+      <c r="D353" s="18"/>
+      <c r="E353" s="5"/>
+      <c r="BO353" s="6"/>
+      <c r="BR353" s="6"/>
     </row>
     <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D354" s="17"/>
-      <c r="E354" s="16"/>
-      <c r="BO354" s="19"/>
-      <c r="BR354" s="19"/>
+      <c r="D354" s="18"/>
+      <c r="E354" s="5"/>
+      <c r="BO354" s="6"/>
+      <c r="BR354" s="6"/>
     </row>
     <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D355" s="17"/>
-      <c r="E355" s="16"/>
-      <c r="BO355" s="19"/>
-      <c r="BR355" s="19"/>
+      <c r="D355" s="18"/>
+      <c r="E355" s="5"/>
+      <c r="BO355" s="6"/>
+      <c r="BR355" s="6"/>
     </row>
     <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D356" s="17"/>
-      <c r="E356" s="16"/>
-      <c r="BO356" s="19"/>
-      <c r="BR356" s="19"/>
+      <c r="D356" s="18"/>
+      <c r="E356" s="5"/>
+      <c r="BO356" s="6"/>
+      <c r="BR356" s="6"/>
     </row>
     <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D357" s="17"/>
-      <c r="E357" s="16"/>
-      <c r="BO357" s="19"/>
-      <c r="BR357" s="19"/>
+      <c r="D357" s="18"/>
+      <c r="E357" s="5"/>
+      <c r="BO357" s="6"/>
+      <c r="BR357" s="6"/>
     </row>
     <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D358" s="17"/>
-      <c r="E358" s="16"/>
-      <c r="BO358" s="19"/>
-      <c r="BR358" s="19"/>
+      <c r="D358" s="18"/>
+      <c r="E358" s="5"/>
+      <c r="BO358" s="6"/>
+      <c r="BR358" s="6"/>
     </row>
     <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D359" s="17"/>
-      <c r="E359" s="16"/>
-      <c r="BO359" s="19"/>
-      <c r="BR359" s="19"/>
+      <c r="D359" s="18"/>
+      <c r="E359" s="5"/>
+      <c r="BO359" s="6"/>
+      <c r="BR359" s="6"/>
     </row>
     <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D360" s="17"/>
-      <c r="E360" s="16"/>
-      <c r="BO360" s="19"/>
-      <c r="BR360" s="19"/>
+      <c r="D360" s="18"/>
+      <c r="E360" s="5"/>
+      <c r="BO360" s="6"/>
+      <c r="BR360" s="6"/>
     </row>
     <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D361" s="17"/>
-      <c r="E361" s="16"/>
-      <c r="BO361" s="19"/>
-      <c r="BR361" s="19"/>
+      <c r="D361" s="18"/>
+      <c r="E361" s="5"/>
+      <c r="BO361" s="6"/>
+      <c r="BR361" s="6"/>
     </row>
     <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D362" s="17"/>
-      <c r="E362" s="16"/>
-      <c r="BO362" s="19"/>
-      <c r="BR362" s="19"/>
+      <c r="D362" s="18"/>
+      <c r="E362" s="5"/>
+      <c r="BO362" s="6"/>
+      <c r="BR362" s="6"/>
     </row>
     <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D363" s="17"/>
-      <c r="E363" s="16"/>
-      <c r="BO363" s="19"/>
-      <c r="BR363" s="19"/>
+      <c r="D363" s="18"/>
+      <c r="E363" s="5"/>
+      <c r="BO363" s="6"/>
+      <c r="BR363" s="6"/>
     </row>
     <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D364" s="17"/>
-      <c r="E364" s="16"/>
-      <c r="BO364" s="19"/>
-      <c r="BR364" s="19"/>
+      <c r="D364" s="18"/>
+      <c r="E364" s="5"/>
+      <c r="BO364" s="6"/>
+      <c r="BR364" s="6"/>
     </row>
     <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D365" s="17"/>
-      <c r="E365" s="16"/>
-      <c r="BO365" s="19"/>
-      <c r="BR365" s="19"/>
+      <c r="D365" s="18"/>
+      <c r="E365" s="5"/>
+      <c r="BO365" s="6"/>
+      <c r="BR365" s="6"/>
     </row>
     <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D366" s="17"/>
-      <c r="E366" s="16"/>
-      <c r="BO366" s="19"/>
-      <c r="BR366" s="19"/>
+      <c r="D366" s="18"/>
+      <c r="E366" s="5"/>
+      <c r="BO366" s="6"/>
+      <c r="BR366" s="6"/>
     </row>
     <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D367" s="17"/>
-      <c r="E367" s="16"/>
-      <c r="BO367" s="19"/>
-      <c r="BR367" s="19"/>
+      <c r="D367" s="18"/>
+      <c r="E367" s="5"/>
+      <c r="BO367" s="6"/>
+      <c r="BR367" s="6"/>
     </row>
     <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D368" s="17"/>
-      <c r="E368" s="16"/>
-      <c r="BO368" s="19"/>
-      <c r="BR368" s="19"/>
+      <c r="D368" s="18"/>
+      <c r="E368" s="5"/>
+      <c r="BO368" s="6"/>
+      <c r="BR368" s="6"/>
     </row>
     <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D369" s="17"/>
-      <c r="E369" s="16"/>
-      <c r="BO369" s="19"/>
-      <c r="BR369" s="19"/>
+      <c r="D369" s="18"/>
+      <c r="E369" s="5"/>
+      <c r="BO369" s="6"/>
+      <c r="BR369" s="6"/>
     </row>
     <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D370" s="17"/>
-      <c r="E370" s="16"/>
-      <c r="BO370" s="19"/>
-      <c r="BR370" s="19"/>
+      <c r="D370" s="18"/>
+      <c r="E370" s="5"/>
+      <c r="BO370" s="6"/>
+      <c r="BR370" s="6"/>
     </row>
     <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D371" s="17"/>
-      <c r="E371" s="16"/>
-      <c r="BR371" s="19"/>
+      <c r="D371" s="18"/>
+      <c r="E371" s="5"/>
+      <c r="BR371" s="6"/>
     </row>
     <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D372" s="17"/>
-      <c r="E372" s="16"/>
-      <c r="BR372" s="19"/>
+      <c r="D372" s="18"/>
+      <c r="E372" s="5"/>
+      <c r="BR372" s="6"/>
     </row>
     <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D373" s="17"/>
-      <c r="E373" s="16"/>
-      <c r="BO373" s="19"/>
-      <c r="BR373" s="19"/>
+      <c r="D373" s="18"/>
+      <c r="E373" s="5"/>
+      <c r="BO373" s="6"/>
+      <c r="BR373" s="6"/>
     </row>
     <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D374" s="17"/>
-      <c r="E374" s="16"/>
-      <c r="BO374" s="19"/>
-      <c r="BR374" s="19"/>
+      <c r="D374" s="18"/>
+      <c r="E374" s="5"/>
+      <c r="BO374" s="6"/>
+      <c r="BR374" s="6"/>
     </row>
     <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D375" s="17"/>
-      <c r="E375" s="16"/>
-      <c r="BO375" s="19"/>
-      <c r="BR375" s="19"/>
+      <c r="D375" s="18"/>
+      <c r="E375" s="5"/>
+      <c r="BO375" s="6"/>
+      <c r="BR375" s="6"/>
     </row>
     <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D376" s="17"/>
-      <c r="E376" s="16"/>
-      <c r="BO376" s="19"/>
-      <c r="BR376" s="19"/>
+      <c r="D376" s="18"/>
+      <c r="E376" s="5"/>
+      <c r="BO376" s="6"/>
+      <c r="BR376" s="6"/>
     </row>
     <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D377" s="17"/>
-      <c r="E377" s="16"/>
-      <c r="BO377" s="19"/>
-      <c r="BR377" s="19"/>
+      <c r="D377" s="18"/>
+      <c r="E377" s="5"/>
+      <c r="BO377" s="6"/>
+      <c r="BR377" s="6"/>
     </row>
     <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D378" s="17"/>
-      <c r="E378" s="16"/>
-      <c r="BO378" s="19"/>
-      <c r="BR378" s="19"/>
+      <c r="D378" s="18"/>
+      <c r="E378" s="5"/>
+      <c r="BO378" s="6"/>
+      <c r="BR378" s="6"/>
     </row>
     <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D379" s="17"/>
-      <c r="E379" s="16"/>
-      <c r="BO379" s="19"/>
-      <c r="BR379" s="19"/>
+      <c r="D379" s="18"/>
+      <c r="E379" s="5"/>
+      <c r="BO379" s="6"/>
+      <c r="BR379" s="6"/>
     </row>
     <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D380" s="17"/>
-      <c r="E380" s="16"/>
-      <c r="BO380" s="19"/>
-      <c r="BR380" s="19"/>
+      <c r="D380" s="18"/>
+      <c r="E380" s="5"/>
+      <c r="BO380" s="6"/>
+      <c r="BR380" s="6"/>
     </row>
     <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D381" s="17"/>
-      <c r="E381" s="16"/>
-      <c r="BO381" s="19"/>
-      <c r="BR381" s="19"/>
+      <c r="D381" s="18"/>
+      <c r="E381" s="5"/>
+      <c r="BO381" s="6"/>
+      <c r="BR381" s="6"/>
     </row>
     <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D382" s="17"/>
-      <c r="E382" s="16"/>
-      <c r="BO382" s="19"/>
-      <c r="BR382" s="19"/>
+      <c r="D382" s="18"/>
+      <c r="E382" s="5"/>
+      <c r="BO382" s="6"/>
+      <c r="BR382" s="6"/>
     </row>
     <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D383" s="17"/>
-      <c r="E383" s="16"/>
-      <c r="BO383" s="19"/>
-      <c r="BR383" s="19"/>
+      <c r="D383" s="18"/>
+      <c r="E383" s="5"/>
+      <c r="BO383" s="6"/>
+      <c r="BR383" s="6"/>
     </row>
     <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D384" s="17"/>
-      <c r="E384" s="16"/>
-      <c r="BO384" s="19"/>
-      <c r="BR384" s="19"/>
+      <c r="D384" s="18"/>
+      <c r="E384" s="5"/>
+      <c r="BO384" s="6"/>
+      <c r="BR384" s="6"/>
     </row>
     <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D385" s="17"/>
-      <c r="E385" s="16"/>
-      <c r="BO385" s="19"/>
-      <c r="BR385" s="19"/>
+      <c r="D385" s="18"/>
+      <c r="E385" s="5"/>
+      <c r="BO385" s="6"/>
+      <c r="BR385" s="6"/>
     </row>
     <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D386" s="17"/>
-      <c r="E386" s="16"/>
-      <c r="BO386" s="19"/>
-      <c r="BR386" s="19"/>
+      <c r="D386" s="18"/>
+      <c r="E386" s="5"/>
+      <c r="BO386" s="6"/>
+      <c r="BR386" s="6"/>
     </row>
     <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D387" s="17"/>
-      <c r="E387" s="16"/>
-      <c r="BO387" s="19"/>
-      <c r="BR387" s="19"/>
+      <c r="D387" s="18"/>
+      <c r="E387" s="5"/>
+      <c r="BO387" s="6"/>
+      <c r="BR387" s="6"/>
     </row>
     <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D388" s="17"/>
-      <c r="E388" s="16"/>
-      <c r="BO388" s="19"/>
-      <c r="BR388" s="19"/>
+      <c r="D388" s="18"/>
+      <c r="E388" s="5"/>
+      <c r="BO388" s="6"/>
+      <c r="BR388" s="6"/>
     </row>
     <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D389" s="17"/>
-      <c r="E389" s="16"/>
-      <c r="BO389" s="19"/>
-      <c r="BR389" s="19"/>
+      <c r="D389" s="18"/>
+      <c r="E389" s="5"/>
+      <c r="BO389" s="6"/>
+      <c r="BR389" s="6"/>
     </row>
     <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D390" s="17"/>
-      <c r="E390" s="16"/>
-      <c r="BO390" s="19"/>
-      <c r="BR390" s="19"/>
+      <c r="D390" s="18"/>
+      <c r="E390" s="5"/>
+      <c r="BO390" s="6"/>
+      <c r="BR390" s="6"/>
     </row>
     <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D391" s="17"/>
-      <c r="E391" s="16"/>
-      <c r="BO391" s="19"/>
-      <c r="BR391" s="19"/>
+      <c r="D391" s="18"/>
+      <c r="E391" s="5"/>
+      <c r="BO391" s="6"/>
+      <c r="BR391" s="6"/>
     </row>
     <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D392" s="17"/>
-      <c r="E392" s="16"/>
-      <c r="BO392" s="19"/>
-      <c r="BR392" s="19"/>
+      <c r="D392" s="18"/>
+      <c r="E392" s="5"/>
+      <c r="BO392" s="6"/>
+      <c r="BR392" s="6"/>
     </row>
     <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D393" s="17"/>
-      <c r="E393" s="16"/>
-      <c r="BO393" s="19"/>
-      <c r="BR393" s="19"/>
+      <c r="D393" s="18"/>
+      <c r="E393" s="5"/>
+      <c r="BO393" s="6"/>
+      <c r="BR393" s="6"/>
     </row>
     <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D394" s="17"/>
-      <c r="E394" s="16"/>
-      <c r="BO394" s="19"/>
-      <c r="BR394" s="19"/>
+      <c r="D394" s="18"/>
+      <c r="E394" s="5"/>
+      <c r="BO394" s="6"/>
+      <c r="BR394" s="6"/>
     </row>
     <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D395" s="17"/>
-      <c r="E395" s="16"/>
-      <c r="BO395" s="19"/>
-      <c r="BR395" s="19"/>
+      <c r="D395" s="18"/>
+      <c r="E395" s="5"/>
+      <c r="BO395" s="6"/>
+      <c r="BR395" s="6"/>
     </row>
     <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D396" s="17"/>
-      <c r="E396" s="16"/>
-      <c r="BR396" s="19"/>
+      <c r="D396" s="18"/>
+      <c r="E396" s="5"/>
+      <c r="BR396" s="6"/>
     </row>
     <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D397" s="17"/>
-      <c r="E397" s="16"/>
-      <c r="BR397" s="19"/>
+      <c r="D397" s="18"/>
+      <c r="E397" s="5"/>
+      <c r="BR397" s="6"/>
     </row>
     <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D398" s="17"/>
-      <c r="E398" s="16"/>
-      <c r="BO398" s="19"/>
-      <c r="BR398" s="19"/>
+      <c r="D398" s="18"/>
+      <c r="E398" s="5"/>
+      <c r="BO398" s="6"/>
+      <c r="BR398" s="6"/>
     </row>
     <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D399" s="17"/>
-      <c r="E399" s="16"/>
-      <c r="BO399" s="19"/>
-      <c r="BR399" s="19"/>
+      <c r="D399" s="18"/>
+      <c r="E399" s="5"/>
+      <c r="BO399" s="6"/>
+      <c r="BR399" s="6"/>
     </row>
     <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D400" s="17"/>
-      <c r="E400" s="16"/>
-      <c r="BR400" s="19"/>
+      <c r="D400" s="18"/>
+      <c r="E400" s="5"/>
+      <c r="BR400" s="6"/>
     </row>
     <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D401" s="17"/>
-      <c r="E401" s="16"/>
-      <c r="BR401" s="19"/>
+      <c r="D401" s="18"/>
+      <c r="E401" s="5"/>
+      <c r="BR401" s="6"/>
     </row>
     <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D402" s="17"/>
-      <c r="E402" s="16"/>
-      <c r="BO402" s="19"/>
-      <c r="BR402" s="19"/>
+      <c r="D402" s="18"/>
+      <c r="E402" s="5"/>
+      <c r="BO402" s="6"/>
+      <c r="BR402" s="6"/>
     </row>
     <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D403" s="17"/>
-      <c r="E403" s="16"/>
-      <c r="BO403" s="19"/>
-      <c r="BR403" s="19"/>
+      <c r="D403" s="18"/>
+      <c r="E403" s="5"/>
+      <c r="BO403" s="6"/>
+      <c r="BR403" s="6"/>
     </row>
     <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D404" s="17"/>
-      <c r="E404" s="16"/>
-      <c r="BO404" s="19"/>
-      <c r="BR404" s="19"/>
+      <c r="D404" s="18"/>
+      <c r="E404" s="5"/>
+      <c r="BO404" s="6"/>
+      <c r="BR404" s="6"/>
     </row>
     <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D405" s="17"/>
-      <c r="E405" s="16"/>
-      <c r="BO405" s="19"/>
-      <c r="BR405" s="19"/>
+      <c r="D405" s="18"/>
+      <c r="E405" s="5"/>
+      <c r="BO405" s="6"/>
+      <c r="BR405" s="6"/>
     </row>
     <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D406" s="17"/>
-      <c r="E406" s="16"/>
-      <c r="BO406" s="19"/>
-      <c r="BR406" s="19"/>
+      <c r="D406" s="18"/>
+      <c r="E406" s="5"/>
+      <c r="BO406" s="6"/>
+      <c r="BR406" s="6"/>
     </row>
     <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D407" s="17"/>
-      <c r="E407" s="16"/>
-      <c r="BO407" s="19"/>
-      <c r="BR407" s="19"/>
+      <c r="D407" s="18"/>
+      <c r="E407" s="5"/>
+      <c r="BO407" s="6"/>
+      <c r="BR407" s="6"/>
     </row>
     <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D408" s="17"/>
-      <c r="E408" s="16"/>
-      <c r="BO408" s="19"/>
-      <c r="BR408" s="19"/>
+      <c r="D408" s="18"/>
+      <c r="E408" s="5"/>
+      <c r="BO408" s="6"/>
+      <c r="BR408" s="6"/>
     </row>
     <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D409" s="17"/>
-      <c r="E409" s="16"/>
-      <c r="BO409" s="19"/>
-      <c r="BR409" s="19"/>
+      <c r="D409" s="18"/>
+      <c r="E409" s="5"/>
+      <c r="BO409" s="6"/>
+      <c r="BR409" s="6"/>
     </row>
     <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D410" s="17"/>
-      <c r="E410" s="16"/>
-      <c r="BO410" s="19"/>
-      <c r="BR410" s="19"/>
+      <c r="D410" s="18"/>
+      <c r="E410" s="5"/>
+      <c r="BO410" s="6"/>
+      <c r="BR410" s="6"/>
     </row>
     <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D411" s="17"/>
-      <c r="E411" s="16"/>
-      <c r="BO411" s="19"/>
-      <c r="BR411" s="19"/>
+      <c r="D411" s="18"/>
+      <c r="E411" s="5"/>
+      <c r="BO411" s="6"/>
+      <c r="BR411" s="6"/>
     </row>
     <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D412" s="17"/>
-      <c r="E412" s="16"/>
-      <c r="BO412" s="19"/>
-      <c r="BR412" s="19"/>
+      <c r="D412" s="18"/>
+      <c r="E412" s="5"/>
+      <c r="BO412" s="6"/>
+      <c r="BR412" s="6"/>
     </row>
     <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D413" s="17"/>
-      <c r="E413" s="16"/>
-      <c r="BO413" s="19"/>
-      <c r="BR413" s="19"/>
+      <c r="D413" s="18"/>
+      <c r="E413" s="5"/>
+      <c r="BO413" s="6"/>
+      <c r="BR413" s="6"/>
     </row>
     <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D414" s="17"/>
-      <c r="E414" s="16"/>
-      <c r="BO414" s="19"/>
-      <c r="BR414" s="19"/>
+      <c r="D414" s="18"/>
+      <c r="E414" s="5"/>
+      <c r="BO414" s="6"/>
+      <c r="BR414" s="6"/>
     </row>
     <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D415" s="17"/>
-      <c r="E415" s="16"/>
-      <c r="BO415" s="19"/>
-      <c r="BR415" s="19"/>
+      <c r="D415" s="18"/>
+      <c r="E415" s="5"/>
+      <c r="BO415" s="6"/>
+      <c r="BR415" s="6"/>
     </row>
     <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D416" s="17"/>
-      <c r="E416" s="16"/>
-      <c r="BO416" s="19"/>
-      <c r="BR416" s="19"/>
+      <c r="D416" s="18"/>
+      <c r="E416" s="5"/>
+      <c r="BO416" s="6"/>
+      <c r="BR416" s="6"/>
     </row>
     <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D417" s="17"/>
-      <c r="E417" s="16"/>
-      <c r="BO417" s="19"/>
-      <c r="BR417" s="19"/>
+      <c r="D417" s="18"/>
+      <c r="E417" s="5"/>
+      <c r="BO417" s="6"/>
+      <c r="BR417" s="6"/>
     </row>
     <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D418" s="17"/>
-      <c r="E418" s="16"/>
-      <c r="BO418" s="19"/>
-      <c r="BR418" s="19"/>
+      <c r="D418" s="18"/>
+      <c r="E418" s="5"/>
+      <c r="BO418" s="6"/>
+      <c r="BR418" s="6"/>
     </row>
     <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D419" s="17"/>
-      <c r="E419" s="16"/>
+      <c r="D419" s="18"/>
+      <c r="E419" s="5"/>
     </row>
     <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D420" s="17"/>
-      <c r="E420" s="16"/>
+      <c r="D420" s="18"/>
+      <c r="E420" s="5"/>
     </row>
     <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D421" s="17"/>
-      <c r="E421" s="16"/>
+      <c r="D421" s="18"/>
+      <c r="E421" s="5"/>
     </row>
     <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D422" s="17"/>
-      <c r="E422" s="16"/>
+      <c r="D422" s="18"/>
+      <c r="E422" s="5"/>
     </row>
     <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D423" s="17"/>
-      <c r="E423" s="16"/>
+      <c r="D423" s="18"/>
+      <c r="E423" s="5"/>
     </row>
     <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D424" s="17"/>
-      <c r="E424" s="16"/>
+      <c r="D424" s="18"/>
+      <c r="E424" s="5"/>
     </row>
     <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D425" s="17"/>
-      <c r="E425" s="16"/>
+      <c r="D425" s="18"/>
+      <c r="E425" s="5"/>
     </row>
     <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D426" s="17"/>
-      <c r="E426" s="16"/>
+      <c r="D426" s="18"/>
+      <c r="E426" s="5"/>
     </row>
     <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D427" s="17"/>
-      <c r="E427" s="16"/>
+      <c r="D427" s="18"/>
+      <c r="E427" s="5"/>
     </row>
     <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D428" s="17"/>
-      <c r="E428" s="16"/>
+      <c r="D428" s="18"/>
+      <c r="E428" s="5"/>
     </row>
     <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D429" s="17"/>
-      <c r="E429" s="16"/>
+      <c r="D429" s="18"/>
+      <c r="E429" s="5"/>
     </row>
     <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D430" s="17"/>
-      <c r="E430" s="16"/>
+      <c r="D430" s="18"/>
+      <c r="E430" s="5"/>
     </row>
     <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D431" s="17"/>
-      <c r="E431" s="16"/>
+      <c r="D431" s="18"/>
+      <c r="E431" s="5"/>
     </row>
     <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D432" s="17"/>
-      <c r="E432" s="16"/>
+      <c r="D432" s="18"/>
+      <c r="E432" s="5"/>
     </row>
     <row r="433" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D433" s="17"/>
-      <c r="E433" s="16"/>
+      <c r="D433" s="18"/>
+      <c r="E433" s="5"/>
     </row>
     <row r="434" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D434" s="17"/>
-      <c r="E434" s="16"/>
+      <c r="D434" s="18"/>
+      <c r="E434" s="5"/>
     </row>
     <row r="435" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D435" s="17"/>
-      <c r="E435" s="16"/>
+      <c r="D435" s="18"/>
+      <c r="E435" s="5"/>
     </row>
     <row r="436" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D436" s="17"/>
-      <c r="E436" s="16"/>
+      <c r="D436" s="18"/>
+      <c r="E436" s="5"/>
     </row>
     <row r="437" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D437" s="17"/>
-      <c r="E437" s="16"/>
+      <c r="D437" s="18"/>
+      <c r="E437" s="5"/>
     </row>
     <row r="438" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D438" s="17"/>
-      <c r="E438" s="16"/>
+      <c r="D438" s="18"/>
+      <c r="E438" s="5"/>
     </row>
     <row r="439" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D439" s="17"/>
-      <c r="E439" s="16"/>
+      <c r="D439" s="18"/>
+      <c r="E439" s="5"/>
     </row>
     <row r="440" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D440" s="17"/>
-      <c r="E440" s="16"/>
+      <c r="D440" s="18"/>
+      <c r="E440" s="5"/>
     </row>
     <row r="441" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D441" s="17"/>
-      <c r="E441" s="16"/>
+      <c r="D441" s="18"/>
+      <c r="E441" s="5"/>
     </row>
     <row r="442" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D442" s="17"/>
-      <c r="E442" s="16"/>
+      <c r="D442" s="18"/>
+      <c r="E442" s="5"/>
     </row>
     <row r="443" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D443" s="17"/>
-      <c r="E443" s="16"/>
+      <c r="D443" s="18"/>
+      <c r="E443" s="5"/>
     </row>
     <row r="444" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D444" s="17"/>
-      <c r="E444" s="16"/>
+      <c r="D444" s="18"/>
+      <c r="E444" s="5"/>
     </row>
     <row r="445" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D445" s="17"/>
-      <c r="E445" s="16"/>
+      <c r="D445" s="18"/>
+      <c r="E445" s="5"/>
     </row>
     <row r="446" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D446" s="17"/>
-      <c r="E446" s="16"/>
+      <c r="D446" s="18"/>
+      <c r="E446" s="5"/>
     </row>
     <row r="447" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D447" s="17"/>
-      <c r="E447" s="16"/>
+      <c r="D447" s="18"/>
+      <c r="E447" s="5"/>
     </row>
     <row r="448" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D448" s="17"/>
-      <c r="E448" s="16"/>
+      <c r="D448" s="18"/>
+      <c r="E448" s="5"/>
     </row>
     <row r="449" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D449" s="17"/>
-      <c r="E449" s="16"/>
+      <c r="D449" s="18"/>
+      <c r="E449" s="5"/>
     </row>
     <row r="450" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D450" s="17"/>
-      <c r="E450" s="16"/>
+      <c r="D450" s="18"/>
+      <c r="E450" s="5"/>
     </row>
     <row r="451" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D451" s="17"/>
-      <c r="E451" s="16"/>
+      <c r="D451" s="18"/>
+      <c r="E451" s="5"/>
     </row>
     <row r="452" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D452" s="17"/>
-      <c r="E452" s="16"/>
+      <c r="D452" s="18"/>
+      <c r="E452" s="5"/>
     </row>
     <row r="453" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D453" s="17"/>
-      <c r="E453" s="16"/>
+      <c r="D453" s="18"/>
+      <c r="E453" s="5"/>
     </row>
     <row r="454" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D454" s="17"/>
-      <c r="E454" s="16"/>
+      <c r="D454" s="18"/>
+      <c r="E454" s="5"/>
     </row>
     <row r="455" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D455" s="17"/>
-      <c r="E455" s="16"/>
+      <c r="D455" s="18"/>
+      <c r="E455" s="5"/>
     </row>
     <row r="456" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D456" s="17"/>
-      <c r="E456" s="16"/>
+      <c r="D456" s="18"/>
+      <c r="E456" s="5"/>
     </row>
     <row r="457" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D457" s="17"/>
-      <c r="E457" s="16"/>
+      <c r="D457" s="18"/>
+      <c r="E457" s="5"/>
     </row>
     <row r="458" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D458" s="17"/>
-      <c r="E458" s="16"/>
+      <c r="D458" s="18"/>
+      <c r="E458" s="5"/>
     </row>
     <row r="459" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D459" s="17"/>
-      <c r="E459" s="16"/>
+      <c r="D459" s="18"/>
+      <c r="E459" s="5"/>
     </row>
     <row r="460" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D460" s="17"/>
-      <c r="E460" s="16"/>
+      <c r="D460" s="18"/>
+      <c r="E460" s="5"/>
     </row>
     <row r="461" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D461" s="17"/>
-      <c r="E461" s="16"/>
+      <c r="D461" s="18"/>
+      <c r="E461" s="5"/>
     </row>
     <row r="462" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D462" s="17"/>
-      <c r="E462" s="16"/>
+      <c r="D462" s="18"/>
+      <c r="E462" s="5"/>
     </row>
     <row r="463" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D463" s="17"/>
-      <c r="E463" s="16"/>
+      <c r="D463" s="18"/>
+      <c r="E463" s="5"/>
     </row>
     <row r="464" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D464" s="17"/>
-      <c r="E464" s="16"/>
+      <c r="D464" s="18"/>
+      <c r="E464" s="5"/>
     </row>
     <row r="465" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D465" s="17"/>
-      <c r="E465" s="16"/>
+      <c r="D465" s="18"/>
+      <c r="E465" s="5"/>
     </row>
     <row r="466" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D466" s="17"/>
-      <c r="E466" s="16"/>
+      <c r="D466" s="18"/>
+      <c r="E466" s="5"/>
     </row>
     <row r="467" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D467" s="17"/>
-      <c r="E467" s="16"/>
+      <c r="D467" s="18"/>
+      <c r="E467" s="5"/>
     </row>
     <row r="468" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D468" s="17"/>
-      <c r="E468" s="16"/>
+      <c r="D468" s="18"/>
+      <c r="E468" s="5"/>
     </row>
     <row r="469" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D469" s="17"/>
-      <c r="E469" s="16"/>
+      <c r="D469" s="18"/>
+      <c r="E469" s="5"/>
     </row>
     <row r="470" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D470" s="17"/>
-      <c r="E470" s="16"/>
+      <c r="D470" s="18"/>
+      <c r="E470" s="5"/>
     </row>
     <row r="471" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D471" s="17"/>
-      <c r="E471" s="16"/>
+      <c r="D471" s="18"/>
+      <c r="E471" s="5"/>
     </row>
     <row r="472" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D472" s="17"/>
-      <c r="E472" s="16"/>
+      <c r="D472" s="18"/>
+      <c r="E472" s="5"/>
     </row>
     <row r="473" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D473" s="17"/>
-      <c r="E473" s="16"/>
+      <c r="D473" s="18"/>
+      <c r="E473" s="5"/>
     </row>
     <row r="474" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D474" s="17"/>
-      <c r="E474" s="16"/>
+      <c r="D474" s="18"/>
+      <c r="E474" s="5"/>
     </row>
     <row r="475" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D475" s="17"/>
-      <c r="E475" s="16"/>
+      <c r="D475" s="18"/>
+      <c r="E475" s="5"/>
     </row>
     <row r="476" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D476" s="17"/>
-      <c r="E476" s="16"/>
+      <c r="D476" s="18"/>
+      <c r="E476" s="5"/>
     </row>
     <row r="477" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D477" s="17"/>
-      <c r="E477" s="16"/>
+      <c r="D477" s="18"/>
+      <c r="E477" s="5"/>
     </row>
     <row r="478" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D478" s="17"/>
-      <c r="E478" s="16"/>
+      <c r="D478" s="18"/>
+      <c r="E478" s="5"/>
     </row>
     <row r="479" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D479" s="17"/>
-      <c r="E479" s="16"/>
+      <c r="D479" s="18"/>
+      <c r="E479" s="5"/>
     </row>
     <row r="480" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D480" s="17"/>
-      <c r="E480" s="16"/>
+      <c r="D480" s="18"/>
+      <c r="E480" s="5"/>
     </row>
     <row r="481" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D481" s="17"/>
-      <c r="E481" s="16"/>
+      <c r="D481" s="18"/>
+      <c r="E481" s="5"/>
     </row>
     <row r="482" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D482" s="17"/>
-      <c r="E482" s="16"/>
+      <c r="D482" s="18"/>
+      <c r="E482" s="5"/>
     </row>
     <row r="483" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D483" s="17"/>
-      <c r="E483" s="16"/>
+      <c r="D483" s="18"/>
+      <c r="E483" s="5"/>
     </row>
     <row r="484" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D484" s="17"/>
-      <c r="E484" s="16"/>
+      <c r="D484" s="18"/>
+      <c r="E484" s="5"/>
     </row>
     <row r="485" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D485" s="17"/>
-      <c r="E485" s="16"/>
+      <c r="D485" s="18"/>
+      <c r="E485" s="5"/>
     </row>
     <row r="486" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D486" s="17"/>
-      <c r="E486" s="16"/>
+      <c r="D486" s="18"/>
+      <c r="E486" s="5"/>
     </row>
     <row r="487" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D487" s="17"/>
-      <c r="E487" s="16"/>
+      <c r="D487" s="18"/>
+      <c r="E487" s="5"/>
     </row>
     <row r="488" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D488" s="17"/>
-      <c r="E488" s="16"/>
+      <c r="D488" s="18"/>
+      <c r="E488" s="5"/>
     </row>
     <row r="489" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D489" s="17"/>
-      <c r="E489" s="16"/>
+      <c r="D489" s="18"/>
+      <c r="E489" s="5"/>
     </row>
     <row r="490" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D490" s="17"/>
-      <c r="E490" s="16"/>
+      <c r="D490" s="18"/>
+      <c r="E490" s="5"/>
     </row>
     <row r="491" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D491" s="17"/>
-      <c r="E491" s="16"/>
+      <c r="D491" s="18"/>
+      <c r="E491" s="5"/>
     </row>
     <row r="492" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D492" s="17"/>
-      <c r="E492" s="16"/>
+      <c r="D492" s="18"/>
+      <c r="E492" s="5"/>
     </row>
     <row r="493" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D493" s="17"/>
-      <c r="E493" s="16"/>
+      <c r="D493" s="18"/>
+      <c r="E493" s="5"/>
     </row>
     <row r="494" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D494" s="17"/>
-      <c r="E494" s="16"/>
+      <c r="D494" s="18"/>
+      <c r="E494" s="5"/>
     </row>
     <row r="495" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D495" s="17"/>
-      <c r="E495" s="16"/>
+      <c r="D495" s="18"/>
+      <c r="E495" s="5"/>
     </row>
     <row r="496" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D496" s="17"/>
-      <c r="E496" s="16"/>
+      <c r="D496" s="18"/>
+      <c r="E496" s="5"/>
     </row>
     <row r="497" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D497" s="17"/>
-      <c r="E497" s="16"/>
+      <c r="D497" s="18"/>
+      <c r="E497" s="5"/>
     </row>
     <row r="498" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D498" s="17"/>
-      <c r="E498" s="16"/>
+      <c r="D498" s="18"/>
+      <c r="E498" s="5"/>
     </row>
     <row r="566" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D566" s="17"/>
-      <c r="E566" s="16"/>
+      <c r="D566" s="18"/>
+      <c r="E566" s="5"/>
     </row>
     <row r="567" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D567" s="17"/>
-      <c r="E567" s="16"/>
+      <c r="D567" s="18"/>
+      <c r="E567" s="5"/>
     </row>
     <row r="568" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D568" s="17"/>
-      <c r="E568" s="16"/>
+      <c r="D568" s="18"/>
+      <c r="E568" s="5"/>
     </row>
     <row r="569" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D569" s="17"/>
-      <c r="E569" s="16"/>
+      <c r="D569" s="18"/>
+      <c r="E569" s="5"/>
     </row>
     <row r="570" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D570" s="17"/>
-      <c r="E570" s="16"/>
+      <c r="D570" s="18"/>
+      <c r="E570" s="5"/>
     </row>
     <row r="571" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D571" s="17"/>
-      <c r="E571" s="16"/>
+      <c r="D571" s="18"/>
+      <c r="E571" s="5"/>
     </row>
     <row r="572" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D572" s="17"/>
-      <c r="E572" s="16"/>
+      <c r="D572" s="18"/>
+      <c r="E572" s="5"/>
     </row>
     <row r="573" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D573" s="17"/>
-      <c r="E573" s="16"/>
+      <c r="D573" s="18"/>
+      <c r="E573" s="5"/>
     </row>
     <row r="574" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D574" s="17"/>
-      <c r="E574" s="16"/>
+      <c r="D574" s="18"/>
+      <c r="E574" s="5"/>
     </row>
     <row r="575" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D575" s="17"/>
-      <c r="E575" s="16"/>
+      <c r="D575" s="18"/>
+      <c r="E575" s="5"/>
     </row>
     <row r="576" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D576" s="17"/>
-      <c r="E576" s="16"/>
+      <c r="D576" s="18"/>
+      <c r="E576" s="5"/>
     </row>
     <row r="577" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D577" s="17"/>
-      <c r="E577" s="16"/>
+      <c r="D577" s="18"/>
+      <c r="E577" s="5"/>
     </row>
     <row r="578" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D578" s="17"/>
-      <c r="E578" s="16"/>
+      <c r="D578" s="18"/>
+      <c r="E578" s="5"/>
     </row>
     <row r="579" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D579" s="17"/>
-      <c r="E579" s="16"/>
+      <c r="D579" s="18"/>
+      <c r="E579" s="5"/>
     </row>
     <row r="580" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D580" s="17"/>
-      <c r="E580" s="16"/>
+      <c r="D580" s="18"/>
+      <c r="E580" s="5"/>
     </row>
     <row r="581" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D581" s="17"/>
-      <c r="E581" s="16"/>
+      <c r="D581" s="18"/>
+      <c r="E581" s="5"/>
     </row>
     <row r="582" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D582" s="17"/>
-      <c r="E582" s="16"/>
+      <c r="D582" s="18"/>
+      <c r="E582" s="5"/>
     </row>
     <row r="583" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D583" s="17"/>
-      <c r="E583" s="16"/>
+      <c r="D583" s="18"/>
+      <c r="E583" s="5"/>
     </row>
     <row r="584" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D584" s="17"/>
-      <c r="E584" s="16"/>
+      <c r="D584" s="18"/>
+      <c r="E584" s="5"/>
     </row>
     <row r="585" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D585" s="17"/>
-      <c r="E585" s="16"/>
+      <c r="D585" s="18"/>
+      <c r="E585" s="5"/>
     </row>
     <row r="586" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D586" s="17"/>
-      <c r="E586" s="16"/>
+      <c r="D586" s="18"/>
+      <c r="E586" s="5"/>
     </row>
     <row r="587" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D587" s="17"/>
-      <c r="E587" s="16"/>
+      <c r="D587" s="18"/>
+      <c r="E587" s="5"/>
     </row>
     <row r="588" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D588" s="17"/>
-      <c r="E588" s="16"/>
+      <c r="D588" s="18"/>
+      <c r="E588" s="5"/>
     </row>
     <row r="589" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D589" s="17"/>
-      <c r="E589" s="16"/>
+      <c r="D589" s="18"/>
+      <c r="E589" s="5"/>
     </row>
     <row r="590" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D590" s="17"/>
-      <c r="E590" s="16"/>
+      <c r="D590" s="18"/>
+      <c r="E590" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -6421,18 +6393,18 @@
     <col min="8" max="8" width="17.83203125" customWidth="1"/>
     <col min="9" max="9" width="7.33203125" customWidth="1"/>
     <col min="10" max="10" width="15.75" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" style="4" customWidth="1"/>
-    <col min="14" max="14" width="11.75" style="4" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" style="4" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="4" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" style="4" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" style="4" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" style="4" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="4" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="4" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" style="4" customWidth="1"/>
-    <col min="24" max="24" width="18.5" style="4" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="9" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" style="9" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="21.5" style="9" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" style="9" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" style="9" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="9" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="9" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" style="9" customWidth="1"/>
+    <col min="24" max="24" width="18.5" style="9" customWidth="1"/>
     <col min="25" max="25" width="16.58203125" customWidth="1"/>
     <col min="26" max="26" width="10.6640625" customWidth="1"/>
     <col min="27" max="27" width="8.33203125" customWidth="1"/>
@@ -6467,10 +6439,10 @@
     <col min="66" max="68" width="11.25" customWidth="1"/>
     <col min="69" max="69" width="6.58203125" customWidth="1"/>
     <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="5" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="5" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="5" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="5" customWidth="1"/>
+    <col min="72" max="72" width="7.33203125" style="10" customWidth="1"/>
+    <col min="73" max="74" width="8.5" style="10" customWidth="1"/>
+    <col min="75" max="76" width="7.83203125" style="10" customWidth="1"/>
+    <col min="77" max="77" width="22.1640625" style="10" customWidth="1"/>
     <col min="78" max="78" width="13.5" customWidth="1"/>
     <col min="79" max="79" width="21.1640625" customWidth="1"/>
     <col min="80" max="80" width="15.75" customWidth="1"/>
@@ -6506,7 +6478,7 @@
       <c r="G1" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>161</v>
       </c>
       <c r="I1" t="s">
@@ -6515,46 +6487,46 @@
       <c r="J1" t="s">
         <v>163</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="9" t="s">
         <v>176</v>
       </c>
       <c r="Y1" t="s">
@@ -6563,7 +6535,7 @@
       <c r="Z1" t="s">
         <v>178</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="9" t="s">
         <v>179</v>
       </c>
       <c r="AB1" t="s">
@@ -6638,7 +6610,7 @@
       <c r="AY1" t="s">
         <v>203</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="8" t="s">
         <v>204</v>
       </c>
       <c r="BA1" t="s">
@@ -6692,31 +6664,31 @@
       <c r="BR1" t="s">
         <v>220</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="BT1" s="5" t="s">
+      <c r="BT1" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="BU1" s="5" t="s">
+      <c r="BU1" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="BV1" s="5" t="s">
+      <c r="BV1" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="BW1" s="5" t="s">
+      <c r="BW1" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="BX1" s="5" t="s">
+      <c r="BX1" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="BY1" s="5" t="s">
+      <c r="BY1" s="10" t="s">
         <v>227</v>
       </c>
       <c r="BZ1" t="s">
         <v>228</v>
       </c>
-      <c r="CA1" s="5" t="s">
+      <c r="CA1" s="10" t="s">
         <v>229</v>
       </c>
       <c r="CB1" t="s">
@@ -6743,7 +6715,7 @@
       <c r="CI1" t="s">
         <v>237</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CJ1" s="8" t="s">
         <v>238</v>
       </c>
       <c r="CK1" t="s">
@@ -6835,7 +6807,7 @@
       <c r="G2" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>262</v>
       </c>
       <c r="I2" t="s">
@@ -6844,46 +6816,46 @@
       <c r="J2" t="s">
         <v>264</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="9" t="s">
         <v>278</v>
       </c>
       <c r="Y2" t="s">
@@ -6892,7 +6864,7 @@
       <c r="Z2" t="s">
         <v>280</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AA2" s="9" t="s">
         <v>281</v>
       </c>
       <c r="AB2" t="s">
@@ -7024,25 +6996,25 @@
       <c r="BR2" t="s">
         <v>323</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BS2" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="BT2" s="5" t="s">
+      <c r="BT2" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="BU2" s="5" t="s">
+      <c r="BU2" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="BV2" s="5" t="s">
+      <c r="BV2" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="BW2" s="5" t="s">
+      <c r="BW2" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="BX2" s="5" t="s">
+      <c r="BX2" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="BY2" s="5" t="s">
+      <c r="BY2" s="10" t="s">
         <v>329</v>
       </c>
       <c r="BZ2" t="s">
@@ -7075,7 +7047,7 @@
       <c r="CI2" t="s">
         <v>339</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="CJ2" s="8" t="s">
         <v>340</v>
       </c>
       <c r="CK2" t="s">
@@ -7167,7 +7139,7 @@
       <c r="G3" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
@@ -7176,46 +7148,46 @@
       <c r="J3" t="s">
         <v>364</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" s="9" t="s">
         <v>116</v>
       </c>
       <c r="Y3" t="s">
@@ -7224,7 +7196,7 @@
       <c r="Z3" t="s">
         <v>116</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AA3" s="9" t="s">
         <v>117</v>
       </c>
       <c r="AB3" t="s">
@@ -7356,25 +7328,25 @@
       <c r="BR3" t="s">
         <v>117</v>
       </c>
-      <c r="BS3" s="1" t="s">
+      <c r="BS3" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="5" t="s">
+      <c r="BT3" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="BU3" s="5" t="s">
+      <c r="BU3" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="BV3" s="5" t="s">
+      <c r="BV3" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="BW3" s="5" t="s">
+      <c r="BW3" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="BX3" s="5" t="s">
+      <c r="BX3" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="BY3" s="5" t="s">
+      <c r="BY3" s="10" t="s">
         <v>374</v>
       </c>
       <c r="BZ3" t="s">
@@ -7407,7 +7379,7 @@
       <c r="CI3" t="s">
         <v>378</v>
       </c>
-      <c r="CJ3" s="1" t="s">
+      <c r="CJ3" s="8" t="s">
         <v>125</v>
       </c>
       <c r="CK3" t="s">
@@ -7480,8 +7452,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:111" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:111" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>381</v>
       </c>
     </row>
@@ -7495,22 +7467,10 @@
       <c r="J5" t="s">
         <v>384</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
       <c r="O5"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
       <c r="AC5">
         <v>1</v>
       </c>
@@ -7520,12 +7480,6 @@
       <c r="AR5" t="s">
         <v>387</v>
       </c>
-      <c r="BT5" s="9"/>
-      <c r="BU5" s="9"/>
-      <c r="BV5" s="9"/>
-      <c r="BW5" s="9"/>
-      <c r="BX5" s="9"/>
-      <c r="BY5" s="9"/>
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -7534,26 +7488,15 @@
       <c r="C6" t="s">
         <v>383</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6">
-        <v>1</v>
-      </c>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
+      <c r="S6" s="9">
+        <v>1</v>
+      </c>
       <c r="AC6">
         <v>1</v>
       </c>
@@ -7578,12 +7521,6 @@
       <c r="BN6" t="s">
         <v>393</v>
       </c>
-      <c r="BT6" s="9"/>
-      <c r="BU6" s="9"/>
-      <c r="BV6" s="9"/>
-      <c r="BW6" s="9"/>
-      <c r="BX6" s="9"/>
-      <c r="BY6" s="9"/>
       <c r="BZ6" t="s">
         <v>57</v>
       </c>
@@ -7601,22 +7538,10 @@
       <c r="I7">
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
       <c r="P7"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
       <c r="AC7">
         <v>1</v>
       </c>
@@ -7638,12 +7563,6 @@
       <c r="BN7" t="s">
         <v>395</v>
       </c>
-      <c r="BT7" s="9"/>
-      <c r="BU7" s="9"/>
-      <c r="BV7" s="9"/>
-      <c r="BW7" s="9"/>
-      <c r="BX7" s="9"/>
-      <c r="BY7" s="9"/>
       <c r="CF7" t="s">
         <v>396</v>
       </c>
@@ -7670,24 +7589,12 @@
       <c r="C8" t="s">
         <v>401</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
       <c r="AC8">
         <v>1</v>
       </c>
@@ -7700,13 +7607,7 @@
       <c r="BB8">
         <v>1</v>
       </c>
-      <c r="BT8" s="9"/>
-      <c r="BU8" s="9"/>
-      <c r="BV8" s="9"/>
-      <c r="BW8" s="9"/>
-      <c r="BX8" s="9"/>
-      <c r="BY8" s="9"/>
-      <c r="CJ8" s="6"/>
+      <c r="CJ8" s="9"/>
       <c r="CS8" t="s">
         <v>404</v>
       </c>
@@ -7730,23 +7631,23 @@
       <c r="I9">
         <v>1</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="13" t="s">
         <v>402</v>
       </c>
       <c r="M9"/>
       <c r="N9"/>
-      <c r="O9" s="7"/>
+      <c r="O9" s="13"/>
       <c r="P9"/>
       <c r="Q9"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
       <c r="X9"/>
       <c r="AC9">
         <v>1</v>
@@ -7763,12 +7664,12 @@
       <c r="BM9" t="s">
         <v>407</v>
       </c>
-      <c r="BS9" s="10"/>
-      <c r="BT9" s="10"/>
-      <c r="BU9" s="10"/>
-      <c r="BV9" s="10"/>
-      <c r="BW9" s="10"/>
-      <c r="BX9" s="10"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
       <c r="BY9"/>
       <c r="CL9" t="s">
         <v>408</v>
@@ -7793,19 +7694,19 @@
       <c r="I10">
         <v>1</v>
       </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
       <c r="M10"/>
       <c r="N10"/>
-      <c r="O10" s="7"/>
+      <c r="O10" s="13"/>
       <c r="P10"/>
       <c r="Q10"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
       <c r="X10"/>
       <c r="AC10">
         <v>1</v>
@@ -7819,14 +7720,14 @@
       <c r="BQ10">
         <v>0.1</v>
       </c>
-      <c r="BS10" s="10"/>
-      <c r="BT10" s="10"/>
-      <c r="BU10" s="10"/>
-      <c r="BV10" s="10"/>
-      <c r="BW10" s="10"/>
-      <c r="BX10" s="10"/>
+      <c r="BS10" s="14"/>
+      <c r="BT10" s="14"/>
+      <c r="BU10" s="14"/>
+      <c r="BV10" s="14"/>
+      <c r="BW10" s="14"/>
+      <c r="BX10" s="14"/>
       <c r="BY10"/>
-      <c r="CL10" s="2" t="s">
+      <c r="CL10" s="12" t="s">
         <v>410</v>
       </c>
       <c r="CM10">
@@ -7846,31 +7747,19 @@
       <c r="C11" t="s">
         <v>383</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" t="s">
         <v>403</v>
       </c>
-      <c r="AW11" s="6"/>
+      <c r="AW11" s="9"/>
       <c r="BB11">
         <v>1</v>
       </c>
@@ -7880,17 +7769,17 @@
       <c r="BW11"/>
       <c r="BX11"/>
       <c r="BY11"/>
-      <c r="BZ11" s="6"/>
-      <c r="CA11" s="6"/>
-      <c r="CB11" s="6"/>
-      <c r="CC11" s="6"/>
-      <c r="CD11" s="6"/>
-      <c r="CF11" s="6"/>
-      <c r="CG11" s="6"/>
-      <c r="CH11" s="6"/>
-      <c r="CI11" s="6"/>
-      <c r="CJ11" s="6"/>
-      <c r="CK11" s="6"/>
+      <c r="BZ11" s="9"/>
+      <c r="CA11" s="9"/>
+      <c r="CB11" s="9"/>
+      <c r="CC11" s="9"/>
+      <c r="CD11" s="9"/>
+      <c r="CF11" s="9"/>
+      <c r="CG11" s="9"/>
+      <c r="CH11" s="9"/>
+      <c r="CI11" s="9"/>
+      <c r="CJ11" s="9"/>
+      <c r="CK11" s="9"/>
       <c r="CL11" t="s">
         <v>412</v>
       </c>
@@ -7908,20 +7797,6 @@
       <c r="I12">
         <v>1</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
       <c r="AC12">
         <v>1</v>
       </c>
@@ -7931,7 +7806,7 @@
       <c r="AT12">
         <v>20</v>
       </c>
-      <c r="AW12" s="6"/>
+      <c r="AW12" s="9"/>
       <c r="BB12">
         <v>1</v>
       </c>
@@ -7944,17 +7819,17 @@
       <c r="BW12"/>
       <c r="BX12"/>
       <c r="BY12"/>
-      <c r="BZ12" s="6"/>
-      <c r="CA12" s="6"/>
-      <c r="CB12" s="6"/>
-      <c r="CC12" s="6"/>
-      <c r="CD12" s="6"/>
-      <c r="CF12" s="6"/>
-      <c r="CG12" s="6"/>
-      <c r="CH12" s="6"/>
-      <c r="CI12" s="6"/>
-      <c r="CJ12" s="6"/>
-      <c r="CK12" s="6"/>
+      <c r="BZ12" s="9"/>
+      <c r="CA12" s="9"/>
+      <c r="CB12" s="9"/>
+      <c r="CC12" s="9"/>
+      <c r="CD12" s="9"/>
+      <c r="CF12" s="9"/>
+      <c r="CG12" s="9"/>
+      <c r="CH12" s="9"/>
+      <c r="CI12" s="9"/>
+      <c r="CJ12" s="9"/>
+      <c r="CK12" s="9"/>
       <c r="CL12" t="s">
         <v>414</v>
       </c>
@@ -7972,23 +7847,16 @@
       <c r="I13">
         <v>1</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L13" s="6"/>
       <c r="M13"/>
       <c r="N13"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="2" t="s">
+      <c r="P13" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="2"/>
+      <c r="R13" s="12"/>
       <c r="S13"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
       <c r="X13"/>
       <c r="AC13">
         <v>1</v>
@@ -8003,12 +7871,7 @@
         <v>1</v>
       </c>
       <c r="BT13"/>
-      <c r="BU13" s="9"/>
-      <c r="BV13" s="9"/>
-      <c r="BW13" s="9"/>
-      <c r="BX13" s="9"/>
-      <c r="BY13" s="9"/>
-      <c r="BZ13" s="9"/>
+      <c r="BZ13" s="10"/>
       <c r="CL13" t="s">
         <v>398</v>
       </c>
@@ -8050,7 +7913,7 @@
       <c r="J17" t="s">
         <v>420</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="9" t="s">
         <v>421</v>
       </c>
       <c r="M17"/>
@@ -8064,7 +7927,7 @@
       <c r="BB17">
         <v>1</v>
       </c>
-      <c r="BM17" s="1" t="s">
+      <c r="BM17" s="8" t="s">
         <v>422</v>
       </c>
       <c r="BN17" t="s">
@@ -8073,19 +7936,19 @@
       <c r="BR17">
         <v>30</v>
       </c>
-      <c r="BT17" s="5">
+      <c r="BT17" s="10">
         <v>13</v>
       </c>
-      <c r="BU17" s="5">
+      <c r="BU17" s="10">
         <v>15</v>
       </c>
-      <c r="BV17" s="5">
-        <v>1</v>
-      </c>
-      <c r="BW17" s="5" t="s">
+      <c r="BV17" s="10">
+        <v>1</v>
+      </c>
+      <c r="BW17" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="CL17" s="8" t="s">
+      <c r="CL17" s="12" t="s">
         <v>425</v>
       </c>
       <c r="CP17">
@@ -8102,9 +7965,9 @@
       <c r="C18" t="s">
         <v>383</v>
       </c>
-      <c r="J18" s="4"/>
+      <c r="J18" s="9"/>
       <c r="M18"/>
-      <c r="O18" s="8" t="s">
+      <c r="O18" s="12" t="s">
         <v>415</v>
       </c>
       <c r="P18"/>
@@ -8148,7 +8011,7 @@
       <c r="CG18" t="s">
         <v>397</v>
       </c>
-      <c r="CL18" s="1" t="s">
+      <c r="CL18" s="8" t="s">
         <v>429</v>
       </c>
       <c r="CM18">
@@ -8174,7 +8037,7 @@
       <c r="I19">
         <v>1</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="9" t="s">
         <v>385</v>
       </c>
       <c r="M19"/>
@@ -8205,14 +8068,14 @@
       <c r="BB19">
         <v>1</v>
       </c>
-      <c r="BZ19" s="11"/>
+      <c r="BZ19" s="3"/>
       <c r="CF19" t="s">
         <v>432</v>
       </c>
       <c r="CG19" t="s">
         <v>397</v>
       </c>
-      <c r="CL19" s="8" t="s">
+      <c r="CL19" s="12" t="s">
         <v>433</v>
       </c>
       <c r="CP19">
@@ -8235,11 +8098,11 @@
       <c r="I20">
         <v>1</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="9" t="s">
         <v>385</v>
       </c>
       <c r="M20"/>
-      <c r="O20" s="8" t="s">
+      <c r="O20" s="12" t="s">
         <v>415</v>
       </c>
       <c r="P20"/>
@@ -8270,7 +8133,7 @@
       </c>
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="8" t="s">
         <v>433</v>
       </c>
       <c r="C21" t="s">
@@ -8280,7 +8143,7 @@
         <v>1</v>
       </c>
       <c r="M21"/>
-      <c r="O21" s="8" t="s">
+      <c r="O21" s="12" t="s">
         <v>415</v>
       </c>
       <c r="P21"/>
@@ -8300,7 +8163,7 @@
       <c r="BQ21">
         <v>0.1</v>
       </c>
-      <c r="CL21" s="8" t="s">
+      <c r="CL21" s="12" t="s">
         <v>433</v>
       </c>
       <c r="CP21">
@@ -8317,7 +8180,7 @@
       <c r="I22">
         <v>1</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="9" t="s">
         <v>385</v>
       </c>
       <c r="M22"/>
@@ -8327,7 +8190,7 @@
       <c r="AG22" t="s">
         <v>403</v>
       </c>
-      <c r="AW22" s="4"/>
+      <c r="AW22" s="9"/>
       <c r="BB22">
         <v>1</v>
       </c>
@@ -8337,16 +8200,16 @@
       <c r="BW22"/>
       <c r="BX22"/>
       <c r="BY22"/>
-      <c r="BZ22" s="4"/>
-      <c r="CA22" s="4"/>
-      <c r="CB22" s="4"/>
-      <c r="CC22" s="4"/>
-      <c r="CD22" s="4"/>
-      <c r="CF22" s="4"/>
-      <c r="CG22" s="4"/>
-      <c r="CH22" s="4"/>
-      <c r="CI22" s="4"/>
-      <c r="CL22" s="8" t="s">
+      <c r="BZ22" s="9"/>
+      <c r="CA22" s="9"/>
+      <c r="CB22" s="9"/>
+      <c r="CC22" s="9"/>
+      <c r="CD22" s="9"/>
+      <c r="CF22" s="9"/>
+      <c r="CG22" s="9"/>
+      <c r="CH22" s="9"/>
+      <c r="CI22" s="9"/>
+      <c r="CL22" s="12" t="s">
         <v>435</v>
       </c>
       <c r="CP22">
@@ -8370,10 +8233,10 @@
         <v>1</v>
       </c>
       <c r="M23"/>
-      <c r="O23" s="8" t="s">
+      <c r="O23" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="P23" s="8" t="s">
+      <c r="P23" s="12" t="s">
         <v>435</v>
       </c>
       <c r="AC23">
@@ -8399,7 +8262,7 @@
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="9" t="s">
         <v>385</v>
       </c>
       <c r="M24"/>
@@ -8423,8 +8286,8 @@
       <c r="CE24" t="s">
         <v>394</v>
       </c>
-      <c r="CG24" s="4"/>
-      <c r="CH24" s="4"/>
+      <c r="CG24" s="9"/>
+      <c r="CH24" s="9"/>
       <c r="DB24">
         <v>1</v>
       </c>
@@ -8445,10 +8308,10 @@
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="K25" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="9" t="s">
         <v>441</v>
       </c>
       <c r="M25"/>
@@ -8472,7 +8335,7 @@
       <c r="CE25" t="s">
         <v>394</v>
       </c>
-      <c r="CH25" s="4"/>
+      <c r="CH25" s="9"/>
       <c r="DB25">
         <v>1</v>
       </c>
@@ -8506,13 +8369,13 @@
         <v>1</v>
       </c>
       <c r="M26"/>
-      <c r="O26" s="8" t="s">
+      <c r="O26" s="12" t="s">
         <v>433</v>
       </c>
       <c r="AC26">
         <v>1</v>
       </c>
-      <c r="AG26" s="1" t="s">
+      <c r="AG26" s="8" t="s">
         <v>403</v>
       </c>
       <c r="AO26" t="s">
@@ -8530,12 +8393,12 @@
       <c r="BB26">
         <v>1</v>
       </c>
-      <c r="BM26" s="1"/>
-      <c r="BN26" s="1"/>
+      <c r="BM26" s="8"/>
+      <c r="BN26" s="8"/>
       <c r="BQ26">
         <v>0.1</v>
       </c>
-      <c r="CE26" s="1" t="s">
+      <c r="CE26" s="8" t="s">
         <v>394</v>
       </c>
       <c r="CF26" t="s">
@@ -8544,7 +8407,7 @@
       <c r="CG26" t="s">
         <v>397</v>
       </c>
-      <c r="CK26" s="1"/>
+      <c r="CK26" s="8"/>
       <c r="CL26" t="s">
         <v>429</v>
       </c>
@@ -8565,7 +8428,7 @@
       </c>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BS27" s="5"/>
+      <c r="BS27" s="10"/>
       <c r="BY27"/>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.25">
@@ -8590,22 +8453,12 @@
       <c r="J28" t="s">
         <v>420</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
       <c r="O28" t="s">
         <v>414</v>
       </c>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
       <c r="W28"/>
       <c r="X28"/>
       <c r="AC28">
@@ -8626,21 +8479,19 @@
       <c r="BR28">
         <v>1</v>
       </c>
-      <c r="BT28" s="9">
+      <c r="BT28" s="10">
         <v>11</v>
       </c>
-      <c r="BU28" s="9">
+      <c r="BU28" s="10">
         <v>15</v>
       </c>
-      <c r="BV28" s="9">
-        <v>1</v>
-      </c>
-      <c r="BW28" s="9" t="s">
+      <c r="BV28" s="10">
+        <v>1</v>
+      </c>
+      <c r="BW28" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="BX28" s="9"/>
-      <c r="BY28" s="9"/>
-      <c r="CL28" s="2" t="s">
+      <c r="CL28" s="12" t="s">
         <v>450</v>
       </c>
       <c r="CM28" t="s">
@@ -8660,22 +8511,12 @@
       <c r="I29">
         <v>1</v>
       </c>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
       <c r="M29"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="2" t="s">
+      <c r="O29" s="12" t="s">
         <v>390</v>
       </c>
       <c r="P29"/>
       <c r="Q29"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
-      <c r="X29" s="6"/>
       <c r="AC29">
         <v>1</v>
       </c>
@@ -8691,13 +8532,7 @@
       <c r="BQ29">
         <v>0.1</v>
       </c>
-      <c r="BT29" s="9"/>
-      <c r="BU29" s="9"/>
-      <c r="BV29" s="9"/>
-      <c r="BW29" s="9"/>
-      <c r="BX29" s="9"/>
-      <c r="BY29" s="9"/>
-      <c r="CL29" s="2" t="s">
+      <c r="CL29" s="12" t="s">
         <v>452</v>
       </c>
       <c r="CP29">
@@ -8717,22 +8552,9 @@
       <c r="J30" t="s">
         <v>384</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
-      <c r="X30" s="6"/>
       <c r="AC30">
         <v>1</v>
       </c>
@@ -8748,13 +8570,7 @@
       <c r="BQ30">
         <v>0.1</v>
       </c>
-      <c r="BT30" s="9"/>
-      <c r="BU30" s="9"/>
-      <c r="BV30" s="9"/>
-      <c r="BW30" s="9"/>
-      <c r="BX30" s="9"/>
-      <c r="BY30" s="9"/>
-      <c r="CJ30" s="6"/>
+      <c r="CJ30" s="9"/>
       <c r="CS30" t="s">
         <v>455</v>
       </c>
@@ -8769,24 +8585,14 @@
       <c r="I31">
         <v>1</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="9" t="s">
         <v>441</v>
       </c>
       <c r="M31"/>
       <c r="N31"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6"/>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6"/>
-      <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
       <c r="AC31">
         <v>1</v>
       </c>
@@ -8800,18 +8606,13 @@
         <v>1</v>
       </c>
       <c r="BT31"/>
-      <c r="BU31" s="9"/>
-      <c r="BV31" s="9"/>
-      <c r="BW31" s="9"/>
-      <c r="BX31" s="9"/>
-      <c r="BY31" s="9"/>
-      <c r="BZ31" s="12" t="s">
+      <c r="BZ31" s="15" t="s">
         <v>457</v>
       </c>
       <c r="CE31" t="s">
         <v>394</v>
       </c>
-      <c r="CH31" s="6"/>
+      <c r="CH31" s="9"/>
       <c r="DB31">
         <v>1</v>
       </c>
@@ -8832,22 +8633,11 @@
       <c r="I32">
         <v>1</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K32" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L32" s="6"/>
       <c r="M32"/>
       <c r="N32"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
       <c r="AC32">
         <v>1</v>
       </c>
@@ -8861,19 +8651,14 @@
         <v>0.66669999999999996</v>
       </c>
       <c r="BT32"/>
-      <c r="BU32" s="9"/>
-      <c r="BV32" s="9"/>
-      <c r="BW32" s="9"/>
-      <c r="BX32" s="9"/>
-      <c r="BY32" s="9"/>
-      <c r="BZ32" s="13" t="s">
+      <c r="BZ32" s="3" t="s">
         <v>459</v>
       </c>
       <c r="CE32" t="s">
         <v>394</v>
       </c>
-      <c r="CG32" s="6"/>
-      <c r="CH32" s="6"/>
+      <c r="CG32" s="9"/>
+      <c r="CH32" s="9"/>
       <c r="DB32">
         <v>1</v>
       </c>
@@ -8883,28 +8668,6 @@
       <c r="DF32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:101" x14ac:dyDescent="0.25">
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="6"/>
-      <c r="BT33" s="9"/>
-      <c r="BU33" s="9"/>
-      <c r="BV33" s="9"/>
-      <c r="BW33" s="9"/>
-      <c r="BX33" s="9"/>
-      <c r="BY33" s="9"/>
     </row>
     <row r="34" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -8928,20 +8691,10 @@
       <c r="J34" t="s">
         <v>420</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
       <c r="O34"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
       <c r="W34"/>
       <c r="X34"/>
       <c r="AC34">
@@ -8959,21 +8712,19 @@
       <c r="BR34">
         <v>25</v>
       </c>
-      <c r="BT34" s="9">
-        <v>1</v>
-      </c>
-      <c r="BU34" s="9">
-        <v>1</v>
-      </c>
-      <c r="BV34" s="9">
-        <v>1</v>
-      </c>
-      <c r="BW34" s="9" t="s">
+      <c r="BT34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BU34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BV34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BW34" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="BX34" s="9"/>
-      <c r="BY34" s="9"/>
-      <c r="CL34" s="2" t="s">
+      <c r="CL34" s="12" t="s">
         <v>462</v>
       </c>
       <c r="CM34" t="s">
@@ -8993,21 +8744,9 @@
       <c r="C35" t="s">
         <v>465</v>
       </c>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="2" t="s">
+      <c r="O35" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="6"/>
-      <c r="S35" s="6"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="6"/>
-      <c r="V35" s="6"/>
-      <c r="W35" s="6"/>
       <c r="X35"/>
       <c r="AC35">
         <v>2</v>
@@ -9030,12 +8769,6 @@
       <c r="BN35" t="s">
         <v>467</v>
       </c>
-      <c r="BT35" s="9"/>
-      <c r="BU35" s="9"/>
-      <c r="BV35" s="9"/>
-      <c r="BW35" s="9"/>
-      <c r="BX35" s="9"/>
-      <c r="BY35" s="9"/>
       <c r="BZ35" t="s">
         <v>468</v>
       </c>
@@ -9059,23 +8792,14 @@
       <c r="I36">
         <v>1</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="2" t="s">
+      <c r="O36" s="12" t="s">
         <v>450</v>
       </c>
       <c r="P36"/>
       <c r="Q36"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
       <c r="X36"/>
       <c r="AC36">
         <v>1</v>
@@ -9101,12 +8825,6 @@
       <c r="BB36">
         <v>1</v>
       </c>
-      <c r="BT36" s="9"/>
-      <c r="BU36" s="9"/>
-      <c r="BV36" s="9"/>
-      <c r="BW36" s="9"/>
-      <c r="BX36" s="9"/>
-      <c r="BY36" s="9"/>
       <c r="CF36" t="s">
         <v>396</v>
       </c>
@@ -9130,24 +8848,12 @@
       <c r="C37" t="s">
         <v>472</v>
       </c>
-      <c r="K37" s="6" t="s">
+      <c r="K37" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L37" s="6" t="s">
+      <c r="L37" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-      <c r="V37" s="6"/>
-      <c r="W37" s="6"/>
-      <c r="X37" s="6"/>
       <c r="AC37">
         <v>1</v>
       </c>
@@ -9157,12 +8863,6 @@
       <c r="BB37">
         <v>1</v>
       </c>
-      <c r="BT37" s="9"/>
-      <c r="BU37" s="9"/>
-      <c r="BV37" s="9"/>
-      <c r="BW37" s="9"/>
-      <c r="BX37" s="9"/>
-      <c r="BY37" s="9"/>
       <c r="CS37" t="s">
         <v>473</v>
       </c>
@@ -9177,24 +8877,12 @@
       <c r="I38">
         <v>1</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
       <c r="AC38">
         <v>1</v>
       </c>
@@ -9204,12 +8892,6 @@
       <c r="BB38">
         <v>1</v>
       </c>
-      <c r="BT38" s="9"/>
-      <c r="BU38" s="9"/>
-      <c r="BV38" s="9"/>
-      <c r="BW38" s="9"/>
-      <c r="BX38" s="9"/>
-      <c r="BY38" s="9"/>
       <c r="CL38" t="s">
         <v>452</v>
       </c>
@@ -9227,20 +8909,6 @@
       <c r="I39">
         <v>1</v>
       </c>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="6"/>
       <c r="AC39">
         <v>1</v>
       </c>
@@ -9256,13 +8924,7 @@
       <c r="BQ39">
         <v>0.1</v>
       </c>
-      <c r="BT39" s="9"/>
-      <c r="BU39" s="9"/>
-      <c r="BV39" s="9"/>
-      <c r="BW39" s="9"/>
-      <c r="BX39" s="9"/>
-      <c r="BY39" s="9"/>
-      <c r="CL39" s="2" t="s">
+      <c r="CL39" s="12" t="s">
         <v>390</v>
       </c>
       <c r="CP39">
@@ -9270,28 +8932,28 @@
       </c>
     </row>
     <row r="42" spans="1:101" x14ac:dyDescent="0.25">
-      <c r="CJ42" s="4"/>
+      <c r="CJ42" s="9"/>
     </row>
     <row r="43" spans="1:101" x14ac:dyDescent="0.25">
-      <c r="CJ43" s="4"/>
+      <c r="CJ43" s="9"/>
     </row>
     <row r="49" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ49" s="4"/>
+      <c r="CJ49" s="9"/>
     </row>
     <row r="50" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ50" s="4"/>
+      <c r="CJ50" s="9"/>
     </row>
     <row r="52" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ52" s="4"/>
+      <c r="CJ52" s="9"/>
     </row>
     <row r="53" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ53" s="4"/>
+      <c r="CJ53" s="9"/>
     </row>
     <row r="54" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ54" s="4"/>
+      <c r="CJ54" s="9"/>
     </row>
     <row r="55" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ55" s="4"/>
+      <c r="CJ55" s="9"/>
     </row>
     <row r="56" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT56"/>
@@ -9301,31 +8963,31 @@
     </row>
     <row r="58" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT58"/>
-      <c r="CJ58" s="4"/>
+      <c r="CJ58" s="9"/>
     </row>
     <row r="59" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ59" s="4"/>
+      <c r="CJ59" s="9"/>
     </row>
     <row r="60" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ60" s="4"/>
+      <c r="CJ60" s="9"/>
     </row>
     <row r="61" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT61"/>
     </row>
     <row r="62" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ62" s="4"/>
+      <c r="CJ62" s="9"/>
     </row>
     <row r="66" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT66"/>
     </row>
     <row r="67" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ67" s="4"/>
+      <c r="CJ67" s="9"/>
     </row>
     <row r="75" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ75" s="4"/>
+      <c r="CJ75" s="9"/>
     </row>
     <row r="76" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ76" s="4"/>
+      <c r="CJ76" s="9"/>
     </row>
     <row r="77" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT77"/>
@@ -9335,279 +8997,279 @@
     </row>
     <row r="83" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT83"/>
-      <c r="CJ83" s="4"/>
+      <c r="CJ83" s="9"/>
     </row>
     <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ84" s="4"/>
+      <c r="CJ84" s="9"/>
     </row>
     <row r="85" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ85" s="4"/>
+      <c r="CJ85" s="9"/>
     </row>
     <row r="86" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ86" s="4"/>
+      <c r="CJ86" s="9"/>
     </row>
     <row r="87" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ87" s="4"/>
+      <c r="CJ87" s="9"/>
     </row>
     <row r="88" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT88"/>
     </row>
     <row r="89" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ89" s="4"/>
+      <c r="CJ89" s="9"/>
     </row>
     <row r="90" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ90" s="4"/>
+      <c r="CJ90" s="9"/>
     </row>
     <row r="91" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ91" s="4"/>
+      <c r="CJ91" s="9"/>
     </row>
     <row r="92" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ92" s="4"/>
+      <c r="CJ92" s="9"/>
     </row>
     <row r="93" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT93"/>
     </row>
     <row r="94" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ94" s="4"/>
+      <c r="CJ94" s="9"/>
     </row>
     <row r="95" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ95" s="4"/>
+      <c r="CJ95" s="9"/>
     </row>
     <row r="96" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ96" s="4"/>
+      <c r="CJ96" s="9"/>
     </row>
     <row r="97" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ97" s="4"/>
+      <c r="CJ97" s="9"/>
     </row>
     <row r="100" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ100" s="4"/>
+      <c r="CJ100" s="9"/>
     </row>
     <row r="101" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ101" s="4"/>
+      <c r="CJ101" s="9"/>
     </row>
     <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="4"/>
+      <c r="CJ102" s="9"/>
     </row>
     <row r="103" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ103" s="4"/>
+      <c r="CJ103" s="9"/>
     </row>
     <row r="104" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ104" s="4"/>
+      <c r="CJ104" s="9"/>
     </row>
     <row r="106" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT106"/>
     </row>
     <row r="107" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ107" s="4"/>
+      <c r="CJ107" s="9"/>
     </row>
     <row r="108" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ108" s="4"/>
+      <c r="CJ108" s="9"/>
     </row>
     <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ109" s="4"/>
+      <c r="CJ109" s="9"/>
     </row>
     <row r="110" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ110" s="4"/>
+      <c r="CJ110" s="9"/>
     </row>
     <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ114" s="4"/>
+      <c r="CJ114" s="9"/>
     </row>
     <row r="116" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT116"/>
     </row>
     <row r="117" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT117"/>
-      <c r="CJ117" s="4"/>
+      <c r="CJ117" s="9"/>
     </row>
     <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ118" s="4"/>
+      <c r="CJ118" s="9"/>
     </row>
     <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="4"/>
+      <c r="CJ119" s="9"/>
     </row>
     <row r="120" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ120" s="4"/>
+      <c r="CJ120" s="9"/>
     </row>
     <row r="121" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ121" s="4"/>
+      <c r="CJ121" s="9"/>
     </row>
     <row r="123" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT123"/>
     </row>
     <row r="124" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ124" s="4"/>
+      <c r="CJ124" s="9"/>
     </row>
     <row r="125" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ125" s="4"/>
+      <c r="CJ125" s="9"/>
     </row>
     <row r="127" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ127" s="4"/>
+      <c r="CJ127" s="9"/>
     </row>
     <row r="128" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ128" s="4"/>
+      <c r="CJ128" s="9"/>
     </row>
     <row r="130" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT130"/>
     </row>
     <row r="131" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ131" s="4"/>
+      <c r="CJ131" s="9"/>
     </row>
     <row r="134" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ134" s="4"/>
+      <c r="CJ134" s="9"/>
     </row>
     <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ135" s="4"/>
+      <c r="CJ135" s="9"/>
     </row>
     <row r="138" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ138" s="4"/>
+      <c r="CJ138" s="9"/>
     </row>
     <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ140" s="4"/>
+      <c r="CJ140" s="9"/>
     </row>
     <row r="142" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT142"/>
     </row>
     <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ143" s="4"/>
+      <c r="CJ143" s="9"/>
     </row>
     <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ144" s="4"/>
+      <c r="CJ144" s="9"/>
     </row>
     <row r="146" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ146" s="4"/>
+      <c r="CJ146" s="9"/>
     </row>
     <row r="147" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ147" s="4"/>
+      <c r="CJ147" s="9"/>
     </row>
     <row r="148" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ148" s="4"/>
+      <c r="CJ148" s="9"/>
     </row>
     <row r="153" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ153" s="4"/>
+      <c r="CJ153" s="9"/>
     </row>
     <row r="154" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ154" s="4"/>
+      <c r="CJ154" s="9"/>
     </row>
     <row r="157" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ157" s="4"/>
+      <c r="CJ157" s="9"/>
     </row>
     <row r="158" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ158" s="4"/>
+      <c r="CJ158" s="9"/>
     </row>
     <row r="162" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ162" s="4"/>
+      <c r="CJ162" s="9"/>
     </row>
     <row r="166" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ166" s="4"/>
+      <c r="CJ166" s="9"/>
     </row>
     <row r="168" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ168" s="4"/>
+      <c r="CJ168" s="9"/>
     </row>
     <row r="169" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ169" s="4"/>
+      <c r="CJ169" s="9"/>
     </row>
     <row r="171" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="4"/>
+      <c r="CJ171" s="9"/>
     </row>
     <row r="172" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ172" s="4"/>
+      <c r="CJ172" s="9"/>
     </row>
     <row r="174" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT174"/>
     </row>
     <row r="175" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT175"/>
-      <c r="CJ175" s="4"/>
+      <c r="CJ175" s="9"/>
     </row>
     <row r="176" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ176" s="4"/>
+      <c r="CJ176" s="9"/>
     </row>
     <row r="178" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ178" s="4"/>
+      <c r="CJ178" s="9"/>
     </row>
     <row r="187" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT187"/>
     </row>
     <row r="188" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT188"/>
-      <c r="CJ188" s="4"/>
+      <c r="CJ188" s="9"/>
     </row>
     <row r="189" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ189" s="4"/>
+      <c r="CJ189" s="9"/>
     </row>
     <row r="190" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ190" s="4"/>
+      <c r="CJ190" s="9"/>
     </row>
     <row r="191" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT191"/>
     </row>
     <row r="192" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT192"/>
-      <c r="CJ192" s="4"/>
+      <c r="CJ192" s="9"/>
     </row>
     <row r="193" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ193" s="4"/>
+      <c r="CJ193" s="9"/>
     </row>
     <row r="195" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT195"/>
     </row>
     <row r="196" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT196"/>
-      <c r="CJ196" s="4"/>
+      <c r="CJ196" s="9"/>
     </row>
     <row r="197" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ197" s="4"/>
+      <c r="CJ197" s="9"/>
     </row>
     <row r="199" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT199"/>
     </row>
     <row r="200" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ200" s="4"/>
+      <c r="CJ200" s="9"/>
     </row>
     <row r="203" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ203" s="4"/>
+      <c r="CJ203" s="9"/>
     </row>
     <row r="207" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ207" s="4"/>
+      <c r="CJ207" s="9"/>
     </row>
     <row r="209" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT209"/>
     </row>
     <row r="210" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ210" s="4"/>
+      <c r="CJ210" s="9"/>
     </row>
     <row r="217" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT217"/>
     </row>
     <row r="218" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ218" s="4"/>
+      <c r="CJ218" s="9"/>
     </row>
     <row r="219" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ219" s="4"/>
+      <c r="CJ219" s="9"/>
     </row>
     <row r="221" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT221"/>
     </row>
     <row r="222" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT222"/>
-      <c r="CJ222" s="4"/>
+      <c r="CJ222" s="9"/>
     </row>
     <row r="223" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ223" s="4"/>
+      <c r="CJ223" s="9"/>
     </row>
     <row r="229" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT229"/>
     </row>
     <row r="230" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT230"/>
-      <c r="CJ230" s="4"/>
+      <c r="CJ230" s="9"/>
     </row>
     <row r="231" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT231"/>
-      <c r="CJ231" s="4"/>
+      <c r="CJ231" s="9"/>
     </row>
     <row r="232" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ232" s="4"/>
+      <c r="CJ232" s="9"/>
     </row>
     <row r="237" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT237"/>
@@ -9619,58 +9281,58 @@
       <c r="BT242"/>
     </row>
     <row r="243" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ243" s="4"/>
+      <c r="CJ243" s="9"/>
     </row>
     <row r="244" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT244"/>
     </row>
     <row r="245" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ245" s="4"/>
+      <c r="CJ245" s="9"/>
     </row>
     <row r="255" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT255"/>
     </row>
     <row r="256" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ256" s="4"/>
+      <c r="CJ256" s="9"/>
     </row>
     <row r="258" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT258"/>
     </row>
     <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ259" s="4"/>
+      <c r="CJ259" s="9"/>
     </row>
     <row r="267" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT267"/>
     </row>
     <row r="268" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ268" s="4"/>
+      <c r="CJ268" s="9"/>
     </row>
     <row r="272" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT272"/>
     </row>
     <row r="273" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ273" s="4"/>
+      <c r="CJ273" s="9"/>
     </row>
     <row r="275" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT275"/>
     </row>
     <row r="276" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ276" s="4"/>
+      <c r="CJ276" s="9"/>
     </row>
     <row r="292" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT292"/>
     </row>
     <row r="293" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT293"/>
-      <c r="CJ293" s="4"/>
+      <c r="CJ293" s="9"/>
     </row>
     <row r="294" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT294"/>
-      <c r="CJ294" s="4"/>
+      <c r="CJ294" s="9"/>
     </row>
     <row r="295" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT295"/>
-      <c r="CJ295" s="4"/>
+      <c r="CJ295" s="9"/>
     </row>
     <row r="296" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT296"/>
@@ -9680,517 +9342,517 @@
     </row>
     <row r="299" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT299"/>
-      <c r="CJ299" s="4"/>
+      <c r="CJ299" s="9"/>
     </row>
     <row r="300" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT300"/>
-      <c r="CJ300" s="4"/>
+      <c r="CJ300" s="9"/>
     </row>
     <row r="301" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ301" s="4"/>
+      <c r="CJ301" s="9"/>
     </row>
     <row r="305" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT305"/>
     </row>
     <row r="306" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ306" s="4"/>
+      <c r="CJ306" s="9"/>
     </row>
     <row r="308" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT308"/>
     </row>
     <row r="309" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT309"/>
-      <c r="CJ309" s="4"/>
+      <c r="CJ309" s="9"/>
     </row>
     <row r="310" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT310"/>
-      <c r="CJ310" s="4"/>
+      <c r="CJ310" s="9"/>
     </row>
     <row r="311" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ311" s="4"/>
+      <c r="CJ311" s="9"/>
     </row>
     <row r="327" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT327"/>
     </row>
     <row r="328" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ328" s="4"/>
+      <c r="CJ328" s="9"/>
     </row>
     <row r="336" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ336" s="4"/>
+      <c r="CJ336" s="9"/>
     </row>
     <row r="337" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ337" s="4"/>
+      <c r="CJ337" s="9"/>
     </row>
     <row r="338" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ338" s="4"/>
+      <c r="CJ338" s="9"/>
     </row>
     <row r="339" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ339" s="4"/>
+      <c r="CJ339" s="9"/>
     </row>
     <row r="340" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ340" s="4"/>
+      <c r="CJ340" s="9"/>
     </row>
     <row r="342" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT342"/>
     </row>
     <row r="343" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ343" s="4"/>
+      <c r="CJ343" s="9"/>
     </row>
     <row r="344" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT344"/>
     </row>
     <row r="345" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT345"/>
-      <c r="CJ345" s="4"/>
+      <c r="CJ345" s="9"/>
     </row>
     <row r="346" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ346" s="4"/>
+      <c r="CJ346" s="9"/>
     </row>
     <row r="348" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT348"/>
     </row>
     <row r="349" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT349"/>
-      <c r="CJ349" s="4"/>
+      <c r="CJ349" s="9"/>
     </row>
     <row r="350" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT350"/>
-      <c r="CJ350" s="4"/>
+      <c r="CJ350" s="9"/>
     </row>
     <row r="351" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ351" s="4"/>
+      <c r="CJ351" s="9"/>
     </row>
     <row r="353" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ353" s="4"/>
+      <c r="CJ353" s="9"/>
     </row>
     <row r="355" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ355" s="4"/>
+      <c r="CJ355" s="9"/>
     </row>
     <row r="357" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ357" s="4"/>
+      <c r="CJ357" s="9"/>
     </row>
     <row r="360" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ360" s="4"/>
+      <c r="CJ360" s="9"/>
     </row>
     <row r="361" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ361" s="4"/>
+      <c r="CJ361" s="9"/>
     </row>
     <row r="362" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ362" s="4"/>
+      <c r="CJ362" s="9"/>
     </row>
     <row r="363" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ363" s="4"/>
+      <c r="CJ363" s="9"/>
     </row>
     <row r="364" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ364" s="4"/>
+      <c r="CJ364" s="9"/>
     </row>
     <row r="365" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ365" s="4"/>
+      <c r="CJ365" s="9"/>
     </row>
     <row r="366" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT366"/>
     </row>
     <row r="367" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT367"/>
-      <c r="CJ367" s="4"/>
+      <c r="CJ367" s="9"/>
     </row>
     <row r="368" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT368"/>
-      <c r="CJ368" s="4"/>
+      <c r="CJ368" s="9"/>
     </row>
     <row r="369" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ369" s="4"/>
+      <c r="CJ369" s="9"/>
     </row>
     <row r="370" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ370" s="4"/>
+      <c r="CJ370" s="9"/>
     </row>
     <row r="371" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ371" s="4"/>
+      <c r="CJ371" s="9"/>
     </row>
     <row r="372" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ372" s="4"/>
+      <c r="CJ372" s="9"/>
     </row>
     <row r="374" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ374" s="4"/>
+      <c r="CJ374" s="9"/>
     </row>
     <row r="375" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ375" s="4"/>
+      <c r="CJ375" s="9"/>
     </row>
     <row r="376" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT376"/>
     </row>
     <row r="377" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT377"/>
-      <c r="CJ377" s="4"/>
+      <c r="CJ377" s="9"/>
     </row>
     <row r="378" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT378"/>
-      <c r="CJ378" s="4"/>
+      <c r="CJ378" s="9"/>
     </row>
     <row r="379" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ379" s="4"/>
+      <c r="CJ379" s="9"/>
     </row>
     <row r="380" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ380" s="4"/>
+      <c r="CJ380" s="9"/>
     </row>
     <row r="382" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ382" s="4"/>
+      <c r="CJ382" s="9"/>
     </row>
     <row r="383" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ383" s="4"/>
+      <c r="CJ383" s="9"/>
     </row>
     <row r="384" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT384"/>
-      <c r="CJ384" s="4"/>
+      <c r="CJ384" s="9"/>
     </row>
     <row r="385" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT385"/>
-      <c r="CJ385" s="4"/>
+      <c r="CJ385" s="9"/>
     </row>
     <row r="386" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ386" s="4"/>
+      <c r="CJ386" s="9"/>
     </row>
     <row r="387" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ387" s="4"/>
+      <c r="CJ387" s="9"/>
     </row>
     <row r="388" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ388" s="4"/>
+      <c r="CJ388" s="9"/>
     </row>
     <row r="390" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT390"/>
-      <c r="CJ390" s="4"/>
+      <c r="CJ390" s="9"/>
     </row>
     <row r="391" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ391" s="4"/>
+      <c r="CJ391" s="9"/>
     </row>
     <row r="392" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ392" s="4"/>
+      <c r="CJ392" s="9"/>
     </row>
     <row r="394" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT394"/>
-      <c r="CJ394" s="4"/>
+      <c r="CJ394" s="9"/>
     </row>
     <row r="395" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT395"/>
-      <c r="CJ395" s="4"/>
+      <c r="CJ395" s="9"/>
     </row>
     <row r="396" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ396" s="4"/>
+      <c r="CJ396" s="9"/>
     </row>
     <row r="398" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ398" s="4"/>
+      <c r="CJ398" s="9"/>
     </row>
     <row r="400" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ400" s="4"/>
+      <c r="CJ400" s="9"/>
     </row>
     <row r="403" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ403" s="4"/>
+      <c r="CJ403" s="9"/>
     </row>
     <row r="404" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ404" s="4"/>
+      <c r="CJ404" s="9"/>
     </row>
     <row r="408" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT408"/>
     </row>
     <row r="409" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT409"/>
-      <c r="CJ409" s="4"/>
+      <c r="CJ409" s="9"/>
     </row>
     <row r="410" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT410"/>
-      <c r="CJ410" s="4"/>
+      <c r="CJ410" s="9"/>
     </row>
     <row r="411" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ411" s="4"/>
+      <c r="CJ411" s="9"/>
     </row>
     <row r="412" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ412" s="4"/>
+      <c r="CJ412" s="9"/>
     </row>
     <row r="413" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT413"/>
     </row>
     <row r="414" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ414" s="4"/>
+      <c r="CJ414" s="9"/>
     </row>
     <row r="416" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ416" s="4"/>
+      <c r="CJ416" s="9"/>
     </row>
     <row r="417" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ417" s="4"/>
+      <c r="CJ417" s="9"/>
     </row>
     <row r="419" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ419" s="4"/>
+      <c r="CJ419" s="9"/>
     </row>
     <row r="420" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ420" s="4"/>
+      <c r="CJ420" s="9"/>
     </row>
     <row r="421" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ421" s="4"/>
+      <c r="CJ421" s="9"/>
     </row>
     <row r="422" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ422" s="4"/>
+      <c r="CJ422" s="9"/>
     </row>
     <row r="423" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ423" s="4"/>
+      <c r="CJ423" s="9"/>
     </row>
     <row r="424" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ424" s="4"/>
+      <c r="CJ424" s="9"/>
     </row>
     <row r="425" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ425" s="4"/>
+      <c r="CJ425" s="9"/>
     </row>
     <row r="427" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT427"/>
     </row>
     <row r="428" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ428" s="4"/>
+      <c r="CJ428" s="9"/>
     </row>
     <row r="429" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ429" s="4"/>
+      <c r="CJ429" s="9"/>
     </row>
     <row r="462" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS462" s="14"/>
-      <c r="BT462" s="15"/>
+      <c r="BS462" s="4"/>
+      <c r="BT462" s="16"/>
     </row>
     <row r="463" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H463" s="14"/>
-      <c r="CJ463" s="14"/>
+      <c r="H463" s="4"/>
+      <c r="CJ463" s="4"/>
     </row>
     <row r="469" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT469"/>
     </row>
     <row r="470" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT470"/>
-      <c r="CJ470" s="4"/>
+      <c r="CJ470" s="9"/>
     </row>
     <row r="471" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT471"/>
-      <c r="CJ471" s="4"/>
+      <c r="CJ471" s="9"/>
     </row>
     <row r="472" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ472" s="4"/>
+      <c r="CJ472" s="9"/>
     </row>
     <row r="489" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT489"/>
     </row>
     <row r="490" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ490" s="4"/>
+      <c r="CJ490" s="9"/>
     </row>
     <row r="522" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT522"/>
     </row>
     <row r="523" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT523"/>
-      <c r="CJ523" s="4"/>
+      <c r="CJ523" s="9"/>
     </row>
     <row r="524" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ524" s="4"/>
+      <c r="CJ524" s="9"/>
     </row>
     <row r="540" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT540"/>
     </row>
     <row r="541" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ541" s="4"/>
+      <c r="CJ541" s="9"/>
     </row>
     <row r="547" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT547"/>
     </row>
     <row r="548" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT548"/>
-      <c r="CJ548" s="4"/>
+      <c r="CJ548" s="9"/>
     </row>
     <row r="549" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ549" s="4"/>
+      <c r="CJ549" s="9"/>
     </row>
     <row r="554" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT554"/>
     </row>
     <row r="555" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT555"/>
-      <c r="CJ555" s="4"/>
+      <c r="CJ555" s="9"/>
     </row>
     <row r="556" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT556"/>
-      <c r="CJ556" s="4"/>
+      <c r="CJ556" s="9"/>
     </row>
     <row r="557" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT557"/>
-      <c r="CJ557" s="4"/>
+      <c r="CJ557" s="9"/>
     </row>
     <row r="558" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT558"/>
-      <c r="CJ558" s="4"/>
+      <c r="CJ558" s="9"/>
     </row>
     <row r="559" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT559"/>
-      <c r="CJ559" s="4"/>
+      <c r="CJ559" s="9"/>
     </row>
     <row r="560" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT560"/>
-      <c r="CJ560" s="4"/>
+      <c r="CJ560" s="9"/>
     </row>
     <row r="561" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT561"/>
-      <c r="CJ561" s="4"/>
+      <c r="CJ561" s="9"/>
     </row>
     <row r="562" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT562"/>
-      <c r="CJ562" s="4"/>
+      <c r="CJ562" s="9"/>
     </row>
     <row r="563" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT563"/>
-      <c r="CJ563" s="4"/>
+      <c r="CJ563" s="9"/>
     </row>
     <row r="564" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT564"/>
-      <c r="CJ564" s="4"/>
+      <c r="CJ564" s="9"/>
     </row>
     <row r="565" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT565"/>
-      <c r="CJ565" s="4"/>
+      <c r="CJ565" s="9"/>
     </row>
     <row r="566" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT566"/>
-      <c r="CJ566" s="4"/>
+      <c r="CJ566" s="9"/>
     </row>
     <row r="567" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT567"/>
-      <c r="CJ567" s="4"/>
+      <c r="CJ567" s="9"/>
     </row>
     <row r="568" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT568"/>
-      <c r="CJ568" s="4"/>
+      <c r="CJ568" s="9"/>
     </row>
     <row r="569" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT569"/>
-      <c r="CJ569" s="4"/>
+      <c r="CJ569" s="9"/>
     </row>
     <row r="570" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ570" s="4"/>
+      <c r="CJ570" s="9"/>
     </row>
     <row r="574" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT574"/>
     </row>
     <row r="575" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT575"/>
-      <c r="CJ575" s="4"/>
+      <c r="CJ575" s="9"/>
     </row>
     <row r="576" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ576" s="4"/>
+      <c r="CJ576" s="9"/>
     </row>
     <row r="577" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT577"/>
     </row>
     <row r="578" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ578" s="4"/>
+      <c r="CJ578" s="9"/>
     </row>
     <row r="581" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT581"/>
     </row>
     <row r="582" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT582"/>
-      <c r="CJ582" s="4"/>
+      <c r="CJ582" s="9"/>
     </row>
     <row r="583" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ583" s="4"/>
+      <c r="CJ583" s="9"/>
     </row>
     <row r="614" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT614"/>
     </row>
     <row r="615" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT615"/>
-      <c r="CJ615" s="4"/>
+      <c r="CJ615" s="9"/>
     </row>
     <row r="616" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT616"/>
-      <c r="CJ616" s="4"/>
+      <c r="CJ616" s="9"/>
     </row>
     <row r="617" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT617"/>
-      <c r="CJ617" s="4"/>
+      <c r="CJ617" s="9"/>
     </row>
     <row r="618" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT618"/>
-      <c r="CJ618" s="4"/>
+      <c r="CJ618" s="9"/>
     </row>
     <row r="619" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT619"/>
-      <c r="CJ619" s="4"/>
+      <c r="CJ619" s="9"/>
     </row>
     <row r="620" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT620"/>
-      <c r="CJ620" s="4"/>
+      <c r="CJ620" s="9"/>
     </row>
     <row r="621" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT621"/>
-      <c r="CJ621" s="4"/>
+      <c r="CJ621" s="9"/>
     </row>
     <row r="622" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ622" s="4"/>
+      <c r="CJ622" s="9"/>
     </row>
     <row r="624" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT624"/>
     </row>
     <row r="625" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ625" s="4"/>
+      <c r="CJ625" s="9"/>
     </row>
     <row r="629" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT629"/>
     </row>
     <row r="630" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ630" s="4"/>
+      <c r="CJ630" s="9"/>
     </row>
     <row r="633" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT633"/>
     </row>
     <row r="634" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT634"/>
-      <c r="CJ634" s="4"/>
+      <c r="CJ634" s="9"/>
     </row>
     <row r="635" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT635"/>
-      <c r="CJ635" s="4"/>
+      <c r="CJ635" s="9"/>
     </row>
     <row r="636" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT636"/>
-      <c r="CJ636" s="4"/>
+      <c r="CJ636" s="9"/>
     </row>
     <row r="637" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ637" s="4"/>
+      <c r="CJ637" s="9"/>
     </row>
     <row r="644" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT644"/>
     </row>
     <row r="645" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ645" s="4"/>
+      <c r="CJ645" s="9"/>
     </row>
     <row r="648" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT648"/>
     </row>
     <row r="649" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT649"/>
-      <c r="CJ649" s="4"/>
+      <c r="CJ649" s="9"/>
     </row>
     <row r="650" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT650"/>
-      <c r="CJ650" s="4"/>
+      <c r="CJ650" s="9"/>
     </row>
     <row r="651" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT651"/>
-      <c r="CJ651" s="4"/>
+      <c r="CJ651" s="9"/>
     </row>
     <row r="652" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ652" s="4"/>
+      <c r="CJ652" s="9"/>
     </row>
     <row r="654" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT654"/>
     </row>
     <row r="655" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT655"/>
-      <c r="CJ655" s="4"/>
+      <c r="CJ655" s="9"/>
     </row>
     <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ656" s="4"/>
+      <c r="CJ656" s="9"/>
     </row>
     <row r="657" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ657">
@@ -10247,383 +9909,383 @@
     </row>
     <row r="681" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT681"/>
-      <c r="CJ681" s="4"/>
+      <c r="CJ681" s="9"/>
     </row>
     <row r="682" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT682"/>
-      <c r="CJ682" s="4"/>
+      <c r="CJ682" s="9"/>
     </row>
     <row r="683" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT683"/>
-      <c r="CJ683" s="4"/>
+      <c r="CJ683" s="9"/>
     </row>
     <row r="684" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT684"/>
-      <c r="CJ684" s="4"/>
+      <c r="CJ684" s="9"/>
     </row>
     <row r="685" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT685"/>
-      <c r="CJ685" s="4"/>
+      <c r="CJ685" s="9"/>
     </row>
     <row r="686" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT686"/>
-      <c r="CJ686" s="4"/>
+      <c r="CJ686" s="9"/>
     </row>
     <row r="687" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT687"/>
-      <c r="CJ687" s="4"/>
+      <c r="CJ687" s="9"/>
     </row>
     <row r="688" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT688"/>
-      <c r="CJ688" s="4"/>
+      <c r="CJ688" s="9"/>
     </row>
     <row r="689" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ689" s="4"/>
+      <c r="CJ689" s="9"/>
     </row>
     <row r="690" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT690"/>
     </row>
     <row r="691" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ691" s="4"/>
+      <c r="CJ691" s="9"/>
     </row>
     <row r="700" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT700"/>
     </row>
     <row r="701" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT701"/>
-      <c r="CJ701" s="4"/>
+      <c r="CJ701" s="9"/>
     </row>
     <row r="702" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT702"/>
-      <c r="CJ702" s="4"/>
+      <c r="CJ702" s="9"/>
     </row>
     <row r="703" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT703"/>
-      <c r="CJ703" s="4"/>
+      <c r="CJ703" s="9"/>
     </row>
     <row r="704" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT704"/>
-      <c r="CJ704" s="4"/>
+      <c r="CJ704" s="9"/>
     </row>
     <row r="705" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT705"/>
-      <c r="CJ705" s="4"/>
+      <c r="CJ705" s="9"/>
     </row>
     <row r="706" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT706"/>
-      <c r="CJ706" s="4"/>
+      <c r="CJ706" s="9"/>
     </row>
     <row r="707" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT707"/>
-      <c r="CJ707" s="4"/>
+      <c r="CJ707" s="9"/>
     </row>
     <row r="708" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ708" s="4"/>
+      <c r="CJ708" s="9"/>
     </row>
     <row r="709" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT709"/>
     </row>
     <row r="710" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ710" s="4"/>
+      <c r="CJ710" s="9"/>
     </row>
     <row r="715" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT715"/>
     </row>
     <row r="716" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT716"/>
-      <c r="CJ716" s="4"/>
+      <c r="CJ716" s="9"/>
     </row>
     <row r="717" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ717" s="4"/>
+      <c r="CJ717" s="9"/>
     </row>
     <row r="718" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT718"/>
     </row>
     <row r="719" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT719"/>
-      <c r="CJ719" s="4"/>
+      <c r="CJ719" s="9"/>
     </row>
     <row r="720" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ720" s="4"/>
+      <c r="CJ720" s="9"/>
     </row>
     <row r="721" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT721"/>
     </row>
     <row r="722" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT722"/>
-      <c r="CJ722" s="4"/>
+      <c r="CJ722" s="9"/>
     </row>
     <row r="723" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT723"/>
-      <c r="CJ723" s="4"/>
+      <c r="CJ723" s="9"/>
     </row>
     <row r="724" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT724"/>
-      <c r="CJ724" s="4"/>
+      <c r="CJ724" s="9"/>
     </row>
     <row r="725" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ725" s="4"/>
+      <c r="CJ725" s="9"/>
     </row>
     <row r="729" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT729"/>
     </row>
     <row r="730" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT730"/>
-      <c r="CJ730" s="4"/>
+      <c r="CJ730" s="9"/>
     </row>
     <row r="731" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT731"/>
-      <c r="CJ731" s="4"/>
+      <c r="CJ731" s="9"/>
     </row>
     <row r="732" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ732" s="4"/>
+      <c r="CJ732" s="9"/>
     </row>
     <row r="733" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT733"/>
     </row>
     <row r="734" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ734" s="4"/>
+      <c r="CJ734" s="9"/>
     </row>
     <row r="735" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS735" s="14"/>
-      <c r="BT735" s="15"/>
+      <c r="BS735" s="4"/>
+      <c r="BT735" s="16"/>
     </row>
     <row r="736" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H736" s="14"/>
-      <c r="CJ736" s="14"/>
+      <c r="H736" s="4"/>
+      <c r="CJ736" s="4"/>
     </row>
     <row r="753" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT753"/>
     </row>
     <row r="754" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT754"/>
-      <c r="CJ754" s="4"/>
+      <c r="CJ754" s="9"/>
     </row>
     <row r="755" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT755"/>
-      <c r="CJ755" s="4"/>
+      <c r="CJ755" s="9"/>
     </row>
     <row r="756" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT756"/>
-      <c r="CJ756" s="4"/>
+      <c r="CJ756" s="9"/>
     </row>
     <row r="757" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ757" s="4"/>
+      <c r="CJ757" s="9"/>
     </row>
     <row r="758" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT758"/>
     </row>
     <row r="759" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT759"/>
-      <c r="CJ759" s="4"/>
+      <c r="CJ759" s="9"/>
     </row>
     <row r="760" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS760" s="14"/>
-      <c r="BT760" s="15"/>
-      <c r="CJ760" s="4"/>
+      <c r="BS760" s="4"/>
+      <c r="BT760" s="16"/>
+      <c r="CJ760" s="9"/>
     </row>
     <row r="761" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H761" s="14"/>
-      <c r="CJ761" s="14"/>
+      <c r="H761" s="4"/>
+      <c r="CJ761" s="4"/>
     </row>
     <row r="764" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT764"/>
     </row>
     <row r="765" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT765"/>
-      <c r="CJ765" s="4"/>
+      <c r="CJ765" s="9"/>
     </row>
     <row r="766" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT766"/>
-      <c r="CJ766" s="4"/>
+      <c r="CJ766" s="9"/>
     </row>
     <row r="767" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT767"/>
-      <c r="CJ767" s="4"/>
+      <c r="CJ767" s="9"/>
     </row>
     <row r="768" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT768"/>
-      <c r="CJ768" s="4"/>
+      <c r="CJ768" s="9"/>
     </row>
     <row r="769" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT769"/>
-      <c r="CJ769" s="4"/>
+      <c r="CJ769" s="9"/>
     </row>
     <row r="770" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT770"/>
-      <c r="CJ770" s="4"/>
+      <c r="CJ770" s="9"/>
     </row>
     <row r="771" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT771"/>
-      <c r="CJ771" s="4"/>
+      <c r="CJ771" s="9"/>
     </row>
     <row r="772" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ772" s="4"/>
+      <c r="CJ772" s="9"/>
     </row>
     <row r="774" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT774"/>
     </row>
     <row r="775" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT775"/>
-      <c r="CJ775" s="4"/>
+      <c r="CJ775" s="9"/>
     </row>
     <row r="776" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT776"/>
-      <c r="CJ776" s="4"/>
+      <c r="CJ776" s="9"/>
     </row>
     <row r="777" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT777"/>
-      <c r="CJ777" s="4"/>
+      <c r="CJ777" s="9"/>
     </row>
     <row r="778" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT778"/>
-      <c r="CJ778" s="4"/>
+      <c r="CJ778" s="9"/>
     </row>
     <row r="779" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT779"/>
-      <c r="CJ779" s="4"/>
+      <c r="CJ779" s="9"/>
     </row>
     <row r="780" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ780" s="4"/>
+      <c r="CJ780" s="9"/>
     </row>
     <row r="781" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT781"/>
     </row>
     <row r="782" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT782"/>
-      <c r="CJ782" s="4"/>
+      <c r="CJ782" s="9"/>
     </row>
     <row r="783" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT783"/>
-      <c r="CJ783" s="4"/>
+      <c r="CJ783" s="9"/>
     </row>
     <row r="784" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT784"/>
-      <c r="CJ784" s="4"/>
+      <c r="CJ784" s="9"/>
     </row>
     <row r="785" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT785"/>
-      <c r="CJ785" s="4"/>
+      <c r="CJ785" s="9"/>
     </row>
     <row r="786" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT786"/>
-      <c r="CJ786" s="4"/>
+      <c r="CJ786" s="9"/>
     </row>
     <row r="787" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT787"/>
-      <c r="CJ787" s="4"/>
+      <c r="CJ787" s="9"/>
     </row>
     <row r="788" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT788"/>
-      <c r="CJ788" s="4"/>
+      <c r="CJ788" s="9"/>
     </row>
     <row r="789" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT789"/>
-      <c r="CJ789" s="4"/>
+      <c r="CJ789" s="9"/>
     </row>
     <row r="790" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT790"/>
-      <c r="CJ790" s="4"/>
+      <c r="CJ790" s="9"/>
     </row>
     <row r="791" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT791"/>
-      <c r="CJ791" s="4"/>
+      <c r="CJ791" s="9"/>
     </row>
     <row r="792" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT792"/>
-      <c r="CJ792" s="4"/>
+      <c r="CJ792" s="9"/>
     </row>
     <row r="793" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT793"/>
-      <c r="CJ793" s="4"/>
+      <c r="CJ793" s="9"/>
     </row>
     <row r="794" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT794"/>
-      <c r="CJ794" s="4"/>
+      <c r="CJ794" s="9"/>
     </row>
     <row r="795" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT795"/>
-      <c r="CJ795" s="4"/>
+      <c r="CJ795" s="9"/>
     </row>
     <row r="796" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT796"/>
-      <c r="CJ796" s="4"/>
+      <c r="CJ796" s="9"/>
     </row>
     <row r="797" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT797"/>
-      <c r="CJ797" s="4"/>
+      <c r="CJ797" s="9"/>
     </row>
     <row r="798" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT798"/>
-      <c r="CJ798" s="4"/>
+      <c r="CJ798" s="9"/>
     </row>
     <row r="799" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT799"/>
-      <c r="CJ799" s="4"/>
+      <c r="CJ799" s="9"/>
     </row>
     <row r="800" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT800"/>
-      <c r="CJ800" s="4"/>
+      <c r="CJ800" s="9"/>
     </row>
     <row r="801" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT801"/>
-      <c r="CJ801" s="4"/>
+      <c r="CJ801" s="9"/>
     </row>
     <row r="802" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT802"/>
-      <c r="CJ802" s="4"/>
+      <c r="CJ802" s="9"/>
     </row>
     <row r="803" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT803"/>
-      <c r="CJ803" s="4"/>
+      <c r="CJ803" s="9"/>
     </row>
     <row r="804" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT804"/>
-      <c r="CJ804" s="4"/>
+      <c r="CJ804" s="9"/>
     </row>
     <row r="805" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT805"/>
-      <c r="CJ805" s="4"/>
+      <c r="CJ805" s="9"/>
     </row>
     <row r="806" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT806"/>
-      <c r="CJ806" s="4"/>
+      <c r="CJ806" s="9"/>
     </row>
     <row r="807" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT807"/>
-      <c r="CJ807" s="4"/>
+      <c r="CJ807" s="9"/>
     </row>
     <row r="808" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT808"/>
-      <c r="CJ808" s="4"/>
+      <c r="CJ808" s="9"/>
     </row>
     <row r="809" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT809"/>
-      <c r="CJ809" s="4"/>
+      <c r="CJ809" s="9"/>
     </row>
     <row r="810" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT810"/>
-      <c r="CJ810" s="4"/>
+      <c r="CJ810" s="9"/>
     </row>
     <row r="811" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ811" s="4"/>
+      <c r="CJ811" s="9"/>
     </row>
     <row r="812" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT812"/>
     </row>
     <row r="813" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT813"/>
-      <c r="CJ813" s="4"/>
+      <c r="CJ813" s="9"/>
     </row>
     <row r="814" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT814"/>
-      <c r="CJ814" s="4"/>
+      <c r="CJ814" s="9"/>
     </row>
     <row r="815" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ815" s="4"/>
+      <c r="CJ815" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -10632,7 +10294,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -10821,83 +10483,91 @@
         <v>501</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C6" t="s">
         <v>496</v>
       </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>502</v>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C7" t="s">
+        <v>499</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>503</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>504</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>506</v>
-      </c>
-      <c r="C8" t="s">
-        <v>504</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>437</v>
+        <v>506</v>
       </c>
       <c r="C10" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
       <c r="Q10" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>508</v>
@@ -10907,143 +10577,169 @@
       </c>
       <c r="K11"/>
     </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C12" s="2" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C12" t="s">
+        <v>496</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="K12"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>509</v>
-      </c>
-      <c r="C13" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>510</v>
-      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13"/>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
       </c>
-      <c r="J14"/>
-      <c r="Q14" s="2" t="s">
-        <v>511</v>
-      </c>
+      <c r="K14"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C15" t="s">
-        <v>499</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="J15" t="s">
-        <v>500</v>
+        <v>231</v>
       </c>
       <c r="Q15" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>513</v>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J16" t="s">
-        <v>514</v>
+        <v>496</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16"/>
+      <c r="Q16" s="2" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>515</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
+      </c>
+      <c r="C17" t="s">
+        <v>499</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>516</v>
+        <v>500</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>508</v>
       </c>
       <c r="J18" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>508</v>
       </c>
       <c r="J19" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>390</v>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>517</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="H20" s="2">
-        <v>1</v>
-      </c>
       <c r="J20" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>519</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="J21" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>522</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" t="s">
         <v>231</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q23" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>414</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C24" t="s">
         <v>508</v>
       </c>
-      <c r="H22">
+      <c r="H24">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -11096,7 +10792,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -11197,7 +10893,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -11424,7 +11120,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -11510,7 +11206,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11520,107 +11216,107 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="20"/>
-    <col min="2" max="2" width="13.83203125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="20.58203125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" style="20" customWidth="1"/>
-    <col min="5" max="5" width="37.58203125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="39.5" style="20" customWidth="1"/>
-    <col min="7" max="7" width="38.58203125" style="20" customWidth="1"/>
-    <col min="8" max="8" width="32.25" style="20" customWidth="1"/>
-    <col min="9" max="9" width="39.9140625" style="20" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="20"/>
+    <col min="1" max="1" width="8.6640625" style="7"/>
+    <col min="2" max="2" width="13.83203125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="39.5" style="7" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="32.25" style="7" customWidth="1"/>
+    <col min="9" max="9" width="39.9140625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="7" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="7" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="7" t="s">
         <v>582</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBCC442-3644-4C42-A42F-1FE1E8E028FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B111302-B69A-45DA-AC6E-B43E33F49D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -53,6 +53,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -61,6 +62,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -86,6 +88,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -94,6 +97,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -101,13 +105,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{FAB3A062-3D99-4909-9B26-62956785CF60}">
+    <comment ref="BB1" authorId="0" shapeId="0" xr:uid="{FAB3A062-3D99-4909-9B26-62956785CF60}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -116,6 +121,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -126,13 +132,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{57547B10-E9EC-4B44-A315-093066824BB2}">
+    <comment ref="BR1" authorId="1" shapeId="0" xr:uid="{57547B10-E9EC-4B44-A315-093066824BB2}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -141,6 +148,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -148,13 +156,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{8CF5D19F-1B33-4A1B-A7CA-31C4C7016343}">
+    <comment ref="CT1" authorId="1" shapeId="0" xr:uid="{8CF5D19F-1B33-4A1B-A7CA-31C4C7016343}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -163,6 +172,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -289,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="590">
   <si>
     <t>Id</t>
   </si>
@@ -2075,12 +2085,28 @@
   <si>
     <t>NotCancelable</t>
   </si>
+  <si>
+    <t>优先Buff</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义优先级</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderBuff</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderExpression</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2133,12 +2159,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2146,6 +2174,7 @@
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2153,6 +2182,7 @@
       <sz val="11"/>
       <color rgb="FFFFC000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2160,47 +2190,42 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF333639"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF333639"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2291,10 +2316,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6380,7 +6405,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH815"/>
+  <dimension ref="A1:DJ815"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6420,49 +6445,49 @@
     <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
     <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
-    <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="19.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
-    <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="10" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="10" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="10" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="10" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
-    <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="17.08203125" customWidth="1"/>
-    <col min="97" max="97" width="14" customWidth="1"/>
-    <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
-    <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="10" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="10" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="10" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="10" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="114" max="114" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>156</v>
       </c>
@@ -6586,209 +6611,215 @@
       <c r="AQ1" t="s">
         <v>195</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="AT1" t="s">
         <v>196</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>197</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>198</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>199</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>200</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>201</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>202</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>203</v>
       </c>
-      <c r="AZ1" s="8" t="s">
+      <c r="BB1" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>205</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>206</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>207</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>208</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>209</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>210</v>
       </c>
       <c r="BH1" t="s">
         <v>210</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
+        <v>210</v>
+      </c>
+      <c r="BK1" t="s">
         <v>211</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>212</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>213</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>214</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>215</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>216</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>217</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>218</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>219</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>220</v>
       </c>
-      <c r="BS1" s="8" t="s">
+      <c r="BU1" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="BT1" s="10" t="s">
+      <c r="BV1" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="BU1" s="10" t="s">
+      <c r="BW1" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="BV1" s="10" t="s">
+      <c r="BX1" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="BW1" s="10" t="s">
+      <c r="BY1" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="BX1" s="10" t="s">
+      <c r="BZ1" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="BY1" s="10" t="s">
+      <c r="CA1" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>228</v>
       </c>
-      <c r="CA1" s="10" t="s">
+      <c r="CC1" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>230</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>231</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>232</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>233</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>234</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>235</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>236</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>237</v>
       </c>
-      <c r="CJ1" s="8" t="s">
+      <c r="CL1" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>239</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CN1" t="s">
         <v>240</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>241</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>242</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>243</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>220</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>244</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>245</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>246</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>247</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>248</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>249</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>250</v>
       </c>
       <c r="CX1" t="s">
         <v>249</v>
       </c>
       <c r="CY1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>249</v>
+      </c>
+      <c r="DA1" t="s">
         <v>251</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DB1" t="s">
         <v>252</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>253</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>254</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>255</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>256</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>257</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>258</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6915,212 +6946,218 @@
       <c r="AQ2" t="s">
         <v>297</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AT2" t="s">
         <v>298</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>299</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>300</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>301</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>302</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>303</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>304</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>306</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>307</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>308</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>309</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>310</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>311</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>312</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>313</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>314</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>315</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>316</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>317</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>318</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BO2" t="s">
         <v>79</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BP2" t="s">
         <v>319</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BQ2" t="s">
         <v>320</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BR2" t="s">
         <v>321</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>322</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>323</v>
       </c>
-      <c r="BS2" s="8" t="s">
+      <c r="BU2" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="BT2" s="10" t="s">
+      <c r="BV2" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="BU2" s="10" t="s">
+      <c r="BW2" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="BV2" s="10" t="s">
+      <c r="BX2" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="BW2" s="10" t="s">
+      <c r="BY2" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="BX2" s="10" t="s">
+      <c r="BZ2" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="BY2" s="10" t="s">
+      <c r="CA2" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CB2" t="s">
         <v>330</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CC2" t="s">
         <v>331</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CD2" t="s">
         <v>332</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CE2" t="s">
         <v>333</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CF2" t="s">
         <v>334</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CG2" t="s">
         <v>335</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CH2" t="s">
         <v>336</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CI2" t="s">
         <v>337</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CJ2" t="s">
         <v>338</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>339</v>
       </c>
-      <c r="CJ2" s="8" t="s">
+      <c r="CL2" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>341</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CN2" t="s">
         <v>342</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>343</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>344</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>345</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>346</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>347</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>348</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>349</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>350</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>351</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>352</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>353</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>354</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>355</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>356</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>357</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>358</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>359</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>360</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>361</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>362</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7247,182 +7284,182 @@
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT3" t="s">
         <v>370</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>117</v>
       </c>
       <c r="AU3" t="s">
         <v>116</v>
       </c>
       <c r="AV3" t="s">
-        <v>371</v>
+        <v>117</v>
       </c>
       <c r="AW3" t="s">
         <v>116</v>
       </c>
       <c r="AX3" t="s">
-        <v>117</v>
+        <v>371</v>
       </c>
       <c r="AY3" t="s">
         <v>116</v>
       </c>
       <c r="AZ3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BB3" t="s">
         <v>118</v>
       </c>
       <c r="BC3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD3" t="s">
         <v>118</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF3" t="s">
         <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>370</v>
       </c>
       <c r="BG3" t="s">
         <v>116</v>
       </c>
       <c r="BH3" t="s">
-        <v>117</v>
+        <v>370</v>
       </c>
       <c r="BI3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BJ3" t="s">
         <v>117</v>
       </c>
       <c r="BK3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM3" t="s">
         <v>118</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BN3" t="s">
         <v>118</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BO3" t="s">
         <v>119</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BP3" t="s">
         <v>119</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BQ3" t="s">
         <v>372</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BR3" t="s">
         <v>373</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BS3" t="s">
         <v>117</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BT3" t="s">
         <v>117</v>
       </c>
-      <c r="BS3" s="8" t="s">
+      <c r="BU3" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="10" t="s">
+      <c r="BV3" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="BU3" s="10" t="s">
+      <c r="BW3" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="BV3" s="10" t="s">
+      <c r="BX3" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="BW3" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="BX3" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="BY3" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="BZ3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>375</v>
+      <c r="BZ3" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="CA3" s="10" t="s">
+        <v>374</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
       </c>
       <c r="CC3" t="s">
-        <v>124</v>
+        <v>375</v>
       </c>
       <c r="CD3" t="s">
         <v>124</v>
       </c>
       <c r="CE3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CG3" t="s">
         <v>376</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CH3" t="s">
         <v>377</v>
       </c>
-      <c r="CG3" t="s">
+      <c r="CI3" t="s">
         <v>2</v>
       </c>
-      <c r="CH3" t="s">
+      <c r="CJ3" t="s">
         <v>378</v>
       </c>
-      <c r="CI3" t="s">
+      <c r="CK3" t="s">
         <v>378</v>
       </c>
-      <c r="CJ3" s="8" t="s">
+      <c r="CL3" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CM3" t="s">
         <v>120</v>
       </c>
-      <c r="CL3" t="s">
+      <c r="CN3" t="s">
         <v>120</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>123</v>
       </c>
       <c r="CO3" t="s">
         <v>123</v>
       </c>
       <c r="CP3" t="s">
-        <v>375</v>
+        <v>123</v>
       </c>
       <c r="CQ3" t="s">
         <v>123</v>
       </c>
       <c r="CR3" t="s">
+        <v>375</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CT3" t="s">
         <v>116</v>
       </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
         <v>125</v>
       </c>
-      <c r="CT3" t="s">
+      <c r="CV3" t="s">
         <v>379</v>
       </c>
-      <c r="CU3" t="s">
+      <c r="CW3" t="s">
         <v>380</v>
       </c>
-      <c r="CV3" t="s">
+      <c r="CX3" t="s">
         <v>380</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>379</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>379</v>
       </c>
       <c r="CY3" t="s">
         <v>379</v>
@@ -7434,10 +7471,10 @@
         <v>379</v>
       </c>
       <c r="DB3" t="s">
-        <v>116</v>
+        <v>379</v>
       </c>
       <c r="DC3" t="s">
-        <v>116</v>
+        <v>379</v>
       </c>
       <c r="DD3" t="s">
         <v>116</v>
@@ -7451,13 +7488,19 @@
       <c r="DG3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="4" spans="1:111" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="DH3" t="s">
+        <v>116</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="5" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>382</v>
       </c>
@@ -7477,11 +7520,11 @@
       <c r="AO5" t="s">
         <v>386</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AT5" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="6" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>388</v>
       </c>
@@ -7503,32 +7546,32 @@
       <c r="AO6" t="s">
         <v>391</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AT6" t="s">
         <v>392</v>
       </c>
-      <c r="AW6">
-        <v>1</v>
-      </c>
-      <c r="AX6">
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
         <v>0.01</v>
       </c>
-      <c r="AZ6">
+      <c r="BB6">
         <v>2</v>
       </c>
-      <c r="BB6">
-        <v>1</v>
-      </c>
-      <c r="BN6" t="s">
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="s">
         <v>393</v>
       </c>
-      <c r="BZ6" t="s">
+      <c r="CB6" t="s">
         <v>57</v>
       </c>
-      <c r="CE6" t="s">
+      <c r="CG6" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="7" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>393</v>
       </c>
@@ -7548,41 +7591,41 @@
       <c r="AO7" t="s">
         <v>391</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AT7" t="s">
         <v>392</v>
       </c>
-      <c r="AW7">
-        <v>1</v>
-      </c>
-      <c r="AX7">
-        <v>1</v>
-      </c>
-      <c r="BB7">
-        <v>1</v>
-      </c>
-      <c r="BN7" t="s">
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="s">
         <v>395</v>
       </c>
-      <c r="CF7" t="s">
+      <c r="CH7" t="s">
         <v>396</v>
       </c>
-      <c r="CG7" t="s">
+      <c r="CI7" t="s">
         <v>397</v>
       </c>
-      <c r="CL7" t="s">
+      <c r="CN7" t="s">
         <v>398</v>
       </c>
-      <c r="CM7">
+      <c r="CO7">
         <v>22</v>
       </c>
-      <c r="CP7">
+      <c r="CR7">
         <v>10</v>
       </c>
-      <c r="CW7" t="s">
+      <c r="CY7" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="8" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>400</v>
       </c>
@@ -7604,24 +7647,24 @@
       <c r="AG8" t="s">
         <v>403</v>
       </c>
-      <c r="BB8">
-        <v>1</v>
-      </c>
-      <c r="CJ8" s="9"/>
-      <c r="CS8" t="s">
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CL8" s="9"/>
+      <c r="CU8" t="s">
         <v>404</v>
       </c>
-      <c r="DB8">
-        <v>1</v>
-      </c>
-      <c r="DE8">
-        <v>1</v>
-      </c>
-      <c r="DF8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="DD8">
+        <v>1</v>
+      </c>
+      <c r="DG8">
+        <v>1</v>
+      </c>
+      <c r="DH8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>405</v>
       </c>
@@ -7655,36 +7698,36 @@
       <c r="AG9" t="s">
         <v>403</v>
       </c>
-      <c r="AR9" t="s">
+      <c r="AT9" t="s">
         <v>406</v>
       </c>
-      <c r="BB9">
-        <v>1</v>
-      </c>
-      <c r="BM9" t="s">
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="s">
         <v>407</v>
       </c>
-      <c r="BS9" s="14"/>
-      <c r="BT9" s="14"/>
       <c r="BU9" s="14"/>
       <c r="BV9" s="14"/>
       <c r="BW9" s="14"/>
       <c r="BX9" s="14"/>
-      <c r="BY9"/>
-      <c r="CL9" t="s">
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9"/>
+      <c r="CN9" t="s">
         <v>408</v>
       </c>
-      <c r="CM9">
+      <c r="CO9">
         <v>8</v>
       </c>
-      <c r="CP9">
+      <c r="CR9">
         <v>9999</v>
       </c>
-      <c r="DB9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="DD9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>407</v>
       </c>
@@ -7711,36 +7754,36 @@
       <c r="AC10">
         <v>1</v>
       </c>
-      <c r="AR10" t="s">
+      <c r="AT10" t="s">
         <v>409</v>
       </c>
-      <c r="BB10">
+      <c r="BD10">
         <v>99</v>
       </c>
-      <c r="BQ10">
+      <c r="BS10">
         <v>0.1</v>
       </c>
-      <c r="BS10" s="14"/>
-      <c r="BT10" s="14"/>
       <c r="BU10" s="14"/>
       <c r="BV10" s="14"/>
       <c r="BW10" s="14"/>
       <c r="BX10" s="14"/>
-      <c r="BY10"/>
-      <c r="CL10" s="12" t="s">
+      <c r="BY10" s="14"/>
+      <c r="BZ10" s="14"/>
+      <c r="CA10"/>
+      <c r="CN10" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="CM10">
+      <c r="CO10">
         <v>0.2</v>
       </c>
-      <c r="CP10">
+      <c r="CR10">
         <v>0.2</v>
       </c>
-      <c r="DB10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="DD10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>411</v>
       </c>
@@ -7759,35 +7802,35 @@
       <c r="AG11" t="s">
         <v>403</v>
       </c>
-      <c r="AW11" s="9"/>
-      <c r="BB11">
-        <v>1</v>
-      </c>
-      <c r="BT11"/>
-      <c r="BU11"/>
+      <c r="AY11" s="9"/>
+      <c r="BD11">
+        <v>1</v>
+      </c>
       <c r="BV11"/>
       <c r="BW11"/>
       <c r="BX11"/>
       <c r="BY11"/>
-      <c r="BZ11" s="9"/>
-      <c r="CA11" s="9"/>
+      <c r="BZ11"/>
+      <c r="CA11"/>
       <c r="CB11" s="9"/>
       <c r="CC11" s="9"/>
       <c r="CD11" s="9"/>
+      <c r="CE11" s="9"/>
       <c r="CF11" s="9"/>
-      <c r="CG11" s="9"/>
       <c r="CH11" s="9"/>
       <c r="CI11" s="9"/>
       <c r="CJ11" s="9"/>
       <c r="CK11" s="9"/>
-      <c r="CL11" t="s">
+      <c r="CL11" s="9"/>
+      <c r="CM11" s="9"/>
+      <c r="CN11" t="s">
         <v>412</v>
       </c>
-      <c r="CP11">
+      <c r="CR11">
         <v>99999</v>
       </c>
     </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>413</v>
       </c>
@@ -7803,41 +7846,41 @@
       <c r="AJ12" t="s">
         <v>4</v>
       </c>
-      <c r="AT12">
+      <c r="AV12">
         <v>20</v>
       </c>
-      <c r="AW12" s="9"/>
-      <c r="BB12">
-        <v>1</v>
-      </c>
-      <c r="BQ12">
+      <c r="AY12" s="9"/>
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BS12">
         <v>0.1</v>
       </c>
-      <c r="BT12"/>
-      <c r="BU12"/>
       <c r="BV12"/>
       <c r="BW12"/>
       <c r="BX12"/>
       <c r="BY12"/>
-      <c r="BZ12" s="9"/>
-      <c r="CA12" s="9"/>
+      <c r="BZ12"/>
+      <c r="CA12"/>
       <c r="CB12" s="9"/>
       <c r="CC12" s="9"/>
       <c r="CD12" s="9"/>
+      <c r="CE12" s="9"/>
       <c r="CF12" s="9"/>
-      <c r="CG12" s="9"/>
       <c r="CH12" s="9"/>
       <c r="CI12" s="9"/>
       <c r="CJ12" s="9"/>
       <c r="CK12" s="9"/>
-      <c r="CL12" t="s">
+      <c r="CL12" s="9"/>
+      <c r="CM12" s="9"/>
+      <c r="CN12" t="s">
         <v>414</v>
       </c>
-      <c r="CP12">
+      <c r="CR12">
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>395</v>
       </c>
@@ -7864,34 +7907,34 @@
       <c r="AG13" t="s">
         <v>403</v>
       </c>
-      <c r="AR13" t="s">
+      <c r="AT13" t="s">
         <v>406</v>
       </c>
-      <c r="BB13">
-        <v>1</v>
-      </c>
-      <c r="BT13"/>
-      <c r="BZ13" s="10"/>
-      <c r="CL13" t="s">
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="BV13"/>
+      <c r="CB13" s="10"/>
+      <c r="CN13" t="s">
         <v>398</v>
       </c>
-      <c r="CM13">
+      <c r="CO13">
         <v>22</v>
       </c>
-      <c r="CP13">
+      <c r="CR13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="BT14"/>
-    </row>
-    <row r="15" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="BT15"/>
-    </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="BT16"/>
-    </row>
-    <row r="17" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="BV14"/>
+    </row>
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="BV15"/>
+    </row>
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="BV16"/>
+    </row>
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>416</v>
       </c>
@@ -7924,41 +7967,41 @@
       <c r="AG17" t="s">
         <v>403</v>
       </c>
-      <c r="BB17">
-        <v>1</v>
-      </c>
-      <c r="BM17" s="8" t="s">
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BO17" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="BN17" t="s">
+      <c r="BP17" t="s">
         <v>423</v>
       </c>
-      <c r="BR17">
+      <c r="BT17">
         <v>30</v>
       </c>
-      <c r="BT17" s="10">
+      <c r="BV17" s="10">
         <v>13</v>
       </c>
-      <c r="BU17" s="10">
+      <c r="BW17" s="10">
         <v>15</v>
       </c>
-      <c r="BV17" s="10">
-        <v>1</v>
-      </c>
-      <c r="BW17" s="10" t="s">
+      <c r="BX17" s="10">
+        <v>1</v>
+      </c>
+      <c r="BY17" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="CL17" s="12" t="s">
+      <c r="CN17" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="CP17">
+      <c r="CR17">
         <v>30</v>
       </c>
-      <c r="DB17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>426</v>
       </c>
@@ -7984,50 +8027,50 @@
       <c r="AQ18" t="s">
         <v>144</v>
       </c>
-      <c r="AU18">
-        <v>1</v>
-      </c>
       <c r="AW18">
         <v>1</v>
       </c>
-      <c r="AX18">
-        <v>1</v>
-      </c>
-      <c r="BB18">
-        <v>1</v>
-      </c>
-      <c r="BN18" t="s">
+      <c r="AY18">
+        <v>1</v>
+      </c>
+      <c r="AZ18">
+        <v>1</v>
+      </c>
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="s">
         <v>427</v>
       </c>
-      <c r="BZ18" t="s">
+      <c r="CB18" t="s">
         <v>428</v>
       </c>
-      <c r="CE18" t="s">
+      <c r="CG18" t="s">
         <v>394</v>
       </c>
-      <c r="CF18" t="s">
+      <c r="CH18" t="s">
         <v>396</v>
       </c>
-      <c r="CG18" t="s">
+      <c r="CI18" t="s">
         <v>397</v>
       </c>
-      <c r="CL18" s="8" t="s">
+      <c r="CN18" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="CM18">
+      <c r="CO18">
         <v>22</v>
       </c>
-      <c r="CN18">
+      <c r="CP18">
         <v>39.6</v>
       </c>
-      <c r="CP18">
+      <c r="CR18">
         <v>10</v>
       </c>
-      <c r="CW18" t="s">
+      <c r="CY18" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="19" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>430</v>
       </c>
@@ -8053,42 +8096,42 @@
       <c r="AO19" t="s">
         <v>391</v>
       </c>
-      <c r="AR19" t="s">
+      <c r="AT19" t="s">
         <v>392</v>
       </c>
-      <c r="AV19" t="s">
+      <c r="AX19" t="s">
         <v>431</v>
       </c>
-      <c r="AX19">
-        <v>1</v>
-      </c>
       <c r="AZ19">
+        <v>1</v>
+      </c>
+      <c r="BB19">
         <v>2</v>
       </c>
-      <c r="BB19">
-        <v>1</v>
-      </c>
-      <c r="BZ19" s="3"/>
-      <c r="CF19" t="s">
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="CB19" s="3"/>
+      <c r="CH19" t="s">
         <v>432</v>
       </c>
-      <c r="CG19" t="s">
+      <c r="CI19" t="s">
         <v>397</v>
       </c>
-      <c r="CL19" s="12" t="s">
+      <c r="CN19" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="CP19">
+      <c r="CR19">
         <v>0.1</v>
       </c>
-      <c r="DB19">
-        <v>1</v>
-      </c>
-      <c r="DF19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD19">
+        <v>1</v>
+      </c>
+      <c r="DH19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>434</v>
       </c>
@@ -8113,26 +8156,26 @@
       <c r="AG20" t="s">
         <v>403</v>
       </c>
-      <c r="AU20">
-        <v>1</v>
-      </c>
-      <c r="BB20">
-        <v>1</v>
-      </c>
-      <c r="CL20" t="s">
+      <c r="AW20">
+        <v>1</v>
+      </c>
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="CN20" t="s">
         <v>429</v>
       </c>
-      <c r="CM20">
+      <c r="CO20">
         <v>22</v>
       </c>
-      <c r="CN20">
+      <c r="CP20">
         <v>39.6</v>
       </c>
-      <c r="CP20">
+      <c r="CR20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>433</v>
       </c>
@@ -8154,23 +8197,23 @@
       <c r="AJ21" t="s">
         <v>144</v>
       </c>
-      <c r="AR21" t="s">
+      <c r="AT21" t="s">
         <v>392</v>
       </c>
-      <c r="BB21">
-        <v>1</v>
-      </c>
-      <c r="BQ21">
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="BS21">
         <v>0.1</v>
       </c>
-      <c r="CL21" s="12" t="s">
+      <c r="CN21" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="CP21">
+      <c r="CR21">
         <v>0.2</v>
       </c>
     </row>
-    <row r="22" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>435</v>
       </c>
@@ -8190,39 +8233,39 @@
       <c r="AG22" t="s">
         <v>403</v>
       </c>
-      <c r="AW22" s="9"/>
-      <c r="BB22">
-        <v>1</v>
-      </c>
-      <c r="BT22"/>
-      <c r="BU22"/>
+      <c r="AY22" s="9"/>
+      <c r="BD22">
+        <v>1</v>
+      </c>
       <c r="BV22"/>
       <c r="BW22"/>
       <c r="BX22"/>
       <c r="BY22"/>
-      <c r="BZ22" s="9"/>
-      <c r="CA22" s="9"/>
+      <c r="BZ22"/>
+      <c r="CA22"/>
       <c r="CB22" s="9"/>
       <c r="CC22" s="9"/>
       <c r="CD22" s="9"/>
+      <c r="CE22" s="9"/>
       <c r="CF22" s="9"/>
-      <c r="CG22" s="9"/>
       <c r="CH22" s="9"/>
       <c r="CI22" s="9"/>
-      <c r="CL22" s="12" t="s">
+      <c r="CJ22" s="9"/>
+      <c r="CK22" s="9"/>
+      <c r="CN22" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="CP22">
+      <c r="CR22">
         <v>40</v>
       </c>
-      <c r="DB22">
-        <v>1</v>
-      </c>
-      <c r="DF22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD22">
+        <v>1</v>
+      </c>
+      <c r="DH22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>436</v>
       </c>
@@ -8242,17 +8285,17 @@
       <c r="AC23">
         <v>1</v>
       </c>
-      <c r="AT23">
+      <c r="AV23">
         <v>20</v>
       </c>
-      <c r="BB23">
+      <c r="BD23">
         <v>99</v>
       </c>
-      <c r="CK23" t="s">
+      <c r="CM23" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>438</v>
       </c>
@@ -8273,32 +8316,32 @@
       <c r="AG24" t="s">
         <v>403</v>
       </c>
-      <c r="BB24">
-        <v>1</v>
-      </c>
-      <c r="BQ24">
+      <c r="BD24">
+        <v>1</v>
+      </c>
+      <c r="BS24">
         <v>0.1</v>
       </c>
-      <c r="BT24"/>
-      <c r="BZ24" t="s">
+      <c r="BV24"/>
+      <c r="CB24" t="s">
         <v>439</v>
       </c>
-      <c r="CE24" t="s">
+      <c r="CG24" t="s">
         <v>394</v>
       </c>
-      <c r="CG24" s="9"/>
-      <c r="CH24" s="9"/>
-      <c r="DB24">
-        <v>1</v>
-      </c>
-      <c r="DE24">
-        <v>1</v>
-      </c>
-      <c r="DF24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CI24" s="9"/>
+      <c r="CJ24" s="9"/>
+      <c r="DD24">
+        <v>1</v>
+      </c>
+      <c r="DG24">
+        <v>1</v>
+      </c>
+      <c r="DH24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>440</v>
       </c>
@@ -8322,31 +8365,31 @@
       <c r="AG25" t="s">
         <v>403</v>
       </c>
-      <c r="BB25">
-        <v>1</v>
-      </c>
-      <c r="BQ25">
+      <c r="BD25">
+        <v>1</v>
+      </c>
+      <c r="BS25">
         <v>0.2</v>
       </c>
-      <c r="BT25"/>
-      <c r="BZ25" t="s">
+      <c r="BV25"/>
+      <c r="CB25" t="s">
         <v>442</v>
       </c>
-      <c r="CE25" t="s">
+      <c r="CG25" t="s">
         <v>394</v>
       </c>
-      <c r="CH25" s="9"/>
-      <c r="DB25">
-        <v>1</v>
-      </c>
-      <c r="DE25">
-        <v>1</v>
-      </c>
-      <c r="DF25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ25" s="9"/>
+      <c r="DD25">
+        <v>1</v>
+      </c>
+      <c r="DG25">
+        <v>1</v>
+      </c>
+      <c r="DH25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>443</v>
       </c>
@@ -8381,57 +8424,57 @@
       <c r="AO26" t="s">
         <v>391</v>
       </c>
-      <c r="AR26" t="s">
+      <c r="AT26" t="s">
         <v>406</v>
       </c>
-      <c r="AW26">
-        <v>1</v>
-      </c>
-      <c r="AX26">
-        <v>1</v>
-      </c>
-      <c r="BB26">
-        <v>1</v>
-      </c>
-      <c r="BM26" s="8"/>
-      <c r="BN26" s="8"/>
-      <c r="BQ26">
+      <c r="AY26">
+        <v>1</v>
+      </c>
+      <c r="AZ26">
+        <v>1</v>
+      </c>
+      <c r="BD26">
+        <v>1</v>
+      </c>
+      <c r="BO26" s="8"/>
+      <c r="BP26" s="8"/>
+      <c r="BS26">
         <v>0.1</v>
       </c>
-      <c r="CE26" s="8" t="s">
+      <c r="CG26" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="CF26" t="s">
+      <c r="CH26" t="s">
         <v>396</v>
       </c>
-      <c r="CG26" t="s">
+      <c r="CI26" t="s">
         <v>397</v>
       </c>
-      <c r="CK26" s="8"/>
-      <c r="CL26" t="s">
+      <c r="CM26" s="8"/>
+      <c r="CN26" t="s">
         <v>429</v>
       </c>
-      <c r="CM26">
+      <c r="CO26">
         <v>22</v>
       </c>
-      <c r="CN26">
+      <c r="CP26">
         <v>39.6</v>
       </c>
-      <c r="CP26">
+      <c r="CR26">
         <v>10</v>
       </c>
-      <c r="CW26" t="s">
+      <c r="CY26" t="s">
         <v>399</v>
       </c>
-      <c r="DB26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BS27" s="10"/>
-      <c r="BY27"/>
-    </row>
-    <row r="28" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="BU27" s="10"/>
+      <c r="CA27"/>
+    </row>
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>444</v>
       </c>
@@ -8467,41 +8510,41 @@
       <c r="AG28" t="s">
         <v>403</v>
       </c>
-      <c r="BB28">
-        <v>1</v>
-      </c>
-      <c r="BM28" t="s">
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="BO28" t="s">
         <v>448</v>
       </c>
-      <c r="BN28" t="s">
+      <c r="BP28" t="s">
         <v>449</v>
       </c>
-      <c r="BR28">
-        <v>1</v>
-      </c>
-      <c r="BT28" s="10">
+      <c r="BT28">
+        <v>1</v>
+      </c>
+      <c r="BV28" s="10">
         <v>11</v>
       </c>
-      <c r="BU28" s="10">
+      <c r="BW28" s="10">
         <v>15</v>
       </c>
-      <c r="BV28" s="10">
-        <v>1</v>
-      </c>
-      <c r="BW28" s="10" t="s">
+      <c r="BX28" s="10">
+        <v>1</v>
+      </c>
+      <c r="BY28" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="CL28" s="12" t="s">
+      <c r="CN28" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="CM28" t="s">
+      <c r="CO28" t="s">
         <v>451</v>
       </c>
-      <c r="CP28">
+      <c r="CR28">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>448</v>
       </c>
@@ -8523,23 +8566,23 @@
       <c r="AG29" t="s">
         <v>403</v>
       </c>
-      <c r="AR29" t="s">
+      <c r="AT29" t="s">
         <v>406</v>
       </c>
-      <c r="BB29">
-        <v>1</v>
-      </c>
-      <c r="BQ29">
+      <c r="BD29">
+        <v>1</v>
+      </c>
+      <c r="BS29">
         <v>0.1</v>
       </c>
-      <c r="CL29" s="12" t="s">
+      <c r="CN29" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="CP29">
+      <c r="CR29">
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>453</v>
       </c>
@@ -8561,21 +8604,21 @@
       <c r="AJ30" t="s">
         <v>144</v>
       </c>
-      <c r="AR30" t="s">
+      <c r="AT30" t="s">
         <v>392</v>
       </c>
-      <c r="BB30">
-        <v>1</v>
-      </c>
-      <c r="BQ30">
+      <c r="BD30">
+        <v>1</v>
+      </c>
+      <c r="BS30">
         <v>0.1</v>
       </c>
-      <c r="CJ30" s="9"/>
-      <c r="CS30" t="s">
+      <c r="CL30" s="9"/>
+      <c r="CU30" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="31" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>456</v>
       </c>
@@ -8599,31 +8642,31 @@
       <c r="AG31" t="s">
         <v>403</v>
       </c>
-      <c r="BB31">
-        <v>1</v>
-      </c>
-      <c r="BQ31">
-        <v>1</v>
-      </c>
-      <c r="BT31"/>
-      <c r="BZ31" s="15" t="s">
+      <c r="BD31">
+        <v>1</v>
+      </c>
+      <c r="BS31">
+        <v>1</v>
+      </c>
+      <c r="BV31"/>
+      <c r="CB31" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="CE31" t="s">
+      <c r="CG31" t="s">
         <v>394</v>
       </c>
-      <c r="CH31" s="9"/>
-      <c r="DB31">
-        <v>1</v>
-      </c>
-      <c r="DE31">
-        <v>1</v>
-      </c>
-      <c r="DF31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ31" s="9"/>
+      <c r="DD31">
+        <v>1</v>
+      </c>
+      <c r="DG31">
+        <v>1</v>
+      </c>
+      <c r="DH31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>458</v>
       </c>
@@ -8644,32 +8687,32 @@
       <c r="AG32" t="s">
         <v>403</v>
       </c>
-      <c r="BB32">
-        <v>1</v>
-      </c>
-      <c r="BQ32">
+      <c r="BD32">
+        <v>1</v>
+      </c>
+      <c r="BS32">
         <v>0.66669999999999996</v>
       </c>
-      <c r="BT32"/>
-      <c r="BZ32" s="3" t="s">
+      <c r="BV32"/>
+      <c r="CB32" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="CE32" t="s">
+      <c r="CG32" t="s">
         <v>394</v>
       </c>
-      <c r="CG32" s="9"/>
-      <c r="CH32" s="9"/>
-      <c r="DB32">
-        <v>1</v>
-      </c>
-      <c r="DE32">
-        <v>1</v>
-      </c>
-      <c r="DF32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:101" x14ac:dyDescent="0.25">
+      <c r="CI32" s="9"/>
+      <c r="CJ32" s="9"/>
+      <c r="DD32">
+        <v>1</v>
+      </c>
+      <c r="DG32">
+        <v>1</v>
+      </c>
+      <c r="DH32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>460</v>
       </c>
@@ -8703,41 +8746,41 @@
       <c r="AG34" t="s">
         <v>403</v>
       </c>
-      <c r="BB34">
-        <v>1</v>
-      </c>
-      <c r="BM34" t="s">
+      <c r="BD34">
+        <v>1</v>
+      </c>
+      <c r="BO34" t="s">
         <v>461</v>
       </c>
-      <c r="BR34">
+      <c r="BT34">
         <v>25</v>
       </c>
-      <c r="BT34" s="10">
-        <v>1</v>
-      </c>
-      <c r="BU34" s="10">
-        <v>1</v>
-      </c>
       <c r="BV34" s="10">
         <v>1</v>
       </c>
-      <c r="BW34" s="10" t="s">
+      <c r="BW34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BX34" s="10">
+        <v>1</v>
+      </c>
+      <c r="BY34" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="CL34" s="12" t="s">
+      <c r="CN34" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="CM34" t="s">
+      <c r="CO34" t="s">
         <v>463</v>
       </c>
-      <c r="CN34">
+      <c r="CP34">
         <v>80</v>
       </c>
-      <c r="CP34">
+      <c r="CR34">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:101" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>464</v>
       </c>
@@ -8754,35 +8797,35 @@
       <c r="AO35" t="s">
         <v>466</v>
       </c>
-      <c r="AR35" t="s">
+      <c r="AT35" t="s">
         <v>409</v>
       </c>
-      <c r="AV35" t="s">
+      <c r="AX35" t="s">
         <v>431</v>
       </c>
-      <c r="AX35">
-        <v>1</v>
-      </c>
-      <c r="BB35">
-        <v>1</v>
-      </c>
-      <c r="BN35" t="s">
+      <c r="AZ35">
+        <v>1</v>
+      </c>
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="s">
         <v>467</v>
       </c>
-      <c r="BZ35" t="s">
+      <c r="CB35" t="s">
         <v>468</v>
       </c>
-      <c r="CE35" t="s">
+      <c r="CG35" t="s">
         <v>394</v>
       </c>
-      <c r="CV35" t="s">
+      <c r="CX35" t="s">
         <v>469</v>
       </c>
-      <c r="CW35" t="s">
+      <c r="CY35" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="36" spans="1:101" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>467</v>
       </c>
@@ -8813,35 +8856,35 @@
       <c r="AO36" t="s">
         <v>391</v>
       </c>
-      <c r="AT36">
-        <v>1</v>
-      </c>
-      <c r="AW36">
-        <v>1</v>
-      </c>
-      <c r="AX36">
+      <c r="AV36">
+        <v>1</v>
+      </c>
+      <c r="AY36">
+        <v>1</v>
+      </c>
+      <c r="AZ36">
         <v>0.5</v>
       </c>
-      <c r="BB36">
-        <v>1</v>
-      </c>
-      <c r="CF36" t="s">
+      <c r="BD36">
+        <v>1</v>
+      </c>
+      <c r="CH36" t="s">
         <v>396</v>
       </c>
-      <c r="CG36" t="s">
+      <c r="CI36" t="s">
         <v>397</v>
       </c>
-      <c r="CL36" t="s">
+      <c r="CN36" t="s">
         <v>398</v>
       </c>
-      <c r="CM36">
+      <c r="CO36">
         <v>22</v>
       </c>
-      <c r="CP36">
+      <c r="CR36">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:101" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>471</v>
       </c>
@@ -8860,14 +8903,14 @@
       <c r="AG37" t="s">
         <v>403</v>
       </c>
-      <c r="BB37">
-        <v>1</v>
-      </c>
-      <c r="CS37" t="s">
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="38" spans="1:101" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>474</v>
       </c>
@@ -8889,17 +8932,17 @@
       <c r="AG38" t="s">
         <v>403</v>
       </c>
-      <c r="BB38">
-        <v>1</v>
-      </c>
-      <c r="CL38" t="s">
+      <c r="BD38">
+        <v>1</v>
+      </c>
+      <c r="CN38" t="s">
         <v>452</v>
       </c>
-      <c r="CP38">
+      <c r="CR38">
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:101" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>475</v>
       </c>
@@ -8915,1374 +8958,1374 @@
       <c r="AJ39" t="s">
         <v>4</v>
       </c>
-      <c r="AT39">
+      <c r="AV39">
         <v>20</v>
       </c>
-      <c r="BB39">
-        <v>1</v>
-      </c>
-      <c r="BQ39">
+      <c r="BD39">
+        <v>1</v>
+      </c>
+      <c r="BS39">
         <v>0.1</v>
       </c>
-      <c r="CL39" s="12" t="s">
+      <c r="CN39" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="CP39">
+      <c r="CR39">
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:101" x14ac:dyDescent="0.25">
-      <c r="CJ42" s="9"/>
-    </row>
-    <row r="43" spans="1:101" x14ac:dyDescent="0.25">
-      <c r="CJ43" s="9"/>
-    </row>
-    <row r="49" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ49" s="9"/>
-    </row>
-    <row r="50" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ50" s="9"/>
-    </row>
-    <row r="52" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ52" s="9"/>
-    </row>
-    <row r="53" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ53" s="9"/>
-    </row>
-    <row r="54" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ54" s="9"/>
-    </row>
-    <row r="55" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ55" s="9"/>
-    </row>
-    <row r="56" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT56"/>
-    </row>
-    <row r="57" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT57"/>
-    </row>
-    <row r="58" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT58"/>
-      <c r="CJ58" s="9"/>
-    </row>
-    <row r="59" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ59" s="9"/>
-    </row>
-    <row r="60" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ60" s="9"/>
-    </row>
-    <row r="61" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT61"/>
-    </row>
-    <row r="62" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ62" s="9"/>
-    </row>
-    <row r="66" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT66"/>
-    </row>
-    <row r="67" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ67" s="9"/>
-    </row>
-    <row r="75" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ75" s="9"/>
-    </row>
-    <row r="76" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ76" s="9"/>
-    </row>
-    <row r="77" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT77"/>
-    </row>
-    <row r="82" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT82"/>
-    </row>
-    <row r="83" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT83"/>
-      <c r="CJ83" s="9"/>
-    </row>
-    <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ84" s="9"/>
-    </row>
-    <row r="85" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ85" s="9"/>
-    </row>
-    <row r="86" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ86" s="9"/>
-    </row>
-    <row r="87" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ87" s="9"/>
-    </row>
-    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT88"/>
-    </row>
-    <row r="89" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ89" s="9"/>
-    </row>
-    <row r="90" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ90" s="9"/>
-    </row>
-    <row r="91" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ91" s="9"/>
-    </row>
-    <row r="92" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ92" s="9"/>
-    </row>
-    <row r="93" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT93"/>
-    </row>
-    <row r="94" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ94" s="9"/>
-    </row>
-    <row r="95" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ95" s="9"/>
-    </row>
-    <row r="96" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ96" s="9"/>
-    </row>
-    <row r="97" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ97" s="9"/>
-    </row>
-    <row r="100" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ100" s="9"/>
-    </row>
-    <row r="101" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ101" s="9"/>
-    </row>
-    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="9"/>
-    </row>
-    <row r="103" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ103" s="9"/>
-    </row>
-    <row r="104" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ104" s="9"/>
-    </row>
-    <row r="106" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT106"/>
-    </row>
-    <row r="107" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ107" s="9"/>
-    </row>
-    <row r="108" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ108" s="9"/>
-    </row>
-    <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ109" s="9"/>
-    </row>
-    <row r="110" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ110" s="9"/>
-    </row>
-    <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ114" s="9"/>
-    </row>
-    <row r="116" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT116"/>
-    </row>
-    <row r="117" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT117"/>
-      <c r="CJ117" s="9"/>
-    </row>
-    <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ118" s="9"/>
-    </row>
-    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="9"/>
-    </row>
-    <row r="120" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ120" s="9"/>
-    </row>
-    <row r="121" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ121" s="9"/>
-    </row>
-    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT123"/>
-    </row>
-    <row r="124" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ124" s="9"/>
-    </row>
-    <row r="125" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ125" s="9"/>
-    </row>
-    <row r="127" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ127" s="9"/>
-    </row>
-    <row r="128" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ128" s="9"/>
-    </row>
-    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT130"/>
-    </row>
-    <row r="131" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ131" s="9"/>
-    </row>
-    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ134" s="9"/>
-    </row>
-    <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ135" s="9"/>
-    </row>
-    <row r="138" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ138" s="9"/>
-    </row>
-    <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ140" s="9"/>
-    </row>
-    <row r="142" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT142"/>
-    </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ143" s="9"/>
-    </row>
-    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ144" s="9"/>
-    </row>
-    <row r="146" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ146" s="9"/>
-    </row>
-    <row r="147" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ147" s="9"/>
-    </row>
-    <row r="148" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ148" s="9"/>
-    </row>
-    <row r="153" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ153" s="9"/>
-    </row>
-    <row r="154" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ154" s="9"/>
-    </row>
-    <row r="157" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ157" s="9"/>
-    </row>
-    <row r="158" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ158" s="9"/>
-    </row>
-    <row r="162" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ162" s="9"/>
-    </row>
-    <row r="166" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ166" s="9"/>
-    </row>
-    <row r="168" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ168" s="9"/>
-    </row>
-    <row r="169" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ169" s="9"/>
-    </row>
-    <row r="171" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="9"/>
-    </row>
-    <row r="172" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ172" s="9"/>
-    </row>
-    <row r="174" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT174"/>
-    </row>
-    <row r="175" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT175"/>
-      <c r="CJ175" s="9"/>
-    </row>
-    <row r="176" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ176" s="9"/>
-    </row>
-    <row r="178" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ178" s="9"/>
-    </row>
-    <row r="187" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT187"/>
-    </row>
-    <row r="188" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT188"/>
-      <c r="CJ188" s="9"/>
-    </row>
-    <row r="189" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ189" s="9"/>
-    </row>
-    <row r="190" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ190" s="9"/>
-    </row>
-    <row r="191" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT191"/>
-    </row>
-    <row r="192" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT192"/>
-      <c r="CJ192" s="9"/>
-    </row>
-    <row r="193" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ193" s="9"/>
-    </row>
-    <row r="195" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT195"/>
-    </row>
-    <row r="196" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT196"/>
-      <c r="CJ196" s="9"/>
-    </row>
-    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ197" s="9"/>
-    </row>
-    <row r="199" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT199"/>
-    </row>
-    <row r="200" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ200" s="9"/>
-    </row>
-    <row r="203" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ203" s="9"/>
-    </row>
-    <row r="207" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ207" s="9"/>
-    </row>
-    <row r="209" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT209"/>
-    </row>
-    <row r="210" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ210" s="9"/>
-    </row>
-    <row r="217" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT217"/>
-    </row>
-    <row r="218" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ218" s="9"/>
-    </row>
-    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ219" s="9"/>
-    </row>
-    <row r="221" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT221"/>
-    </row>
-    <row r="222" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT222"/>
-      <c r="CJ222" s="9"/>
-    </row>
-    <row r="223" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ223" s="9"/>
-    </row>
-    <row r="229" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT229"/>
-    </row>
-    <row r="230" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT230"/>
-      <c r="CJ230" s="9"/>
-    </row>
-    <row r="231" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT231"/>
-      <c r="CJ231" s="9"/>
-    </row>
-    <row r="232" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ232" s="9"/>
-    </row>
-    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT237"/>
-    </row>
-    <row r="238" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT238"/>
-    </row>
-    <row r="242" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT242"/>
-    </row>
-    <row r="243" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ243" s="9"/>
-    </row>
-    <row r="244" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT244"/>
-    </row>
-    <row r="245" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ245" s="9"/>
-    </row>
-    <row r="255" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT255"/>
-    </row>
-    <row r="256" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ256" s="9"/>
-    </row>
-    <row r="258" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT258"/>
-    </row>
-    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ259" s="9"/>
-    </row>
-    <row r="267" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT267"/>
-    </row>
-    <row r="268" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ268" s="9"/>
-    </row>
-    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT272"/>
-    </row>
-    <row r="273" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ273" s="9"/>
-    </row>
-    <row r="275" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT275"/>
-    </row>
-    <row r="276" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ276" s="9"/>
-    </row>
-    <row r="292" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT292"/>
-    </row>
-    <row r="293" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT293"/>
-      <c r="CJ293" s="9"/>
-    </row>
-    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT294"/>
-      <c r="CJ294" s="9"/>
-    </row>
-    <row r="295" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT295"/>
-      <c r="CJ295" s="9"/>
-    </row>
-    <row r="296" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT296"/>
-    </row>
-    <row r="298" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT298"/>
-    </row>
-    <row r="299" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT299"/>
-      <c r="CJ299" s="9"/>
-    </row>
-    <row r="300" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT300"/>
-      <c r="CJ300" s="9"/>
-    </row>
-    <row r="301" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ301" s="9"/>
-    </row>
-    <row r="305" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT305"/>
-    </row>
-    <row r="306" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ306" s="9"/>
-    </row>
-    <row r="308" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT308"/>
-    </row>
-    <row r="309" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT309"/>
-      <c r="CJ309" s="9"/>
-    </row>
-    <row r="310" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT310"/>
-      <c r="CJ310" s="9"/>
-    </row>
-    <row r="311" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ311" s="9"/>
-    </row>
-    <row r="327" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT327"/>
-    </row>
-    <row r="328" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ328" s="9"/>
-    </row>
-    <row r="336" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ336" s="9"/>
-    </row>
-    <row r="337" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ337" s="9"/>
-    </row>
-    <row r="338" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ338" s="9"/>
-    </row>
-    <row r="339" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ339" s="9"/>
-    </row>
-    <row r="340" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ340" s="9"/>
-    </row>
-    <row r="342" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT342"/>
-    </row>
-    <row r="343" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ343" s="9"/>
-    </row>
-    <row r="344" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT344"/>
-    </row>
-    <row r="345" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT345"/>
-      <c r="CJ345" s="9"/>
-    </row>
-    <row r="346" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ346" s="9"/>
-    </row>
-    <row r="348" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT348"/>
-    </row>
-    <row r="349" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT349"/>
-      <c r="CJ349" s="9"/>
-    </row>
-    <row r="350" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT350"/>
-      <c r="CJ350" s="9"/>
-    </row>
-    <row r="351" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ351" s="9"/>
-    </row>
-    <row r="353" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ353" s="9"/>
-    </row>
-    <row r="355" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ355" s="9"/>
-    </row>
-    <row r="357" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ357" s="9"/>
-    </row>
-    <row r="360" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ360" s="9"/>
-    </row>
-    <row r="361" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ361" s="9"/>
-    </row>
-    <row r="362" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ362" s="9"/>
-    </row>
-    <row r="363" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ363" s="9"/>
-    </row>
-    <row r="364" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ364" s="9"/>
-    </row>
-    <row r="365" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ365" s="9"/>
-    </row>
-    <row r="366" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT366"/>
-    </row>
-    <row r="367" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT367"/>
-      <c r="CJ367" s="9"/>
-    </row>
-    <row r="368" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT368"/>
-      <c r="CJ368" s="9"/>
-    </row>
-    <row r="369" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ369" s="9"/>
-    </row>
-    <row r="370" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ370" s="9"/>
-    </row>
-    <row r="371" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ371" s="9"/>
-    </row>
-    <row r="372" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ372" s="9"/>
-    </row>
-    <row r="374" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ374" s="9"/>
-    </row>
-    <row r="375" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ375" s="9"/>
-    </row>
-    <row r="376" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT376"/>
-    </row>
-    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT377"/>
-      <c r="CJ377" s="9"/>
-    </row>
-    <row r="378" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT378"/>
-      <c r="CJ378" s="9"/>
-    </row>
-    <row r="379" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ379" s="9"/>
-    </row>
-    <row r="380" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ380" s="9"/>
-    </row>
-    <row r="382" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ382" s="9"/>
-    </row>
-    <row r="383" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ383" s="9"/>
-    </row>
-    <row r="384" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT384"/>
-      <c r="CJ384" s="9"/>
-    </row>
-    <row r="385" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT385"/>
-      <c r="CJ385" s="9"/>
-    </row>
-    <row r="386" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ386" s="9"/>
-    </row>
-    <row r="387" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ387" s="9"/>
-    </row>
-    <row r="388" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ388" s="9"/>
-    </row>
-    <row r="390" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT390"/>
-      <c r="CJ390" s="9"/>
-    </row>
-    <row r="391" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ391" s="9"/>
-    </row>
-    <row r="392" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ392" s="9"/>
-    </row>
-    <row r="394" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT394"/>
-      <c r="CJ394" s="9"/>
-    </row>
-    <row r="395" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT395"/>
-      <c r="CJ395" s="9"/>
-    </row>
-    <row r="396" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ396" s="9"/>
-    </row>
-    <row r="398" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ398" s="9"/>
-    </row>
-    <row r="400" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ400" s="9"/>
-    </row>
-    <row r="403" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ403" s="9"/>
-    </row>
-    <row r="404" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ404" s="9"/>
-    </row>
-    <row r="408" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT408"/>
-    </row>
-    <row r="409" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT409"/>
-      <c r="CJ409" s="9"/>
-    </row>
-    <row r="410" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT410"/>
-      <c r="CJ410" s="9"/>
-    </row>
-    <row r="411" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ411" s="9"/>
-    </row>
-    <row r="412" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ412" s="9"/>
-    </row>
-    <row r="413" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT413"/>
-    </row>
-    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ414" s="9"/>
-    </row>
-    <row r="416" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ416" s="9"/>
-    </row>
-    <row r="417" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ417" s="9"/>
-    </row>
-    <row r="419" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ419" s="9"/>
-    </row>
-    <row r="420" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ420" s="9"/>
-    </row>
-    <row r="421" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ421" s="9"/>
-    </row>
-    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ422" s="9"/>
-    </row>
-    <row r="423" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ423" s="9"/>
-    </row>
-    <row r="424" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ424" s="9"/>
-    </row>
-    <row r="425" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ425" s="9"/>
-    </row>
-    <row r="427" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT427"/>
-    </row>
-    <row r="428" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ428" s="9"/>
-    </row>
-    <row r="429" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ429" s="9"/>
-    </row>
-    <row r="462" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS462" s="4"/>
-      <c r="BT462" s="16"/>
-    </row>
-    <row r="463" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="CL42" s="9"/>
+    </row>
+    <row r="43" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="CL43" s="9"/>
+    </row>
+    <row r="49" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL49" s="9"/>
+    </row>
+    <row r="50" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL50" s="9"/>
+    </row>
+    <row r="52" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL52" s="9"/>
+    </row>
+    <row r="53" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL53" s="9"/>
+    </row>
+    <row r="54" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL54" s="9"/>
+    </row>
+    <row r="55" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL55" s="9"/>
+    </row>
+    <row r="56" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV56"/>
+    </row>
+    <row r="57" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV57"/>
+    </row>
+    <row r="58" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV58"/>
+      <c r="CL58" s="9"/>
+    </row>
+    <row r="59" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL59" s="9"/>
+    </row>
+    <row r="60" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL60" s="9"/>
+    </row>
+    <row r="61" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV61"/>
+    </row>
+    <row r="62" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL62" s="9"/>
+    </row>
+    <row r="66" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV66"/>
+    </row>
+    <row r="67" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL67" s="9"/>
+    </row>
+    <row r="75" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL75" s="9"/>
+    </row>
+    <row r="76" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL76" s="9"/>
+    </row>
+    <row r="77" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV77"/>
+    </row>
+    <row r="82" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV82"/>
+    </row>
+    <row r="83" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV83"/>
+      <c r="CL83" s="9"/>
+    </row>
+    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL84" s="9"/>
+    </row>
+    <row r="85" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL85" s="9"/>
+    </row>
+    <row r="86" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL86" s="9"/>
+    </row>
+    <row r="87" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL87" s="9"/>
+    </row>
+    <row r="88" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV88"/>
+    </row>
+    <row r="89" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL89" s="9"/>
+    </row>
+    <row r="90" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL90" s="9"/>
+    </row>
+    <row r="91" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL91" s="9"/>
+    </row>
+    <row r="92" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL92" s="9"/>
+    </row>
+    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV93"/>
+    </row>
+    <row r="94" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL94" s="9"/>
+    </row>
+    <row r="95" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL95" s="9"/>
+    </row>
+    <row r="96" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL96" s="9"/>
+    </row>
+    <row r="97" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL97" s="9"/>
+    </row>
+    <row r="100" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL100" s="9"/>
+    </row>
+    <row r="101" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL101" s="9"/>
+    </row>
+    <row r="102" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL102" s="9"/>
+    </row>
+    <row r="103" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL103" s="9"/>
+    </row>
+    <row r="104" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL104" s="9"/>
+    </row>
+    <row r="106" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV106"/>
+    </row>
+    <row r="107" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL107" s="9"/>
+    </row>
+    <row r="108" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL108" s="9"/>
+    </row>
+    <row r="109" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL109" s="9"/>
+    </row>
+    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL110" s="9"/>
+    </row>
+    <row r="114" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL114" s="9"/>
+    </row>
+    <row r="116" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV116"/>
+    </row>
+    <row r="117" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV117"/>
+      <c r="CL117" s="9"/>
+    </row>
+    <row r="118" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL118" s="9"/>
+    </row>
+    <row r="119" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL119" s="9"/>
+    </row>
+    <row r="120" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL120" s="9"/>
+    </row>
+    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL121" s="9"/>
+    </row>
+    <row r="123" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV123"/>
+    </row>
+    <row r="124" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL124" s="9"/>
+    </row>
+    <row r="125" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL125" s="9"/>
+    </row>
+    <row r="127" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL127" s="9"/>
+    </row>
+    <row r="128" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL128" s="9"/>
+    </row>
+    <row r="130" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV130"/>
+    </row>
+    <row r="131" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL131" s="9"/>
+    </row>
+    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL134" s="9"/>
+    </row>
+    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL135" s="9"/>
+    </row>
+    <row r="138" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL138" s="9"/>
+    </row>
+    <row r="140" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL140" s="9"/>
+    </row>
+    <row r="142" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV142"/>
+    </row>
+    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL143" s="9"/>
+    </row>
+    <row r="144" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL144" s="9"/>
+    </row>
+    <row r="146" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL146" s="9"/>
+    </row>
+    <row r="147" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL147" s="9"/>
+    </row>
+    <row r="148" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL148" s="9"/>
+    </row>
+    <row r="153" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL153" s="9"/>
+    </row>
+    <row r="154" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL154" s="9"/>
+    </row>
+    <row r="157" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL157" s="9"/>
+    </row>
+    <row r="158" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL158" s="9"/>
+    </row>
+    <row r="162" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL162" s="9"/>
+    </row>
+    <row r="166" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL166" s="9"/>
+    </row>
+    <row r="168" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL168" s="9"/>
+    </row>
+    <row r="169" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL169" s="9"/>
+    </row>
+    <row r="171" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL171" s="9"/>
+    </row>
+    <row r="172" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL172" s="9"/>
+    </row>
+    <row r="174" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV174"/>
+    </row>
+    <row r="175" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV175"/>
+      <c r="CL175" s="9"/>
+    </row>
+    <row r="176" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL176" s="9"/>
+    </row>
+    <row r="178" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL178" s="9"/>
+    </row>
+    <row r="187" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV187"/>
+    </row>
+    <row r="188" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV188"/>
+      <c r="CL188" s="9"/>
+    </row>
+    <row r="189" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL189" s="9"/>
+    </row>
+    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL190" s="9"/>
+    </row>
+    <row r="191" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV191"/>
+    </row>
+    <row r="192" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV192"/>
+      <c r="CL192" s="9"/>
+    </row>
+    <row r="193" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL193" s="9"/>
+    </row>
+    <row r="195" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV195"/>
+    </row>
+    <row r="196" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV196"/>
+      <c r="CL196" s="9"/>
+    </row>
+    <row r="197" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL197" s="9"/>
+    </row>
+    <row r="199" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV199"/>
+    </row>
+    <row r="200" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL200" s="9"/>
+    </row>
+    <row r="203" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL203" s="9"/>
+    </row>
+    <row r="207" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL207" s="9"/>
+    </row>
+    <row r="209" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV209"/>
+    </row>
+    <row r="210" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL210" s="9"/>
+    </row>
+    <row r="217" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV217"/>
+    </row>
+    <row r="218" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL218" s="9"/>
+    </row>
+    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL219" s="9"/>
+    </row>
+    <row r="221" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV221"/>
+    </row>
+    <row r="222" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV222"/>
+      <c r="CL222" s="9"/>
+    </row>
+    <row r="223" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL223" s="9"/>
+    </row>
+    <row r="229" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV229"/>
+    </row>
+    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV230"/>
+      <c r="CL230" s="9"/>
+    </row>
+    <row r="231" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV231"/>
+      <c r="CL231" s="9"/>
+    </row>
+    <row r="232" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL232" s="9"/>
+    </row>
+    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV237"/>
+    </row>
+    <row r="238" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV238"/>
+    </row>
+    <row r="242" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV242"/>
+    </row>
+    <row r="243" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL243" s="9"/>
+    </row>
+    <row r="244" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV244"/>
+    </row>
+    <row r="245" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL245" s="9"/>
+    </row>
+    <row r="255" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV255"/>
+    </row>
+    <row r="256" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL256" s="9"/>
+    </row>
+    <row r="258" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV258"/>
+    </row>
+    <row r="259" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL259" s="9"/>
+    </row>
+    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV267"/>
+    </row>
+    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL268" s="9"/>
+    </row>
+    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV272"/>
+    </row>
+    <row r="273" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL273" s="9"/>
+    </row>
+    <row r="275" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV275"/>
+    </row>
+    <row r="276" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL276" s="9"/>
+    </row>
+    <row r="292" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV292"/>
+    </row>
+    <row r="293" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV293"/>
+      <c r="CL293" s="9"/>
+    </row>
+    <row r="294" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV294"/>
+      <c r="CL294" s="9"/>
+    </row>
+    <row r="295" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV295"/>
+      <c r="CL295" s="9"/>
+    </row>
+    <row r="296" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV296"/>
+    </row>
+    <row r="298" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV298"/>
+    </row>
+    <row r="299" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV299"/>
+      <c r="CL299" s="9"/>
+    </row>
+    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV300"/>
+      <c r="CL300" s="9"/>
+    </row>
+    <row r="301" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL301" s="9"/>
+    </row>
+    <row r="305" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV305"/>
+    </row>
+    <row r="306" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL306" s="9"/>
+    </row>
+    <row r="308" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV308"/>
+    </row>
+    <row r="309" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV309"/>
+      <c r="CL309" s="9"/>
+    </row>
+    <row r="310" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV310"/>
+      <c r="CL310" s="9"/>
+    </row>
+    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL311" s="9"/>
+    </row>
+    <row r="327" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV327"/>
+    </row>
+    <row r="328" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL328" s="9"/>
+    </row>
+    <row r="336" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL336" s="9"/>
+    </row>
+    <row r="337" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL337" s="9"/>
+    </row>
+    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL338" s="9"/>
+    </row>
+    <row r="339" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL339" s="9"/>
+    </row>
+    <row r="340" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL340" s="9"/>
+    </row>
+    <row r="342" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV342"/>
+    </row>
+    <row r="343" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL343" s="9"/>
+    </row>
+    <row r="344" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV344"/>
+    </row>
+    <row r="345" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV345"/>
+      <c r="CL345" s="9"/>
+    </row>
+    <row r="346" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL346" s="9"/>
+    </row>
+    <row r="348" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV348"/>
+    </row>
+    <row r="349" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV349"/>
+      <c r="CL349" s="9"/>
+    </row>
+    <row r="350" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV350"/>
+      <c r="CL350" s="9"/>
+    </row>
+    <row r="351" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL351" s="9"/>
+    </row>
+    <row r="353" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL353" s="9"/>
+    </row>
+    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL355" s="9"/>
+    </row>
+    <row r="357" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL357" s="9"/>
+    </row>
+    <row r="360" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL360" s="9"/>
+    </row>
+    <row r="361" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL361" s="9"/>
+    </row>
+    <row r="362" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL362" s="9"/>
+    </row>
+    <row r="363" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL363" s="9"/>
+    </row>
+    <row r="364" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL364" s="9"/>
+    </row>
+    <row r="365" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL365" s="9"/>
+    </row>
+    <row r="366" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV366"/>
+    </row>
+    <row r="367" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV367"/>
+      <c r="CL367" s="9"/>
+    </row>
+    <row r="368" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV368"/>
+      <c r="CL368" s="9"/>
+    </row>
+    <row r="369" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL369" s="9"/>
+    </row>
+    <row r="370" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL370" s="9"/>
+    </row>
+    <row r="371" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL371" s="9"/>
+    </row>
+    <row r="372" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL372" s="9"/>
+    </row>
+    <row r="374" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL374" s="9"/>
+    </row>
+    <row r="375" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL375" s="9"/>
+    </row>
+    <row r="376" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV376"/>
+    </row>
+    <row r="377" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV377"/>
+      <c r="CL377" s="9"/>
+    </row>
+    <row r="378" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV378"/>
+      <c r="CL378" s="9"/>
+    </row>
+    <row r="379" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL379" s="9"/>
+    </row>
+    <row r="380" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL380" s="9"/>
+    </row>
+    <row r="382" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL382" s="9"/>
+    </row>
+    <row r="383" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL383" s="9"/>
+    </row>
+    <row r="384" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV384"/>
+      <c r="CL384" s="9"/>
+    </row>
+    <row r="385" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV385"/>
+      <c r="CL385" s="9"/>
+    </row>
+    <row r="386" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL386" s="9"/>
+    </row>
+    <row r="387" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL387" s="9"/>
+    </row>
+    <row r="388" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL388" s="9"/>
+    </row>
+    <row r="390" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV390"/>
+      <c r="CL390" s="9"/>
+    </row>
+    <row r="391" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL391" s="9"/>
+    </row>
+    <row r="392" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL392" s="9"/>
+    </row>
+    <row r="394" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV394"/>
+      <c r="CL394" s="9"/>
+    </row>
+    <row r="395" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV395"/>
+      <c r="CL395" s="9"/>
+    </row>
+    <row r="396" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL396" s="9"/>
+    </row>
+    <row r="398" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL398" s="9"/>
+    </row>
+    <row r="400" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL400" s="9"/>
+    </row>
+    <row r="403" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL403" s="9"/>
+    </row>
+    <row r="404" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL404" s="9"/>
+    </row>
+    <row r="408" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV408"/>
+    </row>
+    <row r="409" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV409"/>
+      <c r="CL409" s="9"/>
+    </row>
+    <row r="410" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV410"/>
+      <c r="CL410" s="9"/>
+    </row>
+    <row r="411" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL411" s="9"/>
+    </row>
+    <row r="412" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL412" s="9"/>
+    </row>
+    <row r="413" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV413"/>
+    </row>
+    <row r="414" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL414" s="9"/>
+    </row>
+    <row r="416" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL416" s="9"/>
+    </row>
+    <row r="417" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL417" s="9"/>
+    </row>
+    <row r="419" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL419" s="9"/>
+    </row>
+    <row r="420" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL420" s="9"/>
+    </row>
+    <row r="421" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL421" s="9"/>
+    </row>
+    <row r="422" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL422" s="9"/>
+    </row>
+    <row r="423" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL423" s="9"/>
+    </row>
+    <row r="424" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL424" s="9"/>
+    </row>
+    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL425" s="9"/>
+    </row>
+    <row r="427" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV427"/>
+    </row>
+    <row r="428" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL428" s="9"/>
+    </row>
+    <row r="429" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL429" s="9"/>
+    </row>
+    <row r="462" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU462" s="4"/>
+      <c r="BV462" s="16"/>
+    </row>
+    <row r="463" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H463" s="4"/>
-      <c r="CJ463" s="4"/>
-    </row>
-    <row r="469" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT469"/>
-    </row>
-    <row r="470" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT470"/>
-      <c r="CJ470" s="9"/>
-    </row>
-    <row r="471" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT471"/>
-      <c r="CJ471" s="9"/>
-    </row>
-    <row r="472" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ472" s="9"/>
-    </row>
-    <row r="489" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT489"/>
-    </row>
-    <row r="490" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ490" s="9"/>
-    </row>
-    <row r="522" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT522"/>
-    </row>
-    <row r="523" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT523"/>
-      <c r="CJ523" s="9"/>
-    </row>
-    <row r="524" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ524" s="9"/>
-    </row>
-    <row r="540" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT540"/>
-    </row>
-    <row r="541" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ541" s="9"/>
-    </row>
-    <row r="547" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT547"/>
-    </row>
-    <row r="548" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT548"/>
-      <c r="CJ548" s="9"/>
-    </row>
-    <row r="549" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ549" s="9"/>
-    </row>
-    <row r="554" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT554"/>
-    </row>
-    <row r="555" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT555"/>
-      <c r="CJ555" s="9"/>
-    </row>
-    <row r="556" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT556"/>
-      <c r="CJ556" s="9"/>
-    </row>
-    <row r="557" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT557"/>
-      <c r="CJ557" s="9"/>
-    </row>
-    <row r="558" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT558"/>
-      <c r="CJ558" s="9"/>
-    </row>
-    <row r="559" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT559"/>
-      <c r="CJ559" s="9"/>
-    </row>
-    <row r="560" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT560"/>
-      <c r="CJ560" s="9"/>
-    </row>
-    <row r="561" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT561"/>
-      <c r="CJ561" s="9"/>
-    </row>
-    <row r="562" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT562"/>
-      <c r="CJ562" s="9"/>
-    </row>
-    <row r="563" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT563"/>
-      <c r="CJ563" s="9"/>
-    </row>
-    <row r="564" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT564"/>
-      <c r="CJ564" s="9"/>
-    </row>
-    <row r="565" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT565"/>
-      <c r="CJ565" s="9"/>
-    </row>
-    <row r="566" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT566"/>
-      <c r="CJ566" s="9"/>
-    </row>
-    <row r="567" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT567"/>
-      <c r="CJ567" s="9"/>
-    </row>
-    <row r="568" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT568"/>
-      <c r="CJ568" s="9"/>
-    </row>
-    <row r="569" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT569"/>
-      <c r="CJ569" s="9"/>
-    </row>
-    <row r="570" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ570" s="9"/>
-    </row>
-    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT574"/>
-    </row>
-    <row r="575" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT575"/>
-      <c r="CJ575" s="9"/>
-    </row>
-    <row r="576" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ576" s="9"/>
-    </row>
-    <row r="577" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT577"/>
-    </row>
-    <row r="578" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ578" s="9"/>
-    </row>
-    <row r="581" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT581"/>
-    </row>
-    <row r="582" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT582"/>
-      <c r="CJ582" s="9"/>
-    </row>
-    <row r="583" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ583" s="9"/>
-    </row>
-    <row r="614" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT614"/>
-    </row>
-    <row r="615" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT615"/>
-      <c r="CJ615" s="9"/>
-    </row>
-    <row r="616" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT616"/>
-      <c r="CJ616" s="9"/>
-    </row>
-    <row r="617" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT617"/>
-      <c r="CJ617" s="9"/>
-    </row>
-    <row r="618" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT618"/>
-      <c r="CJ618" s="9"/>
-    </row>
-    <row r="619" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT619"/>
-      <c r="CJ619" s="9"/>
-    </row>
-    <row r="620" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT620"/>
-      <c r="CJ620" s="9"/>
-    </row>
-    <row r="621" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT621"/>
-      <c r="CJ621" s="9"/>
-    </row>
-    <row r="622" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ622" s="9"/>
-    </row>
-    <row r="624" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT624"/>
-    </row>
-    <row r="625" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ625" s="9"/>
-    </row>
-    <row r="629" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT629"/>
-    </row>
-    <row r="630" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ630" s="9"/>
-    </row>
-    <row r="633" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT633"/>
-    </row>
-    <row r="634" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT634"/>
-      <c r="CJ634" s="9"/>
-    </row>
-    <row r="635" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT635"/>
-      <c r="CJ635" s="9"/>
-    </row>
-    <row r="636" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT636"/>
-      <c r="CJ636" s="9"/>
-    </row>
-    <row r="637" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ637" s="9"/>
-    </row>
-    <row r="644" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT644"/>
-    </row>
-    <row r="645" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ645" s="9"/>
-    </row>
-    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT648"/>
-    </row>
-    <row r="649" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT649"/>
-      <c r="CJ649" s="9"/>
-    </row>
-    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT650"/>
-      <c r="CJ650" s="9"/>
-    </row>
-    <row r="651" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT651"/>
-      <c r="CJ651" s="9"/>
-    </row>
-    <row r="652" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ652" s="9"/>
-    </row>
-    <row r="654" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT654"/>
-    </row>
-    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT655"/>
-      <c r="CJ655" s="9"/>
-    </row>
-    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ656" s="9"/>
-    </row>
-    <row r="657" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ657">
+      <c r="CL463" s="4"/>
+    </row>
+    <row r="469" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV469"/>
+    </row>
+    <row r="470" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV470"/>
+      <c r="CL470" s="9"/>
+    </row>
+    <row r="471" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV471"/>
+      <c r="CL471" s="9"/>
+    </row>
+    <row r="472" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL472" s="9"/>
+    </row>
+    <row r="489" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV489"/>
+    </row>
+    <row r="490" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL490" s="9"/>
+    </row>
+    <row r="522" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV522"/>
+    </row>
+    <row r="523" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV523"/>
+      <c r="CL523" s="9"/>
+    </row>
+    <row r="524" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL524" s="9"/>
+    </row>
+    <row r="540" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV540"/>
+    </row>
+    <row r="541" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL541" s="9"/>
+    </row>
+    <row r="547" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV547"/>
+    </row>
+    <row r="548" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV548"/>
+      <c r="CL548" s="9"/>
+    </row>
+    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL549" s="9"/>
+    </row>
+    <row r="554" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV554"/>
+    </row>
+    <row r="555" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV555"/>
+      <c r="CL555" s="9"/>
+    </row>
+    <row r="556" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV556"/>
+      <c r="CL556" s="9"/>
+    </row>
+    <row r="557" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV557"/>
+      <c r="CL557" s="9"/>
+    </row>
+    <row r="558" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV558"/>
+      <c r="CL558" s="9"/>
+    </row>
+    <row r="559" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV559"/>
+      <c r="CL559" s="9"/>
+    </row>
+    <row r="560" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV560"/>
+      <c r="CL560" s="9"/>
+    </row>
+    <row r="561" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV561"/>
+      <c r="CL561" s="9"/>
+    </row>
+    <row r="562" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV562"/>
+      <c r="CL562" s="9"/>
+    </row>
+    <row r="563" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV563"/>
+      <c r="CL563" s="9"/>
+    </row>
+    <row r="564" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV564"/>
+      <c r="CL564" s="9"/>
+    </row>
+    <row r="565" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV565"/>
+      <c r="CL565" s="9"/>
+    </row>
+    <row r="566" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV566"/>
+      <c r="CL566" s="9"/>
+    </row>
+    <row r="567" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV567"/>
+      <c r="CL567" s="9"/>
+    </row>
+    <row r="568" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV568"/>
+      <c r="CL568" s="9"/>
+    </row>
+    <row r="569" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV569"/>
+      <c r="CL569" s="9"/>
+    </row>
+    <row r="570" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL570" s="9"/>
+    </row>
+    <row r="574" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV574"/>
+    </row>
+    <row r="575" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV575"/>
+      <c r="CL575" s="9"/>
+    </row>
+    <row r="576" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL576" s="9"/>
+    </row>
+    <row r="577" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV577"/>
+    </row>
+    <row r="578" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL578" s="9"/>
+    </row>
+    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV581"/>
+    </row>
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV582"/>
+      <c r="CL582" s="9"/>
+    </row>
+    <row r="583" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL583" s="9"/>
+    </row>
+    <row r="614" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV614"/>
+    </row>
+    <row r="615" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV615"/>
+      <c r="CL615" s="9"/>
+    </row>
+    <row r="616" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV616"/>
+      <c r="CL616" s="9"/>
+    </row>
+    <row r="617" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV617"/>
+      <c r="CL617" s="9"/>
+    </row>
+    <row r="618" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV618"/>
+      <c r="CL618" s="9"/>
+    </row>
+    <row r="619" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV619"/>
+      <c r="CL619" s="9"/>
+    </row>
+    <row r="620" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV620"/>
+      <c r="CL620" s="9"/>
+    </row>
+    <row r="621" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV621"/>
+      <c r="CL621" s="9"/>
+    </row>
+    <row r="622" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL622" s="9"/>
+    </row>
+    <row r="624" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV624"/>
+    </row>
+    <row r="625" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL625" s="9"/>
+    </row>
+    <row r="629" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV629"/>
+    </row>
+    <row r="630" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL630" s="9"/>
+    </row>
+    <row r="633" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV633"/>
+    </row>
+    <row r="634" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV634"/>
+      <c r="CL634" s="9"/>
+    </row>
+    <row r="635" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV635"/>
+      <c r="CL635" s="9"/>
+    </row>
+    <row r="636" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV636"/>
+      <c r="CL636" s="9"/>
+    </row>
+    <row r="637" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL637" s="9"/>
+    </row>
+    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV644"/>
+    </row>
+    <row r="645" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL645" s="9"/>
+    </row>
+    <row r="648" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV648"/>
+    </row>
+    <row r="649" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV649"/>
+      <c r="CL649" s="9"/>
+    </row>
+    <row r="650" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV650"/>
+      <c r="CL650" s="9"/>
+    </row>
+    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV651"/>
+      <c r="CL651" s="9"/>
+    </row>
+    <row r="652" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL652" s="9"/>
+    </row>
+    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV654"/>
+    </row>
+    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV655"/>
+      <c r="CL655" s="9"/>
+    </row>
+    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL656" s="9"/>
+    </row>
+    <row r="657" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL657">
         <v>0.15</v>
       </c>
     </row>
-    <row r="659" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ659">
+    <row r="659" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL659">
         <v>0.2</v>
       </c>
     </row>
-    <row r="660" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ660">
+    <row r="660" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL660">
         <v>0.1</v>
       </c>
     </row>
-    <row r="662" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ662">
+    <row r="662" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL662">
         <v>0.2</v>
       </c>
     </row>
-    <row r="669" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ669">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="671" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ671">
+    <row r="669" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL669">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL671">
         <v>0.4</v>
       </c>
     </row>
-    <row r="672" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ672">
+    <row r="672" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL672">
         <v>0.6</v>
       </c>
     </row>
-    <row r="675" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ675">
+    <row r="675" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL675">
         <v>0.5</v>
       </c>
     </row>
-    <row r="676" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ676">
+    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL676">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ677">
+    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL677">
         <v>0.2</v>
       </c>
     </row>
-    <row r="680" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT680"/>
-    </row>
-    <row r="681" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT681"/>
-      <c r="CJ681" s="9"/>
-    </row>
-    <row r="682" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT682"/>
-      <c r="CJ682" s="9"/>
-    </row>
-    <row r="683" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT683"/>
-      <c r="CJ683" s="9"/>
-    </row>
-    <row r="684" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT684"/>
-      <c r="CJ684" s="9"/>
-    </row>
-    <row r="685" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT685"/>
-      <c r="CJ685" s="9"/>
-    </row>
-    <row r="686" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT686"/>
-      <c r="CJ686" s="9"/>
-    </row>
-    <row r="687" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT687"/>
-      <c r="CJ687" s="9"/>
-    </row>
-    <row r="688" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT688"/>
-      <c r="CJ688" s="9"/>
-    </row>
-    <row r="689" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ689" s="9"/>
-    </row>
-    <row r="690" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT690"/>
-    </row>
-    <row r="691" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ691" s="9"/>
-    </row>
-    <row r="700" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT700"/>
-    </row>
-    <row r="701" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT701"/>
-      <c r="CJ701" s="9"/>
-    </row>
-    <row r="702" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT702"/>
-      <c r="CJ702" s="9"/>
-    </row>
-    <row r="703" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT703"/>
-      <c r="CJ703" s="9"/>
-    </row>
-    <row r="704" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT704"/>
-      <c r="CJ704" s="9"/>
-    </row>
-    <row r="705" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT705"/>
-      <c r="CJ705" s="9"/>
-    </row>
-    <row r="706" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT706"/>
-      <c r="CJ706" s="9"/>
-    </row>
-    <row r="707" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT707"/>
-      <c r="CJ707" s="9"/>
-    </row>
-    <row r="708" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ708" s="9"/>
-    </row>
-    <row r="709" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT709"/>
-    </row>
-    <row r="710" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ710" s="9"/>
-    </row>
-    <row r="715" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT715"/>
-    </row>
-    <row r="716" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT716"/>
-      <c r="CJ716" s="9"/>
-    </row>
-    <row r="717" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ717" s="9"/>
-    </row>
-    <row r="718" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT718"/>
-    </row>
-    <row r="719" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT719"/>
-      <c r="CJ719" s="9"/>
-    </row>
-    <row r="720" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ720" s="9"/>
-    </row>
-    <row r="721" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT721"/>
-    </row>
-    <row r="722" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT722"/>
-      <c r="CJ722" s="9"/>
-    </row>
-    <row r="723" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT723"/>
-      <c r="CJ723" s="9"/>
-    </row>
-    <row r="724" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT724"/>
-      <c r="CJ724" s="9"/>
-    </row>
-    <row r="725" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ725" s="9"/>
-    </row>
-    <row r="729" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT729"/>
-    </row>
-    <row r="730" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT730"/>
-      <c r="CJ730" s="9"/>
-    </row>
-    <row r="731" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT731"/>
-      <c r="CJ731" s="9"/>
-    </row>
-    <row r="732" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ732" s="9"/>
-    </row>
-    <row r="733" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT733"/>
-    </row>
-    <row r="734" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ734" s="9"/>
-    </row>
-    <row r="735" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS735" s="4"/>
-      <c r="BT735" s="16"/>
-    </row>
-    <row r="736" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="680" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV680"/>
+    </row>
+    <row r="681" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV681"/>
+      <c r="CL681" s="9"/>
+    </row>
+    <row r="682" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV682"/>
+      <c r="CL682" s="9"/>
+    </row>
+    <row r="683" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV683"/>
+      <c r="CL683" s="9"/>
+    </row>
+    <row r="684" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV684"/>
+      <c r="CL684" s="9"/>
+    </row>
+    <row r="685" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV685"/>
+      <c r="CL685" s="9"/>
+    </row>
+    <row r="686" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV686"/>
+      <c r="CL686" s="9"/>
+    </row>
+    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV687"/>
+      <c r="CL687" s="9"/>
+    </row>
+    <row r="688" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV688"/>
+      <c r="CL688" s="9"/>
+    </row>
+    <row r="689" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL689" s="9"/>
+    </row>
+    <row r="690" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV690"/>
+    </row>
+    <row r="691" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL691" s="9"/>
+    </row>
+    <row r="700" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV700"/>
+    </row>
+    <row r="701" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV701"/>
+      <c r="CL701" s="9"/>
+    </row>
+    <row r="702" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV702"/>
+      <c r="CL702" s="9"/>
+    </row>
+    <row r="703" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV703"/>
+      <c r="CL703" s="9"/>
+    </row>
+    <row r="704" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV704"/>
+      <c r="CL704" s="9"/>
+    </row>
+    <row r="705" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV705"/>
+      <c r="CL705" s="9"/>
+    </row>
+    <row r="706" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV706"/>
+      <c r="CL706" s="9"/>
+    </row>
+    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV707"/>
+      <c r="CL707" s="9"/>
+    </row>
+    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL708" s="9"/>
+    </row>
+    <row r="709" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV709"/>
+    </row>
+    <row r="710" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL710" s="9"/>
+    </row>
+    <row r="715" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV715"/>
+    </row>
+    <row r="716" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV716"/>
+      <c r="CL716" s="9"/>
+    </row>
+    <row r="717" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL717" s="9"/>
+    </row>
+    <row r="718" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV718"/>
+    </row>
+    <row r="719" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV719"/>
+      <c r="CL719" s="9"/>
+    </row>
+    <row r="720" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL720" s="9"/>
+    </row>
+    <row r="721" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV721"/>
+    </row>
+    <row r="722" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV722"/>
+      <c r="CL722" s="9"/>
+    </row>
+    <row r="723" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV723"/>
+      <c r="CL723" s="9"/>
+    </row>
+    <row r="724" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV724"/>
+      <c r="CL724" s="9"/>
+    </row>
+    <row r="725" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL725" s="9"/>
+    </row>
+    <row r="729" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV729"/>
+    </row>
+    <row r="730" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV730"/>
+      <c r="CL730" s="9"/>
+    </row>
+    <row r="731" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV731"/>
+      <c r="CL731" s="9"/>
+    </row>
+    <row r="732" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL732" s="9"/>
+    </row>
+    <row r="733" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV733"/>
+    </row>
+    <row r="734" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL734" s="9"/>
+    </row>
+    <row r="735" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU735" s="4"/>
+      <c r="BV735" s="16"/>
+    </row>
+    <row r="736" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H736" s="4"/>
-      <c r="CJ736" s="4"/>
-    </row>
-    <row r="753" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT753"/>
-    </row>
-    <row r="754" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT754"/>
-      <c r="CJ754" s="9"/>
-    </row>
-    <row r="755" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT755"/>
-      <c r="CJ755" s="9"/>
-    </row>
-    <row r="756" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT756"/>
-      <c r="CJ756" s="9"/>
-    </row>
-    <row r="757" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ757" s="9"/>
-    </row>
-    <row r="758" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT758"/>
-    </row>
-    <row r="759" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT759"/>
-      <c r="CJ759" s="9"/>
-    </row>
-    <row r="760" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS760" s="4"/>
-      <c r="BT760" s="16"/>
-      <c r="CJ760" s="9"/>
-    </row>
-    <row r="761" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CL736" s="4"/>
+    </row>
+    <row r="753" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV753"/>
+    </row>
+    <row r="754" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV754"/>
+      <c r="CL754" s="9"/>
+    </row>
+    <row r="755" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV755"/>
+      <c r="CL755" s="9"/>
+    </row>
+    <row r="756" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV756"/>
+      <c r="CL756" s="9"/>
+    </row>
+    <row r="757" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL757" s="9"/>
+    </row>
+    <row r="758" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV758"/>
+    </row>
+    <row r="759" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV759"/>
+      <c r="CL759" s="9"/>
+    </row>
+    <row r="760" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU760" s="4"/>
+      <c r="BV760" s="16"/>
+      <c r="CL760" s="9"/>
+    </row>
+    <row r="761" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H761" s="4"/>
-      <c r="CJ761" s="4"/>
-    </row>
-    <row r="764" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT764"/>
-    </row>
-    <row r="765" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT765"/>
-      <c r="CJ765" s="9"/>
-    </row>
-    <row r="766" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT766"/>
-      <c r="CJ766" s="9"/>
-    </row>
-    <row r="767" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT767"/>
-      <c r="CJ767" s="9"/>
-    </row>
-    <row r="768" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT768"/>
-      <c r="CJ768" s="9"/>
-    </row>
-    <row r="769" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT769"/>
-      <c r="CJ769" s="9"/>
-    </row>
-    <row r="770" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT770"/>
-      <c r="CJ770" s="9"/>
-    </row>
-    <row r="771" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT771"/>
-      <c r="CJ771" s="9"/>
-    </row>
-    <row r="772" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ772" s="9"/>
-    </row>
-    <row r="774" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT774"/>
-    </row>
-    <row r="775" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT775"/>
-      <c r="CJ775" s="9"/>
-    </row>
-    <row r="776" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT776"/>
-      <c r="CJ776" s="9"/>
-    </row>
-    <row r="777" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT777"/>
-      <c r="CJ777" s="9"/>
-    </row>
-    <row r="778" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT778"/>
-      <c r="CJ778" s="9"/>
-    </row>
-    <row r="779" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT779"/>
-      <c r="CJ779" s="9"/>
-    </row>
-    <row r="780" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ780" s="9"/>
-    </row>
-    <row r="781" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT781"/>
-    </row>
-    <row r="782" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT782"/>
-      <c r="CJ782" s="9"/>
-    </row>
-    <row r="783" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT783"/>
-      <c r="CJ783" s="9"/>
-    </row>
-    <row r="784" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT784"/>
-      <c r="CJ784" s="9"/>
-    </row>
-    <row r="785" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT785"/>
-      <c r="CJ785" s="9"/>
-    </row>
-    <row r="786" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT786"/>
-      <c r="CJ786" s="9"/>
-    </row>
-    <row r="787" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT787"/>
-      <c r="CJ787" s="9"/>
-    </row>
-    <row r="788" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT788"/>
-      <c r="CJ788" s="9"/>
-    </row>
-    <row r="789" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT789"/>
-      <c r="CJ789" s="9"/>
-    </row>
-    <row r="790" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT790"/>
-      <c r="CJ790" s="9"/>
-    </row>
-    <row r="791" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT791"/>
-      <c r="CJ791" s="9"/>
-    </row>
-    <row r="792" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT792"/>
-      <c r="CJ792" s="9"/>
-    </row>
-    <row r="793" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT793"/>
-      <c r="CJ793" s="9"/>
-    </row>
-    <row r="794" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT794"/>
-      <c r="CJ794" s="9"/>
-    </row>
-    <row r="795" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT795"/>
-      <c r="CJ795" s="9"/>
-    </row>
-    <row r="796" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT796"/>
-      <c r="CJ796" s="9"/>
-    </row>
-    <row r="797" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT797"/>
-      <c r="CJ797" s="9"/>
-    </row>
-    <row r="798" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT798"/>
-      <c r="CJ798" s="9"/>
-    </row>
-    <row r="799" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT799"/>
-      <c r="CJ799" s="9"/>
-    </row>
-    <row r="800" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT800"/>
-      <c r="CJ800" s="9"/>
-    </row>
-    <row r="801" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT801"/>
-      <c r="CJ801" s="9"/>
-    </row>
-    <row r="802" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT802"/>
-      <c r="CJ802" s="9"/>
-    </row>
-    <row r="803" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT803"/>
-      <c r="CJ803" s="9"/>
-    </row>
-    <row r="804" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT804"/>
-      <c r="CJ804" s="9"/>
-    </row>
-    <row r="805" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT805"/>
-      <c r="CJ805" s="9"/>
-    </row>
-    <row r="806" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT806"/>
-      <c r="CJ806" s="9"/>
-    </row>
-    <row r="807" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT807"/>
-      <c r="CJ807" s="9"/>
-    </row>
-    <row r="808" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT808"/>
-      <c r="CJ808" s="9"/>
-    </row>
-    <row r="809" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT809"/>
-      <c r="CJ809" s="9"/>
-    </row>
-    <row r="810" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT810"/>
-      <c r="CJ810" s="9"/>
-    </row>
-    <row r="811" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ811" s="9"/>
-    </row>
-    <row r="812" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT812"/>
-    </row>
-    <row r="813" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT813"/>
-      <c r="CJ813" s="9"/>
-    </row>
-    <row r="814" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT814"/>
-      <c r="CJ814" s="9"/>
-    </row>
-    <row r="815" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ815" s="9"/>
+      <c r="CL761" s="4"/>
+    </row>
+    <row r="764" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV764"/>
+    </row>
+    <row r="765" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV765"/>
+      <c r="CL765" s="9"/>
+    </row>
+    <row r="766" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV766"/>
+      <c r="CL766" s="9"/>
+    </row>
+    <row r="767" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV767"/>
+      <c r="CL767" s="9"/>
+    </row>
+    <row r="768" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV768"/>
+      <c r="CL768" s="9"/>
+    </row>
+    <row r="769" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV769"/>
+      <c r="CL769" s="9"/>
+    </row>
+    <row r="770" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV770"/>
+      <c r="CL770" s="9"/>
+    </row>
+    <row r="771" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV771"/>
+      <c r="CL771" s="9"/>
+    </row>
+    <row r="772" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL772" s="9"/>
+    </row>
+    <row r="774" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV774"/>
+    </row>
+    <row r="775" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV775"/>
+      <c r="CL775" s="9"/>
+    </row>
+    <row r="776" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV776"/>
+      <c r="CL776" s="9"/>
+    </row>
+    <row r="777" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV777"/>
+      <c r="CL777" s="9"/>
+    </row>
+    <row r="778" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV778"/>
+      <c r="CL778" s="9"/>
+    </row>
+    <row r="779" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV779"/>
+      <c r="CL779" s="9"/>
+    </row>
+    <row r="780" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL780" s="9"/>
+    </row>
+    <row r="781" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV781"/>
+    </row>
+    <row r="782" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV782"/>
+      <c r="CL782" s="9"/>
+    </row>
+    <row r="783" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV783"/>
+      <c r="CL783" s="9"/>
+    </row>
+    <row r="784" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV784"/>
+      <c r="CL784" s="9"/>
+    </row>
+    <row r="785" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV785"/>
+      <c r="CL785" s="9"/>
+    </row>
+    <row r="786" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV786"/>
+      <c r="CL786" s="9"/>
+    </row>
+    <row r="787" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV787"/>
+      <c r="CL787" s="9"/>
+    </row>
+    <row r="788" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV788"/>
+      <c r="CL788" s="9"/>
+    </row>
+    <row r="789" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV789"/>
+      <c r="CL789" s="9"/>
+    </row>
+    <row r="790" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV790"/>
+      <c r="CL790" s="9"/>
+    </row>
+    <row r="791" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV791"/>
+      <c r="CL791" s="9"/>
+    </row>
+    <row r="792" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV792"/>
+      <c r="CL792" s="9"/>
+    </row>
+    <row r="793" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV793"/>
+      <c r="CL793" s="9"/>
+    </row>
+    <row r="794" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV794"/>
+      <c r="CL794" s="9"/>
+    </row>
+    <row r="795" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV795"/>
+      <c r="CL795" s="9"/>
+    </row>
+    <row r="796" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV796"/>
+      <c r="CL796" s="9"/>
+    </row>
+    <row r="797" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV797"/>
+      <c r="CL797" s="9"/>
+    </row>
+    <row r="798" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV798"/>
+      <c r="CL798" s="9"/>
+    </row>
+    <row r="799" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV799"/>
+      <c r="CL799" s="9"/>
+    </row>
+    <row r="800" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV800"/>
+      <c r="CL800" s="9"/>
+    </row>
+    <row r="801" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV801"/>
+      <c r="CL801" s="9"/>
+    </row>
+    <row r="802" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV802"/>
+      <c r="CL802" s="9"/>
+    </row>
+    <row r="803" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV803"/>
+      <c r="CL803" s="9"/>
+    </row>
+    <row r="804" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV804"/>
+      <c r="CL804" s="9"/>
+    </row>
+    <row r="805" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV805"/>
+      <c r="CL805" s="9"/>
+    </row>
+    <row r="806" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV806"/>
+      <c r="CL806" s="9"/>
+    </row>
+    <row r="807" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV807"/>
+      <c r="CL807" s="9"/>
+    </row>
+    <row r="808" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV808"/>
+      <c r="CL808" s="9"/>
+    </row>
+    <row r="809" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV809"/>
+      <c r="CL809" s="9"/>
+    </row>
+    <row r="810" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV810"/>
+      <c r="CL810" s="9"/>
+    </row>
+    <row r="811" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL811" s="9"/>
+    </row>
+    <row r="812" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV812"/>
+    </row>
+    <row r="813" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV813"/>
+      <c r="CL813" s="9"/>
+    </row>
+    <row r="814" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV814"/>
+      <c r="CL814" s="9"/>
+    </row>
+    <row r="815" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL815" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B111302-B69A-45DA-AC6E-B43E33F49D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9147C08D-64AB-4D18-8C2F-CCA05FF32782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1674,9 +1674,6 @@
     <t>部署干员</t>
   </si>
   <si>
-    <t>{"UnitId":"地面M3","TargetPos":"useSelfTargetPos","SetMod":"Replace","UseMod":"UserDirection","UserName":"Mon3tr"}</t>
-  </si>
-  <si>
     <t>m33自身结束</t>
   </si>
   <si>
@@ -2099,6 +2096,10 @@
   </si>
   <si>
     <t>OrderExpression</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"地面M3","召唤位置":"使用本技能索敌位置","部署模式":"替换","召唤物方向":"使用指定单位方向","指定单位名称":"Mon3tr"}</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -6612,10 +6613,10 @@
         <v>195</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>587</v>
       </c>
       <c r="AT1" t="s">
         <v>196</v>
@@ -6947,10 +6948,10 @@
         <v>297</v>
       </c>
       <c r="AR2" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="AS2" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="AT2" t="s">
         <v>298</v>
@@ -7285,10 +7286,10 @@
         <v>2</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AT3" t="s">
         <v>370</v>
@@ -8614,13 +8615,13 @@
         <v>0.1</v>
       </c>
       <c r="CL30" s="9"/>
-      <c r="CU30" t="s">
-        <v>455</v>
+      <c r="CU30" s="1" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C31" t="s">
         <v>383</v>
@@ -8650,7 +8651,7 @@
       </c>
       <c r="BV31"/>
       <c r="CB31" s="15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="CG31" t="s">
         <v>394</v>
@@ -8668,7 +8669,7 @@
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C32" t="s">
         <v>383</v>
@@ -8695,7 +8696,7 @@
       </c>
       <c r="BV32"/>
       <c r="CB32" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="CG32" t="s">
         <v>394</v>
@@ -8714,7 +8715,7 @@
     </row>
     <row r="34" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C34" t="s">
         <v>383</v>
@@ -8750,7 +8751,7 @@
         <v>1</v>
       </c>
       <c r="BO34" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="BT34">
         <v>25</v>
@@ -8768,10 +8769,10 @@
         <v>424</v>
       </c>
       <c r="CN34" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="CO34" t="s">
         <v>462</v>
-      </c>
-      <c r="CO34" t="s">
-        <v>463</v>
       </c>
       <c r="CP34">
         <v>80</v>
@@ -8782,10 +8783,10 @@
     </row>
     <row r="35" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>463</v>
+      </c>
+      <c r="C35" t="s">
         <v>464</v>
-      </c>
-      <c r="C35" t="s">
-        <v>465</v>
       </c>
       <c r="O35" s="12" t="s">
         <v>450</v>
@@ -8795,7 +8796,7 @@
         <v>2</v>
       </c>
       <c r="AO35" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AT35" t="s">
         <v>409</v>
@@ -8810,24 +8811,24 @@
         <v>1</v>
       </c>
       <c r="BP35" t="s">
+        <v>466</v>
+      </c>
+      <c r="CB35" t="s">
         <v>467</v>
-      </c>
-      <c r="CB35" t="s">
-        <v>468</v>
       </c>
       <c r="CG35" t="s">
         <v>394</v>
       </c>
       <c r="CX35" t="s">
+        <v>468</v>
+      </c>
+      <c r="CY35" t="s">
         <v>469</v>
-      </c>
-      <c r="CY35" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="36" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C36" t="s">
         <v>383</v>
@@ -8886,10 +8887,10 @@
     </row>
     <row r="37" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>470</v>
+      </c>
+      <c r="C37" t="s">
         <v>471</v>
-      </c>
-      <c r="C37" t="s">
-        <v>472</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>385</v>
@@ -8907,12 +8908,12 @@
         <v>1</v>
       </c>
       <c r="CU37" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="38" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C38" t="s">
         <v>383</v>
@@ -8944,7 +8945,7 @@
     </row>
     <row r="39" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C39" t="s">
         <v>383</v>
@@ -10359,37 +10360,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F1" t="s">
         <v>476</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>477</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>478</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>479</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>480</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>481</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>482</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>483</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>484</v>
       </c>
-      <c r="O1" t="s">
-        <v>485</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10403,40 +10404,40 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>485</v>
+      </c>
+      <c r="F2" t="s">
         <v>486</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>487</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>488</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>489</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>490</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>491</v>
-      </c>
-      <c r="K2" t="s">
-        <v>492</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
+        <v>492</v>
+      </c>
+      <c r="N2" t="s">
         <v>493</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>494</v>
       </c>
-      <c r="O2" t="s">
-        <v>495</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Q2" t="s">
         <v>349</v>
@@ -10497,16 +10498,16 @@
         <v>398</v>
       </c>
       <c r="C4" t="s">
+        <v>495</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>496</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="Q4" t="s">
         <v>497</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -10514,16 +10515,16 @@
         <v>408</v>
       </c>
       <c r="C5" t="s">
+        <v>498</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>499</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="Q5" t="s">
         <v>500</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -10531,16 +10532,16 @@
         <v>398</v>
       </c>
       <c r="C6" t="s">
+        <v>495</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>496</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="Q6" t="s">
         <v>497</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -10548,16 +10549,16 @@
         <v>408</v>
       </c>
       <c r="C7" t="s">
+        <v>498</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
         <v>499</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="Q7" t="s">
         <v>500</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10565,47 +10566,47 @@
         <v>410</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>502</v>
+      </c>
+      <c r="C9" t="s">
         <v>503</v>
       </c>
-      <c r="C9" t="s">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
         <v>504</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>505</v>
+      </c>
+      <c r="C10" t="s">
+        <v>503</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
         <v>506</v>
-      </c>
-      <c r="C10" t="s">
-        <v>504</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10613,7 +10614,7 @@
         <v>415</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -10625,13 +10626,13 @@
         <v>437</v>
       </c>
       <c r="C12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10639,7 +10640,7 @@
         <v>435</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -10651,7 +10652,7 @@
         <v>433</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -10660,13 +10661,13 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C15" t="s">
         <v>231</v>
       </c>
       <c r="Q15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10674,75 +10675,75 @@
         <v>450</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
       </c>
       <c r="J16"/>
       <c r="Q16" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C17" t="s">
+        <v>498</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
         <v>499</v>
       </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="Q17" t="s">
         <v>500</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="J18" t="s">
         <v>513</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J18" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>514</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="J19" t="s">
         <v>515</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J19" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>516</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="J20" t="s">
         <v>517</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J20" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>518</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="J21" t="s">
         <v>519</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J21" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10750,24 +10751,24 @@
         <v>390</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C23" t="s">
         <v>231</v>
       </c>
       <c r="Q23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -10775,7 +10776,7 @@
         <v>414</v>
       </c>
       <c r="C24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -10803,7 +10804,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10814,7 +10815,7 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D2" t="s">
         <v>349</v>
@@ -10863,19 +10864,19 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G2" t="s">
         <v>527</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>528</v>
-      </c>
-      <c r="H2" t="s">
-        <v>529</v>
       </c>
       <c r="I2" t="s">
         <v>349</v>
@@ -10920,10 +10921,10 @@
         <v>396</v>
       </c>
       <c r="B5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C5" t="s">
         <v>530</v>
-      </c>
-      <c r="C5" t="s">
-        <v>531</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -10932,7 +10933,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -10959,34 +10960,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C1" t="s">
         <v>533</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>534</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>535</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>536</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>537</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>538</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>539</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>540</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>541</v>
-      </c>
-      <c r="L1" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10994,34 +10995,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C2" t="s">
         <v>543</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>544</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>545</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>546</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>547</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>548</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>549</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>550</v>
       </c>
-      <c r="J2" t="s">
-        <v>551</v>
-      </c>
       <c r="K2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -11038,7 +11039,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -11067,13 +11068,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B4" t="s">
+        <v>552</v>
+      </c>
+      <c r="E4" t="s">
         <v>553</v>
-      </c>
-      <c r="E4" t="s">
-        <v>554</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -11087,13 +11088,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -11107,13 +11108,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B6" t="s">
+        <v>555</v>
+      </c>
+      <c r="E6" t="s">
         <v>556</v>
-      </c>
-      <c r="E6" t="s">
-        <v>557</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -11127,13 +11128,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -11147,10 +11148,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -11195,22 +11196,22 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E2" t="s">
         <v>560</v>
-      </c>
-      <c r="E2" t="s">
-        <v>561</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2" t="s">
         <v>289</v>
       </c>
       <c r="I2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -11239,7 +11240,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -11273,89 +11274,89 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>580</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>583</v>
-      </c>
       <c r="C3" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9147C08D-64AB-4D18-8C2F-CCA05FF32782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413049C4-4A0C-4CA8-9105-922B68BF19A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="594">
   <si>
     <t>Id</t>
   </si>
@@ -758,9 +758,6 @@
   </si>
   <si>
     <t>地面M3</t>
-  </si>
-  <si>
-    <t>地面m3,地面m3落地无敌,地面m3释放buff</t>
   </si>
   <si>
     <r>
@@ -1902,9 +1899,6 @@
     <t>frostl_attack_01_trail</t>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":4,"SkillId":"干员链式弹道索敌","ReductionRate":0.1,"CanBack":"false"}</t>
-  </si>
-  <si>
     <t>模型</t>
   </si>
   <si>
@@ -2100,6 +2094,30 @@
   </si>
   <si>
     <t>{"召唤物ID":"地面M3","召唤位置":"使用本技能索敌位置","部署模式":"替换","召唤物方向":"使用指定单位方向","指定单位名称":"Mon3tr"}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3链奶衰减</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>链奶伤害衰减</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Rate":0.8}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":4,"SkillId":"干员链式弹道索敌","CanBack":"false"}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面m3落地无敌,地面m3释放buff</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面m3</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3569,8 +3587,11 @@
       <c r="AH7" t="s">
         <v>130</v>
       </c>
-      <c r="AI7" t="s">
-        <v>153</v>
+      <c r="AI7" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>593</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -3612,13 +3633,13 @@
         <v>140</v>
       </c>
       <c r="BM7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BN7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BP7" s="17" t="s">
         <v>154</v>
-      </c>
-      <c r="BN7" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BP7" s="17" t="s">
-        <v>155</v>
       </c>
       <c r="BQ7" t="s">
         <v>143</v>
@@ -6490,334 +6511,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" t="s">
         <v>156</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>157</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>158</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>159</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" t="s">
         <v>161</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>162</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="U1" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="V1" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="V1" s="9" t="s">
+      <c r="W1" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="X1" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="Y1" t="s">
         <v>176</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>177</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AB1" t="s">
         <v>179</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>180</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>181</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>182</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>183</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>184</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>185</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>186</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>187</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>188</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>189</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>190</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>191</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>192</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>193</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>194</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="AT1" t="s">
         <v>195</v>
       </c>
-      <c r="AR1" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>196</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>197</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>198</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>199</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>200</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>201</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>202</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="BB1" s="8" t="s">
+      <c r="BC1" t="s">
         <v>204</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>205</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>206</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>207</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>208</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>209</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
+        <v>209</v>
+      </c>
+      <c r="BK1" t="s">
         <v>210</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>210</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>211</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>212</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>213</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>214</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>215</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>216</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>217</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>218</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>219</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="BU1" s="8" t="s">
+      <c r="BV1" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="BV1" s="10" t="s">
+      <c r="BW1" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="BW1" s="10" t="s">
+      <c r="BX1" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="BX1" s="10" t="s">
+      <c r="BY1" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="BY1" s="10" t="s">
+      <c r="BZ1" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="BZ1" s="10" t="s">
+      <c r="CA1" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="CA1" s="10" t="s">
+      <c r="CB1" t="s">
         <v>227</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="CC1" s="10" t="s">
+      <c r="CD1" t="s">
         <v>229</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>230</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>231</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>232</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>233</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>234</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>235</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>236</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="CL1" s="8" t="s">
+      <c r="CM1" t="s">
         <v>238</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>239</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>240</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>241</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>242</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
+        <v>219</v>
+      </c>
+      <c r="CS1" t="s">
         <v>243</v>
       </c>
-      <c r="CR1" t="s">
-        <v>220</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>244</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>245</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>246</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>247</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>248</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>249</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
+        <v>248</v>
+      </c>
+      <c r="DA1" t="s">
         <v>250</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>249</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>251</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>252</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>253</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>254</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>255</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>256</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>257</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>258</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6831,331 +6852,331 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" t="s">
         <v>260</v>
-      </c>
-      <c r="F2" t="s">
-        <v>261</v>
       </c>
       <c r="G2" t="s">
         <v>53</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="I2" t="s">
         <v>262</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>263</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="Q2" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="R2" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="S2" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="T2" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="U2" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="W2" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="W2" s="9" t="s">
+      <c r="X2" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="Y2" t="s">
         <v>278</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>279</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="AA2" s="9" t="s">
+      <c r="AB2" t="s">
         <v>281</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>282</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>283</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>284</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>285</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>286</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>287</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>288</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>289</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>290</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>291</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>292</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>293</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>294</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>295</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>296</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="AT2" t="s">
         <v>297</v>
       </c>
-      <c r="AR2" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>298</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>299</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>300</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>301</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>302</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>303</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>304</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>305</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>306</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>307</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>308</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>309</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>310</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>311</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>312</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>313</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>314</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>315</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>316</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>317</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>318</v>
       </c>
       <c r="BO2" t="s">
         <v>79</v>
       </c>
       <c r="BP2" t="s">
+        <v>318</v>
+      </c>
+      <c r="BQ2" t="s">
         <v>319</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>320</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>321</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>322</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>323</v>
       </c>
       <c r="BU2" s="8" t="s">
         <v>95</v>
       </c>
       <c r="BV2" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="BW2" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="BW2" s="10" t="s">
+      <c r="BX2" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="BX2" s="10" t="s">
+      <c r="BY2" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="BY2" s="10" t="s">
+      <c r="BZ2" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="BZ2" s="10" t="s">
+      <c r="CA2" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="CA2" s="10" t="s">
+      <c r="CB2" t="s">
         <v>329</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>330</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>331</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>332</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>333</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>334</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>335</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>336</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" t="s">
         <v>337</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CK2" t="s">
         <v>338</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CL2" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="CL2" s="8" t="s">
+      <c r="CM2" t="s">
         <v>340</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>341</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>342</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>343</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>344</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>345</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>347</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>348</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>349</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>350</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>351</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>352</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>353</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>354</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>355</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>356</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>357</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>358</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>359</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>360</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DH2" t="s">
         <v>361</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DI2" t="s">
         <v>362</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -7184,13 +7205,13 @@
         <v>116</v>
       </c>
       <c r="J3" t="s">
+        <v>363</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="M3" s="9" t="s">
         <v>118</v>
@@ -7253,7 +7274,7 @@
         <v>116</v>
       </c>
       <c r="AG3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -7277,22 +7298,22 @@
         <v>116</v>
       </c>
       <c r="AO3" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP3" t="s">
         <v>368</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>369</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AT3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AU3" t="s">
         <v>116</v>
@@ -7304,7 +7325,7 @@
         <v>116</v>
       </c>
       <c r="AX3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AY3" t="s">
         <v>116</v>
@@ -7334,7 +7355,7 @@
         <v>116</v>
       </c>
       <c r="BH3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="BI3" t="s">
         <v>116</v>
@@ -7361,10 +7382,10 @@
         <v>119</v>
       </c>
       <c r="BQ3" t="s">
+        <v>371</v>
+      </c>
+      <c r="BR3" t="s">
         <v>372</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>373</v>
       </c>
       <c r="BS3" t="s">
         <v>117</v>
@@ -7385,19 +7406,19 @@
         <v>118</v>
       </c>
       <c r="BY3" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="BZ3" s="10" t="s">
         <v>116</v>
       </c>
       <c r="CA3" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
       </c>
       <c r="CC3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="CD3" t="s">
         <v>124</v>
@@ -7409,19 +7430,19 @@
         <v>124</v>
       </c>
       <c r="CG3" t="s">
+        <v>375</v>
+      </c>
+      <c r="CH3" t="s">
         <v>376</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>377</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="CK3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="CL3" s="8" t="s">
         <v>125</v>
@@ -7442,7 +7463,7 @@
         <v>123</v>
       </c>
       <c r="CR3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="CS3" t="s">
         <v>123</v>
@@ -7454,28 +7475,28 @@
         <v>125</v>
       </c>
       <c r="CV3" t="s">
+        <v>378</v>
+      </c>
+      <c r="CW3" t="s">
         <v>379</v>
       </c>
-      <c r="CW3" t="s">
-        <v>380</v>
-      </c>
       <c r="CX3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="CY3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="CZ3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="DA3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="DB3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="DC3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="DD3" t="s">
         <v>116</v>
@@ -7498,57 +7519,57 @@
     </row>
     <row r="4" spans="1:113" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C5" t="s">
         <v>382</v>
       </c>
-      <c r="C5" t="s">
+      <c r="J5" t="s">
         <v>383</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" s="9" t="s">
         <v>384</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>385</v>
       </c>
       <c r="O5"/>
       <c r="AC5">
         <v>1</v>
       </c>
       <c r="AO5" t="s">
+        <v>385</v>
+      </c>
+      <c r="AT5" t="s">
         <v>386</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>387</v>
+      </c>
+      <c r="C6" t="s">
+        <v>382</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="C6" t="s">
-        <v>383</v>
-      </c>
-      <c r="K6" s="9" t="s">
+      <c r="P6" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="S6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
         <v>390</v>
       </c>
-      <c r="S6" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="s">
+      <c r="AT6" t="s">
         <v>391</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>392</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -7563,38 +7584,38 @@
         <v>1</v>
       </c>
       <c r="BP6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="CB6" t="s">
         <v>57</v>
       </c>
       <c r="CG6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P7"/>
       <c r="AC7">
         <v>1</v>
       </c>
       <c r="AO7" t="s">
+        <v>390</v>
+      </c>
+      <c r="AT7" t="s">
         <v>391</v>
       </c>
-      <c r="AT7" t="s">
-        <v>392</v>
-      </c>
       <c r="AY7">
         <v>1</v>
       </c>
@@ -7605,16 +7626,16 @@
         <v>1</v>
       </c>
       <c r="BP7" t="s">
+        <v>394</v>
+      </c>
+      <c r="CH7" t="s">
         <v>395</v>
       </c>
-      <c r="CH7" t="s">
+      <c r="CI7" t="s">
         <v>396</v>
       </c>
-      <c r="CI7" t="s">
+      <c r="CN7" t="s">
         <v>397</v>
-      </c>
-      <c r="CN7" t="s">
-        <v>398</v>
       </c>
       <c r="CO7">
         <v>22</v>
@@ -7623,37 +7644,37 @@
         <v>10</v>
       </c>
       <c r="CY7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>399</v>
+      </c>
+      <c r="C8" t="s">
         <v>400</v>
       </c>
-      <c r="C8" t="s">
+      <c r="K8" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="K8" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="L8" s="9" t="s">
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="s">
         <v>402</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AF8">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>403</v>
       </c>
       <c r="BD8">
         <v>1</v>
       </c>
       <c r="CL8" s="9"/>
       <c r="CU8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="DD8">
         <v>1</v>
@@ -7667,19 +7688,19 @@
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M9"/>
       <c r="N9"/>
@@ -7697,16 +7718,16 @@
         <v>1</v>
       </c>
       <c r="AG9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AT9" t="s">
+        <v>405</v>
+      </c>
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="s">
         <v>406</v>
-      </c>
-      <c r="BD9">
-        <v>1</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>407</v>
       </c>
       <c r="BU9" s="14"/>
       <c r="BV9" s="14"/>
@@ -7716,7 +7737,7 @@
       <c r="BZ9" s="14"/>
       <c r="CA9"/>
       <c r="CN9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="CO9">
         <v>8</v>
@@ -7730,10 +7751,10 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -7756,7 +7777,7 @@
         <v>1</v>
       </c>
       <c r="AT10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="BD10">
         <v>99</v>
@@ -7772,7 +7793,7 @@
       <c r="BZ10" s="14"/>
       <c r="CA10"/>
       <c r="CN10" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="CO10">
         <v>0.2</v>
@@ -7786,22 +7807,22 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L11" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="s">
         <v>402</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>403</v>
       </c>
       <c r="AY11" s="9"/>
       <c r="BD11">
@@ -7825,7 +7846,7 @@
       <c r="CL11" s="9"/>
       <c r="CM11" s="9"/>
       <c r="CN11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="CR11">
         <v>99999</v>
@@ -7833,10 +7854,10 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -7875,7 +7896,7 @@
       <c r="CL12" s="9"/>
       <c r="CM12" s="9"/>
       <c r="CN12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="CR12">
         <v>0.2</v>
@@ -7883,21 +7904,21 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M13"/>
       <c r="N13"/>
       <c r="P13" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="R13" s="12"/>
       <c r="S13"/>
@@ -7906,10 +7927,10 @@
         <v>1</v>
       </c>
       <c r="AG13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AT13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -7917,7 +7938,7 @@
       <c r="BV13"/>
       <c r="CB13" s="10"/>
       <c r="CN13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="CO13">
         <v>22</v>
@@ -7937,28 +7958,28 @@
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>415</v>
+      </c>
+      <c r="C17" t="s">
+        <v>382</v>
+      </c>
+      <c r="D17" t="s">
         <v>416</v>
       </c>
-      <c r="C17" t="s">
-        <v>383</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>417</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>418</v>
-      </c>
-      <c r="F17" t="s">
-        <v>419</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="J17" t="s">
+        <v>419</v>
+      </c>
+      <c r="K17" s="9" t="s">
         <v>420</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>421</v>
       </c>
       <c r="M17"/>
       <c r="O17"/>
@@ -7966,16 +7987,16 @@
         <v>1</v>
       </c>
       <c r="AG17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="BD17">
         <v>1</v>
       </c>
       <c r="BO17" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="BP17" t="s">
         <v>422</v>
-      </c>
-      <c r="BP17" t="s">
-        <v>423</v>
       </c>
       <c r="BT17">
         <v>30</v>
@@ -7990,10 +8011,10 @@
         <v>1</v>
       </c>
       <c r="BY17" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="CN17" s="12" t="s">
         <v>424</v>
-      </c>
-      <c r="CN17" s="12" t="s">
-        <v>425</v>
       </c>
       <c r="CR17">
         <v>30</v>
@@ -8004,15 +8025,15 @@
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C18" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J18" s="9"/>
       <c r="M18"/>
       <c r="O18" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
@@ -8023,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="AO18" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AQ18" t="s">
         <v>144</v>
@@ -8041,22 +8062,22 @@
         <v>1</v>
       </c>
       <c r="BP18" t="s">
+        <v>426</v>
+      </c>
+      <c r="CB18" t="s">
         <v>427</v>
       </c>
-      <c r="CB18" t="s">
+      <c r="CG18" t="s">
+        <v>393</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>395</v>
+      </c>
+      <c r="CI18" t="s">
+        <v>396</v>
+      </c>
+      <c r="CN18" s="8" t="s">
         <v>428</v>
-      </c>
-      <c r="CG18" t="s">
-        <v>394</v>
-      </c>
-      <c r="CH18" t="s">
-        <v>396</v>
-      </c>
-      <c r="CI18" t="s">
-        <v>397</v>
-      </c>
-      <c r="CN18" s="8" t="s">
-        <v>429</v>
       </c>
       <c r="CO18">
         <v>22</v>
@@ -8068,21 +8089,21 @@
         <v>10</v>
       </c>
       <c r="CY18" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M19"/>
       <c r="AC19">
@@ -8095,13 +8116,13 @@
         <v>144</v>
       </c>
       <c r="AO19" t="s">
+        <v>390</v>
+      </c>
+      <c r="AT19" t="s">
         <v>391</v>
       </c>
-      <c r="AT19" t="s">
-        <v>392</v>
-      </c>
       <c r="AX19" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AZ19">
         <v>1</v>
@@ -8114,13 +8135,13 @@
       </c>
       <c r="CB19" s="3"/>
       <c r="CH19" t="s">
+        <v>431</v>
+      </c>
+      <c r="CI19" t="s">
+        <v>396</v>
+      </c>
+      <c r="CN19" s="12" t="s">
         <v>432</v>
-      </c>
-      <c r="CI19" t="s">
-        <v>397</v>
-      </c>
-      <c r="CN19" s="12" t="s">
-        <v>433</v>
       </c>
       <c r="CR19">
         <v>0.1</v>
@@ -8134,20 +8155,20 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C20" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M20"/>
       <c r="O20" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P20"/>
       <c r="Q20"/>
@@ -8155,7 +8176,7 @@
         <v>1</v>
       </c>
       <c r="AG20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AW20">
         <v>1</v>
@@ -8164,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="CN20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CO20">
         <v>22</v>
@@ -8178,17 +8199,17 @@
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C21" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="M21"/>
       <c r="O21" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
@@ -8199,7 +8220,7 @@
         <v>144</v>
       </c>
       <c r="AT21" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="BD21">
         <v>1</v>
@@ -8208,7 +8229,7 @@
         <v>0.1</v>
       </c>
       <c r="CN21" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="CR21">
         <v>0.2</v>
@@ -8216,23 +8237,23 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M22"/>
       <c r="AC22">
         <v>1</v>
       </c>
       <c r="AG22" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AY22" s="9"/>
       <c r="BD22">
@@ -8254,7 +8275,7 @@
       <c r="CJ22" s="9"/>
       <c r="CK22" s="9"/>
       <c r="CN22" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="CR22">
         <v>40</v>
@@ -8268,20 +8289,20 @@
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="M23"/>
       <c r="O23" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AC23">
         <v>1</v>
@@ -8293,21 +8314,21 @@
         <v>99</v>
       </c>
       <c r="CM23" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C24" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M24"/>
       <c r="N24"/>
@@ -8315,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="AG24" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="BD24">
         <v>1</v>
@@ -8325,10 +8346,10 @@
       </c>
       <c r="BV24"/>
       <c r="CB24" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CG24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="CI24" s="9"/>
       <c r="CJ24" s="9"/>
@@ -8344,19 +8365,19 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>439</v>
+      </c>
+      <c r="C25" t="s">
+        <v>382</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="L25" s="9" t="s">
         <v>440</v>
-      </c>
-      <c r="C25" t="s">
-        <v>383</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>441</v>
       </c>
       <c r="M25"/>
       <c r="N25"/>
@@ -8364,7 +8385,7 @@
         <v>1</v>
       </c>
       <c r="AG25" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="BD25">
         <v>1</v>
@@ -8374,10 +8395,10 @@
       </c>
       <c r="BV25"/>
       <c r="CB25" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="CG25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="CJ25" s="9"/>
       <c r="DD25">
@@ -8392,19 +8413,19 @@
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C26" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D26" t="s">
+        <v>416</v>
+      </c>
+      <c r="E26" t="s">
         <v>417</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>418</v>
-      </c>
-      <c r="F26" t="s">
-        <v>419</v>
       </c>
       <c r="G26">
         <v>3</v>
@@ -8414,19 +8435,19 @@
       </c>
       <c r="M26"/>
       <c r="O26" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC26">
         <v>1</v>
       </c>
       <c r="AG26" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO26" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AT26" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AY26">
         <v>1</v>
@@ -8443,17 +8464,17 @@
         <v>0.1</v>
       </c>
       <c r="CG26" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="CH26" t="s">
+        <v>395</v>
+      </c>
+      <c r="CI26" t="s">
         <v>396</v>
-      </c>
-      <c r="CI26" t="s">
-        <v>397</v>
       </c>
       <c r="CM26" s="8"/>
       <c r="CN26" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CO26">
         <v>22</v>
@@ -8465,7 +8486,7 @@
         <v>10</v>
       </c>
       <c r="CY26" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="DD26">
         <v>1</v>
@@ -8477,31 +8498,31 @@
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>443</v>
+      </c>
+      <c r="C28" t="s">
+        <v>382</v>
+      </c>
+      <c r="D28" t="s">
         <v>444</v>
       </c>
-      <c r="C28" t="s">
-        <v>383</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>445</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>446</v>
-      </c>
-      <c r="F28" t="s">
-        <v>447</v>
       </c>
       <c r="G28">
         <v>3</v>
       </c>
       <c r="J28" t="s">
+        <v>419</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="K28" s="9" t="s">
-        <v>421</v>
-      </c>
       <c r="O28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="W28"/>
       <c r="X28"/>
@@ -8509,16 +8530,16 @@
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="BD28">
         <v>1</v>
       </c>
       <c r="BO28" t="s">
+        <v>447</v>
+      </c>
+      <c r="BP28" t="s">
         <v>448</v>
-      </c>
-      <c r="BP28" t="s">
-        <v>449</v>
       </c>
       <c r="BT28">
         <v>1</v>
@@ -8533,13 +8554,13 @@
         <v>1</v>
       </c>
       <c r="BY28" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="CN28" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="CO28" t="s">
         <v>450</v>
-      </c>
-      <c r="CO28" t="s">
-        <v>451</v>
       </c>
       <c r="CR28">
         <v>25</v>
@@ -8547,17 +8568,17 @@
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C29" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="M29"/>
       <c r="O29" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P29"/>
       <c r="Q29"/>
@@ -8565,10 +8586,10 @@
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AT29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="BD29">
         <v>1</v>
@@ -8577,7 +8598,7 @@
         <v>0.1</v>
       </c>
       <c r="CN29" s="12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="CR29">
         <v>0.2</v>
@@ -8585,19 +8606,19 @@
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>452</v>
+      </c>
+      <c r="C30" t="s">
         <v>453</v>
       </c>
-      <c r="C30" t="s">
-        <v>454</v>
-      </c>
       <c r="I30">
         <v>1</v>
       </c>
       <c r="J30" t="s">
+        <v>383</v>
+      </c>
+      <c r="K30" s="9" t="s">
         <v>384</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>385</v>
       </c>
       <c r="AC30">
         <v>1</v>
@@ -8606,7 +8627,7 @@
         <v>144</v>
       </c>
       <c r="AT30" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="BD30">
         <v>1</v>
@@ -8616,24 +8637,24 @@
       </c>
       <c r="CL30" s="9"/>
       <c r="CU30" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C31" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I31">
         <v>1</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M31"/>
       <c r="N31"/>
@@ -8641,7 +8662,7 @@
         <v>1</v>
       </c>
       <c r="AG31" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="BD31">
         <v>1</v>
@@ -8651,10 +8672,10 @@
       </c>
       <c r="BV31"/>
       <c r="CB31" s="15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="CG31" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="CJ31" s="9"/>
       <c r="DD31">
@@ -8669,16 +8690,16 @@
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C32" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M32"/>
       <c r="N32"/>
@@ -8686,7 +8707,7 @@
         <v>1</v>
       </c>
       <c r="AG32" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="BD32">
         <v>1</v>
@@ -8696,10 +8717,10 @@
       </c>
       <c r="BV32"/>
       <c r="CB32" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="CG32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="CI32" s="9"/>
       <c r="CJ32" s="9"/>
@@ -8715,28 +8736,28 @@
     </row>
     <row r="34" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C34" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D34" t="s">
+        <v>444</v>
+      </c>
+      <c r="E34" t="s">
         <v>445</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>446</v>
-      </c>
-      <c r="F34" t="s">
-        <v>447</v>
       </c>
       <c r="G34">
         <v>3</v>
       </c>
       <c r="J34" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O34"/>
       <c r="W34"/>
@@ -8745,13 +8766,13 @@
         <v>1</v>
       </c>
       <c r="AG34" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="BD34">
         <v>1</v>
       </c>
       <c r="BO34" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="BT34">
         <v>25</v>
@@ -8766,13 +8787,13 @@
         <v>1</v>
       </c>
       <c r="BY34" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="CN34" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="CO34" t="s">
         <v>461</v>
-      </c>
-      <c r="CO34" t="s">
-        <v>462</v>
       </c>
       <c r="CP34">
         <v>80</v>
@@ -8783,64 +8804,64 @@
     </row>
     <row r="35" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>462</v>
+      </c>
+      <c r="C35" t="s">
         <v>463</v>
       </c>
-      <c r="C35" t="s">
-        <v>464</v>
-      </c>
       <c r="O35" s="12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="X35"/>
       <c r="AC35">
         <v>2</v>
       </c>
       <c r="AO35" t="s">
+        <v>464</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>408</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>430</v>
+      </c>
+      <c r="AZ35">
+        <v>1</v>
+      </c>
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="s">
         <v>465</v>
       </c>
-      <c r="AT35" t="s">
-        <v>409</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>431</v>
-      </c>
-      <c r="AZ35">
-        <v>1</v>
-      </c>
-      <c r="BD35">
-        <v>1</v>
-      </c>
-      <c r="BP35" t="s">
+      <c r="CB35" t="s">
         <v>466</v>
       </c>
-      <c r="CB35" t="s">
+      <c r="CG35" t="s">
+        <v>393</v>
+      </c>
+      <c r="CX35" t="s">
         <v>467</v>
       </c>
-      <c r="CG35" t="s">
-        <v>394</v>
-      </c>
-      <c r="CX35" t="s">
+      <c r="CY35" t="s">
         <v>468</v>
-      </c>
-      <c r="CY35" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="36" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C36" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I36">
         <v>1</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P36"/>
       <c r="Q36"/>
@@ -8849,13 +8870,13 @@
         <v>1</v>
       </c>
       <c r="AG36" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AH36">
         <v>1</v>
       </c>
       <c r="AO36" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AV36">
         <v>1</v>
@@ -8870,13 +8891,13 @@
         <v>1</v>
       </c>
       <c r="CH36" t="s">
+        <v>395</v>
+      </c>
+      <c r="CI36" t="s">
         <v>396</v>
       </c>
-      <c r="CI36" t="s">
+      <c r="CN36" t="s">
         <v>397</v>
-      </c>
-      <c r="CN36" t="s">
-        <v>398</v>
       </c>
       <c r="CO36">
         <v>22</v>
@@ -8887,57 +8908,57 @@
     </row>
     <row r="37" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>469</v>
+      </c>
+      <c r="C37" t="s">
         <v>470</v>
       </c>
-      <c r="C37" t="s">
+      <c r="K37" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>402</v>
+      </c>
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="s">
         <v>471</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="AC37">
-        <v>1</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>403</v>
-      </c>
-      <c r="BD37">
-        <v>1</v>
-      </c>
-      <c r="CU37" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="38" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C38" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L38" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="AC38">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="s">
         <v>402</v>
       </c>
-      <c r="AC38">
-        <v>1</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>403</v>
-      </c>
       <c r="BD38">
         <v>1</v>
       </c>
       <c r="CN38" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="CR38">
         <v>0.5</v>
@@ -8945,10 +8966,10 @@
     </row>
     <row r="39" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -8969,7 +8990,7 @@
         <v>0.1</v>
       </c>
       <c r="CN39" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="CR39">
         <v>0.5</v>
@@ -10360,37 +10381,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F1" t="s">
         <v>475</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>476</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>477</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>478</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>479</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>480</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>481</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>482</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>483</v>
       </c>
-      <c r="O1" t="s">
-        <v>484</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10404,43 +10425,43 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F2" t="s">
         <v>485</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>486</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>487</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>488</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>489</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>490</v>
-      </c>
-      <c r="K2" t="s">
-        <v>491</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
+        <v>491</v>
+      </c>
+      <c r="N2" t="s">
         <v>492</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>493</v>
       </c>
-      <c r="O2" t="s">
-        <v>494</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Q2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -10469,13 +10490,13 @@
         <v>116</v>
       </c>
       <c r="J3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K3" t="s">
         <v>117</v>
       </c>
       <c r="L3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M3" t="s">
         <v>116</v>
@@ -10484,7 +10505,7 @@
         <v>116</v>
       </c>
       <c r="O3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P3" t="s">
         <v>116</v>
@@ -10495,126 +10516,126 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C4" t="s">
+        <v>494</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>495</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="Q4" t="s">
         <v>496</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C5" t="s">
+        <v>497</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>498</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="Q5" t="s">
         <v>499</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C6" t="s">
+        <v>494</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>495</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="Q6" t="s">
         <v>496</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C7" t="s">
+        <v>497</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
         <v>498</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="Q7" t="s">
         <v>499</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>501</v>
+      </c>
+      <c r="C9" t="s">
         <v>502</v>
       </c>
-      <c r="C9" t="s">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
         <v>503</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>504</v>
+      </c>
+      <c r="C10" t="s">
+        <v>502</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
         <v>505</v>
-      </c>
-      <c r="C10" t="s">
-        <v>503</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -10623,24 +10644,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -10649,10 +10670,10 @@
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -10661,122 +10682,122 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C15" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q15" t="s">
         <v>508</v>
-      </c>
-      <c r="C15" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
       </c>
       <c r="J16"/>
       <c r="Q16" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C17" t="s">
+        <v>497</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
         <v>498</v>
       </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="Q17" t="s">
         <v>499</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>511</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J18" t="s">
         <v>512</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="J18" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>513</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J19" t="s">
         <v>514</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="J19" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>515</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J20" t="s">
         <v>516</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="J20" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>517</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J21" t="s">
         <v>518</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="J21" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>520</v>
+      </c>
+      <c r="C23" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q23" t="s">
         <v>521</v>
-      </c>
-      <c r="C23" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -10791,7 +10812,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -10804,7 +10825,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10815,10 +10836,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10829,10 +10850,21 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D3" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -10844,16 +10876,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10864,25 +10901,28 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G2" t="s">
         <v>526</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>527</v>
       </c>
-      <c r="H2" t="s">
-        <v>528</v>
-      </c>
       <c r="I2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+      <c r="J2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10907,24 +10947,27 @@
       <c r="H3" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C5" t="s">
         <v>529</v>
-      </c>
-      <c r="C5" t="s">
-        <v>530</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -10933,7 +10976,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>531</v>
+        <v>588</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -10960,34 +11006,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D1" t="s">
         <v>532</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>533</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>534</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>535</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>536</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>537</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>538</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>539</v>
-      </c>
-      <c r="K1" t="s">
-        <v>540</v>
-      </c>
-      <c r="L1" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10995,34 +11041,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D2" t="s">
         <v>542</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>543</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>544</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>545</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>546</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>547</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>548</v>
       </c>
-      <c r="I2" t="s">
-        <v>549</v>
-      </c>
-      <c r="J2" t="s">
-        <v>550</v>
-      </c>
       <c r="K2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -11039,7 +11085,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -11068,13 +11114,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -11088,13 +11134,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B5" t="s">
+        <v>550</v>
+      </c>
+      <c r="E5" t="s">
         <v>552</v>
-      </c>
-      <c r="E5" t="s">
-        <v>554</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -11108,13 +11154,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -11128,13 +11174,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B7" t="s">
+        <v>553</v>
+      </c>
+      <c r="E7" t="s">
         <v>555</v>
-      </c>
-      <c r="E7" t="s">
-        <v>557</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -11148,10 +11194,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -11190,28 +11236,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C2" t="s">
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -11240,7 +11286,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -11274,89 +11320,89 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>570</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>578</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413049C4-4A0C-4CA8-9105-922B68BF19A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349F98CD-E3A9-40F8-9A77-47B7E7FEF888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="585">
   <si>
     <t>Id</t>
   </si>
@@ -1452,9 +1452,6 @@
     <t>#注意！！！技能的优先顺序是按照此表的顺序来的，排越靠下优先级越高#</t>
   </si>
   <si>
-    <t>干员链式弹道索敌</t>
-  </si>
-  <si>
     <t>普通技能</t>
   </si>
   <si>
@@ -1464,12 +1461,6 @@
     <t>被动</t>
   </si>
   <si>
-    <t>放置降序</t>
-  </si>
-  <si>
-    <t>0,0#-1,-1#0,-1#1,-1#-1,0#1,0#-1,1#0,1#1,1</t>
-  </si>
-  <si>
     <t>干员m3攻击</t>
   </si>
   <si>
@@ -1494,9 +1485,6 @@
     <t>m3自身攻速</t>
   </si>
   <si>
-    <t>M3链式弹道</t>
-  </si>
-  <si>
     <t>Muzzle</t>
   </si>
   <si>
@@ -1891,12 +1879,6 @@
   </si>
   <si>
     <t>EffectBase</t>
-  </si>
-  <si>
-    <t>链式弹道</t>
-  </si>
-  <si>
-    <t>frostl_attack_01_trail</t>
   </si>
   <si>
     <t>模型</t>
@@ -2097,27 +2079,15 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>M3链奶衰减</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>链奶伤害衰减</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"Rate":0.8}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":4,"SkillId":"干员链式弹道索敌","CanBack":"false"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>地面m3落地无敌,地面m3释放buff</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>地面m3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用链奶弹道</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3588,10 +3558,10 @@
         <v>130</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -6634,10 +6604,10 @@
         <v>194</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="AT1" t="s">
         <v>195</v>
@@ -6969,10 +6939,10 @@
         <v>296</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="AT2" t="s">
         <v>297</v>
@@ -7307,10 +7277,10 @@
         <v>2</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="AT3" t="s">
         <v>369</v>
@@ -7522,54 +7492,30 @@
         <v>380</v>
       </c>
     </row>
-    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C5" t="s">
-        <v>382</v>
-      </c>
-      <c r="J5" t="s">
-        <v>383</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="O5"/>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>385</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>386</v>
-      </c>
-    </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C6" t="s">
+        <v>381</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="S6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
         <v>387</v>
       </c>
-      <c r="C6" t="s">
-        <v>382</v>
-      </c>
-      <c r="K6" s="9" t="s">
+      <c r="AT6" t="s">
         <v>388</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="S6" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>390</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>391</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -7584,58 +7530,58 @@
         <v>1</v>
       </c>
       <c r="BP6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="CB6" t="s">
         <v>57</v>
       </c>
       <c r="CG6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P7"/>
       <c r="AC7">
         <v>1</v>
       </c>
       <c r="AO7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AT7" t="s">
+        <v>388</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="s">
         <v>391</v>
       </c>
-      <c r="AY7">
-        <v>1</v>
-      </c>
-      <c r="AZ7">
-        <v>1</v>
-      </c>
-      <c r="BD7">
-        <v>1</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>394</v>
-      </c>
-      <c r="CH7" t="s">
-        <v>395</v>
+      <c r="CH7" s="1" t="s">
+        <v>584</v>
       </c>
       <c r="CI7" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="CN7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CO7">
         <v>22</v>
@@ -7644,21 +7590,21 @@
         <v>10</v>
       </c>
       <c r="CY7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C8" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AC8">
         <v>1</v>
@@ -7667,14 +7613,14 @@
         <v>1</v>
       </c>
       <c r="AG8" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD8">
         <v>1</v>
       </c>
       <c r="CL8" s="9"/>
       <c r="CU8" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="DD8">
         <v>1</v>
@@ -7688,19 +7634,19 @@
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="M9"/>
       <c r="N9"/>
@@ -7718,16 +7664,16 @@
         <v>1</v>
       </c>
       <c r="AG9" t="s">
+        <v>398</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>401</v>
+      </c>
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="s">
         <v>402</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>405</v>
-      </c>
-      <c r="BD9">
-        <v>1</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>406</v>
       </c>
       <c r="BU9" s="14"/>
       <c r="BV9" s="14"/>
@@ -7737,7 +7683,7 @@
       <c r="BZ9" s="14"/>
       <c r="CA9"/>
       <c r="CN9" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="CO9">
         <v>8</v>
@@ -7751,10 +7697,10 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -7777,7 +7723,7 @@
         <v>1</v>
       </c>
       <c r="AT10" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BD10">
         <v>99</v>
@@ -7793,7 +7739,7 @@
       <c r="BZ10" s="14"/>
       <c r="CA10"/>
       <c r="CN10" s="12" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="CO10">
         <v>0.2</v>
@@ -7807,22 +7753,22 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AY11" s="9"/>
       <c r="BD11">
@@ -7846,7 +7792,7 @@
       <c r="CL11" s="9"/>
       <c r="CM11" s="9"/>
       <c r="CN11" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CR11">
         <v>99999</v>
@@ -7854,10 +7800,10 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -7896,7 +7842,7 @@
       <c r="CL12" s="9"/>
       <c r="CM12" s="9"/>
       <c r="CN12" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="CR12">
         <v>0.2</v>
@@ -7904,21 +7850,21 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M13"/>
       <c r="N13"/>
       <c r="P13" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="R13" s="12"/>
       <c r="S13"/>
@@ -7927,10 +7873,10 @@
         <v>1</v>
       </c>
       <c r="AG13" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AT13" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -7938,7 +7884,7 @@
       <c r="BV13"/>
       <c r="CB13" s="10"/>
       <c r="CN13" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CO13">
         <v>22</v>
@@ -7958,28 +7904,28 @@
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D17" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E17" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F17" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="J17" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M17"/>
       <c r="O17"/>
@@ -7987,16 +7933,16 @@
         <v>1</v>
       </c>
       <c r="AG17" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD17">
         <v>1</v>
       </c>
       <c r="BO17" s="8" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="BP17" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="BT17">
         <v>30</v>
@@ -8011,10 +7957,10 @@
         <v>1</v>
       </c>
       <c r="BY17" s="10" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="CN17" s="12" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="CR17">
         <v>30</v>
@@ -8025,15 +7971,15 @@
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C18" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J18" s="9"/>
       <c r="M18"/>
       <c r="O18" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
@@ -8044,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="AO18" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AQ18" t="s">
         <v>144</v>
@@ -8062,22 +8008,22 @@
         <v>1</v>
       </c>
       <c r="BP18" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="CB18" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="CG18" t="s">
-        <v>393</v>
-      </c>
-      <c r="CH18" t="s">
-        <v>395</v>
+        <v>390</v>
+      </c>
+      <c r="CH18" s="1" t="s">
+        <v>584</v>
       </c>
       <c r="CI18" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="CN18" s="8" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="CO18">
         <v>22</v>
@@ -8089,21 +8035,21 @@
         <v>10</v>
       </c>
       <c r="CY18" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M19"/>
       <c r="AC19">
@@ -8116,13 +8062,13 @@
         <v>144</v>
       </c>
       <c r="AO19" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AT19" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AX19" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AZ19">
         <v>1</v>
@@ -8135,13 +8081,13 @@
       </c>
       <c r="CB19" s="3"/>
       <c r="CH19" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="CI19" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="CN19" s="12" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="CR19">
         <v>0.1</v>
@@ -8155,20 +8101,20 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M20"/>
       <c r="O20" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="P20"/>
       <c r="Q20"/>
@@ -8176,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="AG20" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AW20">
         <v>1</v>
@@ -8185,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="CN20" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="CO20">
         <v>22</v>
@@ -8199,17 +8145,17 @@
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C21" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="M21"/>
       <c r="O21" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
@@ -8220,7 +8166,7 @@
         <v>144</v>
       </c>
       <c r="AT21" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="BD21">
         <v>1</v>
@@ -8229,7 +8175,7 @@
         <v>0.1</v>
       </c>
       <c r="CN21" s="12" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="CR21">
         <v>0.2</v>
@@ -8237,23 +8183,23 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C22" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M22"/>
       <c r="AC22">
         <v>1</v>
       </c>
       <c r="AG22" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AY22" s="9"/>
       <c r="BD22">
@@ -8275,7 +8221,7 @@
       <c r="CJ22" s="9"/>
       <c r="CK22" s="9"/>
       <c r="CN22" s="12" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="CR22">
         <v>40</v>
@@ -8289,20 +8235,20 @@
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C23" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="M23"/>
       <c r="O23" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AC23">
         <v>1</v>
@@ -8314,21 +8260,21 @@
         <v>99</v>
       </c>
       <c r="CM23" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C24" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M24"/>
       <c r="N24"/>
@@ -8336,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="AG24" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD24">
         <v>1</v>
@@ -8346,10 +8292,10 @@
       </c>
       <c r="BV24"/>
       <c r="CB24" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="CG24" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="CI24" s="9"/>
       <c r="CJ24" s="9"/>
@@ -8365,19 +8311,19 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C25" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="M25"/>
       <c r="N25"/>
@@ -8385,7 +8331,7 @@
         <v>1</v>
       </c>
       <c r="AG25" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD25">
         <v>1</v>
@@ -8395,10 +8341,10 @@
       </c>
       <c r="BV25"/>
       <c r="CB25" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="CG25" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="CJ25" s="9"/>
       <c r="DD25">
@@ -8413,19 +8359,19 @@
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C26" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D26" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E26" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F26" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G26">
         <v>3</v>
@@ -8435,19 +8381,19 @@
       </c>
       <c r="M26"/>
       <c r="O26" s="12" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AC26">
         <v>1</v>
       </c>
       <c r="AG26" s="8" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AO26" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AT26" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AY26">
         <v>1</v>
@@ -8464,17 +8410,17 @@
         <v>0.1</v>
       </c>
       <c r="CG26" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="CH26" t="s">
-        <v>395</v>
+        <v>390</v>
+      </c>
+      <c r="CH26" s="1" t="s">
+        <v>584</v>
       </c>
       <c r="CI26" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="CM26" s="8"/>
       <c r="CN26" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="CO26">
         <v>22</v>
@@ -8486,7 +8432,7 @@
         <v>10</v>
       </c>
       <c r="CY26" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="DD26">
         <v>1</v>
@@ -8498,31 +8444,31 @@
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C28" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D28" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E28" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F28" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G28">
         <v>3</v>
       </c>
       <c r="J28" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="O28" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="W28"/>
       <c r="X28"/>
@@ -8530,16 +8476,16 @@
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD28">
         <v>1</v>
       </c>
       <c r="BO28" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="BP28" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="BT28">
         <v>1</v>
@@ -8554,13 +8500,13 @@
         <v>1</v>
       </c>
       <c r="BY28" s="10" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="CN28" s="12" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="CO28" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="CR28">
         <v>25</v>
@@ -8568,17 +8514,17 @@
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C29" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="M29"/>
       <c r="O29" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="P29"/>
       <c r="Q29"/>
@@ -8586,10 +8532,10 @@
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AT29" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD29">
         <v>1</v>
@@ -8598,7 +8544,7 @@
         <v>0.1</v>
       </c>
       <c r="CN29" s="12" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="CR29">
         <v>0.2</v>
@@ -8606,19 +8552,19 @@
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C30" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="I30">
         <v>1</v>
       </c>
       <c r="J30" t="s">
+        <v>382</v>
+      </c>
+      <c r="K30" s="9" t="s">
         <v>383</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>384</v>
       </c>
       <c r="AC30">
         <v>1</v>
@@ -8627,7 +8573,7 @@
         <v>144</v>
       </c>
       <c r="AT30" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="BD30">
         <v>1</v>
@@ -8637,24 +8583,24 @@
       </c>
       <c r="CL30" s="9"/>
       <c r="CU30" s="1" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C31" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I31">
         <v>1</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="M31"/>
       <c r="N31"/>
@@ -8662,7 +8608,7 @@
         <v>1</v>
       </c>
       <c r="AG31" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD31">
         <v>1</v>
@@ -8672,10 +8618,10 @@
       </c>
       <c r="BV31"/>
       <c r="CB31" s="15" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="CG31" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="CJ31" s="9"/>
       <c r="DD31">
@@ -8690,16 +8636,16 @@
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C32" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M32"/>
       <c r="N32"/>
@@ -8707,7 +8653,7 @@
         <v>1</v>
       </c>
       <c r="AG32" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD32">
         <v>1</v>
@@ -8717,10 +8663,10 @@
       </c>
       <c r="BV32"/>
       <c r="CB32" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="CG32" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="CI32" s="9"/>
       <c r="CJ32" s="9"/>
@@ -8736,28 +8682,28 @@
     </row>
     <row r="34" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C34" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D34" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E34" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F34" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G34">
         <v>3</v>
       </c>
       <c r="J34" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O34"/>
       <c r="W34"/>
@@ -8766,13 +8712,13 @@
         <v>1</v>
       </c>
       <c r="AG34" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD34">
         <v>1</v>
       </c>
       <c r="BO34" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="BT34">
         <v>25</v>
@@ -8787,13 +8733,13 @@
         <v>1</v>
       </c>
       <c r="BY34" s="10" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="CN34" s="12" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="CO34" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="CP34">
         <v>80</v>
@@ -8804,64 +8750,64 @@
     </row>
     <row r="35" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C35" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="X35"/>
       <c r="AC35">
         <v>2</v>
       </c>
       <c r="AO35" t="s">
+        <v>460</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>404</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>426</v>
+      </c>
+      <c r="AZ35">
+        <v>1</v>
+      </c>
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="s">
+        <v>461</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>462</v>
+      </c>
+      <c r="CG35" t="s">
+        <v>390</v>
+      </c>
+      <c r="CX35" t="s">
+        <v>463</v>
+      </c>
+      <c r="CY35" t="s">
         <v>464</v>
-      </c>
-      <c r="AT35" t="s">
-        <v>408</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>430</v>
-      </c>
-      <c r="AZ35">
-        <v>1</v>
-      </c>
-      <c r="BD35">
-        <v>1</v>
-      </c>
-      <c r="BP35" t="s">
-        <v>465</v>
-      </c>
-      <c r="CB35" t="s">
-        <v>466</v>
-      </c>
-      <c r="CG35" t="s">
-        <v>393</v>
-      </c>
-      <c r="CX35" t="s">
-        <v>467</v>
-      </c>
-      <c r="CY35" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="36" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C36" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I36">
         <v>1</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P36"/>
       <c r="Q36"/>
@@ -8870,13 +8816,13 @@
         <v>1</v>
       </c>
       <c r="AG36" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AH36">
         <v>1</v>
       </c>
       <c r="AO36" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AV36">
         <v>1</v>
@@ -8890,14 +8836,14 @@
       <c r="BD36">
         <v>1</v>
       </c>
-      <c r="CH36" t="s">
-        <v>395</v>
+      <c r="CH36" s="1" t="s">
+        <v>584</v>
       </c>
       <c r="CI36" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="CN36" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CO36">
         <v>22</v>
@@ -8908,57 +8854,57 @@
     </row>
     <row r="37" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C37" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AC37">
         <v>1</v>
       </c>
       <c r="AG37" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD37">
         <v>1</v>
       </c>
       <c r="CU37" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C38" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AC38">
         <v>1</v>
       </c>
       <c r="AG38" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BD38">
         <v>1</v>
       </c>
       <c r="CN38" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="CR38">
         <v>0.5</v>
@@ -8966,10 +8912,10 @@
     </row>
     <row r="39" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C39" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -8990,7 +8936,7 @@
         <v>0.1</v>
       </c>
       <c r="CN39" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="CR39">
         <v>0.5</v>
@@ -10381,37 +10327,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>470</v>
+      </c>
+      <c r="F1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G1" t="s">
+        <v>472</v>
+      </c>
+      <c r="H1" t="s">
+        <v>473</v>
+      </c>
+      <c r="I1" t="s">
         <v>474</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>475</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>476</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>477</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>478</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>479</v>
       </c>
-      <c r="L1" t="s">
-        <v>480</v>
-      </c>
-      <c r="M1" t="s">
-        <v>481</v>
-      </c>
-      <c r="N1" t="s">
-        <v>482</v>
-      </c>
-      <c r="O1" t="s">
-        <v>483</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10425,40 +10371,40 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F2" t="s">
+        <v>481</v>
+      </c>
+      <c r="G2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I2" t="s">
         <v>484</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>485</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>486</v>
-      </c>
-      <c r="H2" t="s">
-        <v>487</v>
-      </c>
-      <c r="I2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J2" t="s">
-        <v>489</v>
-      </c>
-      <c r="K2" t="s">
-        <v>490</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="N2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="O2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="Q2" t="s">
         <v>348</v>
@@ -10516,92 +10462,92 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="Q4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C5" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="Q5" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C6" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="Q6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C7" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="Q7" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C9" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -10610,15 +10556,15 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C10" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -10627,15 +10573,15 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -10644,24 +10590,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C12" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -10670,10 +10616,10 @@
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -10682,122 +10628,122 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C15" t="s">
         <v>230</v>
       </c>
       <c r="Q15" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
       </c>
       <c r="J16"/>
       <c r="Q16" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C17" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="Q17" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J18" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J19" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J20" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J21" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C23" t="s">
         <v>230</v>
       </c>
       <c r="Q23" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C24" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -10812,7 +10758,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -10825,7 +10771,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10836,7 +10782,7 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D2" t="s">
         <v>348</v>
@@ -10854,17 +10800,6 @@
       </c>
       <c r="D3" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -10876,7 +10811,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -10901,19 +10836,19 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="G2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="I2" t="s">
         <v>337</v>
@@ -10958,29 +10893,6 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>395</v>
-      </c>
-      <c r="B5" t="s">
-        <v>528</v>
-      </c>
-      <c r="C5" t="s">
-        <v>529</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>591</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -11006,34 +10918,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H1" t="s">
+        <v>529</v>
+      </c>
+      <c r="I1" t="s">
         <v>530</v>
       </c>
-      <c r="C1" t="s">
+      <c r="J1" t="s">
         <v>531</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
         <v>532</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>533</v>
-      </c>
-      <c r="F1" t="s">
-        <v>534</v>
-      </c>
-      <c r="H1" t="s">
-        <v>535</v>
-      </c>
-      <c r="I1" t="s">
-        <v>536</v>
-      </c>
-      <c r="J1" t="s">
-        <v>537</v>
-      </c>
-      <c r="K1" t="s">
-        <v>538</v>
-      </c>
-      <c r="L1" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -11041,34 +10953,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F2" t="s">
+        <v>538</v>
+      </c>
+      <c r="G2" t="s">
+        <v>539</v>
+      </c>
+      <c r="H2" t="s">
         <v>540</v>
       </c>
-      <c r="C2" t="s">
+      <c r="I2" t="s">
         <v>541</v>
       </c>
-      <c r="D2" t="s">
+      <c r="J2" t="s">
         <v>542</v>
       </c>
-      <c r="E2" t="s">
-        <v>543</v>
-      </c>
-      <c r="F2" t="s">
-        <v>544</v>
-      </c>
-      <c r="G2" t="s">
-        <v>545</v>
-      </c>
-      <c r="H2" t="s">
-        <v>546</v>
-      </c>
-      <c r="I2" t="s">
-        <v>547</v>
-      </c>
-      <c r="J2" t="s">
-        <v>548</v>
-      </c>
       <c r="K2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -11085,7 +10997,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -11114,13 +11026,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B4" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E4" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -11134,13 +11046,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B5" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E5" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -11154,13 +11066,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B6" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E6" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -11174,13 +11086,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B7" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E7" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -11194,10 +11106,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B8" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -11242,22 +11154,22 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="E2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="H2" t="s">
         <v>288</v>
       </c>
       <c r="I2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -11286,7 +11198,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -11320,89 +11232,89 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>564</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349F98CD-E3A9-40F8-9A77-47B7E7FEF888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB195A7-D204-4A1C-AD60-8C7202BCC9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="586">
   <si>
     <t>Id</t>
   </si>
@@ -388,12 +388,6 @@
     <t>高度</t>
   </si>
   <si>
-    <t>高台单位？</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
     <t>阻挡个数</t>
   </si>
   <si>
@@ -548,12 +542,6 @@
   </si>
   <si>
     <t>Height</t>
-  </si>
-  <si>
-    <t>CanSetHigh</t>
-  </si>
-  <si>
-    <t>CanSetGround</t>
   </si>
   <si>
     <t>StopCount</t>
@@ -2088,6 +2076,26 @@
   </si>
   <si>
     <t>通用链奶弹道</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>可部署位</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>高台位</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面位</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2654,7 +2662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS590"/>
+  <dimension ref="A1:BR590"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2684,22 +2692,22 @@
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="34.5" customWidth="1"/>
     <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.5" customWidth="1"/>
+    <col min="49" max="49" width="24.33203125" customWidth="1"/>
+    <col min="51" max="51" width="17.75" customWidth="1"/>
+    <col min="52" max="52" width="7.83203125" customWidth="1"/>
+    <col min="55" max="55" width="24.25" customWidth="1"/>
+    <col min="56" max="56" width="13.25" customWidth="1"/>
+    <col min="57" max="57" width="16.08203125" customWidth="1"/>
+    <col min="58" max="58" width="8" customWidth="1"/>
+    <col min="63" max="63" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="14" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2775,274 +2783,268 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="AN1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="8" t="s">
+      <c r="BC1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="AN2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AO2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>84</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>85</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>86</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>87</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>91</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>93</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>94</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>95</v>
       </c>
-      <c r="AZ2" s="8" t="s">
+      <c r="BC2" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>97</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>98</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>99</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>100</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>107</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
         <v>108</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BP2" t="s">
         <v>109</v>
       </c>
-      <c r="BN2" s="8" t="s">
+      <c r="BQ2" t="s">
         <v>110</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>111</v>
       </c>
-      <c r="BP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3050,88 +3052,88 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="R3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="S3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="W3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Y3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Z3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AA3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AB3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AC3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AE3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AF3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
         <v>2</v>
@@ -3140,61 +3142,61 @@
         <v>2</v>
       </c>
       <c r="AI3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU3" t="s">
         <v>116</v>
       </c>
-      <c r="AN3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AW3" t="s">
         <v>117</v>
       </c>
       <c r="AX3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AZ3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="BC3" t="s">
         <v>2</v>
@@ -3206,60 +3208,57 @@
         <v>2</v>
       </c>
       <c r="BF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>118</v>
-      </c>
       <c r="BI3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>124</v>
-      </c>
       <c r="BK3" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="BL3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BN3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BO3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BP3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F5" t="str">
         <f>"char_"&amp;E5&amp;"_"&amp;D5</f>
@@ -3305,87 +3304,87 @@
         <v>1</v>
       </c>
       <c r="AG5" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>127</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="AN5">
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <v>0.5</v>
+      </c>
+      <c r="AV5">
+        <v>0.25</v>
+      </c>
+      <c r="BA5" t="s">
         <v>129</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="BB5" t="s">
         <v>130</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="BC5" t="s">
         <v>131</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="BD5" t="s">
         <v>132</v>
       </c>
-      <c r="AM5">
-        <v>1</v>
-      </c>
-      <c r="AO5">
-        <v>1</v>
-      </c>
-      <c r="AP5">
-        <v>0.5</v>
-      </c>
-      <c r="AW5">
-        <v>0.25</v>
-      </c>
-      <c r="BB5" t="s">
+      <c r="BE5" t="s">
         <v>133</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BF5" t="s">
         <v>134</v>
       </c>
-      <c r="BD5" t="s">
+      <c r="BG5">
+        <v>6</v>
+      </c>
+      <c r="BH5" t="s">
         <v>135</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BI5" t="s">
         <v>136</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BL5" t="s">
         <v>137</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BM5" t="s">
         <v>138</v>
       </c>
-      <c r="BH5">
-        <v>6</v>
-      </c>
-      <c r="BI5" t="s">
+      <c r="BO5" t="s">
         <v>139</v>
       </c>
-      <c r="BJ5" t="s">
+      <c r="BP5" t="s">
+        <v>139</v>
+      </c>
+      <c r="BR5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>140</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
         <v>141</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="E6" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="BP5" t="s">
+      <c r="F6" t="s">
         <v>143</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" t="s">
-        <v>147</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3430,80 +3429,80 @@
         <v>-1</v>
       </c>
       <c r="AG6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI6" t="s">
         <v>144</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>148</v>
       </c>
       <c r="AK6">
         <v>0</v>
       </c>
+      <c r="AM6" s="1" t="s">
+        <v>585</v>
+      </c>
       <c r="AN6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>149</v>
-      </c>
-      <c r="AW6">
+      <c r="AU6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AV6">
         <v>0.25</v>
       </c>
-      <c r="BB6" t="s">
-        <v>133</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>150</v>
-      </c>
-      <c r="BE6" t="str">
+      <c r="BA6" t="s">
+        <v>129</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>146</v>
+      </c>
+      <c r="BD6" t="str">
         <f>"half_"&amp;D6</f>
         <v>half_otter</v>
       </c>
-      <c r="BF6" t="str">
+      <c r="BE6" t="str">
         <f>D6</f>
         <v>otter</v>
       </c>
-      <c r="BG6" t="s">
+      <c r="BF6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BG6">
+        <v>6</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>147</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BM6" t="s">
         <v>138</v>
       </c>
-      <c r="BH6">
-        <v>6</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>151</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>144</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>142</v>
-      </c>
-      <c r="BS6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BR6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F7" t="str">
         <f>"char_"&amp;E7&amp;"_"&amp;D7</f>
@@ -3552,2474 +3551,2474 @@
         <v>1</v>
       </c>
       <c r="AG7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="AN7">
+        <v>3</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0.25</v>
+      </c>
+      <c r="BA7" t="s">
         <v>129</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="BB7" t="s">
         <v>130</v>
       </c>
-      <c r="AI7" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="AN7">
-        <v>1</v>
-      </c>
-      <c r="AO7">
-        <v>3</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0.25</v>
-      </c>
-      <c r="BB7" t="s">
+      <c r="BC7" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE7" t="s">
         <v>133</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BF7" t="s">
         <v>134</v>
       </c>
-      <c r="BD7" t="s">
+      <c r="BG7">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="s">
         <v>135</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BI7" t="s">
         <v>136</v>
       </c>
-      <c r="BF7" t="s">
-        <v>137</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH7">
-        <v>6</v>
-      </c>
-      <c r="BI7" t="s">
+      <c r="BL7" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BM7" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BO7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="BP7" t="s">
         <v>139</v>
       </c>
-      <c r="BJ7" t="s">
-        <v>140</v>
-      </c>
-      <c r="BM7" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="BN7" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="BP7" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="4:70" x14ac:dyDescent="0.25">
+      <c r="BR7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI17" s="8"/>
     </row>
-    <row r="23" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI23" s="8"/>
-      <c r="BK23" s="8"/>
-    </row>
-    <row r="25" spans="4:70" x14ac:dyDescent="0.25">
+      <c r="BJ23" s="8"/>
+    </row>
+    <row r="25" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI25" s="8"/>
     </row>
-    <row r="26" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI26" s="8"/>
     </row>
-    <row r="27" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:69" x14ac:dyDescent="0.25">
       <c r="AI27" s="8"/>
-      <c r="BK27" s="8"/>
-    </row>
-    <row r="28" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BJ27" s="8"/>
+    </row>
+    <row r="28" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D28" s="18"/>
       <c r="E28" s="5"/>
-      <c r="BO28" s="6"/>
-      <c r="BR28" s="6"/>
-    </row>
-    <row r="29" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN28" s="6"/>
+      <c r="BQ28" s="6"/>
+    </row>
+    <row r="29" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D29" s="18"/>
       <c r="E29" s="5"/>
-      <c r="BO29" s="6"/>
-      <c r="BR29" s="6"/>
-    </row>
-    <row r="30" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN29" s="6"/>
+      <c r="BQ29" s="6"/>
+    </row>
+    <row r="30" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D30" s="18"/>
       <c r="E30" s="5"/>
-      <c r="BO30" s="6"/>
-      <c r="BR30" s="6"/>
-    </row>
-    <row r="31" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN30" s="6"/>
+      <c r="BQ30" s="6"/>
+    </row>
+    <row r="31" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D31" s="18"/>
       <c r="E31" s="5"/>
-      <c r="BO31" s="6"/>
-      <c r="BR31" s="6"/>
-    </row>
-    <row r="32" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN31" s="6"/>
+      <c r="BQ31" s="6"/>
+    </row>
+    <row r="32" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D32" s="18"/>
       <c r="E32" s="5"/>
-      <c r="BO32" s="6"/>
-      <c r="BR32" s="6"/>
-    </row>
-    <row r="33" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN32" s="6"/>
+      <c r="BQ32" s="6"/>
+    </row>
+    <row r="33" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D33" s="18"/>
       <c r="E33" s="5"/>
-      <c r="BO33" s="6"/>
-      <c r="BR33" s="6"/>
-    </row>
-    <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN33" s="6"/>
+      <c r="BQ33" s="6"/>
+    </row>
+    <row r="34" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D34" s="18"/>
       <c r="E34" s="5"/>
-      <c r="BO34" s="6"/>
-      <c r="BR34" s="6"/>
-    </row>
-    <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN34" s="6"/>
+      <c r="BQ34" s="6"/>
+    </row>
+    <row r="35" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D35" s="18"/>
       <c r="E35" s="5"/>
-      <c r="BR35" s="6"/>
-    </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ35" s="6"/>
+    </row>
+    <row r="36" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="18"/>
       <c r="E36" s="5"/>
-      <c r="BR36" s="6"/>
-    </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ36" s="6"/>
+    </row>
+    <row r="37" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="18"/>
       <c r="E37" s="5"/>
-      <c r="BR37" s="6"/>
-    </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ37" s="6"/>
+    </row>
+    <row r="38" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="18"/>
       <c r="E38" s="5"/>
-      <c r="BO38" s="6"/>
-      <c r="BR38" s="6"/>
-    </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN38" s="6"/>
+      <c r="BQ38" s="6"/>
+    </row>
+    <row r="39" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="18"/>
       <c r="E39" s="5"/>
-      <c r="BO39" s="6"/>
-      <c r="BR39" s="6"/>
-    </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN39" s="6"/>
+      <c r="BQ39" s="6"/>
+    </row>
+    <row r="40" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="18"/>
       <c r="E40" s="5"/>
-      <c r="BO40" s="6"/>
-      <c r="BR40" s="6"/>
-    </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN40" s="6"/>
+      <c r="BQ40" s="6"/>
+    </row>
+    <row r="41" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="18"/>
       <c r="E41" s="5"/>
-      <c r="BO41" s="6"/>
-      <c r="BR41" s="6"/>
-    </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN41" s="6"/>
+      <c r="BQ41" s="6"/>
+    </row>
+    <row r="42" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="18"/>
       <c r="E42" s="5"/>
-      <c r="BO42" s="6"/>
-      <c r="BR42" s="6"/>
-    </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN42" s="6"/>
+      <c r="BQ42" s="6"/>
+    </row>
+    <row r="43" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="18"/>
       <c r="E43" s="5"/>
-      <c r="BO43" s="6"/>
-      <c r="BR43" s="6"/>
-    </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN43" s="6"/>
+      <c r="BQ43" s="6"/>
+    </row>
+    <row r="44" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="18"/>
       <c r="E44" s="5"/>
-      <c r="BO44" s="6"/>
-      <c r="BR44" s="6"/>
-    </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN44" s="6"/>
+      <c r="BQ44" s="6"/>
+    </row>
+    <row r="45" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="18"/>
       <c r="E45" s="5"/>
-      <c r="BO45" s="6"/>
-      <c r="BR45" s="6"/>
-    </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN45" s="6"/>
+      <c r="BQ45" s="6"/>
+    </row>
+    <row r="46" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="18"/>
       <c r="E46" s="5"/>
-      <c r="BO46" s="6"/>
-      <c r="BR46" s="6"/>
-    </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN46" s="6"/>
+      <c r="BQ46" s="6"/>
+    </row>
+    <row r="47" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="18"/>
       <c r="E47" s="5"/>
-      <c r="BO47" s="6"/>
-      <c r="BR47" s="6"/>
-    </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN47" s="6"/>
+      <c r="BQ47" s="6"/>
+    </row>
+    <row r="48" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="18"/>
       <c r="E48" s="5"/>
-      <c r="BO48" s="6"/>
-      <c r="BR48" s="6"/>
-    </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN48" s="6"/>
+      <c r="BQ48" s="6"/>
+    </row>
+    <row r="49" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="18"/>
       <c r="E49" s="5"/>
-      <c r="BO49" s="6"/>
-      <c r="BR49" s="6"/>
-    </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN49" s="6"/>
+      <c r="BQ49" s="6"/>
+    </row>
+    <row r="50" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="18"/>
       <c r="E50" s="5"/>
-      <c r="BO50" s="6"/>
-      <c r="BR50" s="6"/>
-    </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN50" s="6"/>
+      <c r="BQ50" s="6"/>
+    </row>
+    <row r="51" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="18"/>
       <c r="E51" s="5"/>
-      <c r="BO51" s="6"/>
-      <c r="BR51" s="6"/>
-    </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN51" s="6"/>
+      <c r="BQ51" s="6"/>
+    </row>
+    <row r="52" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="18"/>
       <c r="E52" s="5"/>
-      <c r="BO52" s="6"/>
-      <c r="BR52" s="6"/>
-    </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN52" s="6"/>
+      <c r="BQ52" s="6"/>
+    </row>
+    <row r="53" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="18"/>
       <c r="E53" s="5"/>
-      <c r="BO53" s="6"/>
-      <c r="BR53" s="6"/>
-    </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN53" s="6"/>
+      <c r="BQ53" s="6"/>
+    </row>
+    <row r="54" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="18"/>
       <c r="E54" s="5"/>
-      <c r="BO54" s="6"/>
-      <c r="BR54" s="6"/>
-    </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN54" s="6"/>
+      <c r="BQ54" s="6"/>
+    </row>
+    <row r="55" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="18"/>
       <c r="E55" s="5"/>
-      <c r="BO55" s="6"/>
-      <c r="BR55" s="6"/>
-    </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN55" s="6"/>
+      <c r="BQ55" s="6"/>
+    </row>
+    <row r="56" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="18"/>
       <c r="E56" s="5"/>
-      <c r="BO56" s="6"/>
-      <c r="BR56" s="6"/>
-    </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN56" s="6"/>
+      <c r="BQ56" s="6"/>
+    </row>
+    <row r="57" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="18"/>
       <c r="E57" s="5"/>
-      <c r="BO57" s="6"/>
-      <c r="BR57" s="6"/>
-    </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN57" s="6"/>
+      <c r="BQ57" s="6"/>
+    </row>
+    <row r="58" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="18"/>
       <c r="E58" s="5"/>
-      <c r="BO58" s="6"/>
-      <c r="BR58" s="6"/>
-    </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN58" s="6"/>
+      <c r="BQ58" s="6"/>
+    </row>
+    <row r="59" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="18"/>
       <c r="E59" s="5"/>
-      <c r="BO59" s="6"/>
-      <c r="BR59" s="6"/>
-    </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN59" s="6"/>
+      <c r="BQ59" s="6"/>
+    </row>
+    <row r="60" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="18"/>
       <c r="E60" s="5"/>
-      <c r="BO60" s="6"/>
-      <c r="BR60" s="6"/>
-    </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN60" s="6"/>
+      <c r="BQ60" s="6"/>
+    </row>
+    <row r="61" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="18"/>
       <c r="E61" s="5"/>
-      <c r="BO61" s="6"/>
-      <c r="BR61" s="6"/>
-    </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN61" s="6"/>
+      <c r="BQ61" s="6"/>
+    </row>
+    <row r="62" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="18"/>
       <c r="E62" s="5"/>
-      <c r="BO62" s="6"/>
-      <c r="BR62" s="6"/>
-    </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN62" s="6"/>
+      <c r="BQ62" s="6"/>
+    </row>
+    <row r="63" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="18"/>
       <c r="E63" s="5"/>
-      <c r="BO63" s="6"/>
-      <c r="BR63" s="6"/>
-    </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN63" s="6"/>
+      <c r="BQ63" s="6"/>
+    </row>
+    <row r="64" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="18"/>
       <c r="E64" s="5"/>
-      <c r="BO64" s="6"/>
-      <c r="BR64" s="6"/>
-    </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN64" s="6"/>
+      <c r="BQ64" s="6"/>
+    </row>
+    <row r="65" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="18"/>
       <c r="E65" s="5"/>
-      <c r="BO65" s="6"/>
-      <c r="BR65" s="6"/>
-    </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN65" s="6"/>
+      <c r="BQ65" s="6"/>
+    </row>
+    <row r="66" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="18"/>
       <c r="E66" s="5"/>
-      <c r="BO66" s="6"/>
-      <c r="BR66" s="6"/>
-    </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN66" s="6"/>
+      <c r="BQ66" s="6"/>
+    </row>
+    <row r="67" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="18"/>
       <c r="E67" s="5"/>
-      <c r="BO67" s="6"/>
-      <c r="BR67" s="6"/>
-    </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN67" s="6"/>
+      <c r="BQ67" s="6"/>
+    </row>
+    <row r="68" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="18"/>
       <c r="E68" s="5"/>
-      <c r="BO68" s="6"/>
-      <c r="BR68" s="6"/>
-    </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN68" s="6"/>
+      <c r="BQ68" s="6"/>
+    </row>
+    <row r="69" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="18"/>
       <c r="E69" s="5"/>
-      <c r="BO69" s="6"/>
-      <c r="BR69" s="6"/>
-    </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN69" s="6"/>
+      <c r="BQ69" s="6"/>
+    </row>
+    <row r="70" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="18"/>
       <c r="E70" s="5"/>
-      <c r="BO70" s="6"/>
-      <c r="BR70" s="6"/>
-    </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN70" s="6"/>
+      <c r="BQ70" s="6"/>
+    </row>
+    <row r="71" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="18"/>
       <c r="E71" s="5"/>
-      <c r="BO71" s="6"/>
-      <c r="BR71" s="6"/>
-    </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN71" s="6"/>
+      <c r="BQ71" s="6"/>
+    </row>
+    <row r="72" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="18"/>
       <c r="E72" s="5"/>
-      <c r="BO72" s="6"/>
-      <c r="BR72" s="6"/>
-    </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN72" s="6"/>
+      <c r="BQ72" s="6"/>
+    </row>
+    <row r="73" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="18"/>
       <c r="E73" s="5"/>
-      <c r="BO73" s="6"/>
-      <c r="BR73" s="6"/>
-    </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN73" s="6"/>
+      <c r="BQ73" s="6"/>
+    </row>
+    <row r="74" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="18"/>
       <c r="E74" s="5"/>
-      <c r="BO74" s="6"/>
-      <c r="BR74" s="6"/>
-    </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN74" s="6"/>
+      <c r="BQ74" s="6"/>
+    </row>
+    <row r="75" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="18"/>
       <c r="E75" s="5"/>
-      <c r="BO75" s="6"/>
-      <c r="BR75" s="6"/>
-    </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN75" s="6"/>
+      <c r="BQ75" s="6"/>
+    </row>
+    <row r="76" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="18"/>
       <c r="E76" s="5"/>
-      <c r="BO76" s="6"/>
-      <c r="BR76" s="6"/>
-    </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN76" s="6"/>
+      <c r="BQ76" s="6"/>
+    </row>
+    <row r="77" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="18"/>
       <c r="E77" s="5"/>
-      <c r="BO77" s="6"/>
-      <c r="BR77" s="6"/>
-    </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN77" s="6"/>
+      <c r="BQ77" s="6"/>
+    </row>
+    <row r="78" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="18"/>
       <c r="E78" s="5"/>
-      <c r="BO78" s="6"/>
-      <c r="BR78" s="6"/>
-    </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN78" s="6"/>
+      <c r="BQ78" s="6"/>
+    </row>
+    <row r="79" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="18"/>
       <c r="E79" s="5"/>
-      <c r="BO79" s="6"/>
-      <c r="BR79" s="6"/>
-    </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN79" s="6"/>
+      <c r="BQ79" s="6"/>
+    </row>
+    <row r="80" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="18"/>
       <c r="E80" s="5"/>
-      <c r="BO80" s="6"/>
-      <c r="BR80" s="6"/>
-    </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN80" s="6"/>
+      <c r="BQ80" s="6"/>
+    </row>
+    <row r="81" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="18"/>
       <c r="E81" s="5"/>
-      <c r="BO81" s="6"/>
-      <c r="BR81" s="6"/>
-    </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN81" s="6"/>
+      <c r="BQ81" s="6"/>
+    </row>
+    <row r="82" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="18"/>
       <c r="E82" s="5"/>
-      <c r="BO82" s="6"/>
-      <c r="BR82" s="6"/>
-    </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN82" s="6"/>
+      <c r="BQ82" s="6"/>
+    </row>
+    <row r="83" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="18"/>
       <c r="E83" s="5"/>
-      <c r="BO83" s="6"/>
-      <c r="BR83" s="6"/>
-    </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN83" s="6"/>
+      <c r="BQ83" s="6"/>
+    </row>
+    <row r="84" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="18"/>
       <c r="E84" s="5"/>
-      <c r="BO84" s="6"/>
-      <c r="BR84" s="6"/>
-    </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN84" s="6"/>
+      <c r="BQ84" s="6"/>
+    </row>
+    <row r="85" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="18"/>
       <c r="E85" s="5"/>
-      <c r="BO85" s="6"/>
-      <c r="BR85" s="6"/>
-    </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN85" s="6"/>
+      <c r="BQ85" s="6"/>
+    </row>
+    <row r="86" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="18"/>
       <c r="E86" s="5"/>
-      <c r="BO86" s="6"/>
-      <c r="BR86" s="6"/>
-    </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN86" s="6"/>
+      <c r="BQ86" s="6"/>
+    </row>
+    <row r="87" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="18"/>
       <c r="E87" s="5"/>
-      <c r="BO87" s="6"/>
-      <c r="BR87" s="6"/>
-    </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN87" s="6"/>
+      <c r="BQ87" s="6"/>
+    </row>
+    <row r="88" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="18"/>
       <c r="E88" s="5"/>
-      <c r="BO88" s="6"/>
-      <c r="BR88" s="6"/>
-    </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN88" s="6"/>
+      <c r="BQ88" s="6"/>
+    </row>
+    <row r="89" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="18"/>
       <c r="E89" s="5"/>
-      <c r="BO89" s="6"/>
-      <c r="BR89" s="6"/>
-    </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN89" s="6"/>
+      <c r="BQ89" s="6"/>
+    </row>
+    <row r="90" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="18"/>
       <c r="E90" s="5"/>
-      <c r="BO90" s="6"/>
-      <c r="BR90" s="6"/>
-    </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN90" s="6"/>
+      <c r="BQ90" s="6"/>
+    </row>
+    <row r="91" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="18"/>
       <c r="E91" s="5"/>
-      <c r="BO91" s="6"/>
-      <c r="BR91" s="6"/>
-    </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN91" s="6"/>
+      <c r="BQ91" s="6"/>
+    </row>
+    <row r="92" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="18"/>
       <c r="E92" s="5"/>
-      <c r="BO92" s="6"/>
-      <c r="BR92" s="6"/>
-    </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN92" s="6"/>
+      <c r="BQ92" s="6"/>
+    </row>
+    <row r="93" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="18"/>
       <c r="E93" s="5"/>
-      <c r="BO93" s="6"/>
-      <c r="BR93" s="6"/>
-    </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN93" s="6"/>
+      <c r="BQ93" s="6"/>
+    </row>
+    <row r="94" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="18"/>
       <c r="E94" s="5"/>
-      <c r="BO94" s="6"/>
-      <c r="BR94" s="6"/>
-    </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN94" s="6"/>
+      <c r="BQ94" s="6"/>
+    </row>
+    <row r="95" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="18"/>
       <c r="E95" s="5"/>
-      <c r="BO95" s="6"/>
-      <c r="BR95" s="6"/>
-    </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN95" s="6"/>
+      <c r="BQ95" s="6"/>
+    </row>
+    <row r="96" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="18"/>
       <c r="E96" s="5"/>
-      <c r="BO96" s="6"/>
-      <c r="BR96" s="6"/>
-    </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN96" s="6"/>
+      <c r="BQ96" s="6"/>
+    </row>
+    <row r="97" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="18"/>
       <c r="E97" s="5"/>
-      <c r="BO97" s="6"/>
-      <c r="BR97" s="6"/>
-    </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN97" s="6"/>
+      <c r="BQ97" s="6"/>
+    </row>
+    <row r="98" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="18"/>
       <c r="E98" s="5"/>
-      <c r="BO98" s="6"/>
-      <c r="BR98" s="6"/>
-    </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN98" s="6"/>
+      <c r="BQ98" s="6"/>
+    </row>
+    <row r="99" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="18"/>
       <c r="E99" s="5"/>
-      <c r="BO99" s="6"/>
-      <c r="BR99" s="6"/>
-    </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN99" s="6"/>
+      <c r="BQ99" s="6"/>
+    </row>
+    <row r="100" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="18"/>
       <c r="E100" s="5"/>
-      <c r="BO100" s="6"/>
-      <c r="BR100" s="6"/>
-    </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN100" s="6"/>
+      <c r="BQ100" s="6"/>
+    </row>
+    <row r="101" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="18"/>
       <c r="E101" s="5"/>
-      <c r="BO101" s="6"/>
-      <c r="BR101" s="6"/>
-    </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN101" s="6"/>
+      <c r="BQ101" s="6"/>
+    </row>
+    <row r="102" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="18"/>
       <c r="E102" s="5"/>
-      <c r="BO102" s="6"/>
-      <c r="BR102" s="6"/>
-    </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN102" s="6"/>
+      <c r="BQ102" s="6"/>
+    </row>
+    <row r="103" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="18"/>
       <c r="E103" s="5"/>
-      <c r="BO103" s="6"/>
-      <c r="BR103" s="6"/>
-    </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN103" s="6"/>
+      <c r="BQ103" s="6"/>
+    </row>
+    <row r="104" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="18"/>
       <c r="E104" s="5"/>
-      <c r="BO104" s="6"/>
-      <c r="BR104" s="6"/>
-    </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN104" s="6"/>
+      <c r="BQ104" s="6"/>
+    </row>
+    <row r="105" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="18"/>
       <c r="E105" s="5"/>
-      <c r="BO105" s="6"/>
-      <c r="BR105" s="6"/>
-    </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN105" s="6"/>
+      <c r="BQ105" s="6"/>
+    </row>
+    <row r="106" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="18"/>
       <c r="E106" s="5"/>
-      <c r="BO106" s="6"/>
-      <c r="BR106" s="6"/>
-    </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN106" s="6"/>
+      <c r="BQ106" s="6"/>
+    </row>
+    <row r="107" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="18"/>
       <c r="E107" s="5"/>
-      <c r="BO107" s="6"/>
-      <c r="BR107" s="6"/>
-    </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN107" s="6"/>
+      <c r="BQ107" s="6"/>
+    </row>
+    <row r="108" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="18"/>
       <c r="E108" s="5"/>
-      <c r="BO108" s="6"/>
-      <c r="BR108" s="6"/>
-    </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN108" s="6"/>
+      <c r="BQ108" s="6"/>
+    </row>
+    <row r="109" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="18"/>
       <c r="E109" s="5"/>
-      <c r="BO109" s="6"/>
-      <c r="BR109" s="6"/>
-    </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN109" s="6"/>
+      <c r="BQ109" s="6"/>
+    </row>
+    <row r="110" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="18"/>
       <c r="E110" s="5"/>
-      <c r="BO110" s="6"/>
-      <c r="BR110" s="6"/>
-    </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN110" s="6"/>
+      <c r="BQ110" s="6"/>
+    </row>
+    <row r="111" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="18"/>
       <c r="E111" s="5"/>
-      <c r="BO111" s="6"/>
-      <c r="BR111" s="6"/>
-    </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN111" s="6"/>
+      <c r="BQ111" s="6"/>
+    </row>
+    <row r="112" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="18"/>
       <c r="E112" s="5"/>
-      <c r="BO112" s="6"/>
-      <c r="BR112" s="6"/>
-    </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN112" s="6"/>
+      <c r="BQ112" s="6"/>
+    </row>
+    <row r="113" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="18"/>
       <c r="E113" s="5"/>
-      <c r="BO113" s="6"/>
-      <c r="BR113" s="6"/>
-    </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN113" s="6"/>
+      <c r="BQ113" s="6"/>
+    </row>
+    <row r="114" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="18"/>
       <c r="E114" s="5"/>
-      <c r="BO114" s="6"/>
-      <c r="BR114" s="6"/>
-    </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN114" s="6"/>
+      <c r="BQ114" s="6"/>
+    </row>
+    <row r="115" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="18"/>
       <c r="E115" s="5"/>
-      <c r="BO115" s="6"/>
-      <c r="BR115" s="6"/>
-    </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN115" s="6"/>
+      <c r="BQ115" s="6"/>
+    </row>
+    <row r="116" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="18"/>
       <c r="E116" s="5"/>
-      <c r="BO116" s="6"/>
-      <c r="BR116" s="6"/>
-    </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN116" s="6"/>
+      <c r="BQ116" s="6"/>
+    </row>
+    <row r="117" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="18"/>
       <c r="E117" s="5"/>
-      <c r="BO117" s="6"/>
-      <c r="BR117" s="6"/>
-    </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN117" s="6"/>
+      <c r="BQ117" s="6"/>
+    </row>
+    <row r="118" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="18"/>
       <c r="E118" s="5"/>
-      <c r="BO118" s="6"/>
-      <c r="BR118" s="6"/>
-    </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN118" s="6"/>
+      <c r="BQ118" s="6"/>
+    </row>
+    <row r="119" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="18"/>
       <c r="E119" s="5"/>
-      <c r="BO119" s="6"/>
-      <c r="BR119" s="6"/>
-    </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN119" s="6"/>
+      <c r="BQ119" s="6"/>
+    </row>
+    <row r="120" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="18"/>
       <c r="E120" s="5"/>
-      <c r="BO120" s="6"/>
-      <c r="BR120" s="6"/>
-    </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN120" s="6"/>
+      <c r="BQ120" s="6"/>
+    </row>
+    <row r="121" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="18"/>
       <c r="E121" s="5"/>
-      <c r="BO121" s="6"/>
-      <c r="BR121" s="6"/>
-    </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN121" s="6"/>
+      <c r="BQ121" s="6"/>
+    </row>
+    <row r="122" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="18"/>
       <c r="E122" s="5"/>
-      <c r="BO122" s="6"/>
-      <c r="BR122" s="6"/>
-    </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN122" s="6"/>
+      <c r="BQ122" s="6"/>
+    </row>
+    <row r="123" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="18"/>
       <c r="E123" s="5"/>
-      <c r="BO123" s="6"/>
-      <c r="BR123" s="6"/>
-    </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN123" s="6"/>
+      <c r="BQ123" s="6"/>
+    </row>
+    <row r="124" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="18"/>
       <c r="E124" s="5"/>
-      <c r="BO124" s="6"/>
-      <c r="BR124" s="6"/>
-    </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN124" s="6"/>
+      <c r="BQ124" s="6"/>
+    </row>
+    <row r="125" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="18"/>
       <c r="E125" s="5"/>
-      <c r="BO125" s="6"/>
-      <c r="BR125" s="6"/>
-    </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN125" s="6"/>
+      <c r="BQ125" s="6"/>
+    </row>
+    <row r="126" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="18"/>
       <c r="E126" s="5"/>
-      <c r="BO126" s="6"/>
-      <c r="BR126" s="6"/>
-    </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN126" s="6"/>
+      <c r="BQ126" s="6"/>
+    </row>
+    <row r="127" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="18"/>
       <c r="E127" s="5"/>
-      <c r="BO127" s="6"/>
-      <c r="BR127" s="6"/>
-    </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN127" s="6"/>
+      <c r="BQ127" s="6"/>
+    </row>
+    <row r="128" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="18"/>
       <c r="E128" s="5"/>
-      <c r="BO128" s="6"/>
-      <c r="BR128" s="6"/>
-    </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN128" s="6"/>
+      <c r="BQ128" s="6"/>
+    </row>
+    <row r="129" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="18"/>
       <c r="E129" s="5"/>
-      <c r="BO129" s="6"/>
-      <c r="BR129" s="6"/>
-    </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN129" s="6"/>
+      <c r="BQ129" s="6"/>
+    </row>
+    <row r="130" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="18"/>
       <c r="E130" s="5"/>
-      <c r="BO130" s="6"/>
-      <c r="BR130" s="6"/>
-    </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN130" s="6"/>
+      <c r="BQ130" s="6"/>
+    </row>
+    <row r="131" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="18"/>
       <c r="E131" s="5"/>
-      <c r="BO131" s="6"/>
-      <c r="BR131" s="6"/>
-    </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN131" s="6"/>
+      <c r="BQ131" s="6"/>
+    </row>
+    <row r="132" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="18"/>
       <c r="E132" s="5"/>
-      <c r="BO132" s="6"/>
-      <c r="BR132" s="6"/>
-    </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN132" s="6"/>
+      <c r="BQ132" s="6"/>
+    </row>
+    <row r="133" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="18"/>
       <c r="E133" s="5"/>
-      <c r="BO133" s="6"/>
-      <c r="BR133" s="6"/>
-    </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN133" s="6"/>
+      <c r="BQ133" s="6"/>
+    </row>
+    <row r="134" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="18"/>
       <c r="E134" s="5"/>
-      <c r="BO134" s="6"/>
-      <c r="BR134" s="6"/>
-    </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN134" s="6"/>
+      <c r="BQ134" s="6"/>
+    </row>
+    <row r="135" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="18"/>
       <c r="E135" s="5"/>
-      <c r="BO135" s="6"/>
-      <c r="BR135" s="6"/>
-    </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN135" s="6"/>
+      <c r="BQ135" s="6"/>
+    </row>
+    <row r="136" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="18"/>
       <c r="E136" s="5"/>
-      <c r="BO136" s="6"/>
-      <c r="BR136" s="6"/>
-    </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN136" s="6"/>
+      <c r="BQ136" s="6"/>
+    </row>
+    <row r="137" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="18"/>
       <c r="E137" s="5"/>
-      <c r="BO137" s="6"/>
-      <c r="BR137" s="6"/>
-    </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN137" s="6"/>
+      <c r="BQ137" s="6"/>
+    </row>
+    <row r="138" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="18"/>
       <c r="E138" s="5"/>
-      <c r="BO138" s="6"/>
-      <c r="BR138" s="6"/>
-    </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN138" s="6"/>
+      <c r="BQ138" s="6"/>
+    </row>
+    <row r="139" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="18"/>
       <c r="E139" s="5"/>
-      <c r="BO139" s="6"/>
-      <c r="BR139" s="6"/>
-    </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN139" s="6"/>
+      <c r="BQ139" s="6"/>
+    </row>
+    <row r="140" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="18"/>
       <c r="E140" s="5"/>
-      <c r="BO140" s="6"/>
-      <c r="BR140" s="6"/>
-    </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN140" s="6"/>
+      <c r="BQ140" s="6"/>
+    </row>
+    <row r="141" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="18"/>
       <c r="E141" s="5"/>
-      <c r="BO141" s="6"/>
-      <c r="BR141" s="6"/>
-    </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN141" s="6"/>
+      <c r="BQ141" s="6"/>
+    </row>
+    <row r="142" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="18"/>
       <c r="E142" s="5"/>
-      <c r="BO142" s="6"/>
-      <c r="BR142" s="6"/>
-    </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN142" s="6"/>
+      <c r="BQ142" s="6"/>
+    </row>
+    <row r="143" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="18"/>
       <c r="E143" s="5"/>
-      <c r="BO143" s="6"/>
-      <c r="BR143" s="6"/>
-    </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN143" s="6"/>
+      <c r="BQ143" s="6"/>
+    </row>
+    <row r="144" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="18"/>
       <c r="E144" s="5"/>
-      <c r="BO144" s="6"/>
-      <c r="BR144" s="6"/>
-    </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN144" s="6"/>
+      <c r="BQ144" s="6"/>
+    </row>
+    <row r="145" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="18"/>
       <c r="E145" s="5"/>
-      <c r="BO145" s="6"/>
-      <c r="BR145" s="6"/>
-    </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN145" s="6"/>
+      <c r="BQ145" s="6"/>
+    </row>
+    <row r="146" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="18"/>
       <c r="E146" s="5"/>
-      <c r="BO146" s="6"/>
-      <c r="BR146" s="6"/>
-    </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN146" s="6"/>
+      <c r="BQ146" s="6"/>
+    </row>
+    <row r="147" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="18"/>
       <c r="E147" s="5"/>
-      <c r="BO147" s="6"/>
-      <c r="BR147" s="6"/>
-    </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN147" s="6"/>
+      <c r="BQ147" s="6"/>
+    </row>
+    <row r="148" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="18"/>
       <c r="E148" s="5"/>
-      <c r="BO148" s="6"/>
-      <c r="BR148" s="6"/>
-    </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN148" s="6"/>
+      <c r="BQ148" s="6"/>
+    </row>
+    <row r="149" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="18"/>
       <c r="E149" s="5"/>
-      <c r="BO149" s="6"/>
-      <c r="BR149" s="6"/>
-    </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN149" s="6"/>
+      <c r="BQ149" s="6"/>
+    </row>
+    <row r="150" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="18"/>
       <c r="E150" s="5"/>
-      <c r="BO150" s="6"/>
-      <c r="BR150" s="6"/>
-    </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN150" s="6"/>
+      <c r="BQ150" s="6"/>
+    </row>
+    <row r="151" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="18"/>
       <c r="E151" s="5"/>
-      <c r="BO151" s="6"/>
-      <c r="BR151" s="6"/>
-    </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN151" s="6"/>
+      <c r="BQ151" s="6"/>
+    </row>
+    <row r="152" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="18"/>
       <c r="E152" s="5"/>
-      <c r="BO152" s="6"/>
-      <c r="BR152" s="6"/>
-    </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN152" s="6"/>
+      <c r="BQ152" s="6"/>
+    </row>
+    <row r="153" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="18"/>
       <c r="E153" s="5"/>
-      <c r="BO153" s="6"/>
-      <c r="BR153" s="6"/>
-    </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN153" s="6"/>
+      <c r="BQ153" s="6"/>
+    </row>
+    <row r="154" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="18"/>
       <c r="E154" s="5"/>
-      <c r="BO154" s="6"/>
-      <c r="BR154" s="6"/>
-    </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN154" s="6"/>
+      <c r="BQ154" s="6"/>
+    </row>
+    <row r="155" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="18"/>
       <c r="E155" s="5"/>
-      <c r="BO155" s="6"/>
-      <c r="BR155" s="6"/>
-    </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN155" s="6"/>
+      <c r="BQ155" s="6"/>
+    </row>
+    <row r="156" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="18"/>
       <c r="E156" s="5"/>
-      <c r="BO156" s="6"/>
-      <c r="BR156" s="6"/>
-    </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN156" s="6"/>
+      <c r="BQ156" s="6"/>
+    </row>
+    <row r="157" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="18"/>
       <c r="E157" s="5"/>
-      <c r="BO157" s="6"/>
-      <c r="BR157" s="6"/>
-    </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN157" s="6"/>
+      <c r="BQ157" s="6"/>
+    </row>
+    <row r="158" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="18"/>
       <c r="E158" s="5"/>
-      <c r="BO158" s="6"/>
-      <c r="BR158" s="6"/>
-    </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN158" s="6"/>
+      <c r="BQ158" s="6"/>
+    </row>
+    <row r="159" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="18"/>
       <c r="E159" s="5"/>
-      <c r="BO159" s="6"/>
-      <c r="BR159" s="6"/>
-    </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN159" s="6"/>
+      <c r="BQ159" s="6"/>
+    </row>
+    <row r="160" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="18"/>
       <c r="E160" s="5"/>
-      <c r="BO160" s="6"/>
-      <c r="BR160" s="6"/>
-    </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN160" s="6"/>
+      <c r="BQ160" s="6"/>
+    </row>
+    <row r="161" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="18"/>
       <c r="E161" s="5"/>
-      <c r="BO161" s="6"/>
-      <c r="BR161" s="6"/>
-    </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN161" s="6"/>
+      <c r="BQ161" s="6"/>
+    </row>
+    <row r="162" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="18"/>
       <c r="E162" s="5"/>
-      <c r="BO162" s="6"/>
-      <c r="BR162" s="6"/>
-    </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN162" s="6"/>
+      <c r="BQ162" s="6"/>
+    </row>
+    <row r="163" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="18"/>
       <c r="E163" s="5"/>
-      <c r="BO163" s="6"/>
-      <c r="BR163" s="6"/>
-    </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN163" s="6"/>
+      <c r="BQ163" s="6"/>
+    </row>
+    <row r="164" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="18"/>
       <c r="E164" s="5"/>
-      <c r="BO164" s="6"/>
-      <c r="BR164" s="6"/>
-    </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN164" s="6"/>
+      <c r="BQ164" s="6"/>
+    </row>
+    <row r="165" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="18"/>
       <c r="E165" s="5"/>
-      <c r="BO165" s="6"/>
-      <c r="BR165" s="6"/>
-    </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN165" s="6"/>
+      <c r="BQ165" s="6"/>
+    </row>
+    <row r="166" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="18"/>
       <c r="E166" s="5"/>
-      <c r="BO166" s="6"/>
-      <c r="BR166" s="6"/>
-    </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN166" s="6"/>
+      <c r="BQ166" s="6"/>
+    </row>
+    <row r="167" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="18"/>
       <c r="E167" s="5"/>
-      <c r="BO167" s="6"/>
-      <c r="BR167" s="6"/>
-    </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN167" s="6"/>
+      <c r="BQ167" s="6"/>
+    </row>
+    <row r="168" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="18"/>
       <c r="E168" s="5"/>
-      <c r="BO168" s="6"/>
-      <c r="BR168" s="6"/>
-    </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN168" s="6"/>
+      <c r="BQ168" s="6"/>
+    </row>
+    <row r="169" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="18"/>
       <c r="E169" s="5"/>
-      <c r="BO169" s="6"/>
-      <c r="BR169" s="6"/>
-    </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN169" s="6"/>
+      <c r="BQ169" s="6"/>
+    </row>
+    <row r="170" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="18"/>
       <c r="E170" s="5"/>
-      <c r="BO170" s="6"/>
-      <c r="BR170" s="6"/>
-    </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN170" s="6"/>
+      <c r="BQ170" s="6"/>
+    </row>
+    <row r="171" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="18"/>
       <c r="E171" s="5"/>
-      <c r="BO171" s="6"/>
-      <c r="BR171" s="6"/>
-    </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN171" s="6"/>
+      <c r="BQ171" s="6"/>
+    </row>
+    <row r="172" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="18"/>
       <c r="E172" s="5"/>
-      <c r="BO172" s="6"/>
-      <c r="BR172" s="6"/>
-    </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN172" s="6"/>
+      <c r="BQ172" s="6"/>
+    </row>
+    <row r="173" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="18"/>
       <c r="E173" s="5"/>
-      <c r="BO173" s="6"/>
-      <c r="BR173" s="6"/>
-    </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN173" s="6"/>
+      <c r="BQ173" s="6"/>
+    </row>
+    <row r="174" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="18"/>
       <c r="E174" s="5"/>
-      <c r="BO174" s="6"/>
-      <c r="BR174" s="6"/>
-    </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN174" s="6"/>
+      <c r="BQ174" s="6"/>
+    </row>
+    <row r="175" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="18"/>
       <c r="E175" s="5"/>
-      <c r="BO175" s="6"/>
-      <c r="BR175" s="6"/>
-    </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN175" s="6"/>
+      <c r="BQ175" s="6"/>
+    </row>
+    <row r="176" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="18"/>
       <c r="E176" s="5"/>
-      <c r="BO176" s="6"/>
-      <c r="BR176" s="6"/>
-    </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN176" s="6"/>
+      <c r="BQ176" s="6"/>
+    </row>
+    <row r="177" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="18"/>
       <c r="E177" s="5"/>
-      <c r="BO177" s="6"/>
-      <c r="BR177" s="6"/>
-    </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN177" s="6"/>
+      <c r="BQ177" s="6"/>
+    </row>
+    <row r="178" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="18"/>
       <c r="E178" s="5"/>
-      <c r="BO178" s="6"/>
-      <c r="BR178" s="6"/>
-    </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN178" s="6"/>
+      <c r="BQ178" s="6"/>
+    </row>
+    <row r="179" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="18"/>
       <c r="E179" s="5"/>
-      <c r="BO179" s="6"/>
-      <c r="BR179" s="6"/>
-    </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN179" s="6"/>
+      <c r="BQ179" s="6"/>
+    </row>
+    <row r="180" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="18"/>
       <c r="E180" s="5"/>
-      <c r="BO180" s="6"/>
-      <c r="BR180" s="6"/>
-    </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN180" s="6"/>
+      <c r="BQ180" s="6"/>
+    </row>
+    <row r="181" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="18"/>
       <c r="E181" s="5"/>
-      <c r="BO181" s="6"/>
-      <c r="BR181" s="6"/>
-    </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN181" s="6"/>
+      <c r="BQ181" s="6"/>
+    </row>
+    <row r="182" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="18"/>
       <c r="E182" s="5"/>
-      <c r="BO182" s="6"/>
-      <c r="BR182" s="6"/>
-    </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN182" s="6"/>
+      <c r="BQ182" s="6"/>
+    </row>
+    <row r="183" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="18"/>
       <c r="E183" s="5"/>
-      <c r="BO183" s="6"/>
-      <c r="BR183" s="6"/>
-    </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN183" s="6"/>
+      <c r="BQ183" s="6"/>
+    </row>
+    <row r="184" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="18"/>
       <c r="E184" s="5"/>
-      <c r="BO184" s="6"/>
-      <c r="BR184" s="6"/>
-    </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN184" s="6"/>
+      <c r="BQ184" s="6"/>
+    </row>
+    <row r="185" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="18"/>
       <c r="E185" s="5"/>
-      <c r="BO185" s="6"/>
-      <c r="BR185" s="6"/>
-    </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN185" s="6"/>
+      <c r="BQ185" s="6"/>
+    </row>
+    <row r="186" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="18"/>
       <c r="E186" s="5"/>
-      <c r="BO186" s="6"/>
-      <c r="BR186" s="6"/>
-    </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN186" s="6"/>
+      <c r="BQ186" s="6"/>
+    </row>
+    <row r="187" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="18"/>
       <c r="E187" s="5"/>
-      <c r="BO187" s="6"/>
-      <c r="BR187" s="6"/>
-    </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN187" s="6"/>
+      <c r="BQ187" s="6"/>
+    </row>
+    <row r="188" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="18"/>
       <c r="E188" s="5"/>
-      <c r="BO188" s="6"/>
-      <c r="BR188" s="6"/>
-    </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN188" s="6"/>
+      <c r="BQ188" s="6"/>
+    </row>
+    <row r="189" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="18"/>
       <c r="E189" s="5"/>
-      <c r="BO189" s="6"/>
-      <c r="BR189" s="6"/>
-    </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN189" s="6"/>
+      <c r="BQ189" s="6"/>
+    </row>
+    <row r="190" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="18"/>
       <c r="E190" s="5"/>
-      <c r="BO190" s="6"/>
-      <c r="BR190" s="6"/>
-    </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN190" s="6"/>
+      <c r="BQ190" s="6"/>
+    </row>
+    <row r="191" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="18"/>
       <c r="E191" s="5"/>
-      <c r="BO191" s="6"/>
-      <c r="BR191" s="6"/>
-    </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN191" s="6"/>
+      <c r="BQ191" s="6"/>
+    </row>
+    <row r="192" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="18"/>
       <c r="E192" s="5"/>
-      <c r="BO192" s="6"/>
-      <c r="BR192" s="6"/>
-    </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN192" s="6"/>
+      <c r="BQ192" s="6"/>
+    </row>
+    <row r="193" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="18"/>
       <c r="E193" s="5"/>
-      <c r="BO193" s="6"/>
-      <c r="BR193" s="6"/>
-    </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN193" s="6"/>
+      <c r="BQ193" s="6"/>
+    </row>
+    <row r="194" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="18"/>
       <c r="E194" s="5"/>
-      <c r="BO194" s="6"/>
-      <c r="BR194" s="6"/>
-    </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN194" s="6"/>
+      <c r="BQ194" s="6"/>
+    </row>
+    <row r="195" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="18"/>
       <c r="E195" s="5"/>
-      <c r="BO195" s="6"/>
-      <c r="BR195" s="6"/>
-    </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN195" s="6"/>
+      <c r="BQ195" s="6"/>
+    </row>
+    <row r="196" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="18"/>
       <c r="E196" s="5"/>
-      <c r="BO196" s="6"/>
-      <c r="BR196" s="6"/>
-    </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN196" s="6"/>
+      <c r="BQ196" s="6"/>
+    </row>
+    <row r="197" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="18"/>
       <c r="E197" s="5"/>
-      <c r="BO197" s="6"/>
-      <c r="BR197" s="6"/>
-    </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN197" s="6"/>
+      <c r="BQ197" s="6"/>
+    </row>
+    <row r="198" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="18"/>
       <c r="E198" s="5"/>
-      <c r="BO198" s="6"/>
-      <c r="BR198" s="6"/>
-    </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN198" s="6"/>
+      <c r="BQ198" s="6"/>
+    </row>
+    <row r="199" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="18"/>
       <c r="E199" s="5"/>
-      <c r="BO199" s="6"/>
-      <c r="BR199" s="6"/>
-    </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN199" s="6"/>
+      <c r="BQ199" s="6"/>
+    </row>
+    <row r="200" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="18"/>
       <c r="E200" s="5"/>
-      <c r="BO200" s="6"/>
-      <c r="BR200" s="6"/>
-    </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN200" s="6"/>
+      <c r="BQ200" s="6"/>
+    </row>
+    <row r="201" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="18"/>
       <c r="E201" s="5"/>
-      <c r="BO201" s="6"/>
-      <c r="BR201" s="6"/>
-    </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN201" s="6"/>
+      <c r="BQ201" s="6"/>
+    </row>
+    <row r="202" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="18"/>
       <c r="E202" s="5"/>
-      <c r="BO202" s="6"/>
-      <c r="BR202" s="6"/>
-    </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN202" s="6"/>
+      <c r="BQ202" s="6"/>
+    </row>
+    <row r="203" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="18"/>
       <c r="E203" s="5"/>
-      <c r="BO203" s="6"/>
-      <c r="BR203" s="6"/>
-    </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN203" s="6"/>
+      <c r="BQ203" s="6"/>
+    </row>
+    <row r="204" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="18"/>
       <c r="E204" s="5"/>
-      <c r="BO204" s="6"/>
-      <c r="BR204" s="6"/>
-    </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN204" s="6"/>
+      <c r="BQ204" s="6"/>
+    </row>
+    <row r="205" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="18"/>
       <c r="E205" s="5"/>
-      <c r="BO205" s="6"/>
-      <c r="BR205" s="6"/>
-    </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN205" s="6"/>
+      <c r="BQ205" s="6"/>
+    </row>
+    <row r="206" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="18"/>
       <c r="E206" s="5"/>
-      <c r="BO206" s="6"/>
-      <c r="BR206" s="6"/>
-    </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN206" s="6"/>
+      <c r="BQ206" s="6"/>
+    </row>
+    <row r="207" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="18"/>
       <c r="E207" s="5"/>
-      <c r="BO207" s="6"/>
-      <c r="BR207" s="6"/>
-    </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN207" s="6"/>
+      <c r="BQ207" s="6"/>
+    </row>
+    <row r="208" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="18"/>
       <c r="E208" s="5"/>
-      <c r="BO208" s="6"/>
-      <c r="BR208" s="6"/>
-    </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN208" s="6"/>
+      <c r="BQ208" s="6"/>
+    </row>
+    <row r="209" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="18"/>
       <c r="E209" s="5"/>
-      <c r="BO209" s="6"/>
-      <c r="BR209" s="6"/>
-    </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN209" s="6"/>
+      <c r="BQ209" s="6"/>
+    </row>
+    <row r="210" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="18"/>
       <c r="E210" s="5"/>
-      <c r="BO210" s="6"/>
-      <c r="BR210" s="6"/>
-    </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN210" s="6"/>
+      <c r="BQ210" s="6"/>
+    </row>
+    <row r="211" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="18"/>
       <c r="E211" s="5"/>
-      <c r="BO211" s="6"/>
-      <c r="BR211" s="6"/>
-    </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN211" s="6"/>
+      <c r="BQ211" s="6"/>
+    </row>
+    <row r="212" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="18"/>
       <c r="E212" s="5"/>
-      <c r="BO212" s="6"/>
-      <c r="BR212" s="6"/>
-    </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN212" s="6"/>
+      <c r="BQ212" s="6"/>
+    </row>
+    <row r="213" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="18"/>
       <c r="E213" s="5"/>
-      <c r="BO213" s="6"/>
-      <c r="BR213" s="6"/>
-    </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN213" s="6"/>
+      <c r="BQ213" s="6"/>
+    </row>
+    <row r="214" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="18"/>
       <c r="E214" s="5"/>
-      <c r="BO214" s="6"/>
-      <c r="BR214" s="6"/>
-    </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN214" s="6"/>
+      <c r="BQ214" s="6"/>
+    </row>
+    <row r="215" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="18"/>
       <c r="E215" s="5"/>
-      <c r="BO215" s="6"/>
-      <c r="BR215" s="6"/>
-    </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN215" s="6"/>
+      <c r="BQ215" s="6"/>
+    </row>
+    <row r="216" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="18"/>
       <c r="E216" s="5"/>
-      <c r="BO216" s="6"/>
-      <c r="BR216" s="6"/>
-    </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN216" s="6"/>
+      <c r="BQ216" s="6"/>
+    </row>
+    <row r="217" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="18"/>
       <c r="E217" s="5"/>
-      <c r="BO217" s="6"/>
-      <c r="BR217" s="6"/>
-    </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN217" s="6"/>
+      <c r="BQ217" s="6"/>
+    </row>
+    <row r="218" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="18"/>
       <c r="E218" s="5"/>
-      <c r="BO218" s="6"/>
-      <c r="BR218" s="6"/>
-    </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN218" s="6"/>
+      <c r="BQ218" s="6"/>
+    </row>
+    <row r="219" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="18"/>
       <c r="E219" s="5"/>
-      <c r="BO219" s="6"/>
-      <c r="BR219" s="6"/>
-    </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN219" s="6"/>
+      <c r="BQ219" s="6"/>
+    </row>
+    <row r="220" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="18"/>
       <c r="E220" s="5"/>
-      <c r="BO220" s="6"/>
-      <c r="BR220" s="6"/>
-    </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN220" s="6"/>
+      <c r="BQ220" s="6"/>
+    </row>
+    <row r="221" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="18"/>
       <c r="E221" s="5"/>
-      <c r="BO221" s="6"/>
-      <c r="BR221" s="6"/>
-    </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN221" s="6"/>
+      <c r="BQ221" s="6"/>
+    </row>
+    <row r="222" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="18"/>
       <c r="E222" s="5"/>
-      <c r="BO222" s="6"/>
-      <c r="BR222" s="6"/>
-    </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN222" s="6"/>
+      <c r="BQ222" s="6"/>
+    </row>
+    <row r="223" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="18"/>
       <c r="E223" s="5"/>
-      <c r="BO223" s="6"/>
-      <c r="BR223" s="6"/>
-    </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN223" s="6"/>
+      <c r="BQ223" s="6"/>
+    </row>
+    <row r="224" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="18"/>
       <c r="E224" s="5"/>
-      <c r="BO224" s="6"/>
-      <c r="BR224" s="6"/>
-    </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN224" s="6"/>
+      <c r="BQ224" s="6"/>
+    </row>
+    <row r="225" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="18"/>
       <c r="E225" s="5"/>
-      <c r="BO225" s="6"/>
-      <c r="BR225" s="6"/>
-    </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN225" s="6"/>
+      <c r="BQ225" s="6"/>
+    </row>
+    <row r="226" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="18"/>
       <c r="E226" s="5"/>
-      <c r="BO226" s="6"/>
-      <c r="BR226" s="6"/>
-    </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN226" s="6"/>
+      <c r="BQ226" s="6"/>
+    </row>
+    <row r="227" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="18"/>
       <c r="E227" s="5"/>
-      <c r="BO227" s="6"/>
-      <c r="BR227" s="6"/>
-    </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN227" s="6"/>
+      <c r="BQ227" s="6"/>
+    </row>
+    <row r="228" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="18"/>
       <c r="E228" s="5"/>
-      <c r="BO228" s="6"/>
-      <c r="BR228" s="6"/>
-    </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN228" s="6"/>
+      <c r="BQ228" s="6"/>
+    </row>
+    <row r="229" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="18"/>
       <c r="E229" s="5"/>
-      <c r="BO229" s="6"/>
-      <c r="BR229" s="6"/>
-    </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN229" s="6"/>
+      <c r="BQ229" s="6"/>
+    </row>
+    <row r="230" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="18"/>
       <c r="E230" s="5"/>
-      <c r="BO230" s="6"/>
-      <c r="BR230" s="6"/>
-    </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN230" s="6"/>
+      <c r="BQ230" s="6"/>
+    </row>
+    <row r="231" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="18"/>
       <c r="E231" s="5"/>
-      <c r="BO231" s="6"/>
-      <c r="BR231" s="6"/>
-    </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN231" s="6"/>
+      <c r="BQ231" s="6"/>
+    </row>
+    <row r="232" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="18"/>
       <c r="E232" s="5"/>
-      <c r="BO232" s="6"/>
-      <c r="BR232" s="6"/>
-    </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN232" s="6"/>
+      <c r="BQ232" s="6"/>
+    </row>
+    <row r="233" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="18"/>
       <c r="E233" s="5"/>
-      <c r="BO233" s="6"/>
-      <c r="BR233" s="6"/>
-    </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN233" s="6"/>
+      <c r="BQ233" s="6"/>
+    </row>
+    <row r="234" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="18"/>
       <c r="E234" s="5"/>
-      <c r="BO234" s="6"/>
-      <c r="BR234" s="6"/>
-    </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN234" s="6"/>
+      <c r="BQ234" s="6"/>
+    </row>
+    <row r="235" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="18"/>
       <c r="E235" s="5"/>
-      <c r="BR235" s="6"/>
-    </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ235" s="6"/>
+    </row>
+    <row r="236" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="18"/>
       <c r="E236" s="5"/>
-      <c r="BO236" s="6"/>
-      <c r="BR236" s="6"/>
-    </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN236" s="6"/>
+      <c r="BQ236" s="6"/>
+    </row>
+    <row r="237" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="18"/>
       <c r="E237" s="5"/>
-      <c r="BO237" s="6"/>
-      <c r="BR237" s="6"/>
-    </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN237" s="6"/>
+      <c r="BQ237" s="6"/>
+    </row>
+    <row r="238" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="18"/>
       <c r="E238" s="5"/>
-      <c r="BO238" s="6"/>
-      <c r="BR238" s="6"/>
-    </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN238" s="6"/>
+      <c r="BQ238" s="6"/>
+    </row>
+    <row r="239" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="18"/>
       <c r="E239" s="5"/>
-      <c r="BO239" s="6"/>
-      <c r="BR239" s="6"/>
-    </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN239" s="6"/>
+      <c r="BQ239" s="6"/>
+    </row>
+    <row r="240" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="18"/>
       <c r="E240" s="5"/>
-      <c r="BO240" s="6"/>
-      <c r="BR240" s="6"/>
-    </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN240" s="6"/>
+      <c r="BQ240" s="6"/>
+    </row>
+    <row r="241" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="18"/>
       <c r="E241" s="5"/>
-      <c r="BO241" s="6"/>
-      <c r="BR241" s="6"/>
-    </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN241" s="6"/>
+      <c r="BQ241" s="6"/>
+    </row>
+    <row r="242" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="18"/>
       <c r="E242" s="5"/>
-      <c r="BO242" s="6"/>
-      <c r="BR242" s="6"/>
-    </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN242" s="6"/>
+      <c r="BQ242" s="6"/>
+    </row>
+    <row r="243" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="18"/>
       <c r="E243" s="5"/>
-      <c r="BO243" s="6"/>
-      <c r="BR243" s="6"/>
-    </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN243" s="6"/>
+      <c r="BQ243" s="6"/>
+    </row>
+    <row r="244" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="18"/>
       <c r="E244" s="5"/>
-      <c r="BO244" s="6"/>
-      <c r="BR244" s="6"/>
-    </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN244" s="6"/>
+      <c r="BQ244" s="6"/>
+    </row>
+    <row r="245" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="18"/>
       <c r="E245" s="5"/>
-      <c r="BO245" s="6"/>
-      <c r="BR245" s="6"/>
-    </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN245" s="6"/>
+      <c r="BQ245" s="6"/>
+    </row>
+    <row r="246" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="18"/>
       <c r="E246" s="5"/>
-      <c r="BO246" s="6"/>
-      <c r="BR246" s="6"/>
-    </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN246" s="6"/>
+      <c r="BQ246" s="6"/>
+    </row>
+    <row r="247" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="18"/>
       <c r="E247" s="5"/>
-      <c r="BO247" s="6"/>
-      <c r="BR247" s="6"/>
-    </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN247" s="6"/>
+      <c r="BQ247" s="6"/>
+    </row>
+    <row r="248" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="18"/>
       <c r="E248" s="5"/>
-      <c r="BO248" s="6"/>
-      <c r="BR248" s="6"/>
-    </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN248" s="6"/>
+      <c r="BQ248" s="6"/>
+    </row>
+    <row r="249" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="18"/>
       <c r="E249" s="5"/>
-      <c r="BO249" s="6"/>
-      <c r="BR249" s="6"/>
-    </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN249" s="6"/>
+      <c r="BQ249" s="6"/>
+    </row>
+    <row r="250" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="18"/>
       <c r="E250" s="5"/>
-      <c r="BO250" s="6"/>
-      <c r="BR250" s="6"/>
-    </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN250" s="6"/>
+      <c r="BQ250" s="6"/>
+    </row>
+    <row r="251" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="18"/>
       <c r="E251" s="5"/>
-      <c r="BO251" s="6"/>
-      <c r="BR251" s="6"/>
-    </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN251" s="6"/>
+      <c r="BQ251" s="6"/>
+    </row>
+    <row r="252" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="18"/>
       <c r="E252" s="5"/>
-      <c r="BO252" s="6"/>
-      <c r="BR252" s="6"/>
-    </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN252" s="6"/>
+      <c r="BQ252" s="6"/>
+    </row>
+    <row r="253" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="18"/>
       <c r="E253" s="5"/>
-      <c r="BO253" s="6"/>
-      <c r="BR253" s="6"/>
-    </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN253" s="6"/>
+      <c r="BQ253" s="6"/>
+    </row>
+    <row r="254" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="18"/>
       <c r="E254" s="5"/>
-      <c r="BO254" s="6"/>
-      <c r="BR254" s="6"/>
-    </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN254" s="6"/>
+      <c r="BQ254" s="6"/>
+    </row>
+    <row r="255" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="18"/>
       <c r="E255" s="5"/>
-      <c r="BO255" s="6"/>
-      <c r="BR255" s="6"/>
-    </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN255" s="6"/>
+      <c r="BQ255" s="6"/>
+    </row>
+    <row r="256" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="18"/>
       <c r="E256" s="5"/>
-      <c r="BO256" s="6"/>
-      <c r="BR256" s="6"/>
-    </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN256" s="6"/>
+      <c r="BQ256" s="6"/>
+    </row>
+    <row r="257" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="18"/>
       <c r="E257" s="5"/>
-      <c r="BO257" s="6"/>
-      <c r="BR257" s="6"/>
-    </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN257" s="6"/>
+      <c r="BQ257" s="6"/>
+    </row>
+    <row r="258" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="18"/>
       <c r="E258" s="5"/>
-      <c r="BO258" s="6"/>
-      <c r="BR258" s="6"/>
-    </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN258" s="6"/>
+      <c r="BQ258" s="6"/>
+    </row>
+    <row r="259" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="18"/>
       <c r="E259" s="5"/>
-      <c r="BO259" s="6"/>
-      <c r="BR259" s="6"/>
-    </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN259" s="6"/>
+      <c r="BQ259" s="6"/>
+    </row>
+    <row r="260" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="18"/>
       <c r="E260" s="5"/>
-      <c r="BO260" s="6"/>
-      <c r="BR260" s="6"/>
-    </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN260" s="6"/>
+      <c r="BQ260" s="6"/>
+    </row>
+    <row r="261" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="18"/>
       <c r="E261" s="5"/>
-      <c r="BO261" s="6"/>
-      <c r="BR261" s="6"/>
-    </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN261" s="6"/>
+      <c r="BQ261" s="6"/>
+    </row>
+    <row r="262" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="18"/>
       <c r="E262" s="5"/>
-      <c r="BO262" s="6"/>
-      <c r="BR262" s="6"/>
-    </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN262" s="6"/>
+      <c r="BQ262" s="6"/>
+    </row>
+    <row r="263" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="18"/>
       <c r="E263" s="5"/>
-      <c r="BO263" s="6"/>
-      <c r="BR263" s="6"/>
-    </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN263" s="6"/>
+      <c r="BQ263" s="6"/>
+    </row>
+    <row r="264" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="18"/>
       <c r="E264" s="5"/>
-      <c r="BO264" s="6"/>
-      <c r="BR264" s="6"/>
-    </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN264" s="6"/>
+      <c r="BQ264" s="6"/>
+    </row>
+    <row r="265" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="18"/>
       <c r="E265" s="5"/>
-      <c r="BO265" s="6"/>
-      <c r="BR265" s="6"/>
-    </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN265" s="6"/>
+      <c r="BQ265" s="6"/>
+    </row>
+    <row r="266" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="18"/>
       <c r="E266" s="5"/>
-      <c r="BO266" s="6"/>
-      <c r="BR266" s="6"/>
-    </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN266" s="6"/>
+      <c r="BQ266" s="6"/>
+    </row>
+    <row r="267" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="18"/>
       <c r="E267" s="5"/>
-      <c r="BO267" s="6"/>
-      <c r="BR267" s="6"/>
-    </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN267" s="6"/>
+      <c r="BQ267" s="6"/>
+    </row>
+    <row r="268" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="18"/>
       <c r="E268" s="5"/>
-      <c r="BO268" s="6"/>
-      <c r="BR268" s="6"/>
-    </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN268" s="6"/>
+      <c r="BQ268" s="6"/>
+    </row>
+    <row r="269" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="18"/>
       <c r="E269" s="5"/>
-      <c r="BO269" s="6"/>
-      <c r="BR269" s="6"/>
-    </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN269" s="6"/>
+      <c r="BQ269" s="6"/>
+    </row>
+    <row r="270" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="18"/>
       <c r="E270" s="5"/>
-      <c r="BO270" s="6"/>
-      <c r="BR270" s="6"/>
-    </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN270" s="6"/>
+      <c r="BQ270" s="6"/>
+    </row>
+    <row r="271" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="18"/>
       <c r="E271" s="5"/>
-      <c r="BO271" s="6"/>
-      <c r="BR271" s="6"/>
-    </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN271" s="6"/>
+      <c r="BQ271" s="6"/>
+    </row>
+    <row r="272" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="18"/>
       <c r="E272" s="5"/>
-      <c r="BO272" s="6"/>
-      <c r="BR272" s="6"/>
-    </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN272" s="6"/>
+      <c r="BQ272" s="6"/>
+    </row>
+    <row r="273" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="18"/>
       <c r="E273" s="5"/>
-      <c r="BO273" s="6"/>
-      <c r="BR273" s="6"/>
-    </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN273" s="6"/>
+      <c r="BQ273" s="6"/>
+    </row>
+    <row r="274" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="18"/>
       <c r="E274" s="5"/>
-      <c r="BO274" s="6"/>
-      <c r="BR274" s="6"/>
-    </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN274" s="6"/>
+      <c r="BQ274" s="6"/>
+    </row>
+    <row r="275" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="18"/>
       <c r="E275" s="5"/>
-      <c r="BO275" s="6"/>
-      <c r="BR275" s="6"/>
-    </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN275" s="6"/>
+      <c r="BQ275" s="6"/>
+    </row>
+    <row r="276" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="18"/>
       <c r="E276" s="5"/>
-      <c r="BO276" s="6"/>
-      <c r="BR276" s="6"/>
-    </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN276" s="6"/>
+      <c r="BQ276" s="6"/>
+    </row>
+    <row r="277" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="18"/>
       <c r="E277" s="5"/>
-      <c r="BO277" s="6"/>
-      <c r="BR277" s="6"/>
-    </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN277" s="6"/>
+      <c r="BQ277" s="6"/>
+    </row>
+    <row r="278" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="18"/>
       <c r="E278" s="5"/>
-      <c r="BR278" s="6"/>
-    </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ278" s="6"/>
+    </row>
+    <row r="279" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="18"/>
       <c r="E279" s="5"/>
-      <c r="BO279" s="6"/>
-      <c r="BR279" s="6"/>
-    </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN279" s="6"/>
+      <c r="BQ279" s="6"/>
+    </row>
+    <row r="280" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="18"/>
       <c r="E280" s="5"/>
-      <c r="BO280" s="6"/>
-      <c r="BR280" s="6"/>
-    </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN280" s="6"/>
+      <c r="BQ280" s="6"/>
+    </row>
+    <row r="281" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="18"/>
       <c r="E281" s="5"/>
-      <c r="BO281" s="6"/>
-      <c r="BR281" s="6"/>
-    </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN281" s="6"/>
+      <c r="BQ281" s="6"/>
+    </row>
+    <row r="282" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="18"/>
       <c r="E282" s="5"/>
-      <c r="BO282" s="6"/>
-      <c r="BR282" s="6"/>
-    </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN282" s="6"/>
+      <c r="BQ282" s="6"/>
+    </row>
+    <row r="283" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="18"/>
       <c r="E283" s="5"/>
-      <c r="BO283" s="6"/>
-      <c r="BR283" s="6"/>
-    </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN283" s="6"/>
+      <c r="BQ283" s="6"/>
+    </row>
+    <row r="284" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="18"/>
       <c r="E284" s="5"/>
-      <c r="BO284" s="6"/>
-      <c r="BR284" s="6"/>
-    </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN284" s="6"/>
+      <c r="BQ284" s="6"/>
+    </row>
+    <row r="285" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="18"/>
       <c r="E285" s="5"/>
-      <c r="BO285" s="6"/>
-      <c r="BR285" s="6"/>
-    </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN285" s="6"/>
+      <c r="BQ285" s="6"/>
+    </row>
+    <row r="286" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="18"/>
       <c r="E286" s="5"/>
-      <c r="BO286" s="6"/>
-      <c r="BR286" s="6"/>
-    </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN286" s="6"/>
+      <c r="BQ286" s="6"/>
+    </row>
+    <row r="287" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="18"/>
       <c r="E287" s="5"/>
-      <c r="BO287" s="6"/>
-      <c r="BR287" s="6"/>
-    </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN287" s="6"/>
+      <c r="BQ287" s="6"/>
+    </row>
+    <row r="288" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="18"/>
       <c r="E288" s="5"/>
-      <c r="BO288" s="6"/>
-      <c r="BR288" s="6"/>
-    </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN288" s="6"/>
+      <c r="BQ288" s="6"/>
+    </row>
+    <row r="289" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="18"/>
       <c r="E289" s="5"/>
-      <c r="BO289" s="6"/>
-      <c r="BR289" s="6"/>
-    </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN289" s="6"/>
+      <c r="BQ289" s="6"/>
+    </row>
+    <row r="290" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="18"/>
       <c r="E290" s="5"/>
-      <c r="BO290" s="6"/>
-      <c r="BR290" s="6"/>
-    </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN290" s="6"/>
+      <c r="BQ290" s="6"/>
+    </row>
+    <row r="291" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="18"/>
       <c r="E291" s="5"/>
-      <c r="BO291" s="6"/>
-      <c r="BR291" s="6"/>
-    </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN291" s="6"/>
+      <c r="BQ291" s="6"/>
+    </row>
+    <row r="292" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="18"/>
       <c r="E292" s="5"/>
-      <c r="BO292" s="6"/>
-      <c r="BR292" s="6"/>
-    </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN292" s="6"/>
+      <c r="BQ292" s="6"/>
+    </row>
+    <row r="293" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="18"/>
       <c r="E293" s="5"/>
-      <c r="BO293" s="6"/>
-      <c r="BR293" s="6"/>
-    </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN293" s="6"/>
+      <c r="BQ293" s="6"/>
+    </row>
+    <row r="294" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="18"/>
       <c r="E294" s="5"/>
-      <c r="BO294" s="6"/>
-      <c r="BR294" s="6"/>
-    </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN294" s="6"/>
+      <c r="BQ294" s="6"/>
+    </row>
+    <row r="295" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="18"/>
       <c r="E295" s="5"/>
-      <c r="BO295" s="6"/>
-      <c r="BR295" s="6"/>
-    </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN295" s="6"/>
+      <c r="BQ295" s="6"/>
+    </row>
+    <row r="296" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="18"/>
       <c r="E296" s="5"/>
-      <c r="BO296" s="6"/>
-      <c r="BR296" s="6"/>
-    </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN296" s="6"/>
+      <c r="BQ296" s="6"/>
+    </row>
+    <row r="297" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="18"/>
       <c r="E297" s="5"/>
-      <c r="BO297" s="6"/>
-      <c r="BR297" s="6"/>
-    </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN297" s="6"/>
+      <c r="BQ297" s="6"/>
+    </row>
+    <row r="298" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="18"/>
       <c r="E298" s="5"/>
-      <c r="BO298" s="6"/>
-      <c r="BR298" s="6"/>
-    </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN298" s="6"/>
+      <c r="BQ298" s="6"/>
+    </row>
+    <row r="299" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="18"/>
       <c r="E299" s="5"/>
-      <c r="BO299" s="6"/>
-      <c r="BR299" s="6"/>
-    </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN299" s="6"/>
+      <c r="BQ299" s="6"/>
+    </row>
+    <row r="300" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="18"/>
       <c r="E300" s="5"/>
-      <c r="BO300" s="6"/>
-      <c r="BR300" s="6"/>
-    </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN300" s="6"/>
+      <c r="BQ300" s="6"/>
+    </row>
+    <row r="301" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="18"/>
       <c r="E301" s="5"/>
-      <c r="BO301" s="6"/>
-      <c r="BR301" s="6"/>
-    </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN301" s="6"/>
+      <c r="BQ301" s="6"/>
+    </row>
+    <row r="302" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="18"/>
       <c r="E302" s="5"/>
-      <c r="BO302" s="6"/>
-      <c r="BR302" s="6"/>
-    </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN302" s="6"/>
+      <c r="BQ302" s="6"/>
+    </row>
+    <row r="303" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="18"/>
       <c r="E303" s="5"/>
-      <c r="BO303" s="6"/>
-      <c r="BR303" s="6"/>
-    </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN303" s="6"/>
+      <c r="BQ303" s="6"/>
+    </row>
+    <row r="304" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="18"/>
       <c r="E304" s="5"/>
-      <c r="BO304" s="6"/>
-      <c r="BR304" s="6"/>
-    </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN304" s="6"/>
+      <c r="BQ304" s="6"/>
+    </row>
+    <row r="305" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="18"/>
       <c r="E305" s="5"/>
-      <c r="BO305" s="6"/>
-      <c r="BR305" s="6"/>
-    </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN305" s="6"/>
+      <c r="BQ305" s="6"/>
+    </row>
+    <row r="306" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="18"/>
       <c r="E306" s="5"/>
-      <c r="BO306" s="6"/>
-      <c r="BR306" s="6"/>
-    </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN306" s="6"/>
+      <c r="BQ306" s="6"/>
+    </row>
+    <row r="307" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="18"/>
       <c r="E307" s="5"/>
-      <c r="BO307" s="6"/>
-      <c r="BR307" s="6"/>
-    </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN307" s="6"/>
+      <c r="BQ307" s="6"/>
+    </row>
+    <row r="308" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="18"/>
       <c r="E308" s="5"/>
-      <c r="BO308" s="6"/>
-      <c r="BR308" s="6"/>
-    </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN308" s="6"/>
+      <c r="BQ308" s="6"/>
+    </row>
+    <row r="309" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="18"/>
       <c r="E309" s="5"/>
-      <c r="BO309" s="6"/>
-      <c r="BR309" s="6"/>
-    </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN309" s="6"/>
+      <c r="BQ309" s="6"/>
+    </row>
+    <row r="310" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="18"/>
       <c r="E310" s="5"/>
-      <c r="BO310" s="6"/>
-      <c r="BR310" s="6"/>
-    </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN310" s="6"/>
+      <c r="BQ310" s="6"/>
+    </row>
+    <row r="311" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="18"/>
       <c r="E311" s="5"/>
-      <c r="BO311" s="6"/>
-      <c r="BR311" s="6"/>
-    </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN311" s="6"/>
+      <c r="BQ311" s="6"/>
+    </row>
+    <row r="312" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="18"/>
       <c r="E312" s="5"/>
-      <c r="BO312" s="6"/>
-      <c r="BR312" s="6"/>
-    </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN312" s="6"/>
+      <c r="BQ312" s="6"/>
+    </row>
+    <row r="313" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="18"/>
       <c r="E313" s="5"/>
-      <c r="BO313" s="6"/>
-      <c r="BR313" s="6"/>
-    </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN313" s="6"/>
+      <c r="BQ313" s="6"/>
+    </row>
+    <row r="314" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="18"/>
       <c r="E314" s="5"/>
-      <c r="BO314" s="6"/>
-      <c r="BR314" s="6"/>
-    </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN314" s="6"/>
+      <c r="BQ314" s="6"/>
+    </row>
+    <row r="315" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="18"/>
       <c r="E315" s="5"/>
-      <c r="BO315" s="6"/>
-      <c r="BR315" s="6"/>
-    </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN315" s="6"/>
+      <c r="BQ315" s="6"/>
+    </row>
+    <row r="316" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="18"/>
       <c r="E316" s="5"/>
-      <c r="BO316" s="6"/>
-      <c r="BR316" s="6"/>
-    </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN316" s="6"/>
+      <c r="BQ316" s="6"/>
+    </row>
+    <row r="317" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="18"/>
       <c r="E317" s="5"/>
-      <c r="BO317" s="6"/>
-      <c r="BR317" s="6"/>
-    </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN317" s="6"/>
+      <c r="BQ317" s="6"/>
+    </row>
+    <row r="318" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="18"/>
       <c r="E318" s="5"/>
-      <c r="BO318" s="6"/>
-      <c r="BR318" s="6"/>
-    </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN318" s="6"/>
+      <c r="BQ318" s="6"/>
+    </row>
+    <row r="319" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="18"/>
       <c r="E319" s="5"/>
-      <c r="BO319" s="6"/>
-      <c r="BR319" s="6"/>
-    </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN319" s="6"/>
+      <c r="BQ319" s="6"/>
+    </row>
+    <row r="320" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="18"/>
       <c r="E320" s="5"/>
-      <c r="BO320" s="6"/>
-      <c r="BR320" s="6"/>
-    </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN320" s="6"/>
+      <c r="BQ320" s="6"/>
+    </row>
+    <row r="321" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="18"/>
       <c r="E321" s="5"/>
-      <c r="BO321" s="6"/>
-      <c r="BR321" s="6"/>
-    </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN321" s="6"/>
+      <c r="BQ321" s="6"/>
+    </row>
+    <row r="322" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="18"/>
       <c r="E322" s="5"/>
-      <c r="BO322" s="6"/>
-      <c r="BR322" s="6"/>
-    </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN322" s="6"/>
+      <c r="BQ322" s="6"/>
+    </row>
+    <row r="323" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="18"/>
       <c r="E323" s="5"/>
-      <c r="BO323" s="6"/>
-      <c r="BR323" s="6"/>
-    </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN323" s="6"/>
+      <c r="BQ323" s="6"/>
+    </row>
+    <row r="324" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="18"/>
       <c r="E324" s="5"/>
-      <c r="BO324" s="6"/>
-      <c r="BR324" s="6"/>
-    </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN324" s="6"/>
+      <c r="BQ324" s="6"/>
+    </row>
+    <row r="325" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="18"/>
       <c r="E325" s="5"/>
-      <c r="BO325" s="6"/>
-      <c r="BR325" s="6"/>
-    </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN325" s="6"/>
+      <c r="BQ325" s="6"/>
+    </row>
+    <row r="326" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="18"/>
       <c r="E326" s="5"/>
-      <c r="BO326" s="6"/>
-      <c r="BR326" s="6"/>
-    </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN326" s="6"/>
+      <c r="BQ326" s="6"/>
+    </row>
+    <row r="327" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="18"/>
       <c r="E327" s="5"/>
-      <c r="BO327" s="6"/>
-      <c r="BR327" s="6"/>
-    </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN327" s="6"/>
+      <c r="BQ327" s="6"/>
+    </row>
+    <row r="328" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="18"/>
       <c r="E328" s="5"/>
-      <c r="BO328" s="6"/>
-      <c r="BR328" s="6"/>
-    </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN328" s="6"/>
+      <c r="BQ328" s="6"/>
+    </row>
+    <row r="329" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="18"/>
       <c r="E329" s="5"/>
-      <c r="BO329" s="6"/>
-      <c r="BR329" s="6"/>
-    </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN329" s="6"/>
+      <c r="BQ329" s="6"/>
+    </row>
+    <row r="330" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="18"/>
       <c r="E330" s="5"/>
-      <c r="BO330" s="6"/>
-      <c r="BR330" s="6"/>
-    </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN330" s="6"/>
+      <c r="BQ330" s="6"/>
+    </row>
+    <row r="331" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="18"/>
       <c r="E331" s="5"/>
-      <c r="BO331" s="6"/>
-      <c r="BR331" s="6"/>
-    </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN331" s="6"/>
+      <c r="BQ331" s="6"/>
+    </row>
+    <row r="332" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="18"/>
       <c r="E332" s="5"/>
-      <c r="BO332" s="6"/>
-      <c r="BR332" s="6"/>
-    </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN332" s="6"/>
+      <c r="BQ332" s="6"/>
+    </row>
+    <row r="333" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="18"/>
       <c r="E333" s="5"/>
-      <c r="BO333" s="6"/>
-      <c r="BR333" s="6"/>
-    </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN333" s="6"/>
+      <c r="BQ333" s="6"/>
+    </row>
+    <row r="334" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="18"/>
       <c r="E334" s="5"/>
-      <c r="BR334" s="6"/>
-    </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ334" s="6"/>
+    </row>
+    <row r="335" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="18"/>
       <c r="E335" s="5"/>
-      <c r="BR335" s="6"/>
-    </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ335" s="6"/>
+    </row>
+    <row r="336" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="18"/>
       <c r="E336" s="5"/>
-      <c r="BR336" s="6"/>
-    </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ336" s="6"/>
+    </row>
+    <row r="337" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="18"/>
       <c r="E337" s="5"/>
-      <c r="BO337" s="6"/>
-      <c r="BR337" s="6"/>
-    </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN337" s="6"/>
+      <c r="BQ337" s="6"/>
+    </row>
+    <row r="338" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="18"/>
       <c r="E338" s="5"/>
-      <c r="BO338" s="6"/>
-      <c r="BR338" s="6"/>
-    </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN338" s="6"/>
+      <c r="BQ338" s="6"/>
+    </row>
+    <row r="339" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="18"/>
       <c r="E339" s="5"/>
-      <c r="BO339" s="6"/>
-      <c r="BR339" s="6"/>
-    </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN339" s="6"/>
+      <c r="BQ339" s="6"/>
+    </row>
+    <row r="340" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="18"/>
       <c r="E340" s="5"/>
-      <c r="BO340" s="6"/>
-      <c r="BR340" s="6"/>
-    </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN340" s="6"/>
+      <c r="BQ340" s="6"/>
+    </row>
+    <row r="341" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="18"/>
       <c r="E341" s="5"/>
-      <c r="BO341" s="6"/>
-      <c r="BR341" s="6"/>
-    </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN341" s="6"/>
+      <c r="BQ341" s="6"/>
+    </row>
+    <row r="342" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="18"/>
       <c r="E342" s="5"/>
-      <c r="BO342" s="6"/>
-      <c r="BR342" s="6"/>
-    </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN342" s="6"/>
+      <c r="BQ342" s="6"/>
+    </row>
+    <row r="343" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="18"/>
       <c r="E343" s="5"/>
-      <c r="BO343" s="6"/>
-      <c r="BR343" s="6"/>
-    </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN343" s="6"/>
+      <c r="BQ343" s="6"/>
+    </row>
+    <row r="344" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="18"/>
       <c r="E344" s="5"/>
-      <c r="BO344" s="6"/>
-      <c r="BR344" s="6"/>
-    </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN344" s="6"/>
+      <c r="BQ344" s="6"/>
+    </row>
+    <row r="345" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="18"/>
       <c r="E345" s="5"/>
-      <c r="BO345" s="6"/>
-      <c r="BR345" s="6"/>
-    </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN345" s="6"/>
+      <c r="BQ345" s="6"/>
+    </row>
+    <row r="346" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="18"/>
       <c r="E346" s="5"/>
-      <c r="BO346" s="6"/>
-      <c r="BR346" s="6"/>
-    </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN346" s="6"/>
+      <c r="BQ346" s="6"/>
+    </row>
+    <row r="347" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="18"/>
       <c r="E347" s="5"/>
-      <c r="BO347" s="6"/>
-      <c r="BR347" s="6"/>
-    </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN347" s="6"/>
+      <c r="BQ347" s="6"/>
+    </row>
+    <row r="348" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="18"/>
       <c r="E348" s="5"/>
-      <c r="BO348" s="6"/>
-      <c r="BR348" s="6"/>
-    </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN348" s="6"/>
+      <c r="BQ348" s="6"/>
+    </row>
+    <row r="349" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="18"/>
       <c r="E349" s="5"/>
-      <c r="BO349" s="6"/>
-      <c r="BR349" s="6"/>
-    </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN349" s="6"/>
+      <c r="BQ349" s="6"/>
+    </row>
+    <row r="350" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="18"/>
       <c r="E350" s="5"/>
-      <c r="BO350" s="6"/>
-      <c r="BR350" s="6"/>
-    </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN350" s="6"/>
+      <c r="BQ350" s="6"/>
+    </row>
+    <row r="351" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="18"/>
       <c r="E351" s="5"/>
-      <c r="BO351" s="6"/>
-      <c r="BR351" s="6"/>
-    </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN351" s="6"/>
+      <c r="BQ351" s="6"/>
+    </row>
+    <row r="352" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="18"/>
       <c r="E352" s="5"/>
-      <c r="BO352" s="6"/>
-      <c r="BR352" s="6"/>
-    </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN352" s="6"/>
+      <c r="BQ352" s="6"/>
+    </row>
+    <row r="353" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="18"/>
       <c r="E353" s="5"/>
-      <c r="BO353" s="6"/>
-      <c r="BR353" s="6"/>
-    </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN353" s="6"/>
+      <c r="BQ353" s="6"/>
+    </row>
+    <row r="354" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="18"/>
       <c r="E354" s="5"/>
-      <c r="BO354" s="6"/>
-      <c r="BR354" s="6"/>
-    </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN354" s="6"/>
+      <c r="BQ354" s="6"/>
+    </row>
+    <row r="355" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="18"/>
       <c r="E355" s="5"/>
-      <c r="BO355" s="6"/>
-      <c r="BR355" s="6"/>
-    </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN355" s="6"/>
+      <c r="BQ355" s="6"/>
+    </row>
+    <row r="356" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="18"/>
       <c r="E356" s="5"/>
-      <c r="BO356" s="6"/>
-      <c r="BR356" s="6"/>
-    </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN356" s="6"/>
+      <c r="BQ356" s="6"/>
+    </row>
+    <row r="357" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="18"/>
       <c r="E357" s="5"/>
-      <c r="BO357" s="6"/>
-      <c r="BR357" s="6"/>
-    </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN357" s="6"/>
+      <c r="BQ357" s="6"/>
+    </row>
+    <row r="358" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="18"/>
       <c r="E358" s="5"/>
-      <c r="BO358" s="6"/>
-      <c r="BR358" s="6"/>
-    </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN358" s="6"/>
+      <c r="BQ358" s="6"/>
+    </row>
+    <row r="359" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="18"/>
       <c r="E359" s="5"/>
-      <c r="BO359" s="6"/>
-      <c r="BR359" s="6"/>
-    </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN359" s="6"/>
+      <c r="BQ359" s="6"/>
+    </row>
+    <row r="360" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="18"/>
       <c r="E360" s="5"/>
-      <c r="BO360" s="6"/>
-      <c r="BR360" s="6"/>
-    </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN360" s="6"/>
+      <c r="BQ360" s="6"/>
+    </row>
+    <row r="361" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="18"/>
       <c r="E361" s="5"/>
-      <c r="BO361" s="6"/>
-      <c r="BR361" s="6"/>
-    </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN361" s="6"/>
+      <c r="BQ361" s="6"/>
+    </row>
+    <row r="362" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="18"/>
       <c r="E362" s="5"/>
-      <c r="BO362" s="6"/>
-      <c r="BR362" s="6"/>
-    </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN362" s="6"/>
+      <c r="BQ362" s="6"/>
+    </row>
+    <row r="363" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="18"/>
       <c r="E363" s="5"/>
-      <c r="BO363" s="6"/>
-      <c r="BR363" s="6"/>
-    </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN363" s="6"/>
+      <c r="BQ363" s="6"/>
+    </row>
+    <row r="364" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="18"/>
       <c r="E364" s="5"/>
-      <c r="BO364" s="6"/>
-      <c r="BR364" s="6"/>
-    </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN364" s="6"/>
+      <c r="BQ364" s="6"/>
+    </row>
+    <row r="365" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="18"/>
       <c r="E365" s="5"/>
-      <c r="BO365" s="6"/>
-      <c r="BR365" s="6"/>
-    </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN365" s="6"/>
+      <c r="BQ365" s="6"/>
+    </row>
+    <row r="366" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="18"/>
       <c r="E366" s="5"/>
-      <c r="BO366" s="6"/>
-      <c r="BR366" s="6"/>
-    </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN366" s="6"/>
+      <c r="BQ366" s="6"/>
+    </row>
+    <row r="367" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="18"/>
       <c r="E367" s="5"/>
-      <c r="BO367" s="6"/>
-      <c r="BR367" s="6"/>
-    </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN367" s="6"/>
+      <c r="BQ367" s="6"/>
+    </row>
+    <row r="368" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="18"/>
       <c r="E368" s="5"/>
-      <c r="BO368" s="6"/>
-      <c r="BR368" s="6"/>
-    </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN368" s="6"/>
+      <c r="BQ368" s="6"/>
+    </row>
+    <row r="369" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="18"/>
       <c r="E369" s="5"/>
-      <c r="BO369" s="6"/>
-      <c r="BR369" s="6"/>
-    </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN369" s="6"/>
+      <c r="BQ369" s="6"/>
+    </row>
+    <row r="370" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="18"/>
       <c r="E370" s="5"/>
-      <c r="BO370" s="6"/>
-      <c r="BR370" s="6"/>
-    </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN370" s="6"/>
+      <c r="BQ370" s="6"/>
+    </row>
+    <row r="371" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="18"/>
       <c r="E371" s="5"/>
-      <c r="BR371" s="6"/>
-    </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ371" s="6"/>
+    </row>
+    <row r="372" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="18"/>
       <c r="E372" s="5"/>
-      <c r="BR372" s="6"/>
-    </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ372" s="6"/>
+    </row>
+    <row r="373" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="18"/>
       <c r="E373" s="5"/>
-      <c r="BO373" s="6"/>
-      <c r="BR373" s="6"/>
-    </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN373" s="6"/>
+      <c r="BQ373" s="6"/>
+    </row>
+    <row r="374" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="18"/>
       <c r="E374" s="5"/>
-      <c r="BO374" s="6"/>
-      <c r="BR374" s="6"/>
-    </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN374" s="6"/>
+      <c r="BQ374" s="6"/>
+    </row>
+    <row r="375" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="18"/>
       <c r="E375" s="5"/>
-      <c r="BO375" s="6"/>
-      <c r="BR375" s="6"/>
-    </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN375" s="6"/>
+      <c r="BQ375" s="6"/>
+    </row>
+    <row r="376" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="18"/>
       <c r="E376" s="5"/>
-      <c r="BO376" s="6"/>
-      <c r="BR376" s="6"/>
-    </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN376" s="6"/>
+      <c r="BQ376" s="6"/>
+    </row>
+    <row r="377" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="18"/>
       <c r="E377" s="5"/>
-      <c r="BO377" s="6"/>
-      <c r="BR377" s="6"/>
-    </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN377" s="6"/>
+      <c r="BQ377" s="6"/>
+    </row>
+    <row r="378" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="18"/>
       <c r="E378" s="5"/>
-      <c r="BO378" s="6"/>
-      <c r="BR378" s="6"/>
-    </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN378" s="6"/>
+      <c r="BQ378" s="6"/>
+    </row>
+    <row r="379" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="18"/>
       <c r="E379" s="5"/>
-      <c r="BO379" s="6"/>
-      <c r="BR379" s="6"/>
-    </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN379" s="6"/>
+      <c r="BQ379" s="6"/>
+    </row>
+    <row r="380" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="18"/>
       <c r="E380" s="5"/>
-      <c r="BO380" s="6"/>
-      <c r="BR380" s="6"/>
-    </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN380" s="6"/>
+      <c r="BQ380" s="6"/>
+    </row>
+    <row r="381" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="18"/>
       <c r="E381" s="5"/>
-      <c r="BO381" s="6"/>
-      <c r="BR381" s="6"/>
-    </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN381" s="6"/>
+      <c r="BQ381" s="6"/>
+    </row>
+    <row r="382" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="18"/>
       <c r="E382" s="5"/>
-      <c r="BO382" s="6"/>
-      <c r="BR382" s="6"/>
-    </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN382" s="6"/>
+      <c r="BQ382" s="6"/>
+    </row>
+    <row r="383" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="18"/>
       <c r="E383" s="5"/>
-      <c r="BO383" s="6"/>
-      <c r="BR383" s="6"/>
-    </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN383" s="6"/>
+      <c r="BQ383" s="6"/>
+    </row>
+    <row r="384" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="18"/>
       <c r="E384" s="5"/>
-      <c r="BO384" s="6"/>
-      <c r="BR384" s="6"/>
-    </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN384" s="6"/>
+      <c r="BQ384" s="6"/>
+    </row>
+    <row r="385" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="18"/>
       <c r="E385" s="5"/>
-      <c r="BO385" s="6"/>
-      <c r="BR385" s="6"/>
-    </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN385" s="6"/>
+      <c r="BQ385" s="6"/>
+    </row>
+    <row r="386" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="18"/>
       <c r="E386" s="5"/>
-      <c r="BO386" s="6"/>
-      <c r="BR386" s="6"/>
-    </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN386" s="6"/>
+      <c r="BQ386" s="6"/>
+    </row>
+    <row r="387" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="18"/>
       <c r="E387" s="5"/>
-      <c r="BO387" s="6"/>
-      <c r="BR387" s="6"/>
-    </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN387" s="6"/>
+      <c r="BQ387" s="6"/>
+    </row>
+    <row r="388" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="18"/>
       <c r="E388" s="5"/>
-      <c r="BO388" s="6"/>
-      <c r="BR388" s="6"/>
-    </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN388" s="6"/>
+      <c r="BQ388" s="6"/>
+    </row>
+    <row r="389" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="18"/>
       <c r="E389" s="5"/>
-      <c r="BO389" s="6"/>
-      <c r="BR389" s="6"/>
-    </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN389" s="6"/>
+      <c r="BQ389" s="6"/>
+    </row>
+    <row r="390" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="18"/>
       <c r="E390" s="5"/>
-      <c r="BO390" s="6"/>
-      <c r="BR390" s="6"/>
-    </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN390" s="6"/>
+      <c r="BQ390" s="6"/>
+    </row>
+    <row r="391" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="18"/>
       <c r="E391" s="5"/>
-      <c r="BO391" s="6"/>
-      <c r="BR391" s="6"/>
-    </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN391" s="6"/>
+      <c r="BQ391" s="6"/>
+    </row>
+    <row r="392" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="18"/>
       <c r="E392" s="5"/>
-      <c r="BO392" s="6"/>
-      <c r="BR392" s="6"/>
-    </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN392" s="6"/>
+      <c r="BQ392" s="6"/>
+    </row>
+    <row r="393" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="18"/>
       <c r="E393" s="5"/>
-      <c r="BO393" s="6"/>
-      <c r="BR393" s="6"/>
-    </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN393" s="6"/>
+      <c r="BQ393" s="6"/>
+    </row>
+    <row r="394" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="18"/>
       <c r="E394" s="5"/>
-      <c r="BO394" s="6"/>
-      <c r="BR394" s="6"/>
-    </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN394" s="6"/>
+      <c r="BQ394" s="6"/>
+    </row>
+    <row r="395" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="18"/>
       <c r="E395" s="5"/>
-      <c r="BO395" s="6"/>
-      <c r="BR395" s="6"/>
-    </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN395" s="6"/>
+      <c r="BQ395" s="6"/>
+    </row>
+    <row r="396" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="18"/>
       <c r="E396" s="5"/>
-      <c r="BR396" s="6"/>
-    </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ396" s="6"/>
+    </row>
+    <row r="397" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="18"/>
       <c r="E397" s="5"/>
-      <c r="BR397" s="6"/>
-    </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ397" s="6"/>
+    </row>
+    <row r="398" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="18"/>
       <c r="E398" s="5"/>
-      <c r="BO398" s="6"/>
-      <c r="BR398" s="6"/>
-    </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN398" s="6"/>
+      <c r="BQ398" s="6"/>
+    </row>
+    <row r="399" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="18"/>
       <c r="E399" s="5"/>
-      <c r="BO399" s="6"/>
-      <c r="BR399" s="6"/>
-    </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN399" s="6"/>
+      <c r="BQ399" s="6"/>
+    </row>
+    <row r="400" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="18"/>
       <c r="E400" s="5"/>
-      <c r="BR400" s="6"/>
-    </row>
-    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ400" s="6"/>
+    </row>
+    <row r="401" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="18"/>
       <c r="E401" s="5"/>
-      <c r="BR401" s="6"/>
-    </row>
-    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ401" s="6"/>
+    </row>
+    <row r="402" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="18"/>
       <c r="E402" s="5"/>
-      <c r="BO402" s="6"/>
-      <c r="BR402" s="6"/>
-    </row>
-    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN402" s="6"/>
+      <c r="BQ402" s="6"/>
+    </row>
+    <row r="403" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="18"/>
       <c r="E403" s="5"/>
-      <c r="BO403" s="6"/>
-      <c r="BR403" s="6"/>
-    </row>
-    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN403" s="6"/>
+      <c r="BQ403" s="6"/>
+    </row>
+    <row r="404" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="18"/>
       <c r="E404" s="5"/>
-      <c r="BO404" s="6"/>
-      <c r="BR404" s="6"/>
-    </row>
-    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN404" s="6"/>
+      <c r="BQ404" s="6"/>
+    </row>
+    <row r="405" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="18"/>
       <c r="E405" s="5"/>
-      <c r="BO405" s="6"/>
-      <c r="BR405" s="6"/>
-    </row>
-    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN405" s="6"/>
+      <c r="BQ405" s="6"/>
+    </row>
+    <row r="406" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="18"/>
       <c r="E406" s="5"/>
-      <c r="BO406" s="6"/>
-      <c r="BR406" s="6"/>
-    </row>
-    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN406" s="6"/>
+      <c r="BQ406" s="6"/>
+    </row>
+    <row r="407" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="18"/>
       <c r="E407" s="5"/>
-      <c r="BO407" s="6"/>
-      <c r="BR407" s="6"/>
-    </row>
-    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN407" s="6"/>
+      <c r="BQ407" s="6"/>
+    </row>
+    <row r="408" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="18"/>
       <c r="E408" s="5"/>
-      <c r="BO408" s="6"/>
-      <c r="BR408" s="6"/>
-    </row>
-    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN408" s="6"/>
+      <c r="BQ408" s="6"/>
+    </row>
+    <row r="409" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="18"/>
       <c r="E409" s="5"/>
-      <c r="BO409" s="6"/>
-      <c r="BR409" s="6"/>
-    </row>
-    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN409" s="6"/>
+      <c r="BQ409" s="6"/>
+    </row>
+    <row r="410" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="18"/>
       <c r="E410" s="5"/>
-      <c r="BO410" s="6"/>
-      <c r="BR410" s="6"/>
-    </row>
-    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN410" s="6"/>
+      <c r="BQ410" s="6"/>
+    </row>
+    <row r="411" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="18"/>
       <c r="E411" s="5"/>
-      <c r="BO411" s="6"/>
-      <c r="BR411" s="6"/>
-    </row>
-    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN411" s="6"/>
+      <c r="BQ411" s="6"/>
+    </row>
+    <row r="412" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="18"/>
       <c r="E412" s="5"/>
-      <c r="BO412" s="6"/>
-      <c r="BR412" s="6"/>
-    </row>
-    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN412" s="6"/>
+      <c r="BQ412" s="6"/>
+    </row>
+    <row r="413" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="18"/>
       <c r="E413" s="5"/>
-      <c r="BO413" s="6"/>
-      <c r="BR413" s="6"/>
-    </row>
-    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN413" s="6"/>
+      <c r="BQ413" s="6"/>
+    </row>
+    <row r="414" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="18"/>
       <c r="E414" s="5"/>
-      <c r="BO414" s="6"/>
-      <c r="BR414" s="6"/>
-    </row>
-    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN414" s="6"/>
+      <c r="BQ414" s="6"/>
+    </row>
+    <row r="415" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="18"/>
       <c r="E415" s="5"/>
-      <c r="BO415" s="6"/>
-      <c r="BR415" s="6"/>
-    </row>
-    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN415" s="6"/>
+      <c r="BQ415" s="6"/>
+    </row>
+    <row r="416" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="18"/>
       <c r="E416" s="5"/>
-      <c r="BO416" s="6"/>
-      <c r="BR416" s="6"/>
-    </row>
-    <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN416" s="6"/>
+      <c r="BQ416" s="6"/>
+    </row>
+    <row r="417" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D417" s="18"/>
       <c r="E417" s="5"/>
-      <c r="BO417" s="6"/>
-      <c r="BR417" s="6"/>
-    </row>
-    <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN417" s="6"/>
+      <c r="BQ417" s="6"/>
+    </row>
+    <row r="418" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D418" s="18"/>
       <c r="E418" s="5"/>
-      <c r="BO418" s="6"/>
-      <c r="BR418" s="6"/>
-    </row>
-    <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN418" s="6"/>
+      <c r="BQ418" s="6"/>
+    </row>
+    <row r="419" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D419" s="18"/>
       <c r="E419" s="5"/>
     </row>
-    <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D420" s="18"/>
       <c r="E420" s="5"/>
     </row>
-    <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D421" s="18"/>
       <c r="E421" s="5"/>
     </row>
-    <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D422" s="18"/>
       <c r="E422" s="5"/>
     </row>
-    <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D423" s="18"/>
       <c r="E423" s="5"/>
     </row>
-    <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D424" s="18"/>
       <c r="E424" s="5"/>
     </row>
-    <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D425" s="18"/>
       <c r="E425" s="5"/>
     </row>
-    <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D426" s="18"/>
       <c r="E426" s="5"/>
     </row>
-    <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D427" s="18"/>
       <c r="E427" s="5"/>
     </row>
-    <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D428" s="18"/>
       <c r="E428" s="5"/>
     </row>
-    <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D429" s="18"/>
       <c r="E429" s="5"/>
     </row>
-    <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D430" s="18"/>
       <c r="E430" s="5"/>
     </row>
-    <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D431" s="18"/>
       <c r="E431" s="5"/>
     </row>
-    <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D432" s="18"/>
       <c r="E432" s="5"/>
     </row>
@@ -6481,334 +6480,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" t="s">
         <v>155</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>157</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>158</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="U1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="V1" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="W1" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="X1" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="Y1" t="s">
         <v>172</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="V1" s="9" t="s">
+      <c r="Z1" t="s">
         <v>173</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="AA1" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="AB1" t="s">
         <v>175</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>176</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>177</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AE1" t="s">
         <v>178</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>179</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>180</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>181</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>182</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>183</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>184</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>185</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AM1" t="s">
         <v>186</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AN1" t="s">
         <v>187</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AO1" t="s">
         <v>188</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>189</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>190</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="AT1" t="s">
         <v>191</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AU1" t="s">
         <v>192</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AV1" t="s">
         <v>193</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AW1" t="s">
         <v>194</v>
       </c>
-      <c r="AR1" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>195</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AY1" t="s">
         <v>196</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AZ1" t="s">
         <v>197</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BA1" t="s">
         <v>198</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BB1" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>200</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BD1" t="s">
         <v>201</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BE1" t="s">
         <v>202</v>
       </c>
-      <c r="BB1" s="8" t="s">
+      <c r="BF1" t="s">
         <v>203</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BG1" t="s">
         <v>204</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BH1" t="s">
         <v>205</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BJ1" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK1" t="s">
         <v>206</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>207</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BM1" t="s">
         <v>208</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BN1" t="s">
         <v>209</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>209</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BO1" t="s">
         <v>210</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BP1" t="s">
         <v>211</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BQ1" t="s">
         <v>212</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BR1" t="s">
         <v>213</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BS1" t="s">
         <v>214</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BT1" t="s">
         <v>215</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BU1" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="BU1" s="8" t="s">
+      <c r="BY1" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="BV1" s="10" t="s">
+      <c r="BZ1" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="BW1" s="10" t="s">
+      <c r="CA1" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="BX1" s="10" t="s">
+      <c r="CB1" t="s">
         <v>223</v>
       </c>
-      <c r="BY1" s="10" t="s">
+      <c r="CC1" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="BZ1" s="10" t="s">
+      <c r="CD1" t="s">
         <v>225</v>
       </c>
-      <c r="CA1" s="10" t="s">
+      <c r="CE1" t="s">
         <v>226</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>227</v>
       </c>
-      <c r="CC1" s="10" t="s">
+      <c r="CG1" t="s">
         <v>228</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>229</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>230</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>231</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>232</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>234</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>235</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>236</v>
       </c>
-      <c r="CL1" s="8" t="s">
+      <c r="CP1" t="s">
         <v>237</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>238</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
+        <v>215</v>
+      </c>
+      <c r="CS1" t="s">
         <v>239</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CT1" t="s">
         <v>240</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CU1" t="s">
         <v>241</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CV1" t="s">
         <v>242</v>
       </c>
-      <c r="CR1" t="s">
-        <v>219</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>243</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>244</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>245</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
+        <v>244</v>
+      </c>
+      <c r="DA1" t="s">
         <v>246</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DB1" t="s">
         <v>247</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DC1" t="s">
         <v>248</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DD1" t="s">
         <v>249</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>248</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>250</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>251</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>252</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DH1" t="s">
         <v>253</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DI1" t="s">
         <v>254</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>255</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>256</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>257</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6816,337 +6815,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J2" t="s">
+        <v>259</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>285</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>286</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>287</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>289</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>290</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>291</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>292</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>295</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>296</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>297</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>300</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>301</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>302</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>303</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>305</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>309</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>312</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>313</v>
+      </c>
+      <c r="BO2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="I2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="S2" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="U2" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="V2" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="W2" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="X2" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AA2" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>290</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>291</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>293</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>295</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>296</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>297</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>298</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>299</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>300</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>301</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>302</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>303</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>304</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>305</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>309</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>311</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>312</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>313</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BP2" t="s">
         <v>314</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BQ2" t="s">
         <v>315</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BR2" t="s">
         <v>316</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BS2" t="s">
         <v>317</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BT2" t="s">
         <v>318</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV2" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BW2" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BX2" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BY2" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="BU2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="BV2" s="10" t="s">
+      <c r="BZ2" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="BW2" s="10" t="s">
+      <c r="CA2" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="BX2" s="10" t="s">
+      <c r="CB2" t="s">
         <v>325</v>
       </c>
-      <c r="BY2" s="10" t="s">
+      <c r="CC2" t="s">
         <v>326</v>
       </c>
-      <c r="BZ2" s="10" t="s">
+      <c r="CD2" t="s">
         <v>327</v>
       </c>
-      <c r="CA2" s="10" t="s">
+      <c r="CE2" t="s">
         <v>328</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CF2" t="s">
         <v>329</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CG2" t="s">
         <v>330</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CH2" t="s">
         <v>331</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CI2" t="s">
         <v>332</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
         <v>333</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CK2" t="s">
         <v>334</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CL2" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CM2" t="s">
         <v>336</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CN2" t="s">
         <v>337</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CO2" t="s">
         <v>338</v>
       </c>
-      <c r="CL2" s="8" t="s">
+      <c r="CP2" t="s">
         <v>339</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CQ2" t="s">
         <v>340</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CR2" t="s">
         <v>341</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CS2" t="s">
         <v>342</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CT2" t="s">
         <v>343</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CU2" t="s">
         <v>344</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CV2" t="s">
         <v>345</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CW2" t="s">
         <v>346</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CX2" t="s">
         <v>347</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CY2" t="s">
         <v>348</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CZ2" t="s">
         <v>349</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="DA2" t="s">
         <v>350</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DB2" t="s">
         <v>351</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DC2" t="s">
         <v>352</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DD2" t="s">
         <v>353</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DE2" t="s">
         <v>354</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DF2" t="s">
         <v>355</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DG2" t="s">
         <v>356</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DH2" t="s">
         <v>357</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DI2" t="s">
         <v>358</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>359</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>360</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>361</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -7166,356 +7165,356 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>359</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="J3" t="s">
-        <v>363</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="M3" s="9" t="s">
+      <c r="P3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>362</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI3" t="s">
         <v>118</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="V3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>366</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>122</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AN3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AO3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AP3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AT3" t="s">
+        <v>365</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>366</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>365</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>367</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>368</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV3" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW3" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="BX3" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY3" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="AU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
+      <c r="BZ3" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA3" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CC3" t="s">
         <v>370</v>
       </c>
-      <c r="AY3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>369</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="CD3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG3" t="s">
         <v>371</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="CH3" t="s">
         <v>372</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="BX3" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="BZ3" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>374</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>375</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>376</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="CK3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="CL3" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="CM3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CN3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CO3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CQ3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CR3" t="s">
+        <v>370</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CV3" t="s">
         <v>374</v>
       </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>378</v>
-      </c>
       <c r="CW3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CX3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CY3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="CZ3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="DA3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="DB3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="DC3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="DD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DE3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DF3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DG3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DH3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DI3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:113" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C6" t="s">
+        <v>377</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="S6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>383</v>
+      </c>
+      <c r="AT6" t="s">
         <v>384</v>
-      </c>
-      <c r="C6" t="s">
-        <v>381</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="S6" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>387</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>388</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -7530,58 +7529,58 @@
         <v>1</v>
       </c>
       <c r="BP6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="CB6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CG6" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C7" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="P7"/>
       <c r="AC7">
         <v>1</v>
       </c>
       <c r="AO7" t="s">
+        <v>383</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>384</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="s">
         <v>387</v>
       </c>
-      <c r="AT7" t="s">
+      <c r="CH7" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="CI7" t="s">
         <v>388</v>
       </c>
-      <c r="AY7">
-        <v>1</v>
-      </c>
-      <c r="AZ7">
-        <v>1</v>
-      </c>
-      <c r="BD7">
-        <v>1</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>391</v>
-      </c>
-      <c r="CH7" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="CI7" t="s">
-        <v>392</v>
-      </c>
       <c r="CN7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CO7">
         <v>22</v>
@@ -7590,21 +7589,21 @@
         <v>10</v>
       </c>
       <c r="CY7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C8" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AC8">
         <v>1</v>
@@ -7613,14 +7612,14 @@
         <v>1</v>
       </c>
       <c r="AG8" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD8">
         <v>1</v>
       </c>
       <c r="CL8" s="9"/>
       <c r="CU8" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="DD8">
         <v>1</v>
@@ -7634,19 +7633,19 @@
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="M9"/>
       <c r="N9"/>
@@ -7664,16 +7663,16 @@
         <v>1</v>
       </c>
       <c r="AG9" t="s">
+        <v>394</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>397</v>
+      </c>
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="s">
         <v>398</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>401</v>
-      </c>
-      <c r="BD9">
-        <v>1</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>402</v>
       </c>
       <c r="BU9" s="14"/>
       <c r="BV9" s="14"/>
@@ -7683,7 +7682,7 @@
       <c r="BZ9" s="14"/>
       <c r="CA9"/>
       <c r="CN9" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="CO9">
         <v>8</v>
@@ -7697,10 +7696,10 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C10" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -7723,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="AT10" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="BD10">
         <v>99</v>
@@ -7739,7 +7738,7 @@
       <c r="BZ10" s="14"/>
       <c r="CA10"/>
       <c r="CN10" s="12" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="CO10">
         <v>0.2</v>
@@ -7753,22 +7752,22 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C11" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AY11" s="9"/>
       <c r="BD11">
@@ -7792,7 +7791,7 @@
       <c r="CL11" s="9"/>
       <c r="CM11" s="9"/>
       <c r="CN11" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="CR11">
         <v>99999</v>
@@ -7800,10 +7799,10 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C12" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -7842,7 +7841,7 @@
       <c r="CL12" s="9"/>
       <c r="CM12" s="9"/>
       <c r="CN12" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="CR12">
         <v>0.2</v>
@@ -7850,21 +7849,21 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M13"/>
       <c r="N13"/>
       <c r="P13" s="12" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="R13" s="12"/>
       <c r="S13"/>
@@ -7873,10 +7872,10 @@
         <v>1</v>
       </c>
       <c r="AG13" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AT13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -7884,7 +7883,7 @@
       <c r="BV13"/>
       <c r="CB13" s="10"/>
       <c r="CN13" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CO13">
         <v>22</v>
@@ -7904,28 +7903,28 @@
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E17" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F17" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="J17" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M17"/>
       <c r="O17"/>
@@ -7933,16 +7932,16 @@
         <v>1</v>
       </c>
       <c r="AG17" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD17">
         <v>1</v>
       </c>
       <c r="BO17" s="8" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BP17" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="BT17">
         <v>30</v>
@@ -7957,10 +7956,10 @@
         <v>1</v>
       </c>
       <c r="BY17" s="10" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="CN17" s="12" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="CR17">
         <v>30</v>
@@ -7971,15 +7970,15 @@
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C18" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="J18" s="9"/>
       <c r="M18"/>
       <c r="O18" s="12" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
@@ -7990,10 +7989,10 @@
         <v>1</v>
       </c>
       <c r="AO18" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AQ18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AW18">
         <v>1</v>
@@ -8008,22 +8007,22 @@
         <v>1</v>
       </c>
       <c r="BP18" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="CB18" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="CG18" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="CH18" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="CI18" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="CN18" s="8" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="CO18">
         <v>22</v>
@@ -8035,21 +8034,21 @@
         <v>10</v>
       </c>
       <c r="CY18" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C19" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M19"/>
       <c r="AC19">
@@ -8059,16 +8058,16 @@
         <v>1</v>
       </c>
       <c r="AJ19" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AO19" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AT19" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AX19" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AZ19">
         <v>1</v>
@@ -8081,13 +8080,13 @@
       </c>
       <c r="CB19" s="3"/>
       <c r="CH19" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="CI19" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="CN19" s="12" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="CR19">
         <v>0.1</v>
@@ -8101,20 +8100,20 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C20" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M20"/>
       <c r="O20" s="12" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="P20"/>
       <c r="Q20"/>
@@ -8122,7 +8121,7 @@
         <v>1</v>
       </c>
       <c r="AG20" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AW20">
         <v>1</v>
@@ -8131,7 +8130,7 @@
         <v>1</v>
       </c>
       <c r="CN20" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="CO20">
         <v>22</v>
@@ -8145,17 +8144,17 @@
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C21" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="M21"/>
       <c r="O21" s="12" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
@@ -8163,10 +8162,10 @@
         <v>1</v>
       </c>
       <c r="AJ21" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AT21" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BD21">
         <v>1</v>
@@ -8175,7 +8174,7 @@
         <v>0.1</v>
       </c>
       <c r="CN21" s="12" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="CR21">
         <v>0.2</v>
@@ -8183,23 +8182,23 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C22" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M22"/>
       <c r="AC22">
         <v>1</v>
       </c>
       <c r="AG22" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AY22" s="9"/>
       <c r="BD22">
@@ -8221,7 +8220,7 @@
       <c r="CJ22" s="9"/>
       <c r="CK22" s="9"/>
       <c r="CN22" s="12" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="CR22">
         <v>40</v>
@@ -8235,20 +8234,20 @@
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C23" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="M23"/>
       <c r="O23" s="12" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AC23">
         <v>1</v>
@@ -8260,21 +8259,21 @@
         <v>99</v>
       </c>
       <c r="CM23" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C24" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M24"/>
       <c r="N24"/>
@@ -8282,7 +8281,7 @@
         <v>1</v>
       </c>
       <c r="AG24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD24">
         <v>1</v>
@@ -8292,10 +8291,10 @@
       </c>
       <c r="BV24"/>
       <c r="CB24" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="CG24" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="CI24" s="9"/>
       <c r="CJ24" s="9"/>
@@ -8311,19 +8310,19 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C25" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="M25"/>
       <c r="N25"/>
@@ -8331,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="AG25" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD25">
         <v>1</v>
@@ -8341,10 +8340,10 @@
       </c>
       <c r="BV25"/>
       <c r="CB25" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="CG25" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="CJ25" s="9"/>
       <c r="DD25">
@@ -8359,19 +8358,19 @@
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C26" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D26" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E26" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F26" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G26">
         <v>3</v>
@@ -8381,19 +8380,19 @@
       </c>
       <c r="M26"/>
       <c r="O26" s="12" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="AC26">
         <v>1</v>
       </c>
       <c r="AG26" s="8" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AO26" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AT26" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AY26">
         <v>1</v>
@@ -8410,17 +8409,17 @@
         <v>0.1</v>
       </c>
       <c r="CG26" s="8" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="CH26" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="CI26" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="CM26" s="8"/>
       <c r="CN26" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="CO26">
         <v>22</v>
@@ -8432,7 +8431,7 @@
         <v>10</v>
       </c>
       <c r="CY26" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="DD26">
         <v>1</v>
@@ -8444,31 +8443,31 @@
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C28" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D28" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E28" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F28" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="G28">
         <v>3</v>
       </c>
       <c r="J28" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="O28" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="W28"/>
       <c r="X28"/>
@@ -8476,16 +8475,16 @@
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD28">
         <v>1</v>
       </c>
       <c r="BO28" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="BP28" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="BT28">
         <v>1</v>
@@ -8500,13 +8499,13 @@
         <v>1</v>
       </c>
       <c r="BY28" s="10" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="CN28" s="12" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="CO28" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="CR28">
         <v>25</v>
@@ -8514,17 +8513,17 @@
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C29" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="M29"/>
       <c r="O29" s="12" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="P29"/>
       <c r="Q29"/>
@@ -8532,10 +8531,10 @@
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AT29" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BD29">
         <v>1</v>
@@ -8544,7 +8543,7 @@
         <v>0.1</v>
       </c>
       <c r="CN29" s="12" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="CR29">
         <v>0.2</v>
@@ -8552,28 +8551,28 @@
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C30" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I30">
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AC30">
         <v>1</v>
       </c>
       <c r="AJ30" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AT30" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BD30">
         <v>1</v>
@@ -8583,24 +8582,24 @@
       </c>
       <c r="CL30" s="9"/>
       <c r="CU30" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C31" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I31">
         <v>1</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="M31"/>
       <c r="N31"/>
@@ -8608,7 +8607,7 @@
         <v>1</v>
       </c>
       <c r="AG31" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD31">
         <v>1</v>
@@ -8618,10 +8617,10 @@
       </c>
       <c r="BV31"/>
       <c r="CB31" s="15" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="CG31" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="CJ31" s="9"/>
       <c r="DD31">
@@ -8636,16 +8635,16 @@
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C32" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M32"/>
       <c r="N32"/>
@@ -8653,7 +8652,7 @@
         <v>1</v>
       </c>
       <c r="AG32" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD32">
         <v>1</v>
@@ -8663,10 +8662,10 @@
       </c>
       <c r="BV32"/>
       <c r="CB32" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="CG32" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="CI32" s="9"/>
       <c r="CJ32" s="9"/>
@@ -8682,28 +8681,28 @@
     </row>
     <row r="34" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C34" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D34" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E34" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F34" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="G34">
         <v>3</v>
       </c>
       <c r="J34" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="O34"/>
       <c r="W34"/>
@@ -8712,13 +8711,13 @@
         <v>1</v>
       </c>
       <c r="AG34" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD34">
         <v>1</v>
       </c>
       <c r="BO34" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="BT34">
         <v>25</v>
@@ -8733,13 +8732,13 @@
         <v>1</v>
       </c>
       <c r="BY34" s="10" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="CN34" s="12" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="CO34" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="CP34">
         <v>80</v>
@@ -8750,64 +8749,64 @@
     </row>
     <row r="35" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C35" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="X35"/>
       <c r="AC35">
         <v>2</v>
       </c>
       <c r="AO35" t="s">
+        <v>456</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>400</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>422</v>
+      </c>
+      <c r="AZ35">
+        <v>1</v>
+      </c>
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="s">
+        <v>457</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>458</v>
+      </c>
+      <c r="CG35" t="s">
+        <v>386</v>
+      </c>
+      <c r="CX35" t="s">
+        <v>459</v>
+      </c>
+      <c r="CY35" t="s">
         <v>460</v>
-      </c>
-      <c r="AT35" t="s">
-        <v>404</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>426</v>
-      </c>
-      <c r="AZ35">
-        <v>1</v>
-      </c>
-      <c r="BD35">
-        <v>1</v>
-      </c>
-      <c r="BP35" t="s">
-        <v>461</v>
-      </c>
-      <c r="CB35" t="s">
-        <v>462</v>
-      </c>
-      <c r="CG35" t="s">
-        <v>390</v>
-      </c>
-      <c r="CX35" t="s">
-        <v>463</v>
-      </c>
-      <c r="CY35" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="36" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C36" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I36">
         <v>1</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="P36"/>
       <c r="Q36"/>
@@ -8816,13 +8815,13 @@
         <v>1</v>
       </c>
       <c r="AG36" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AH36">
         <v>1</v>
       </c>
       <c r="AO36" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AV36">
         <v>1</v>
@@ -8837,13 +8836,13 @@
         <v>1</v>
       </c>
       <c r="CH36" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="CI36" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="CN36" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CO36">
         <v>22</v>
@@ -8854,57 +8853,57 @@
     </row>
     <row r="37" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C37" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AC37">
         <v>1</v>
       </c>
       <c r="AG37" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD37">
         <v>1</v>
       </c>
       <c r="CU37" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C38" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AC38">
         <v>1</v>
       </c>
       <c r="AG38" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BD38">
         <v>1</v>
       </c>
       <c r="CN38" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="CR38">
         <v>0.5</v>
@@ -8912,10 +8911,10 @@
     </row>
     <row r="39" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C39" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -8936,7 +8935,7 @@
         <v>0.1</v>
       </c>
       <c r="CN39" s="12" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="CR39">
         <v>0.5</v>
@@ -10327,37 +10326,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F1" t="s">
+        <v>467</v>
+      </c>
+      <c r="G1" t="s">
+        <v>468</v>
+      </c>
+      <c r="H1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I1" t="s">
         <v>470</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>471</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>472</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>473</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>474</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>475</v>
       </c>
-      <c r="L1" t="s">
-        <v>476</v>
-      </c>
-      <c r="M1" t="s">
-        <v>477</v>
-      </c>
-      <c r="N1" t="s">
-        <v>478</v>
-      </c>
-      <c r="O1" t="s">
-        <v>479</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10365,49 +10364,49 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I2" t="s">
         <v>480</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>481</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>482</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
         <v>483</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>484</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>485</v>
       </c>
-      <c r="K2" t="s">
-        <v>486</v>
-      </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>487</v>
-      </c>
-      <c r="N2" t="s">
-        <v>488</v>
-      </c>
-      <c r="O2" t="s">
-        <v>489</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="Q2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -10421,133 +10420,133 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="Q4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C5" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Q5" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C6" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="Q6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C7" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Q7" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C9" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -10556,15 +10555,15 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C10" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -10573,15 +10572,15 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -10590,24 +10589,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C12" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -10616,10 +10615,10 @@
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -10628,122 +10627,122 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Q15" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
       </c>
       <c r="J16"/>
       <c r="Q16" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C17" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Q17" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J18" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J19" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J20" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J21" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Q23" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C24" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -10771,7 +10770,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10779,13 +10778,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10796,10 +10795,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -10822,7 +10821,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10830,31 +10829,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="G2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="I2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10871,22 +10870,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -10918,34 +10917,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E1" t="s">
+        <v>523</v>
+      </c>
+      <c r="F1" t="s">
         <v>524</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>525</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>526</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>527</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>528</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>529</v>
-      </c>
-      <c r="I1" t="s">
-        <v>530</v>
-      </c>
-      <c r="J1" t="s">
-        <v>531</v>
-      </c>
-      <c r="K1" t="s">
-        <v>532</v>
-      </c>
-      <c r="L1" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10953,37 +10952,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F2" t="s">
         <v>534</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>535</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>536</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>537</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>538</v>
       </c>
-      <c r="G2" t="s">
-        <v>539</v>
-      </c>
-      <c r="H2" t="s">
-        <v>540</v>
-      </c>
-      <c r="I2" t="s">
-        <v>541</v>
-      </c>
-      <c r="J2" t="s">
-        <v>542</v>
-      </c>
       <c r="K2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -10994,45 +10993,45 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E4" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -11046,13 +11045,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B5" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E5" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -11066,13 +11065,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B6" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E6" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -11086,13 +11085,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B7" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E7" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -11106,10 +11105,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B8" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -11148,31 +11147,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -11189,22 +11188,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -11232,89 +11231,89 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>568</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD972FE-BD25-4E3D-82D5-5385284CBD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234D0D8F-8355-47B5-9889-56B9DE93132D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="586">
   <si>
     <t>Id</t>
   </si>
@@ -2054,14 +2054,17 @@
   </si>
   <si>
     <t>BackSkelPath</t>
+  </si>
+  <si>
+    <t>干员M3</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2073,6 +2076,27 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2102,19 +2126,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2419,37 +2443,36 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
+      <c r="B4" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2458,1203 +2481,977 @@
   <dimension ref="A1:BT7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
-    <col min="8" max="8" width="9" customWidth="1" style="2"/>
-    <col min="9" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="9" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6" customWidth="1" style="2"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1" style="2"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="4" customWidth="1" style="2"/>
-    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
-    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
-    <col min="27" max="27" width="9" customWidth="1" style="2"/>
-    <col min="28" max="28" width="9" customWidth="1" style="2"/>
-    <col min="29" max="29" width="8" customWidth="1" style="2"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="9" customWidth="1" style="2"/>
-    <col min="32" max="32" width="9" customWidth="1" style="2"/>
-    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
-    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
-    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
-    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="9" customWidth="1" style="2"/>
-    <col min="41" max="41" width="9" customWidth="1" style="2"/>
-    <col min="42" max="42" width="9" customWidth="1" style="2"/>
-    <col min="43" max="43" width="9" customWidth="1" style="2"/>
-    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
-    <col min="45" max="45" width="9" customWidth="1" style="2"/>
-    <col min="46" max="46" width="9" customWidth="1" style="2"/>
-    <col min="47" max="47" width="9" customWidth="1" style="2"/>
-    <col min="48" max="48" width="9" customWidth="1" style="2"/>
-    <col min="49" max="49" width="9" customWidth="1" style="2"/>
-    <col min="50" max="50" width="9" customWidth="1" style="2"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
-    <col min="52" max="52" width="9" customWidth="1" style="2"/>
-    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
-    <col min="55" max="55" width="9" customWidth="1" style="2"/>
-    <col min="56" max="56" width="9" customWidth="1" style="2"/>
-    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
-    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8" customWidth="1" style="2"/>
-    <col min="61" max="61" width="9" customWidth="1" style="2"/>
-    <col min="62" max="62" width="9" customWidth="1" style="2"/>
-    <col min="63" max="63" width="9" customWidth="1" style="2"/>
-    <col min="64" max="64" width="9" customWidth="1" style="2"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
-    <col min="66" max="66" width="14" customWidth="1" style="2"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
-    <col min="71" max="71" width="14" customWidth="1" style="2"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="4.08203125" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1"/>
+    <col min="14" max="14" width="4" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1"/>
+    <col min="26" max="26" width="10.75" customWidth="1"/>
+    <col min="27" max="28" width="9" customWidth="1"/>
+    <col min="29" max="29" width="8" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1"/>
+    <col min="31" max="32" width="9" customWidth="1"/>
+    <col min="33" max="33" width="9.75" customWidth="1"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1"/>
+    <col min="37" max="37" width="34.5" customWidth="1"/>
+    <col min="38" max="39" width="9.83203125" customWidth="1"/>
+    <col min="40" max="43" width="9" customWidth="1"/>
+    <col min="44" max="44" width="12.5" customWidth="1"/>
+    <col min="45" max="50" width="9" customWidth="1"/>
+    <col min="51" max="51" width="24.33203125" customWidth="1"/>
+    <col min="52" max="52" width="9" customWidth="1"/>
+    <col min="53" max="53" width="17.75" customWidth="1"/>
+    <col min="54" max="54" width="7.83203125" customWidth="1"/>
+    <col min="55" max="56" width="9" customWidth="1"/>
+    <col min="57" max="57" width="24.25" customWidth="1"/>
+    <col min="58" max="58" width="13.25" customWidth="1"/>
+    <col min="59" max="59" width="16.08203125" customWidth="1"/>
+    <col min="60" max="60" width="8" customWidth="1"/>
+    <col min="61" max="64" width="9" customWidth="1"/>
+    <col min="65" max="65" width="39.58203125" customWidth="1"/>
+    <col min="66" max="66" width="14" customWidth="1"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1"/>
+    <col min="68" max="71" width="14" customWidth="1"/>
+    <col min="72" max="72" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2" t="s">
+      <c r="U1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2" t="s">
+      <c r="X1" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>43</v>
       </c>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>47</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" t="s">
         <v>48</v>
       </c>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>63</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>65</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>66</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>67</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>68</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>72</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" t="s">
         <v>73</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" t="s">
         <v>74</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>75</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" t="s">
         <v>76</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" t="s">
         <v>78</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" t="s">
         <v>79</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AI2" t="s">
         <v>80</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" t="s">
         <v>81</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AK2" t="s">
         <v>82</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" t="s">
         <v>83</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" t="s">
         <v>84</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AN2" t="s">
         <v>85</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AO2" t="s">
         <v>86</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AP2" t="s">
         <v>87</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AQ2" t="s">
         <v>88</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AR2" t="s">
         <v>89</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AS2" t="s">
         <v>90</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AT2" t="s">
         <v>91</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AU2" t="s">
         <v>92</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AV2" t="s">
         <v>93</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AW2" t="s">
         <v>94</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AX2" t="s">
         <v>95</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AY2" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AZ2" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BA2" t="s">
         <v>98</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BB2" t="s">
         <v>99</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>100</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BD2" t="s">
         <v>101</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BE2" t="s">
         <v>102</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BF2" t="s">
         <v>103</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BG2" t="s">
         <v>104</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BH2" t="s">
         <v>105</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BI2" t="s">
         <v>106</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BJ2" t="s">
         <v>107</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BK2" t="s">
         <v>108</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BL2" t="s">
         <v>109</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BM2" t="s">
         <v>110</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BN2" t="s">
         <v>111</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BO2" t="s">
         <v>112</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BP2" t="s">
         <v>113</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>114</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BR2" t="s">
         <v>115</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BS2" t="s">
         <v>116</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BT2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>120</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>120</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>120</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>120</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>120</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>120</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>120</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>120</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>120</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>120</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" t="s">
         <v>120</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" t="s">
         <v>119</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" t="s">
         <v>120</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" t="s">
         <v>120</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" t="s">
         <v>119</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" t="s">
         <v>119</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" t="s">
         <v>119</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" t="s">
         <v>120</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" t="s">
         <v>119</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" t="s">
         <v>120</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" t="s">
         <v>118</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AE3" t="s">
         <v>2</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AF3" t="s">
         <v>120</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" t="s">
         <v>120</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" t="s">
         <v>120</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AI3" t="s">
         <v>2</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ3" t="s">
         <v>2</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AK3" t="s">
         <v>121</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" t="s">
         <v>121</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" t="s">
         <v>120</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AN3" t="s">
         <v>119</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" t="s">
         <v>122</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AP3" t="s">
         <v>120</v>
       </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AQ3" t="s">
         <v>119</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" t="s">
         <v>118</v>
       </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2" t="s">
+      <c r="AT3" t="s">
         <v>119</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" t="s">
         <v>118</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AV3" t="s">
         <v>120</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AW3" t="s">
         <v>123</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" t="s">
         <v>119</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="AY3" t="s">
         <v>124</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="AZ3" t="s">
         <v>118</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" t="s">
         <v>118</v>
       </c>
-      <c r="BB3" s="2" t="s">
+      <c r="BB3" t="s">
         <v>119</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BC3" t="s">
         <v>125</v>
       </c>
-      <c r="BD3" s="2" t="s">
+      <c r="BD3" t="s">
         <v>2</v>
       </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BE3" t="s">
         <v>2</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BF3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" s="2" t="s">
+      <c r="BG3" t="s">
         <v>2</v>
       </c>
-      <c r="BH3" s="2" t="s">
+      <c r="BH3" t="s">
         <v>126</v>
       </c>
-      <c r="BI3" s="2" t="s">
+      <c r="BI3" t="s">
         <v>120</v>
       </c>
-      <c r="BJ3" s="2" t="s">
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BK3" t="s">
         <v>122</v>
       </c>
-      <c r="BL3" s="2" t="s">
+      <c r="BL3" t="s">
         <v>2</v>
       </c>
-      <c r="BM3" s="2" t="s">
+      <c r="BM3" t="s">
         <v>127</v>
       </c>
-      <c r="BN3" s="2" t="s">
+      <c r="BN3" t="s">
         <v>122</v>
       </c>
-      <c r="BO3" s="2" t="s">
+      <c r="BO3" t="s">
         <v>122</v>
       </c>
-      <c r="BP3" s="2" t="s">
+      <c r="BP3" t="s">
         <v>122</v>
       </c>
-      <c r="BQ3" s="2" t="s">
+      <c r="BQ3" t="s">
         <v>122</v>
       </c>
-      <c r="BR3" s="2" t="s">
+      <c r="BR3" t="s">
         <v>122</v>
       </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BS3" t="s">
         <v>122</v>
       </c>
-      <c r="BT3" s="2" t="s">
+      <c r="BT3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2"/>
-      <c r="BD4" s="2"/>
-      <c r="BE4" s="2"/>
-      <c r="BF4" s="2"/>
-      <c r="BG4" s="2"/>
-      <c r="BH4" s="2"/>
-      <c r="BI4" s="2"/>
-      <c r="BJ4" s="2"/>
-      <c r="BK4" s="2"/>
-      <c r="BL4" s="2"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2"/>
-      <c r="BO4" s="2"/>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2"/>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2"/>
-    </row>
-    <row r="5">
+    <row r="5" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>2</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5">
         <v>90</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5">
         <v>2235</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2">
+      <c r="M5">
         <v>583</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2">
+      <c r="O5">
         <v>221</v>
       </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2">
+      <c r="Q5">
         <v>0</v>
       </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2">
+      <c r="S5">
         <v>16</v>
       </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2">
+      <c r="U5">
         <v>0.5</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5">
         <v>70</v>
       </c>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2">
+      <c r="Y5">
         <v>0.05</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="Z5">
         <v>2.85</v>
       </c>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2" t="s">
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="s">
         <v>4</v>
       </c>
-      <c r="AJ5" s="2" t="s">
+      <c r="AJ5" t="s">
         <v>132</v>
       </c>
-      <c r="AK5" s="2" t="s">
+      <c r="AK5" t="s">
         <v>133</v>
       </c>
-      <c r="AL5" s="2" t="s">
+      <c r="AL5" t="s">
         <v>134</v>
       </c>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2" t="s">
+      <c r="AO5" t="s">
         <v>135</v>
       </c>
-      <c r="AP5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ5" s="2">
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
         <v>0.5</v>
       </c>
-      <c r="AR5" s="2"/>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2">
+      <c r="AX5">
         <v>0.25</v>
       </c>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2" t="s">
+      <c r="BC5" t="s">
         <v>136</v>
       </c>
-      <c r="BD5" s="2" t="s">
+      <c r="BD5" t="s">
         <v>137</v>
       </c>
-      <c r="BE5" s="2" t="s">
+      <c r="BE5" t="s">
         <v>138</v>
       </c>
-      <c r="BF5" s="2" t="s">
+      <c r="BF5" t="s">
         <v>139</v>
       </c>
-      <c r="BG5" s="2" t="s">
+      <c r="BG5" t="s">
         <v>140</v>
       </c>
-      <c r="BH5" s="2" t="s">
+      <c r="BH5" t="s">
         <v>141</v>
       </c>
-      <c r="BI5" s="2">
+      <c r="BI5">
         <v>6</v>
       </c>
-      <c r="BJ5" s="2" t="s">
+      <c r="BJ5" t="s">
         <v>142</v>
       </c>
-      <c r="BK5" s="2" t="s">
+      <c r="BK5" t="s">
         <v>143</v>
       </c>
-      <c r="BL5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="BN5" s="2" t="s">
+      <c r="BN5" t="s">
         <v>144</v>
       </c>
-      <c r="BO5" s="2" t="s">
+      <c r="BO5" t="s">
         <v>145</v>
       </c>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2" t="s">
+      <c r="BQ5" t="s">
         <v>146</v>
       </c>
-      <c r="BR5" s="2" t="s">
+      <c r="BR5" t="s">
         <v>146</v>
       </c>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="BT5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6">
         <v>90</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <v>5433</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2">
+      <c r="M6">
         <v>583</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2">
+      <c r="O6">
         <v>221</v>
       </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2">
+      <c r="Q6">
         <v>0</v>
       </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2">
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2">
+      <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6">
         <v>15</v>
       </c>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2">
+      <c r="Y6">
         <v>0.05</v>
       </c>
-      <c r="Z6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2">
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
         <v>0</v>
       </c>
-      <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2">
+      <c r="AG6">
         <v>-1</v>
       </c>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2" t="s">
+      <c r="AI6" t="s">
         <v>147</v>
       </c>
-      <c r="AJ6" s="2" t="s">
+      <c r="AJ6" t="s">
         <v>132</v>
       </c>
-      <c r="AK6" s="2" t="s">
+      <c r="AK6" t="s">
         <v>150</v>
       </c>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2">
+      <c r="AM6">
         <v>0</v>
       </c>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2" t="s">
+      <c r="AO6" t="s">
         <v>151</v>
       </c>
-      <c r="AP6" s="2">
+      <c r="AP6">
         <v>0</v>
       </c>
-      <c r="AQ6" s="2">
+      <c r="AQ6">
         <v>0</v>
       </c>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2" t="s">
+      <c r="AW6" t="s">
         <v>152</v>
       </c>
-      <c r="AX6" s="2">
+      <c r="AX6">
         <v>0.25</v>
       </c>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2" t="s">
+      <c r="BC6" t="s">
         <v>136</v>
       </c>
-      <c r="BD6" s="2"/>
-      <c r="BE6" s="2" t="s">
+      <c r="BE6" t="s">
         <v>153</v>
       </c>
-      <c r="BF6" s="2" t="s">
+      <c r="BF6" t="s">
         <v>154</v>
       </c>
-      <c r="BG6" s="2" t="s">
+      <c r="BG6" t="s">
         <v>148</v>
       </c>
-      <c r="BH6" s="2" t="s">
+      <c r="BH6" t="s">
         <v>141</v>
       </c>
-      <c r="BI6" s="2">
+      <c r="BI6">
         <v>6</v>
       </c>
-      <c r="BJ6" s="2" t="s">
+      <c r="BJ6" t="s">
         <v>155</v>
       </c>
-      <c r="BK6" s="2" t="s">
+      <c r="BK6" t="s">
         <v>147</v>
       </c>
-      <c r="BL6" s="2"/>
-      <c r="BM6" s="2"/>
-      <c r="BN6" s="2" t="s">
+      <c r="BN6" t="s">
         <v>144</v>
       </c>
-      <c r="BO6" s="2" t="s">
+      <c r="BO6" t="s">
         <v>145</v>
       </c>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2"/>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="BT6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>130</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>131</v>
       </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>2</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7">
         <v>90</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7">
         <v>2235</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2">
+      <c r="M7">
         <v>583</v>
       </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2">
+      <c r="O7">
         <v>221</v>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2">
+      <c r="Q7">
         <v>0</v>
       </c>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2">
+      <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2">
+      <c r="U7">
         <v>0.5</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V7">
         <v>70</v>
       </c>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2">
+      <c r="Y7">
         <v>0.05</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="Z7">
         <v>2.85</v>
       </c>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2" t="s">
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="s">
         <v>4</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AJ7" t="s">
         <v>132</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AK7" t="s">
         <v>157</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL7" t="s">
         <v>158</v>
       </c>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2" t="s">
+      <c r="AO7" t="s">
         <v>151</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AP7">
         <v>3</v>
       </c>
-      <c r="AQ7" s="2">
+      <c r="AQ7">
         <v>0</v>
       </c>
-      <c r="AR7" s="2"/>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2">
+      <c r="AX7">
         <v>0.25</v>
       </c>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-      <c r="BA7" s="2"/>
-      <c r="BB7" s="2"/>
-      <c r="BC7" s="2" t="s">
+      <c r="BC7" t="s">
         <v>136</v>
       </c>
-      <c r="BD7" s="2" t="s">
+      <c r="BD7" t="s">
         <v>137</v>
       </c>
-      <c r="BE7" s="2" t="s">
+      <c r="BE7" t="s">
         <v>138</v>
       </c>
-      <c r="BF7" s="2" t="s">
+      <c r="BF7" t="s">
         <v>139</v>
       </c>
-      <c r="BG7" s="2" t="s">
+      <c r="BG7" t="s">
         <v>140</v>
       </c>
-      <c r="BH7" s="2" t="s">
+      <c r="BH7" t="s">
         <v>141</v>
       </c>
-      <c r="BI7" s="2">
+      <c r="BI7">
         <v>6</v>
       </c>
-      <c r="BJ7" s="2" t="s">
+      <c r="BJ7" t="s">
         <v>142</v>
       </c>
-      <c r="BK7" s="2" t="s">
+      <c r="BK7" t="s">
         <v>143</v>
       </c>
-      <c r="BL7" s="2"/>
-      <c r="BM7" s="2"/>
-      <c r="BN7" s="2" t="s">
+      <c r="BN7" t="s">
         <v>159</v>
       </c>
-      <c r="BO7" s="2" t="s">
+      <c r="BO7" t="s">
         <v>159</v>
       </c>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2" t="s">
+      <c r="BQ7" t="s">
         <v>160</v>
       </c>
-      <c r="BR7" s="2" t="s">
+      <c r="BR7" t="s">
         <v>146</v>
       </c>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2">
+      <c r="BT7">
         <v>1</v>
       </c>
     </row>
@@ -3662,7 +3459,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3672,2435 +3468,2435 @@
   <dimension ref="A1:DI677"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="113" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
+    <col min="40" max="40" width="15" customWidth="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="51" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="86" max="86" width="9" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="93" max="98" width="9" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="101" max="101" width="9" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="104" max="109" width="9" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="111" max="113" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>161</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>163</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>164</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>165</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>166</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>167</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>168</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>169</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>170</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>171</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>172</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>173</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>174</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>175</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" t="s">
         <v>176</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" t="s">
         <v>177</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" t="s">
         <v>178</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" t="s">
         <v>178</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>179</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" t="s">
         <v>180</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" t="s">
         <v>181</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>182</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>183</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>185</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>186</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>187</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>188</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>189</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>190</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" t="s">
         <v>191</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" t="s">
         <v>192</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>193</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>194</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>195</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>196</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>197</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>198</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>199</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>200</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>201</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" t="s">
         <v>202</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>203</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>204</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>205</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>206</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>207</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>208</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>209</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>210</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>211</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>212</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" t="s">
         <v>213</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" t="s">
         <v>214</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>215</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>216</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>217</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" t="s">
         <v>217</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" t="s">
         <v>218</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BL1" t="s">
         <v>219</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BM1" t="s">
         <v>220</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BN1" t="s">
         <v>221</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BO1" t="s">
         <v>222</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BP1" t="s">
         <v>223</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BQ1" t="s">
         <v>224</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BR1" t="s">
         <v>225</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BS1" t="s">
         <v>226</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BT1" t="s">
         <v>227</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BU1" t="s">
         <v>228</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BV1" t="s">
         <v>229</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BW1" t="s">
         <v>230</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BX1" t="s">
         <v>231</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BY1" t="s">
         <v>232</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BZ1" t="s">
         <v>233</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CA1" t="s">
         <v>234</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CB1" t="s">
         <v>235</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CC1" t="s">
         <v>236</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CD1" t="s">
         <v>237</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CE1" t="s">
         <v>238</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CF1" t="s">
         <v>239</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CG1" t="s">
         <v>240</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CH1" t="s">
         <v>241</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CI1" t="s">
         <v>242</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CJ1" t="s">
         <v>243</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CK1" t="s">
         <v>244</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CL1" t="s">
         <v>245</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CM1" t="s">
         <v>246</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CN1" t="s">
         <v>247</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CO1" t="s">
         <v>248</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CP1" t="s">
         <v>249</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CQ1" t="s">
         <v>250</v>
       </c>
-      <c r="CR1" s="2" t="s">
+      <c r="CR1" t="s">
         <v>227</v>
       </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CS1" t="s">
         <v>251</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CT1" t="s">
         <v>252</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CU1" t="s">
         <v>253</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CV1" t="s">
         <v>254</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CW1" t="s">
         <v>255</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CX1" t="s">
         <v>256</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CY1" t="s">
         <v>257</v>
       </c>
-      <c r="CZ1" s="2" t="s">
+      <c r="CZ1" t="s">
         <v>256</v>
       </c>
-      <c r="DA1" s="2" t="s">
+      <c r="DA1" t="s">
         <v>258</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="DB1" t="s">
         <v>259</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="DC1" t="s">
         <v>260</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DD1" t="s">
         <v>261</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DE1" t="s">
         <v>262</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DF1" t="s">
         <v>263</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DG1" t="s">
         <v>264</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DH1" t="s">
         <v>265</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DI1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>267</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>268</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>269</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>270</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>271</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>272</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>273</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>274</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>275</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>276</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>277</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>278</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>279</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>280</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>281</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>282</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>283</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>284</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" t="s">
         <v>285</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>286</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>287</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>288</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" t="s">
         <v>289</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" t="s">
         <v>290</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>291</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" t="s">
         <v>292</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" t="s">
         <v>293</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" t="s">
         <v>294</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" t="s">
         <v>295</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AI2" t="s">
         <v>296</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" t="s">
         <v>297</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AK2" t="s">
         <v>298</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" t="s">
         <v>299</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" t="s">
         <v>300</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AN2" t="s">
         <v>301</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AO2" t="s">
         <v>302</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AP2" t="s">
         <v>303</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AQ2" t="s">
         <v>304</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AR2" t="s">
         <v>305</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AS2" t="s">
         <v>306</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AT2" t="s">
         <v>307</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AU2" t="s">
         <v>308</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AV2" t="s">
         <v>309</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AW2" t="s">
         <v>310</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AX2" t="s">
         <v>311</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AY2" t="s">
         <v>312</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AZ2" t="s">
         <v>313</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BA2" t="s">
         <v>314</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BB2" t="s">
         <v>315</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>316</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BD2" t="s">
         <v>317</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BE2" t="s">
         <v>318</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BF2" t="s">
         <v>319</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BG2" t="s">
         <v>320</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BH2" t="s">
         <v>321</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BI2" t="s">
         <v>322</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BJ2" t="s">
         <v>323</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BK2" t="s">
         <v>324</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BL2" t="s">
         <v>325</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BM2" t="s">
         <v>326</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BN2" t="s">
         <v>327</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BO2" t="s">
         <v>82</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BP2" t="s">
         <v>328</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>329</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BR2" t="s">
         <v>330</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BS2" t="s">
         <v>331</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BT2" t="s">
         <v>332</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BU2" t="s">
         <v>97</v>
       </c>
-      <c r="BV2" s="2" t="s">
+      <c r="BV2" t="s">
         <v>333</v>
       </c>
-      <c r="BW2" s="2" t="s">
+      <c r="BW2" t="s">
         <v>334</v>
       </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BX2" t="s">
         <v>335</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BY2" t="s">
         <v>336</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BZ2" t="s">
         <v>337</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="CA2" t="s">
         <v>338</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="CB2" t="s">
         <v>339</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CC2" t="s">
         <v>340</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CD2" t="s">
         <v>341</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CE2" t="s">
         <v>342</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CF2" t="s">
         <v>343</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CG2" t="s">
         <v>344</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CH2" t="s">
         <v>345</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CI2" t="s">
         <v>346</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CJ2" t="s">
         <v>347</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CK2" t="s">
         <v>348</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CL2" t="s">
         <v>349</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CM2" t="s">
         <v>350</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CN2" t="s">
         <v>351</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CO2" t="s">
         <v>352</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CP2" t="s">
         <v>353</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CQ2" t="s">
         <v>354</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CR2" t="s">
         <v>355</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CS2" t="s">
         <v>356</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CT2" t="s">
         <v>357</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CU2" t="s">
         <v>358</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CV2" t="s">
         <v>359</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CW2" t="s">
         <v>360</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CX2" t="s">
         <v>361</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CY2" t="s">
         <v>362</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CZ2" t="s">
         <v>363</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="DA2" t="s">
         <v>364</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="DB2" t="s">
         <v>365</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DC2" t="s">
         <v>366</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DD2" t="s">
         <v>367</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DE2" t="s">
         <v>368</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DF2" t="s">
         <v>369</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DG2" t="s">
         <v>370</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DH2" t="s">
         <v>371</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DI2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>118</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>373</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>374</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>375</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>120</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>120</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>123</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>123</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>123</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>123</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>118</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" t="s">
         <v>119</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" t="s">
         <v>119</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" t="s">
         <v>118</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" t="s">
         <v>118</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" t="s">
         <v>118</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" t="s">
         <v>119</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" t="s">
         <v>118</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" t="s">
         <v>120</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" t="s">
         <v>118</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AE3" t="s">
         <v>118</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AF3" t="s">
         <v>118</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" t="s">
         <v>376</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" t="s">
         <v>118</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AI3" t="s">
         <v>125</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ3" t="s">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AK3" t="s">
         <v>120</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" t="s">
         <v>120</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" t="s">
         <v>120</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AN3" t="s">
         <v>118</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" t="s">
         <v>377</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AP3" t="s">
         <v>378</v>
       </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" t="s">
         <v>2</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AS3" t="s">
         <v>2</v>
       </c>
-      <c r="AT3" s="2" t="s">
+      <c r="AT3" t="s">
         <v>379</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" t="s">
         <v>118</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AV3" t="s">
         <v>119</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AW3" t="s">
         <v>118</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" t="s">
         <v>380</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="AY3" t="s">
         <v>118</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="AZ3" t="s">
         <v>119</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" t="s">
         <v>118</v>
       </c>
-      <c r="BB3" s="2" t="s">
+      <c r="BB3" t="s">
         <v>120</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BC3" t="s">
         <v>119</v>
       </c>
-      <c r="BD3" s="2" t="s">
+      <c r="BD3" t="s">
         <v>120</v>
       </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BE3" t="s">
         <v>120</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BF3" t="s">
         <v>119</v>
       </c>
-      <c r="BG3" s="2" t="s">
+      <c r="BG3" t="s">
         <v>118</v>
       </c>
-      <c r="BH3" s="2" t="s">
+      <c r="BH3" t="s">
         <v>379</v>
       </c>
-      <c r="BI3" s="2" t="s">
+      <c r="BI3" t="s">
         <v>118</v>
       </c>
-      <c r="BJ3" s="2" t="s">
+      <c r="BJ3" t="s">
         <v>119</v>
       </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BK3" t="s">
         <v>119</v>
       </c>
-      <c r="BL3" s="2" t="s">
+      <c r="BL3" t="s">
         <v>119</v>
       </c>
-      <c r="BM3" s="2" t="s">
+      <c r="BM3" t="s">
         <v>120</v>
       </c>
-      <c r="BN3" s="2" t="s">
+      <c r="BN3" t="s">
         <v>120</v>
       </c>
-      <c r="BO3" s="2" t="s">
+      <c r="BO3" t="s">
         <v>121</v>
       </c>
-      <c r="BP3" s="2" t="s">
+      <c r="BP3" t="s">
         <v>121</v>
       </c>
-      <c r="BQ3" s="2" t="s">
+      <c r="BQ3" t="s">
         <v>381</v>
       </c>
-      <c r="BR3" s="2" t="s">
+      <c r="BR3" t="s">
         <v>382</v>
       </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BS3" t="s">
         <v>119</v>
       </c>
-      <c r="BT3" s="2" t="s">
+      <c r="BT3" t="s">
         <v>119</v>
       </c>
-      <c r="BU3" s="2" t="s">
+      <c r="BU3" t="s">
         <v>118</v>
       </c>
-      <c r="BV3" s="2" t="s">
+      <c r="BV3" t="s">
         <v>119</v>
       </c>
-      <c r="BW3" s="2" t="s">
+      <c r="BW3" t="s">
         <v>119</v>
       </c>
-      <c r="BX3" s="2" t="s">
+      <c r="BX3" t="s">
         <v>120</v>
       </c>
-      <c r="BY3" s="2" t="s">
+      <c r="BY3" t="s">
         <v>383</v>
       </c>
-      <c r="BZ3" s="2" t="s">
+      <c r="BZ3" t="s">
         <v>118</v>
       </c>
-      <c r="CA3" s="2" t="s">
+      <c r="CA3" t="s">
         <v>383</v>
       </c>
-      <c r="CB3" s="2" t="s">
+      <c r="CB3" t="s">
         <v>122</v>
       </c>
-      <c r="CC3" s="2" t="s">
+      <c r="CC3" t="s">
         <v>384</v>
       </c>
-      <c r="CD3" s="2" t="s">
+      <c r="CD3" t="s">
         <v>122</v>
       </c>
-      <c r="CE3" s="2" t="s">
+      <c r="CE3" t="s">
         <v>122</v>
       </c>
-      <c r="CF3" s="2" t="s">
+      <c r="CF3" t="s">
         <v>122</v>
       </c>
-      <c r="CG3" s="2" t="s">
+      <c r="CG3" t="s">
         <v>385</v>
       </c>
-      <c r="CH3" s="2" t="s">
+      <c r="CH3" t="s">
         <v>386</v>
       </c>
-      <c r="CI3" s="2" t="s">
+      <c r="CI3" t="s">
         <v>2</v>
       </c>
-      <c r="CJ3" s="2" t="s">
+      <c r="CJ3" t="s">
         <v>387</v>
       </c>
-      <c r="CK3" s="2" t="s">
+      <c r="CK3" t="s">
         <v>387</v>
       </c>
-      <c r="CL3" s="2" t="s">
+      <c r="CL3" t="s">
         <v>127</v>
       </c>
-      <c r="CM3" s="2" t="s">
+      <c r="CM3" t="s">
         <v>123</v>
       </c>
-      <c r="CN3" s="2" t="s">
+      <c r="CN3" t="s">
         <v>123</v>
       </c>
-      <c r="CO3" s="2" t="s">
+      <c r="CO3" t="s">
         <v>126</v>
       </c>
-      <c r="CP3" s="2" t="s">
+      <c r="CP3" t="s">
         <v>126</v>
       </c>
-      <c r="CQ3" s="2" t="s">
+      <c r="CQ3" t="s">
         <v>126</v>
       </c>
-      <c r="CR3" s="2" t="s">
+      <c r="CR3" t="s">
         <v>384</v>
       </c>
-      <c r="CS3" s="2" t="s">
+      <c r="CS3" t="s">
         <v>126</v>
       </c>
-      <c r="CT3" s="2" t="s">
+      <c r="CT3" t="s">
         <v>118</v>
       </c>
-      <c r="CU3" s="2" t="s">
+      <c r="CU3" t="s">
         <v>127</v>
       </c>
-      <c r="CV3" s="2" t="s">
+      <c r="CV3" t="s">
         <v>388</v>
       </c>
-      <c r="CW3" s="2" t="s">
+      <c r="CW3" t="s">
         <v>389</v>
       </c>
-      <c r="CX3" s="2" t="s">
+      <c r="CX3" t="s">
         <v>389</v>
       </c>
-      <c r="CY3" s="2" t="s">
+      <c r="CY3" t="s">
         <v>388</v>
       </c>
-      <c r="CZ3" s="2" t="s">
+      <c r="CZ3" t="s">
         <v>388</v>
       </c>
-      <c r="DA3" s="2" t="s">
+      <c r="DA3" t="s">
         <v>388</v>
       </c>
-      <c r="DB3" s="2" t="s">
+      <c r="DB3" t="s">
         <v>388</v>
       </c>
-      <c r="DC3" s="2" t="s">
+      <c r="DC3" t="s">
         <v>388</v>
       </c>
-      <c r="DD3" s="2" t="s">
+      <c r="DD3" t="s">
         <v>118</v>
       </c>
-      <c r="DE3" s="2" t="s">
+      <c r="DE3" t="s">
         <v>118</v>
       </c>
-      <c r="DF3" s="2" t="s">
+      <c r="DF3" t="s">
         <v>118</v>
       </c>
-      <c r="DG3" s="2" t="s">
+      <c r="DG3" t="s">
         <v>118</v>
       </c>
-      <c r="DH3" s="2" t="s">
+      <c r="DH3" t="s">
         <v>118</v>
       </c>
-      <c r="DI3" s="2" t="s">
+      <c r="DI3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>391</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>392</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" t="s">
         <v>393</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" t="s">
         <v>394</v>
       </c>
-      <c r="S6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="2" t="s">
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
         <v>395</v>
       </c>
-      <c r="AT6" s="2" t="s">
+      <c r="AT6" t="s">
         <v>396</v>
       </c>
-      <c r="AY6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ6" s="2">
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
         <v>0.01</v>
       </c>
-      <c r="BB6" s="2">
+      <c r="BB6">
         <v>2</v>
       </c>
-      <c r="BD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP6" s="2" t="s">
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="s">
         <v>397</v>
       </c>
-      <c r="CB6" s="2" t="s">
+      <c r="CB6" t="s">
         <v>58</v>
       </c>
-      <c r="CG6" s="2" t="s">
+      <c r="CG6" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>397</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>392</v>
       </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>399</v>
       </c>
-      <c r="AC7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="s">
         <v>395</v>
       </c>
-      <c r="AT7" s="2" t="s">
+      <c r="AT7" t="s">
         <v>396</v>
       </c>
-      <c r="AY7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ7" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP7" s="2" t="s">
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="s">
         <v>400</v>
       </c>
-      <c r="CH7" s="2" t="s">
+      <c r="CH7" t="s">
         <v>401</v>
       </c>
-      <c r="CI7" s="2" t="s">
+      <c r="CI7" t="s">
         <v>402</v>
       </c>
-      <c r="CN7" s="2" t="s">
+      <c r="CN7" t="s">
         <v>403</v>
       </c>
-      <c r="CO7" s="2">
+      <c r="CO7">
         <v>22</v>
       </c>
-      <c r="CR7" s="2">
+      <c r="CR7">
         <v>10</v>
       </c>
-      <c r="CY7" s="2" t="s">
+      <c r="CY7" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>406</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" t="s">
         <v>399</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" t="s">
         <v>407</v>
       </c>
-      <c r="AC8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="2" t="s">
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="s">
         <v>408</v>
       </c>
-      <c r="BD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU8" s="2" t="s">
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="s">
         <v>409</v>
       </c>
-      <c r="DD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG8" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="DD8">
+        <v>1</v>
+      </c>
+      <c r="DG8">
+        <v>1</v>
+      </c>
+      <c r="DH8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>410</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>392</v>
       </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
         <v>399</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" t="s">
         <v>407</v>
       </c>
-      <c r="AC9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="2" t="s">
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="s">
         <v>408</v>
       </c>
-      <c r="AT9" s="2" t="s">
+      <c r="AT9" t="s">
         <v>411</v>
       </c>
-      <c r="BD9" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO9" s="2" t="s">
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="s">
         <v>412</v>
       </c>
-      <c r="CN9" s="2" t="s">
+      <c r="CN9" t="s">
         <v>413</v>
       </c>
-      <c r="CO9" s="2">
+      <c r="CO9">
         <v>8</v>
       </c>
-      <c r="CR9" s="2">
+      <c r="CR9">
         <v>9999</v>
       </c>
-      <c r="DD9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="DD9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>412</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>392</v>
       </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT10" s="2" t="s">
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="s">
         <v>414</v>
       </c>
-      <c r="BD10" s="2">
+      <c r="BD10">
         <v>99</v>
       </c>
-      <c r="BS10" s="2">
+      <c r="BS10">
         <v>0.1</v>
       </c>
-      <c r="CN10" s="2" t="s">
+      <c r="CN10" t="s">
         <v>415</v>
       </c>
-      <c r="CO10" s="2">
+      <c r="CO10">
         <v>0.2</v>
       </c>
-      <c r="CR10" s="2">
+      <c r="CR10">
         <v>0.2</v>
       </c>
-      <c r="DD10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="DD10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>416</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>392</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" t="s">
         <v>399</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L11" t="s">
         <v>407</v>
       </c>
-      <c r="AC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="s">
         <v>408</v>
       </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN11" s="2" t="s">
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="CN11" t="s">
         <v>417</v>
       </c>
-      <c r="CR11" s="2">
+      <c r="CR11">
         <v>99999</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>418</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>392</v>
       </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ12" s="2" t="s">
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="s">
         <v>128</v>
       </c>
-      <c r="AV12" s="2">
+      <c r="AV12">
         <v>20</v>
       </c>
-      <c r="BD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS12" s="2">
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BS12">
         <v>0.1</v>
       </c>
-      <c r="CN12" s="2" t="s">
+      <c r="CN12" t="s">
         <v>419</v>
       </c>
-      <c r="CR12" s="2">
+      <c r="CR12">
         <v>0.2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>400</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>392</v>
       </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="s">
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
         <v>399</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="P13" t="s">
         <v>420</v>
       </c>
-      <c r="AC13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="2" t="s">
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="s">
         <v>408</v>
       </c>
-      <c r="AT13" s="2" t="s">
+      <c r="AT13" t="s">
         <v>411</v>
       </c>
-      <c r="BD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN13" s="2" t="s">
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="CN13" t="s">
         <v>403</v>
       </c>
-      <c r="CO13" s="2">
+      <c r="CO13">
         <v>22</v>
       </c>
-      <c r="CR13" s="2">
+      <c r="CR13">
         <v>10</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>421</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>392</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>422</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>423</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" t="s">
         <v>424</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17">
         <v>3</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" t="s">
         <v>425</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" t="s">
         <v>426</v>
       </c>
-      <c r="AC17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="2" t="s">
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="s">
         <v>408</v>
       </c>
-      <c r="BD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO17" s="2" t="s">
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BO17" t="s">
         <v>427</v>
       </c>
-      <c r="BP17" s="2" t="s">
+      <c r="BP17" t="s">
         <v>428</v>
       </c>
-      <c r="BT17" s="2">
+      <c r="BT17">
         <v>30</v>
       </c>
-      <c r="BV17" s="2">
+      <c r="BV17">
         <v>13</v>
       </c>
-      <c r="BW17" s="2">
+      <c r="BW17">
         <v>15</v>
       </c>
-      <c r="BX17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY17" s="2" t="s">
+      <c r="BX17">
+        <v>1</v>
+      </c>
+      <c r="BY17" t="s">
         <v>429</v>
       </c>
-      <c r="CN17" s="2" t="s">
+      <c r="CN17" t="s">
         <v>430</v>
       </c>
-      <c r="CR17" s="2">
+      <c r="CR17">
         <v>30</v>
       </c>
-      <c r="DD17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="DD17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>431</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>392</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="O18" t="s">
         <v>420</v>
       </c>
-      <c r="AC18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO18" s="2" t="s">
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="s">
         <v>395</v>
       </c>
-      <c r="AQ18" s="2" t="s">
+      <c r="AQ18" t="s">
         <v>147</v>
       </c>
-      <c r="AW18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP18" s="2" t="s">
+      <c r="AW18">
+        <v>1</v>
+      </c>
+      <c r="AY18">
+        <v>1</v>
+      </c>
+      <c r="AZ18">
+        <v>1</v>
+      </c>
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="s">
         <v>432</v>
       </c>
-      <c r="CB18" s="2" t="s">
+      <c r="CB18" t="s">
         <v>433</v>
       </c>
-      <c r="CG18" s="2" t="s">
+      <c r="CG18" t="s">
         <v>398</v>
       </c>
-      <c r="CH18" s="2" t="s">
+      <c r="CH18" t="s">
         <v>401</v>
       </c>
-      <c r="CI18" s="2" t="s">
+      <c r="CI18" t="s">
         <v>402</v>
       </c>
-      <c r="CN18" s="2" t="s">
+      <c r="CN18" t="s">
         <v>434</v>
       </c>
-      <c r="CO18" s="2">
+      <c r="CO18">
         <v>22</v>
       </c>
-      <c r="CP18" s="2">
+      <c r="CP18">
         <v>39.6</v>
       </c>
-      <c r="CR18" s="2">
+      <c r="CR18">
         <v>10</v>
       </c>
-      <c r="CY18" s="2" t="s">
+      <c r="CY18" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>435</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>392</v>
       </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="K19" s="2" t="s">
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
         <v>399</v>
       </c>
-      <c r="AC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ19" s="2" t="s">
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="s">
         <v>147</v>
       </c>
-      <c r="AO19" s="2" t="s">
+      <c r="AO19" t="s">
         <v>395</v>
       </c>
-      <c r="AT19" s="2" t="s">
+      <c r="AT19" t="s">
         <v>396</v>
       </c>
-      <c r="AX19" s="2" t="s">
+      <c r="AX19" t="s">
         <v>436</v>
       </c>
-      <c r="AZ19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB19" s="2">
+      <c r="AZ19">
+        <v>1</v>
+      </c>
+      <c r="BB19">
         <v>2</v>
       </c>
-      <c r="BD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="CH19" s="2" t="s">
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="CH19" t="s">
         <v>437</v>
       </c>
-      <c r="CI19" s="2" t="s">
+      <c r="CI19" t="s">
         <v>402</v>
       </c>
-      <c r="CN19" s="2" t="s">
+      <c r="CN19" t="s">
         <v>438</v>
       </c>
-      <c r="CR19" s="2">
+      <c r="CR19">
         <v>0.1</v>
       </c>
-      <c r="DD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="DD19">
+        <v>1</v>
+      </c>
+      <c r="DH19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>439</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>392</v>
       </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2" t="s">
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
         <v>399</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="O20" t="s">
         <v>420</v>
       </c>
-      <c r="AC20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="2" t="s">
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="s">
         <v>408</v>
       </c>
-      <c r="AW20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN20" s="2" t="s">
+      <c r="AW20">
+        <v>1</v>
+      </c>
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="CN20" t="s">
         <v>434</v>
       </c>
-      <c r="CO20" s="2">
+      <c r="CO20">
         <v>22</v>
       </c>
-      <c r="CP20" s="2">
+      <c r="CP20">
         <v>39.6</v>
       </c>
-      <c r="CR20" s="2">
+      <c r="CR20">
         <v>10</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>438</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>392</v>
       </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2" t="s">
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
         <v>420</v>
       </c>
-      <c r="AC21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ21" s="2" t="s">
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="s">
         <v>147</v>
       </c>
-      <c r="AT21" s="2" t="s">
+      <c r="AT21" t="s">
         <v>396</v>
       </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS21" s="2">
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="BS21">
         <v>0.1</v>
       </c>
-      <c r="CN21" s="2" t="s">
+      <c r="CN21" t="s">
         <v>438</v>
       </c>
-      <c r="CR21" s="2">
+      <c r="CR21">
         <v>0.2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>440</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>392</v>
       </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2" t="s">
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
         <v>399</v>
       </c>
-      <c r="AC22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="2" t="s">
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="s">
         <v>408</v>
       </c>
-      <c r="BD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN22" s="2" t="s">
+      <c r="BD22">
+        <v>1</v>
+      </c>
+      <c r="CN22" t="s">
         <v>440</v>
       </c>
-      <c r="CR22" s="2">
+      <c r="CR22">
         <v>40</v>
       </c>
-      <c r="DD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="DD22">
+        <v>1</v>
+      </c>
+      <c r="DH22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>441</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>392</v>
       </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="s">
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
         <v>420</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="P23" t="s">
         <v>440</v>
       </c>
-      <c r="AC23" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV23" s="2">
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AV23">
         <v>20</v>
       </c>
-      <c r="BD23" s="2">
+      <c r="BD23">
         <v>99</v>
       </c>
-      <c r="CM23" s="2" t="s">
+      <c r="CM23" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>443</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>392</v>
       </c>
-      <c r="I24" s="2">
-        <v>1</v>
-      </c>
-      <c r="K24" s="2" t="s">
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="s">
         <v>399</v>
       </c>
-      <c r="AC24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="2" t="s">
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="s">
         <v>408</v>
       </c>
-      <c r="BD24" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS24" s="2">
+      <c r="BD24">
+        <v>1</v>
+      </c>
+      <c r="BS24">
         <v>0.1</v>
       </c>
-      <c r="CB24" s="2" t="s">
+      <c r="CB24" t="s">
         <v>444</v>
       </c>
-      <c r="CG24" s="2" t="s">
+      <c r="CG24" t="s">
         <v>398</v>
       </c>
-      <c r="DD24" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG24" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH24" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
+      <c r="DD24">
+        <v>1</v>
+      </c>
+      <c r="DG24">
+        <v>1</v>
+      </c>
+      <c r="DH24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>445</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>392</v>
       </c>
-      <c r="I25" s="2">
-        <v>1</v>
-      </c>
-      <c r="K25" s="2" t="s">
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
         <v>399</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="L25" t="s">
         <v>446</v>
       </c>
-      <c r="AC25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="2" t="s">
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="s">
         <v>408</v>
       </c>
-      <c r="BD25" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS25" s="2">
+      <c r="BD25">
+        <v>1</v>
+      </c>
+      <c r="BS25">
         <v>0.2</v>
       </c>
-      <c r="CB25" s="2" t="s">
+      <c r="CB25" t="s">
         <v>447</v>
       </c>
-      <c r="CG25" s="2" t="s">
+      <c r="CG25" t="s">
         <v>398</v>
       </c>
-      <c r="DD25" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG25" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
+      <c r="DD25">
+        <v>1</v>
+      </c>
+      <c r="DG25">
+        <v>1</v>
+      </c>
+      <c r="DH25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>448</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>392</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>422</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>423</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" t="s">
         <v>424</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26">
         <v>3</v>
       </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2" t="s">
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="s">
         <v>438</v>
       </c>
-      <c r="AC26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="s">
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="s">
         <v>408</v>
       </c>
-      <c r="AO26" s="2" t="s">
+      <c r="AO26" t="s">
         <v>395</v>
       </c>
-      <c r="AT26" s="2" t="s">
+      <c r="AT26" t="s">
         <v>411</v>
       </c>
-      <c r="AY26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ26" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD26" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS26" s="2">
+      <c r="AY26">
+        <v>1</v>
+      </c>
+      <c r="AZ26">
+        <v>1</v>
+      </c>
+      <c r="BD26">
+        <v>1</v>
+      </c>
+      <c r="BS26">
         <v>0.1</v>
       </c>
-      <c r="CG26" s="2" t="s">
+      <c r="CG26" t="s">
         <v>398</v>
       </c>
-      <c r="CH26" s="2" t="s">
+      <c r="CH26" t="s">
         <v>401</v>
       </c>
-      <c r="CI26" s="2" t="s">
+      <c r="CI26" t="s">
         <v>402</v>
       </c>
-      <c r="CN26" s="2" t="s">
+      <c r="CN26" t="s">
         <v>434</v>
       </c>
-      <c r="CO26" s="2">
+      <c r="CO26">
         <v>22</v>
       </c>
-      <c r="CP26" s="2">
+      <c r="CP26">
         <v>39.6</v>
       </c>
-      <c r="CR26" s="2">
+      <c r="CR26">
         <v>10</v>
       </c>
-      <c r="CY26" s="2" t="s">
+      <c r="CY26" t="s">
         <v>404</v>
       </c>
-      <c r="DD26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
+      <c r="DD26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>449</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>392</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" t="s">
         <v>450</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>451</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" t="s">
         <v>452</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28">
         <v>3</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" t="s">
         <v>425</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" t="s">
         <v>426</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="O28" t="s">
         <v>419</v>
       </c>
-      <c r="AC28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="s">
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="s">
         <v>408</v>
       </c>
-      <c r="BD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO28" s="2" t="s">
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="BO28" t="s">
         <v>453</v>
       </c>
-      <c r="BP28" s="2" t="s">
+      <c r="BP28" t="s">
         <v>454</v>
       </c>
-      <c r="BT28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BV28" s="2">
+      <c r="BT28">
+        <v>1</v>
+      </c>
+      <c r="BV28">
         <v>11</v>
       </c>
-      <c r="BW28" s="2">
+      <c r="BW28">
         <v>15</v>
       </c>
-      <c r="BX28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY28" s="2" t="s">
+      <c r="BX28">
+        <v>1</v>
+      </c>
+      <c r="BY28" t="s">
         <v>429</v>
       </c>
-      <c r="CN28" s="2" t="s">
+      <c r="CN28" t="s">
         <v>455</v>
       </c>
-      <c r="CO28" s="2" t="s">
+      <c r="CO28" t="s">
         <v>456</v>
       </c>
-      <c r="CR28" s="2">
+      <c r="CR28">
         <v>25</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>453</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>392</v>
       </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="O29" s="2" t="s">
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="O29" t="s">
         <v>394</v>
       </c>
-      <c r="AC29" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="2" t="s">
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="s">
         <v>408</v>
       </c>
-      <c r="AT29" s="2" t="s">
+      <c r="AT29" t="s">
         <v>411</v>
       </c>
-      <c r="BD29" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS29" s="2">
+      <c r="BD29">
+        <v>1</v>
+      </c>
+      <c r="BS29">
         <v>0.1</v>
       </c>
-      <c r="CN29" s="2" t="s">
+      <c r="CN29" t="s">
         <v>457</v>
       </c>
-      <c r="CR29" s="2">
+      <c r="CR29">
         <v>0.2</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>458</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>459</v>
       </c>
-      <c r="I30" s="2">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="s">
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
         <v>460</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" t="s">
         <v>399</v>
       </c>
-      <c r="AC30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ30" s="2" t="s">
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="s">
         <v>147</v>
       </c>
-      <c r="AT30" s="2" t="s">
+      <c r="AT30" t="s">
         <v>396</v>
       </c>
-      <c r="BD30" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS30" s="2">
+      <c r="BD30">
+        <v>1</v>
+      </c>
+      <c r="BS30">
         <v>0.1</v>
       </c>
-      <c r="CU30" s="2" t="s">
+      <c r="CU30" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>462</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>392</v>
       </c>
-      <c r="I31" s="2">
-        <v>1</v>
-      </c>
-      <c r="K31" s="2" t="s">
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
         <v>399</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="L31" t="s">
         <v>446</v>
       </c>
-      <c r="AC31" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="2" t="s">
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="s">
         <v>408</v>
       </c>
-      <c r="BD31" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS31" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB31" s="2" t="s">
+      <c r="BD31">
+        <v>1</v>
+      </c>
+      <c r="BS31">
+        <v>1</v>
+      </c>
+      <c r="CB31" t="s">
         <v>463</v>
       </c>
-      <c r="CG31" s="2" t="s">
+      <c r="CG31" t="s">
         <v>398</v>
       </c>
-      <c r="DD31" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG31" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="s">
+      <c r="DD31">
+        <v>1</v>
+      </c>
+      <c r="DG31">
+        <v>1</v>
+      </c>
+      <c r="DH31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>464</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>392</v>
       </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="K32" s="2" t="s">
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
         <v>399</v>
       </c>
-      <c r="AC32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="2" t="s">
+      <c r="AC32">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="s">
         <v>408</v>
       </c>
-      <c r="BD32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS32" s="2">
-        <v>0.6667</v>
-      </c>
-      <c r="CB32" s="2" t="s">
+      <c r="BD32">
+        <v>1</v>
+      </c>
+      <c r="BS32">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="CB32" t="s">
         <v>465</v>
       </c>
-      <c r="CG32" s="2" t="s">
+      <c r="CG32" t="s">
         <v>398</v>
       </c>
-      <c r="DD32" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG32" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="s">
+      <c r="DD32">
+        <v>1</v>
+      </c>
+      <c r="DG32">
+        <v>1</v>
+      </c>
+      <c r="DH32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>158</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" t="s">
         <v>392</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" t="s">
         <v>450</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" t="s">
         <v>451</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" t="s">
         <v>452</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34">
         <v>3</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" t="s">
         <v>425</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K34" t="s">
         <v>393</v>
       </c>
-      <c r="AC34" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="2" t="s">
+      <c r="AC34">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="s">
         <v>408</v>
       </c>
-      <c r="BD34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO34" s="2" t="s">
+      <c r="BD34">
+        <v>1</v>
+      </c>
+      <c r="BO34" t="s">
         <v>466</v>
       </c>
-      <c r="BT34" s="2">
+      <c r="BT34">
         <v>25</v>
       </c>
-      <c r="BV34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BW34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BX34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY34" s="2" t="s">
+      <c r="BV34">
+        <v>1</v>
+      </c>
+      <c r="BW34">
+        <v>1</v>
+      </c>
+      <c r="BX34">
+        <v>1</v>
+      </c>
+      <c r="BY34" t="s">
         <v>429</v>
       </c>
-      <c r="CN34" s="2" t="s">
+      <c r="CN34" t="s">
         <v>467</v>
       </c>
-      <c r="CO34" s="2" t="s">
+      <c r="CO34" t="s">
         <v>468</v>
       </c>
-      <c r="CP34" s="2">
+      <c r="CP34">
         <v>80</v>
       </c>
-      <c r="CR34" s="2">
+      <c r="CR34">
         <v>25</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>469</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" t="s">
         <v>470</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="O35" t="s">
         <v>455</v>
       </c>
-      <c r="AC35" s="2">
+      <c r="AC35">
         <v>2</v>
       </c>
-      <c r="AO35" s="2" t="s">
+      <c r="AO35" t="s">
         <v>471</v>
       </c>
-      <c r="AT35" s="2" t="s">
+      <c r="AT35" t="s">
         <v>414</v>
       </c>
-      <c r="AX35" s="2" t="s">
+      <c r="AX35" t="s">
         <v>436</v>
       </c>
-      <c r="AZ35" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD35" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP35" s="2" t="s">
+      <c r="AZ35">
+        <v>1</v>
+      </c>
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="s">
         <v>472</v>
       </c>
-      <c r="CB35" s="2" t="s">
+      <c r="CB35" t="s">
         <v>473</v>
       </c>
-      <c r="CG35" s="2" t="s">
+      <c r="CG35" t="s">
         <v>398</v>
       </c>
-      <c r="CX35" s="2" t="s">
+      <c r="CX35" t="s">
         <v>474</v>
       </c>
-      <c r="CY35" s="2" t="s">
+      <c r="CY35" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>472</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" t="s">
         <v>392</v>
       </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="K36" s="2" t="s">
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
         <v>399</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="O36" t="s">
         <v>455</v>
       </c>
-      <c r="AC36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG36" s="2" t="s">
+      <c r="AC36">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="s">
         <v>408</v>
       </c>
-      <c r="AH36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO36" s="2" t="s">
+      <c r="AH36">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="s">
         <v>395</v>
       </c>
-      <c r="AV36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ36" s="2">
+      <c r="AV36">
+        <v>1</v>
+      </c>
+      <c r="AY36">
+        <v>1</v>
+      </c>
+      <c r="AZ36">
         <v>0.5</v>
       </c>
-      <c r="BD36" s="2">
-        <v>1</v>
-      </c>
-      <c r="CH36" s="2" t="s">
+      <c r="BD36">
+        <v>1</v>
+      </c>
+      <c r="CH36" t="s">
         <v>401</v>
       </c>
-      <c r="CI36" s="2" t="s">
+      <c r="CI36" t="s">
         <v>402</v>
       </c>
-      <c r="CN36" s="2" t="s">
+      <c r="CN36" t="s">
         <v>403</v>
       </c>
-      <c r="CO36" s="2">
+      <c r="CO36">
         <v>22</v>
       </c>
-      <c r="CR36" s="2">
+      <c r="CR36">
         <v>10</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>476</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" t="s">
         <v>477</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="K37" t="s">
         <v>399</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="L37" t="s">
         <v>407</v>
       </c>
-      <c r="AC37" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG37" s="2" t="s">
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="s">
         <v>408</v>
       </c>
-      <c r="BD37" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU37" s="2" t="s">
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>479</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" t="s">
         <v>392</v>
       </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="K38" s="2" t="s">
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="K38" t="s">
         <v>399</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="L38" t="s">
         <v>407</v>
       </c>
-      <c r="AC38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="2" t="s">
+      <c r="AC38">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="s">
         <v>408</v>
       </c>
-      <c r="BD38" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN38" s="2" t="s">
+      <c r="BD38">
+        <v>1</v>
+      </c>
+      <c r="CN38" t="s">
         <v>457</v>
       </c>
-      <c r="CR38" s="2">
+      <c r="CR38">
         <v>0.5</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>480</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>392</v>
       </c>
-      <c r="I39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ39" s="2" t="s">
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="AC39">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="s">
         <v>128</v>
       </c>
-      <c r="AV39" s="2">
+      <c r="AV39">
         <v>20</v>
       </c>
-      <c r="BD39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS39" s="2">
+      <c r="BD39">
+        <v>1</v>
+      </c>
+      <c r="BS39">
         <v>0.1</v>
       </c>
-      <c r="CN39" s="2" t="s">
+      <c r="CN39" t="s">
         <v>394</v>
       </c>
-      <c r="CR39" s="2">
+      <c r="CR39">
         <v>0.5</v>
       </c>
     </row>
-    <row r="657">
-      <c r="CL657" s="2">
+    <row r="657" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL657">
         <v>0.15</v>
       </c>
     </row>
-    <row r="659">
-      <c r="CL659" s="2">
+    <row r="659" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL659">
         <v>0.2</v>
       </c>
     </row>
-    <row r="660">
-      <c r="CL660" s="2">
+    <row r="660" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL660">
         <v>0.1</v>
       </c>
     </row>
-    <row r="662">
-      <c r="CL662" s="2">
+    <row r="662" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL662">
         <v>0.2</v>
       </c>
     </row>
-    <row r="669">
-      <c r="CL669" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="CL671" s="2">
+    <row r="669" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL669">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL671">
         <v>0.4</v>
       </c>
     </row>
-    <row r="672">
-      <c r="CL672" s="2">
+    <row r="672" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL672">
         <v>0.6</v>
       </c>
     </row>
-    <row r="675">
-      <c r="CL675" s="2">
+    <row r="675" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL675">
         <v>0.5</v>
       </c>
     </row>
-    <row r="676">
-      <c r="CL676" s="2">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="CL677" s="2">
+    <row r="676" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL676">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="677" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL677">
         <v>0.2</v>
       </c>
     </row>
@@ -6108,7 +5904,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6118,441 +5913,441 @@
   <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="19.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="3" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="19.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>481</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>482</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>483</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>484</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>485</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>486</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>487</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>488</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>489</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>490</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>492</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>493</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>494</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>495</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>496</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>497</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>498</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>499</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>500</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>501</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>502</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>118</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>388</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>352</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>118</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>118</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>352</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>118</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>403</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>503</v>
       </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>504</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>413</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>506</v>
       </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>507</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>403</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>503</v>
       </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>504</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>413</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>506</v>
       </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
         <v>507</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>415</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>503</v>
       </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="s">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>510</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>511</v>
       </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="2" t="s">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>513</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>511</v>
       </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="s">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>420</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>515</v>
       </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>442</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>503</v>
       </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="2" t="s">
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>440</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>515</v>
       </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>438</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>515</v>
       </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>516</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>238</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="Q15" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>455</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>503</v>
       </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="2" t="s">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>519</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>506</v>
       </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="s">
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
         <v>507</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="Q17" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>520</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>515</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>522</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>515</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>524</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>515</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>526</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>515</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>394</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>515</v>
       </c>
-      <c r="H22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>529</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>238</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="Q23" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>419</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>515</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24">
         <v>1</v>
       </c>
     </row>
@@ -6560,7 +6355,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6569,45 +6363,45 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>532</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>352</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6615,7 +6409,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6624,79 +6417,79 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="I1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>533</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>534</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>535</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>536</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>347</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>387</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6704,7 +6497,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6713,219 +6505,219 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>537</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>538</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>539</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>540</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>541</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>542</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>543</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>544</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>545</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>547</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>548</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>549</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>550</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>551</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>552</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>553</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>554</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>555</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>534</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>556</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>120</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>521</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>557</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>558</v>
       </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>523</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>557</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>559</v>
       </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>525</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>560</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>561</v>
       </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>527</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>560</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>562</v>
       </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>474</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>563</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8">
         <v>2</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8">
         <v>60</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8">
         <v>1</v>
       </c>
     </row>
@@ -6933,7 +6725,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6943,49 +6734,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>268</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>564</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>565</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>566</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>296</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>567</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1">
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7020,7 +6811,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7029,108 +6819,107 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1"/>
+    <col min="6" max="6" width="39.5" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1"/>
+    <col min="8" max="8" width="32.25" customWidth="1"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>569</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>570</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>571</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>572</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>573</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>574</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>575</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>577</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>578</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>579</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>580</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>581</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>582</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>583</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234D0D8F-8355-47B5-9889-56B9DE93132D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DAE28D-2942-49A0-9FF2-C4902FA9ABA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -47,6 +47,30 @@
   </authors>
   <commentList>
     <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{0379C7A9-D991-4A21-88DD-9E4A331E1726}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>PC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:干员 1:敌人 2:仅技能条 3:技能+血条</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0" xr:uid="{FC749843-DFBF-4D09-8A08-9668C8A0548B}">
       <text>
         <r>
           <rPr>
@@ -299,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="592">
   <si>
     <t>Id</t>
   </si>
@@ -388,9 +412,6 @@
     <t>可选技能</t>
   </si>
   <si>
-    <t>血条类型</t>
-  </si>
-  <si>
     <t>高度</t>
   </si>
   <si>
@@ -701,9 +722,6 @@
   </si>
   <si>
     <t>干员m3攻击,获取重构体</t>
-  </si>
-  <si>
-    <t>m32,m33</t>
   </si>
   <si>
     <t>高台位</t>
@@ -2058,13 +2076,44 @@
   <si>
     <t>干员M3</t>
     <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>血条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技力条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpBarType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>m32,m33</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2099,6 +2148,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2125,7 +2181,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2133,6 +2189,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2467,7 +2529,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2478,7 +2540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BT7"/>
+  <dimension ref="A1:BU7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2510,28 +2572,28 @@
     <col min="35" max="35" width="15.83203125" customWidth="1"/>
     <col min="36" max="36" width="13.83203125" customWidth="1"/>
     <col min="37" max="37" width="34.5" customWidth="1"/>
-    <col min="38" max="39" width="9.83203125" customWidth="1"/>
-    <col min="40" max="43" width="9" customWidth="1"/>
-    <col min="44" max="44" width="12.5" customWidth="1"/>
-    <col min="45" max="50" width="9" customWidth="1"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="9" customWidth="1"/>
-    <col min="53" max="53" width="17.75" customWidth="1"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1"/>
-    <col min="55" max="56" width="9" customWidth="1"/>
-    <col min="57" max="57" width="24.25" customWidth="1"/>
-    <col min="58" max="58" width="13.25" customWidth="1"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1"/>
-    <col min="60" max="60" width="8" customWidth="1"/>
-    <col min="61" max="64" width="9" customWidth="1"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1"/>
-    <col min="66" max="66" width="14" customWidth="1"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1"/>
-    <col min="68" max="71" width="14" customWidth="1"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1"/>
+    <col min="38" max="40" width="9.83203125" customWidth="1"/>
+    <col min="41" max="44" width="9" customWidth="1"/>
+    <col min="45" max="45" width="12.5" customWidth="1"/>
+    <col min="46" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="24.33203125" customWidth="1"/>
+    <col min="53" max="53" width="9" customWidth="1"/>
+    <col min="54" max="54" width="17.75" customWidth="1"/>
+    <col min="55" max="55" width="7.83203125" customWidth="1"/>
+    <col min="56" max="57" width="9" customWidth="1"/>
+    <col min="58" max="58" width="24.25" customWidth="1"/>
+    <col min="59" max="59" width="13.25" customWidth="1"/>
+    <col min="60" max="60" width="16.08203125" customWidth="1"/>
+    <col min="61" max="61" width="8" customWidth="1"/>
+    <col min="62" max="65" width="9" customWidth="1"/>
+    <col min="66" max="66" width="39.58203125" customWidth="1"/>
+    <col min="67" max="67" width="14" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" customWidth="1"/>
+    <col min="69" max="72" width="14" customWidth="1"/>
+    <col min="73" max="73" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2607,280 +2669,286 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="AN1" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="AO1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AU1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BF1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>47</v>
       </c>
-      <c r="BI1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>51</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>52</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>53</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>54</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>55</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>58</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>59</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>60</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>62</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>63</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>64</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>65</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>66</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>67</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>68</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>72</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>73</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>74</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>75</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>76</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>78</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>79</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>80</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>81</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>82</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="AO2" t="s">
         <v>84</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AP2" t="s">
         <v>85</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AQ2" t="s">
         <v>86</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AR2" t="s">
         <v>87</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AS2" t="s">
         <v>88</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AT2" t="s">
         <v>89</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>90</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>91</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>92</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>93</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>94</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>95</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>98</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>99</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>100</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>101</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>102</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>103</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>104</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>105</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>106</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>107</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>108</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>109</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BO2" t="s">
         <v>110</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BP2" t="s">
         <v>111</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BQ2" t="s">
         <v>112</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BR2" t="s">
         <v>113</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>114</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>115</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BU2" t="s">
         <v>116</v>
       </c>
-      <c r="BT2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2888,94 +2956,94 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" t="s">
         <v>119</v>
       </c>
-      <c r="V3" t="s">
-        <v>120</v>
-      </c>
       <c r="W3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" t="s">
         <v>119</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AB3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" t="s">
         <v>119</v>
       </c>
-      <c r="Z3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>120</v>
-      </c>
       <c r="AD3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AE3" t="s">
         <v>2</v>
       </c>
       <c r="AF3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AH3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AI3" t="s">
         <v>2</v>
@@ -2984,22 +3052,22 @@
         <v>2</v>
       </c>
       <c r="AK3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP3" t="s">
         <v>121</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>120</v>
       </c>
       <c r="AQ3" t="s">
         <v>119</v>
@@ -3007,38 +3075,38 @@
       <c r="AR3" t="s">
         <v>118</v>
       </c>
-      <c r="AT3" t="s">
-        <v>119</v>
+      <c r="AS3" t="s">
+        <v>117</v>
       </c>
       <c r="AU3" t="s">
         <v>118</v>
       </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AW3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ3" t="s">
         <v>123</v>
       </c>
-      <c r="AX3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AY3" t="s">
+      <c r="BA3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD3" t="s">
         <v>124</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>2</v>
       </c>
       <c r="BE3" t="s">
         <v>2</v>
@@ -3050,60 +3118,63 @@
         <v>2</v>
       </c>
       <c r="BH3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN3" t="s">
         <v>126</v>
       </c>
-      <c r="BI3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>127</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>122</v>
-      </c>
       <c r="BO3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BP3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BQ3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BR3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BS3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BT3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" t="s">
         <v>129</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" t="s">
         <v>130</v>
-      </c>
-      <c r="E5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" t="s">
-        <v>131</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3148,84 +3219,90 @@
         <v>4</v>
       </c>
       <c r="AJ5" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK5" t="s">
         <v>132</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
+        <v>591</v>
+      </c>
+      <c r="AM5" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="AN5" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="AP5" t="s">
         <v>133</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>0.5</v>
+      </c>
+      <c r="AY5">
+        <v>0.25</v>
+      </c>
+      <c r="BD5" t="s">
         <v>134</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="BE5" t="s">
         <v>135</v>
       </c>
-      <c r="AP5">
-        <v>1</v>
-      </c>
-      <c r="AQ5">
-        <v>0.5</v>
-      </c>
-      <c r="AX5">
-        <v>0.25</v>
-      </c>
-      <c r="BC5" t="s">
+      <c r="BF5" t="s">
         <v>136</v>
       </c>
-      <c r="BD5" t="s">
+      <c r="BG5" t="s">
         <v>137</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BH5" t="s">
         <v>138</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BI5" t="s">
         <v>139</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BJ5">
+        <v>6</v>
+      </c>
+      <c r="BK5" t="s">
         <v>140</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BL5" t="s">
         <v>141</v>
       </c>
-      <c r="BI5">
-        <v>6</v>
-      </c>
-      <c r="BJ5" t="s">
+      <c r="BO5" t="s">
         <v>142</v>
       </c>
-      <c r="BK5" t="s">
+      <c r="BP5" t="s">
         <v>143</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BR5" t="s">
         <v>144</v>
       </c>
-      <c r="BO5" t="s">
+      <c r="BS5" t="s">
+        <v>144</v>
+      </c>
+      <c r="BU5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>145</v>
       </c>
-      <c r="BQ5" t="s">
+      <c r="B6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" t="s">
         <v>146</v>
       </c>
-      <c r="BR5" t="s">
+      <c r="E6" t="s">
         <v>146</v>
       </c>
-      <c r="BT5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="F6" t="s">
         <v>147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" t="s">
-        <v>149</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3270,81 +3347,84 @@
         <v>-1</v>
       </c>
       <c r="AI6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AJ6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK6" t="s">
-        <v>150</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>151</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
+        <v>148</v>
+      </c>
+      <c r="AM6" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="AN6" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>149</v>
       </c>
       <c r="AQ6">
         <v>0</v>
       </c>
-      <c r="AW6" t="s">
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY6">
+        <v>0.25</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>151</v>
+      </c>
+      <c r="BG6" t="s">
         <v>152</v>
       </c>
-      <c r="AX6">
-        <v>0.25</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BE6" t="s">
+      <c r="BH6" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ6">
+        <v>6</v>
+      </c>
+      <c r="BK6" t="s">
         <v>153</v>
       </c>
-      <c r="BF6" t="s">
+      <c r="BL6" t="s">
+        <v>145</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>142</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>143</v>
+      </c>
+      <c r="BU6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>154</v>
       </c>
-      <c r="BG6" t="s">
-        <v>148</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BI6">
-        <v>6</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>147</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>144</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>145</v>
-      </c>
-      <c r="BT6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>156</v>
-      </c>
       <c r="B7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" t="s">
         <v>129</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" t="s">
         <v>130</v>
-      </c>
-      <c r="E7" t="s">
-        <v>130</v>
-      </c>
-      <c r="F7" t="s">
-        <v>131</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3392,66 +3472,72 @@
         <v>4</v>
       </c>
       <c r="AJ7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK7" t="s">
+        <v>155</v>
+      </c>
+      <c r="AL7" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM7" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AQ7">
+        <v>3</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0.25</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>136</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>138</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ7">
+        <v>6</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>140</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>141</v>
+      </c>
+      <c r="BO7" t="s">
         <v>157</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="BP7" t="s">
+        <v>157</v>
+      </c>
+      <c r="BR7" t="s">
         <v>158</v>
       </c>
-      <c r="AO7" t="s">
-        <v>151</v>
-      </c>
-      <c r="AP7">
-        <v>3</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0.25</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>136</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>137</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>138</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>139</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>140</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>141</v>
-      </c>
-      <c r="BI7">
-        <v>6</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>142</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>143</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>159</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>159</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>160</v>
-      </c>
-      <c r="BR7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BT7">
+      <c r="BS7" t="s">
+        <v>144</v>
+      </c>
+      <c r="BU7">
         <v>1</v>
       </c>
     </row>
@@ -3554,334 +3640,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E1" t="s">
         <v>161</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>162</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>163</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>164</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>165</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>166</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>167</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>168</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>169</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>170</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>171</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>172</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>173</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>174</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>175</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>176</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
+        <v>176</v>
+      </c>
+      <c r="V1" t="s">
         <v>177</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>178</v>
       </c>
-      <c r="U1" t="s">
-        <v>178</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>179</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>180</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>181</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>182</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>183</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>185</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>186</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>187</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>188</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>189</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>190</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>191</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>192</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>193</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>194</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>195</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>196</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>197</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>198</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>199</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>200</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>201</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>202</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>203</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>204</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>205</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>206</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>207</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>208</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>209</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>210</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>211</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>212</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>213</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>214</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>215</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BJ1" t="s">
+        <v>215</v>
+      </c>
+      <c r="BK1" t="s">
         <v>216</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BL1" t="s">
         <v>217</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>217</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>218</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>219</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>220</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>221</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>222</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>223</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>224</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>225</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>226</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BV1" t="s">
         <v>227</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BW1" t="s">
         <v>228</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BX1" t="s">
         <v>229</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BY1" t="s">
         <v>230</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BZ1" t="s">
         <v>231</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CA1" t="s">
         <v>232</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>233</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CC1" t="s">
         <v>234</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>235</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>236</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>237</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>238</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>239</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>240</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>241</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>242</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" t="s">
         <v>243</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>244</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CN1" t="s">
         <v>245</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>246</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>247</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>248</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
+        <v>225</v>
+      </c>
+      <c r="CS1" t="s">
         <v>249</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CT1" t="s">
         <v>250</v>
       </c>
-      <c r="CR1" t="s">
-        <v>227</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>251</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>252</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>253</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CX1" t="s">
         <v>254</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CY1" t="s">
         <v>255</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CZ1" t="s">
+        <v>254</v>
+      </c>
+      <c r="DA1" t="s">
         <v>256</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DB1" t="s">
         <v>257</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>256</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>258</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>259</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>260</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>261</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>262</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>263</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>264</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>265</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -3889,337 +3975,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
         <v>267</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>268</v>
       </c>
-      <c r="G2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>269</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>270</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>271</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>272</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>273</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>274</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>275</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>276</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>277</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>278</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>279</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>280</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>281</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>282</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>283</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>284</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>285</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>286</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>287</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>288</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>289</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>290</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>291</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>292</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>293</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>294</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>295</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>296</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>297</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" t="s">
         <v>298</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AN2" t="s">
         <v>299</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AO2" t="s">
         <v>300</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AP2" t="s">
         <v>301</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AQ2" t="s">
         <v>302</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AR2" t="s">
         <v>303</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AS2" t="s">
         <v>304</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AT2" t="s">
         <v>305</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>306</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>307</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>308</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>309</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>310</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>311</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>312</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>313</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>314</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>315</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>316</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>317</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>318</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>319</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>320</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>321</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>322</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>323</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>324</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>325</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BO2" t="s">
+        <v>81</v>
+      </c>
+      <c r="BP2" t="s">
         <v>326</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BQ2" t="s">
         <v>327</v>
       </c>
-      <c r="BO2" t="s">
-        <v>82</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BR2" t="s">
         <v>328</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>329</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>330</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BU2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV2" t="s">
         <v>331</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BW2" t="s">
         <v>332</v>
       </c>
-      <c r="BU2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BX2" t="s">
         <v>333</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BY2" t="s">
         <v>334</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BZ2" t="s">
         <v>335</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="CA2" t="s">
         <v>336</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CB2" t="s">
         <v>337</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CC2" t="s">
         <v>338</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CD2" t="s">
         <v>339</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CE2" t="s">
         <v>340</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CF2" t="s">
         <v>341</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CG2" t="s">
         <v>342</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CH2" t="s">
         <v>343</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CI2" t="s">
         <v>344</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CJ2" t="s">
         <v>345</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>346</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CL2" t="s">
         <v>347</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>348</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CN2" t="s">
         <v>349</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>350</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>351</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>352</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>353</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>354</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>355</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>356</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>357</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>358</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>359</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>360</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>361</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>362</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>363</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>364</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>365</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>366</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>367</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>368</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>369</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>370</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>371</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -4239,112 +4325,112 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" t="s">
+        <v>371</v>
+      </c>
+      <c r="K3" t="s">
+        <v>372</v>
+      </c>
+      <c r="L3" t="s">
+        <v>373</v>
+      </c>
+      <c r="M3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" t="s">
+        <v>122</v>
+      </c>
+      <c r="P3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>122</v>
+      </c>
+      <c r="R3" t="s">
+        <v>122</v>
+      </c>
+      <c r="S3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T3" t="s">
         <v>118</v>
       </c>
-      <c r="J3" t="s">
-        <v>373</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="U3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" t="s">
+        <v>118</v>
+      </c>
+      <c r="W3" t="s">
+        <v>117</v>
+      </c>
+      <c r="X3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG3" t="s">
         <v>374</v>
       </c>
-      <c r="L3" t="s">
-        <v>375</v>
-      </c>
-      <c r="M3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" t="s">
-        <v>123</v>
-      </c>
-      <c r="P3" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>123</v>
-      </c>
-      <c r="R3" t="s">
-        <v>123</v>
-      </c>
-      <c r="S3" t="s">
-        <v>118</v>
-      </c>
-      <c r="T3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" t="s">
-        <v>119</v>
-      </c>
-      <c r="V3" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" t="s">
-        <v>118</v>
-      </c>
-      <c r="X3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>376</v>
-      </c>
       <c r="AH3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AI3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AL3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AM3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AN3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AO3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AP3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
@@ -4356,239 +4442,239 @@
         <v>2</v>
       </c>
       <c r="AT3" t="s">
+        <v>377</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>378</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>377</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BQ3" t="s">
         <v>379</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="BR3" t="s">
+        <v>380</v>
+      </c>
+      <c r="BS3" t="s">
         <v>118</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="BT3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX3" t="s">
         <v>119</v>
       </c>
-      <c r="AW3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>380</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>379</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BO3" t="s">
+      <c r="BY3" t="s">
+        <v>381</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CB3" t="s">
         <v>121</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="CC3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CD3" t="s">
         <v>121</v>
       </c>
-      <c r="BQ3" t="s">
-        <v>381</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>382</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BY3" t="s">
+      <c r="CE3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG3" t="s">
         <v>383</v>
       </c>
-      <c r="BZ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>383</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CC3" t="s">
+      <c r="CH3" t="s">
         <v>384</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>385</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>386</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
+        <v>385</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>385</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CV3" t="s">
+        <v>386</v>
+      </c>
+      <c r="CW3" t="s">
         <v>387</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CX3" t="s">
         <v>387</v>
       </c>
-      <c r="CL3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>384</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>118</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>388</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>389</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>389</v>
-      </c>
       <c r="CY3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="CZ3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="DA3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="DB3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="DC3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="DD3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DE3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DF3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DG3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DH3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DI3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C6" t="s">
+        <v>390</v>
+      </c>
+      <c r="K6" t="s">
         <v>391</v>
       </c>
-      <c r="C6" t="s">
+      <c r="P6" t="s">
         <v>392</v>
       </c>
-      <c r="K6" t="s">
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
         <v>393</v>
       </c>
-      <c r="P6" t="s">
+      <c r="AT6" t="s">
         <v>394</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>395</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>396</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -4603,57 +4689,57 @@
         <v>1</v>
       </c>
       <c r="BP6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="CB6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CG6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C7" t="s">
+        <v>390</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>397</v>
       </c>
-      <c r="C7" t="s">
-        <v>392</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>393</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>394</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>398</v>
+      </c>
+      <c r="CH7" t="s">
         <v>399</v>
       </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>395</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>396</v>
-      </c>
-      <c r="AY7">
-        <v>1</v>
-      </c>
-      <c r="AZ7">
-        <v>1</v>
-      </c>
-      <c r="BD7">
-        <v>1</v>
-      </c>
-      <c r="BP7" t="s">
+      <c r="CI7" t="s">
         <v>400</v>
       </c>
-      <c r="CH7" t="s">
+      <c r="CN7" t="s">
         <v>401</v>
-      </c>
-      <c r="CI7" t="s">
-        <v>402</v>
-      </c>
-      <c r="CN7" t="s">
-        <v>403</v>
       </c>
       <c r="CO7">
         <v>22</v>
@@ -4662,36 +4748,36 @@
         <v>10</v>
       </c>
       <c r="CY7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" t="s">
+        <v>404</v>
+      </c>
+      <c r="K8" t="s">
+        <v>397</v>
+      </c>
+      <c r="L8" t="s">
         <v>405</v>
       </c>
-      <c r="C8" t="s">
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="s">
         <v>406</v>
       </c>
-      <c r="K8" t="s">
-        <v>399</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="s">
         <v>407</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AF8">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>408</v>
-      </c>
-      <c r="BD8">
-        <v>1</v>
-      </c>
-      <c r="CU8" t="s">
-        <v>409</v>
       </c>
       <c r="DD8">
         <v>1</v>
@@ -4705,37 +4791,37 @@
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>408</v>
+      </c>
+      <c r="C9" t="s">
+        <v>390</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>397</v>
+      </c>
+      <c r="L9" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>409</v>
+      </c>
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="s">
         <v>410</v>
       </c>
-      <c r="C9" t="s">
-        <v>392</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>399</v>
-      </c>
-      <c r="L9" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>408</v>
-      </c>
-      <c r="AT9" t="s">
+      <c r="CN9" t="s">
         <v>411</v>
-      </c>
-      <c r="BD9">
-        <v>1</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>412</v>
-      </c>
-      <c r="CN9" t="s">
-        <v>413</v>
       </c>
       <c r="CO9">
         <v>8</v>
@@ -4749,19 +4835,19 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>410</v>
+      </c>
+      <c r="C10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="s">
         <v>412</v>
-      </c>
-      <c r="C10" t="s">
-        <v>392</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>414</v>
       </c>
       <c r="BD10">
         <v>99</v>
@@ -4770,7 +4856,7 @@
         <v>0.1</v>
       </c>
       <c r="CN10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="CO10">
         <v>0.2</v>
@@ -4784,28 +4870,28 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L11" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD11">
         <v>1</v>
       </c>
       <c r="CN11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="CR11">
         <v>99999</v>
@@ -4813,10 +4899,10 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -4825,7 +4911,7 @@
         <v>1</v>
       </c>
       <c r="AJ12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AV12">
         <v>20</v>
@@ -4837,7 +4923,7 @@
         <v>0.1</v>
       </c>
       <c r="CN12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="CR12">
         <v>0.2</v>
@@ -4845,34 +4931,34 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="P13" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AC13">
         <v>1</v>
       </c>
       <c r="AG13" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AT13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="BD13">
         <v>1</v>
       </c>
       <c r="CN13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="CO13">
         <v>22</v>
@@ -4883,43 +4969,43 @@
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>419</v>
+      </c>
+      <c r="C17" t="s">
+        <v>390</v>
+      </c>
+      <c r="D17" t="s">
+        <v>420</v>
+      </c>
+      <c r="E17" t="s">
         <v>421</v>
       </c>
-      <c r="C17" t="s">
-        <v>392</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>422</v>
-      </c>
-      <c r="E17" t="s">
-        <v>423</v>
-      </c>
-      <c r="F17" t="s">
-        <v>424</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="J17" t="s">
+        <v>423</v>
+      </c>
+      <c r="K17" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>406</v>
+      </c>
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BO17" t="s">
         <v>425</v>
       </c>
-      <c r="K17" t="s">
+      <c r="BP17" t="s">
         <v>426</v>
-      </c>
-      <c r="AC17">
-        <v>1</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>408</v>
-      </c>
-      <c r="BD17">
-        <v>1</v>
-      </c>
-      <c r="BO17" t="s">
-        <v>427</v>
-      </c>
-      <c r="BP17" t="s">
-        <v>428</v>
       </c>
       <c r="BT17">
         <v>30</v>
@@ -4934,10 +5020,10 @@
         <v>1</v>
       </c>
       <c r="BY17" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="CN17" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="CR17">
         <v>30</v>
@@ -4948,55 +5034,55 @@
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>429</v>
+      </c>
+      <c r="C18" t="s">
+        <v>390</v>
+      </c>
+      <c r="O18" t="s">
+        <v>418</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>393</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>145</v>
+      </c>
+      <c r="AW18">
+        <v>1</v>
+      </c>
+      <c r="AY18">
+        <v>1</v>
+      </c>
+      <c r="AZ18">
+        <v>1</v>
+      </c>
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="s">
+        <v>430</v>
+      </c>
+      <c r="CB18" t="s">
         <v>431</v>
       </c>
-      <c r="C18" t="s">
-        <v>392</v>
-      </c>
-      <c r="O18" t="s">
-        <v>420</v>
-      </c>
-      <c r="AC18">
-        <v>1</v>
-      </c>
-      <c r="AD18">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="s">
-        <v>395</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>147</v>
-      </c>
-      <c r="AW18">
-        <v>1</v>
-      </c>
-      <c r="AY18">
-        <v>1</v>
-      </c>
-      <c r="AZ18">
-        <v>1</v>
-      </c>
-      <c r="BD18">
-        <v>1</v>
-      </c>
-      <c r="BP18" t="s">
+      <c r="CG18" t="s">
+        <v>396</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>399</v>
+      </c>
+      <c r="CI18" t="s">
+        <v>400</v>
+      </c>
+      <c r="CN18" t="s">
         <v>432</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>433</v>
-      </c>
-      <c r="CG18" t="s">
-        <v>398</v>
-      </c>
-      <c r="CH18" t="s">
-        <v>401</v>
-      </c>
-      <c r="CI18" t="s">
-        <v>402</v>
-      </c>
-      <c r="CN18" t="s">
-        <v>434</v>
       </c>
       <c r="CO18">
         <v>22</v>
@@ -5008,21 +5094,21 @@
         <v>10</v>
       </c>
       <c r="CY18" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C19" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AC19">
         <v>1</v>
@@ -5031,16 +5117,16 @@
         <v>1</v>
       </c>
       <c r="AJ19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AO19" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AT19" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AX19" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AZ19">
         <v>1</v>
@@ -5052,13 +5138,13 @@
         <v>1</v>
       </c>
       <c r="CH19" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="CI19" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="CN19" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="CR19">
         <v>0.1</v>
@@ -5072,25 +5158,25 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="O20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AC20">
         <v>1</v>
       </c>
       <c r="AG20" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AW20">
         <v>1</v>
@@ -5099,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="CN20" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="CO20">
         <v>22</v>
@@ -5113,25 +5199,25 @@
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AC21">
         <v>1</v>
       </c>
       <c r="AJ21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AT21" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="BD21">
         <v>1</v>
@@ -5140,7 +5226,7 @@
         <v>0.1</v>
       </c>
       <c r="CN21" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="CR21">
         <v>0.2</v>
@@ -5148,28 +5234,28 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C22" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AC22">
         <v>1</v>
       </c>
       <c r="AG22" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD22">
         <v>1</v>
       </c>
       <c r="CN22" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="CR22">
         <v>40</v>
@@ -5183,19 +5269,19 @@
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C23" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P23" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AC23">
         <v>1</v>
@@ -5207,27 +5293,27 @@
         <v>99</v>
       </c>
       <c r="CM23" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C24" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AC24">
         <v>1</v>
       </c>
       <c r="AG24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD24">
         <v>1</v>
@@ -5236,10 +5322,10 @@
         <v>0.1</v>
       </c>
       <c r="CB24" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="CG24" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="DD24">
         <v>1</v>
@@ -5253,25 +5339,25 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C25" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AC25">
         <v>1</v>
       </c>
       <c r="AG25" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD25">
         <v>1</v>
@@ -5280,10 +5366,10 @@
         <v>0.2</v>
       </c>
       <c r="CB25" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="CG25" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="DD25">
         <v>1</v>
@@ -5297,19 +5383,19 @@
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C26" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D26" t="s">
+        <v>420</v>
+      </c>
+      <c r="E26" t="s">
+        <v>421</v>
+      </c>
+      <c r="F26" t="s">
         <v>422</v>
-      </c>
-      <c r="E26" t="s">
-        <v>423</v>
-      </c>
-      <c r="F26" t="s">
-        <v>424</v>
       </c>
       <c r="G26">
         <v>3</v>
@@ -5318,19 +5404,19 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AC26">
         <v>1</v>
       </c>
       <c r="AG26" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AO26" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AT26" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AY26">
         <v>1</v>
@@ -5345,16 +5431,16 @@
         <v>0.1</v>
       </c>
       <c r="CG26" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="CH26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="CI26" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="CN26" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="CO26">
         <v>22</v>
@@ -5366,7 +5452,7 @@
         <v>10</v>
       </c>
       <c r="CY26" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="DD26">
         <v>1</v>
@@ -5374,46 +5460,46 @@
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>447</v>
+      </c>
+      <c r="C28" t="s">
+        <v>390</v>
+      </c>
+      <c r="D28" t="s">
+        <v>448</v>
+      </c>
+      <c r="E28" t="s">
         <v>449</v>
       </c>
-      <c r="C28" t="s">
-        <v>392</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>450</v>
-      </c>
-      <c r="E28" t="s">
-        <v>451</v>
-      </c>
-      <c r="F28" t="s">
-        <v>452</v>
       </c>
       <c r="G28">
         <v>3</v>
       </c>
       <c r="J28" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K28" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="O28" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AC28">
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD28">
         <v>1</v>
       </c>
       <c r="BO28" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="BP28" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="BT28">
         <v>1</v>
@@ -5428,13 +5514,13 @@
         <v>1</v>
       </c>
       <c r="BY28" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="CN28" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="CO28" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="CR28">
         <v>25</v>
@@ -5442,25 +5528,25 @@
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C29" t="s">
+        <v>390</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="O29" t="s">
         <v>392</v>
       </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="O29" t="s">
-        <v>394</v>
-      </c>
       <c r="AC29">
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AT29" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="BD29">
         <v>1</v>
@@ -5469,7 +5555,7 @@
         <v>0.1</v>
       </c>
       <c r="CN29" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="CR29">
         <v>0.2</v>
@@ -5477,28 +5563,28 @@
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>456</v>
+      </c>
+      <c r="C30" t="s">
+        <v>457</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
         <v>458</v>
       </c>
-      <c r="C30" t="s">
-        <v>459</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>460</v>
-      </c>
       <c r="K30" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AC30">
         <v>1</v>
       </c>
       <c r="AJ30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AT30" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="BD30">
         <v>1</v>
@@ -5507,30 +5593,30 @@
         <v>0.1</v>
       </c>
       <c r="CU30" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I31">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L31" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AC31">
         <v>1</v>
       </c>
       <c r="AG31" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD31">
         <v>1</v>
@@ -5539,10 +5625,10 @@
         <v>1</v>
       </c>
       <c r="CB31" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="CG31" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="DD31">
         <v>1</v>
@@ -5556,22 +5642,22 @@
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C32" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AC32">
         <v>1</v>
       </c>
       <c r="AG32" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD32">
         <v>1</v>
@@ -5580,10 +5666,10 @@
         <v>0.66669999999999996</v>
       </c>
       <c r="CB32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="CG32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="DD32">
         <v>1</v>
@@ -5597,40 +5683,40 @@
     </row>
     <row r="34" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D34" t="s">
+        <v>448</v>
+      </c>
+      <c r="E34" t="s">
+        <v>449</v>
+      </c>
+      <c r="F34" t="s">
         <v>450</v>
-      </c>
-      <c r="E34" t="s">
-        <v>451</v>
-      </c>
-      <c r="F34" t="s">
-        <v>452</v>
       </c>
       <c r="G34">
         <v>3</v>
       </c>
       <c r="J34" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K34" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AC34">
         <v>1</v>
       </c>
       <c r="AG34" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD34">
         <v>1</v>
       </c>
       <c r="BO34" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="BT34">
         <v>25</v>
@@ -5645,13 +5731,13 @@
         <v>1</v>
       </c>
       <c r="BY34" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="CN34" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="CO34" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="CP34">
         <v>80</v>
@@ -5662,75 +5748,75 @@
     </row>
     <row r="35" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C35" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="O35" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AC35">
         <v>2</v>
       </c>
       <c r="AO35" t="s">
+        <v>469</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>412</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>434</v>
+      </c>
+      <c r="AZ35">
+        <v>1</v>
+      </c>
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="s">
+        <v>470</v>
+      </c>
+      <c r="CB35" t="s">
         <v>471</v>
       </c>
-      <c r="AT35" t="s">
-        <v>414</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>436</v>
-      </c>
-      <c r="AZ35">
-        <v>1</v>
-      </c>
-      <c r="BD35">
-        <v>1</v>
-      </c>
-      <c r="BP35" t="s">
+      <c r="CG35" t="s">
+        <v>396</v>
+      </c>
+      <c r="CX35" t="s">
         <v>472</v>
       </c>
-      <c r="CB35" t="s">
+      <c r="CY35" t="s">
         <v>473</v>
-      </c>
-      <c r="CG35" t="s">
-        <v>398</v>
-      </c>
-      <c r="CX35" t="s">
-        <v>474</v>
-      </c>
-      <c r="CY35" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="36" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I36">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="O36" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AC36">
         <v>1</v>
       </c>
       <c r="AG36" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AH36">
         <v>1</v>
       </c>
       <c r="AO36" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AV36">
         <v>1</v>
@@ -5745,13 +5831,13 @@
         <v>1</v>
       </c>
       <c r="CH36" t="s">
+        <v>399</v>
+      </c>
+      <c r="CI36" t="s">
+        <v>400</v>
+      </c>
+      <c r="CN36" t="s">
         <v>401</v>
-      </c>
-      <c r="CI36" t="s">
-        <v>402</v>
-      </c>
-      <c r="CN36" t="s">
-        <v>403</v>
       </c>
       <c r="CO36">
         <v>22</v>
@@ -5762,57 +5848,57 @@
     </row>
     <row r="37" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>474</v>
+      </c>
+      <c r="C37" t="s">
+        <v>475</v>
+      </c>
+      <c r="K37" t="s">
+        <v>397</v>
+      </c>
+      <c r="L37" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>406</v>
+      </c>
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="s">
         <v>476</v>
-      </c>
-      <c r="C37" t="s">
-        <v>477</v>
-      </c>
-      <c r="K37" t="s">
-        <v>399</v>
-      </c>
-      <c r="L37" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC37">
-        <v>1</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>408</v>
-      </c>
-      <c r="BD37">
-        <v>1</v>
-      </c>
-      <c r="CU37" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="38" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C38" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L38" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AC38">
         <v>1</v>
       </c>
       <c r="AG38" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BD38">
         <v>1</v>
       </c>
       <c r="CN38" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="CR38">
         <v>0.5</v>
@@ -5820,10 +5906,10 @@
     </row>
     <row r="39" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C39" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -5832,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="AJ39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AV39">
         <v>20</v>
@@ -5844,7 +5930,7 @@
         <v>0.1</v>
       </c>
       <c r="CN39" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="CR39">
         <v>0.5</v>
@@ -5933,37 +6019,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>479</v>
+      </c>
+      <c r="F1" t="s">
+        <v>480</v>
+      </c>
+      <c r="G1" t="s">
         <v>481</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>482</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>483</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>484</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>485</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>486</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>487</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>488</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>489</v>
-      </c>
-      <c r="O1" t="s">
-        <v>490</v>
-      </c>
-      <c r="P1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -5971,49 +6057,49 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F2" t="s">
+        <v>491</v>
+      </c>
+      <c r="G2" t="s">
         <v>492</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>493</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>494</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>495</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>496</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" t="s">
         <v>497</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>498</v>
       </c>
-      <c r="L2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>499</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>500</v>
       </c>
-      <c r="O2" t="s">
-        <v>501</v>
-      </c>
-      <c r="P2" t="s">
-        <v>502</v>
-      </c>
       <c r="Q2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -6027,150 +6113,150 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" t="s">
+        <v>386</v>
+      </c>
+      <c r="K3" t="s">
         <v>118</v>
       </c>
-      <c r="I3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" t="s">
-        <v>388</v>
-      </c>
-      <c r="K3" t="s">
-        <v>119</v>
-      </c>
       <c r="L3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C4" t="s">
+        <v>501</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q4" t="s">
         <v>503</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C5" t="s">
+        <v>504</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q5" t="s">
         <v>506</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C6" t="s">
+        <v>501</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q6" t="s">
         <v>503</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C7" t="s">
+        <v>504</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q7" t="s">
         <v>506</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" t="s">
+        <v>509</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
         <v>510</v>
-      </c>
-      <c r="C9" t="s">
-        <v>511</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C10" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -6179,15 +6265,15 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -6195,24 +6281,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C12" t="s">
+        <v>501</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="s">
         <v>503</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C13" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -6220,10 +6306,10 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C14" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -6231,121 +6317,121 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C15" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Q15" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C16" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C17" t="s">
+        <v>504</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q17" t="s">
         <v>506</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="J17" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C18" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C19" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J19" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C20" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J20" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C21" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J21" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C22" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C23" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Q23" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C24" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -6374,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6382,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6399,10 +6485,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -6426,7 +6512,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -6434,31 +6520,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G2" t="s">
         <v>533</v>
       </c>
-      <c r="E2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>534</v>
       </c>
-      <c r="G2" t="s">
-        <v>535</v>
-      </c>
-      <c r="H2" t="s">
-        <v>536</v>
-      </c>
       <c r="I2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6475,22 +6561,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" t="s">
         <v>119</v>
       </c>
-      <c r="F3" t="s">
-        <v>120</v>
-      </c>
       <c r="G3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -6518,34 +6604,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D1" t="s">
         <v>537</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>538</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>539</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>540</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>541</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>542</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>543</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>544</v>
-      </c>
-      <c r="K1" t="s">
-        <v>545</v>
-      </c>
-      <c r="L1" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -6553,37 +6639,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D2" t="s">
         <v>547</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>548</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>549</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>550</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>551</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>552</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>553</v>
       </c>
-      <c r="I2" t="s">
-        <v>554</v>
-      </c>
-      <c r="J2" t="s">
-        <v>555</v>
-      </c>
       <c r="K2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="L2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -6594,45 +6680,45 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" t="s">
         <v>118</v>
       </c>
-      <c r="G3" t="s">
+      <c r="L3" t="s">
         <v>118</v>
-      </c>
-      <c r="H3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -6646,13 +6732,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B5" t="s">
+        <v>555</v>
+      </c>
+      <c r="E5" t="s">
         <v>557</v>
-      </c>
-      <c r="E5" t="s">
-        <v>559</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -6666,13 +6752,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E6" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -6686,13 +6772,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B7" t="s">
+        <v>558</v>
+      </c>
+      <c r="E7" t="s">
         <v>560</v>
-      </c>
-      <c r="E7" t="s">
-        <v>562</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -6706,10 +6792,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B8" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -6749,31 +6835,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
         <v>564</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I2" t="s">
         <v>565</v>
       </c>
-      <c r="F2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" t="s">
-        <v>566</v>
-      </c>
-      <c r="H2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I2" t="s">
-        <v>567</v>
-      </c>
       <c r="J2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6790,22 +6876,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -6835,28 +6921,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D1" t="s">
         <v>569</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>570</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>571</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>572</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>573</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>574</v>
-      </c>
-      <c r="H1" t="s">
-        <v>575</v>
-      </c>
-      <c r="I1" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6864,28 +6950,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D2" t="s">
         <v>577</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>578</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>579</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>580</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>581</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>582</v>
-      </c>
-      <c r="H2" t="s">
-        <v>583</v>
-      </c>
-      <c r="I2" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6893,10 +6979,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
         <v>2</v>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="594">
   <si>
     <t>Id</t>
   </si>
@@ -673,6 +673,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -689,6 +692,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -2146,11 +2152,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -2464,30 +2473,30 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2500,7 +2509,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV7"/>
+  <dimension ref="A1:BX7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2570,13 +2579,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2748,6 +2759,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2968,6 +2981,12 @@
       <c r="BV2" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2977,7 +2996,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2985,91 +3004,91 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="AD3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>2</v>
@@ -3078,10 +3097,10 @@
         <v>2</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AN3" s="2" t="s">
         <v>2</v>
@@ -3090,50 +3109,50 @@
         <v>2</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AQ3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AS3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="BA3" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BF3" s="2" t="s">
         <v>2</v>
@@ -3148,43 +3167,49 @@
         <v>2</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BP3" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BQ3" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BS3" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4">
@@ -3262,23 +3287,25 @@
       <c r="BT4" s="2"/>
       <c r="BU4" s="2"/>
       <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -3339,23 +3366,23 @@
         <v>4</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AR5" s="2">
         <v>1</v>
@@ -3377,68 +3404,70 @@
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BG5" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BH5" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BI5" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BK5" s="2">
         <v>6</v>
       </c>
       <c r="BL5" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BM5" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BN5" s="2"/>
       <c r="BO5" s="2"/>
-      <c r="BP5" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="BP5" s="2"/>
       <c r="BQ5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="BR5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BS5" s="2"/>
       <c r="BT5" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BU5" s="2"/>
-      <c r="BV5" s="2">
+        <v>155</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BV5" s="2"/>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -3498,24 +3527,24 @@
       </c>
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AR6" s="2">
         <v>0</v>
@@ -3529,7 +3558,7 @@
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
       <c r="AY6" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AZ6" s="2">
         <v>0.25</v>
@@ -3539,62 +3568,64 @@
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
       <c r="BE6" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BF6" s="2"/>
       <c r="BG6" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BH6" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BI6" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BJ6" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BK6" s="2">
         <v>6</v>
       </c>
       <c r="BL6" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BM6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BN6" s="2"/>
       <c r="BO6" s="2"/>
-      <c r="BP6" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="BP6" s="2"/>
       <c r="BQ6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BR6" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="BS6" s="2"/>
       <c r="BT6" s="2"/>
       <c r="BU6" s="2"/>
-      <c r="BV6" s="2">
+      <c r="BV6" s="2"/>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -3657,23 +3688,23 @@
         <v>4</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AR7" s="2">
         <v>3</v>
@@ -3695,49 +3726,51 @@
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BG7" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BH7" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BI7" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BJ7" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BK7" s="2">
         <v>6</v>
       </c>
       <c r="BL7" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BM7" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BN7" s="2"/>
       <c r="BO7" s="2"/>
-      <c r="BP7" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="BP7" s="2"/>
       <c r="BQ7" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR7" s="2"/>
-      <c r="BS7" s="2" t="s">
-        <v>168</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="BR7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS7" s="2"/>
       <c r="BT7" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BU7" s="2"/>
-      <c r="BV7" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BV7" s="2"/>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3755,2435 +3788,2435 @@
   <dimension ref="A1:DI677"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="113" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="3"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="3"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
+    <col min="40" max="40" width="15" customWidth="1" style="3"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="3"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="3"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9" customWidth="1" style="3"/>
+    <col min="52" max="52" width="7" customWidth="1" style="3"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="3"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
+    <col min="72" max="73" width="8" customWidth="1" style="3"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
+    <col min="86" max="86" width="9" customWidth="1" style="3"/>
+    <col min="87" max="87" width="16" customWidth="1" style="3"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
+    <col min="93" max="98" width="9" customWidth="1" style="3"/>
+    <col min="99" max="99" width="14" customWidth="1" style="3"/>
+    <col min="100" max="100" width="8" customWidth="1" style="3"/>
+    <col min="101" max="101" width="9" customWidth="1" style="3"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
+    <col min="104" max="109" width="9" customWidth="1" style="3"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
+    <col min="111" max="113" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="U1" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="BK1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="CS1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="DA1" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>274</v>
       </c>
+      <c r="DH1" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AI2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AP2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AX2" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="AY2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BA2" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BB2" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BC2" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BE2" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BH2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BI2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BK2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BL2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BM2" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BP2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BR2" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BS2" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="BU2" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BV2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BW2" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BX2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="BY2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="BZ2" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CA2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CB2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CC2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CD2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CE2" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CF2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CG2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CH2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CI2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CJ2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CK2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CL2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CM2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CO2" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CP2" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CQ2" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CR2" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CS2" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CT2" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CU2" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CV2" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CW2" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CX2" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="CY2" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="CZ2" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DA2" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DB2" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DC2" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DD2" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DE2" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DF2" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DG2" s="3" t="s">
         <v>380</v>
       </c>
+      <c r="DH2" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="DI2" s="3" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="U3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AW3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="BA3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BO3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="BP3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="BQ3" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="BT3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="BZ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA3" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="CB3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CC3" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CD3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CE3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CF3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="CM3" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="CN3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CR3" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CS3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CT3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CU3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="CW3" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="CX3" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="CY3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="CZ3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="DA3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="DB3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="DD3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="DE3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="DF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="DG3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="DH3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="DI3" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="S6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AT6" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AY6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="BB6" s="3">
+        <v>2</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP6" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="CB6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="CG6" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AT7" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP7" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="CH7" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="CI7" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN7" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="CO7" s="3">
+        <v>22</v>
+      </c>
+      <c r="CR7" s="3">
+        <v>10</v>
+      </c>
+      <c r="CY7" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU8" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="DD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG8" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AT9" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="BD9" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO9" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="CN9" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="CO9" s="3">
+        <v>8</v>
+      </c>
+      <c r="CR9" s="3">
+        <v>9999</v>
+      </c>
+      <c r="DD9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="BD10" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN10" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="CO10" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="CR10" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="DD10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN11" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="CR11" s="3">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV12" s="3">
+        <v>20</v>
+      </c>
+      <c r="BD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN12" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="CR12" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AT13" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="BD13" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN13" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="CO13" s="3">
+        <v>22</v>
+      </c>
+      <c r="CR13" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G17" s="3">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="J17" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD17" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO17" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BP17" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="BT17" s="3">
+        <v>30</v>
+      </c>
+      <c r="BV17" s="3">
+        <v>13</v>
+      </c>
+      <c r="BW17" s="3">
+        <v>15</v>
+      </c>
+      <c r="BX17" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY17" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="CN17" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="CR17" s="3">
+        <v>30</v>
+      </c>
+      <c r="DD17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AQ18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AW18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP18" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="CB18" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="CG18" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="CH18" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="CI18" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN18" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="CO18" s="3">
+        <v>22</v>
+      </c>
+      <c r="CP18" s="3">
+        <v>39.6</v>
+      </c>
+      <c r="CR18" s="3">
+        <v>10</v>
+      </c>
+      <c r="CY18" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AO19" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AT19" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AX19" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="AZ19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BB19" s="3">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="BD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="CH19" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="CI19" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN19" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="CR19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="DD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AW20" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD20" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN20" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="CO20" s="3">
+        <v>22</v>
+      </c>
+      <c r="CP20" s="3">
+        <v>39.6</v>
+      </c>
+      <c r="CR20" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ21" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AT21" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="BD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS21" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN21" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="CR21" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD22" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN22" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="CR22" s="3">
+        <v>40</v>
+      </c>
+      <c r="DD22" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AV23" s="3">
+        <v>20</v>
+      </c>
+      <c r="BD23" s="3">
+        <v>99</v>
+      </c>
+      <c r="CM23" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD24" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS24" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CB24" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="CG24" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="DD24" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG24" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD25" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS25" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="CB25" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="CG25" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="DD25" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG25" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AO26" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AT26" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="AY26" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ26" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD26" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS26" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CG26" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="CH26" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="CI26" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN26" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="CO26" s="3">
+        <v>22</v>
+      </c>
+      <c r="CP26" s="3">
+        <v>39.6</v>
+      </c>
+      <c r="CR26" s="3">
+        <v>10</v>
+      </c>
+      <c r="CY26" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="DD26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G28" s="3">
+        <v>3</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD28" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO28" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="BP28" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="BT28" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV28" s="3">
+        <v>11</v>
+      </c>
+      <c r="BW28" s="3">
+        <v>15</v>
+      </c>
+      <c r="BX28" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY28" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="CN28" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="CO28" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="CR28" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AT29" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="BD29" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS29" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN29" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="CR29" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AT30" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="BD30" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS30" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CU30" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I31" s="3">
+        <v>1</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD31" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS31" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB31" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG31" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="DD31" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG31" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD32" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS32" s="3">
+        <v>0.6667</v>
+      </c>
+      <c r="CB32" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="CG32" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="DD32" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG32" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G34" s="3">
+        <v>3</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD34" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO34" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="BT34" s="3">
+        <v>25</v>
+      </c>
+      <c r="BV34" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW34" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX34" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY34" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="CN34" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="CO34" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="CP34" s="3">
+        <v>80</v>
+      </c>
+      <c r="CR34" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="AC35" s="3">
         <v>2</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="P6" s="2" t="s">
+      <c r="AO35" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="AT35" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="AX35" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="AZ35" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD35" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP35" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="CB35" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="CG35" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="CX35" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="CY35" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="S6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AT6" s="2" t="s">
+      <c r="I36" s="3">
+        <v>1</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="AC36" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AH36" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO36" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV36" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY36" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ36" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="BD36" s="3">
+        <v>1</v>
+      </c>
+      <c r="CH36" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="CI36" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN36" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="CO36" s="3">
+        <v>22</v>
+      </c>
+      <c r="CR36" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC37" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG37" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD37" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU37" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC38" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BD38" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN38" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="CR38" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I39" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV39" s="3">
+        <v>20</v>
+      </c>
+      <c r="BD39" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS39" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN39" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="AY6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ6" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="BB6" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP6" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="CB6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="CG6" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AT7" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AY7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ7" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP7" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="CH7" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="CI7" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN7" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CO7" s="2">
-        <v>22</v>
-      </c>
-      <c r="CR7" s="2">
-        <v>10</v>
-      </c>
-      <c r="CY7" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU8" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="DD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG8" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AT9" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="BD9" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO9" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="CN9" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="CO9" s="2">
-        <v>8</v>
-      </c>
-      <c r="CR9" s="2">
-        <v>9999</v>
-      </c>
-      <c r="DD9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT10" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="BD10" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS10" s="2">
+      <c r="CR39" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="CL657" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="CL659" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="CL660" s="3">
         <v>0.1</v>
       </c>
-      <c r="CN10" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="CO10" s="2">
+    </row>
+    <row r="662">
+      <c r="CL662" s="3">
         <v>0.2</v>
       </c>
-      <c r="CR10" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="DD10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN11" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="CR11" s="2">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="AV12" s="2">
-        <v>20</v>
-      </c>
-      <c r="BD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS12" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN12" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="CR12" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="AC13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AT13" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="BD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN13" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CO13" s="2">
-        <v>22</v>
-      </c>
-      <c r="CR13" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="G17" s="2">
-        <v>3</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="AC17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BP17" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="BT17" s="2">
-        <v>30</v>
-      </c>
-      <c r="BV17" s="2">
-        <v>13</v>
-      </c>
-      <c r="BW17" s="2">
-        <v>15</v>
-      </c>
-      <c r="BX17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY17" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="CN17" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="CR17" s="2">
-        <v>30</v>
-      </c>
-      <c r="DD17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO18" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AQ18" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AW18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP18" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="CB18" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="CG18" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="CH18" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="CI18" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN18" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="CO18" s="2">
-        <v>22</v>
-      </c>
-      <c r="CP18" s="2">
-        <v>39.6</v>
-      </c>
-      <c r="CR18" s="2">
-        <v>10</v>
-      </c>
-      <c r="CY18" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AO19" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AT19" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AX19" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AZ19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB19" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="CH19" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="CI19" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN19" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="CR19" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="DD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="AC20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AW20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN20" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="CO20" s="2">
-        <v>22</v>
-      </c>
-      <c r="CP20" s="2">
-        <v>39.6</v>
-      </c>
-      <c r="CR20" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="AC21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ21" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AT21" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS21" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="CR21" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN22" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="CR22" s="2">
-        <v>40</v>
-      </c>
-      <c r="DD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="AC23" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV23" s="2">
-        <v>20</v>
-      </c>
-      <c r="BD23" s="2">
-        <v>99</v>
-      </c>
-      <c r="CM23" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD24" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS24" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CB24" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="CG24" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="DD24" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG24" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH24" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I25" s="2">
-        <v>1</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="AC25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD25" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS25" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="CB25" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="CG25" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="DD25" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG25" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="G26" s="2">
-        <v>3</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="AC26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AO26" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AT26" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="AY26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ26" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD26" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS26" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CG26" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="CH26" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="CI26" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN26" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="CO26" s="2">
-        <v>22</v>
-      </c>
-      <c r="CP26" s="2">
-        <v>39.6</v>
-      </c>
-      <c r="CR26" s="2">
-        <v>10</v>
-      </c>
-      <c r="CY26" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="DD26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="G28" s="2">
-        <v>3</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="AC28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO28" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="BP28" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="BT28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BV28" s="2">
-        <v>11</v>
-      </c>
-      <c r="BW28" s="2">
-        <v>15</v>
-      </c>
-      <c r="BX28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY28" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="CN28" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="CO28" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="CR28" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="AC29" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AT29" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="BD29" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS29" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN29" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="CR29" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="I30" s="2">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ30" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AT30" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="BD30" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS30" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CU30" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I31" s="2">
-        <v>1</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="AC31" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD31" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS31" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB31" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="CG31" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="DD31" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG31" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS32" s="2">
-        <v>0.6667</v>
-      </c>
-      <c r="CB32" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="CG32" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="DD32" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG32" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="G34" s="2">
-        <v>3</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="AC34" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO34" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="BT34" s="2">
-        <v>25</v>
-      </c>
-      <c r="BV34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BW34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BX34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY34" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="CN34" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="CO34" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="CP34" s="2">
-        <v>80</v>
-      </c>
-      <c r="CR34" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="AC35" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO35" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="AT35" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="AX35" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AZ35" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD35" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP35" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="CB35" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="CG35" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="CX35" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="CY35" s="2" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="AC36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG36" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AH36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO36" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AV36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ36" s="2">
+    </row>
+    <row r="669">
+      <c r="CL669" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="CL671" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="CL672" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="CL675" s="3">
         <v>0.5</v>
       </c>
-      <c r="BD36" s="2">
-        <v>1</v>
-      </c>
-      <c r="CH36" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="CI36" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN36" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CO36" s="2">
-        <v>22</v>
-      </c>
-      <c r="CR36" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC37" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG37" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD37" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU37" s="2" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BD38" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN38" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="CR38" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="AV39" s="2">
-        <v>20</v>
-      </c>
-      <c r="BD39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS39" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN39" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="CR39" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="657">
-      <c r="CL657" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="659">
-      <c r="CL659" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="660">
-      <c r="CL660" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="662">
-      <c r="CL662" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="CL669" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="CL671" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="CL672" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="CL675" s="2">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="676">
-      <c r="CL676" s="2">
+      <c r="CL676" s="3">
         <v>0.667</v>
       </c>
     </row>
     <row r="677">
-      <c r="CL677" s="2">
+      <c r="CL677" s="3">
         <v>0.2</v>
       </c>
     </row>
@@ -6201,441 +6234,441 @@
   <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="19.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1" style="3"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
+    <col min="3" max="6" width="9" customWidth="1" style="3"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="9" max="13" width="9" customWidth="1" style="3"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
+    <col min="16" max="16" width="19.1640625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>499</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>501</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>366</v>
+      <c r="O2" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>133</v>
+      <c r="L3" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q4" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>513</v>
       </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="Q6" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="Q5" s="2" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q6" s="2" t="s">
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="Q7" s="2" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="s">
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="Q17" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q15" s="2" t="s">
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>529</v>
+      <c r="J18" s="3" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>531</v>
+      <c r="A19" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>533</v>
+      <c r="A20" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>535</v>
+      <c r="A21" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>536</v>
+      <c r="A22" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>538</v>
+      <c r="A23" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H24" s="2">
+      <c r="A24" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="H24" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6652,46 +6685,46 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9" customWidth="1" style="3"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>539</v>
+      <c r="C1" s="3" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>366</v>
+      <c r="C2" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>133</v>
+      <c r="C3" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -6707,80 +6740,80 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="9" customWidth="1" style="3"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>251</v>
+      <c r="I1" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>366</v>
+      <c r="G2" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>133</v>
+      <c r="F3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -6796,219 +6829,219 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="28" customWidth="1" style="3"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>554</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="L3" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2">
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
         <v>2</v>
       </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="I8" s="3">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="I8" s="2">
-        <v>2</v>
-      </c>
-      <c r="K8" s="2">
+      <c r="K8" s="3">
         <v>60</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -7026,45 +7059,45 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
+    <col min="7" max="9" width="9" customWidth="1" style="3"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7082,22 +7115,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -7112,101 +7145,101 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1" style="3"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1" style="3"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="39.5" customWidth="1" style="3"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="32.25" customWidth="1" style="3"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>583</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>591</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>593</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
     </row>

--- a/Excel/一方通行/Mon3ter.xlsx
+++ b/Excel/一方通行/Mon3ter.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="594">
   <si>
     <t>Id</t>
   </si>
@@ -2111,8 +2111,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2125,6 +2124,19 @@
       <name val="宋体"/>
       <family val="3"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2152,23 +2164,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2473,37 +2479,36 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="3"/>
+    <col min="1" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2512,1265 +2517,1024 @@
   <dimension ref="A1:BX7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
-    <col min="8" max="8" width="9" customWidth="1" style="2"/>
-    <col min="9" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="9" customWidth="1" style="2"/>
-    <col min="11" max="11" width="9" customWidth="1" style="2"/>
-    <col min="12" max="12" width="6" customWidth="1" style="2"/>
-    <col min="13" max="13" width="4.08203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="5.58203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="4" customWidth="1" style="2"/>
-    <col min="16" max="16" width="7.75" customWidth="1" style="2"/>
-    <col min="17" max="17" width="10.83203125" customWidth="1" style="2"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="3.83203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="3.58203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="10.25" customWidth="1" style="2"/>
-    <col min="23" max="23" width="9.58203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="10.75" customWidth="1" style="2"/>
-    <col min="25" max="25" width="12.83203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="13.08203125" customWidth="1" style="2"/>
-    <col min="27" max="27" width="10.75" customWidth="1" style="2"/>
-    <col min="28" max="28" width="9" customWidth="1" style="2"/>
-    <col min="29" max="29" width="9" customWidth="1" style="2"/>
-    <col min="30" max="30" width="8" customWidth="1" style="2"/>
-    <col min="31" max="31" width="17.08203125" customWidth="1" style="2"/>
-    <col min="32" max="32" width="9" customWidth="1" style="2"/>
-    <col min="33" max="33" width="9" customWidth="1" style="2"/>
-    <col min="34" max="34" width="9.75" customWidth="1" style="2"/>
-    <col min="35" max="35" width="7.83203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="15.83203125" customWidth="1" style="2"/>
-    <col min="37" max="37" width="13.83203125" customWidth="1" style="2"/>
-    <col min="38" max="38" width="34.5" customWidth="1" style="2"/>
-    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="9.83203125" customWidth="1" style="2"/>
-    <col min="41" max="41" width="9.83203125" customWidth="1" style="2"/>
-    <col min="42" max="42" width="9" customWidth="1" style="2"/>
-    <col min="43" max="43" width="9" customWidth="1" style="2"/>
-    <col min="44" max="44" width="9" customWidth="1" style="2"/>
-    <col min="45" max="45" width="9" customWidth="1" style="2"/>
-    <col min="46" max="46" width="12.5" customWidth="1" style="2"/>
-    <col min="47" max="47" width="9" customWidth="1" style="2"/>
-    <col min="48" max="48" width="9" customWidth="1" style="2"/>
-    <col min="49" max="49" width="9" customWidth="1" style="2"/>
-    <col min="50" max="50" width="9" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="9" customWidth="1" style="2"/>
-    <col min="53" max="53" width="24.33203125" customWidth="1" style="2"/>
-    <col min="54" max="54" width="9" customWidth="1" style="2"/>
-    <col min="55" max="55" width="17.75" customWidth="1" style="2"/>
-    <col min="56" max="56" width="7.83203125" customWidth="1" style="2"/>
-    <col min="57" max="57" width="9" customWidth="1" style="2"/>
-    <col min="58" max="58" width="9" customWidth="1" style="2"/>
-    <col min="59" max="59" width="24.25" customWidth="1" style="2"/>
-    <col min="60" max="60" width="13.25" customWidth="1" style="2"/>
-    <col min="61" max="61" width="16.08203125" customWidth="1" style="2"/>
-    <col min="62" max="62" width="8" customWidth="1" style="2"/>
-    <col min="63" max="63" width="9" customWidth="1" style="2"/>
-    <col min="64" max="64" width="9" customWidth="1" style="2"/>
-    <col min="65" max="65" width="9" customWidth="1" style="2"/>
-    <col min="66" max="66" width="9" customWidth="1" style="2"/>
-    <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="9" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
-    <col min="71" max="71" width="14" customWidth="1" style="2"/>
-    <col min="72" max="72" width="14" customWidth="1" style="2"/>
-    <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="14" customWidth="1" style="2"/>
-    <col min="75" max="75" width="9" customWidth="1" style="2"/>
-    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="4.08203125" customWidth="1"/>
+    <col min="14" max="14" width="5.58203125" customWidth="1"/>
+    <col min="15" max="15" width="4" customWidth="1"/>
+    <col min="16" max="16" width="7.75" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="18" max="19" width="3.83203125" customWidth="1"/>
+    <col min="20" max="21" width="3.58203125" customWidth="1"/>
+    <col min="22" max="22" width="10.25" customWidth="1"/>
+    <col min="23" max="23" width="9.58203125" customWidth="1"/>
+    <col min="24" max="24" width="10.75" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1"/>
+    <col min="26" max="26" width="13.08203125" customWidth="1"/>
+    <col min="27" max="27" width="10.75" customWidth="1"/>
+    <col min="28" max="29" width="9" customWidth="1"/>
+    <col min="30" max="30" width="8" customWidth="1"/>
+    <col min="31" max="31" width="17.08203125" customWidth="1"/>
+    <col min="32" max="33" width="9" customWidth="1"/>
+    <col min="34" max="34" width="9.75" customWidth="1"/>
+    <col min="35" max="35" width="7.83203125" customWidth="1"/>
+    <col min="36" max="36" width="15.83203125" customWidth="1"/>
+    <col min="37" max="37" width="13.83203125" customWidth="1"/>
+    <col min="38" max="38" width="34.5" customWidth="1"/>
+    <col min="39" max="41" width="9.83203125" customWidth="1"/>
+    <col min="42" max="45" width="9" customWidth="1"/>
+    <col min="46" max="46" width="12.5" customWidth="1"/>
+    <col min="47" max="52" width="9" customWidth="1"/>
+    <col min="53" max="53" width="24.33203125" customWidth="1"/>
+    <col min="54" max="54" width="9" customWidth="1"/>
+    <col min="55" max="55" width="17.75" customWidth="1"/>
+    <col min="56" max="56" width="7.83203125" customWidth="1"/>
+    <col min="57" max="58" width="9" customWidth="1"/>
+    <col min="59" max="59" width="24.25" customWidth="1"/>
+    <col min="60" max="60" width="13.25" customWidth="1"/>
+    <col min="61" max="61" width="16.08203125" customWidth="1"/>
+    <col min="62" max="62" width="8" customWidth="1"/>
+    <col min="63" max="66" width="9" customWidth="1"/>
+    <col min="67" max="67" width="39.58203125" customWidth="1"/>
+    <col min="68" max="68" width="9" customWidth="1"/>
+    <col min="69" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1"/>
+    <col min="71" max="74" width="14" customWidth="1"/>
+    <col min="75" max="75" width="9" customWidth="1"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2" t="s">
+      <c r="T1" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>18</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>23</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>24</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>25</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>26</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" t="s">
         <v>27</v>
       </c>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>28</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>29</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>30</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>32</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>33</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>34</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>35</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" t="s">
         <v>36</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="2"/>
-      <c r="BF1" s="2"/>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>47</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>48</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" t="s">
         <v>49</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" t="s">
         <v>50</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" t="s">
         <v>51</v>
       </c>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-      <c r="BU1" s="2"/>
-      <c r="BV1" s="2"/>
-      <c r="BW1" s="2"/>
-      <c r="BX1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>59</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>60</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>61</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>62</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>63</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>64</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>65</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>66</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>67</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>68</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>69</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>70</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>71</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" t="s">
         <v>72</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>73</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>74</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>75</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" t="s">
         <v>76</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" t="s">
         <v>77</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>78</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" t="s">
         <v>79</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" t="s">
         <v>80</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" t="s">
         <v>81</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" t="s">
         <v>82</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AI2" t="s">
         <v>83</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" t="s">
         <v>84</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AK2" t="s">
         <v>85</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" t="s">
         <v>86</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" t="s">
         <v>87</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AN2" t="s">
         <v>88</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AO2" t="s">
         <v>89</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AP2" t="s">
         <v>90</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AQ2" t="s">
         <v>91</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AR2" t="s">
         <v>92</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AS2" t="s">
         <v>93</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AT2" t="s">
         <v>94</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AU2" t="s">
         <v>95</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AV2" t="s">
         <v>96</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AW2" t="s">
         <v>97</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AX2" t="s">
         <v>98</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AY2" t="s">
         <v>99</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AZ2" t="s">
         <v>100</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BA2" t="s">
         <v>101</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BB2" t="s">
         <v>102</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>103</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BD2" t="s">
         <v>104</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BE2" t="s">
         <v>105</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BF2" t="s">
         <v>106</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BG2" t="s">
         <v>107</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BH2" t="s">
         <v>108</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BI2" t="s">
         <v>109</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BJ2" t="s">
         <v>110</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BK2" t="s">
         <v>111</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BL2" t="s">
         <v>112</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BM2" t="s">
         <v>113</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BN2" t="s">
         <v>114</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BO2" t="s">
         <v>115</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BP2" t="s">
         <v>116</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>117</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BR2" t="s">
         <v>118</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BS2" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BT2" t="s">
         <v>120</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BU2" t="s">
         <v>121</v>
       </c>
-      <c r="BV2" s="2" t="s">
+      <c r="BV2" t="s">
         <v>122</v>
       </c>
-      <c r="BW2" s="2" t="s">
+      <c r="BW2" t="s">
         <v>123</v>
       </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BX2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>126</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>128</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>128</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>128</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>128</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>128</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>128</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" t="s">
         <v>128</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" t="s">
         <v>128</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" t="s">
         <v>126</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" t="s">
         <v>128</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" t="s">
         <v>128</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" t="s">
         <v>126</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" t="s">
         <v>126</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" t="s">
         <v>126</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" t="s">
         <v>128</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" t="s">
         <v>126</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" t="s">
         <v>128</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AE3" t="s">
         <v>125</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AF3" t="s">
         <v>2</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" t="s">
         <v>128</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" t="s">
         <v>128</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AI3" t="s">
         <v>128</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ3" t="s">
         <v>2</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AK3" t="s">
         <v>2</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" t="s">
         <v>129</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" t="s">
         <v>129</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AN3" t="s">
         <v>2</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" t="s">
         <v>2</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AP3" t="s">
         <v>126</v>
       </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AQ3" t="s">
         <v>130</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" t="s">
         <v>128</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AS3" t="s">
         <v>126</v>
       </c>
-      <c r="AT3" s="2" t="s">
+      <c r="AT3" t="s">
         <v>125</v>
       </c>
-      <c r="AU3" s="2"/>
-      <c r="AV3" s="2" t="s">
+      <c r="AV3" t="s">
         <v>126</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AW3" t="s">
         <v>125</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" t="s">
         <v>128</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="AY3" t="s">
         <v>131</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="AZ3" t="s">
         <v>126</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" t="s">
         <v>132</v>
       </c>
-      <c r="BB3" s="2" t="s">
+      <c r="BB3" t="s">
         <v>125</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BC3" t="s">
         <v>125</v>
       </c>
-      <c r="BD3" s="2" t="s">
+      <c r="BD3" t="s">
         <v>126</v>
       </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BE3" t="s">
         <v>133</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BF3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" s="2" t="s">
+      <c r="BG3" t="s">
         <v>2</v>
       </c>
-      <c r="BH3" s="2" t="s">
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BI3" s="2" t="s">
+      <c r="BI3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" s="2" t="s">
+      <c r="BJ3" t="s">
         <v>134</v>
       </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BK3" t="s">
         <v>128</v>
       </c>
-      <c r="BL3" s="2" t="s">
+      <c r="BL3" t="s">
         <v>2</v>
       </c>
-      <c r="BM3" s="2" t="s">
+      <c r="BM3" t="s">
         <v>130</v>
       </c>
-      <c r="BN3" s="2" t="s">
+      <c r="BN3" t="s">
         <v>2</v>
       </c>
-      <c r="BO3" s="2" t="s">
+      <c r="BO3" t="s">
         <v>135</v>
       </c>
-      <c r="BP3" s="2" t="s">
+      <c r="BP3" t="s">
         <v>130</v>
       </c>
-      <c r="BQ3" s="2" t="s">
+      <c r="BQ3" t="s">
         <v>130</v>
       </c>
-      <c r="BR3" s="2" t="s">
+      <c r="BR3" t="s">
         <v>130</v>
       </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BS3" t="s">
         <v>130</v>
       </c>
-      <c r="BT3" s="2" t="s">
+      <c r="BT3" t="s">
         <v>130</v>
       </c>
-      <c r="BU3" s="2" t="s">
+      <c r="BU3" t="s">
         <v>130</v>
       </c>
-      <c r="BV3" s="2" t="s">
+      <c r="BV3" t="s">
         <v>130</v>
       </c>
-      <c r="BW3" s="2" t="s">
+      <c r="BW3" t="s">
         <v>130</v>
       </c>
-      <c r="BX3" s="2" t="s">
+      <c r="BX3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2"/>
-      <c r="BD4" s="2"/>
-      <c r="BE4" s="2"/>
-      <c r="BF4" s="2"/>
-      <c r="BG4" s="2"/>
-      <c r="BH4" s="2"/>
-      <c r="BI4" s="2"/>
-      <c r="BJ4" s="2"/>
-      <c r="BK4" s="2"/>
-      <c r="BL4" s="2"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2"/>
-      <c r="BO4" s="2"/>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2"/>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2"/>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2"/>
-      <c r="BW4" s="2"/>
-      <c r="BX4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>138</v>
       </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5">
         <v>90</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5">
         <v>2235</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2">
+      <c r="N5">
         <v>583</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2">
+      <c r="P5">
         <v>221</v>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2">
+      <c r="R5">
         <v>0</v>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2">
+      <c r="T5">
         <v>16</v>
       </c>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2">
+      <c r="V5">
         <v>0.5</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5">
         <v>70</v>
       </c>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2">
+      <c r="Z5">
         <v>0.05</v>
       </c>
-      <c r="AA5" s="2">
+      <c r="AA5">
         <v>2.85</v>
       </c>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2" t="s">
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>4</v>
       </c>
-      <c r="AK5" s="2" t="s">
+      <c r="AK5" t="s">
         <v>139</v>
       </c>
-      <c r="AL5" s="2" t="s">
+      <c r="AL5" t="s">
         <v>140</v>
       </c>
-      <c r="AM5" s="2" t="s">
+      <c r="AM5" t="s">
         <v>141</v>
       </c>
-      <c r="AN5" s="2" t="s">
+      <c r="AN5" t="s">
         <v>142</v>
       </c>
-      <c r="AO5" s="2" t="s">
+      <c r="AO5" t="s">
         <v>143</v>
       </c>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2" t="s">
+      <c r="AQ5" t="s">
         <v>144</v>
       </c>
-      <c r="AR5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS5" s="2">
+      <c r="AR5">
+        <v>1</v>
+      </c>
+      <c r="AS5">
         <v>0.5</v>
       </c>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2"/>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2">
+      <c r="AZ5">
         <v>0.25</v>
       </c>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2"/>
-      <c r="BD5" s="2"/>
-      <c r="BE5" s="2" t="s">
+      <c r="BE5" t="s">
         <v>145</v>
       </c>
-      <c r="BF5" s="2" t="s">
+      <c r="BF5" t="s">
         <v>146</v>
       </c>
-      <c r="BG5" s="2" t="s">
+      <c r="BG5" t="s">
         <v>147</v>
       </c>
-      <c r="BH5" s="2" t="s">
+      <c r="BH5" t="s">
         <v>148</v>
       </c>
-      <c r="BI5" s="2" t="s">
+      <c r="BI5" t="s">
         <v>149</v>
       </c>
-      <c r="BJ5" s="2" t="s">
+      <c r="BJ5" t="s">
         <v>150</v>
       </c>
-      <c r="BK5" s="2">
+      <c r="BK5">
         <v>6</v>
       </c>
-      <c r="BL5" s="2" t="s">
+      <c r="BL5" t="s">
         <v>151</v>
       </c>
-      <c r="BM5" s="2" t="s">
+      <c r="BM5" t="s">
         <v>152</v>
       </c>
-      <c r="BN5" s="2"/>
-      <c r="BO5" s="2"/>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2" t="s">
+      <c r="BQ5" t="s">
         <v>153</v>
       </c>
-      <c r="BR5" s="2" t="s">
+      <c r="BR5" t="s">
         <v>154</v>
       </c>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2" t="s">
+      <c r="BT5" t="s">
         <v>155</v>
       </c>
-      <c r="BU5" s="2" t="s">
+      <c r="BU5" t="s">
         <v>155</v>
       </c>
-      <c r="BV5" s="2"/>
-      <c r="BW5" s="2"/>
-      <c r="BX5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="BX5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>156</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>157</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>157</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>158</v>
       </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <v>90</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>5433</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2">
+      <c r="N6">
         <v>583</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2">
+      <c r="P6">
         <v>221</v>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2">
+      <c r="R6">
         <v>0</v>
       </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2">
+      <c r="T6">
         <v>3</v>
       </c>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2">
+      <c r="V6">
         <v>0</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6">
         <v>15</v>
       </c>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2">
+      <c r="Z6">
         <v>0.05</v>
       </c>
-      <c r="AA6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2">
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
         <v>0</v>
       </c>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2">
+      <c r="AH6">
         <v>-1</v>
       </c>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2" t="s">
+      <c r="AJ6" t="s">
         <v>156</v>
       </c>
-      <c r="AK6" s="2" t="s">
+      <c r="AK6" t="s">
         <v>139</v>
       </c>
-      <c r="AL6" s="2" t="s">
+      <c r="AL6" t="s">
         <v>159</v>
       </c>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2" t="s">
+      <c r="AN6" t="s">
         <v>142</v>
       </c>
-      <c r="AO6" s="2" t="s">
+      <c r="AO6" t="s">
         <v>160</v>
       </c>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2" t="s">
+      <c r="AQ6" t="s">
         <v>161</v>
       </c>
-      <c r="AR6" s="2">
+      <c r="AR6">
         <v>0</v>
       </c>
-      <c r="AS6" s="2">
+      <c r="AS6">
         <v>0</v>
       </c>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2" t="s">
+      <c r="AY6" t="s">
         <v>162</v>
       </c>
-      <c r="AZ6" s="2">
+      <c r="AZ6">
         <v>0.25</v>
       </c>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2"/>
-      <c r="BD6" s="2"/>
-      <c r="BE6" s="2" t="s">
+      <c r="BE6" t="s">
         <v>145</v>
       </c>
-      <c r="BF6" s="2"/>
-      <c r="BG6" s="2" t="s">
+      <c r="BG6" t="s">
         <v>163</v>
       </c>
-      <c r="BH6" s="2" t="s">
+      <c r="BH6" t="s">
         <v>164</v>
       </c>
-      <c r="BI6" s="2" t="s">
+      <c r="BI6" t="s">
         <v>157</v>
       </c>
-      <c r="BJ6" s="2" t="s">
+      <c r="BJ6" t="s">
         <v>150</v>
       </c>
-      <c r="BK6" s="2">
+      <c r="BK6">
         <v>6</v>
       </c>
-      <c r="BL6" s="2" t="s">
+      <c r="BL6" t="s">
         <v>165</v>
       </c>
-      <c r="BM6" s="2" t="s">
+      <c r="BM6" t="s">
         <v>156</v>
       </c>
-      <c r="BN6" s="2"/>
-      <c r="BO6" s="2"/>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2" t="s">
+      <c r="BQ6" t="s">
         <v>153</v>
       </c>
-      <c r="BR6" s="2" t="s">
+      <c r="BR6" t="s">
         <v>154</v>
       </c>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2"/>
-      <c r="BU6" s="2"/>
-      <c r="BV6" s="2"/>
-      <c r="BW6" s="2"/>
-      <c r="BX6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="BX6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>138</v>
       </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>2</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7">
         <v>90</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7">
         <v>2235</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
+      <c r="N7">
         <v>583</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2">
+      <c r="P7">
         <v>221</v>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2">
+      <c r="R7">
         <v>0</v>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2">
+      <c r="T7">
         <v>0</v>
       </c>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2">
+      <c r="V7">
         <v>0.5</v>
       </c>
-      <c r="W7" s="2">
+      <c r="W7">
         <v>70</v>
       </c>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2">
+      <c r="Z7">
         <v>0.05</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AA7">
         <v>2.85</v>
       </c>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2" t="s">
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>4</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AK7" t="s">
         <v>139</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL7" t="s">
         <v>167</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AM7" t="s">
         <v>168</v>
       </c>
-      <c r="AN7" s="2" t="s">
+      <c r="AN7" t="s">
         <v>142</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AO7" t="s">
         <v>143</v>
       </c>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2" t="s">
+      <c r="AQ7" t="s">
         <v>161</v>
       </c>
-      <c r="AR7" s="2">
+      <c r="AR7">
         <v>3</v>
       </c>
-      <c r="AS7" s="2">
+      <c r="AS7">
         <v>0</v>
       </c>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2">
+      <c r="AZ7">
         <v>0.25</v>
       </c>
-      <c r="BA7" s="2"/>
-      <c r="BB7" s="2"/>
-      <c r="BC7" s="2"/>
-      <c r="BD7" s="2"/>
-      <c r="BE7" s="2" t="s">
+      <c r="BE7" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="2" t="s">
+      <c r="BF7" t="s">
         <v>146</v>
       </c>
-      <c r="BG7" s="2" t="s">
+      <c r="BG7" t="s">
         <v>147</v>
       </c>
-      <c r="BH7" s="2" t="s">
+      <c r="BH7" t="s">
         <v>148</v>
       </c>
-      <c r="BI7" s="2" t="s">
+      <c r="BI7" t="s">
         <v>149</v>
       </c>
-      <c r="BJ7" s="2" t="s">
+      <c r="BJ7" t="s">
         <v>150</v>
       </c>
-      <c r="BK7" s="2">
+      <c r="BK7">
         <v>6</v>
       </c>
-      <c r="BL7" s="2" t="s">
+      <c r="BL7" t="s">
         <v>151</v>
       </c>
-      <c r="BM7" s="2" t="s">
+      <c r="BM7" t="s">
         <v>152</v>
       </c>
-      <c r="BN7" s="2"/>
-      <c r="BO7" s="2"/>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2" t="s">
+      <c r="BQ7" t="s">
         <v>169</v>
       </c>
-      <c r="BR7" s="2" t="s">
+      <c r="BR7" t="s">
         <v>169</v>
       </c>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2" t="s">
+      <c r="BT7" t="s">
         <v>170</v>
       </c>
-      <c r="BU7" s="2" t="s">
+      <c r="BU7" t="s">
         <v>155</v>
       </c>
-      <c r="BV7" s="2"/>
-      <c r="BW7" s="2"/>
-      <c r="BX7" s="2">
+      <c r="BX7">
         <v>1</v>
       </c>
     </row>
@@ -3778,7 +3542,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3788,2435 +3551,2435 @@
   <dimension ref="A1:DI677"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="3"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="3"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
-    <col min="40" max="40" width="15" customWidth="1" style="3"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="3"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="3"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
-    <col min="51" max="51" width="9" customWidth="1" style="3"/>
-    <col min="52" max="52" width="7" customWidth="1" style="3"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="3"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
-    <col min="72" max="73" width="8" customWidth="1" style="3"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
-    <col min="86" max="86" width="9" customWidth="1" style="3"/>
-    <col min="87" max="87" width="16" customWidth="1" style="3"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
-    <col min="93" max="98" width="9" customWidth="1" style="3"/>
-    <col min="99" max="99" width="14" customWidth="1" style="3"/>
-    <col min="100" max="100" width="8" customWidth="1" style="3"/>
-    <col min="101" max="101" width="9" customWidth="1" style="3"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
-    <col min="104" max="109" width="9" customWidth="1" style="3"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
-    <col min="111" max="113" width="9" customWidth="1" style="3"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
+    <col min="40" max="40" width="15" customWidth="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="51" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="86" max="86" width="9" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="93" max="98" width="9" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="101" max="101" width="9" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="104" max="109" width="9" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="111" max="113" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>175</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>176</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>177</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>178</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>179</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>180</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>181</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>182</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>183</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>184</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>185</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" t="s">
         <v>186</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" t="s">
         <v>187</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" t="s">
         <v>188</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" t="s">
         <v>188</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" t="s">
         <v>189</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" t="s">
         <v>190</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" t="s">
         <v>191</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>192</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" t="s">
         <v>193</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" t="s">
         <v>194</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>195</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" t="s">
         <v>196</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" t="s">
         <v>197</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" t="s">
         <v>198</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" t="s">
         <v>199</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" t="s">
         <v>200</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" t="s">
         <v>201</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" t="s">
         <v>202</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" t="s">
         <v>203</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" t="s">
         <v>204</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" t="s">
         <v>205</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" t="s">
         <v>206</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" t="s">
         <v>207</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" t="s">
         <v>208</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" t="s">
         <v>209</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" t="s">
         <v>210</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" t="s">
         <v>211</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" t="s">
         <v>212</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AT1" t="s">
         <v>213</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AU1" t="s">
         <v>214</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" t="s">
         <v>215</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AW1" t="s">
         <v>216</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AX1" t="s">
         <v>217</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AY1" t="s">
         <v>218</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="AZ1" t="s">
         <v>219</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" t="s">
         <v>220</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BB1" t="s">
         <v>221</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BC1" t="s">
         <v>222</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BD1" t="s">
         <v>223</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BE1" t="s">
         <v>224</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BF1" t="s">
         <v>225</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BG1" t="s">
         <v>226</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BH1" t="s">
         <v>227</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BJ1" t="s">
         <v>227</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BK1" t="s">
         <v>228</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BL1" t="s">
         <v>229</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BM1" t="s">
         <v>230</v>
       </c>
-      <c r="BN1" s="3" t="s">
+      <c r="BN1" t="s">
         <v>231</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BO1" t="s">
         <v>232</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BP1" t="s">
         <v>233</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BQ1" t="s">
         <v>234</v>
       </c>
-      <c r="BR1" s="3" t="s">
+      <c r="BR1" t="s">
         <v>235</v>
       </c>
-      <c r="BS1" s="3" t="s">
+      <c r="BS1" t="s">
         <v>236</v>
       </c>
-      <c r="BT1" s="3" t="s">
+      <c r="BT1" t="s">
         <v>237</v>
       </c>
-      <c r="BU1" s="3" t="s">
+      <c r="BU1" t="s">
         <v>238</v>
       </c>
-      <c r="BV1" s="3" t="s">
+      <c r="BV1" t="s">
         <v>239</v>
       </c>
-      <c r="BW1" s="3" t="s">
+      <c r="BW1" t="s">
         <v>240</v>
       </c>
-      <c r="BX1" s="3" t="s">
+      <c r="BX1" t="s">
         <v>241</v>
       </c>
-      <c r="BY1" s="3" t="s">
+      <c r="BY1" t="s">
         <v>242</v>
       </c>
-      <c r="BZ1" s="3" t="s">
+      <c r="BZ1" t="s">
         <v>243</v>
       </c>
-      <c r="CA1" s="3" t="s">
+      <c r="CA1" t="s">
         <v>244</v>
       </c>
-      <c r="CB1" s="3" t="s">
+      <c r="CB1" t="s">
         <v>245</v>
       </c>
-      <c r="CC1" s="3" t="s">
+      <c r="CC1" t="s">
         <v>246</v>
       </c>
-      <c r="CD1" s="3" t="s">
+      <c r="CD1" t="s">
         <v>247</v>
       </c>
-      <c r="CE1" s="3" t="s">
+      <c r="CE1" t="s">
         <v>248</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CF1" t="s">
         <v>249</v>
       </c>
-      <c r="CG1" s="3" t="s">
+      <c r="CG1" t="s">
         <v>250</v>
       </c>
-      <c r="CH1" s="3" t="s">
+      <c r="CH1" t="s">
         <v>251</v>
       </c>
-      <c r="CI1" s="3" t="s">
+      <c r="CI1" t="s">
         <v>252</v>
       </c>
-      <c r="CJ1" s="3" t="s">
+      <c r="CJ1" t="s">
         <v>253</v>
       </c>
-      <c r="CK1" s="3" t="s">
+      <c r="CK1" t="s">
         <v>254</v>
       </c>
-      <c r="CL1" s="3" t="s">
+      <c r="CL1" t="s">
         <v>255</v>
       </c>
-      <c r="CM1" s="3" t="s">
+      <c r="CM1" t="s">
         <v>256</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CN1" t="s">
         <v>257</v>
       </c>
-      <c r="CO1" s="3" t="s">
+      <c r="CO1" t="s">
         <v>258</v>
       </c>
-      <c r="CP1" s="3" t="s">
+      <c r="CP1" t="s">
         <v>259</v>
       </c>
-      <c r="CQ1" s="3" t="s">
+      <c r="CQ1" t="s">
         <v>260</v>
       </c>
-      <c r="CR1" s="3" t="s">
+      <c r="CR1" t="s">
         <v>237</v>
       </c>
-      <c r="CS1" s="3" t="s">
+      <c r="CS1" t="s">
         <v>261</v>
       </c>
-      <c r="CT1" s="3" t="s">
+      <c r="CT1" t="s">
         <v>262</v>
       </c>
-      <c r="CU1" s="3" t="s">
+      <c r="CU1" t="s">
         <v>263</v>
       </c>
-      <c r="CV1" s="3" t="s">
+      <c r="CV1" t="s">
         <v>264</v>
       </c>
-      <c r="CW1" s="3" t="s">
+      <c r="CW1" t="s">
         <v>265</v>
       </c>
-      <c r="CX1" s="3" t="s">
+      <c r="CX1" t="s">
         <v>266</v>
       </c>
-      <c r="CY1" s="3" t="s">
+      <c r="CY1" t="s">
         <v>267</v>
       </c>
-      <c r="CZ1" s="3" t="s">
+      <c r="CZ1" t="s">
         <v>266</v>
       </c>
-      <c r="DA1" s="3" t="s">
+      <c r="DA1" t="s">
         <v>268</v>
       </c>
-      <c r="DB1" s="3" t="s">
+      <c r="DB1" t="s">
         <v>269</v>
       </c>
-      <c r="DC1" s="3" t="s">
+      <c r="DC1" t="s">
         <v>270</v>
       </c>
-      <c r="DD1" s="3" t="s">
+      <c r="DD1" t="s">
         <v>271</v>
       </c>
-      <c r="DE1" s="3" t="s">
+      <c r="DE1" t="s">
         <v>272</v>
       </c>
-      <c r="DF1" s="3" t="s">
+      <c r="DF1" t="s">
         <v>273</v>
       </c>
-      <c r="DG1" s="3" t="s">
+      <c r="DG1" t="s">
         <v>274</v>
       </c>
-      <c r="DH1" s="3" t="s">
+      <c r="DH1" t="s">
         <v>275</v>
       </c>
-      <c r="DI1" s="3" t="s">
+      <c r="DI1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>277</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>278</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>279</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>280</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>281</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>282</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>283</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" t="s">
         <v>284</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" t="s">
         <v>285</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" t="s">
         <v>286</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" t="s">
         <v>287</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" t="s">
         <v>288</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" t="s">
         <v>289</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" t="s">
         <v>290</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" t="s">
         <v>291</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" t="s">
         <v>292</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" t="s">
         <v>293</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" t="s">
         <v>294</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" t="s">
         <v>295</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" t="s">
         <v>296</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" t="s">
         <v>297</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AA2" t="s">
         <v>298</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AB2" t="s">
         <v>299</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AC2" t="s">
         <v>300</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" t="s">
         <v>301</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AE2" t="s">
         <v>302</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AF2" t="s">
         <v>303</v>
       </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AG2" t="s">
         <v>304</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AH2" t="s">
         <v>305</v>
       </c>
-      <c r="AI2" s="3" t="s">
+      <c r="AI2" t="s">
         <v>306</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AJ2" t="s">
         <v>307</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AK2" t="s">
         <v>308</v>
       </c>
-      <c r="AL2" s="3" t="s">
+      <c r="AL2" t="s">
         <v>309</v>
       </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AM2" t="s">
         <v>310</v>
       </c>
-      <c r="AN2" s="3" t="s">
+      <c r="AN2" t="s">
         <v>311</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AO2" t="s">
         <v>312</v>
       </c>
-      <c r="AP2" s="3" t="s">
+      <c r="AP2" t="s">
         <v>313</v>
       </c>
-      <c r="AQ2" s="3" t="s">
+      <c r="AQ2" t="s">
         <v>314</v>
       </c>
-      <c r="AR2" s="3" t="s">
+      <c r="AR2" t="s">
         <v>315</v>
       </c>
-      <c r="AS2" s="3" t="s">
+      <c r="AS2" t="s">
         <v>316</v>
       </c>
-      <c r="AT2" s="3" t="s">
+      <c r="AT2" t="s">
         <v>317</v>
       </c>
-      <c r="AU2" s="3" t="s">
+      <c r="AU2" t="s">
         <v>318</v>
       </c>
-      <c r="AV2" s="3" t="s">
+      <c r="AV2" t="s">
         <v>319</v>
       </c>
-      <c r="AW2" s="3" t="s">
+      <c r="AW2" t="s">
         <v>320</v>
       </c>
-      <c r="AX2" s="3" t="s">
+      <c r="AX2" t="s">
         <v>321</v>
       </c>
-      <c r="AY2" s="3" t="s">
+      <c r="AY2" t="s">
         <v>322</v>
       </c>
-      <c r="AZ2" s="3" t="s">
+      <c r="AZ2" t="s">
         <v>323</v>
       </c>
-      <c r="BA2" s="3" t="s">
+      <c r="BA2" t="s">
         <v>324</v>
       </c>
-      <c r="BB2" s="3" t="s">
+      <c r="BB2" t="s">
         <v>325</v>
       </c>
-      <c r="BC2" s="3" t="s">
+      <c r="BC2" t="s">
         <v>326</v>
       </c>
-      <c r="BD2" s="3" t="s">
+      <c r="BD2" t="s">
         <v>327</v>
       </c>
-      <c r="BE2" s="3" t="s">
+      <c r="BE2" t="s">
         <v>328</v>
       </c>
-      <c r="BF2" s="3" t="s">
+      <c r="BF2" t="s">
         <v>329</v>
       </c>
-      <c r="BG2" s="3" t="s">
+      <c r="BG2" t="s">
         <v>330</v>
       </c>
-      <c r="BH2" s="3" t="s">
+      <c r="BH2" t="s">
         <v>331</v>
       </c>
-      <c r="BI2" s="3" t="s">
+      <c r="BI2" t="s">
         <v>332</v>
       </c>
-      <c r="BJ2" s="3" t="s">
+      <c r="BJ2" t="s">
         <v>333</v>
       </c>
-      <c r="BK2" s="3" t="s">
+      <c r="BK2" t="s">
         <v>334</v>
       </c>
-      <c r="BL2" s="3" t="s">
+      <c r="BL2" t="s">
         <v>335</v>
       </c>
-      <c r="BM2" s="3" t="s">
+      <c r="BM2" t="s">
         <v>336</v>
       </c>
-      <c r="BN2" s="3" t="s">
+      <c r="BN2" t="s">
         <v>337</v>
       </c>
-      <c r="BO2" s="3" t="s">
+      <c r="BO2" t="s">
         <v>86</v>
       </c>
-      <c r="BP2" s="3" t="s">
+      <c r="BP2" t="s">
         <v>338</v>
       </c>
-      <c r="BQ2" s="3" t="s">
+      <c r="BQ2" t="s">
         <v>339</v>
       </c>
-      <c r="BR2" s="3" t="s">
+      <c r="BR2" t="s">
         <v>340</v>
       </c>
-      <c r="BS2" s="3" t="s">
+      <c r="BS2" t="s">
         <v>341</v>
       </c>
-      <c r="BT2" s="3" t="s">
+      <c r="BT2" t="s">
         <v>342</v>
       </c>
-      <c r="BU2" s="3" t="s">
+      <c r="BU2" t="s">
         <v>102</v>
       </c>
-      <c r="BV2" s="3" t="s">
+      <c r="BV2" t="s">
         <v>343</v>
       </c>
-      <c r="BW2" s="3" t="s">
+      <c r="BW2" t="s">
         <v>344</v>
       </c>
-      <c r="BX2" s="3" t="s">
+      <c r="BX2" t="s">
         <v>345</v>
       </c>
-      <c r="BY2" s="3" t="s">
+      <c r="BY2" t="s">
         <v>346</v>
       </c>
-      <c r="BZ2" s="3" t="s">
+      <c r="BZ2" t="s">
         <v>347</v>
       </c>
-      <c r="CA2" s="3" t="s">
+      <c r="CA2" t="s">
         <v>348</v>
       </c>
-      <c r="CB2" s="3" t="s">
+      <c r="CB2" t="s">
         <v>349</v>
       </c>
-      <c r="CC2" s="3" t="s">
+      <c r="CC2" t="s">
         <v>350</v>
       </c>
-      <c r="CD2" s="3" t="s">
+      <c r="CD2" t="s">
         <v>351</v>
       </c>
-      <c r="CE2" s="3" t="s">
+      <c r="CE2" t="s">
         <v>352</v>
       </c>
-      <c r="CF2" s="3" t="s">
+      <c r="CF2" t="s">
         <v>353</v>
       </c>
-      <c r="CG2" s="3" t="s">
+      <c r="CG2" t="s">
         <v>354</v>
       </c>
-      <c r="CH2" s="3" t="s">
+      <c r="CH2" t="s">
         <v>355</v>
       </c>
-      <c r="CI2" s="3" t="s">
+      <c r="CI2" t="s">
         <v>356</v>
       </c>
-      <c r="CJ2" s="3" t="s">
+      <c r="CJ2" t="s">
         <v>357</v>
       </c>
-      <c r="CK2" s="3" t="s">
+      <c r="CK2" t="s">
         <v>358</v>
       </c>
-      <c r="CL2" s="3" t="s">
+      <c r="CL2" t="s">
         <v>359</v>
       </c>
-      <c r="CM2" s="3" t="s">
+      <c r="CM2" t="s">
         <v>360</v>
       </c>
-      <c r="CN2" s="3" t="s">
+      <c r="CN2" t="s">
         <v>361</v>
       </c>
-      <c r="CO2" s="3" t="s">
+      <c r="CO2" t="s">
         <v>362</v>
       </c>
-      <c r="CP2" s="3" t="s">
+      <c r="CP2" t="s">
         <v>363</v>
       </c>
-      <c r="CQ2" s="3" t="s">
+      <c r="CQ2" t="s">
         <v>364</v>
       </c>
-      <c r="CR2" s="3" t="s">
+      <c r="CR2" t="s">
         <v>365</v>
       </c>
-      <c r="CS2" s="3" t="s">
+      <c r="CS2" t="s">
         <v>366</v>
       </c>
-      <c r="CT2" s="3" t="s">
+      <c r="CT2" t="s">
         <v>367</v>
       </c>
-      <c r="CU2" s="3" t="s">
+      <c r="CU2" t="s">
         <v>368</v>
       </c>
-      <c r="CV2" s="3" t="s">
+      <c r="CV2" t="s">
         <v>369</v>
       </c>
-      <c r="CW2" s="3" t="s">
+      <c r="CW2" t="s">
         <v>370</v>
       </c>
-      <c r="CX2" s="3" t="s">
+      <c r="CX2" t="s">
         <v>371</v>
       </c>
-      <c r="CY2" s="3" t="s">
+      <c r="CY2" t="s">
         <v>372</v>
       </c>
-      <c r="CZ2" s="3" t="s">
+      <c r="CZ2" t="s">
         <v>373</v>
       </c>
-      <c r="DA2" s="3" t="s">
+      <c r="DA2" t="s">
         <v>374</v>
       </c>
-      <c r="DB2" s="3" t="s">
+      <c r="DB2" t="s">
         <v>375</v>
       </c>
-      <c r="DC2" s="3" t="s">
+      <c r="DC2" t="s">
         <v>376</v>
       </c>
-      <c r="DD2" s="3" t="s">
+      <c r="DD2" t="s">
         <v>377</v>
       </c>
-      <c r="DE2" s="3" t="s">
+      <c r="DE2" t="s">
         <v>378</v>
       </c>
-      <c r="DF2" s="3" t="s">
+      <c r="DF2" t="s">
         <v>379</v>
       </c>
-      <c r="DG2" s="3" t="s">
+      <c r="DG2" t="s">
         <v>380</v>
       </c>
-      <c r="DH2" s="3" t="s">
+      <c r="DH2" t="s">
         <v>381</v>
       </c>
-      <c r="DI2" s="3" t="s">
+      <c r="DI2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>128</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>125</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>383</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>384</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" t="s">
         <v>385</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" t="s">
         <v>128</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" t="s">
         <v>128</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" t="s">
         <v>131</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" t="s">
         <v>131</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" t="s">
         <v>131</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" t="s">
         <v>131</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" t="s">
         <v>125</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" t="s">
         <v>126</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" t="s">
         <v>126</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" t="s">
         <v>126</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" t="s">
         <v>125</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" t="s">
         <v>125</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" t="s">
         <v>125</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" t="s">
         <v>125</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AA3" t="s">
         <v>126</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" t="s">
         <v>125</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" t="s">
         <v>128</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" t="s">
         <v>125</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" t="s">
         <v>125</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AF3" t="s">
         <v>125</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AG3" t="s">
         <v>386</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AH3" t="s">
         <v>125</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AI3" t="s">
         <v>133</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AJ3" t="s">
         <v>3</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AK3" t="s">
         <v>128</v>
       </c>
-      <c r="AL3" s="3" t="s">
+      <c r="AL3" t="s">
         <v>128</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AM3" t="s">
         <v>128</v>
       </c>
-      <c r="AN3" s="3" t="s">
+      <c r="AN3" t="s">
         <v>125</v>
       </c>
-      <c r="AO3" s="3" t="s">
+      <c r="AO3" t="s">
         <v>387</v>
       </c>
-      <c r="AP3" s="3" t="s">
+      <c r="AP3" t="s">
         <v>388</v>
       </c>
-      <c r="AQ3" s="3" t="s">
+      <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" s="3" t="s">
+      <c r="AR3" t="s">
         <v>2</v>
       </c>
-      <c r="AS3" s="3" t="s">
+      <c r="AS3" t="s">
         <v>2</v>
       </c>
-      <c r="AT3" s="3" t="s">
+      <c r="AT3" t="s">
         <v>389</v>
       </c>
-      <c r="AU3" s="3" t="s">
+      <c r="AU3" t="s">
         <v>125</v>
       </c>
-      <c r="AV3" s="3" t="s">
+      <c r="AV3" t="s">
         <v>126</v>
       </c>
-      <c r="AW3" s="3" t="s">
+      <c r="AW3" t="s">
         <v>125</v>
       </c>
-      <c r="AX3" s="3" t="s">
+      <c r="AX3" t="s">
         <v>390</v>
       </c>
-      <c r="AY3" s="3" t="s">
+      <c r="AY3" t="s">
         <v>125</v>
       </c>
-      <c r="AZ3" s="3" t="s">
+      <c r="AZ3" t="s">
         <v>126</v>
       </c>
-      <c r="BA3" s="3" t="s">
+      <c r="BA3" t="s">
         <v>125</v>
       </c>
-      <c r="BB3" s="3" t="s">
+      <c r="BB3" t="s">
         <v>128</v>
       </c>
-      <c r="BC3" s="3" t="s">
+      <c r="BC3" t="s">
         <v>126</v>
       </c>
-      <c r="BD3" s="3" t="s">
+      <c r="BD3" t="s">
         <v>128</v>
       </c>
-      <c r="BE3" s="3" t="s">
+      <c r="BE3" t="s">
         <v>128</v>
       </c>
-      <c r="BF3" s="3" t="s">
+      <c r="BF3" t="s">
         <v>126</v>
       </c>
-      <c r="BG3" s="3" t="s">
+      <c r="BG3" t="s">
         <v>125</v>
       </c>
-      <c r="BH3" s="3" t="s">
+      <c r="BH3" t="s">
         <v>389</v>
       </c>
-      <c r="BI3" s="3" t="s">
+      <c r="BI3" t="s">
         <v>125</v>
       </c>
-      <c r="BJ3" s="3" t="s">
+      <c r="BJ3" t="s">
         <v>126</v>
       </c>
-      <c r="BK3" s="3" t="s">
+      <c r="BK3" t="s">
         <v>126</v>
       </c>
-      <c r="BL3" s="3" t="s">
+      <c r="BL3" t="s">
         <v>126</v>
       </c>
-      <c r="BM3" s="3" t="s">
+      <c r="BM3" t="s">
         <v>128</v>
       </c>
-      <c r="BN3" s="3" t="s">
+      <c r="BN3" t="s">
         <v>128</v>
       </c>
-      <c r="BO3" s="3" t="s">
+      <c r="BO3" t="s">
         <v>129</v>
       </c>
-      <c r="BP3" s="3" t="s">
+      <c r="BP3" t="s">
         <v>129</v>
       </c>
-      <c r="BQ3" s="3" t="s">
+      <c r="BQ3" t="s">
         <v>391</v>
       </c>
-      <c r="BR3" s="3" t="s">
+      <c r="BR3" t="s">
         <v>392</v>
       </c>
-      <c r="BS3" s="3" t="s">
+      <c r="BS3" t="s">
         <v>126</v>
       </c>
-      <c r="BT3" s="3" t="s">
+      <c r="BT3" t="s">
         <v>126</v>
       </c>
-      <c r="BU3" s="3" t="s">
+      <c r="BU3" t="s">
         <v>125</v>
       </c>
-      <c r="BV3" s="3" t="s">
+      <c r="BV3" t="s">
         <v>126</v>
       </c>
-      <c r="BW3" s="3" t="s">
+      <c r="BW3" t="s">
         <v>126</v>
       </c>
-      <c r="BX3" s="3" t="s">
+      <c r="BX3" t="s">
         <v>128</v>
       </c>
-      <c r="BY3" s="3" t="s">
+      <c r="BY3" t="s">
         <v>393</v>
       </c>
-      <c r="BZ3" s="3" t="s">
+      <c r="BZ3" t="s">
         <v>125</v>
       </c>
-      <c r="CA3" s="3" t="s">
+      <c r="CA3" t="s">
         <v>393</v>
       </c>
-      <c r="CB3" s="3" t="s">
+      <c r="CB3" t="s">
         <v>130</v>
       </c>
-      <c r="CC3" s="3" t="s">
+      <c r="CC3" t="s">
         <v>394</v>
       </c>
-      <c r="CD3" s="3" t="s">
+      <c r="CD3" t="s">
         <v>130</v>
       </c>
-      <c r="CE3" s="3" t="s">
+      <c r="CE3" t="s">
         <v>130</v>
       </c>
-      <c r="CF3" s="3" t="s">
+      <c r="CF3" t="s">
         <v>130</v>
       </c>
-      <c r="CG3" s="3" t="s">
+      <c r="CG3" t="s">
         <v>395</v>
       </c>
-      <c r="CH3" s="3" t="s">
+      <c r="CH3" t="s">
         <v>396</v>
       </c>
-      <c r="CI3" s="3" t="s">
+      <c r="CI3" t="s">
         <v>2</v>
       </c>
-      <c r="CJ3" s="3" t="s">
+      <c r="CJ3" t="s">
         <v>397</v>
       </c>
-      <c r="CK3" s="3" t="s">
+      <c r="CK3" t="s">
         <v>397</v>
       </c>
-      <c r="CL3" s="3" t="s">
+      <c r="CL3" t="s">
         <v>135</v>
       </c>
-      <c r="CM3" s="3" t="s">
+      <c r="CM3" t="s">
         <v>131</v>
       </c>
-      <c r="CN3" s="3" t="s">
+      <c r="CN3" t="s">
         <v>131</v>
       </c>
-      <c r="CO3" s="3" t="s">
+      <c r="CO3" t="s">
         <v>134</v>
       </c>
-      <c r="CP3" s="3" t="s">
+      <c r="CP3" t="s">
         <v>134</v>
       </c>
-      <c r="CQ3" s="3" t="s">
+      <c r="CQ3" t="s">
         <v>134</v>
       </c>
-      <c r="CR3" s="3" t="s">
+      <c r="CR3" t="s">
         <v>394</v>
       </c>
-      <c r="CS3" s="3" t="s">
+      <c r="CS3" t="s">
         <v>134</v>
       </c>
-      <c r="CT3" s="3" t="s">
+      <c r="CT3" t="s">
         <v>125</v>
       </c>
-      <c r="CU3" s="3" t="s">
+      <c r="CU3" t="s">
         <v>135</v>
       </c>
-      <c r="CV3" s="3" t="s">
+      <c r="CV3" t="s">
         <v>398</v>
       </c>
-      <c r="CW3" s="3" t="s">
+      <c r="CW3" t="s">
         <v>399</v>
       </c>
-      <c r="CX3" s="3" t="s">
+      <c r="CX3" t="s">
         <v>399</v>
       </c>
-      <c r="CY3" s="3" t="s">
+      <c r="CY3" t="s">
         <v>398</v>
       </c>
-      <c r="CZ3" s="3" t="s">
+      <c r="CZ3" t="s">
         <v>398</v>
       </c>
-      <c r="DA3" s="3" t="s">
+      <c r="DA3" t="s">
         <v>398</v>
       </c>
-      <c r="DB3" s="3" t="s">
+      <c r="DB3" t="s">
         <v>398</v>
       </c>
-      <c r="DC3" s="3" t="s">
+      <c r="DC3" t="s">
         <v>398</v>
       </c>
-      <c r="DD3" s="3" t="s">
+      <c r="DD3" t="s">
         <v>125</v>
       </c>
-      <c r="DE3" s="3" t="s">
+      <c r="DE3" t="s">
         <v>125</v>
       </c>
-      <c r="DF3" s="3" t="s">
+      <c r="DF3" t="s">
         <v>125</v>
       </c>
-      <c r="DG3" s="3" t="s">
+      <c r="DG3" t="s">
         <v>125</v>
       </c>
-      <c r="DH3" s="3" t="s">
+      <c r="DH3" t="s">
         <v>125</v>
       </c>
-      <c r="DI3" s="3" t="s">
+      <c r="DI3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>401</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>402</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" t="s">
         <v>403</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" t="s">
         <v>404</v>
       </c>
-      <c r="S6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="3" t="s">
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
         <v>405</v>
       </c>
-      <c r="AT6" s="3" t="s">
+      <c r="AT6" t="s">
         <v>406</v>
       </c>
-      <c r="AY6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ6" s="3">
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
         <v>0.01</v>
       </c>
-      <c r="BB6" s="3">
+      <c r="BB6">
         <v>2</v>
       </c>
-      <c r="BD6" s="3">
-        <v>1</v>
-      </c>
-      <c r="BP6" s="3" t="s">
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="s">
         <v>407</v>
       </c>
-      <c r="CB6" s="3" t="s">
+      <c r="CB6" t="s">
         <v>62</v>
       </c>
-      <c r="CG6" s="3" t="s">
+      <c r="CG6" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>407</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>402</v>
       </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3" t="s">
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>409</v>
       </c>
-      <c r="AC7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="3" t="s">
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="s">
         <v>405</v>
       </c>
-      <c r="AT7" s="3" t="s">
+      <c r="AT7" t="s">
         <v>406</v>
       </c>
-      <c r="AY7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ7" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="3">
-        <v>1</v>
-      </c>
-      <c r="BP7" s="3" t="s">
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="BP7" t="s">
         <v>410</v>
       </c>
-      <c r="CH7" s="3" t="s">
+      <c r="CH7" t="s">
         <v>411</v>
       </c>
-      <c r="CI7" s="3" t="s">
+      <c r="CI7" t="s">
         <v>412</v>
       </c>
-      <c r="CN7" s="3" t="s">
+      <c r="CN7" t="s">
         <v>413</v>
       </c>
-      <c r="CO7" s="3">
+      <c r="CO7">
         <v>22</v>
       </c>
-      <c r="CR7" s="3">
+      <c r="CR7">
         <v>10</v>
       </c>
-      <c r="CY7" s="3" t="s">
+      <c r="CY7" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>415</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>416</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" t="s">
         <v>409</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" t="s">
         <v>417</v>
       </c>
-      <c r="AC8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="3" t="s">
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="s">
         <v>418</v>
       </c>
-      <c r="BD8" s="3">
-        <v>1</v>
-      </c>
-      <c r="CU8" s="3" t="s">
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="s">
         <v>419</v>
       </c>
-      <c r="DD8" s="3">
-        <v>1</v>
-      </c>
-      <c r="DG8" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+      <c r="DD8">
+        <v>1</v>
+      </c>
+      <c r="DG8">
+        <v>1</v>
+      </c>
+      <c r="DH8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>420</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>402</v>
       </c>
-      <c r="I9" s="3">
-        <v>1</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
         <v>409</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" t="s">
         <v>417</v>
       </c>
-      <c r="AC9" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="3" t="s">
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="s">
         <v>418</v>
       </c>
-      <c r="AT9" s="3" t="s">
+      <c r="AT9" t="s">
         <v>421</v>
       </c>
-      <c r="BD9" s="3">
-        <v>1</v>
-      </c>
-      <c r="BO9" s="3" t="s">
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="s">
         <v>422</v>
       </c>
-      <c r="CN9" s="3" t="s">
+      <c r="CN9" t="s">
         <v>423</v>
       </c>
-      <c r="CO9" s="3">
+      <c r="CO9">
         <v>8</v>
       </c>
-      <c r="CR9" s="3">
+      <c r="CR9">
         <v>9999</v>
       </c>
-      <c r="DD9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+      <c r="DD9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>422</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>402</v>
       </c>
-      <c r="I10" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT10" s="3" t="s">
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="s">
         <v>424</v>
       </c>
-      <c r="BD10" s="3">
+      <c r="BD10">
         <v>99</v>
       </c>
-      <c r="BS10" s="3">
+      <c r="BS10">
         <v>0.1</v>
       </c>
-      <c r="CN10" s="3" t="s">
+      <c r="CN10" t="s">
         <v>425</v>
       </c>
-      <c r="CO10" s="3">
+      <c r="CO10">
         <v>0.2</v>
       </c>
-      <c r="CR10" s="3">
+      <c r="CR10">
         <v>0.2</v>
       </c>
-      <c r="DD10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="DD10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>426</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>402</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" t="s">
         <v>409</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" t="s">
         <v>417</v>
       </c>
-      <c r="AC11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="3" t="s">
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="s">
         <v>418</v>
       </c>
-      <c r="BD11" s="3">
-        <v>1</v>
-      </c>
-      <c r="CN11" s="3" t="s">
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="CN11" t="s">
         <v>427</v>
       </c>
-      <c r="CR11" s="3">
+      <c r="CR11">
         <v>99999</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>428</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>402</v>
       </c>
-      <c r="I12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ12" s="3" t="s">
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="s">
         <v>5</v>
       </c>
-      <c r="AV12" s="3">
+      <c r="AV12">
         <v>20</v>
       </c>
-      <c r="BD12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS12" s="3">
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BS12">
         <v>0.1</v>
       </c>
-      <c r="CN12" s="3" t="s">
+      <c r="CN12" t="s">
         <v>429</v>
       </c>
-      <c r="CR12" s="3">
+      <c r="CR12">
         <v>0.2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>410</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>402</v>
       </c>
-      <c r="I13" s="3">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3" t="s">
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
         <v>409</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="P13" t="s">
         <v>430</v>
       </c>
-      <c r="AC13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="3" t="s">
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="s">
         <v>418</v>
       </c>
-      <c r="AT13" s="3" t="s">
+      <c r="AT13" t="s">
         <v>421</v>
       </c>
-      <c r="BD13" s="3">
-        <v>1</v>
-      </c>
-      <c r="CN13" s="3" t="s">
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="CN13" t="s">
         <v>413</v>
       </c>
-      <c r="CO13" s="3">
+      <c r="CO13">
         <v>22</v>
       </c>
-      <c r="CR13" s="3">
+      <c r="CR13">
         <v>10</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>431</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" t="s">
         <v>402</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" t="s">
         <v>432</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" t="s">
         <v>433</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" t="s">
         <v>434</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>3</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" t="s">
         <v>435</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="K17" t="s">
         <v>436</v>
       </c>
-      <c r="AC17" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="3" t="s">
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="s">
         <v>418</v>
       </c>
-      <c r="BD17" s="3">
-        <v>1</v>
-      </c>
-      <c r="BO17" s="3" t="s">
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BO17" t="s">
         <v>437</v>
       </c>
-      <c r="BP17" s="3" t="s">
+      <c r="BP17" t="s">
         <v>438</v>
       </c>
-      <c r="BT17" s="3">
+      <c r="BT17">
         <v>30</v>
       </c>
-      <c r="BV17" s="3">
+      <c r="BV17">
         <v>13</v>
       </c>
-      <c r="BW17" s="3">
+      <c r="BW17">
         <v>15</v>
       </c>
-      <c r="BX17" s="3">
-        <v>1</v>
-      </c>
-      <c r="BY17" s="3" t="s">
+      <c r="BX17">
+        <v>1</v>
+      </c>
+      <c r="BY17" t="s">
         <v>439</v>
       </c>
-      <c r="CN17" s="3" t="s">
+      <c r="CN17" t="s">
         <v>440</v>
       </c>
-      <c r="CR17" s="3">
+      <c r="CR17">
         <v>30</v>
       </c>
-      <c r="DD17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+      <c r="DD17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>441</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" t="s">
         <v>402</v>
       </c>
-      <c r="O18" s="3" t="s">
+      <c r="O18" t="s">
         <v>430</v>
       </c>
-      <c r="AC18" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO18" s="3" t="s">
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="s">
         <v>405</v>
       </c>
-      <c r="AQ18" s="3" t="s">
+      <c r="AQ18" t="s">
         <v>156</v>
       </c>
-      <c r="AW18" s="3">
-        <v>1</v>
-      </c>
-      <c r="AY18" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ18" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD18" s="3">
-        <v>1</v>
-      </c>
-      <c r="BP18" s="3" t="s">
+      <c r="AW18">
+        <v>1</v>
+      </c>
+      <c r="AY18">
+        <v>1</v>
+      </c>
+      <c r="AZ18">
+        <v>1</v>
+      </c>
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="s">
         <v>442</v>
       </c>
-      <c r="CB18" s="3" t="s">
+      <c r="CB18" t="s">
         <v>443</v>
       </c>
-      <c r="CG18" s="3" t="s">
+      <c r="CG18" t="s">
         <v>408</v>
       </c>
-      <c r="CH18" s="3" t="s">
+      <c r="CH18" t="s">
         <v>411</v>
       </c>
-      <c r="CI18" s="3" t="s">
+      <c r="CI18" t="s">
         <v>412</v>
       </c>
-      <c r="CN18" s="3" t="s">
+      <c r="CN18" t="s">
         <v>444</v>
       </c>
-      <c r="CO18" s="3">
+      <c r="CO18">
         <v>22</v>
       </c>
-      <c r="CP18" s="3">
+      <c r="CP18">
         <v>39.6</v>
       </c>
-      <c r="CR18" s="3">
+      <c r="CR18">
         <v>10</v>
       </c>
-      <c r="CY18" s="3" t="s">
+      <c r="CY18" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>445</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>402</v>
       </c>
-      <c r="I19" s="3">
-        <v>1</v>
-      </c>
-      <c r="K19" s="3" t="s">
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
         <v>409</v>
       </c>
-      <c r="AC19" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ19" s="3" t="s">
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="s">
         <v>156</v>
       </c>
-      <c r="AO19" s="3" t="s">
+      <c r="AO19" t="s">
         <v>405</v>
       </c>
-      <c r="AT19" s="3" t="s">
+      <c r="AT19" t="s">
         <v>406</v>
       </c>
-      <c r="AX19" s="3" t="s">
+      <c r="AX19" t="s">
         <v>446</v>
       </c>
-      <c r="AZ19" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB19" s="3">
+      <c r="AZ19">
+        <v>1</v>
+      </c>
+      <c r="BB19">
         <v>2</v>
       </c>
-      <c r="BD19" s="3">
-        <v>1</v>
-      </c>
-      <c r="CH19" s="3" t="s">
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="CH19" t="s">
         <v>447</v>
       </c>
-      <c r="CI19" s="3" t="s">
+      <c r="CI19" t="s">
         <v>412</v>
       </c>
-      <c r="CN19" s="3" t="s">
+      <c r="CN19" t="s">
         <v>448</v>
       </c>
-      <c r="CR19" s="3">
+      <c r="CR19">
         <v>0.1</v>
       </c>
-      <c r="DD19" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH19" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="DD19">
+        <v>1</v>
+      </c>
+      <c r="DH19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>449</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" t="s">
         <v>402</v>
       </c>
-      <c r="I20" s="3">
-        <v>1</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
         <v>409</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="O20" t="s">
         <v>430</v>
       </c>
-      <c r="AC20" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="3" t="s">
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="s">
         <v>418</v>
       </c>
-      <c r="AW20" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD20" s="3">
-        <v>1</v>
-      </c>
-      <c r="CN20" s="3" t="s">
+      <c r="AW20">
+        <v>1</v>
+      </c>
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="CN20" t="s">
         <v>444</v>
       </c>
-      <c r="CO20" s="3">
+      <c r="CO20">
         <v>22</v>
       </c>
-      <c r="CP20" s="3">
+      <c r="CP20">
         <v>39.6</v>
       </c>
-      <c r="CR20" s="3">
+      <c r="CR20">
         <v>10</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>448</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" t="s">
         <v>402</v>
       </c>
-      <c r="I21" s="3">
-        <v>1</v>
-      </c>
-      <c r="O21" s="3" t="s">
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
         <v>430</v>
       </c>
-      <c r="AC21" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="s">
         <v>156</v>
       </c>
-      <c r="AT21" s="3" t="s">
+      <c r="AT21" t="s">
         <v>406</v>
       </c>
-      <c r="BD21" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS21" s="3">
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="BS21">
         <v>0.1</v>
       </c>
-      <c r="CN21" s="3" t="s">
+      <c r="CN21" t="s">
         <v>448</v>
       </c>
-      <c r="CR21" s="3">
+      <c r="CR21">
         <v>0.2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>450</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" t="s">
         <v>402</v>
       </c>
-      <c r="I22" s="3">
-        <v>1</v>
-      </c>
-      <c r="K22" s="3" t="s">
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
         <v>409</v>
       </c>
-      <c r="AC22" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="3" t="s">
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="s">
         <v>418</v>
       </c>
-      <c r="BD22" s="3">
-        <v>1</v>
-      </c>
-      <c r="CN22" s="3" t="s">
+      <c r="BD22">
+        <v>1</v>
+      </c>
+      <c r="CN22" t="s">
         <v>450</v>
       </c>
-      <c r="CR22" s="3">
+      <c r="CR22">
         <v>40</v>
       </c>
-      <c r="DD22" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH22" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
+      <c r="DD22">
+        <v>1</v>
+      </c>
+      <c r="DH22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>451</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" t="s">
         <v>402</v>
       </c>
-      <c r="I23" s="3">
-        <v>1</v>
-      </c>
-      <c r="O23" s="3" t="s">
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
         <v>430</v>
       </c>
-      <c r="P23" s="3" t="s">
+      <c r="P23" t="s">
         <v>450</v>
       </c>
-      <c r="AC23" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV23" s="3">
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AV23">
         <v>20</v>
       </c>
-      <c r="BD23" s="3">
+      <c r="BD23">
         <v>99</v>
       </c>
-      <c r="CM23" s="3" t="s">
+      <c r="CM23" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>453</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" t="s">
         <v>402</v>
       </c>
-      <c r="I24" s="3">
-        <v>1</v>
-      </c>
-      <c r="K24" s="3" t="s">
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="s">
         <v>409</v>
       </c>
-      <c r="AC24" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="3" t="s">
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="s">
         <v>418</v>
       </c>
-      <c r="BD24" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS24" s="3">
+      <c r="BD24">
+        <v>1</v>
+      </c>
+      <c r="BS24">
         <v>0.1</v>
       </c>
-      <c r="CB24" s="3" t="s">
+      <c r="CB24" t="s">
         <v>454</v>
       </c>
-      <c r="CG24" s="3" t="s">
+      <c r="CG24" t="s">
         <v>408</v>
       </c>
-      <c r="DD24" s="3">
-        <v>1</v>
-      </c>
-      <c r="DG24" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH24" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
+      <c r="DD24">
+        <v>1</v>
+      </c>
+      <c r="DG24">
+        <v>1</v>
+      </c>
+      <c r="DH24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>455</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" t="s">
         <v>402</v>
       </c>
-      <c r="I25" s="3">
-        <v>1</v>
-      </c>
-      <c r="K25" s="3" t="s">
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
         <v>409</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="L25" t="s">
         <v>456</v>
       </c>
-      <c r="AC25" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="3" t="s">
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="s">
         <v>418</v>
       </c>
-      <c r="BD25" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS25" s="3">
+      <c r="BD25">
+        <v>1</v>
+      </c>
+      <c r="BS25">
         <v>0.2</v>
       </c>
-      <c r="CB25" s="3" t="s">
+      <c r="CB25" t="s">
         <v>457</v>
       </c>
-      <c r="CG25" s="3" t="s">
+      <c r="CG25" t="s">
         <v>408</v>
       </c>
-      <c r="DD25" s="3">
-        <v>1</v>
-      </c>
-      <c r="DG25" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH25" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
+      <c r="DD25">
+        <v>1</v>
+      </c>
+      <c r="DG25">
+        <v>1</v>
+      </c>
+      <c r="DH25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>458</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" t="s">
         <v>402</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" t="s">
         <v>432</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" t="s">
         <v>433</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" t="s">
         <v>434</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>3</v>
       </c>
-      <c r="I26" s="3">
-        <v>1</v>
-      </c>
-      <c r="O26" s="3" t="s">
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="s">
         <v>448</v>
       </c>
-      <c r="AC26" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="3" t="s">
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="s">
         <v>418</v>
       </c>
-      <c r="AO26" s="3" t="s">
+      <c r="AO26" t="s">
         <v>405</v>
       </c>
-      <c r="AT26" s="3" t="s">
+      <c r="AT26" t="s">
         <v>421</v>
       </c>
-      <c r="AY26" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ26" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD26" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS26" s="3">
+      <c r="AY26">
+        <v>1</v>
+      </c>
+      <c r="AZ26">
+        <v>1</v>
+      </c>
+      <c r="BD26">
+        <v>1</v>
+      </c>
+      <c r="BS26">
         <v>0.1</v>
       </c>
-      <c r="CG26" s="3" t="s">
+      <c r="CG26" t="s">
         <v>408</v>
       </c>
-      <c r="CH26" s="3" t="s">
+      <c r="CH26" t="s">
         <v>411</v>
       </c>
-      <c r="CI26" s="3" t="s">
+      <c r="CI26" t="s">
         <v>412</v>
       </c>
-      <c r="CN26" s="3" t="s">
+      <c r="CN26" t="s">
         <v>444</v>
       </c>
-      <c r="CO26" s="3">
+      <c r="CO26">
         <v>22</v>
       </c>
-      <c r="CP26" s="3">
+      <c r="CP26">
         <v>39.6</v>
       </c>
-      <c r="CR26" s="3">
+      <c r="CR26">
         <v>10</v>
       </c>
-      <c r="CY26" s="3" t="s">
+      <c r="CY26" t="s">
         <v>414</v>
       </c>
-      <c r="DD26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
+      <c r="DD26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>459</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" t="s">
         <v>402</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" t="s">
         <v>460</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" t="s">
         <v>461</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" t="s">
         <v>462</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28">
         <v>3</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" t="s">
         <v>435</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="K28" t="s">
         <v>436</v>
       </c>
-      <c r="O28" s="3" t="s">
+      <c r="O28" t="s">
         <v>429</v>
       </c>
-      <c r="AC28" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="3" t="s">
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="s">
         <v>418</v>
       </c>
-      <c r="BD28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BO28" s="3" t="s">
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="BO28" t="s">
         <v>463</v>
       </c>
-      <c r="BP28" s="3" t="s">
+      <c r="BP28" t="s">
         <v>464</v>
       </c>
-      <c r="BT28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BV28" s="3">
+      <c r="BT28">
+        <v>1</v>
+      </c>
+      <c r="BV28">
         <v>11</v>
       </c>
-      <c r="BW28" s="3">
+      <c r="BW28">
         <v>15</v>
       </c>
-      <c r="BX28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BY28" s="3" t="s">
+      <c r="BX28">
+        <v>1</v>
+      </c>
+      <c r="BY28" t="s">
         <v>439</v>
       </c>
-      <c r="CN28" s="3" t="s">
+      <c r="CN28" t="s">
         <v>465</v>
       </c>
-      <c r="CO28" s="3" t="s">
+      <c r="CO28" t="s">
         <v>466</v>
       </c>
-      <c r="CR28" s="3">
+      <c r="CR28">
         <v>25</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>463</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" t="s">
         <v>402</v>
       </c>
-      <c r="I29" s="3">
-        <v>1</v>
-      </c>
-      <c r="O29" s="3" t="s">
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="O29" t="s">
         <v>404</v>
       </c>
-      <c r="AC29" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="s">
         <v>418</v>
       </c>
-      <c r="AT29" s="3" t="s">
+      <c r="AT29" t="s">
         <v>421</v>
       </c>
-      <c r="BD29" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS29" s="3">
+      <c r="BD29">
+        <v>1</v>
+      </c>
+      <c r="BS29">
         <v>0.1</v>
       </c>
-      <c r="CN29" s="3" t="s">
+      <c r="CN29" t="s">
         <v>467</v>
       </c>
-      <c r="CR29" s="3">
+      <c r="CR29">
         <v>0.2</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>468</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" t="s">
         <v>469</v>
       </c>
-      <c r="I30" s="3">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3" t="s">
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
         <v>470</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="K30" t="s">
         <v>409</v>
       </c>
-      <c r="AC30" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ30" s="3" t="s">
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="s">
         <v>156</v>
       </c>
-      <c r="AT30" s="3" t="s">
+      <c r="AT30" t="s">
         <v>406</v>
       </c>
-      <c r="BD30" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS30" s="3">
+      <c r="BD30">
+        <v>1</v>
+      </c>
+      <c r="BS30">
         <v>0.1</v>
       </c>
-      <c r="CU30" s="3" t="s">
+      <c r="CU30" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>472</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" t="s">
         <v>402</v>
       </c>
-      <c r="I31" s="3">
-        <v>1</v>
-      </c>
-      <c r="K31" s="3" t="s">
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
         <v>409</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="L31" t="s">
         <v>456</v>
       </c>
-      <c r="AC31" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="3" t="s">
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="s">
         <v>418</v>
       </c>
-      <c r="BD31" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS31" s="3">
-        <v>1</v>
-      </c>
-      <c r="CB31" s="3" t="s">
+      <c r="BD31">
+        <v>1</v>
+      </c>
+      <c r="BS31">
+        <v>1</v>
+      </c>
+      <c r="CB31" t="s">
         <v>473</v>
       </c>
-      <c r="CG31" s="3" t="s">
+      <c r="CG31" t="s">
         <v>408</v>
       </c>
-      <c r="DD31" s="3">
-        <v>1</v>
-      </c>
-      <c r="DG31" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH31" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
+      <c r="DD31">
+        <v>1</v>
+      </c>
+      <c r="DG31">
+        <v>1</v>
+      </c>
+      <c r="DH31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>474</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" t="s">
         <v>402</v>
       </c>
-      <c r="I32" s="3">
-        <v>1</v>
-      </c>
-      <c r="K32" s="3" t="s">
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
         <v>409</v>
       </c>
-      <c r="AC32" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="3" t="s">
+      <c r="AC32">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="s">
         <v>418</v>
       </c>
-      <c r="BD32" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS32" s="3">
-        <v>0.6667</v>
-      </c>
-      <c r="CB32" s="3" t="s">
+      <c r="BD32">
+        <v>1</v>
+      </c>
+      <c r="BS32">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="CB32" t="s">
         <v>475</v>
       </c>
-      <c r="CG32" s="3" t="s">
+      <c r="CG32" t="s">
         <v>408</v>
       </c>
-      <c r="DD32" s="3">
-        <v>1</v>
-      </c>
-      <c r="DG32" s="3">
-        <v>1</v>
-      </c>
-      <c r="DH32" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
+      <c r="DD32">
+        <v>1</v>
+      </c>
+      <c r="DG32">
+        <v>1</v>
+      </c>
+      <c r="DH32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>168</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" t="s">
         <v>402</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" t="s">
         <v>460</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" t="s">
         <v>461</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" t="s">
         <v>462</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34">
         <v>3</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" t="s">
         <v>435</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="K34" t="s">
         <v>403</v>
       </c>
-      <c r="AC34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="3" t="s">
+      <c r="AC34">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="s">
         <v>418</v>
       </c>
-      <c r="BD34" s="3">
-        <v>1</v>
-      </c>
-      <c r="BO34" s="3" t="s">
+      <c r="BD34">
+        <v>1</v>
+      </c>
+      <c r="BO34" t="s">
         <v>476</v>
       </c>
-      <c r="BT34" s="3">
+      <c r="BT34">
         <v>25</v>
       </c>
-      <c r="BV34" s="3">
-        <v>1</v>
-      </c>
-      <c r="BW34" s="3">
-        <v>1</v>
-      </c>
-      <c r="BX34" s="3">
-        <v>1</v>
-      </c>
-      <c r="BY34" s="3" t="s">
+      <c r="BV34">
+        <v>1</v>
+      </c>
+      <c r="BW34">
+        <v>1</v>
+      </c>
+      <c r="BX34">
+        <v>1</v>
+      </c>
+      <c r="BY34" t="s">
         <v>439</v>
       </c>
-      <c r="CN34" s="3" t="s">
+      <c r="CN34" t="s">
         <v>477</v>
       </c>
-      <c r="CO34" s="3" t="s">
+      <c r="CO34" t="s">
         <v>478</v>
       </c>
-      <c r="CP34" s="3">
+      <c r="CP34">
         <v>80</v>
       </c>
-      <c r="CR34" s="3">
+      <c r="CR34">
         <v>25</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>479</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" t="s">
         <v>480</v>
       </c>
-      <c r="O35" s="3" t="s">
+      <c r="O35" t="s">
         <v>465</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AC35">
         <v>2</v>
       </c>
-      <c r="AO35" s="3" t="s">
+      <c r="AO35" t="s">
         <v>481</v>
       </c>
-      <c r="AT35" s="3" t="s">
+      <c r="AT35" t="s">
         <v>424</v>
       </c>
-      <c r="AX35" s="3" t="s">
+      <c r="AX35" t="s">
         <v>446</v>
       </c>
-      <c r="AZ35" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD35" s="3">
-        <v>1</v>
-      </c>
-      <c r="BP35" s="3" t="s">
+      <c r="AZ35">
+        <v>1</v>
+      </c>
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="s">
         <v>482</v>
       </c>
-      <c r="CB35" s="3" t="s">
+      <c r="CB35" t="s">
         <v>483</v>
       </c>
-      <c r="CG35" s="3" t="s">
+      <c r="CG35" t="s">
         <v>408</v>
       </c>
-      <c r="CX35" s="3" t="s">
+      <c r="CX35" t="s">
         <v>484</v>
       </c>
-      <c r="CY35" s="3" t="s">
+      <c r="CY35" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>482</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" t="s">
         <v>402</v>
       </c>
-      <c r="I36" s="3">
-        <v>1</v>
-      </c>
-      <c r="K36" s="3" t="s">
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
         <v>409</v>
       </c>
-      <c r="O36" s="3" t="s">
+      <c r="O36" t="s">
         <v>465</v>
       </c>
-      <c r="AC36" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG36" s="3" t="s">
+      <c r="AC36">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="s">
         <v>418</v>
       </c>
-      <c r="AH36" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO36" s="3" t="s">
+      <c r="AH36">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="s">
         <v>405</v>
       </c>
-      <c r="AV36" s="3">
-        <v>1</v>
-      </c>
-      <c r="AY36" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ36" s="3">
+      <c r="AV36">
+        <v>1</v>
+      </c>
+      <c r="AY36">
+        <v>1</v>
+      </c>
+      <c r="AZ36">
         <v>0.5</v>
       </c>
-      <c r="BD36" s="3">
-        <v>1</v>
-      </c>
-      <c r="CH36" s="3" t="s">
+      <c r="BD36">
+        <v>1</v>
+      </c>
+      <c r="CH36" t="s">
         <v>411</v>
       </c>
-      <c r="CI36" s="3" t="s">
+      <c r="CI36" t="s">
         <v>412</v>
       </c>
-      <c r="CN36" s="3" t="s">
+      <c r="CN36" t="s">
         <v>413</v>
       </c>
-      <c r="CO36" s="3">
+      <c r="CO36">
         <v>22</v>
       </c>
-      <c r="CR36" s="3">
+      <c r="CR36">
         <v>10</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>486</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" t="s">
         <v>487</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="K37" t="s">
         <v>409</v>
       </c>
-      <c r="L37" s="3" t="s">
+      <c r="L37" t="s">
         <v>417</v>
       </c>
-      <c r="AC37" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG37" s="3" t="s">
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="s">
         <v>418</v>
       </c>
-      <c r="BD37" s="3">
-        <v>1</v>
-      </c>
-      <c r="CU37" s="3" t="s">
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>489</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" t="s">
         <v>402</v>
       </c>
-      <c r="I38" s="3">
-        <v>1</v>
-      </c>
-      <c r="K38" s="3" t="s">
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="K38" t="s">
         <v>409</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="L38" t="s">
         <v>417</v>
       </c>
-      <c r="AC38" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="3" t="s">
+      <c r="AC38">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="s">
         <v>418</v>
       </c>
-      <c r="BD38" s="3">
-        <v>1</v>
-      </c>
-      <c r="CN38" s="3" t="s">
+      <c r="BD38">
+        <v>1</v>
+      </c>
+      <c r="CN38" t="s">
         <v>467</v>
       </c>
-      <c r="CR38" s="3">
+      <c r="CR38">
         <v>0.5</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>490</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" t="s">
         <v>402</v>
       </c>
-      <c r="I39" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ39" s="3" t="s">
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="AC39">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="s">
         <v>5</v>
       </c>
-      <c r="AV39" s="3">
+      <c r="AV39">
         <v>20</v>
       </c>
-      <c r="BD39" s="3">
-        <v>1</v>
-      </c>
-      <c r="BS39" s="3">
+      <c r="BD39">
+        <v>1</v>
+      </c>
+      <c r="BS39">
         <v>0.1</v>
       </c>
-      <c r="CN39" s="3" t="s">
+      <c r="CN39" t="s">
         <v>404</v>
       </c>
-      <c r="CR39" s="3">
+      <c r="CR39">
         <v>0.5</v>
       </c>
     </row>
-    <row r="657">
-      <c r="CL657" s="3">
+    <row r="657" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL657">
         <v>0.15</v>
       </c>
     </row>
-    <row r="659">
-      <c r="CL659" s="3">
+    <row r="659" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL659">
         <v>0.2</v>
       </c>
     </row>
-    <row r="660">
-      <c r="CL660" s="3">
+    <row r="660" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL660">
         <v>0.1</v>
       </c>
     </row>
-    <row r="662">
-      <c r="CL662" s="3">
+    <row r="662" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL662">
         <v>0.2</v>
       </c>
     </row>
-    <row r="669">
-      <c r="CL669" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="CL671" s="3">
+    <row r="669" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL669">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL671">
         <v>0.4</v>
       </c>
     </row>
-    <row r="672">
-      <c r="CL672" s="3">
+    <row r="672" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL672">
         <v>0.6</v>
       </c>
     </row>
-    <row r="675">
-      <c r="CL675" s="3">
+    <row r="675" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL675">
         <v>0.5</v>
       </c>
     </row>
-    <row r="676">
-      <c r="CL676" s="3">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="CL677" s="3">
+    <row r="676" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL676">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="677" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL677">
         <v>0.2</v>
       </c>
     </row>
@@ -6224,7 +5987,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6234,441 +5996,441 @@
   <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="3"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
-    <col min="3" max="6" width="9" customWidth="1" style="3"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
-    <col min="8" max="8" width="15" customWidth="1" style="3"/>
-    <col min="9" max="13" width="9" customWidth="1" style="3"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
-    <col min="16" max="16" width="19.1640625" customWidth="1" style="3"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="3" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="19.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>491</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>492</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>493</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>494</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>495</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>496</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>497</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>498</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>499</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>500</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>502</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>503</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>504</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>505</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>506</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>507</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>508</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>58</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" t="s">
         <v>509</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" t="s">
         <v>510</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" t="s">
         <v>511</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" t="s">
         <v>512</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>128</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>125</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>125</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>398</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>126</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" t="s">
         <v>362</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" t="s">
         <v>362</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" t="s">
         <v>125</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>413</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>513</v>
       </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>514</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>423</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>516</v>
       </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>517</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>413</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>513</v>
       </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>514</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="Q6" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>423</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>516</v>
       </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
         <v>517</v>
       </c>
-      <c r="Q7" s="3" t="s">
+      <c r="Q7" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>425</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>513</v>
       </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="3" t="s">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>520</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>521</v>
       </c>
-      <c r="H9" s="3">
-        <v>1</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="3" t="s">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>523</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>521</v>
       </c>
-      <c r="H10" s="3">
-        <v>1</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="3" t="s">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>430</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>525</v>
       </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>452</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>513</v>
       </c>
-      <c r="H12" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="3" t="s">
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>450</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>525</v>
       </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>448</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>525</v>
       </c>
-      <c r="H14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>526</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" t="s">
         <v>248</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="Q15" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>465</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" t="s">
         <v>513</v>
       </c>
-      <c r="H16" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="3" t="s">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>529</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" t="s">
         <v>516</v>
       </c>
-      <c r="H17" s="3">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3" t="s">
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
         <v>517</v>
       </c>
-      <c r="Q17" s="3" t="s">
+      <c r="Q17" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>530</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" t="s">
         <v>525</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>532</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>525</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>534</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" t="s">
         <v>525</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>536</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" t="s">
         <v>525</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>404</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" t="s">
         <v>525</v>
       </c>
-      <c r="H22" s="3">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>539</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" t="s">
         <v>248</v>
       </c>
-      <c r="Q23" s="3" t="s">
+      <c r="Q23" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>429</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" t="s">
         <v>525</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24">
         <v>1</v>
       </c>
     </row>
@@ -6676,7 +6438,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6685,45 +6446,45 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
-    <col min="3" max="3" width="9" customWidth="1" style="3"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>542</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>135</v>
       </c>
     </row>
@@ -6731,7 +6492,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6740,79 +6500,79 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
-    <col min="2" max="2" width="9" customWidth="1" style="3"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
-    <col min="5" max="10" width="9" customWidth="1" style="3"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="I1" s="3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>543</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>544</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>545</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>546</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>357</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>126</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>128</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>397</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>135</v>
       </c>
     </row>
@@ -6820,7 +6580,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6829,219 +6588,219 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
-    <col min="2" max="2" width="28" customWidth="1" style="3"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
-    <col min="12" max="12" width="9" customWidth="1" style="3"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>547</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>548</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>549</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>550</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>551</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>552</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>553</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>554</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>555</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>557</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>558</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>559</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>560</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>561</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>562</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>563</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>564</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>565</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>544</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>128</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>126</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>531</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>566</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>567</v>
       </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>533</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>566</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>568</v>
       </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>535</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>569</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
         <v>570</v>
       </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>537</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>569</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" t="s">
         <v>571</v>
       </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>484</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>572</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8">
         <v>2</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8">
         <v>60</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8">
         <v>1</v>
       </c>
     </row>
@@ -7049,7 +6808,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -7059,49 +6817,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
-    <col min="7" max="9" width="9" customWidth="1" style="3"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>278</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>573</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>574</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>575</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>306</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>576</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1">
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7136,7 +6894,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7145,108 +6902,107 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1" style="3"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1" style="3"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1" style="3"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1" style="3"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1" style="3"/>
-    <col min="6" max="6" width="39.5" customWidth="1" style="3"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1" style="3"/>
-    <col min="8" max="8" width="32.25" customWidth="1" style="3"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1" style="3"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1"/>
+    <col min="6" max="6" width="39.5" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1"/>
+    <col min="8" max="8" width="32.25" customWidth="1"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>578</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>579</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>580</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>581</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>582</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>583</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>584</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>586</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>587</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>588</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>589</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>590</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>591</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>592</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
